--- a/2025_2026/Playoffs/Brackets.xlsx
+++ b/2025_2026/Playoffs/Brackets.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\NHLStats\Templates\Playoffs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\NHLStats\2025_2026\Playoffs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9671C46C-9EE8-4F83-8D98-49A640B312EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6FF1BC5-F5DA-4A55-A482-D5C4A29150D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="45">
   <si>
     <t>Eastern Conference Playoff Teams</t>
   </si>
@@ -73,24 +73,6 @@
     <t>1st Round</t>
   </si>
   <si>
-    <t>1 vs 8</t>
-  </si>
-  <si>
-    <t>2 vs 7</t>
-  </si>
-  <si>
-    <t>3 vs 6</t>
-  </si>
-  <si>
-    <t>4 vs 5</t>
-  </si>
-  <si>
-    <t>1 vs 8 Winner vs 3 vs 6 Winner</t>
-  </si>
-  <si>
-    <t>2 vs 7 Winner vs 4 vs 5 Winner</t>
-  </si>
-  <si>
     <t>2nd Round</t>
   </si>
   <si>
@@ -106,31 +88,79 @@
     <t>Conference Winners</t>
   </si>
   <si>
-    <t>1st Place vs 8th Place</t>
-  </si>
-  <si>
-    <t>3rd Place vs 6th Place</t>
-  </si>
-  <si>
-    <t>4th Place vs 5th Place</t>
-  </si>
-  <si>
-    <t>2nd Place vs 7th Place</t>
-  </si>
-  <si>
     <t>Round 2</t>
   </si>
   <si>
-    <t>1st/8th Place Winner vs 3rd/6th Place Winner</t>
-  </si>
-  <si>
-    <t>2nd/7th Place Winner vs 4th/5th Place Winner</t>
-  </si>
-  <si>
     <t>NHL Finals</t>
   </si>
   <si>
     <t>Date</t>
+  </si>
+  <si>
+    <t>Anaheim Ducks</t>
+  </si>
+  <si>
+    <t>Boston Bruins</t>
+  </si>
+  <si>
+    <t>Buffalo Sabres</t>
+  </si>
+  <si>
+    <t>Carolina Hurricanes</t>
+  </si>
+  <si>
+    <t>Colorado Avalanche</t>
+  </si>
+  <si>
+    <t>Dallas Stars</t>
+  </si>
+  <si>
+    <t>Edmonton Oilers</t>
+  </si>
+  <si>
+    <t>Los Angeles Kings</t>
+  </si>
+  <si>
+    <t>Minnesota Wild</t>
+  </si>
+  <si>
+    <t>Montreal Canadiens</t>
+  </si>
+  <si>
+    <t>Ottawa Senators</t>
+  </si>
+  <si>
+    <t>Philadelphia Flyers</t>
+  </si>
+  <si>
+    <t>Pittsburgh Penguins</t>
+  </si>
+  <si>
+    <t>Tampa Bay Lightning</t>
+  </si>
+  <si>
+    <t>Utah Mammoth</t>
+  </si>
+  <si>
+    <t>Vegas Golden Knights</t>
+  </si>
+  <si>
+    <t>1 vs 4</t>
+  </si>
+  <si>
+    <t>2 vs 3</t>
+  </si>
+  <si>
+    <t>1 vs 4 Winner vs 2 vs 3 Winner</t>
+  </si>
+  <si>
+    <t>1st Place vs 4th Place</t>
+  </si>
+  <si>
+    <t>2nd Place vs 3rd Place</t>
+  </si>
+  <si>
+    <t>1st/4th Place Winner vs 2nd/3rd Place Winner</t>
   </si>
 </sst>
 </file>
@@ -384,7 +414,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -509,13 +539,43 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -537,34 +597,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -846,7 +879,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L55"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31.85546875" style="1" bestFit="1" customWidth="1"/>
@@ -867,22 +900,86 @@
         <v>1</v>
       </c>
     </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
     <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="11" spans="1:7" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="44" t="s">
+      <c r="A11" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="44"/>
-      <c r="C11" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="D11" s="44"/>
-      <c r="E11" s="44" t="s">
-        <v>22</v>
-      </c>
-      <c r="F11" s="44"/>
+      <c r="B11" s="42"/>
+      <c r="C11" s="42" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="42"/>
+      <c r="E11" s="42" t="s">
+        <v>16</v>
+      </c>
+      <c r="F11" s="42"/>
       <c r="G11" s="4" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -905,163 +1002,236 @@
         <v>5</v>
       </c>
       <c r="G12" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" s="44"/>
+      <c r="C13" s="43" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" s="44"/>
+      <c r="E13" s="43" t="s">
+        <v>17</v>
+      </c>
+      <c r="F13" s="44"/>
+      <c r="G13" s="5"/>
+    </row>
+    <row r="14" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="42" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" s="43"/>
-      <c r="C13" s="42" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" s="43"/>
-      <c r="E13" s="42" t="s">
-        <v>23</v>
-      </c>
-      <c r="F13" s="43"/>
-      <c r="G13" s="5"/>
-    </row>
-    <row r="14" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
+      <c r="B14" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
       <c r="G14" s="6"/>
     </row>
     <row r="15" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="6"/>
+      <c r="A15" s="6" t="s">
+        <v>24</v>
+      </c>
       <c r="B15" s="6"/>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
     </row>
     <row r="16" spans="1:7" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="42" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16" s="43"/>
-      <c r="C16" s="42" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" s="43"/>
+      <c r="A16" s="43" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="44"/>
+      <c r="C16" s="43" t="s">
+        <v>41</v>
+      </c>
+      <c r="D16" s="44"/>
     </row>
     <row r="17" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="5"/>
-      <c r="B17" s="5"/>
+      <c r="A17" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>28</v>
+      </c>
       <c r="D17" s="5"/>
     </row>
     <row r="18" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="6"/>
-      <c r="B18" s="6"/>
+      <c r="A18" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>31</v>
+      </c>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
     </row>
     <row r="19" spans="1:4" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="42" t="s">
-        <v>17</v>
-      </c>
-      <c r="B19" s="43"/>
+      <c r="A19" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="44"/>
     </row>
     <row r="20" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="5"/>
-      <c r="B20" s="5"/>
+      <c r="A20" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="21" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="6"/>
-      <c r="B21" s="6"/>
+      <c r="A21" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="22" spans="1:4" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="42" t="s">
-        <v>18</v>
-      </c>
-      <c r="B22" s="43"/>
+      <c r="A22" s="43" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" s="44"/>
     </row>
     <row r="23" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="5"/>
+      <c r="A23" s="5" t="s">
+        <v>35</v>
+      </c>
       <c r="B23" s="5"/>
     </row>
     <row r="24" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="6"/>
+      <c r="A24" s="6" t="s">
+        <v>34</v>
+      </c>
       <c r="B24" s="6"/>
     </row>
     <row r="25" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
-    <row r="39" spans="7:12" x14ac:dyDescent="0.25">
-      <c r="L39" s="2"/>
-    </row>
-    <row r="40" spans="7:12" x14ac:dyDescent="0.25">
-      <c r="L40" s="2"/>
-    </row>
-    <row r="41" spans="7:12" x14ac:dyDescent="0.25">
-      <c r="L41" s="2"/>
-    </row>
-    <row r="42" spans="7:12" x14ac:dyDescent="0.25">
-      <c r="L42" s="2"/>
-    </row>
-    <row r="43" spans="7:12" x14ac:dyDescent="0.25">
-      <c r="L43" s="2"/>
-    </row>
-    <row r="44" spans="7:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="7:10" x14ac:dyDescent="0.25">
+      <c r="J39" s="2"/>
+    </row>
+    <row r="40" spans="7:10" x14ac:dyDescent="0.25">
+      <c r="J40" s="2"/>
+    </row>
+    <row r="41" spans="7:10" x14ac:dyDescent="0.25">
+      <c r="J41" s="2"/>
+    </row>
+    <row r="42" spans="7:10" x14ac:dyDescent="0.25">
+      <c r="J42" s="2"/>
+    </row>
+    <row r="43" spans="7:10" x14ac:dyDescent="0.25">
+      <c r="J43" s="2"/>
+    </row>
+    <row r="44" spans="7:10" x14ac:dyDescent="0.25">
       <c r="H44" s="2"/>
-      <c r="L44" s="2"/>
-    </row>
-    <row r="45" spans="7:12" x14ac:dyDescent="0.25">
+      <c r="J44" s="2"/>
+    </row>
+    <row r="45" spans="7:10" x14ac:dyDescent="0.25">
       <c r="H45" s="2"/>
-      <c r="L45" s="2"/>
-    </row>
-    <row r="46" spans="7:12" x14ac:dyDescent="0.25">
+      <c r="J45" s="2"/>
+    </row>
+    <row r="46" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
-      <c r="L46" s="2"/>
-    </row>
-    <row r="48" spans="7:12" x14ac:dyDescent="0.25">
-      <c r="L48" s="2"/>
-    </row>
-    <row r="49" spans="7:12" x14ac:dyDescent="0.25">
+      <c r="J46" s="2"/>
+    </row>
+    <row r="48" spans="7:10" x14ac:dyDescent="0.25">
+      <c r="J48" s="2"/>
+    </row>
+    <row r="49" spans="7:10" x14ac:dyDescent="0.25">
       <c r="H49" s="2"/>
-      <c r="L49" s="2"/>
-    </row>
-    <row r="50" spans="7:12" x14ac:dyDescent="0.25">
-      <c r="L50" s="2"/>
-    </row>
-    <row r="51" spans="7:12" x14ac:dyDescent="0.25">
+      <c r="J49" s="2"/>
+    </row>
+    <row r="50" spans="7:10" x14ac:dyDescent="0.25">
+      <c r="J50" s="2"/>
+    </row>
+    <row r="51" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G51" s="2"/>
-      <c r="L51" s="2"/>
-    </row>
-    <row r="52" spans="7:12" x14ac:dyDescent="0.25">
+      <c r="J51" s="2"/>
+    </row>
+    <row r="52" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G52" s="2"/>
       <c r="H52" s="2"/>
-      <c r="L52" s="2"/>
-    </row>
-    <row r="53" spans="7:12" x14ac:dyDescent="0.25">
+      <c r="J52" s="2"/>
+    </row>
+    <row r="53" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G53" s="2"/>
-      <c r="L53" s="2"/>
-    </row>
-    <row r="54" spans="7:12" x14ac:dyDescent="0.25">
+      <c r="J53" s="2"/>
+    </row>
+    <row r="54" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G54" s="2"/>
       <c r="H54" s="2"/>
-      <c r="L54" s="2"/>
-    </row>
-    <row r="55" spans="7:12" x14ac:dyDescent="0.25">
+      <c r="J54" s="2"/>
+    </row>
+    <row r="55" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G55" s="2"/>
       <c r="H55" s="2"/>
-      <c r="L55" s="2"/>
+      <c r="J55" s="2"/>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:B9">
+    <sortCondition ref="B2:B9"/>
+  </sortState>
   <mergeCells count="10">
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C16:D16"/>
     <mergeCell ref="E11:F11"/>
     <mergeCell ref="E13:F13"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C16:D16"/>
   </mergeCells>
+  <dataValidations count="14">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C14" xr:uid="{2C3D9587-ABAE-4E3F-8B22-396DF812BF02}">
+      <formula1>$A$14:$A$15</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C15" xr:uid="{8DE4863B-2686-49D5-BB45-3752C66D5E22}">
+      <formula1>$A$17:$A$18</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C17" xr:uid="{E66A2425-1AA1-48D2-A4B6-97C32F158533}">
+      <formula1>$A$20:$A$21</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C18" xr:uid="{F6E22D2B-2B40-4D82-A2EE-A239255CF281}">
+      <formula1>$A$23:$A$24</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D14" xr:uid="{3DA081A4-EE0F-47F2-9F99-B108AE8ADB36}">
+      <formula1>$B$14:$B$15</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D15" xr:uid="{97E63494-3514-491F-9641-2A056B99F347}">
+      <formula1>$B$17:$B$18</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D17" xr:uid="{D2920E57-DEEF-43EF-8228-5DD487B71DF3}">
+      <formula1>$B$20:$B$21</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D18" xr:uid="{F14E9FAC-A521-44BE-83D2-B29CED4621B3}">
+      <formula1>$B$23:$B$24</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14" xr:uid="{3E16574B-23A8-447A-8B61-33431BFB0753}">
+      <formula1>$C$14:$C$15</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E15" xr:uid="{D83B2B57-B3C8-4CFA-B59F-7D889B597A68}">
+      <formula1>$C$17:$C$18</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14" xr:uid="{0DC2FF58-D0E2-4530-811E-B3740AFAB9C9}">
+      <formula1>$D$14:$D$15</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F15" xr:uid="{D0DD5C61-3357-4435-AF8C-D02F80F157FB}">
+      <formula1>$D$17:$D$18</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G13" xr:uid="{A73EC919-6CEE-4241-90E3-53B08BEC28A5}">
+      <formula1>$E$14:$E$15</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G14" xr:uid="{D05939E7-4959-4994-ACBD-7EC440AAA176}">
+      <formula1>$F$14:$F$15</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
@@ -1114,131 +1284,131 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:53" ht="27.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="54"/>
-      <c r="K1" s="54"/>
-      <c r="L1" s="54"/>
-      <c r="M1" s="54"/>
-      <c r="N1" s="54"/>
-      <c r="O1" s="54"/>
-      <c r="P1" s="54"/>
-      <c r="Q1" s="54"/>
-      <c r="R1" s="54"/>
-      <c r="S1" s="54"/>
-      <c r="T1" s="54"/>
-      <c r="U1" s="55"/>
-      <c r="Z1" s="53" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA1" s="54"/>
-      <c r="AB1" s="55"/>
-      <c r="AF1" s="53" t="s">
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="53"/>
+      <c r="M1" s="53"/>
+      <c r="N1" s="53"/>
+      <c r="O1" s="53"/>
+      <c r="P1" s="53"/>
+      <c r="Q1" s="53"/>
+      <c r="R1" s="53"/>
+      <c r="S1" s="53"/>
+      <c r="T1" s="53"/>
+      <c r="U1" s="54"/>
+      <c r="Z1" s="52" t="s">
+        <v>21</v>
+      </c>
+      <c r="AA1" s="53"/>
+      <c r="AB1" s="54"/>
+      <c r="AF1" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="AG1" s="54"/>
-      <c r="AH1" s="54"/>
-      <c r="AI1" s="54"/>
-      <c r="AJ1" s="54"/>
-      <c r="AK1" s="54"/>
-      <c r="AL1" s="54"/>
-      <c r="AM1" s="54"/>
-      <c r="AN1" s="54"/>
-      <c r="AO1" s="54"/>
-      <c r="AP1" s="54"/>
-      <c r="AQ1" s="54"/>
-      <c r="AR1" s="54"/>
-      <c r="AS1" s="54"/>
-      <c r="AT1" s="54"/>
-      <c r="AU1" s="54"/>
-      <c r="AV1" s="54"/>
-      <c r="AW1" s="54"/>
-      <c r="AX1" s="54"/>
-      <c r="AY1" s="54"/>
-      <c r="AZ1" s="54"/>
-      <c r="BA1" s="55"/>
+      <c r="AG1" s="53"/>
+      <c r="AH1" s="53"/>
+      <c r="AI1" s="53"/>
+      <c r="AJ1" s="53"/>
+      <c r="AK1" s="53"/>
+      <c r="AL1" s="53"/>
+      <c r="AM1" s="53"/>
+      <c r="AN1" s="53"/>
+      <c r="AO1" s="53"/>
+      <c r="AP1" s="53"/>
+      <c r="AQ1" s="53"/>
+      <c r="AR1" s="53"/>
+      <c r="AS1" s="53"/>
+      <c r="AT1" s="53"/>
+      <c r="AU1" s="53"/>
+      <c r="AV1" s="53"/>
+      <c r="AW1" s="53"/>
+      <c r="AX1" s="53"/>
+      <c r="AY1" s="53"/>
+      <c r="AZ1" s="53"/>
+      <c r="BA1" s="54"/>
     </row>
     <row r="2" spans="1:53" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="57" t="s">
+      <c r="A2" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="59"/>
-      <c r="M2" s="57" t="s">
-        <v>30</v>
-      </c>
-      <c r="N2" s="58"/>
-      <c r="O2" s="58"/>
-      <c r="P2" s="58"/>
-      <c r="Q2" s="58"/>
-      <c r="R2" s="59"/>
-      <c r="AI2" s="57" t="s">
-        <v>30</v>
-      </c>
-      <c r="AJ2" s="58"/>
-      <c r="AK2" s="58"/>
-      <c r="AL2" s="58"/>
-      <c r="AM2" s="58"/>
-      <c r="AN2" s="58"/>
-      <c r="AO2" s="59"/>
-      <c r="AU2" s="57" t="s">
+      <c r="B2" s="49"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="50"/>
+      <c r="M2" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="N2" s="49"/>
+      <c r="O2" s="49"/>
+      <c r="P2" s="49"/>
+      <c r="Q2" s="49"/>
+      <c r="R2" s="50"/>
+      <c r="AI2" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="AJ2" s="49"/>
+      <c r="AK2" s="49"/>
+      <c r="AL2" s="49"/>
+      <c r="AM2" s="49"/>
+      <c r="AN2" s="49"/>
+      <c r="AO2" s="50"/>
+      <c r="AU2" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="AV2" s="58"/>
-      <c r="AW2" s="58"/>
-      <c r="AX2" s="58"/>
-      <c r="AY2" s="58"/>
-      <c r="AZ2" s="58"/>
-      <c r="BA2" s="59"/>
+      <c r="AV2" s="49"/>
+      <c r="AW2" s="49"/>
+      <c r="AX2" s="49"/>
+      <c r="AY2" s="49"/>
+      <c r="AZ2" s="49"/>
+      <c r="BA2" s="50"/>
     </row>
     <row r="3" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3" s="51"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="AI3" s="51" t="s">
-        <v>31</v>
-      </c>
-      <c r="AJ3" s="51"/>
-      <c r="AK3" s="51"/>
-      <c r="AL3" s="51"/>
-      <c r="AM3" s="51"/>
-      <c r="AN3" s="51"/>
-      <c r="AO3" s="51"/>
-      <c r="AU3" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="AV3" s="51"/>
-      <c r="AW3" s="51"/>
-      <c r="AX3" s="51"/>
-      <c r="AY3" s="51"/>
-      <c r="AZ3" s="51"/>
-      <c r="BA3" s="51"/>
+      <c r="A3" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="45"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="45"/>
+      <c r="AI3" s="55" t="s">
+        <v>44</v>
+      </c>
+      <c r="AJ3" s="56"/>
+      <c r="AK3" s="56"/>
+      <c r="AL3" s="56"/>
+      <c r="AM3" s="56"/>
+      <c r="AN3" s="56"/>
+      <c r="AO3" s="57"/>
+      <c r="AU3" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="AV3" s="45"/>
+      <c r="AW3" s="45"/>
+      <c r="AX3" s="45"/>
+      <c r="AY3" s="45"/>
+      <c r="AZ3" s="45"/>
+      <c r="BA3" s="45"/>
     </row>
     <row r="4" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>3</v>
@@ -1255,20 +1425,20 @@
       <c r="G4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="N4" s="46"/>
-      <c r="O4" s="46"/>
-      <c r="P4" s="46"/>
-      <c r="Q4" s="46"/>
-      <c r="R4" s="46"/>
-      <c r="S4" s="47"/>
+      <c r="M4" s="55" t="s">
+        <v>44</v>
+      </c>
+      <c r="N4" s="56"/>
+      <c r="O4" s="56"/>
+      <c r="P4" s="56"/>
+      <c r="Q4" s="56"/>
+      <c r="R4" s="56"/>
+      <c r="S4" s="57"/>
       <c r="AI4" s="3" t="s">
         <v>2</v>
       </c>
       <c r="AJ4" s="3" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="AK4" s="3" t="s">
         <v>3</v>
@@ -1289,7 +1459,7 @@
         <v>2</v>
       </c>
       <c r="AV4" s="3" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="AW4" s="3" t="s">
         <v>3</v>
@@ -1312,16 +1482,20 @@
         <v>1</v>
       </c>
       <c r="B5" s="26"/>
-      <c r="C5" s="10"/>
+      <c r="C5" s="10" t="s">
+        <v>24</v>
+      </c>
       <c r="D5" s="11"/>
-      <c r="E5" s="10"/>
+      <c r="E5" s="10" t="s">
+        <v>25</v>
+      </c>
       <c r="F5" s="11"/>
       <c r="G5" s="5"/>
       <c r="M5" s="22" t="s">
         <v>2</v>
       </c>
       <c r="N5" s="22" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="O5" s="22" t="s">
         <v>3</v>
@@ -1362,9 +1536,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="27"/>
-      <c r="C6" s="12"/>
+      <c r="C6" s="12" t="s">
+        <v>24</v>
+      </c>
       <c r="D6" s="13"/>
-      <c r="E6" s="12"/>
+      <c r="E6" s="12" t="s">
+        <v>25</v>
+      </c>
       <c r="F6" s="13"/>
       <c r="G6" s="16"/>
       <c r="M6" s="7">
@@ -1400,9 +1578,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="27"/>
-      <c r="C7" s="12"/>
+      <c r="C7" s="12" t="s">
+        <v>25</v>
+      </c>
       <c r="D7" s="13"/>
-      <c r="E7" s="12"/>
+      <c r="E7" s="12" t="s">
+        <v>24</v>
+      </c>
       <c r="F7" s="13"/>
       <c r="G7" s="16"/>
       <c r="M7" s="8">
@@ -1438,14 +1620,18 @@
         <v>4</v>
       </c>
       <c r="B8" s="27"/>
-      <c r="C8" s="12"/>
+      <c r="C8" s="12" t="s">
+        <v>25</v>
+      </c>
       <c r="D8" s="13"/>
-      <c r="E8" s="12"/>
+      <c r="E8" s="12" t="s">
+        <v>24</v>
+      </c>
       <c r="F8" s="13"/>
       <c r="G8" s="16"/>
-      <c r="I8" s="52"/>
-      <c r="J8" s="52"/>
-      <c r="K8" s="52"/>
+      <c r="I8" s="46"/>
+      <c r="J8" s="46"/>
+      <c r="K8" s="46"/>
       <c r="M8" s="8">
         <v>3</v>
       </c>
@@ -1464,9 +1650,9 @@
       <c r="AM8" s="30"/>
       <c r="AN8" s="31"/>
       <c r="AO8" s="16"/>
-      <c r="AQ8" s="52"/>
-      <c r="AR8" s="52"/>
-      <c r="AS8" s="52"/>
+      <c r="AQ8" s="46"/>
+      <c r="AR8" s="46"/>
+      <c r="AS8" s="46"/>
       <c r="AU8" s="38">
         <v>4</v>
       </c>
@@ -1482,9 +1668,13 @@
         <v>11</v>
       </c>
       <c r="B9" s="27"/>
-      <c r="C9" s="12"/>
+      <c r="C9" s="12" t="s">
+        <v>24</v>
+      </c>
       <c r="D9" s="13"/>
-      <c r="E9" s="12"/>
+      <c r="E9" s="12" t="s">
+        <v>25</v>
+      </c>
       <c r="F9" s="13"/>
       <c r="G9" s="16"/>
       <c r="L9" s="12"/>
@@ -1524,9 +1714,13 @@
         <v>10</v>
       </c>
       <c r="B10" s="27"/>
-      <c r="C10" s="12"/>
+      <c r="C10" s="12" t="s">
+        <v>25</v>
+      </c>
       <c r="D10" s="13"/>
-      <c r="E10" s="12"/>
+      <c r="E10" s="12" t="s">
+        <v>24</v>
+      </c>
       <c r="F10" s="13"/>
       <c r="G10" s="16"/>
       <c r="L10" s="12"/>
@@ -1564,9 +1758,13 @@
         <v>12</v>
       </c>
       <c r="B11" s="28"/>
-      <c r="C11" s="14"/>
+      <c r="C11" s="14" t="s">
+        <v>24</v>
+      </c>
       <c r="D11" s="15"/>
-      <c r="E11" s="14"/>
+      <c r="E11" s="14" t="s">
+        <v>25</v>
+      </c>
       <c r="F11" s="15"/>
       <c r="G11" s="6"/>
       <c r="L11" s="12"/>
@@ -1600,15 +1798,15 @@
       <c r="BA11" s="6"/>
     </row>
     <row r="12" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="51" t="s">
+      <c r="A12" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="51"/>
-      <c r="C12" s="51"/>
-      <c r="D12" s="51"/>
-      <c r="E12" s="51"/>
-      <c r="F12" s="51"/>
-      <c r="G12" s="51"/>
+      <c r="B12" s="45"/>
+      <c r="C12" s="45"/>
+      <c r="D12" s="45"/>
+      <c r="E12" s="45"/>
+      <c r="F12" s="45"/>
+      <c r="G12" s="45"/>
       <c r="L12" s="12"/>
       <c r="M12" s="8" t="s">
         <v>12</v>
@@ -1619,72 +1817,72 @@
       <c r="Q12" s="12"/>
       <c r="R12" s="13"/>
       <c r="S12" s="16"/>
-      <c r="AI12" s="51" t="s">
+      <c r="AI12" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="AJ12" s="51"/>
-      <c r="AK12" s="51"/>
-      <c r="AL12" s="51"/>
-      <c r="AM12" s="51"/>
-      <c r="AN12" s="51"/>
-      <c r="AO12" s="51"/>
+      <c r="AJ12" s="45"/>
+      <c r="AK12" s="45"/>
+      <c r="AL12" s="45"/>
+      <c r="AM12" s="45"/>
+      <c r="AN12" s="45"/>
+      <c r="AO12" s="45"/>
       <c r="AQ12" s="12"/>
-      <c r="AU12" s="51" t="s">
+      <c r="AU12" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="AV12" s="51"/>
-      <c r="AW12" s="51"/>
-      <c r="AX12" s="51"/>
-      <c r="AY12" s="51"/>
-      <c r="AZ12" s="51"/>
-      <c r="BA12" s="51"/>
+      <c r="AV12" s="45"/>
+      <c r="AW12" s="45"/>
+      <c r="AX12" s="45"/>
+      <c r="AY12" s="45"/>
+      <c r="AZ12" s="45"/>
+      <c r="BA12" s="45"/>
     </row>
     <row r="13" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L13" s="12"/>
-      <c r="M13" s="45" t="s">
+      <c r="M13" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="N13" s="46"/>
-      <c r="O13" s="46"/>
-      <c r="P13" s="46"/>
-      <c r="Q13" s="46"/>
-      <c r="R13" s="46"/>
-      <c r="S13" s="47"/>
+      <c r="N13" s="56"/>
+      <c r="O13" s="56"/>
+      <c r="P13" s="56"/>
+      <c r="Q13" s="56"/>
+      <c r="R13" s="56"/>
+      <c r="S13" s="57"/>
       <c r="AQ13" s="12"/>
     </row>
     <row r="14" spans="1:53" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="51" t="s">
-        <v>27</v>
-      </c>
-      <c r="B14" s="51"/>
-      <c r="C14" s="51"/>
-      <c r="D14" s="51"/>
-      <c r="E14" s="51"/>
-      <c r="F14" s="51"/>
-      <c r="G14" s="51"/>
-      <c r="L14" s="56"/>
-      <c r="M14" s="52"/>
-      <c r="N14" s="52"/>
-      <c r="AN14" s="52"/>
-      <c r="AO14" s="52"/>
-      <c r="AP14" s="52"/>
+      <c r="A14" s="61" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="61"/>
+      <c r="C14" s="61"/>
+      <c r="D14" s="61"/>
+      <c r="E14" s="61"/>
+      <c r="F14" s="61"/>
+      <c r="G14" s="61"/>
+      <c r="L14" s="47"/>
+      <c r="M14" s="46"/>
+      <c r="N14" s="46"/>
+      <c r="AN14" s="46"/>
+      <c r="AO14" s="46"/>
+      <c r="AP14" s="46"/>
       <c r="AQ14" s="12"/>
-      <c r="AU14" s="51" t="s">
-        <v>27</v>
-      </c>
-      <c r="AV14" s="51"/>
-      <c r="AW14" s="51"/>
-      <c r="AX14" s="51"/>
-      <c r="AY14" s="51"/>
-      <c r="AZ14" s="51"/>
-      <c r="BA14" s="51"/>
+      <c r="AU14" s="61" t="s">
+        <v>43</v>
+      </c>
+      <c r="AV14" s="61"/>
+      <c r="AW14" s="61"/>
+      <c r="AX14" s="61"/>
+      <c r="AY14" s="61"/>
+      <c r="AZ14" s="61"/>
+      <c r="BA14" s="61"/>
     </row>
     <row r="15" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>3</v>
@@ -1709,7 +1907,7 @@
         <v>2</v>
       </c>
       <c r="AV15" s="3" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="AW15" s="3" t="s">
         <v>3</v>
@@ -1732,9 +1930,13 @@
         <v>1</v>
       </c>
       <c r="B16" s="26"/>
-      <c r="C16" s="10"/>
+      <c r="C16" s="10" t="s">
+        <v>32</v>
+      </c>
       <c r="D16" s="11"/>
-      <c r="E16" s="10"/>
+      <c r="E16" s="10" t="s">
+        <v>36</v>
+      </c>
       <c r="F16" s="11"/>
       <c r="G16" s="5"/>
       <c r="L16" s="12"/>
@@ -1756,9 +1958,13 @@
         <v>2</v>
       </c>
       <c r="B17" s="27"/>
-      <c r="C17" s="12"/>
+      <c r="C17" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="D17" s="13"/>
-      <c r="E17" s="12"/>
+      <c r="E17" s="12" t="s">
+        <v>36</v>
+      </c>
       <c r="F17" s="13"/>
       <c r="G17" s="16"/>
       <c r="L17" s="12"/>
@@ -1780,9 +1986,13 @@
         <v>3</v>
       </c>
       <c r="B18" s="27"/>
-      <c r="C18" s="12"/>
+      <c r="C18" s="12" t="s">
+        <v>36</v>
+      </c>
       <c r="D18" s="13"/>
-      <c r="E18" s="12"/>
+      <c r="E18" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="F18" s="13"/>
       <c r="G18" s="16"/>
       <c r="L18" s="12"/>
@@ -1804,20 +2014,24 @@
         <v>4</v>
       </c>
       <c r="B19" s="33"/>
-      <c r="C19" s="30"/>
+      <c r="C19" s="30" t="s">
+        <v>36</v>
+      </c>
       <c r="D19" s="31"/>
-      <c r="E19" s="30"/>
+      <c r="E19" s="30" t="s">
+        <v>32</v>
+      </c>
       <c r="F19" s="31"/>
       <c r="G19" s="32"/>
-      <c r="I19" s="52"/>
-      <c r="J19" s="52"/>
-      <c r="K19" s="52"/>
+      <c r="I19" s="46"/>
+      <c r="J19" s="46"/>
+      <c r="K19" s="46"/>
       <c r="L19" s="12"/>
       <c r="O19" s="12"/>
       <c r="AN19" s="12"/>
-      <c r="AQ19" s="56"/>
-      <c r="AR19" s="52"/>
-      <c r="AS19" s="52"/>
+      <c r="AQ19" s="47"/>
+      <c r="AR19" s="46"/>
+      <c r="AS19" s="46"/>
       <c r="AU19" s="38">
         <v>4</v>
       </c>
@@ -1833,9 +2047,13 @@
         <v>11</v>
       </c>
       <c r="B20" s="27"/>
-      <c r="C20" s="12"/>
+      <c r="C20" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="D20" s="13"/>
-      <c r="E20" s="12"/>
+      <c r="E20" s="12" t="s">
+        <v>36</v>
+      </c>
       <c r="F20" s="13"/>
       <c r="G20" s="16"/>
       <c r="O20" s="12"/>
@@ -1855,9 +2073,13 @@
         <v>10</v>
       </c>
       <c r="B21" s="27"/>
-      <c r="C21" s="12"/>
+      <c r="C21" s="12" t="s">
+        <v>36</v>
+      </c>
       <c r="D21" s="13"/>
-      <c r="E21" s="12"/>
+      <c r="E21" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="F21" s="13"/>
       <c r="G21" s="16"/>
       <c r="O21" s="12"/>
@@ -1877,9 +2099,13 @@
         <v>12</v>
       </c>
       <c r="B22" s="28"/>
-      <c r="C22" s="14"/>
+      <c r="C22" s="14" t="s">
+        <v>32</v>
+      </c>
       <c r="D22" s="15"/>
-      <c r="E22" s="14"/>
+      <c r="E22" s="14" t="s">
+        <v>36</v>
+      </c>
       <c r="F22" s="15"/>
       <c r="G22" s="6"/>
       <c r="O22" s="12"/>
@@ -1895,59 +2121,59 @@
       <c r="BA22" s="6"/>
     </row>
     <row r="23" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="51" t="s">
+      <c r="A23" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="B23" s="51"/>
-      <c r="C23" s="51"/>
-      <c r="D23" s="51"/>
-      <c r="E23" s="51"/>
-      <c r="F23" s="51"/>
-      <c r="G23" s="51"/>
+      <c r="B23" s="45"/>
+      <c r="C23" s="45"/>
+      <c r="D23" s="45"/>
+      <c r="E23" s="45"/>
+      <c r="F23" s="45"/>
+      <c r="G23" s="45"/>
       <c r="O23" s="12"/>
       <c r="AN23" s="12"/>
-      <c r="AU23" s="51" t="s">
+      <c r="AU23" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="AV23" s="51"/>
-      <c r="AW23" s="51"/>
-      <c r="AX23" s="51"/>
-      <c r="AY23" s="51"/>
-      <c r="AZ23" s="51"/>
-      <c r="BA23" s="51"/>
+      <c r="AV23" s="45"/>
+      <c r="AW23" s="45"/>
+      <c r="AX23" s="45"/>
+      <c r="AY23" s="45"/>
+      <c r="AZ23" s="45"/>
+      <c r="BA23" s="45"/>
     </row>
     <row r="24" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="O24" s="12"/>
       <c r="AN24" s="12"/>
     </row>
     <row r="25" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="51" t="s">
-        <v>28</v>
-      </c>
-      <c r="B25" s="51"/>
-      <c r="C25" s="51"/>
-      <c r="D25" s="51"/>
-      <c r="E25" s="51"/>
-      <c r="F25" s="51"/>
-      <c r="G25" s="51"/>
+      <c r="A25" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="B25" s="45"/>
+      <c r="C25" s="45"/>
+      <c r="D25" s="45"/>
+      <c r="E25" s="45"/>
+      <c r="F25" s="45"/>
+      <c r="G25" s="45"/>
       <c r="O25" s="12"/>
       <c r="AN25" s="12"/>
-      <c r="AU25" s="51" t="s">
-        <v>28</v>
-      </c>
-      <c r="AV25" s="51"/>
-      <c r="AW25" s="51"/>
-      <c r="AX25" s="51"/>
-      <c r="AY25" s="51"/>
-      <c r="AZ25" s="51"/>
-      <c r="BA25" s="51"/>
+      <c r="AU25" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="AV25" s="45"/>
+      <c r="AW25" s="45"/>
+      <c r="AX25" s="45"/>
+      <c r="AY25" s="45"/>
+      <c r="AZ25" s="45"/>
+      <c r="BA25" s="45"/>
     </row>
     <row r="26" spans="1:53" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="20" t="s">
         <v>2</v>
       </c>
       <c r="B26" s="21" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C26" s="20" t="s">
         <v>3</v>
@@ -1964,29 +2190,29 @@
       <c r="G26" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="O26" s="56"/>
-      <c r="P26" s="52"/>
-      <c r="Q26" s="52"/>
-      <c r="R26" s="52"/>
-      <c r="S26" s="52"/>
-      <c r="T26" s="52"/>
-      <c r="U26" s="52"/>
-      <c r="V26" s="52"/>
-      <c r="W26" s="52"/>
-      <c r="AE26" s="52"/>
-      <c r="AF26" s="52"/>
-      <c r="AG26" s="52"/>
-      <c r="AH26" s="52"/>
-      <c r="AI26" s="52"/>
-      <c r="AJ26" s="52"/>
-      <c r="AK26" s="52"/>
-      <c r="AL26" s="52"/>
-      <c r="AM26" s="60"/>
+      <c r="O26" s="47"/>
+      <c r="P26" s="46"/>
+      <c r="Q26" s="46"/>
+      <c r="R26" s="46"/>
+      <c r="S26" s="46"/>
+      <c r="T26" s="46"/>
+      <c r="U26" s="46"/>
+      <c r="V26" s="46"/>
+      <c r="W26" s="46"/>
+      <c r="AE26" s="46"/>
+      <c r="AF26" s="46"/>
+      <c r="AG26" s="46"/>
+      <c r="AH26" s="46"/>
+      <c r="AI26" s="46"/>
+      <c r="AJ26" s="46"/>
+      <c r="AK26" s="46"/>
+      <c r="AL26" s="46"/>
+      <c r="AM26" s="51"/>
       <c r="AU26" s="20" t="s">
         <v>2</v>
       </c>
       <c r="AV26" s="20" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="AW26" s="20" t="s">
         <v>3</v>
@@ -2009,9 +2235,13 @@
         <v>1</v>
       </c>
       <c r="B27" s="26"/>
-      <c r="C27" s="10"/>
+      <c r="C27" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="D27" s="11"/>
-      <c r="E27" s="10"/>
+      <c r="E27" s="10" t="s">
+        <v>26</v>
+      </c>
       <c r="F27" s="11"/>
       <c r="G27" s="5"/>
       <c r="O27" s="12"/>
@@ -2033,32 +2263,36 @@
         <v>2</v>
       </c>
       <c r="B28" s="27"/>
-      <c r="C28" s="12"/>
+      <c r="C28" s="12" t="s">
+        <v>33</v>
+      </c>
       <c r="D28" s="13"/>
-      <c r="E28" s="12"/>
+      <c r="E28" s="12" t="s">
+        <v>26</v>
+      </c>
       <c r="F28" s="13"/>
       <c r="G28" s="16"/>
       <c r="O28" s="12"/>
-      <c r="P28" s="45" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q28" s="46"/>
-      <c r="R28" s="46"/>
-      <c r="S28" s="46"/>
-      <c r="T28" s="46"/>
-      <c r="U28" s="46"/>
-      <c r="V28" s="47"/>
+      <c r="P28" s="55" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q28" s="56"/>
+      <c r="R28" s="56"/>
+      <c r="S28" s="56"/>
+      <c r="T28" s="56"/>
+      <c r="U28" s="56"/>
+      <c r="V28" s="57"/>
       <c r="X28" s="12"/>
       <c r="AD28" s="13"/>
-      <c r="AF28" s="51" t="s">
-        <v>22</v>
-      </c>
-      <c r="AG28" s="51"/>
-      <c r="AH28" s="51"/>
-      <c r="AI28" s="51"/>
-      <c r="AJ28" s="51"/>
-      <c r="AK28" s="51"/>
-      <c r="AL28" s="51"/>
+      <c r="AF28" s="45" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG28" s="45"/>
+      <c r="AH28" s="45"/>
+      <c r="AI28" s="45"/>
+      <c r="AJ28" s="45"/>
+      <c r="AK28" s="45"/>
+      <c r="AL28" s="45"/>
       <c r="AN28" s="12"/>
       <c r="AU28" s="8">
         <v>2</v>
@@ -2075,9 +2309,13 @@
         <v>3</v>
       </c>
       <c r="B29" s="27"/>
-      <c r="C29" s="12"/>
+      <c r="C29" s="12" t="s">
+        <v>26</v>
+      </c>
       <c r="D29" s="13"/>
-      <c r="E29" s="12"/>
+      <c r="E29" s="12" t="s">
+        <v>33</v>
+      </c>
       <c r="F29" s="13"/>
       <c r="G29" s="16"/>
       <c r="O29" s="12"/>
@@ -2085,7 +2323,7 @@
         <v>2</v>
       </c>
       <c r="Q29" s="22" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="R29" s="22" t="s">
         <v>3</v>
@@ -2108,7 +2346,7 @@
         <v>2</v>
       </c>
       <c r="AG29" s="3" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="AH29" s="3" t="s">
         <v>3</v>
@@ -2141,14 +2379,18 @@
         <v>4</v>
       </c>
       <c r="B30" s="33"/>
-      <c r="C30" s="30"/>
+      <c r="C30" s="30" t="s">
+        <v>26</v>
+      </c>
       <c r="D30" s="31"/>
-      <c r="E30" s="30"/>
+      <c r="E30" s="30" t="s">
+        <v>33</v>
+      </c>
       <c r="F30" s="31"/>
       <c r="G30" s="32"/>
-      <c r="I30" s="52"/>
-      <c r="J30" s="52"/>
-      <c r="K30" s="52"/>
+      <c r="I30" s="46"/>
+      <c r="J30" s="46"/>
+      <c r="K30" s="46"/>
       <c r="O30" s="12"/>
       <c r="P30" s="7">
         <v>1</v>
@@ -2171,9 +2413,9 @@
       <c r="AK30" s="24"/>
       <c r="AL30" s="25"/>
       <c r="AN30" s="12"/>
-      <c r="AQ30" s="52"/>
-      <c r="AR30" s="52"/>
-      <c r="AS30" s="52"/>
+      <c r="AQ30" s="46"/>
+      <c r="AR30" s="46"/>
+      <c r="AS30" s="46"/>
       <c r="AU30" s="38">
         <v>4</v>
       </c>
@@ -2189,9 +2431,13 @@
         <v>11</v>
       </c>
       <c r="B31" s="27"/>
-      <c r="C31" s="12"/>
+      <c r="C31" s="12" t="s">
+        <v>33</v>
+      </c>
       <c r="D31" s="13"/>
-      <c r="E31" s="12"/>
+      <c r="E31" s="12" t="s">
+        <v>26</v>
+      </c>
       <c r="F31" s="13"/>
       <c r="G31" s="32"/>
       <c r="L31" s="12"/>
@@ -2235,9 +2481,13 @@
         <v>10</v>
       </c>
       <c r="B32" s="27"/>
-      <c r="C32" s="12"/>
+      <c r="C32" s="12" t="s">
+        <v>26</v>
+      </c>
       <c r="D32" s="13"/>
-      <c r="E32" s="12"/>
+      <c r="E32" s="12" t="s">
+        <v>33</v>
+      </c>
       <c r="F32" s="13"/>
       <c r="G32" s="16"/>
       <c r="L32" s="12"/>
@@ -2279,9 +2529,13 @@
         <v>12</v>
       </c>
       <c r="B33" s="28"/>
-      <c r="C33" s="14"/>
+      <c r="C33" s="14" t="s">
+        <v>33</v>
+      </c>
       <c r="D33" s="15"/>
-      <c r="E33" s="14"/>
+      <c r="E33" s="14" t="s">
+        <v>26</v>
+      </c>
       <c r="F33" s="15"/>
       <c r="G33" s="6"/>
       <c r="L33" s="12"/>
@@ -2319,15 +2573,15 @@
       <c r="BA33" s="6"/>
     </row>
     <row r="34" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="51" t="s">
+      <c r="A34" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="B34" s="51"/>
-      <c r="C34" s="51"/>
-      <c r="D34" s="51"/>
-      <c r="E34" s="51"/>
-      <c r="F34" s="51"/>
-      <c r="G34" s="51"/>
+      <c r="B34" s="45"/>
+      <c r="C34" s="45"/>
+      <c r="D34" s="45"/>
+      <c r="E34" s="45"/>
+      <c r="F34" s="45"/>
+      <c r="G34" s="45"/>
       <c r="L34" s="12"/>
       <c r="O34" s="12"/>
       <c r="P34" s="8" t="s">
@@ -2352,15 +2606,15 @@
       <c r="AL34" s="16"/>
       <c r="AN34" s="12"/>
       <c r="AQ34" s="12"/>
-      <c r="AU34" s="51" t="s">
+      <c r="AU34" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="AV34" s="51"/>
-      <c r="AW34" s="51"/>
-      <c r="AX34" s="51"/>
-      <c r="AY34" s="51"/>
-      <c r="AZ34" s="51"/>
-      <c r="BA34" s="51"/>
+      <c r="AV34" s="45"/>
+      <c r="AW34" s="45"/>
+      <c r="AX34" s="45"/>
+      <c r="AY34" s="45"/>
+      <c r="AZ34" s="45"/>
+      <c r="BA34" s="45"/>
     </row>
     <row r="35" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L35" s="12"/>
@@ -2389,18 +2643,18 @@
       <c r="AQ35" s="12"/>
     </row>
     <row r="36" spans="1:53" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="51" t="s">
-        <v>29</v>
-      </c>
-      <c r="B36" s="51"/>
-      <c r="C36" s="51"/>
-      <c r="D36" s="51"/>
-      <c r="E36" s="51"/>
-      <c r="F36" s="51"/>
-      <c r="G36" s="51"/>
-      <c r="L36" s="56"/>
-      <c r="M36" s="52"/>
-      <c r="N36" s="52"/>
+      <c r="A36" s="61" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36" s="61"/>
+      <c r="C36" s="61"/>
+      <c r="D36" s="61"/>
+      <c r="E36" s="61"/>
+      <c r="F36" s="61"/>
+      <c r="G36" s="61"/>
+      <c r="L36" s="47"/>
+      <c r="M36" s="46"/>
+      <c r="N36" s="46"/>
       <c r="O36" s="12"/>
       <c r="P36" s="8" t="s">
         <v>12</v>
@@ -2422,26 +2676,26 @@
       <c r="AJ36" s="35"/>
       <c r="AK36" s="36"/>
       <c r="AL36" s="37"/>
-      <c r="AN36" s="56"/>
-      <c r="AO36" s="52"/>
-      <c r="AP36" s="52"/>
+      <c r="AN36" s="47"/>
+      <c r="AO36" s="46"/>
+      <c r="AP36" s="46"/>
       <c r="AQ36" s="12"/>
-      <c r="AU36" s="51" t="s">
-        <v>29</v>
-      </c>
-      <c r="AV36" s="51"/>
-      <c r="AW36" s="51"/>
-      <c r="AX36" s="51"/>
-      <c r="AY36" s="51"/>
-      <c r="AZ36" s="51"/>
-      <c r="BA36" s="51"/>
+      <c r="AU36" s="61" t="s">
+        <v>43</v>
+      </c>
+      <c r="AV36" s="61"/>
+      <c r="AW36" s="61"/>
+      <c r="AX36" s="61"/>
+      <c r="AY36" s="61"/>
+      <c r="AZ36" s="61"/>
+      <c r="BA36" s="61"/>
     </row>
     <row r="37" spans="1:53" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37" s="20" t="s">
         <v>2</v>
       </c>
       <c r="B37" s="21" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C37" s="20" t="s">
         <v>3</v>
@@ -2459,37 +2713,37 @@
         <v>9</v>
       </c>
       <c r="L37" s="12"/>
-      <c r="P37" s="48" t="s">
+      <c r="P37" s="58" t="s">
         <v>13</v>
       </c>
-      <c r="Q37" s="49"/>
-      <c r="R37" s="49"/>
-      <c r="S37" s="49"/>
-      <c r="T37" s="49"/>
-      <c r="U37" s="49"/>
-      <c r="V37" s="50"/>
-      <c r="X37" s="56"/>
-      <c r="Y37" s="52"/>
-      <c r="Z37" s="52"/>
-      <c r="AA37" s="52"/>
-      <c r="AB37" s="52"/>
-      <c r="AC37" s="52"/>
-      <c r="AD37" s="60"/>
-      <c r="AF37" s="51" t="s">
+      <c r="Q37" s="59"/>
+      <c r="R37" s="59"/>
+      <c r="S37" s="59"/>
+      <c r="T37" s="59"/>
+      <c r="U37" s="59"/>
+      <c r="V37" s="60"/>
+      <c r="X37" s="47"/>
+      <c r="Y37" s="46"/>
+      <c r="Z37" s="46"/>
+      <c r="AA37" s="46"/>
+      <c r="AB37" s="46"/>
+      <c r="AC37" s="46"/>
+      <c r="AD37" s="51"/>
+      <c r="AF37" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="AG37" s="51"/>
-      <c r="AH37" s="51"/>
-      <c r="AI37" s="51"/>
-      <c r="AJ37" s="51"/>
-      <c r="AK37" s="51"/>
-      <c r="AL37" s="51"/>
+      <c r="AG37" s="45"/>
+      <c r="AH37" s="45"/>
+      <c r="AI37" s="45"/>
+      <c r="AJ37" s="45"/>
+      <c r="AK37" s="45"/>
+      <c r="AL37" s="45"/>
       <c r="AQ37" s="12"/>
       <c r="AU37" s="3" t="s">
         <v>2</v>
       </c>
       <c r="AV37" s="3" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="AW37" s="3" t="s">
         <v>3</v>
@@ -2512,9 +2766,13 @@
         <v>1</v>
       </c>
       <c r="B38" s="26"/>
-      <c r="C38" s="10"/>
+      <c r="C38" s="10" t="s">
+        <v>34</v>
+      </c>
       <c r="D38" s="11"/>
-      <c r="E38" s="10"/>
+      <c r="E38" s="10" t="s">
+        <v>35</v>
+      </c>
       <c r="F38" s="11"/>
       <c r="G38" s="5"/>
       <c r="L38" s="12"/>
@@ -2534,39 +2792,43 @@
         <v>2</v>
       </c>
       <c r="B39" s="27"/>
-      <c r="C39" s="12"/>
+      <c r="C39" s="12" t="s">
+        <v>34</v>
+      </c>
       <c r="D39" s="13"/>
-      <c r="E39" s="12"/>
+      <c r="E39" s="12" t="s">
+        <v>35</v>
+      </c>
       <c r="F39" s="13"/>
       <c r="G39" s="16"/>
       <c r="L39" s="12"/>
-      <c r="M39" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="N39" s="46"/>
-      <c r="O39" s="46"/>
-      <c r="P39" s="46"/>
-      <c r="Q39" s="46"/>
-      <c r="R39" s="46"/>
-      <c r="S39" s="47"/>
-      <c r="X39" s="51" t="s">
-        <v>33</v>
-      </c>
-      <c r="Y39" s="51"/>
-      <c r="Z39" s="51"/>
-      <c r="AA39" s="51"/>
-      <c r="AB39" s="51"/>
-      <c r="AC39" s="51"/>
-      <c r="AD39" s="51"/>
-      <c r="AI39" s="51" t="s">
-        <v>32</v>
-      </c>
-      <c r="AJ39" s="51"/>
-      <c r="AK39" s="51"/>
-      <c r="AL39" s="51"/>
-      <c r="AM39" s="51"/>
-      <c r="AN39" s="51"/>
-      <c r="AO39" s="51"/>
+      <c r="M39" s="55" t="s">
+        <v>44</v>
+      </c>
+      <c r="N39" s="56"/>
+      <c r="O39" s="56"/>
+      <c r="P39" s="56"/>
+      <c r="Q39" s="56"/>
+      <c r="R39" s="56"/>
+      <c r="S39" s="57"/>
+      <c r="X39" s="45" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y39" s="45"/>
+      <c r="Z39" s="45"/>
+      <c r="AA39" s="45"/>
+      <c r="AB39" s="45"/>
+      <c r="AC39" s="45"/>
+      <c r="AD39" s="45"/>
+      <c r="AI39" s="55" t="s">
+        <v>44</v>
+      </c>
+      <c r="AJ39" s="56"/>
+      <c r="AK39" s="56"/>
+      <c r="AL39" s="56"/>
+      <c r="AM39" s="56"/>
+      <c r="AN39" s="56"/>
+      <c r="AO39" s="57"/>
       <c r="AQ39" s="12"/>
       <c r="AU39" s="8">
         <v>2</v>
@@ -2583,9 +2845,13 @@
         <v>3</v>
       </c>
       <c r="B40" s="27"/>
-      <c r="C40" s="12"/>
+      <c r="C40" s="12" t="s">
+        <v>35</v>
+      </c>
       <c r="D40" s="13"/>
-      <c r="E40" s="12"/>
+      <c r="E40" s="12" t="s">
+        <v>34</v>
+      </c>
       <c r="F40" s="13"/>
       <c r="G40" s="16"/>
       <c r="L40" s="12"/>
@@ -2593,7 +2859,7 @@
         <v>2</v>
       </c>
       <c r="N40" s="22" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="O40" s="22" t="s">
         <v>3</v>
@@ -2614,7 +2880,7 @@
         <v>2</v>
       </c>
       <c r="Y40" s="3" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="Z40" s="3" t="s">
         <v>3</v>
@@ -2635,7 +2901,7 @@
         <v>2</v>
       </c>
       <c r="AJ40" s="3" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="AK40" s="3" t="s">
         <v>3</v>
@@ -2668,14 +2934,18 @@
         <v>4</v>
       </c>
       <c r="B41" s="33"/>
-      <c r="C41" s="30"/>
+      <c r="C41" s="30" t="s">
+        <v>35</v>
+      </c>
       <c r="D41" s="31"/>
-      <c r="E41" s="30"/>
+      <c r="E41" s="30" t="s">
+        <v>34</v>
+      </c>
       <c r="F41" s="31"/>
       <c r="G41" s="32"/>
-      <c r="I41" s="52"/>
-      <c r="J41" s="52"/>
-      <c r="K41" s="52"/>
+      <c r="I41" s="46"/>
+      <c r="J41" s="46"/>
+      <c r="K41" s="46"/>
       <c r="L41" s="12"/>
       <c r="M41" s="7">
         <v>1</v>
@@ -2704,9 +2974,9 @@
       <c r="AM41" s="23"/>
       <c r="AN41" s="24"/>
       <c r="AO41" s="25"/>
-      <c r="AQ41" s="56"/>
-      <c r="AR41" s="52"/>
-      <c r="AS41" s="52"/>
+      <c r="AQ41" s="47"/>
+      <c r="AR41" s="46"/>
+      <c r="AS41" s="46"/>
       <c r="AU41" s="8">
         <v>4</v>
       </c>
@@ -2722,9 +2992,13 @@
         <v>11</v>
       </c>
       <c r="B42" s="27"/>
-      <c r="C42" s="12"/>
+      <c r="C42" s="12" t="s">
+        <v>35</v>
+      </c>
       <c r="D42" s="13"/>
-      <c r="E42" s="12"/>
+      <c r="E42" s="12" t="s">
+        <v>35</v>
+      </c>
       <c r="F42" s="13"/>
       <c r="G42" s="16"/>
       <c r="M42" s="8">
@@ -2769,9 +3043,13 @@
         <v>10</v>
       </c>
       <c r="B43" s="27"/>
-      <c r="C43" s="12"/>
+      <c r="C43" s="12" t="s">
+        <v>34</v>
+      </c>
       <c r="D43" s="13"/>
-      <c r="E43" s="12"/>
+      <c r="E43" s="12" t="s">
+        <v>34</v>
+      </c>
       <c r="F43" s="13"/>
       <c r="G43" s="16"/>
       <c r="M43" s="8">
@@ -2816,9 +3094,13 @@
         <v>12</v>
       </c>
       <c r="B44" s="28"/>
-      <c r="C44" s="14"/>
+      <c r="C44" s="14" t="s">
+        <v>35</v>
+      </c>
       <c r="D44" s="15"/>
-      <c r="E44" s="14"/>
+      <c r="E44" s="14" t="s">
+        <v>35</v>
+      </c>
       <c r="F44" s="15"/>
       <c r="G44" s="6"/>
       <c r="M44" s="8">
@@ -2859,15 +3141,15 @@
       <c r="BA44" s="6"/>
     </row>
     <row r="45" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="51" t="s">
+      <c r="A45" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="B45" s="51"/>
-      <c r="C45" s="51"/>
-      <c r="D45" s="51"/>
-      <c r="E45" s="51"/>
-      <c r="F45" s="51"/>
-      <c r="G45" s="51"/>
+      <c r="B45" s="45"/>
+      <c r="C45" s="45"/>
+      <c r="D45" s="45"/>
+      <c r="E45" s="45"/>
+      <c r="F45" s="45"/>
+      <c r="G45" s="45"/>
       <c r="M45" s="8" t="s">
         <v>11</v>
       </c>
@@ -2895,15 +3177,15 @@
       <c r="AM45" s="12"/>
       <c r="AN45" s="13"/>
       <c r="AO45" s="16"/>
-      <c r="AU45" s="51" t="s">
+      <c r="AU45" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="AV45" s="51"/>
-      <c r="AW45" s="51"/>
-      <c r="AX45" s="51"/>
-      <c r="AY45" s="51"/>
-      <c r="AZ45" s="51"/>
-      <c r="BA45" s="51"/>
+      <c r="AV45" s="45"/>
+      <c r="AW45" s="45"/>
+      <c r="AX45" s="45"/>
+      <c r="AY45" s="45"/>
+      <c r="AZ45" s="45"/>
+      <c r="BA45" s="45"/>
     </row>
     <row r="46" spans="1:53" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="M46" s="8" t="s">
@@ -2964,49 +3246,61 @@
       <c r="AO47" s="6"/>
     </row>
     <row r="48" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="M48" s="45" t="s">
+      <c r="M48" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="N48" s="46"/>
-      <c r="O48" s="46"/>
-      <c r="P48" s="46"/>
-      <c r="Q48" s="46"/>
-      <c r="R48" s="46"/>
-      <c r="S48" s="47"/>
-      <c r="X48" s="51" t="s">
+      <c r="N48" s="56"/>
+      <c r="O48" s="56"/>
+      <c r="P48" s="56"/>
+      <c r="Q48" s="56"/>
+      <c r="R48" s="56"/>
+      <c r="S48" s="57"/>
+      <c r="X48" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="Y48" s="51"/>
-      <c r="Z48" s="51"/>
-      <c r="AA48" s="51"/>
-      <c r="AB48" s="51"/>
-      <c r="AC48" s="51"/>
-      <c r="AD48" s="51"/>
-      <c r="AI48" s="51" t="s">
+      <c r="Y48" s="45"/>
+      <c r="Z48" s="45"/>
+      <c r="AA48" s="45"/>
+      <c r="AB48" s="45"/>
+      <c r="AC48" s="45"/>
+      <c r="AD48" s="45"/>
+      <c r="AI48" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="AJ48" s="51"/>
-      <c r="AK48" s="51"/>
-      <c r="AL48" s="51"/>
-      <c r="AM48" s="51"/>
-      <c r="AN48" s="51"/>
-      <c r="AO48" s="51"/>
+      <c r="AJ48" s="45"/>
+      <c r="AK48" s="45"/>
+      <c r="AL48" s="45"/>
+      <c r="AM48" s="45"/>
+      <c r="AN48" s="45"/>
+      <c r="AO48" s="45"/>
     </row>
     <row r="49" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="AU45:BA45"/>
-    <mergeCell ref="AF28:AL28"/>
-    <mergeCell ref="AF37:AL37"/>
-    <mergeCell ref="AQ30:AS30"/>
-    <mergeCell ref="AQ41:AS41"/>
-    <mergeCell ref="AU34:BA34"/>
-    <mergeCell ref="AU36:BA36"/>
-    <mergeCell ref="AU2:BA2"/>
-    <mergeCell ref="AU3:BA3"/>
-    <mergeCell ref="AU12:BA12"/>
-    <mergeCell ref="AU14:BA14"/>
-    <mergeCell ref="AU23:BA23"/>
+    <mergeCell ref="M48:S48"/>
+    <mergeCell ref="M39:S39"/>
+    <mergeCell ref="P37:V37"/>
+    <mergeCell ref="P28:V28"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A1:U1"/>
+    <mergeCell ref="O26:W26"/>
+    <mergeCell ref="I41:K41"/>
+    <mergeCell ref="L14:N14"/>
+    <mergeCell ref="L36:N36"/>
+    <mergeCell ref="M2:R2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="M4:S4"/>
+    <mergeCell ref="M13:S13"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="A25:G25"/>
     <mergeCell ref="X37:AD37"/>
     <mergeCell ref="AE26:AM26"/>
     <mergeCell ref="Z1:AB1"/>
@@ -3023,30 +3317,18 @@
     <mergeCell ref="AN36:AP36"/>
     <mergeCell ref="AQ8:AS8"/>
     <mergeCell ref="AQ19:AS19"/>
-    <mergeCell ref="A1:U1"/>
-    <mergeCell ref="O26:W26"/>
-    <mergeCell ref="I41:K41"/>
-    <mergeCell ref="L14:N14"/>
-    <mergeCell ref="L36:N36"/>
-    <mergeCell ref="M2:R2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="M4:S4"/>
-    <mergeCell ref="M13:S13"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A23:G23"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="M48:S48"/>
-    <mergeCell ref="M39:S39"/>
-    <mergeCell ref="P37:V37"/>
-    <mergeCell ref="P28:V28"/>
-    <mergeCell ref="A36:G36"/>
-    <mergeCell ref="A45:G45"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="AU2:BA2"/>
+    <mergeCell ref="AU3:BA3"/>
+    <mergeCell ref="AU12:BA12"/>
+    <mergeCell ref="AU14:BA14"/>
+    <mergeCell ref="AU23:BA23"/>
+    <mergeCell ref="AU45:BA45"/>
+    <mergeCell ref="AF28:AL28"/>
+    <mergeCell ref="AF37:AL37"/>
+    <mergeCell ref="AQ30:AS30"/>
+    <mergeCell ref="AQ41:AS41"/>
+    <mergeCell ref="AU34:BA34"/>
+    <mergeCell ref="AU36:BA36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3063,25 +3345,25 @@
           <x14:formula1>
             <xm:f>Matchups!$A$20:$A$21</xm:f>
           </x14:formula1>
-          <xm:sqref>C16:C22 E16:E22 I19:K19</xm:sqref>
+          <xm:sqref>E27:E33 C27:C33 I30:K30</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000002000000}">
           <x14:formula1>
             <xm:f>Matchups!$A$23:$A$24</xm:f>
           </x14:formula1>
-          <xm:sqref>C27:C33 E27:E33 I30:K30</xm:sqref>
+          <xm:sqref>E38:E44 C38:C44 I41:K41</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000003000000}">
           <x14:formula1>
             <xm:f>Matchups!$A$17:$A$18</xm:f>
           </x14:formula1>
-          <xm:sqref>C38:C44 E38:E44 I41:K41</xm:sqref>
+          <xm:sqref>C16:C22 E16:E22 I19:K19</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000004000000}">
           <x14:formula1>
             <xm:f>Matchups!$C$14:$C$15</xm:f>
           </x14:formula1>
-          <xm:sqref>L14:N14 Q6:Q12 O6:O12</xm:sqref>
+          <xm:sqref>O6:O12 Q6:Q12 L14:N14</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000005000000}">
           <x14:formula1>
@@ -3117,19 +3399,19 @@
           <x14:formula1>
             <xm:f>Matchups!$B$20:$B$21</xm:f>
           </x14:formula1>
-          <xm:sqref>AW16:AW22 AY16:AY22 AQ19:AS19</xm:sqref>
+          <xm:sqref>AY27:AY33 AW27:AW33 AQ30:AS30</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-00000B000000}">
           <x14:formula1>
             <xm:f>Matchups!$B$23:$B$24</xm:f>
           </x14:formula1>
-          <xm:sqref>AW27:AW33 AY27:AY33 AQ30:AS30</xm:sqref>
+          <xm:sqref>AY38:AY44 AW38:AW44 AQ41:AS41</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-00000C000000}">
           <x14:formula1>
             <xm:f>Matchups!$B$17:$B$18</xm:f>
           </x14:formula1>
-          <xm:sqref>AW38:AW44 AY38:AY44 AQ41:AS41</xm:sqref>
+          <xm:sqref>AW16:AW22 AY16:AY22 AQ19:AS19</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-00000D000000}">
           <x14:formula1>

--- a/2025_2026/Playoffs/Brackets.xlsx
+++ b/2025_2026/Playoffs/Brackets.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\NHLStats\2025_2026\Playoffs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6FF1BC5-F5DA-4A55-A482-D5C4A29150D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2DA6820-BF0F-4B43-92FC-BC6905DFA134}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Matchups" sheetId="3" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="45">
   <si>
     <t>Eastern Conference Playoff Teams</t>
   </si>
@@ -539,43 +539,13 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -598,6 +568,36 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -966,18 +966,18 @@
     </row>
     <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="11" spans="1:7" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="42" t="s">
+      <c r="A11" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="42"/>
-      <c r="C11" s="42" t="s">
+      <c r="B11" s="44"/>
+      <c r="C11" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="42"/>
-      <c r="E11" s="42" t="s">
+      <c r="D11" s="44"/>
+      <c r="E11" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="42"/>
+      <c r="F11" s="44"/>
       <c r="G11" s="4" t="s">
         <v>18</v>
       </c>
@@ -1006,18 +1006,18 @@
       </c>
     </row>
     <row r="13" spans="1:7" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="43" t="s">
+      <c r="A13" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="44"/>
-      <c r="C13" s="43" t="s">
+      <c r="B13" s="43"/>
+      <c r="C13" s="42" t="s">
         <v>41</v>
       </c>
-      <c r="D13" s="44"/>
-      <c r="E13" s="43" t="s">
+      <c r="D13" s="43"/>
+      <c r="E13" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="F13" s="44"/>
+      <c r="F13" s="43"/>
       <c r="G13" s="5"/>
     </row>
     <row r="14" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1036,20 +1036,22 @@
       <c r="A15" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="6"/>
+      <c r="B15" s="6" t="s">
+        <v>30</v>
+      </c>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
     </row>
     <row r="16" spans="1:7" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="43" t="s">
+      <c r="A16" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="44"/>
-      <c r="C16" s="43" t="s">
+      <c r="B16" s="43"/>
+      <c r="C16" s="42" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="44"/>
+      <c r="D16" s="43"/>
     </row>
     <row r="17" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
@@ -1071,10 +1073,10 @@
       <c r="D18" s="6"/>
     </row>
     <row r="19" spans="1:4" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="43" t="s">
+      <c r="A19" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="44"/>
+      <c r="B19" s="43"/>
     </row>
     <row r="20" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
@@ -1093,22 +1095,26 @@
       </c>
     </row>
     <row r="22" spans="1:4" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="43" t="s">
+      <c r="A22" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="44"/>
+      <c r="B22" s="43"/>
     </row>
     <row r="23" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B23" s="5"/>
+      <c r="B23" s="5" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="24" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B24" s="6"/>
+      <c r="B24" s="6" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="25" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="39" spans="7:10" x14ac:dyDescent="0.25">
@@ -1177,18 +1183,18 @@
     <sortCondition ref="B2:B9"/>
   </sortState>
   <mergeCells count="10">
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A16:B16"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A16:B16"/>
   </mergeCells>
-  <dataValidations count="14">
+  <dataValidations count="16">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C14" xr:uid="{2C3D9587-ABAE-4E3F-8B22-396DF812BF02}">
       <formula1>$A$14:$A$15</formula1>
     </dataValidation>
@@ -1230,6 +1236,12 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G14" xr:uid="{D05939E7-4959-4994-ACBD-7EC440AAA176}">
       <formula1>$F$14:$F$15</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A14:A15 A17:A18 A20:A21 A23:A24" xr:uid="{BC55B300-FFE7-46B9-802A-95DAE25DB57E}">
+      <formula1>$A$2:$A$9</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B14:B15 B17:B18 B20:B21 B23:B24" xr:uid="{6D825B7D-CB04-442D-BD56-F0A1A7E73239}">
+      <formula1>$B$2:$B$9</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1284,124 +1296,124 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:53" ht="27.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
-      <c r="G1" s="53"/>
-      <c r="H1" s="53"/>
-      <c r="I1" s="53"/>
-      <c r="J1" s="53"/>
-      <c r="K1" s="53"/>
-      <c r="L1" s="53"/>
-      <c r="M1" s="53"/>
-      <c r="N1" s="53"/>
-      <c r="O1" s="53"/>
-      <c r="P1" s="53"/>
-      <c r="Q1" s="53"/>
-      <c r="R1" s="53"/>
-      <c r="S1" s="53"/>
-      <c r="T1" s="53"/>
-      <c r="U1" s="54"/>
-      <c r="Z1" s="52" t="s">
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
+      <c r="J1" s="55"/>
+      <c r="K1" s="55"/>
+      <c r="L1" s="55"/>
+      <c r="M1" s="55"/>
+      <c r="N1" s="55"/>
+      <c r="O1" s="55"/>
+      <c r="P1" s="55"/>
+      <c r="Q1" s="55"/>
+      <c r="R1" s="55"/>
+      <c r="S1" s="55"/>
+      <c r="T1" s="55"/>
+      <c r="U1" s="56"/>
+      <c r="Z1" s="54" t="s">
         <v>21</v>
       </c>
-      <c r="AA1" s="53"/>
-      <c r="AB1" s="54"/>
-      <c r="AF1" s="52" t="s">
+      <c r="AA1" s="55"/>
+      <c r="AB1" s="56"/>
+      <c r="AF1" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="AG1" s="53"/>
-      <c r="AH1" s="53"/>
-      <c r="AI1" s="53"/>
-      <c r="AJ1" s="53"/>
-      <c r="AK1" s="53"/>
-      <c r="AL1" s="53"/>
-      <c r="AM1" s="53"/>
-      <c r="AN1" s="53"/>
-      <c r="AO1" s="53"/>
-      <c r="AP1" s="53"/>
-      <c r="AQ1" s="53"/>
-      <c r="AR1" s="53"/>
-      <c r="AS1" s="53"/>
-      <c r="AT1" s="53"/>
-      <c r="AU1" s="53"/>
-      <c r="AV1" s="53"/>
-      <c r="AW1" s="53"/>
-      <c r="AX1" s="53"/>
-      <c r="AY1" s="53"/>
-      <c r="AZ1" s="53"/>
-      <c r="BA1" s="54"/>
+      <c r="AG1" s="55"/>
+      <c r="AH1" s="55"/>
+      <c r="AI1" s="55"/>
+      <c r="AJ1" s="55"/>
+      <c r="AK1" s="55"/>
+      <c r="AL1" s="55"/>
+      <c r="AM1" s="55"/>
+      <c r="AN1" s="55"/>
+      <c r="AO1" s="55"/>
+      <c r="AP1" s="55"/>
+      <c r="AQ1" s="55"/>
+      <c r="AR1" s="55"/>
+      <c r="AS1" s="55"/>
+      <c r="AT1" s="55"/>
+      <c r="AU1" s="55"/>
+      <c r="AV1" s="55"/>
+      <c r="AW1" s="55"/>
+      <c r="AX1" s="55"/>
+      <c r="AY1" s="55"/>
+      <c r="AZ1" s="55"/>
+      <c r="BA1" s="56"/>
     </row>
     <row r="2" spans="1:53" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="48" t="s">
+      <c r="A2" s="58" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="49"/>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="50"/>
-      <c r="M2" s="48" t="s">
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="60"/>
+      <c r="M2" s="58" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="49"/>
-      <c r="O2" s="49"/>
-      <c r="P2" s="49"/>
-      <c r="Q2" s="49"/>
-      <c r="R2" s="50"/>
-      <c r="AI2" s="48" t="s">
+      <c r="N2" s="59"/>
+      <c r="O2" s="59"/>
+      <c r="P2" s="59"/>
+      <c r="Q2" s="59"/>
+      <c r="R2" s="60"/>
+      <c r="AI2" s="58" t="s">
         <v>20</v>
       </c>
-      <c r="AJ2" s="49"/>
-      <c r="AK2" s="49"/>
-      <c r="AL2" s="49"/>
-      <c r="AM2" s="49"/>
-      <c r="AN2" s="49"/>
-      <c r="AO2" s="50"/>
-      <c r="AU2" s="48" t="s">
+      <c r="AJ2" s="59"/>
+      <c r="AK2" s="59"/>
+      <c r="AL2" s="59"/>
+      <c r="AM2" s="59"/>
+      <c r="AN2" s="59"/>
+      <c r="AO2" s="60"/>
+      <c r="AU2" s="58" t="s">
         <v>6</v>
       </c>
-      <c r="AV2" s="49"/>
-      <c r="AW2" s="49"/>
-      <c r="AX2" s="49"/>
-      <c r="AY2" s="49"/>
-      <c r="AZ2" s="49"/>
-      <c r="BA2" s="50"/>
+      <c r="AV2" s="59"/>
+      <c r="AW2" s="59"/>
+      <c r="AX2" s="59"/>
+      <c r="AY2" s="59"/>
+      <c r="AZ2" s="59"/>
+      <c r="BA2" s="60"/>
     </row>
     <row r="3" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="45" t="s">
+      <c r="A3" s="52" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="45"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="45"/>
-      <c r="AI3" s="55" t="s">
+      <c r="B3" s="52"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="52"/>
+      <c r="AI3" s="45" t="s">
         <v>44</v>
       </c>
-      <c r="AJ3" s="56"/>
-      <c r="AK3" s="56"/>
-      <c r="AL3" s="56"/>
-      <c r="AM3" s="56"/>
-      <c r="AN3" s="56"/>
-      <c r="AO3" s="57"/>
-      <c r="AU3" s="45" t="s">
+      <c r="AJ3" s="46"/>
+      <c r="AK3" s="46"/>
+      <c r="AL3" s="46"/>
+      <c r="AM3" s="46"/>
+      <c r="AN3" s="46"/>
+      <c r="AO3" s="47"/>
+      <c r="AU3" s="52" t="s">
         <v>42</v>
       </c>
-      <c r="AV3" s="45"/>
-      <c r="AW3" s="45"/>
-      <c r="AX3" s="45"/>
-      <c r="AY3" s="45"/>
-      <c r="AZ3" s="45"/>
-      <c r="BA3" s="45"/>
+      <c r="AV3" s="52"/>
+      <c r="AW3" s="52"/>
+      <c r="AX3" s="52"/>
+      <c r="AY3" s="52"/>
+      <c r="AZ3" s="52"/>
+      <c r="BA3" s="52"/>
     </row>
     <row r="4" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
@@ -1425,15 +1437,15 @@
       <c r="G4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="55" t="s">
+      <c r="M4" s="45" t="s">
         <v>44</v>
       </c>
-      <c r="N4" s="56"/>
-      <c r="O4" s="56"/>
-      <c r="P4" s="56"/>
-      <c r="Q4" s="56"/>
-      <c r="R4" s="56"/>
-      <c r="S4" s="57"/>
+      <c r="N4" s="46"/>
+      <c r="O4" s="46"/>
+      <c r="P4" s="46"/>
+      <c r="Q4" s="46"/>
+      <c r="R4" s="46"/>
+      <c r="S4" s="47"/>
       <c r="AI4" s="3" t="s">
         <v>2</v>
       </c>
@@ -1481,7 +1493,9 @@
       <c r="A5" s="7">
         <v>1</v>
       </c>
-      <c r="B5" s="26"/>
+      <c r="B5" s="26">
+        <v>46131</v>
+      </c>
       <c r="C5" s="10" t="s">
         <v>24</v>
       </c>
@@ -1524,10 +1538,16 @@
       <c r="AU5" s="7">
         <v>1</v>
       </c>
-      <c r="AV5" s="26"/>
-      <c r="AW5" s="10"/>
+      <c r="AV5" s="26">
+        <v>46131</v>
+      </c>
+      <c r="AW5" s="10" t="s">
+        <v>30</v>
+      </c>
       <c r="AX5" s="11"/>
-      <c r="AY5" s="10"/>
+      <c r="AY5" s="10" t="s">
+        <v>27</v>
+      </c>
       <c r="AZ5" s="11"/>
       <c r="BA5" s="5"/>
     </row>
@@ -1535,7 +1555,9 @@
       <c r="A6" s="8">
         <v>2</v>
       </c>
-      <c r="B6" s="27"/>
+      <c r="B6" s="27">
+        <v>46133</v>
+      </c>
       <c r="C6" s="12" t="s">
         <v>24</v>
       </c>
@@ -1566,10 +1588,16 @@
       <c r="AU6" s="8">
         <v>2</v>
       </c>
-      <c r="AV6" s="27"/>
-      <c r="AW6" s="12"/>
+      <c r="AV6" s="27">
+        <v>46133</v>
+      </c>
+      <c r="AW6" s="12" t="s">
+        <v>30</v>
+      </c>
       <c r="AX6" s="13"/>
-      <c r="AY6" s="12"/>
+      <c r="AY6" s="12" t="s">
+        <v>27</v>
+      </c>
       <c r="AZ6" s="13"/>
       <c r="BA6" s="16"/>
     </row>
@@ -1577,7 +1605,9 @@
       <c r="A7" s="8">
         <v>3</v>
       </c>
-      <c r="B7" s="27"/>
+      <c r="B7" s="27">
+        <v>46135</v>
+      </c>
       <c r="C7" s="12" t="s">
         <v>25</v>
       </c>
@@ -1608,10 +1638,16 @@
       <c r="AU7" s="8">
         <v>3</v>
       </c>
-      <c r="AV7" s="27"/>
-      <c r="AW7" s="12"/>
+      <c r="AV7" s="27">
+        <v>46135</v>
+      </c>
+      <c r="AW7" s="12" t="s">
+        <v>27</v>
+      </c>
       <c r="AX7" s="13"/>
-      <c r="AY7" s="12"/>
+      <c r="AY7" s="12" t="s">
+        <v>30</v>
+      </c>
       <c r="AZ7" s="13"/>
       <c r="BA7" s="16"/>
     </row>
@@ -1619,7 +1655,9 @@
       <c r="A8" s="8">
         <v>4</v>
       </c>
-      <c r="B8" s="27"/>
+      <c r="B8" s="27">
+        <v>46138</v>
+      </c>
       <c r="C8" s="12" t="s">
         <v>25</v>
       </c>
@@ -1629,9 +1667,9 @@
       </c>
       <c r="F8" s="13"/>
       <c r="G8" s="16"/>
-      <c r="I8" s="46"/>
-      <c r="J8" s="46"/>
-      <c r="K8" s="46"/>
+      <c r="I8" s="53"/>
+      <c r="J8" s="53"/>
+      <c r="K8" s="53"/>
       <c r="M8" s="8">
         <v>3</v>
       </c>
@@ -1650,16 +1688,22 @@
       <c r="AM8" s="30"/>
       <c r="AN8" s="31"/>
       <c r="AO8" s="16"/>
-      <c r="AQ8" s="46"/>
-      <c r="AR8" s="46"/>
-      <c r="AS8" s="46"/>
+      <c r="AQ8" s="53"/>
+      <c r="AR8" s="53"/>
+      <c r="AS8" s="53"/>
       <c r="AU8" s="38">
         <v>4</v>
       </c>
-      <c r="AV8" s="33"/>
-      <c r="AW8" s="30"/>
+      <c r="AV8" s="33">
+        <v>46138</v>
+      </c>
+      <c r="AW8" s="30" t="s">
+        <v>27</v>
+      </c>
       <c r="AX8" s="31"/>
-      <c r="AY8" s="30"/>
+      <c r="AY8" s="30" t="s">
+        <v>30</v>
+      </c>
       <c r="AZ8" s="31"/>
       <c r="BA8" s="32"/>
     </row>
@@ -1667,7 +1711,9 @@
       <c r="A9" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="27"/>
+      <c r="B9" s="27">
+        <v>46140</v>
+      </c>
       <c r="C9" s="12" t="s">
         <v>24</v>
       </c>
@@ -1702,10 +1748,16 @@
       <c r="AU9" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="AV9" s="27"/>
-      <c r="AW9" s="12"/>
+      <c r="AV9" s="27">
+        <v>46141</v>
+      </c>
+      <c r="AW9" s="12" t="s">
+        <v>30</v>
+      </c>
       <c r="AX9" s="13"/>
-      <c r="AY9" s="12"/>
+      <c r="AY9" s="12" t="s">
+        <v>27</v>
+      </c>
       <c r="AZ9" s="13"/>
       <c r="BA9" s="32"/>
     </row>
@@ -1713,7 +1765,9 @@
       <c r="A10" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="27"/>
+      <c r="B10" s="27">
+        <v>46143</v>
+      </c>
       <c r="C10" s="12" t="s">
         <v>25</v>
       </c>
@@ -1746,10 +1800,16 @@
       <c r="AU10" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="AV10" s="27"/>
-      <c r="AW10" s="12"/>
+      <c r="AV10" s="27">
+        <v>46143</v>
+      </c>
+      <c r="AW10" s="12" t="s">
+        <v>27</v>
+      </c>
       <c r="AX10" s="13"/>
-      <c r="AY10" s="12"/>
+      <c r="AY10" s="12" t="s">
+        <v>30</v>
+      </c>
       <c r="AZ10" s="13"/>
       <c r="BA10" s="16"/>
     </row>
@@ -1757,7 +1817,9 @@
       <c r="A11" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="28"/>
+      <c r="B11" s="28">
+        <v>46145</v>
+      </c>
       <c r="C11" s="14" t="s">
         <v>24</v>
       </c>
@@ -1790,23 +1852,29 @@
       <c r="AU11" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="AV11" s="28"/>
-      <c r="AW11" s="14"/>
+      <c r="AV11" s="28">
+        <v>46145</v>
+      </c>
+      <c r="AW11" s="14" t="s">
+        <v>30</v>
+      </c>
       <c r="AX11" s="15"/>
-      <c r="AY11" s="14"/>
+      <c r="AY11" s="14" t="s">
+        <v>27</v>
+      </c>
       <c r="AZ11" s="15"/>
       <c r="BA11" s="6"/>
     </row>
     <row r="12" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="45" t="s">
+      <c r="A12" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="45"/>
-      <c r="C12" s="45"/>
-      <c r="D12" s="45"/>
-      <c r="E12" s="45"/>
-      <c r="F12" s="45"/>
-      <c r="G12" s="45"/>
+      <c r="B12" s="52"/>
+      <c r="C12" s="52"/>
+      <c r="D12" s="52"/>
+      <c r="E12" s="52"/>
+      <c r="F12" s="52"/>
+      <c r="G12" s="52"/>
       <c r="L12" s="12"/>
       <c r="M12" s="8" t="s">
         <v>12</v>
@@ -1817,65 +1885,65 @@
       <c r="Q12" s="12"/>
       <c r="R12" s="13"/>
       <c r="S12" s="16"/>
-      <c r="AI12" s="45" t="s">
+      <c r="AI12" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="AJ12" s="45"/>
-      <c r="AK12" s="45"/>
-      <c r="AL12" s="45"/>
-      <c r="AM12" s="45"/>
-      <c r="AN12" s="45"/>
-      <c r="AO12" s="45"/>
+      <c r="AJ12" s="52"/>
+      <c r="AK12" s="52"/>
+      <c r="AL12" s="52"/>
+      <c r="AM12" s="52"/>
+      <c r="AN12" s="52"/>
+      <c r="AO12" s="52"/>
       <c r="AQ12" s="12"/>
-      <c r="AU12" s="45" t="s">
+      <c r="AU12" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="AV12" s="45"/>
-      <c r="AW12" s="45"/>
-      <c r="AX12" s="45"/>
-      <c r="AY12" s="45"/>
-      <c r="AZ12" s="45"/>
-      <c r="BA12" s="45"/>
+      <c r="AV12" s="52"/>
+      <c r="AW12" s="52"/>
+      <c r="AX12" s="52"/>
+      <c r="AY12" s="52"/>
+      <c r="AZ12" s="52"/>
+      <c r="BA12" s="52"/>
     </row>
     <row r="13" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L13" s="12"/>
-      <c r="M13" s="55" t="s">
+      <c r="M13" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="N13" s="56"/>
-      <c r="O13" s="56"/>
-      <c r="P13" s="56"/>
-      <c r="Q13" s="56"/>
-      <c r="R13" s="56"/>
-      <c r="S13" s="57"/>
+      <c r="N13" s="46"/>
+      <c r="O13" s="46"/>
+      <c r="P13" s="46"/>
+      <c r="Q13" s="46"/>
+      <c r="R13" s="46"/>
+      <c r="S13" s="47"/>
       <c r="AQ13" s="12"/>
     </row>
     <row r="14" spans="1:53" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="61" t="s">
+      <c r="A14" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="61"/>
-      <c r="C14" s="61"/>
-      <c r="D14" s="61"/>
-      <c r="E14" s="61"/>
-      <c r="F14" s="61"/>
-      <c r="G14" s="61"/>
-      <c r="L14" s="47"/>
-      <c r="M14" s="46"/>
-      <c r="N14" s="46"/>
-      <c r="AN14" s="46"/>
-      <c r="AO14" s="46"/>
-      <c r="AP14" s="46"/>
+      <c r="B14" s="51"/>
+      <c r="C14" s="51"/>
+      <c r="D14" s="51"/>
+      <c r="E14" s="51"/>
+      <c r="F14" s="51"/>
+      <c r="G14" s="51"/>
+      <c r="L14" s="57"/>
+      <c r="M14" s="53"/>
+      <c r="N14" s="53"/>
+      <c r="AN14" s="53"/>
+      <c r="AO14" s="53"/>
+      <c r="AP14" s="53"/>
       <c r="AQ14" s="12"/>
-      <c r="AU14" s="61" t="s">
+      <c r="AU14" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="AV14" s="61"/>
-      <c r="AW14" s="61"/>
-      <c r="AX14" s="61"/>
-      <c r="AY14" s="61"/>
-      <c r="AZ14" s="61"/>
-      <c r="BA14" s="61"/>
+      <c r="AV14" s="51"/>
+      <c r="AW14" s="51"/>
+      <c r="AX14" s="51"/>
+      <c r="AY14" s="51"/>
+      <c r="AZ14" s="51"/>
+      <c r="BA14" s="51"/>
     </row>
     <row r="15" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
@@ -1929,7 +1997,9 @@
       <c r="A16" s="7">
         <v>1</v>
       </c>
-      <c r="B16" s="26"/>
+      <c r="B16" s="26">
+        <v>46131</v>
+      </c>
       <c r="C16" s="10" t="s">
         <v>32</v>
       </c>
@@ -1946,10 +2016,16 @@
       <c r="AU16" s="7">
         <v>1</v>
       </c>
-      <c r="AV16" s="26"/>
-      <c r="AW16" s="10"/>
+      <c r="AV16" s="26">
+        <v>46130</v>
+      </c>
+      <c r="AW16" s="10" t="s">
+        <v>31</v>
+      </c>
       <c r="AX16" s="11"/>
-      <c r="AY16" s="10"/>
+      <c r="AY16" s="10" t="s">
+        <v>28</v>
+      </c>
       <c r="AZ16" s="11"/>
       <c r="BA16" s="5"/>
     </row>
@@ -1957,7 +2033,9 @@
       <c r="A17" s="8">
         <v>2</v>
       </c>
-      <c r="B17" s="27"/>
+      <c r="B17" s="27">
+        <v>46133</v>
+      </c>
       <c r="C17" s="12" t="s">
         <v>32</v>
       </c>
@@ -1974,10 +2052,16 @@
       <c r="AU17" s="8">
         <v>2</v>
       </c>
-      <c r="AV17" s="27"/>
-      <c r="AW17" s="12"/>
+      <c r="AV17" s="27">
+        <v>46132</v>
+      </c>
+      <c r="AW17" s="12" t="s">
+        <v>31</v>
+      </c>
       <c r="AX17" s="13"/>
-      <c r="AY17" s="12"/>
+      <c r="AY17" s="12" t="s">
+        <v>28</v>
+      </c>
       <c r="AZ17" s="13"/>
       <c r="BA17" s="16"/>
     </row>
@@ -1985,7 +2069,9 @@
       <c r="A18" s="8">
         <v>3</v>
       </c>
-      <c r="B18" s="27"/>
+      <c r="B18" s="27">
+        <v>46136</v>
+      </c>
       <c r="C18" s="12" t="s">
         <v>36</v>
       </c>
@@ -2002,10 +2088,16 @@
       <c r="AU18" s="8">
         <v>3</v>
       </c>
-      <c r="AV18" s="27"/>
-      <c r="AW18" s="12"/>
+      <c r="AV18" s="27">
+        <v>46134</v>
+      </c>
+      <c r="AW18" s="12" t="s">
+        <v>28</v>
+      </c>
       <c r="AX18" s="13"/>
-      <c r="AY18" s="12"/>
+      <c r="AY18" s="12" t="s">
+        <v>31</v>
+      </c>
       <c r="AZ18" s="13"/>
       <c r="BA18" s="16"/>
     </row>
@@ -2013,7 +2105,9 @@
       <c r="A19" s="8">
         <v>4</v>
       </c>
-      <c r="B19" s="33"/>
+      <c r="B19" s="33">
+        <v>46138</v>
+      </c>
       <c r="C19" s="30" t="s">
         <v>36</v>
       </c>
@@ -2023,22 +2117,28 @@
       </c>
       <c r="F19" s="31"/>
       <c r="G19" s="32"/>
-      <c r="I19" s="46"/>
-      <c r="J19" s="46"/>
-      <c r="K19" s="46"/>
+      <c r="I19" s="53"/>
+      <c r="J19" s="53"/>
+      <c r="K19" s="53"/>
       <c r="L19" s="12"/>
       <c r="O19" s="12"/>
       <c r="AN19" s="12"/>
-      <c r="AQ19" s="47"/>
-      <c r="AR19" s="46"/>
-      <c r="AS19" s="46"/>
+      <c r="AQ19" s="57"/>
+      <c r="AR19" s="53"/>
+      <c r="AS19" s="53"/>
       <c r="AU19" s="38">
         <v>4</v>
       </c>
-      <c r="AV19" s="33"/>
-      <c r="AW19" s="30"/>
+      <c r="AV19" s="33">
+        <v>46137</v>
+      </c>
+      <c r="AW19" s="30" t="s">
+        <v>28</v>
+      </c>
       <c r="AX19" s="31"/>
-      <c r="AY19" s="30"/>
+      <c r="AY19" s="30" t="s">
+        <v>31</v>
+      </c>
       <c r="AZ19" s="31"/>
       <c r="BA19" s="32"/>
     </row>
@@ -2046,7 +2146,9 @@
       <c r="A20" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B20" s="27"/>
+      <c r="B20" s="27">
+        <v>46141</v>
+      </c>
       <c r="C20" s="12" t="s">
         <v>32</v>
       </c>
@@ -2061,10 +2163,16 @@
       <c r="AU20" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="AV20" s="27"/>
-      <c r="AW20" s="12"/>
+      <c r="AV20" s="27">
+        <v>46140</v>
+      </c>
+      <c r="AW20" s="12" t="s">
+        <v>31</v>
+      </c>
       <c r="AX20" s="13"/>
-      <c r="AY20" s="12"/>
+      <c r="AY20" s="12" t="s">
+        <v>28</v>
+      </c>
       <c r="AZ20" s="13"/>
       <c r="BA20" s="16"/>
     </row>
@@ -2072,7 +2180,9 @@
       <c r="A21" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B21" s="27"/>
+      <c r="B21" s="27">
+        <v>46143</v>
+      </c>
       <c r="C21" s="12" t="s">
         <v>36</v>
       </c>
@@ -2087,10 +2197,16 @@
       <c r="AU21" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="AV21" s="27"/>
-      <c r="AW21" s="12"/>
+      <c r="AV21" s="27">
+        <v>46142</v>
+      </c>
+      <c r="AW21" s="12" t="s">
+        <v>28</v>
+      </c>
       <c r="AX21" s="13"/>
-      <c r="AY21" s="12"/>
+      <c r="AY21" s="12" t="s">
+        <v>31</v>
+      </c>
       <c r="AZ21" s="13"/>
       <c r="BA21" s="16"/>
     </row>
@@ -2098,7 +2214,9 @@
       <c r="A22" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B22" s="28"/>
+      <c r="B22" s="28">
+        <v>46145</v>
+      </c>
       <c r="C22" s="14" t="s">
         <v>32</v>
       </c>
@@ -2113,60 +2231,66 @@
       <c r="AU22" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="AV22" s="28"/>
-      <c r="AW22" s="14"/>
+      <c r="AV22" s="28">
+        <v>46144</v>
+      </c>
+      <c r="AW22" s="14" t="s">
+        <v>31</v>
+      </c>
       <c r="AX22" s="15"/>
-      <c r="AY22" s="14"/>
+      <c r="AY22" s="14" t="s">
+        <v>28</v>
+      </c>
       <c r="AZ22" s="15"/>
       <c r="BA22" s="6"/>
     </row>
     <row r="23" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="45" t="s">
+      <c r="A23" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="B23" s="45"/>
-      <c r="C23" s="45"/>
-      <c r="D23" s="45"/>
-      <c r="E23" s="45"/>
-      <c r="F23" s="45"/>
-      <c r="G23" s="45"/>
+      <c r="B23" s="52"/>
+      <c r="C23" s="52"/>
+      <c r="D23" s="52"/>
+      <c r="E23" s="52"/>
+      <c r="F23" s="52"/>
+      <c r="G23" s="52"/>
       <c r="O23" s="12"/>
       <c r="AN23" s="12"/>
-      <c r="AU23" s="45" t="s">
+      <c r="AU23" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="AV23" s="45"/>
-      <c r="AW23" s="45"/>
-      <c r="AX23" s="45"/>
-      <c r="AY23" s="45"/>
-      <c r="AZ23" s="45"/>
-      <c r="BA23" s="45"/>
+      <c r="AV23" s="52"/>
+      <c r="AW23" s="52"/>
+      <c r="AX23" s="52"/>
+      <c r="AY23" s="52"/>
+      <c r="AZ23" s="52"/>
+      <c r="BA23" s="52"/>
     </row>
     <row r="24" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="O24" s="12"/>
       <c r="AN24" s="12"/>
     </row>
     <row r="25" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="45" t="s">
+      <c r="A25" s="52" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="45"/>
-      <c r="C25" s="45"/>
-      <c r="D25" s="45"/>
-      <c r="E25" s="45"/>
-      <c r="F25" s="45"/>
-      <c r="G25" s="45"/>
+      <c r="B25" s="52"/>
+      <c r="C25" s="52"/>
+      <c r="D25" s="52"/>
+      <c r="E25" s="52"/>
+      <c r="F25" s="52"/>
+      <c r="G25" s="52"/>
       <c r="O25" s="12"/>
       <c r="AN25" s="12"/>
-      <c r="AU25" s="45" t="s">
+      <c r="AU25" s="52" t="s">
         <v>42</v>
       </c>
-      <c r="AV25" s="45"/>
-      <c r="AW25" s="45"/>
-      <c r="AX25" s="45"/>
-      <c r="AY25" s="45"/>
-      <c r="AZ25" s="45"/>
-      <c r="BA25" s="45"/>
+      <c r="AV25" s="52"/>
+      <c r="AW25" s="52"/>
+      <c r="AX25" s="52"/>
+      <c r="AY25" s="52"/>
+      <c r="AZ25" s="52"/>
+      <c r="BA25" s="52"/>
     </row>
     <row r="26" spans="1:53" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="20" t="s">
@@ -2190,24 +2314,24 @@
       <c r="G26" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="O26" s="47"/>
-      <c r="P26" s="46"/>
-      <c r="Q26" s="46"/>
-      <c r="R26" s="46"/>
-      <c r="S26" s="46"/>
-      <c r="T26" s="46"/>
-      <c r="U26" s="46"/>
-      <c r="V26" s="46"/>
-      <c r="W26" s="46"/>
-      <c r="AE26" s="46"/>
-      <c r="AF26" s="46"/>
-      <c r="AG26" s="46"/>
-      <c r="AH26" s="46"/>
-      <c r="AI26" s="46"/>
-      <c r="AJ26" s="46"/>
-      <c r="AK26" s="46"/>
-      <c r="AL26" s="46"/>
-      <c r="AM26" s="51"/>
+      <c r="O26" s="57"/>
+      <c r="P26" s="53"/>
+      <c r="Q26" s="53"/>
+      <c r="R26" s="53"/>
+      <c r="S26" s="53"/>
+      <c r="T26" s="53"/>
+      <c r="U26" s="53"/>
+      <c r="V26" s="53"/>
+      <c r="W26" s="53"/>
+      <c r="AE26" s="53"/>
+      <c r="AF26" s="53"/>
+      <c r="AG26" s="53"/>
+      <c r="AH26" s="53"/>
+      <c r="AI26" s="53"/>
+      <c r="AJ26" s="53"/>
+      <c r="AK26" s="53"/>
+      <c r="AL26" s="53"/>
+      <c r="AM26" s="61"/>
       <c r="AU26" s="20" t="s">
         <v>2</v>
       </c>
@@ -2234,7 +2358,9 @@
       <c r="A27" s="7">
         <v>1</v>
       </c>
-      <c r="B27" s="26"/>
+      <c r="B27" s="26">
+        <v>46130</v>
+      </c>
       <c r="C27" s="10" t="s">
         <v>33</v>
       </c>
@@ -2251,10 +2377,16 @@
       <c r="AU27" s="7">
         <v>1</v>
       </c>
-      <c r="AV27" s="26"/>
-      <c r="AW27" s="10"/>
+      <c r="AV27" s="26">
+        <v>46131</v>
+      </c>
+      <c r="AW27" s="10" t="s">
+        <v>37</v>
+      </c>
       <c r="AX27" s="11"/>
-      <c r="AY27" s="10"/>
+      <c r="AY27" s="10" t="s">
+        <v>38</v>
+      </c>
       <c r="AZ27" s="11"/>
       <c r="BA27" s="5"/>
     </row>
@@ -2262,7 +2394,9 @@
       <c r="A28" s="8">
         <v>2</v>
       </c>
-      <c r="B28" s="27"/>
+      <c r="B28" s="27">
+        <v>46132</v>
+      </c>
       <c r="C28" s="12" t="s">
         <v>33</v>
       </c>
@@ -2273,34 +2407,40 @@
       <c r="F28" s="13"/>
       <c r="G28" s="16"/>
       <c r="O28" s="12"/>
-      <c r="P28" s="55" t="s">
+      <c r="P28" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="Q28" s="56"/>
-      <c r="R28" s="56"/>
-      <c r="S28" s="56"/>
-      <c r="T28" s="56"/>
-      <c r="U28" s="56"/>
-      <c r="V28" s="57"/>
+      <c r="Q28" s="46"/>
+      <c r="R28" s="46"/>
+      <c r="S28" s="46"/>
+      <c r="T28" s="46"/>
+      <c r="U28" s="46"/>
+      <c r="V28" s="47"/>
       <c r="X28" s="12"/>
       <c r="AD28" s="13"/>
-      <c r="AF28" s="45" t="s">
+      <c r="AF28" s="52" t="s">
         <v>16</v>
       </c>
-      <c r="AG28" s="45"/>
-      <c r="AH28" s="45"/>
-      <c r="AI28" s="45"/>
-      <c r="AJ28" s="45"/>
-      <c r="AK28" s="45"/>
-      <c r="AL28" s="45"/>
+      <c r="AG28" s="52"/>
+      <c r="AH28" s="52"/>
+      <c r="AI28" s="52"/>
+      <c r="AJ28" s="52"/>
+      <c r="AK28" s="52"/>
+      <c r="AL28" s="52"/>
       <c r="AN28" s="12"/>
       <c r="AU28" s="8">
         <v>2</v>
       </c>
-      <c r="AV28" s="27"/>
-      <c r="AW28" s="12"/>
+      <c r="AV28" s="27">
+        <v>46133</v>
+      </c>
+      <c r="AW28" s="12" t="s">
+        <v>37</v>
+      </c>
       <c r="AX28" s="13"/>
-      <c r="AY28" s="12"/>
+      <c r="AY28" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="AZ28" s="13"/>
       <c r="BA28" s="16"/>
     </row>
@@ -2308,7 +2448,9 @@
       <c r="A29" s="8">
         <v>3</v>
       </c>
-      <c r="B29" s="27"/>
+      <c r="B29" s="27">
+        <v>46135</v>
+      </c>
       <c r="C29" s="12" t="s">
         <v>26</v>
       </c>
@@ -2367,10 +2509,16 @@
       <c r="AU29" s="8">
         <v>3</v>
       </c>
-      <c r="AV29" s="27"/>
-      <c r="AW29" s="12"/>
+      <c r="AV29" s="27">
+        <v>46136</v>
+      </c>
+      <c r="AW29" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="AX29" s="13"/>
-      <c r="AY29" s="12"/>
+      <c r="AY29" s="12" t="s">
+        <v>37</v>
+      </c>
       <c r="AZ29" s="13"/>
       <c r="BA29" s="16"/>
     </row>
@@ -2378,7 +2526,9 @@
       <c r="A30" s="8">
         <v>4</v>
       </c>
-      <c r="B30" s="33"/>
+      <c r="B30" s="33">
+        <v>46137</v>
+      </c>
       <c r="C30" s="30" t="s">
         <v>26</v>
       </c>
@@ -2388,9 +2538,9 @@
       </c>
       <c r="F30" s="31"/>
       <c r="G30" s="32"/>
-      <c r="I30" s="46"/>
-      <c r="J30" s="46"/>
-      <c r="K30" s="46"/>
+      <c r="I30" s="53"/>
+      <c r="J30" s="53"/>
+      <c r="K30" s="53"/>
       <c r="O30" s="12"/>
       <c r="P30" s="7">
         <v>1</v>
@@ -2413,16 +2563,22 @@
       <c r="AK30" s="24"/>
       <c r="AL30" s="25"/>
       <c r="AN30" s="12"/>
-      <c r="AQ30" s="46"/>
-      <c r="AR30" s="46"/>
-      <c r="AS30" s="46"/>
+      <c r="AQ30" s="53"/>
+      <c r="AR30" s="53"/>
+      <c r="AS30" s="53"/>
       <c r="AU30" s="38">
         <v>4</v>
       </c>
-      <c r="AV30" s="33"/>
-      <c r="AW30" s="30"/>
+      <c r="AV30" s="33">
+        <v>46139</v>
+      </c>
+      <c r="AW30" s="30" t="s">
+        <v>38</v>
+      </c>
       <c r="AX30" s="31"/>
-      <c r="AY30" s="30"/>
+      <c r="AY30" s="30" t="s">
+        <v>37</v>
+      </c>
       <c r="AZ30" s="31"/>
       <c r="BA30" s="32"/>
     </row>
@@ -2430,7 +2586,9 @@
       <c r="A31" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B31" s="27"/>
+      <c r="B31" s="27">
+        <v>46139</v>
+      </c>
       <c r="C31" s="12" t="s">
         <v>33</v>
       </c>
@@ -2469,10 +2627,16 @@
       <c r="AU31" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="AV31" s="27"/>
-      <c r="AW31" s="12"/>
+      <c r="AV31" s="27">
+        <v>46141</v>
+      </c>
+      <c r="AW31" s="12" t="s">
+        <v>37</v>
+      </c>
       <c r="AX31" s="13"/>
-      <c r="AY31" s="12"/>
+      <c r="AY31" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="AZ31" s="13"/>
       <c r="BA31" s="16"/>
     </row>
@@ -2480,7 +2644,9 @@
       <c r="A32" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B32" s="27"/>
+      <c r="B32" s="27">
+        <v>46142</v>
+      </c>
       <c r="C32" s="12" t="s">
         <v>26</v>
       </c>
@@ -2517,10 +2683,16 @@
       <c r="AU32" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="AV32" s="27"/>
-      <c r="AW32" s="12"/>
+      <c r="AV32" s="27">
+        <v>46143</v>
+      </c>
+      <c r="AW32" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="AX32" s="13"/>
-      <c r="AY32" s="12"/>
+      <c r="AY32" s="12" t="s">
+        <v>37</v>
+      </c>
       <c r="AZ32" s="13"/>
       <c r="BA32" s="16"/>
     </row>
@@ -2528,7 +2700,9 @@
       <c r="A33" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B33" s="28"/>
+      <c r="B33" s="28">
+        <v>46144</v>
+      </c>
       <c r="C33" s="14" t="s">
         <v>33</v>
       </c>
@@ -2565,23 +2739,29 @@
       <c r="AU33" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="AV33" s="28"/>
-      <c r="AW33" s="14"/>
+      <c r="AV33" s="28">
+        <v>46145</v>
+      </c>
+      <c r="AW33" s="14" t="s">
+        <v>37</v>
+      </c>
       <c r="AX33" s="15"/>
-      <c r="AY33" s="14"/>
+      <c r="AY33" s="14" t="s">
+        <v>38</v>
+      </c>
       <c r="AZ33" s="15"/>
       <c r="BA33" s="6"/>
     </row>
     <row r="34" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="45" t="s">
+      <c r="A34" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="B34" s="45"/>
-      <c r="C34" s="45"/>
-      <c r="D34" s="45"/>
-      <c r="E34" s="45"/>
-      <c r="F34" s="45"/>
-      <c r="G34" s="45"/>
+      <c r="B34" s="52"/>
+      <c r="C34" s="52"/>
+      <c r="D34" s="52"/>
+      <c r="E34" s="52"/>
+      <c r="F34" s="52"/>
+      <c r="G34" s="52"/>
       <c r="L34" s="12"/>
       <c r="O34" s="12"/>
       <c r="P34" s="8" t="s">
@@ -2606,15 +2786,15 @@
       <c r="AL34" s="16"/>
       <c r="AN34" s="12"/>
       <c r="AQ34" s="12"/>
-      <c r="AU34" s="45" t="s">
+      <c r="AU34" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="AV34" s="45"/>
-      <c r="AW34" s="45"/>
-      <c r="AX34" s="45"/>
-      <c r="AY34" s="45"/>
-      <c r="AZ34" s="45"/>
-      <c r="BA34" s="45"/>
+      <c r="AV34" s="52"/>
+      <c r="AW34" s="52"/>
+      <c r="AX34" s="52"/>
+      <c r="AY34" s="52"/>
+      <c r="AZ34" s="52"/>
+      <c r="BA34" s="52"/>
     </row>
     <row r="35" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L35" s="12"/>
@@ -2643,18 +2823,18 @@
       <c r="AQ35" s="12"/>
     </row>
     <row r="36" spans="1:53" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="61" t="s">
+      <c r="A36" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="B36" s="61"/>
-      <c r="C36" s="61"/>
-      <c r="D36" s="61"/>
-      <c r="E36" s="61"/>
-      <c r="F36" s="61"/>
-      <c r="G36" s="61"/>
-      <c r="L36" s="47"/>
-      <c r="M36" s="46"/>
-      <c r="N36" s="46"/>
+      <c r="B36" s="51"/>
+      <c r="C36" s="51"/>
+      <c r="D36" s="51"/>
+      <c r="E36" s="51"/>
+      <c r="F36" s="51"/>
+      <c r="G36" s="51"/>
+      <c r="L36" s="57"/>
+      <c r="M36" s="53"/>
+      <c r="N36" s="53"/>
       <c r="O36" s="12"/>
       <c r="P36" s="8" t="s">
         <v>12</v>
@@ -2676,19 +2856,19 @@
       <c r="AJ36" s="35"/>
       <c r="AK36" s="36"/>
       <c r="AL36" s="37"/>
-      <c r="AN36" s="47"/>
-      <c r="AO36" s="46"/>
-      <c r="AP36" s="46"/>
+      <c r="AN36" s="57"/>
+      <c r="AO36" s="53"/>
+      <c r="AP36" s="53"/>
       <c r="AQ36" s="12"/>
-      <c r="AU36" s="61" t="s">
+      <c r="AU36" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="AV36" s="61"/>
-      <c r="AW36" s="61"/>
-      <c r="AX36" s="61"/>
-      <c r="AY36" s="61"/>
-      <c r="AZ36" s="61"/>
-      <c r="BA36" s="61"/>
+      <c r="AV36" s="51"/>
+      <c r="AW36" s="51"/>
+      <c r="AX36" s="51"/>
+      <c r="AY36" s="51"/>
+      <c r="AZ36" s="51"/>
+      <c r="BA36" s="51"/>
     </row>
     <row r="37" spans="1:53" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37" s="20" t="s">
@@ -2713,31 +2893,31 @@
         <v>9</v>
       </c>
       <c r="L37" s="12"/>
-      <c r="P37" s="58" t="s">
+      <c r="P37" s="48" t="s">
         <v>13</v>
       </c>
-      <c r="Q37" s="59"/>
-      <c r="R37" s="59"/>
-      <c r="S37" s="59"/>
-      <c r="T37" s="59"/>
-      <c r="U37" s="59"/>
-      <c r="V37" s="60"/>
-      <c r="X37" s="47"/>
-      <c r="Y37" s="46"/>
-      <c r="Z37" s="46"/>
-      <c r="AA37" s="46"/>
-      <c r="AB37" s="46"/>
-      <c r="AC37" s="46"/>
-      <c r="AD37" s="51"/>
-      <c r="AF37" s="45" t="s">
+      <c r="Q37" s="49"/>
+      <c r="R37" s="49"/>
+      <c r="S37" s="49"/>
+      <c r="T37" s="49"/>
+      <c r="U37" s="49"/>
+      <c r="V37" s="50"/>
+      <c r="X37" s="57"/>
+      <c r="Y37" s="53"/>
+      <c r="Z37" s="53"/>
+      <c r="AA37" s="53"/>
+      <c r="AB37" s="53"/>
+      <c r="AC37" s="53"/>
+      <c r="AD37" s="61"/>
+      <c r="AF37" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="AG37" s="45"/>
-      <c r="AH37" s="45"/>
-      <c r="AI37" s="45"/>
-      <c r="AJ37" s="45"/>
-      <c r="AK37" s="45"/>
-      <c r="AL37" s="45"/>
+      <c r="AG37" s="52"/>
+      <c r="AH37" s="52"/>
+      <c r="AI37" s="52"/>
+      <c r="AJ37" s="52"/>
+      <c r="AK37" s="52"/>
+      <c r="AL37" s="52"/>
       <c r="AQ37" s="12"/>
       <c r="AU37" s="3" t="s">
         <v>2</v>
@@ -2765,7 +2945,9 @@
       <c r="A38" s="7">
         <v>1</v>
       </c>
-      <c r="B38" s="26"/>
+      <c r="B38" s="26">
+        <v>46130</v>
+      </c>
       <c r="C38" s="10" t="s">
         <v>34</v>
       </c>
@@ -2780,10 +2962,16 @@
       <c r="AU38" s="7">
         <v>1</v>
       </c>
-      <c r="AV38" s="26"/>
-      <c r="AW38" s="10"/>
+      <c r="AV38" s="26">
+        <v>46132</v>
+      </c>
+      <c r="AW38" s="10" t="s">
+        <v>23</v>
+      </c>
       <c r="AX38" s="11"/>
-      <c r="AY38" s="10"/>
+      <c r="AY38" s="10" t="s">
+        <v>29</v>
+      </c>
       <c r="AZ38" s="11"/>
       <c r="BA38" s="5"/>
     </row>
@@ -2791,7 +2979,9 @@
       <c r="A39" s="8">
         <v>2</v>
       </c>
-      <c r="B39" s="27"/>
+      <c r="B39" s="27">
+        <v>46132</v>
+      </c>
       <c r="C39" s="12" t="s">
         <v>34</v>
       </c>
@@ -2802,41 +2992,47 @@
       <c r="F39" s="13"/>
       <c r="G39" s="16"/>
       <c r="L39" s="12"/>
-      <c r="M39" s="55" t="s">
+      <c r="M39" s="45" t="s">
         <v>44</v>
       </c>
-      <c r="N39" s="56"/>
-      <c r="O39" s="56"/>
-      <c r="P39" s="56"/>
-      <c r="Q39" s="56"/>
-      <c r="R39" s="56"/>
-      <c r="S39" s="57"/>
-      <c r="X39" s="45" t="s">
+      <c r="N39" s="46"/>
+      <c r="O39" s="46"/>
+      <c r="P39" s="46"/>
+      <c r="Q39" s="46"/>
+      <c r="R39" s="46"/>
+      <c r="S39" s="47"/>
+      <c r="X39" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="Y39" s="45"/>
-      <c r="Z39" s="45"/>
-      <c r="AA39" s="45"/>
-      <c r="AB39" s="45"/>
-      <c r="AC39" s="45"/>
-      <c r="AD39" s="45"/>
-      <c r="AI39" s="55" t="s">
+      <c r="Y39" s="52"/>
+      <c r="Z39" s="52"/>
+      <c r="AA39" s="52"/>
+      <c r="AB39" s="52"/>
+      <c r="AC39" s="52"/>
+      <c r="AD39" s="52"/>
+      <c r="AI39" s="45" t="s">
         <v>44</v>
       </c>
-      <c r="AJ39" s="56"/>
-      <c r="AK39" s="56"/>
-      <c r="AL39" s="56"/>
-      <c r="AM39" s="56"/>
-      <c r="AN39" s="56"/>
-      <c r="AO39" s="57"/>
+      <c r="AJ39" s="46"/>
+      <c r="AK39" s="46"/>
+      <c r="AL39" s="46"/>
+      <c r="AM39" s="46"/>
+      <c r="AN39" s="46"/>
+      <c r="AO39" s="47"/>
       <c r="AQ39" s="12"/>
       <c r="AU39" s="8">
         <v>2</v>
       </c>
-      <c r="AV39" s="27"/>
-      <c r="AW39" s="12"/>
+      <c r="AV39" s="27">
+        <v>46134</v>
+      </c>
+      <c r="AW39" s="12" t="s">
+        <v>23</v>
+      </c>
       <c r="AX39" s="13"/>
-      <c r="AY39" s="12"/>
+      <c r="AY39" s="12" t="s">
+        <v>29</v>
+      </c>
       <c r="AZ39" s="13"/>
       <c r="BA39" s="16"/>
     </row>
@@ -2844,7 +3040,9 @@
       <c r="A40" s="8">
         <v>3</v>
       </c>
-      <c r="B40" s="27"/>
+      <c r="B40" s="27">
+        <v>46134</v>
+      </c>
       <c r="C40" s="12" t="s">
         <v>35</v>
       </c>
@@ -2922,10 +3120,16 @@
       <c r="AU40" s="8">
         <v>3</v>
       </c>
-      <c r="AV40" s="27"/>
-      <c r="AW40" s="12"/>
+      <c r="AV40" s="27">
+        <v>46136</v>
+      </c>
+      <c r="AW40" s="12" t="s">
+        <v>29</v>
+      </c>
       <c r="AX40" s="13"/>
-      <c r="AY40" s="12"/>
+      <c r="AY40" s="12" t="s">
+        <v>23</v>
+      </c>
       <c r="AZ40" s="13"/>
       <c r="BA40" s="16"/>
     </row>
@@ -2933,7 +3137,9 @@
       <c r="A41" s="8">
         <v>4</v>
       </c>
-      <c r="B41" s="33"/>
+      <c r="B41" s="33">
+        <v>46137</v>
+      </c>
       <c r="C41" s="30" t="s">
         <v>35</v>
       </c>
@@ -2943,9 +3149,9 @@
       </c>
       <c r="F41" s="31"/>
       <c r="G41" s="32"/>
-      <c r="I41" s="46"/>
-      <c r="J41" s="46"/>
-      <c r="K41" s="46"/>
+      <c r="I41" s="53"/>
+      <c r="J41" s="53"/>
+      <c r="K41" s="53"/>
       <c r="L41" s="12"/>
       <c r="M41" s="7">
         <v>1</v>
@@ -2974,16 +3180,22 @@
       <c r="AM41" s="23"/>
       <c r="AN41" s="24"/>
       <c r="AO41" s="25"/>
-      <c r="AQ41" s="47"/>
-      <c r="AR41" s="46"/>
-      <c r="AS41" s="46"/>
-      <c r="AU41" s="8">
+      <c r="AQ41" s="57"/>
+      <c r="AR41" s="53"/>
+      <c r="AS41" s="53"/>
+      <c r="AU41" s="38">
         <v>4</v>
       </c>
-      <c r="AV41" s="33"/>
-      <c r="AW41" s="30"/>
+      <c r="AV41" s="33">
+        <v>46138</v>
+      </c>
+      <c r="AW41" s="30" t="s">
+        <v>29</v>
+      </c>
       <c r="AX41" s="31"/>
-      <c r="AY41" s="30"/>
+      <c r="AY41" s="30" t="s">
+        <v>23</v>
+      </c>
       <c r="AZ41" s="31"/>
       <c r="BA41" s="32"/>
     </row>
@@ -2991,9 +3203,11 @@
       <c r="A42" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B42" s="27"/>
+      <c r="B42" s="27">
+        <v>46139</v>
+      </c>
       <c r="C42" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D42" s="13"/>
       <c r="E42" s="12" t="s">
@@ -3031,10 +3245,16 @@
       <c r="AU42" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="AV42" s="27"/>
-      <c r="AW42" s="12"/>
+      <c r="AV42" s="27">
+        <v>46140</v>
+      </c>
+      <c r="AW42" s="12" t="s">
+        <v>23</v>
+      </c>
       <c r="AX42" s="13"/>
-      <c r="AY42" s="12"/>
+      <c r="AY42" s="12" t="s">
+        <v>29</v>
+      </c>
       <c r="AZ42" s="13"/>
       <c r="BA42" s="16"/>
     </row>
@@ -3042,9 +3262,11 @@
       <c r="A43" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B43" s="27"/>
+      <c r="B43" s="27">
+        <v>46141</v>
+      </c>
       <c r="C43" s="12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D43" s="13"/>
       <c r="E43" s="12" t="s">
@@ -3082,10 +3304,16 @@
       <c r="AU43" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="AV43" s="27"/>
-      <c r="AW43" s="12"/>
+      <c r="AV43" s="27">
+        <v>46142</v>
+      </c>
+      <c r="AW43" s="12" t="s">
+        <v>29</v>
+      </c>
       <c r="AX43" s="13"/>
-      <c r="AY43" s="12"/>
+      <c r="AY43" s="12" t="s">
+        <v>23</v>
+      </c>
       <c r="AZ43" s="13"/>
       <c r="BA43" s="32"/>
     </row>
@@ -3093,9 +3321,11 @@
       <c r="A44" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B44" s="28"/>
+      <c r="B44" s="28">
+        <v>46144</v>
+      </c>
       <c r="C44" s="14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D44" s="15"/>
       <c r="E44" s="14" t="s">
@@ -3133,23 +3363,29 @@
       <c r="AU44" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="AV44" s="28"/>
-      <c r="AW44" s="14"/>
+      <c r="AV44" s="28">
+        <v>46144</v>
+      </c>
+      <c r="AW44" s="14" t="s">
+        <v>23</v>
+      </c>
       <c r="AX44" s="15"/>
-      <c r="AY44" s="14"/>
+      <c r="AY44" s="14" t="s">
+        <v>29</v>
+      </c>
       <c r="AZ44" s="15"/>
       <c r="BA44" s="6"/>
     </row>
     <row r="45" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="45" t="s">
+      <c r="A45" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="B45" s="45"/>
-      <c r="C45" s="45"/>
-      <c r="D45" s="45"/>
-      <c r="E45" s="45"/>
-      <c r="F45" s="45"/>
-      <c r="G45" s="45"/>
+      <c r="B45" s="52"/>
+      <c r="C45" s="52"/>
+      <c r="D45" s="52"/>
+      <c r="E45" s="52"/>
+      <c r="F45" s="52"/>
+      <c r="G45" s="52"/>
       <c r="M45" s="8" t="s">
         <v>11</v>
       </c>
@@ -3177,15 +3413,15 @@
       <c r="AM45" s="12"/>
       <c r="AN45" s="13"/>
       <c r="AO45" s="16"/>
-      <c r="AU45" s="45" t="s">
+      <c r="AU45" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="AV45" s="45"/>
-      <c r="AW45" s="45"/>
-      <c r="AX45" s="45"/>
-      <c r="AY45" s="45"/>
-      <c r="AZ45" s="45"/>
-      <c r="BA45" s="45"/>
+      <c r="AV45" s="52"/>
+      <c r="AW45" s="52"/>
+      <c r="AX45" s="52"/>
+      <c r="AY45" s="52"/>
+      <c r="AZ45" s="52"/>
+      <c r="BA45" s="52"/>
     </row>
     <row r="46" spans="1:53" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="M46" s="8" t="s">
@@ -3246,45 +3482,65 @@
       <c r="AO47" s="6"/>
     </row>
     <row r="48" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="M48" s="55" t="s">
+      <c r="M48" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="N48" s="56"/>
-      <c r="O48" s="56"/>
-      <c r="P48" s="56"/>
-      <c r="Q48" s="56"/>
-      <c r="R48" s="56"/>
-      <c r="S48" s="57"/>
-      <c r="X48" s="45" t="s">
+      <c r="N48" s="46"/>
+      <c r="O48" s="46"/>
+      <c r="P48" s="46"/>
+      <c r="Q48" s="46"/>
+      <c r="R48" s="46"/>
+      <c r="S48" s="47"/>
+      <c r="X48" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="Y48" s="45"/>
-      <c r="Z48" s="45"/>
-      <c r="AA48" s="45"/>
-      <c r="AB48" s="45"/>
-      <c r="AC48" s="45"/>
-      <c r="AD48" s="45"/>
-      <c r="AI48" s="45" t="s">
+      <c r="Y48" s="52"/>
+      <c r="Z48" s="52"/>
+      <c r="AA48" s="52"/>
+      <c r="AB48" s="52"/>
+      <c r="AC48" s="52"/>
+      <c r="AD48" s="52"/>
+      <c r="AI48" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="AJ48" s="45"/>
-      <c r="AK48" s="45"/>
-      <c r="AL48" s="45"/>
-      <c r="AM48" s="45"/>
-      <c r="AN48" s="45"/>
-      <c r="AO48" s="45"/>
+      <c r="AJ48" s="52"/>
+      <c r="AK48" s="52"/>
+      <c r="AL48" s="52"/>
+      <c r="AM48" s="52"/>
+      <c r="AN48" s="52"/>
+      <c r="AO48" s="52"/>
     </row>
     <row r="49" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="M48:S48"/>
-    <mergeCell ref="M39:S39"/>
-    <mergeCell ref="P37:V37"/>
-    <mergeCell ref="P28:V28"/>
-    <mergeCell ref="A36:G36"/>
-    <mergeCell ref="A45:G45"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="AU45:BA45"/>
+    <mergeCell ref="AF28:AL28"/>
+    <mergeCell ref="AF37:AL37"/>
+    <mergeCell ref="AQ30:AS30"/>
+    <mergeCell ref="AQ41:AS41"/>
+    <mergeCell ref="AU34:BA34"/>
+    <mergeCell ref="AU36:BA36"/>
+    <mergeCell ref="AU2:BA2"/>
+    <mergeCell ref="AU3:BA3"/>
+    <mergeCell ref="AU12:BA12"/>
+    <mergeCell ref="AU14:BA14"/>
+    <mergeCell ref="AU23:BA23"/>
+    <mergeCell ref="X37:AD37"/>
+    <mergeCell ref="AE26:AM26"/>
+    <mergeCell ref="Z1:AB1"/>
+    <mergeCell ref="X39:AD39"/>
+    <mergeCell ref="X48:AD48"/>
+    <mergeCell ref="AF1:BA1"/>
+    <mergeCell ref="AI2:AO2"/>
+    <mergeCell ref="AI3:AO3"/>
+    <mergeCell ref="AI12:AO12"/>
+    <mergeCell ref="AI39:AO39"/>
+    <mergeCell ref="AU25:BA25"/>
+    <mergeCell ref="AI48:AO48"/>
+    <mergeCell ref="AN14:AP14"/>
+    <mergeCell ref="AN36:AP36"/>
+    <mergeCell ref="AQ8:AS8"/>
+    <mergeCell ref="AQ19:AS19"/>
     <mergeCell ref="A1:U1"/>
     <mergeCell ref="O26:W26"/>
     <mergeCell ref="I41:K41"/>
@@ -3301,34 +3557,14 @@
     <mergeCell ref="I8:K8"/>
     <mergeCell ref="I19:K19"/>
     <mergeCell ref="A25:G25"/>
-    <mergeCell ref="X37:AD37"/>
-    <mergeCell ref="AE26:AM26"/>
-    <mergeCell ref="Z1:AB1"/>
-    <mergeCell ref="X39:AD39"/>
-    <mergeCell ref="X48:AD48"/>
-    <mergeCell ref="AF1:BA1"/>
-    <mergeCell ref="AI2:AO2"/>
-    <mergeCell ref="AI3:AO3"/>
-    <mergeCell ref="AI12:AO12"/>
-    <mergeCell ref="AI39:AO39"/>
-    <mergeCell ref="AU25:BA25"/>
-    <mergeCell ref="AI48:AO48"/>
-    <mergeCell ref="AN14:AP14"/>
-    <mergeCell ref="AN36:AP36"/>
-    <mergeCell ref="AQ8:AS8"/>
-    <mergeCell ref="AQ19:AS19"/>
-    <mergeCell ref="AU2:BA2"/>
-    <mergeCell ref="AU3:BA3"/>
-    <mergeCell ref="AU12:BA12"/>
-    <mergeCell ref="AU14:BA14"/>
-    <mergeCell ref="AU23:BA23"/>
-    <mergeCell ref="AU45:BA45"/>
-    <mergeCell ref="AF28:AL28"/>
-    <mergeCell ref="AF37:AL37"/>
-    <mergeCell ref="AQ30:AS30"/>
-    <mergeCell ref="AQ41:AS41"/>
-    <mergeCell ref="AU34:BA34"/>
-    <mergeCell ref="AU36:BA36"/>
+    <mergeCell ref="M48:S48"/>
+    <mergeCell ref="M39:S39"/>
+    <mergeCell ref="P37:V37"/>
+    <mergeCell ref="P28:V28"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="A34:G34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/2025_2026/Playoffs/Brackets.xlsx
+++ b/2025_2026/Playoffs/Brackets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\NHLStats\2025_2026\Playoffs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2DA6820-BF0F-4B43-92FC-BC6905DFA134}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DF58263-D0EB-46B4-AE34-4D743E74537F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="48">
   <si>
     <t>Eastern Conference Playoff Teams</t>
   </si>
@@ -161,6 +161,15 @@
   </si>
   <si>
     <t>1st/4th Place Winner vs 2nd/3rd Place Winner</t>
+  </si>
+  <si>
+    <t>Hurricanes Lead 1-0</t>
+  </si>
+  <si>
+    <t>Flyers Lead 1-0</t>
+  </si>
+  <si>
+    <t>Wild Lead 1-0</t>
   </si>
 </sst>
 </file>
@@ -539,13 +548,37 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -566,37 +599,13 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -966,18 +975,18 @@
     </row>
     <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="11" spans="1:7" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="44" t="s">
+      <c r="A11" s="59" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="44"/>
-      <c r="C11" s="44" t="s">
+      <c r="B11" s="59"/>
+      <c r="C11" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="44"/>
-      <c r="E11" s="44" t="s">
+      <c r="D11" s="59"/>
+      <c r="E11" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="44"/>
+      <c r="F11" s="59"/>
       <c r="G11" s="4" t="s">
         <v>18</v>
       </c>
@@ -1006,18 +1015,18 @@
       </c>
     </row>
     <row r="13" spans="1:7" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="42" t="s">
+      <c r="A13" s="60" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="43"/>
-      <c r="C13" s="42" t="s">
+      <c r="B13" s="61"/>
+      <c r="C13" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="D13" s="43"/>
-      <c r="E13" s="42" t="s">
+      <c r="D13" s="61"/>
+      <c r="E13" s="60" t="s">
         <v>17</v>
       </c>
-      <c r="F13" s="43"/>
+      <c r="F13" s="61"/>
       <c r="G13" s="5"/>
     </row>
     <row r="14" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1044,14 +1053,14 @@
       <c r="F15" s="6"/>
     </row>
     <row r="16" spans="1:7" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="42" t="s">
+      <c r="A16" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="43"/>
-      <c r="C16" s="42" t="s">
+      <c r="B16" s="61"/>
+      <c r="C16" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="43"/>
+      <c r="D16" s="61"/>
     </row>
     <row r="17" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
@@ -1073,10 +1082,10 @@
       <c r="D18" s="6"/>
     </row>
     <row r="19" spans="1:4" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="42" t="s">
+      <c r="A19" s="60" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="43"/>
+      <c r="B19" s="61"/>
     </row>
     <row r="20" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
@@ -1095,10 +1104,10 @@
       </c>
     </row>
     <row r="22" spans="1:4" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="42" t="s">
+      <c r="A22" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="43"/>
+      <c r="B22" s="61"/>
     </row>
     <row r="23" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
@@ -1183,16 +1192,16 @@
     <sortCondition ref="B2:B9"/>
   </sortState>
   <mergeCells count="10">
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C16:D16"/>
     <mergeCell ref="E11:F11"/>
     <mergeCell ref="E13:F13"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C16:D16"/>
   </mergeCells>
   <dataValidations count="16">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C14" xr:uid="{2C3D9587-ABAE-4E3F-8B22-396DF812BF02}">
@@ -1296,124 +1305,124 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:53" ht="27.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="55"/>
-      <c r="J1" s="55"/>
-      <c r="K1" s="55"/>
-      <c r="L1" s="55"/>
-      <c r="M1" s="55"/>
-      <c r="N1" s="55"/>
-      <c r="O1" s="55"/>
-      <c r="P1" s="55"/>
-      <c r="Q1" s="55"/>
-      <c r="R1" s="55"/>
-      <c r="S1" s="55"/>
-      <c r="T1" s="55"/>
-      <c r="U1" s="56"/>
-      <c r="Z1" s="54" t="s">
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
+      <c r="K1" s="51"/>
+      <c r="L1" s="51"/>
+      <c r="M1" s="51"/>
+      <c r="N1" s="51"/>
+      <c r="O1" s="51"/>
+      <c r="P1" s="51"/>
+      <c r="Q1" s="51"/>
+      <c r="R1" s="51"/>
+      <c r="S1" s="51"/>
+      <c r="T1" s="51"/>
+      <c r="U1" s="52"/>
+      <c r="Z1" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="AA1" s="55"/>
-      <c r="AB1" s="56"/>
-      <c r="AF1" s="54" t="s">
+      <c r="AA1" s="51"/>
+      <c r="AB1" s="52"/>
+      <c r="AF1" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="AG1" s="55"/>
-      <c r="AH1" s="55"/>
-      <c r="AI1" s="55"/>
-      <c r="AJ1" s="55"/>
-      <c r="AK1" s="55"/>
-      <c r="AL1" s="55"/>
-      <c r="AM1" s="55"/>
-      <c r="AN1" s="55"/>
-      <c r="AO1" s="55"/>
-      <c r="AP1" s="55"/>
-      <c r="AQ1" s="55"/>
-      <c r="AR1" s="55"/>
-      <c r="AS1" s="55"/>
-      <c r="AT1" s="55"/>
-      <c r="AU1" s="55"/>
-      <c r="AV1" s="55"/>
-      <c r="AW1" s="55"/>
-      <c r="AX1" s="55"/>
-      <c r="AY1" s="55"/>
-      <c r="AZ1" s="55"/>
-      <c r="BA1" s="56"/>
+      <c r="AG1" s="51"/>
+      <c r="AH1" s="51"/>
+      <c r="AI1" s="51"/>
+      <c r="AJ1" s="51"/>
+      <c r="AK1" s="51"/>
+      <c r="AL1" s="51"/>
+      <c r="AM1" s="51"/>
+      <c r="AN1" s="51"/>
+      <c r="AO1" s="51"/>
+      <c r="AP1" s="51"/>
+      <c r="AQ1" s="51"/>
+      <c r="AR1" s="51"/>
+      <c r="AS1" s="51"/>
+      <c r="AT1" s="51"/>
+      <c r="AU1" s="51"/>
+      <c r="AV1" s="51"/>
+      <c r="AW1" s="51"/>
+      <c r="AX1" s="51"/>
+      <c r="AY1" s="51"/>
+      <c r="AZ1" s="51"/>
+      <c r="BA1" s="52"/>
     </row>
     <row r="2" spans="1:53" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="58" t="s">
+      <c r="A2" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="59"/>
-      <c r="C2" s="59"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="59"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="60"/>
-      <c r="M2" s="58" t="s">
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="48"/>
+      <c r="M2" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="59"/>
-      <c r="O2" s="59"/>
-      <c r="P2" s="59"/>
-      <c r="Q2" s="59"/>
-      <c r="R2" s="60"/>
-      <c r="AI2" s="58" t="s">
+      <c r="N2" s="47"/>
+      <c r="O2" s="47"/>
+      <c r="P2" s="47"/>
+      <c r="Q2" s="47"/>
+      <c r="R2" s="48"/>
+      <c r="AI2" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="AJ2" s="59"/>
-      <c r="AK2" s="59"/>
-      <c r="AL2" s="59"/>
-      <c r="AM2" s="59"/>
-      <c r="AN2" s="59"/>
-      <c r="AO2" s="60"/>
-      <c r="AU2" s="58" t="s">
+      <c r="AJ2" s="47"/>
+      <c r="AK2" s="47"/>
+      <c r="AL2" s="47"/>
+      <c r="AM2" s="47"/>
+      <c r="AN2" s="47"/>
+      <c r="AO2" s="48"/>
+      <c r="AU2" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="AV2" s="59"/>
-      <c r="AW2" s="59"/>
-      <c r="AX2" s="59"/>
-      <c r="AY2" s="59"/>
-      <c r="AZ2" s="59"/>
-      <c r="BA2" s="60"/>
+      <c r="AV2" s="47"/>
+      <c r="AW2" s="47"/>
+      <c r="AX2" s="47"/>
+      <c r="AY2" s="47"/>
+      <c r="AZ2" s="47"/>
+      <c r="BA2" s="48"/>
     </row>
     <row r="3" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="52" t="s">
+      <c r="A3" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="52"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="52"/>
-      <c r="AI3" s="45" t="s">
+      <c r="B3" s="42"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="42"/>
+      <c r="AI3" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="AJ3" s="46"/>
-      <c r="AK3" s="46"/>
-      <c r="AL3" s="46"/>
-      <c r="AM3" s="46"/>
-      <c r="AN3" s="46"/>
-      <c r="AO3" s="47"/>
-      <c r="AU3" s="52" t="s">
+      <c r="AJ3" s="54"/>
+      <c r="AK3" s="54"/>
+      <c r="AL3" s="54"/>
+      <c r="AM3" s="54"/>
+      <c r="AN3" s="54"/>
+      <c r="AO3" s="55"/>
+      <c r="AU3" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="AV3" s="52"/>
-      <c r="AW3" s="52"/>
-      <c r="AX3" s="52"/>
-      <c r="AY3" s="52"/>
-      <c r="AZ3" s="52"/>
-      <c r="BA3" s="52"/>
+      <c r="AV3" s="42"/>
+      <c r="AW3" s="42"/>
+      <c r="AX3" s="42"/>
+      <c r="AY3" s="42"/>
+      <c r="AZ3" s="42"/>
+      <c r="BA3" s="42"/>
     </row>
     <row r="4" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
@@ -1437,15 +1446,15 @@
       <c r="G4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="45" t="s">
+      <c r="M4" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="N4" s="46"/>
-      <c r="O4" s="46"/>
-      <c r="P4" s="46"/>
-      <c r="Q4" s="46"/>
-      <c r="R4" s="46"/>
-      <c r="S4" s="47"/>
+      <c r="N4" s="54"/>
+      <c r="O4" s="54"/>
+      <c r="P4" s="54"/>
+      <c r="Q4" s="54"/>
+      <c r="R4" s="54"/>
+      <c r="S4" s="55"/>
       <c r="AI4" s="3" t="s">
         <v>2</v>
       </c>
@@ -1667,9 +1676,9 @@
       </c>
       <c r="F8" s="13"/>
       <c r="G8" s="16"/>
-      <c r="I8" s="53"/>
-      <c r="J8" s="53"/>
-      <c r="K8" s="53"/>
+      <c r="I8" s="43"/>
+      <c r="J8" s="43"/>
+      <c r="K8" s="43"/>
       <c r="M8" s="8">
         <v>3</v>
       </c>
@@ -1688,9 +1697,9 @@
       <c r="AM8" s="30"/>
       <c r="AN8" s="31"/>
       <c r="AO8" s="16"/>
-      <c r="AQ8" s="53"/>
-      <c r="AR8" s="53"/>
-      <c r="AS8" s="53"/>
+      <c r="AQ8" s="43"/>
+      <c r="AR8" s="43"/>
+      <c r="AS8" s="43"/>
       <c r="AU8" s="38">
         <v>4</v>
       </c>
@@ -1866,15 +1875,15 @@
       <c r="BA11" s="6"/>
     </row>
     <row r="12" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="52" t="s">
+      <c r="A12" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="52"/>
-      <c r="C12" s="52"/>
-      <c r="D12" s="52"/>
-      <c r="E12" s="52"/>
-      <c r="F12" s="52"/>
-      <c r="G12" s="52"/>
+      <c r="B12" s="42"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="42"/>
       <c r="L12" s="12"/>
       <c r="M12" s="8" t="s">
         <v>12</v>
@@ -1885,65 +1894,65 @@
       <c r="Q12" s="12"/>
       <c r="R12" s="13"/>
       <c r="S12" s="16"/>
-      <c r="AI12" s="52" t="s">
+      <c r="AI12" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AJ12" s="52"/>
-      <c r="AK12" s="52"/>
-      <c r="AL12" s="52"/>
-      <c r="AM12" s="52"/>
-      <c r="AN12" s="52"/>
-      <c r="AO12" s="52"/>
+      <c r="AJ12" s="42"/>
+      <c r="AK12" s="42"/>
+      <c r="AL12" s="42"/>
+      <c r="AM12" s="42"/>
+      <c r="AN12" s="42"/>
+      <c r="AO12" s="42"/>
       <c r="AQ12" s="12"/>
-      <c r="AU12" s="52" t="s">
+      <c r="AU12" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AV12" s="52"/>
-      <c r="AW12" s="52"/>
-      <c r="AX12" s="52"/>
-      <c r="AY12" s="52"/>
-      <c r="AZ12" s="52"/>
-      <c r="BA12" s="52"/>
+      <c r="AV12" s="42"/>
+      <c r="AW12" s="42"/>
+      <c r="AX12" s="42"/>
+      <c r="AY12" s="42"/>
+      <c r="AZ12" s="42"/>
+      <c r="BA12" s="42"/>
     </row>
     <row r="13" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L13" s="12"/>
-      <c r="M13" s="45" t="s">
+      <c r="M13" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="N13" s="46"/>
-      <c r="O13" s="46"/>
-      <c r="P13" s="46"/>
-      <c r="Q13" s="46"/>
-      <c r="R13" s="46"/>
-      <c r="S13" s="47"/>
+      <c r="N13" s="54"/>
+      <c r="O13" s="54"/>
+      <c r="P13" s="54"/>
+      <c r="Q13" s="54"/>
+      <c r="R13" s="54"/>
+      <c r="S13" s="55"/>
       <c r="AQ13" s="12"/>
     </row>
     <row r="14" spans="1:53" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="51" t="s">
+      <c r="A14" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="51"/>
-      <c r="C14" s="51"/>
-      <c r="D14" s="51"/>
-      <c r="E14" s="51"/>
-      <c r="F14" s="51"/>
-      <c r="G14" s="51"/>
-      <c r="L14" s="57"/>
-      <c r="M14" s="53"/>
-      <c r="N14" s="53"/>
-      <c r="AN14" s="53"/>
-      <c r="AO14" s="53"/>
-      <c r="AP14" s="53"/>
+      <c r="B14" s="45"/>
+      <c r="C14" s="45"/>
+      <c r="D14" s="45"/>
+      <c r="E14" s="45"/>
+      <c r="F14" s="45"/>
+      <c r="G14" s="45"/>
+      <c r="L14" s="44"/>
+      <c r="M14" s="43"/>
+      <c r="N14" s="43"/>
+      <c r="AN14" s="43"/>
+      <c r="AO14" s="43"/>
+      <c r="AP14" s="43"/>
       <c r="AQ14" s="12"/>
-      <c r="AU14" s="51" t="s">
+      <c r="AU14" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="AV14" s="51"/>
-      <c r="AW14" s="51"/>
-      <c r="AX14" s="51"/>
-      <c r="AY14" s="51"/>
-      <c r="AZ14" s="51"/>
-      <c r="BA14" s="51"/>
+      <c r="AV14" s="45"/>
+      <c r="AW14" s="45"/>
+      <c r="AX14" s="45"/>
+      <c r="AY14" s="45"/>
+      <c r="AZ14" s="45"/>
+      <c r="BA14" s="45"/>
     </row>
     <row r="15" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
@@ -2022,12 +2031,18 @@
       <c r="AW16" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="AX16" s="11"/>
+      <c r="AX16" s="11">
+        <v>6</v>
+      </c>
       <c r="AY16" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="AZ16" s="11"/>
-      <c r="BA16" s="5"/>
+      <c r="AZ16" s="11">
+        <v>1</v>
+      </c>
+      <c r="BA16" s="5" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="17" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A17" s="8">
@@ -2117,15 +2132,15 @@
       </c>
       <c r="F19" s="31"/>
       <c r="G19" s="32"/>
-      <c r="I19" s="53"/>
-      <c r="J19" s="53"/>
-      <c r="K19" s="53"/>
+      <c r="I19" s="43"/>
+      <c r="J19" s="43"/>
+      <c r="K19" s="43"/>
       <c r="L19" s="12"/>
       <c r="O19" s="12"/>
       <c r="AN19" s="12"/>
-      <c r="AQ19" s="57"/>
-      <c r="AR19" s="53"/>
-      <c r="AS19" s="53"/>
+      <c r="AQ19" s="44"/>
+      <c r="AR19" s="43"/>
+      <c r="AS19" s="43"/>
       <c r="AU19" s="38">
         <v>4</v>
       </c>
@@ -2245,52 +2260,52 @@
       <c r="BA22" s="6"/>
     </row>
     <row r="23" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="52" t="s">
+      <c r="A23" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B23" s="52"/>
-      <c r="C23" s="52"/>
-      <c r="D23" s="52"/>
-      <c r="E23" s="52"/>
-      <c r="F23" s="52"/>
-      <c r="G23" s="52"/>
+      <c r="B23" s="42"/>
+      <c r="C23" s="42"/>
+      <c r="D23" s="42"/>
+      <c r="E23" s="42"/>
+      <c r="F23" s="42"/>
+      <c r="G23" s="42"/>
       <c r="O23" s="12"/>
       <c r="AN23" s="12"/>
-      <c r="AU23" s="52" t="s">
+      <c r="AU23" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AV23" s="52"/>
-      <c r="AW23" s="52"/>
-      <c r="AX23" s="52"/>
-      <c r="AY23" s="52"/>
-      <c r="AZ23" s="52"/>
-      <c r="BA23" s="52"/>
+      <c r="AV23" s="42"/>
+      <c r="AW23" s="42"/>
+      <c r="AX23" s="42"/>
+      <c r="AY23" s="42"/>
+      <c r="AZ23" s="42"/>
+      <c r="BA23" s="42"/>
     </row>
     <row r="24" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="O24" s="12"/>
       <c r="AN24" s="12"/>
     </row>
     <row r="25" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="52" t="s">
+      <c r="A25" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="52"/>
-      <c r="C25" s="52"/>
-      <c r="D25" s="52"/>
-      <c r="E25" s="52"/>
-      <c r="F25" s="52"/>
-      <c r="G25" s="52"/>
+      <c r="B25" s="42"/>
+      <c r="C25" s="42"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="42"/>
+      <c r="F25" s="42"/>
+      <c r="G25" s="42"/>
       <c r="O25" s="12"/>
       <c r="AN25" s="12"/>
-      <c r="AU25" s="52" t="s">
+      <c r="AU25" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="AV25" s="52"/>
-      <c r="AW25" s="52"/>
-      <c r="AX25" s="52"/>
-      <c r="AY25" s="52"/>
-      <c r="AZ25" s="52"/>
-      <c r="BA25" s="52"/>
+      <c r="AV25" s="42"/>
+      <c r="AW25" s="42"/>
+      <c r="AX25" s="42"/>
+      <c r="AY25" s="42"/>
+      <c r="AZ25" s="42"/>
+      <c r="BA25" s="42"/>
     </row>
     <row r="26" spans="1:53" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="20" t="s">
@@ -2314,24 +2329,24 @@
       <c r="G26" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="O26" s="57"/>
-      <c r="P26" s="53"/>
-      <c r="Q26" s="53"/>
-      <c r="R26" s="53"/>
-      <c r="S26" s="53"/>
-      <c r="T26" s="53"/>
-      <c r="U26" s="53"/>
-      <c r="V26" s="53"/>
-      <c r="W26" s="53"/>
-      <c r="AE26" s="53"/>
-      <c r="AF26" s="53"/>
-      <c r="AG26" s="53"/>
-      <c r="AH26" s="53"/>
-      <c r="AI26" s="53"/>
-      <c r="AJ26" s="53"/>
-      <c r="AK26" s="53"/>
-      <c r="AL26" s="53"/>
-      <c r="AM26" s="61"/>
+      <c r="O26" s="44"/>
+      <c r="P26" s="43"/>
+      <c r="Q26" s="43"/>
+      <c r="R26" s="43"/>
+      <c r="S26" s="43"/>
+      <c r="T26" s="43"/>
+      <c r="U26" s="43"/>
+      <c r="V26" s="43"/>
+      <c r="W26" s="43"/>
+      <c r="AE26" s="43"/>
+      <c r="AF26" s="43"/>
+      <c r="AG26" s="43"/>
+      <c r="AH26" s="43"/>
+      <c r="AI26" s="43"/>
+      <c r="AJ26" s="43"/>
+      <c r="AK26" s="43"/>
+      <c r="AL26" s="43"/>
+      <c r="AM26" s="49"/>
       <c r="AU26" s="20" t="s">
         <v>2</v>
       </c>
@@ -2364,12 +2379,18 @@
       <c r="C27" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="D27" s="11"/>
+      <c r="D27" s="11">
+        <v>0</v>
+      </c>
       <c r="E27" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="F27" s="11"/>
-      <c r="G27" s="5"/>
+      <c r="F27" s="11">
+        <v>2</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>45</v>
+      </c>
       <c r="O27" s="12"/>
       <c r="X27" s="12"/>
       <c r="AD27" s="13"/>
@@ -2407,26 +2428,26 @@
       <c r="F28" s="13"/>
       <c r="G28" s="16"/>
       <c r="O28" s="12"/>
-      <c r="P28" s="45" t="s">
+      <c r="P28" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="Q28" s="46"/>
-      <c r="R28" s="46"/>
-      <c r="S28" s="46"/>
-      <c r="T28" s="46"/>
-      <c r="U28" s="46"/>
-      <c r="V28" s="47"/>
+      <c r="Q28" s="54"/>
+      <c r="R28" s="54"/>
+      <c r="S28" s="54"/>
+      <c r="T28" s="54"/>
+      <c r="U28" s="54"/>
+      <c r="V28" s="55"/>
       <c r="X28" s="12"/>
       <c r="AD28" s="13"/>
-      <c r="AF28" s="52" t="s">
+      <c r="AF28" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="AG28" s="52"/>
-      <c r="AH28" s="52"/>
-      <c r="AI28" s="52"/>
-      <c r="AJ28" s="52"/>
-      <c r="AK28" s="52"/>
-      <c r="AL28" s="52"/>
+      <c r="AG28" s="42"/>
+      <c r="AH28" s="42"/>
+      <c r="AI28" s="42"/>
+      <c r="AJ28" s="42"/>
+      <c r="AK28" s="42"/>
+      <c r="AL28" s="42"/>
       <c r="AN28" s="12"/>
       <c r="AU28" s="8">
         <v>2</v>
@@ -2538,9 +2559,9 @@
       </c>
       <c r="F30" s="31"/>
       <c r="G30" s="32"/>
-      <c r="I30" s="53"/>
-      <c r="J30" s="53"/>
-      <c r="K30" s="53"/>
+      <c r="I30" s="43"/>
+      <c r="J30" s="43"/>
+      <c r="K30" s="43"/>
       <c r="O30" s="12"/>
       <c r="P30" s="7">
         <v>1</v>
@@ -2563,9 +2584,9 @@
       <c r="AK30" s="24"/>
       <c r="AL30" s="25"/>
       <c r="AN30" s="12"/>
-      <c r="AQ30" s="53"/>
-      <c r="AR30" s="53"/>
-      <c r="AS30" s="53"/>
+      <c r="AQ30" s="43"/>
+      <c r="AR30" s="43"/>
+      <c r="AS30" s="43"/>
       <c r="AU30" s="38">
         <v>4</v>
       </c>
@@ -2753,15 +2774,15 @@
       <c r="BA33" s="6"/>
     </row>
     <row r="34" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="52" t="s">
+      <c r="A34" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B34" s="52"/>
-      <c r="C34" s="52"/>
-      <c r="D34" s="52"/>
-      <c r="E34" s="52"/>
-      <c r="F34" s="52"/>
-      <c r="G34" s="52"/>
+      <c r="B34" s="42"/>
+      <c r="C34" s="42"/>
+      <c r="D34" s="42"/>
+      <c r="E34" s="42"/>
+      <c r="F34" s="42"/>
+      <c r="G34" s="42"/>
       <c r="L34" s="12"/>
       <c r="O34" s="12"/>
       <c r="P34" s="8" t="s">
@@ -2786,15 +2807,15 @@
       <c r="AL34" s="16"/>
       <c r="AN34" s="12"/>
       <c r="AQ34" s="12"/>
-      <c r="AU34" s="52" t="s">
+      <c r="AU34" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AV34" s="52"/>
-      <c r="AW34" s="52"/>
-      <c r="AX34" s="52"/>
-      <c r="AY34" s="52"/>
-      <c r="AZ34" s="52"/>
-      <c r="BA34" s="52"/>
+      <c r="AV34" s="42"/>
+      <c r="AW34" s="42"/>
+      <c r="AX34" s="42"/>
+      <c r="AY34" s="42"/>
+      <c r="AZ34" s="42"/>
+      <c r="BA34" s="42"/>
     </row>
     <row r="35" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L35" s="12"/>
@@ -2823,18 +2844,18 @@
       <c r="AQ35" s="12"/>
     </row>
     <row r="36" spans="1:53" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="51" t="s">
+      <c r="A36" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="B36" s="51"/>
-      <c r="C36" s="51"/>
-      <c r="D36" s="51"/>
-      <c r="E36" s="51"/>
-      <c r="F36" s="51"/>
-      <c r="G36" s="51"/>
-      <c r="L36" s="57"/>
-      <c r="M36" s="53"/>
-      <c r="N36" s="53"/>
+      <c r="B36" s="45"/>
+      <c r="C36" s="45"/>
+      <c r="D36" s="45"/>
+      <c r="E36" s="45"/>
+      <c r="F36" s="45"/>
+      <c r="G36" s="45"/>
+      <c r="L36" s="44"/>
+      <c r="M36" s="43"/>
+      <c r="N36" s="43"/>
       <c r="O36" s="12"/>
       <c r="P36" s="8" t="s">
         <v>12</v>
@@ -2856,19 +2877,19 @@
       <c r="AJ36" s="35"/>
       <c r="AK36" s="36"/>
       <c r="AL36" s="37"/>
-      <c r="AN36" s="57"/>
-      <c r="AO36" s="53"/>
-      <c r="AP36" s="53"/>
+      <c r="AN36" s="44"/>
+      <c r="AO36" s="43"/>
+      <c r="AP36" s="43"/>
       <c r="AQ36" s="12"/>
-      <c r="AU36" s="51" t="s">
+      <c r="AU36" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="AV36" s="51"/>
-      <c r="AW36" s="51"/>
-      <c r="AX36" s="51"/>
-      <c r="AY36" s="51"/>
-      <c r="AZ36" s="51"/>
-      <c r="BA36" s="51"/>
+      <c r="AV36" s="45"/>
+      <c r="AW36" s="45"/>
+      <c r="AX36" s="45"/>
+      <c r="AY36" s="45"/>
+      <c r="AZ36" s="45"/>
+      <c r="BA36" s="45"/>
     </row>
     <row r="37" spans="1:53" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37" s="20" t="s">
@@ -2893,31 +2914,31 @@
         <v>9</v>
       </c>
       <c r="L37" s="12"/>
-      <c r="P37" s="48" t="s">
+      <c r="P37" s="56" t="s">
         <v>13</v>
       </c>
-      <c r="Q37" s="49"/>
-      <c r="R37" s="49"/>
-      <c r="S37" s="49"/>
-      <c r="T37" s="49"/>
-      <c r="U37" s="49"/>
-      <c r="V37" s="50"/>
-      <c r="X37" s="57"/>
-      <c r="Y37" s="53"/>
-      <c r="Z37" s="53"/>
-      <c r="AA37" s="53"/>
-      <c r="AB37" s="53"/>
-      <c r="AC37" s="53"/>
-      <c r="AD37" s="61"/>
-      <c r="AF37" s="52" t="s">
+      <c r="Q37" s="57"/>
+      <c r="R37" s="57"/>
+      <c r="S37" s="57"/>
+      <c r="T37" s="57"/>
+      <c r="U37" s="57"/>
+      <c r="V37" s="58"/>
+      <c r="X37" s="44"/>
+      <c r="Y37" s="43"/>
+      <c r="Z37" s="43"/>
+      <c r="AA37" s="43"/>
+      <c r="AB37" s="43"/>
+      <c r="AC37" s="43"/>
+      <c r="AD37" s="49"/>
+      <c r="AF37" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AG37" s="52"/>
-      <c r="AH37" s="52"/>
-      <c r="AI37" s="52"/>
-      <c r="AJ37" s="52"/>
-      <c r="AK37" s="52"/>
-      <c r="AL37" s="52"/>
+      <c r="AG37" s="42"/>
+      <c r="AH37" s="42"/>
+      <c r="AI37" s="42"/>
+      <c r="AJ37" s="42"/>
+      <c r="AK37" s="42"/>
+      <c r="AL37" s="42"/>
       <c r="AQ37" s="12"/>
       <c r="AU37" s="3" t="s">
         <v>2</v>
@@ -2951,12 +2972,18 @@
       <c r="C38" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="D38" s="11"/>
+      <c r="D38" s="11">
+        <v>3</v>
+      </c>
       <c r="E38" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="F38" s="11"/>
-      <c r="G38" s="5"/>
+      <c r="F38" s="11">
+        <v>2</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="L38" s="12"/>
       <c r="AQ38" s="12"/>
       <c r="AU38" s="7">
@@ -2992,33 +3019,33 @@
       <c r="F39" s="13"/>
       <c r="G39" s="16"/>
       <c r="L39" s="12"/>
-      <c r="M39" s="45" t="s">
+      <c r="M39" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="N39" s="46"/>
-      <c r="O39" s="46"/>
-      <c r="P39" s="46"/>
-      <c r="Q39" s="46"/>
-      <c r="R39" s="46"/>
-      <c r="S39" s="47"/>
-      <c r="X39" s="52" t="s">
+      <c r="N39" s="54"/>
+      <c r="O39" s="54"/>
+      <c r="P39" s="54"/>
+      <c r="Q39" s="54"/>
+      <c r="R39" s="54"/>
+      <c r="S39" s="55"/>
+      <c r="X39" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="Y39" s="52"/>
-      <c r="Z39" s="52"/>
-      <c r="AA39" s="52"/>
-      <c r="AB39" s="52"/>
-      <c r="AC39" s="52"/>
-      <c r="AD39" s="52"/>
-      <c r="AI39" s="45" t="s">
+      <c r="Y39" s="42"/>
+      <c r="Z39" s="42"/>
+      <c r="AA39" s="42"/>
+      <c r="AB39" s="42"/>
+      <c r="AC39" s="42"/>
+      <c r="AD39" s="42"/>
+      <c r="AI39" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="AJ39" s="46"/>
-      <c r="AK39" s="46"/>
-      <c r="AL39" s="46"/>
-      <c r="AM39" s="46"/>
-      <c r="AN39" s="46"/>
-      <c r="AO39" s="47"/>
+      <c r="AJ39" s="54"/>
+      <c r="AK39" s="54"/>
+      <c r="AL39" s="54"/>
+      <c r="AM39" s="54"/>
+      <c r="AN39" s="54"/>
+      <c r="AO39" s="55"/>
       <c r="AQ39" s="12"/>
       <c r="AU39" s="8">
         <v>2</v>
@@ -3149,9 +3176,9 @@
       </c>
       <c r="F41" s="31"/>
       <c r="G41" s="32"/>
-      <c r="I41" s="53"/>
-      <c r="J41" s="53"/>
-      <c r="K41" s="53"/>
+      <c r="I41" s="43"/>
+      <c r="J41" s="43"/>
+      <c r="K41" s="43"/>
       <c r="L41" s="12"/>
       <c r="M41" s="7">
         <v>1</v>
@@ -3180,9 +3207,9 @@
       <c r="AM41" s="23"/>
       <c r="AN41" s="24"/>
       <c r="AO41" s="25"/>
-      <c r="AQ41" s="57"/>
-      <c r="AR41" s="53"/>
-      <c r="AS41" s="53"/>
+      <c r="AQ41" s="44"/>
+      <c r="AR41" s="43"/>
+      <c r="AS41" s="43"/>
       <c r="AU41" s="38">
         <v>4</v>
       </c>
@@ -3377,15 +3404,15 @@
       <c r="BA44" s="6"/>
     </row>
     <row r="45" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="52" t="s">
+      <c r="A45" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B45" s="52"/>
-      <c r="C45" s="52"/>
-      <c r="D45" s="52"/>
-      <c r="E45" s="52"/>
-      <c r="F45" s="52"/>
-      <c r="G45" s="52"/>
+      <c r="B45" s="42"/>
+      <c r="C45" s="42"/>
+      <c r="D45" s="42"/>
+      <c r="E45" s="42"/>
+      <c r="F45" s="42"/>
+      <c r="G45" s="42"/>
       <c r="M45" s="8" t="s">
         <v>11</v>
       </c>
@@ -3413,15 +3440,15 @@
       <c r="AM45" s="12"/>
       <c r="AN45" s="13"/>
       <c r="AO45" s="16"/>
-      <c r="AU45" s="52" t="s">
+      <c r="AU45" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AV45" s="52"/>
-      <c r="AW45" s="52"/>
-      <c r="AX45" s="52"/>
-      <c r="AY45" s="52"/>
-      <c r="AZ45" s="52"/>
-      <c r="BA45" s="52"/>
+      <c r="AV45" s="42"/>
+      <c r="AW45" s="42"/>
+      <c r="AX45" s="42"/>
+      <c r="AY45" s="42"/>
+      <c r="AZ45" s="42"/>
+      <c r="BA45" s="42"/>
     </row>
     <row r="46" spans="1:53" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="M46" s="8" t="s">
@@ -3482,49 +3509,61 @@
       <c r="AO47" s="6"/>
     </row>
     <row r="48" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="M48" s="45" t="s">
+      <c r="M48" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="N48" s="46"/>
-      <c r="O48" s="46"/>
-      <c r="P48" s="46"/>
-      <c r="Q48" s="46"/>
-      <c r="R48" s="46"/>
-      <c r="S48" s="47"/>
-      <c r="X48" s="52" t="s">
+      <c r="N48" s="54"/>
+      <c r="O48" s="54"/>
+      <c r="P48" s="54"/>
+      <c r="Q48" s="54"/>
+      <c r="R48" s="54"/>
+      <c r="S48" s="55"/>
+      <c r="X48" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="Y48" s="52"/>
-      <c r="Z48" s="52"/>
-      <c r="AA48" s="52"/>
-      <c r="AB48" s="52"/>
-      <c r="AC48" s="52"/>
-      <c r="AD48" s="52"/>
-      <c r="AI48" s="52" t="s">
+      <c r="Y48" s="42"/>
+      <c r="Z48" s="42"/>
+      <c r="AA48" s="42"/>
+      <c r="AB48" s="42"/>
+      <c r="AC48" s="42"/>
+      <c r="AD48" s="42"/>
+      <c r="AI48" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AJ48" s="52"/>
-      <c r="AK48" s="52"/>
-      <c r="AL48" s="52"/>
-      <c r="AM48" s="52"/>
-      <c r="AN48" s="52"/>
-      <c r="AO48" s="52"/>
+      <c r="AJ48" s="42"/>
+      <c r="AK48" s="42"/>
+      <c r="AL48" s="42"/>
+      <c r="AM48" s="42"/>
+      <c r="AN48" s="42"/>
+      <c r="AO48" s="42"/>
     </row>
     <row r="49" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="AU45:BA45"/>
-    <mergeCell ref="AF28:AL28"/>
-    <mergeCell ref="AF37:AL37"/>
-    <mergeCell ref="AQ30:AS30"/>
-    <mergeCell ref="AQ41:AS41"/>
-    <mergeCell ref="AU34:BA34"/>
-    <mergeCell ref="AU36:BA36"/>
-    <mergeCell ref="AU2:BA2"/>
-    <mergeCell ref="AU3:BA3"/>
-    <mergeCell ref="AU12:BA12"/>
-    <mergeCell ref="AU14:BA14"/>
-    <mergeCell ref="AU23:BA23"/>
+    <mergeCell ref="M48:S48"/>
+    <mergeCell ref="M39:S39"/>
+    <mergeCell ref="P37:V37"/>
+    <mergeCell ref="P28:V28"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A1:U1"/>
+    <mergeCell ref="O26:W26"/>
+    <mergeCell ref="I41:K41"/>
+    <mergeCell ref="L14:N14"/>
+    <mergeCell ref="L36:N36"/>
+    <mergeCell ref="M2:R2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="M4:S4"/>
+    <mergeCell ref="M13:S13"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="A25:G25"/>
     <mergeCell ref="X37:AD37"/>
     <mergeCell ref="AE26:AM26"/>
     <mergeCell ref="Z1:AB1"/>
@@ -3541,30 +3580,18 @@
     <mergeCell ref="AN36:AP36"/>
     <mergeCell ref="AQ8:AS8"/>
     <mergeCell ref="AQ19:AS19"/>
-    <mergeCell ref="A1:U1"/>
-    <mergeCell ref="O26:W26"/>
-    <mergeCell ref="I41:K41"/>
-    <mergeCell ref="L14:N14"/>
-    <mergeCell ref="L36:N36"/>
-    <mergeCell ref="M2:R2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="M4:S4"/>
-    <mergeCell ref="M13:S13"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A23:G23"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="M48:S48"/>
-    <mergeCell ref="M39:S39"/>
-    <mergeCell ref="P37:V37"/>
-    <mergeCell ref="P28:V28"/>
-    <mergeCell ref="A36:G36"/>
-    <mergeCell ref="A45:G45"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="AU2:BA2"/>
+    <mergeCell ref="AU3:BA3"/>
+    <mergeCell ref="AU12:BA12"/>
+    <mergeCell ref="AU14:BA14"/>
+    <mergeCell ref="AU23:BA23"/>
+    <mergeCell ref="AU45:BA45"/>
+    <mergeCell ref="AF28:AL28"/>
+    <mergeCell ref="AF37:AL37"/>
+    <mergeCell ref="AQ30:AS30"/>
+    <mergeCell ref="AQ41:AS41"/>
+    <mergeCell ref="AU34:BA34"/>
+    <mergeCell ref="AU36:BA36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/2025_2026/Playoffs/Brackets.xlsx
+++ b/2025_2026/Playoffs/Brackets.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\NHLStats\2025_2026\Playoffs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DF58263-D0EB-46B4-AE34-4D743E74537F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EC26303-2FE5-4DE6-BE70-820EC07153A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Matchups" sheetId="3" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="60">
   <si>
     <t>Eastern Conference Playoff Teams</t>
   </si>
@@ -170,6 +170,42 @@
   </si>
   <si>
     <t>Wild Lead 1-0</t>
+  </si>
+  <si>
+    <t>Avalanche Lead 1-0</t>
+  </si>
+  <si>
+    <t>OT</t>
+  </si>
+  <si>
+    <t>Canadiens Lead 1-0</t>
+  </si>
+  <si>
+    <t>Sabres Lead 1-0</t>
+  </si>
+  <si>
+    <t>Golden Knights Lead 1-0</t>
+  </si>
+  <si>
+    <t>Flyers Lead 2-0</t>
+  </si>
+  <si>
+    <t>2OT</t>
+  </si>
+  <si>
+    <t>Hurricanes Lead 2-0</t>
+  </si>
+  <si>
+    <t>Series Tied 1-1</t>
+  </si>
+  <si>
+    <t>Oilers Lead 1-0</t>
+  </si>
+  <si>
+    <t>Avalanche Lead 2-0</t>
+  </si>
+  <si>
+    <t>Flyers Lead 3-0</t>
   </si>
 </sst>
 </file>
@@ -548,18 +584,45 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -572,40 +635,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -975,18 +1011,18 @@
     </row>
     <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="11" spans="1:7" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="59" t="s">
+      <c r="A11" s="61" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="59"/>
-      <c r="C11" s="59" t="s">
+      <c r="B11" s="61"/>
+      <c r="C11" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="59"/>
-      <c r="E11" s="59" t="s">
+      <c r="D11" s="61"/>
+      <c r="E11" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="59"/>
+      <c r="F11" s="61"/>
       <c r="G11" s="4" t="s">
         <v>18</v>
       </c>
@@ -1015,18 +1051,18 @@
       </c>
     </row>
     <row r="13" spans="1:7" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="60" t="s">
+      <c r="A13" s="59" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="61"/>
-      <c r="C13" s="60" t="s">
+      <c r="B13" s="60"/>
+      <c r="C13" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="D13" s="61"/>
-      <c r="E13" s="60" t="s">
+      <c r="D13" s="60"/>
+      <c r="E13" s="59" t="s">
         <v>17</v>
       </c>
-      <c r="F13" s="61"/>
+      <c r="F13" s="60"/>
       <c r="G13" s="5"/>
     </row>
     <row r="14" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1053,14 +1089,14 @@
       <c r="F15" s="6"/>
     </row>
     <row r="16" spans="1:7" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="60" t="s">
+      <c r="A16" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="61"/>
-      <c r="C16" s="60" t="s">
+      <c r="B16" s="60"/>
+      <c r="C16" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="61"/>
+      <c r="D16" s="60"/>
     </row>
     <row r="17" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
@@ -1082,10 +1118,10 @@
       <c r="D18" s="6"/>
     </row>
     <row r="19" spans="1:4" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="60" t="s">
+      <c r="A19" s="59" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="61"/>
+      <c r="B19" s="60"/>
     </row>
     <row r="20" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
@@ -1104,10 +1140,10 @@
       </c>
     </row>
     <row r="22" spans="1:4" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="60" t="s">
+      <c r="A22" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="61"/>
+      <c r="B22" s="60"/>
     </row>
     <row r="23" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
@@ -1192,16 +1228,16 @@
     <sortCondition ref="B2:B9"/>
   </sortState>
   <mergeCells count="10">
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A16:B16"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A16:B16"/>
   </mergeCells>
   <dataValidations count="16">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C14" xr:uid="{2C3D9587-ABAE-4E3F-8B22-396DF812BF02}">
@@ -1260,7 +1296,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:BA49"/>
+  <dimension ref="A1:BB49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -1304,127 +1340,127 @@
     <col min="54" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:53" ht="27.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="50" t="s">
+    <row r="1" spans="1:54" ht="27.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
-      <c r="I1" s="51"/>
-      <c r="J1" s="51"/>
-      <c r="K1" s="51"/>
-      <c r="L1" s="51"/>
-      <c r="M1" s="51"/>
-      <c r="N1" s="51"/>
-      <c r="O1" s="51"/>
-      <c r="P1" s="51"/>
-      <c r="Q1" s="51"/>
-      <c r="R1" s="51"/>
-      <c r="S1" s="51"/>
-      <c r="T1" s="51"/>
-      <c r="U1" s="52"/>
-      <c r="Z1" s="50" t="s">
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="52"/>
+      <c r="M1" s="52"/>
+      <c r="N1" s="52"/>
+      <c r="O1" s="52"/>
+      <c r="P1" s="52"/>
+      <c r="Q1" s="52"/>
+      <c r="R1" s="52"/>
+      <c r="S1" s="52"/>
+      <c r="T1" s="52"/>
+      <c r="U1" s="53"/>
+      <c r="Z1" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="AA1" s="51"/>
-      <c r="AB1" s="52"/>
-      <c r="AF1" s="50" t="s">
+      <c r="AA1" s="52"/>
+      <c r="AB1" s="53"/>
+      <c r="AF1" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="AG1" s="51"/>
-      <c r="AH1" s="51"/>
-      <c r="AI1" s="51"/>
-      <c r="AJ1" s="51"/>
-      <c r="AK1" s="51"/>
-      <c r="AL1" s="51"/>
-      <c r="AM1" s="51"/>
-      <c r="AN1" s="51"/>
-      <c r="AO1" s="51"/>
-      <c r="AP1" s="51"/>
-      <c r="AQ1" s="51"/>
-      <c r="AR1" s="51"/>
-      <c r="AS1" s="51"/>
-      <c r="AT1" s="51"/>
-      <c r="AU1" s="51"/>
-      <c r="AV1" s="51"/>
-      <c r="AW1" s="51"/>
-      <c r="AX1" s="51"/>
-      <c r="AY1" s="51"/>
-      <c r="AZ1" s="51"/>
-      <c r="BA1" s="52"/>
-    </row>
-    <row r="2" spans="1:53" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="46" t="s">
+      <c r="AG1" s="52"/>
+      <c r="AH1" s="52"/>
+      <c r="AI1" s="52"/>
+      <c r="AJ1" s="52"/>
+      <c r="AK1" s="52"/>
+      <c r="AL1" s="52"/>
+      <c r="AM1" s="52"/>
+      <c r="AN1" s="52"/>
+      <c r="AO1" s="52"/>
+      <c r="AP1" s="52"/>
+      <c r="AQ1" s="52"/>
+      <c r="AR1" s="52"/>
+      <c r="AS1" s="52"/>
+      <c r="AT1" s="52"/>
+      <c r="AU1" s="52"/>
+      <c r="AV1" s="52"/>
+      <c r="AW1" s="52"/>
+      <c r="AX1" s="52"/>
+      <c r="AY1" s="52"/>
+      <c r="AZ1" s="52"/>
+      <c r="BA1" s="53"/>
+    </row>
+    <row r="2" spans="1:54" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="48"/>
-      <c r="M2" s="46" t="s">
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="57"/>
+      <c r="M2" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="47"/>
-      <c r="O2" s="47"/>
-      <c r="P2" s="47"/>
-      <c r="Q2" s="47"/>
-      <c r="R2" s="48"/>
-      <c r="AI2" s="46" t="s">
+      <c r="N2" s="56"/>
+      <c r="O2" s="56"/>
+      <c r="P2" s="56"/>
+      <c r="Q2" s="56"/>
+      <c r="R2" s="57"/>
+      <c r="AI2" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="AJ2" s="47"/>
-      <c r="AK2" s="47"/>
-      <c r="AL2" s="47"/>
-      <c r="AM2" s="47"/>
-      <c r="AN2" s="47"/>
-      <c r="AO2" s="48"/>
-      <c r="AU2" s="46" t="s">
+      <c r="AJ2" s="56"/>
+      <c r="AK2" s="56"/>
+      <c r="AL2" s="56"/>
+      <c r="AM2" s="56"/>
+      <c r="AN2" s="56"/>
+      <c r="AO2" s="57"/>
+      <c r="AU2" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="AV2" s="47"/>
-      <c r="AW2" s="47"/>
-      <c r="AX2" s="47"/>
-      <c r="AY2" s="47"/>
-      <c r="AZ2" s="47"/>
-      <c r="BA2" s="48"/>
-    </row>
-    <row r="3" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="42" t="s">
+      <c r="AV2" s="56"/>
+      <c r="AW2" s="56"/>
+      <c r="AX2" s="56"/>
+      <c r="AY2" s="56"/>
+      <c r="AZ2" s="56"/>
+      <c r="BA2" s="57"/>
+    </row>
+    <row r="3" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="42"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="42"/>
-      <c r="AI3" s="53" t="s">
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="AI3" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="AJ3" s="54"/>
-      <c r="AK3" s="54"/>
-      <c r="AL3" s="54"/>
-      <c r="AM3" s="54"/>
-      <c r="AN3" s="54"/>
-      <c r="AO3" s="55"/>
-      <c r="AU3" s="42" t="s">
+      <c r="AJ3" s="43"/>
+      <c r="AK3" s="43"/>
+      <c r="AL3" s="43"/>
+      <c r="AM3" s="43"/>
+      <c r="AN3" s="43"/>
+      <c r="AO3" s="44"/>
+      <c r="AU3" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="AV3" s="42"/>
-      <c r="AW3" s="42"/>
-      <c r="AX3" s="42"/>
-      <c r="AY3" s="42"/>
-      <c r="AZ3" s="42"/>
-      <c r="BA3" s="42"/>
-    </row>
-    <row r="4" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="AV3" s="49"/>
+      <c r="AW3" s="49"/>
+      <c r="AX3" s="49"/>
+      <c r="AY3" s="49"/>
+      <c r="AZ3" s="49"/>
+      <c r="BA3" s="49"/>
+    </row>
+    <row r="4" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
@@ -1446,15 +1482,15 @@
       <c r="G4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="53" t="s">
+      <c r="M4" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="N4" s="54"/>
-      <c r="O4" s="54"/>
-      <c r="P4" s="54"/>
-      <c r="Q4" s="54"/>
-      <c r="R4" s="54"/>
-      <c r="S4" s="55"/>
+      <c r="N4" s="43"/>
+      <c r="O4" s="43"/>
+      <c r="P4" s="43"/>
+      <c r="Q4" s="43"/>
+      <c r="R4" s="43"/>
+      <c r="S4" s="44"/>
       <c r="AI4" s="3" t="s">
         <v>2</v>
       </c>
@@ -1498,7 +1534,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7">
         <v>1</v>
       </c>
@@ -1508,12 +1544,18 @@
       <c r="C5" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="11"/>
+      <c r="D5" s="11">
+        <v>3</v>
+      </c>
       <c r="E5" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="F5" s="11"/>
-      <c r="G5" s="5"/>
+      <c r="F5" s="11">
+        <v>4</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>51</v>
+      </c>
       <c r="M5" s="22" t="s">
         <v>2</v>
       </c>
@@ -1553,14 +1595,20 @@
       <c r="AW5" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="AX5" s="11"/>
+      <c r="AX5" s="11">
+        <v>1</v>
+      </c>
       <c r="AY5" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="AZ5" s="11"/>
-      <c r="BA5" s="5"/>
-    </row>
-    <row r="6" spans="1:53" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="AZ5" s="11">
+        <v>2</v>
+      </c>
+      <c r="BA5" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:54" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8">
         <v>2</v>
       </c>
@@ -1570,12 +1618,18 @@
       <c r="C6" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="13"/>
+      <c r="D6" s="13">
+        <v>4</v>
+      </c>
       <c r="E6" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="F6" s="13"/>
-      <c r="G6" s="16"/>
+      <c r="F6" s="13">
+        <v>2</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>56</v>
+      </c>
       <c r="M6" s="7">
         <v>1</v>
       </c>
@@ -1603,14 +1657,23 @@
       <c r="AW6" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="AX6" s="13"/>
+      <c r="AX6" s="13">
+        <v>1</v>
+      </c>
       <c r="AY6" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="AZ6" s="13"/>
-      <c r="BA6" s="16"/>
-    </row>
-    <row r="7" spans="1:53" x14ac:dyDescent="0.25">
+      <c r="AZ6" s="13">
+        <v>2</v>
+      </c>
+      <c r="BA6" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="BB6" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A7" s="8">
         <v>3</v>
       </c>
@@ -1660,7 +1723,7 @@
       <c r="AZ7" s="13"/>
       <c r="BA7" s="16"/>
     </row>
-    <row r="8" spans="1:53" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:54" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="8">
         <v>4</v>
       </c>
@@ -1676,9 +1739,9 @@
       </c>
       <c r="F8" s="13"/>
       <c r="G8" s="16"/>
-      <c r="I8" s="43"/>
-      <c r="J8" s="43"/>
-      <c r="K8" s="43"/>
+      <c r="I8" s="50"/>
+      <c r="J8" s="50"/>
+      <c r="K8" s="50"/>
       <c r="M8" s="8">
         <v>3</v>
       </c>
@@ -1697,9 +1760,9 @@
       <c r="AM8" s="30"/>
       <c r="AN8" s="31"/>
       <c r="AO8" s="16"/>
-      <c r="AQ8" s="43"/>
-      <c r="AR8" s="43"/>
-      <c r="AS8" s="43"/>
+      <c r="AQ8" s="50"/>
+      <c r="AR8" s="50"/>
+      <c r="AS8" s="50"/>
       <c r="AU8" s="38">
         <v>4</v>
       </c>
@@ -1716,7 +1779,7 @@
       <c r="AZ8" s="31"/>
       <c r="BA8" s="32"/>
     </row>
-    <row r="9" spans="1:53" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:54" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>11</v>
       </c>
@@ -1770,7 +1833,7 @@
       <c r="AZ9" s="13"/>
       <c r="BA9" s="32"/>
     </row>
-    <row r="10" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>10</v>
       </c>
@@ -1822,7 +1885,7 @@
       <c r="AZ10" s="13"/>
       <c r="BA10" s="16"/>
     </row>
-    <row r="11" spans="1:53" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:54" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
         <v>12</v>
       </c>
@@ -1874,16 +1937,16 @@
       <c r="AZ11" s="15"/>
       <c r="BA11" s="6"/>
     </row>
-    <row r="12" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="42" t="s">
+    <row r="12" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="42"/>
-      <c r="C12" s="42"/>
-      <c r="D12" s="42"/>
-      <c r="E12" s="42"/>
-      <c r="F12" s="42"/>
-      <c r="G12" s="42"/>
+      <c r="B12" s="49"/>
+      <c r="C12" s="49"/>
+      <c r="D12" s="49"/>
+      <c r="E12" s="49"/>
+      <c r="F12" s="49"/>
+      <c r="G12" s="49"/>
       <c r="L12" s="12"/>
       <c r="M12" s="8" t="s">
         <v>12</v>
@@ -1894,67 +1957,67 @@
       <c r="Q12" s="12"/>
       <c r="R12" s="13"/>
       <c r="S12" s="16"/>
-      <c r="AI12" s="42" t="s">
+      <c r="AI12" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AJ12" s="42"/>
-      <c r="AK12" s="42"/>
-      <c r="AL12" s="42"/>
-      <c r="AM12" s="42"/>
-      <c r="AN12" s="42"/>
-      <c r="AO12" s="42"/>
+      <c r="AJ12" s="49"/>
+      <c r="AK12" s="49"/>
+      <c r="AL12" s="49"/>
+      <c r="AM12" s="49"/>
+      <c r="AN12" s="49"/>
+      <c r="AO12" s="49"/>
       <c r="AQ12" s="12"/>
-      <c r="AU12" s="42" t="s">
+      <c r="AU12" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AV12" s="42"/>
-      <c r="AW12" s="42"/>
-      <c r="AX12" s="42"/>
-      <c r="AY12" s="42"/>
-      <c r="AZ12" s="42"/>
-      <c r="BA12" s="42"/>
-    </row>
-    <row r="13" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="AV12" s="49"/>
+      <c r="AW12" s="49"/>
+      <c r="AX12" s="49"/>
+      <c r="AY12" s="49"/>
+      <c r="AZ12" s="49"/>
+      <c r="BA12" s="49"/>
+    </row>
+    <row r="13" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L13" s="12"/>
-      <c r="M13" s="53" t="s">
+      <c r="M13" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="N13" s="54"/>
-      <c r="O13" s="54"/>
-      <c r="P13" s="54"/>
-      <c r="Q13" s="54"/>
-      <c r="R13" s="54"/>
-      <c r="S13" s="55"/>
+      <c r="N13" s="43"/>
+      <c r="O13" s="43"/>
+      <c r="P13" s="43"/>
+      <c r="Q13" s="43"/>
+      <c r="R13" s="43"/>
+      <c r="S13" s="44"/>
       <c r="AQ13" s="12"/>
     </row>
-    <row r="14" spans="1:53" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="45" t="s">
+    <row r="14" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="45"/>
-      <c r="C14" s="45"/>
-      <c r="D14" s="45"/>
-      <c r="E14" s="45"/>
-      <c r="F14" s="45"/>
-      <c r="G14" s="45"/>
-      <c r="L14" s="44"/>
-      <c r="M14" s="43"/>
-      <c r="N14" s="43"/>
-      <c r="AN14" s="43"/>
-      <c r="AO14" s="43"/>
-      <c r="AP14" s="43"/>
+      <c r="B14" s="48"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="48"/>
+      <c r="E14" s="48"/>
+      <c r="F14" s="48"/>
+      <c r="G14" s="48"/>
+      <c r="L14" s="54"/>
+      <c r="M14" s="50"/>
+      <c r="N14" s="50"/>
+      <c r="AN14" s="50"/>
+      <c r="AO14" s="50"/>
+      <c r="AP14" s="50"/>
       <c r="AQ14" s="12"/>
-      <c r="AU14" s="45" t="s">
+      <c r="AU14" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="AV14" s="45"/>
-      <c r="AW14" s="45"/>
-      <c r="AX14" s="45"/>
-      <c r="AY14" s="45"/>
-      <c r="AZ14" s="45"/>
-      <c r="BA14" s="45"/>
-    </row>
-    <row r="15" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="AV14" s="48"/>
+      <c r="AW14" s="48"/>
+      <c r="AX14" s="48"/>
+      <c r="AY14" s="48"/>
+      <c r="AZ14" s="48"/>
+      <c r="BA14" s="48"/>
+    </row>
+    <row r="15" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>2</v>
       </c>
@@ -2002,7 +2065,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:53" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:54" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7">
         <v>1</v>
       </c>
@@ -2012,12 +2075,21 @@
       <c r="C16" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="D16" s="11"/>
+      <c r="D16" s="11">
+        <v>4</v>
+      </c>
       <c r="E16" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="F16" s="11"/>
-      <c r="G16" s="5"/>
+      <c r="F16" s="11">
+        <v>3</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="L16" s="12"/>
       <c r="O16" s="12"/>
       <c r="AN16" s="12"/>
@@ -2054,12 +2126,21 @@
       <c r="C17" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="D17" s="13"/>
+      <c r="D17" s="13">
+        <v>2</v>
+      </c>
       <c r="E17" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="F17" s="13"/>
-      <c r="G17" s="16"/>
+      <c r="F17" s="13">
+        <v>3</v>
+      </c>
+      <c r="G17" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="L17" s="12"/>
       <c r="O17" s="12"/>
       <c r="AN17" s="12"/>
@@ -2073,12 +2154,18 @@
       <c r="AW17" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="AX17" s="13"/>
+      <c r="AX17" s="13">
+        <v>2</v>
+      </c>
       <c r="AY17" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="AZ17" s="13"/>
-      <c r="BA17" s="16"/>
+      <c r="AZ17" s="13">
+        <v>4</v>
+      </c>
+      <c r="BA17" s="16" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="18" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A18" s="8">
@@ -2132,15 +2219,15 @@
       </c>
       <c r="F19" s="31"/>
       <c r="G19" s="32"/>
-      <c r="I19" s="43"/>
-      <c r="J19" s="43"/>
-      <c r="K19" s="43"/>
+      <c r="I19" s="50"/>
+      <c r="J19" s="50"/>
+      <c r="K19" s="50"/>
       <c r="L19" s="12"/>
       <c r="O19" s="12"/>
       <c r="AN19" s="12"/>
-      <c r="AQ19" s="44"/>
-      <c r="AR19" s="43"/>
-      <c r="AS19" s="43"/>
+      <c r="AQ19" s="54"/>
+      <c r="AR19" s="50"/>
+      <c r="AS19" s="50"/>
       <c r="AU19" s="38">
         <v>4</v>
       </c>
@@ -2260,52 +2347,52 @@
       <c r="BA22" s="6"/>
     </row>
     <row r="23" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="42" t="s">
+      <c r="A23" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="B23" s="42"/>
-      <c r="C23" s="42"/>
-      <c r="D23" s="42"/>
-      <c r="E23" s="42"/>
-      <c r="F23" s="42"/>
-      <c r="G23" s="42"/>
+      <c r="B23" s="49"/>
+      <c r="C23" s="49"/>
+      <c r="D23" s="49"/>
+      <c r="E23" s="49"/>
+      <c r="F23" s="49"/>
+      <c r="G23" s="49"/>
       <c r="O23" s="12"/>
       <c r="AN23" s="12"/>
-      <c r="AU23" s="42" t="s">
+      <c r="AU23" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AV23" s="42"/>
-      <c r="AW23" s="42"/>
-      <c r="AX23" s="42"/>
-      <c r="AY23" s="42"/>
-      <c r="AZ23" s="42"/>
-      <c r="BA23" s="42"/>
+      <c r="AV23" s="49"/>
+      <c r="AW23" s="49"/>
+      <c r="AX23" s="49"/>
+      <c r="AY23" s="49"/>
+      <c r="AZ23" s="49"/>
+      <c r="BA23" s="49"/>
     </row>
     <row r="24" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="O24" s="12"/>
       <c r="AN24" s="12"/>
     </row>
     <row r="25" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="42" t="s">
+      <c r="A25" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="42"/>
-      <c r="C25" s="42"/>
-      <c r="D25" s="42"/>
-      <c r="E25" s="42"/>
-      <c r="F25" s="42"/>
-      <c r="G25" s="42"/>
+      <c r="B25" s="49"/>
+      <c r="C25" s="49"/>
+      <c r="D25" s="49"/>
+      <c r="E25" s="49"/>
+      <c r="F25" s="49"/>
+      <c r="G25" s="49"/>
       <c r="O25" s="12"/>
       <c r="AN25" s="12"/>
-      <c r="AU25" s="42" t="s">
+      <c r="AU25" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="AV25" s="42"/>
-      <c r="AW25" s="42"/>
-      <c r="AX25" s="42"/>
-      <c r="AY25" s="42"/>
-      <c r="AZ25" s="42"/>
-      <c r="BA25" s="42"/>
+      <c r="AV25" s="49"/>
+      <c r="AW25" s="49"/>
+      <c r="AX25" s="49"/>
+      <c r="AY25" s="49"/>
+      <c r="AZ25" s="49"/>
+      <c r="BA25" s="49"/>
     </row>
     <row r="26" spans="1:53" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="20" t="s">
@@ -2329,24 +2416,24 @@
       <c r="G26" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="O26" s="44"/>
-      <c r="P26" s="43"/>
-      <c r="Q26" s="43"/>
-      <c r="R26" s="43"/>
-      <c r="S26" s="43"/>
-      <c r="T26" s="43"/>
-      <c r="U26" s="43"/>
-      <c r="V26" s="43"/>
-      <c r="W26" s="43"/>
-      <c r="AE26" s="43"/>
-      <c r="AF26" s="43"/>
-      <c r="AG26" s="43"/>
-      <c r="AH26" s="43"/>
-      <c r="AI26" s="43"/>
-      <c r="AJ26" s="43"/>
-      <c r="AK26" s="43"/>
-      <c r="AL26" s="43"/>
-      <c r="AM26" s="49"/>
+      <c r="O26" s="54"/>
+      <c r="P26" s="50"/>
+      <c r="Q26" s="50"/>
+      <c r="R26" s="50"/>
+      <c r="S26" s="50"/>
+      <c r="T26" s="50"/>
+      <c r="U26" s="50"/>
+      <c r="V26" s="50"/>
+      <c r="W26" s="50"/>
+      <c r="AE26" s="50"/>
+      <c r="AF26" s="50"/>
+      <c r="AG26" s="50"/>
+      <c r="AH26" s="50"/>
+      <c r="AI26" s="50"/>
+      <c r="AJ26" s="50"/>
+      <c r="AK26" s="50"/>
+      <c r="AL26" s="50"/>
+      <c r="AM26" s="58"/>
       <c r="AU26" s="20" t="s">
         <v>2</v>
       </c>
@@ -2404,12 +2491,18 @@
       <c r="AW27" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AX27" s="11"/>
+      <c r="AX27" s="11">
+        <v>2</v>
+      </c>
       <c r="AY27" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="AZ27" s="11"/>
-      <c r="BA27" s="5"/>
+      <c r="AZ27" s="11">
+        <v>4</v>
+      </c>
+      <c r="BA27" s="5" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="28" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="8">
@@ -2421,33 +2514,42 @@
       <c r="C28" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="D28" s="13"/>
+      <c r="D28" s="13">
+        <v>2</v>
+      </c>
       <c r="E28" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="F28" s="13"/>
-      <c r="G28" s="16"/>
+      <c r="F28" s="13">
+        <v>3</v>
+      </c>
+      <c r="G28" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>54</v>
+      </c>
       <c r="O28" s="12"/>
-      <c r="P28" s="53" t="s">
+      <c r="P28" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="Q28" s="54"/>
-      <c r="R28" s="54"/>
-      <c r="S28" s="54"/>
-      <c r="T28" s="54"/>
-      <c r="U28" s="54"/>
-      <c r="V28" s="55"/>
+      <c r="Q28" s="43"/>
+      <c r="R28" s="43"/>
+      <c r="S28" s="43"/>
+      <c r="T28" s="43"/>
+      <c r="U28" s="43"/>
+      <c r="V28" s="44"/>
       <c r="X28" s="12"/>
       <c r="AD28" s="13"/>
-      <c r="AF28" s="42" t="s">
+      <c r="AF28" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="AG28" s="42"/>
-      <c r="AH28" s="42"/>
-      <c r="AI28" s="42"/>
-      <c r="AJ28" s="42"/>
-      <c r="AK28" s="42"/>
-      <c r="AL28" s="42"/>
+      <c r="AG28" s="49"/>
+      <c r="AH28" s="49"/>
+      <c r="AI28" s="49"/>
+      <c r="AJ28" s="49"/>
+      <c r="AK28" s="49"/>
+      <c r="AL28" s="49"/>
       <c r="AN28" s="12"/>
       <c r="AU28" s="8">
         <v>2</v>
@@ -2458,12 +2560,18 @@
       <c r="AW28" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="AX28" s="13"/>
+      <c r="AX28" s="13">
+        <v>3</v>
+      </c>
       <c r="AY28" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="AZ28" s="13"/>
-      <c r="BA28" s="16"/>
+      <c r="AZ28" s="13">
+        <v>2</v>
+      </c>
+      <c r="BA28" s="16" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="29" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="8">
@@ -2559,9 +2667,9 @@
       </c>
       <c r="F30" s="31"/>
       <c r="G30" s="32"/>
-      <c r="I30" s="43"/>
-      <c r="J30" s="43"/>
-      <c r="K30" s="43"/>
+      <c r="I30" s="50"/>
+      <c r="J30" s="50"/>
+      <c r="K30" s="50"/>
       <c r="O30" s="12"/>
       <c r="P30" s="7">
         <v>1</v>
@@ -2584,9 +2692,9 @@
       <c r="AK30" s="24"/>
       <c r="AL30" s="25"/>
       <c r="AN30" s="12"/>
-      <c r="AQ30" s="43"/>
-      <c r="AR30" s="43"/>
-      <c r="AS30" s="43"/>
+      <c r="AQ30" s="50"/>
+      <c r="AR30" s="50"/>
+      <c r="AS30" s="50"/>
       <c r="AU30" s="38">
         <v>4</v>
       </c>
@@ -2774,15 +2882,15 @@
       <c r="BA33" s="6"/>
     </row>
     <row r="34" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="42" t="s">
+      <c r="A34" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="B34" s="42"/>
-      <c r="C34" s="42"/>
-      <c r="D34" s="42"/>
-      <c r="E34" s="42"/>
-      <c r="F34" s="42"/>
-      <c r="G34" s="42"/>
+      <c r="B34" s="49"/>
+      <c r="C34" s="49"/>
+      <c r="D34" s="49"/>
+      <c r="E34" s="49"/>
+      <c r="F34" s="49"/>
+      <c r="G34" s="49"/>
       <c r="L34" s="12"/>
       <c r="O34" s="12"/>
       <c r="P34" s="8" t="s">
@@ -2807,15 +2915,15 @@
       <c r="AL34" s="16"/>
       <c r="AN34" s="12"/>
       <c r="AQ34" s="12"/>
-      <c r="AU34" s="42" t="s">
+      <c r="AU34" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AV34" s="42"/>
-      <c r="AW34" s="42"/>
-      <c r="AX34" s="42"/>
-      <c r="AY34" s="42"/>
-      <c r="AZ34" s="42"/>
-      <c r="BA34" s="42"/>
+      <c r="AV34" s="49"/>
+      <c r="AW34" s="49"/>
+      <c r="AX34" s="49"/>
+      <c r="AY34" s="49"/>
+      <c r="AZ34" s="49"/>
+      <c r="BA34" s="49"/>
     </row>
     <row r="35" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L35" s="12"/>
@@ -2844,18 +2952,18 @@
       <c r="AQ35" s="12"/>
     </row>
     <row r="36" spans="1:53" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="45" t="s">
+      <c r="A36" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="B36" s="45"/>
-      <c r="C36" s="45"/>
-      <c r="D36" s="45"/>
-      <c r="E36" s="45"/>
-      <c r="F36" s="45"/>
-      <c r="G36" s="45"/>
-      <c r="L36" s="44"/>
-      <c r="M36" s="43"/>
-      <c r="N36" s="43"/>
+      <c r="B36" s="48"/>
+      <c r="C36" s="48"/>
+      <c r="D36" s="48"/>
+      <c r="E36" s="48"/>
+      <c r="F36" s="48"/>
+      <c r="G36" s="48"/>
+      <c r="L36" s="54"/>
+      <c r="M36" s="50"/>
+      <c r="N36" s="50"/>
       <c r="O36" s="12"/>
       <c r="P36" s="8" t="s">
         <v>12</v>
@@ -2877,19 +2985,19 @@
       <c r="AJ36" s="35"/>
       <c r="AK36" s="36"/>
       <c r="AL36" s="37"/>
-      <c r="AN36" s="44"/>
-      <c r="AO36" s="43"/>
-      <c r="AP36" s="43"/>
+      <c r="AN36" s="54"/>
+      <c r="AO36" s="50"/>
+      <c r="AP36" s="50"/>
       <c r="AQ36" s="12"/>
-      <c r="AU36" s="45" t="s">
+      <c r="AU36" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="AV36" s="45"/>
-      <c r="AW36" s="45"/>
-      <c r="AX36" s="45"/>
-      <c r="AY36" s="45"/>
-      <c r="AZ36" s="45"/>
-      <c r="BA36" s="45"/>
+      <c r="AV36" s="48"/>
+      <c r="AW36" s="48"/>
+      <c r="AX36" s="48"/>
+      <c r="AY36" s="48"/>
+      <c r="AZ36" s="48"/>
+      <c r="BA36" s="48"/>
     </row>
     <row r="37" spans="1:53" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37" s="20" t="s">
@@ -2914,31 +3022,31 @@
         <v>9</v>
       </c>
       <c r="L37" s="12"/>
-      <c r="P37" s="56" t="s">
+      <c r="P37" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="Q37" s="57"/>
-      <c r="R37" s="57"/>
-      <c r="S37" s="57"/>
-      <c r="T37" s="57"/>
-      <c r="U37" s="57"/>
-      <c r="V37" s="58"/>
-      <c r="X37" s="44"/>
-      <c r="Y37" s="43"/>
-      <c r="Z37" s="43"/>
-      <c r="AA37" s="43"/>
-      <c r="AB37" s="43"/>
-      <c r="AC37" s="43"/>
-      <c r="AD37" s="49"/>
-      <c r="AF37" s="42" t="s">
+      <c r="Q37" s="46"/>
+      <c r="R37" s="46"/>
+      <c r="S37" s="46"/>
+      <c r="T37" s="46"/>
+      <c r="U37" s="46"/>
+      <c r="V37" s="47"/>
+      <c r="X37" s="54"/>
+      <c r="Y37" s="50"/>
+      <c r="Z37" s="50"/>
+      <c r="AA37" s="50"/>
+      <c r="AB37" s="50"/>
+      <c r="AC37" s="50"/>
+      <c r="AD37" s="58"/>
+      <c r="AF37" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AG37" s="42"/>
-      <c r="AH37" s="42"/>
-      <c r="AI37" s="42"/>
-      <c r="AJ37" s="42"/>
-      <c r="AK37" s="42"/>
-      <c r="AL37" s="42"/>
+      <c r="AG37" s="49"/>
+      <c r="AH37" s="49"/>
+      <c r="AI37" s="49"/>
+      <c r="AJ37" s="49"/>
+      <c r="AK37" s="49"/>
+      <c r="AL37" s="49"/>
       <c r="AQ37" s="12"/>
       <c r="AU37" s="3" t="s">
         <v>2</v>
@@ -2995,12 +3103,18 @@
       <c r="AW38" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="AX38" s="11"/>
+      <c r="AX38" s="11">
+        <v>3</v>
+      </c>
       <c r="AY38" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="AZ38" s="11"/>
-      <c r="BA38" s="5"/>
+      <c r="AZ38" s="11">
+        <v>4</v>
+      </c>
+      <c r="BA38" s="5" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="39" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="8">
@@ -3012,40 +3126,46 @@
       <c r="C39" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D39" s="13"/>
+      <c r="D39" s="13">
+        <v>3</v>
+      </c>
       <c r="E39" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="F39" s="13"/>
-      <c r="G39" s="16"/>
+      <c r="F39" s="13">
+        <v>0</v>
+      </c>
+      <c r="G39" s="16" t="s">
+        <v>53</v>
+      </c>
       <c r="L39" s="12"/>
-      <c r="M39" s="53" t="s">
+      <c r="M39" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="N39" s="54"/>
-      <c r="O39" s="54"/>
-      <c r="P39" s="54"/>
-      <c r="Q39" s="54"/>
-      <c r="R39" s="54"/>
-      <c r="S39" s="55"/>
-      <c r="X39" s="42" t="s">
+      <c r="N39" s="43"/>
+      <c r="O39" s="43"/>
+      <c r="P39" s="43"/>
+      <c r="Q39" s="43"/>
+      <c r="R39" s="43"/>
+      <c r="S39" s="44"/>
+      <c r="X39" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="Y39" s="42"/>
-      <c r="Z39" s="42"/>
-      <c r="AA39" s="42"/>
-      <c r="AB39" s="42"/>
-      <c r="AC39" s="42"/>
-      <c r="AD39" s="42"/>
-      <c r="AI39" s="53" t="s">
+      <c r="Y39" s="49"/>
+      <c r="Z39" s="49"/>
+      <c r="AA39" s="49"/>
+      <c r="AB39" s="49"/>
+      <c r="AC39" s="49"/>
+      <c r="AD39" s="49"/>
+      <c r="AI39" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="AJ39" s="54"/>
-      <c r="AK39" s="54"/>
-      <c r="AL39" s="54"/>
-      <c r="AM39" s="54"/>
-      <c r="AN39" s="54"/>
-      <c r="AO39" s="55"/>
+      <c r="AJ39" s="43"/>
+      <c r="AK39" s="43"/>
+      <c r="AL39" s="43"/>
+      <c r="AM39" s="43"/>
+      <c r="AN39" s="43"/>
+      <c r="AO39" s="44"/>
       <c r="AQ39" s="12"/>
       <c r="AU39" s="8">
         <v>2</v>
@@ -3056,12 +3176,18 @@
       <c r="AW39" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="AX39" s="13"/>
+      <c r="AX39" s="13">
+        <v>6</v>
+      </c>
       <c r="AY39" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="AZ39" s="13"/>
-      <c r="BA39" s="16"/>
+      <c r="AZ39" s="13">
+        <v>4</v>
+      </c>
+      <c r="BA39" s="16" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="40" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="8">
@@ -3073,12 +3199,18 @@
       <c r="C40" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="D40" s="13"/>
+      <c r="D40" s="13">
+        <v>2</v>
+      </c>
       <c r="E40" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="F40" s="13"/>
-      <c r="G40" s="16"/>
+      <c r="F40" s="13">
+        <v>5</v>
+      </c>
+      <c r="G40" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="L40" s="12"/>
       <c r="M40" s="22" t="s">
         <v>2</v>
@@ -3176,9 +3308,9 @@
       </c>
       <c r="F41" s="31"/>
       <c r="G41" s="32"/>
-      <c r="I41" s="43"/>
-      <c r="J41" s="43"/>
-      <c r="K41" s="43"/>
+      <c r="I41" s="50"/>
+      <c r="J41" s="50"/>
+      <c r="K41" s="50"/>
       <c r="L41" s="12"/>
       <c r="M41" s="7">
         <v>1</v>
@@ -3207,9 +3339,9 @@
       <c r="AM41" s="23"/>
       <c r="AN41" s="24"/>
       <c r="AO41" s="25"/>
-      <c r="AQ41" s="44"/>
-      <c r="AR41" s="43"/>
-      <c r="AS41" s="43"/>
+      <c r="AQ41" s="54"/>
+      <c r="AR41" s="50"/>
+      <c r="AS41" s="50"/>
       <c r="AU41" s="38">
         <v>4</v>
       </c>
@@ -3404,15 +3536,15 @@
       <c r="BA44" s="6"/>
     </row>
     <row r="45" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="42" t="s">
+      <c r="A45" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="B45" s="42"/>
-      <c r="C45" s="42"/>
-      <c r="D45" s="42"/>
-      <c r="E45" s="42"/>
-      <c r="F45" s="42"/>
-      <c r="G45" s="42"/>
+      <c r="B45" s="49"/>
+      <c r="C45" s="49"/>
+      <c r="D45" s="49"/>
+      <c r="E45" s="49"/>
+      <c r="F45" s="49"/>
+      <c r="G45" s="49"/>
       <c r="M45" s="8" t="s">
         <v>11</v>
       </c>
@@ -3440,15 +3572,15 @@
       <c r="AM45" s="12"/>
       <c r="AN45" s="13"/>
       <c r="AO45" s="16"/>
-      <c r="AU45" s="42" t="s">
+      <c r="AU45" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AV45" s="42"/>
-      <c r="AW45" s="42"/>
-      <c r="AX45" s="42"/>
-      <c r="AY45" s="42"/>
-      <c r="AZ45" s="42"/>
-      <c r="BA45" s="42"/>
+      <c r="AV45" s="49"/>
+      <c r="AW45" s="49"/>
+      <c r="AX45" s="49"/>
+      <c r="AY45" s="49"/>
+      <c r="AZ45" s="49"/>
+      <c r="BA45" s="49"/>
     </row>
     <row r="46" spans="1:53" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="M46" s="8" t="s">
@@ -3509,45 +3641,65 @@
       <c r="AO47" s="6"/>
     </row>
     <row r="48" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="M48" s="53" t="s">
+      <c r="M48" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="N48" s="54"/>
-      <c r="O48" s="54"/>
-      <c r="P48" s="54"/>
-      <c r="Q48" s="54"/>
-      <c r="R48" s="54"/>
-      <c r="S48" s="55"/>
-      <c r="X48" s="42" t="s">
+      <c r="N48" s="43"/>
+      <c r="O48" s="43"/>
+      <c r="P48" s="43"/>
+      <c r="Q48" s="43"/>
+      <c r="R48" s="43"/>
+      <c r="S48" s="44"/>
+      <c r="X48" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="Y48" s="42"/>
-      <c r="Z48" s="42"/>
-      <c r="AA48" s="42"/>
-      <c r="AB48" s="42"/>
-      <c r="AC48" s="42"/>
-      <c r="AD48" s="42"/>
-      <c r="AI48" s="42" t="s">
+      <c r="Y48" s="49"/>
+      <c r="Z48" s="49"/>
+      <c r="AA48" s="49"/>
+      <c r="AB48" s="49"/>
+      <c r="AC48" s="49"/>
+      <c r="AD48" s="49"/>
+      <c r="AI48" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AJ48" s="42"/>
-      <c r="AK48" s="42"/>
-      <c r="AL48" s="42"/>
-      <c r="AM48" s="42"/>
-      <c r="AN48" s="42"/>
-      <c r="AO48" s="42"/>
+      <c r="AJ48" s="49"/>
+      <c r="AK48" s="49"/>
+      <c r="AL48" s="49"/>
+      <c r="AM48" s="49"/>
+      <c r="AN48" s="49"/>
+      <c r="AO48" s="49"/>
     </row>
     <row r="49" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="M48:S48"/>
-    <mergeCell ref="M39:S39"/>
-    <mergeCell ref="P37:V37"/>
-    <mergeCell ref="P28:V28"/>
-    <mergeCell ref="A36:G36"/>
-    <mergeCell ref="A45:G45"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="AU45:BA45"/>
+    <mergeCell ref="AF28:AL28"/>
+    <mergeCell ref="AF37:AL37"/>
+    <mergeCell ref="AQ30:AS30"/>
+    <mergeCell ref="AQ41:AS41"/>
+    <mergeCell ref="AU34:BA34"/>
+    <mergeCell ref="AU36:BA36"/>
+    <mergeCell ref="AU2:BA2"/>
+    <mergeCell ref="AU3:BA3"/>
+    <mergeCell ref="AU12:BA12"/>
+    <mergeCell ref="AU14:BA14"/>
+    <mergeCell ref="AU23:BA23"/>
+    <mergeCell ref="X37:AD37"/>
+    <mergeCell ref="AE26:AM26"/>
+    <mergeCell ref="Z1:AB1"/>
+    <mergeCell ref="X39:AD39"/>
+    <mergeCell ref="X48:AD48"/>
+    <mergeCell ref="AF1:BA1"/>
+    <mergeCell ref="AI2:AO2"/>
+    <mergeCell ref="AI3:AO3"/>
+    <mergeCell ref="AI12:AO12"/>
+    <mergeCell ref="AI39:AO39"/>
+    <mergeCell ref="AU25:BA25"/>
+    <mergeCell ref="AI48:AO48"/>
+    <mergeCell ref="AN14:AP14"/>
+    <mergeCell ref="AN36:AP36"/>
+    <mergeCell ref="AQ8:AS8"/>
+    <mergeCell ref="AQ19:AS19"/>
     <mergeCell ref="A1:U1"/>
     <mergeCell ref="O26:W26"/>
     <mergeCell ref="I41:K41"/>
@@ -3564,34 +3716,14 @@
     <mergeCell ref="I8:K8"/>
     <mergeCell ref="I19:K19"/>
     <mergeCell ref="A25:G25"/>
-    <mergeCell ref="X37:AD37"/>
-    <mergeCell ref="AE26:AM26"/>
-    <mergeCell ref="Z1:AB1"/>
-    <mergeCell ref="X39:AD39"/>
-    <mergeCell ref="X48:AD48"/>
-    <mergeCell ref="AF1:BA1"/>
-    <mergeCell ref="AI2:AO2"/>
-    <mergeCell ref="AI3:AO3"/>
-    <mergeCell ref="AI12:AO12"/>
-    <mergeCell ref="AI39:AO39"/>
-    <mergeCell ref="AU25:BA25"/>
-    <mergeCell ref="AI48:AO48"/>
-    <mergeCell ref="AN14:AP14"/>
-    <mergeCell ref="AN36:AP36"/>
-    <mergeCell ref="AQ8:AS8"/>
-    <mergeCell ref="AQ19:AS19"/>
-    <mergeCell ref="AU2:BA2"/>
-    <mergeCell ref="AU3:BA3"/>
-    <mergeCell ref="AU12:BA12"/>
-    <mergeCell ref="AU14:BA14"/>
-    <mergeCell ref="AU23:BA23"/>
-    <mergeCell ref="AU45:BA45"/>
-    <mergeCell ref="AF28:AL28"/>
-    <mergeCell ref="AF37:AL37"/>
-    <mergeCell ref="AQ30:AS30"/>
-    <mergeCell ref="AQ41:AS41"/>
-    <mergeCell ref="AU34:BA34"/>
-    <mergeCell ref="AU36:BA36"/>
+    <mergeCell ref="M48:S48"/>
+    <mergeCell ref="M39:S39"/>
+    <mergeCell ref="P37:V37"/>
+    <mergeCell ref="P28:V28"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="A34:G34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/2025_2026/Playoffs/Brackets.xlsx
+++ b/2025_2026/Playoffs/Brackets.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\NHLStats\2025_2026\Playoffs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EC26303-2FE5-4DE6-BE70-820EC07153A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28CB2692-EFA9-4C40-A921-FF7AF51D293C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Matchups" sheetId="3" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="61">
   <si>
     <t>Eastern Conference Playoff Teams</t>
   </si>
@@ -206,6 +206,9 @@
   </si>
   <si>
     <t>Flyers Lead 3-0</t>
+  </si>
+  <si>
+    <t>Stars Lead 2-1</t>
   </si>
 </sst>
 </file>
@@ -584,6 +587,39 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -602,46 +638,13 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1011,18 +1014,18 @@
     </row>
     <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="11" spans="1:7" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="61" t="s">
+      <c r="A11" s="59" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="61"/>
-      <c r="C11" s="61" t="s">
+      <c r="B11" s="59"/>
+      <c r="C11" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="61"/>
-      <c r="E11" s="61" t="s">
+      <c r="D11" s="59"/>
+      <c r="E11" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="61"/>
+      <c r="F11" s="59"/>
       <c r="G11" s="4" t="s">
         <v>18</v>
       </c>
@@ -1051,18 +1054,18 @@
       </c>
     </row>
     <row r="13" spans="1:7" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="59" t="s">
+      <c r="A13" s="60" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="60"/>
-      <c r="C13" s="59" t="s">
+      <c r="B13" s="61"/>
+      <c r="C13" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="D13" s="60"/>
-      <c r="E13" s="59" t="s">
+      <c r="D13" s="61"/>
+      <c r="E13" s="60" t="s">
         <v>17</v>
       </c>
-      <c r="F13" s="60"/>
+      <c r="F13" s="61"/>
       <c r="G13" s="5"/>
     </row>
     <row r="14" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1089,14 +1092,14 @@
       <c r="F15" s="6"/>
     </row>
     <row r="16" spans="1:7" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="59" t="s">
+      <c r="A16" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="60"/>
-      <c r="C16" s="59" t="s">
+      <c r="B16" s="61"/>
+      <c r="C16" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="60"/>
+      <c r="D16" s="61"/>
     </row>
     <row r="17" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
@@ -1118,10 +1121,10 @@
       <c r="D18" s="6"/>
     </row>
     <row r="19" spans="1:4" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="59" t="s">
+      <c r="A19" s="60" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="60"/>
+      <c r="B19" s="61"/>
     </row>
     <row r="20" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
@@ -1140,10 +1143,10 @@
       </c>
     </row>
     <row r="22" spans="1:4" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="59" t="s">
+      <c r="A22" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="60"/>
+      <c r="B22" s="61"/>
     </row>
     <row r="23" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
@@ -1228,16 +1231,16 @@
     <sortCondition ref="B2:B9"/>
   </sortState>
   <mergeCells count="10">
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C16:D16"/>
     <mergeCell ref="E11:F11"/>
     <mergeCell ref="E13:F13"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C16:D16"/>
   </mergeCells>
   <dataValidations count="16">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C14" xr:uid="{2C3D9587-ABAE-4E3F-8B22-396DF812BF02}">
@@ -1341,124 +1344,124 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:54" ht="27.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
-      <c r="M1" s="52"/>
-      <c r="N1" s="52"/>
-      <c r="O1" s="52"/>
-      <c r="P1" s="52"/>
-      <c r="Q1" s="52"/>
-      <c r="R1" s="52"/>
-      <c r="S1" s="52"/>
-      <c r="T1" s="52"/>
-      <c r="U1" s="53"/>
-      <c r="Z1" s="51" t="s">
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
+      <c r="K1" s="51"/>
+      <c r="L1" s="51"/>
+      <c r="M1" s="51"/>
+      <c r="N1" s="51"/>
+      <c r="O1" s="51"/>
+      <c r="P1" s="51"/>
+      <c r="Q1" s="51"/>
+      <c r="R1" s="51"/>
+      <c r="S1" s="51"/>
+      <c r="T1" s="51"/>
+      <c r="U1" s="52"/>
+      <c r="Z1" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="AA1" s="52"/>
-      <c r="AB1" s="53"/>
-      <c r="AF1" s="51" t="s">
+      <c r="AA1" s="51"/>
+      <c r="AB1" s="52"/>
+      <c r="AF1" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="AG1" s="52"/>
-      <c r="AH1" s="52"/>
-      <c r="AI1" s="52"/>
-      <c r="AJ1" s="52"/>
-      <c r="AK1" s="52"/>
-      <c r="AL1" s="52"/>
-      <c r="AM1" s="52"/>
-      <c r="AN1" s="52"/>
-      <c r="AO1" s="52"/>
-      <c r="AP1" s="52"/>
-      <c r="AQ1" s="52"/>
-      <c r="AR1" s="52"/>
-      <c r="AS1" s="52"/>
-      <c r="AT1" s="52"/>
-      <c r="AU1" s="52"/>
-      <c r="AV1" s="52"/>
-      <c r="AW1" s="52"/>
-      <c r="AX1" s="52"/>
-      <c r="AY1" s="52"/>
-      <c r="AZ1" s="52"/>
-      <c r="BA1" s="53"/>
+      <c r="AG1" s="51"/>
+      <c r="AH1" s="51"/>
+      <c r="AI1" s="51"/>
+      <c r="AJ1" s="51"/>
+      <c r="AK1" s="51"/>
+      <c r="AL1" s="51"/>
+      <c r="AM1" s="51"/>
+      <c r="AN1" s="51"/>
+      <c r="AO1" s="51"/>
+      <c r="AP1" s="51"/>
+      <c r="AQ1" s="51"/>
+      <c r="AR1" s="51"/>
+      <c r="AS1" s="51"/>
+      <c r="AT1" s="51"/>
+      <c r="AU1" s="51"/>
+      <c r="AV1" s="51"/>
+      <c r="AW1" s="51"/>
+      <c r="AX1" s="51"/>
+      <c r="AY1" s="51"/>
+      <c r="AZ1" s="51"/>
+      <c r="BA1" s="52"/>
     </row>
     <row r="2" spans="1:54" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="55" t="s">
+      <c r="A2" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="57"/>
-      <c r="M2" s="55" t="s">
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="48"/>
+      <c r="M2" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="56"/>
-      <c r="O2" s="56"/>
-      <c r="P2" s="56"/>
-      <c r="Q2" s="56"/>
-      <c r="R2" s="57"/>
-      <c r="AI2" s="55" t="s">
+      <c r="N2" s="47"/>
+      <c r="O2" s="47"/>
+      <c r="P2" s="47"/>
+      <c r="Q2" s="47"/>
+      <c r="R2" s="48"/>
+      <c r="AI2" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="AJ2" s="56"/>
-      <c r="AK2" s="56"/>
-      <c r="AL2" s="56"/>
-      <c r="AM2" s="56"/>
-      <c r="AN2" s="56"/>
-      <c r="AO2" s="57"/>
-      <c r="AU2" s="55" t="s">
+      <c r="AJ2" s="47"/>
+      <c r="AK2" s="47"/>
+      <c r="AL2" s="47"/>
+      <c r="AM2" s="47"/>
+      <c r="AN2" s="47"/>
+      <c r="AO2" s="48"/>
+      <c r="AU2" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="AV2" s="56"/>
-      <c r="AW2" s="56"/>
-      <c r="AX2" s="56"/>
-      <c r="AY2" s="56"/>
-      <c r="AZ2" s="56"/>
-      <c r="BA2" s="57"/>
+      <c r="AV2" s="47"/>
+      <c r="AW2" s="47"/>
+      <c r="AX2" s="47"/>
+      <c r="AY2" s="47"/>
+      <c r="AZ2" s="47"/>
+      <c r="BA2" s="48"/>
     </row>
     <row r="3" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="49" t="s">
+      <c r="A3" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="49"/>
-      <c r="C3" s="49"/>
-      <c r="D3" s="49"/>
-      <c r="E3" s="49"/>
-      <c r="F3" s="49"/>
-      <c r="G3" s="49"/>
-      <c r="AI3" s="42" t="s">
+      <c r="B3" s="42"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="42"/>
+      <c r="AI3" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="AJ3" s="43"/>
-      <c r="AK3" s="43"/>
-      <c r="AL3" s="43"/>
-      <c r="AM3" s="43"/>
-      <c r="AN3" s="43"/>
-      <c r="AO3" s="44"/>
-      <c r="AU3" s="49" t="s">
+      <c r="AJ3" s="54"/>
+      <c r="AK3" s="54"/>
+      <c r="AL3" s="54"/>
+      <c r="AM3" s="54"/>
+      <c r="AN3" s="54"/>
+      <c r="AO3" s="55"/>
+      <c r="AU3" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="AV3" s="49"/>
-      <c r="AW3" s="49"/>
-      <c r="AX3" s="49"/>
-      <c r="AY3" s="49"/>
-      <c r="AZ3" s="49"/>
-      <c r="BA3" s="49"/>
+      <c r="AV3" s="42"/>
+      <c r="AW3" s="42"/>
+      <c r="AX3" s="42"/>
+      <c r="AY3" s="42"/>
+      <c r="AZ3" s="42"/>
+      <c r="BA3" s="42"/>
     </row>
     <row r="4" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
@@ -1482,15 +1485,15 @@
       <c r="G4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="42" t="s">
+      <c r="M4" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="N4" s="43"/>
-      <c r="O4" s="43"/>
-      <c r="P4" s="43"/>
-      <c r="Q4" s="43"/>
-      <c r="R4" s="43"/>
-      <c r="S4" s="44"/>
+      <c r="N4" s="54"/>
+      <c r="O4" s="54"/>
+      <c r="P4" s="54"/>
+      <c r="Q4" s="54"/>
+      <c r="R4" s="54"/>
+      <c r="S4" s="55"/>
       <c r="AI4" s="3" t="s">
         <v>2</v>
       </c>
@@ -1739,9 +1742,9 @@
       </c>
       <c r="F8" s="13"/>
       <c r="G8" s="16"/>
-      <c r="I8" s="50"/>
-      <c r="J8" s="50"/>
-      <c r="K8" s="50"/>
+      <c r="I8" s="43"/>
+      <c r="J8" s="43"/>
+      <c r="K8" s="43"/>
       <c r="M8" s="8">
         <v>3</v>
       </c>
@@ -1760,9 +1763,9 @@
       <c r="AM8" s="30"/>
       <c r="AN8" s="31"/>
       <c r="AO8" s="16"/>
-      <c r="AQ8" s="50"/>
-      <c r="AR8" s="50"/>
-      <c r="AS8" s="50"/>
+      <c r="AQ8" s="43"/>
+      <c r="AR8" s="43"/>
+      <c r="AS8" s="43"/>
       <c r="AU8" s="38">
         <v>4</v>
       </c>
@@ -1938,15 +1941,15 @@
       <c r="BA11" s="6"/>
     </row>
     <row r="12" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="49" t="s">
+      <c r="A12" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="49"/>
-      <c r="C12" s="49"/>
-      <c r="D12" s="49"/>
-      <c r="E12" s="49"/>
-      <c r="F12" s="49"/>
-      <c r="G12" s="49"/>
+      <c r="B12" s="42"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="42"/>
       <c r="L12" s="12"/>
       <c r="M12" s="8" t="s">
         <v>12</v>
@@ -1957,65 +1960,65 @@
       <c r="Q12" s="12"/>
       <c r="R12" s="13"/>
       <c r="S12" s="16"/>
-      <c r="AI12" s="49" t="s">
+      <c r="AI12" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AJ12" s="49"/>
-      <c r="AK12" s="49"/>
-      <c r="AL12" s="49"/>
-      <c r="AM12" s="49"/>
-      <c r="AN12" s="49"/>
-      <c r="AO12" s="49"/>
+      <c r="AJ12" s="42"/>
+      <c r="AK12" s="42"/>
+      <c r="AL12" s="42"/>
+      <c r="AM12" s="42"/>
+      <c r="AN12" s="42"/>
+      <c r="AO12" s="42"/>
       <c r="AQ12" s="12"/>
-      <c r="AU12" s="49" t="s">
+      <c r="AU12" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AV12" s="49"/>
-      <c r="AW12" s="49"/>
-      <c r="AX12" s="49"/>
-      <c r="AY12" s="49"/>
-      <c r="AZ12" s="49"/>
-      <c r="BA12" s="49"/>
+      <c r="AV12" s="42"/>
+      <c r="AW12" s="42"/>
+      <c r="AX12" s="42"/>
+      <c r="AY12" s="42"/>
+      <c r="AZ12" s="42"/>
+      <c r="BA12" s="42"/>
     </row>
     <row r="13" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L13" s="12"/>
-      <c r="M13" s="42" t="s">
+      <c r="M13" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="N13" s="43"/>
-      <c r="O13" s="43"/>
-      <c r="P13" s="43"/>
-      <c r="Q13" s="43"/>
-      <c r="R13" s="43"/>
-      <c r="S13" s="44"/>
+      <c r="N13" s="54"/>
+      <c r="O13" s="54"/>
+      <c r="P13" s="54"/>
+      <c r="Q13" s="54"/>
+      <c r="R13" s="54"/>
+      <c r="S13" s="55"/>
       <c r="AQ13" s="12"/>
     </row>
     <row r="14" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="48" t="s">
+      <c r="A14" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="48"/>
-      <c r="C14" s="48"/>
-      <c r="D14" s="48"/>
-      <c r="E14" s="48"/>
-      <c r="F14" s="48"/>
-      <c r="G14" s="48"/>
-      <c r="L14" s="54"/>
-      <c r="M14" s="50"/>
-      <c r="N14" s="50"/>
-      <c r="AN14" s="50"/>
-      <c r="AO14" s="50"/>
-      <c r="AP14" s="50"/>
+      <c r="B14" s="45"/>
+      <c r="C14" s="45"/>
+      <c r="D14" s="45"/>
+      <c r="E14" s="45"/>
+      <c r="F14" s="45"/>
+      <c r="G14" s="45"/>
+      <c r="L14" s="44"/>
+      <c r="M14" s="43"/>
+      <c r="N14" s="43"/>
+      <c r="AN14" s="43"/>
+      <c r="AO14" s="43"/>
+      <c r="AP14" s="43"/>
       <c r="AQ14" s="12"/>
-      <c r="AU14" s="48" t="s">
+      <c r="AU14" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="AV14" s="48"/>
-      <c r="AW14" s="48"/>
-      <c r="AX14" s="48"/>
-      <c r="AY14" s="48"/>
-      <c r="AZ14" s="48"/>
-      <c r="BA14" s="48"/>
+      <c r="AV14" s="45"/>
+      <c r="AW14" s="45"/>
+      <c r="AX14" s="45"/>
+      <c r="AY14" s="45"/>
+      <c r="AZ14" s="45"/>
+      <c r="BA14" s="45"/>
     </row>
     <row r="15" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
@@ -2116,7 +2119,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A17" s="8">
         <v>2</v>
       </c>
@@ -2167,7 +2170,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="18" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A18" s="8">
         <v>3</v>
       </c>
@@ -2196,14 +2199,23 @@
       <c r="AW18" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="AX18" s="13"/>
+      <c r="AX18" s="13">
+        <v>4</v>
+      </c>
       <c r="AY18" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="AZ18" s="13"/>
-      <c r="BA18" s="16"/>
-    </row>
-    <row r="19" spans="1:53" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AZ18" s="13">
+        <v>3</v>
+      </c>
+      <c r="BA18" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="BB18" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="19" spans="1:54" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="8">
         <v>4</v>
       </c>
@@ -2219,15 +2231,15 @@
       </c>
       <c r="F19" s="31"/>
       <c r="G19" s="32"/>
-      <c r="I19" s="50"/>
-      <c r="J19" s="50"/>
-      <c r="K19" s="50"/>
+      <c r="I19" s="43"/>
+      <c r="J19" s="43"/>
+      <c r="K19" s="43"/>
       <c r="L19" s="12"/>
       <c r="O19" s="12"/>
       <c r="AN19" s="12"/>
-      <c r="AQ19" s="54"/>
-      <c r="AR19" s="50"/>
-      <c r="AS19" s="50"/>
+      <c r="AQ19" s="44"/>
+      <c r="AR19" s="43"/>
+      <c r="AS19" s="43"/>
       <c r="AU19" s="38">
         <v>4</v>
       </c>
@@ -2244,7 +2256,7 @@
       <c r="AZ19" s="31"/>
       <c r="BA19" s="32"/>
     </row>
-    <row r="20" spans="1:53" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:54" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
         <v>11</v>
       </c>
@@ -2278,7 +2290,7 @@
       <c r="AZ20" s="13"/>
       <c r="BA20" s="16"/>
     </row>
-    <row r="21" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
         <v>10</v>
       </c>
@@ -2312,7 +2324,7 @@
       <c r="AZ21" s="13"/>
       <c r="BA21" s="16"/>
     </row>
-    <row r="22" spans="1:53" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:54" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
         <v>12</v>
       </c>
@@ -2346,55 +2358,55 @@
       <c r="AZ22" s="15"/>
       <c r="BA22" s="6"/>
     </row>
-    <row r="23" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="49" t="s">
+    <row r="23" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B23" s="49"/>
-      <c r="C23" s="49"/>
-      <c r="D23" s="49"/>
-      <c r="E23" s="49"/>
-      <c r="F23" s="49"/>
-      <c r="G23" s="49"/>
+      <c r="B23" s="42"/>
+      <c r="C23" s="42"/>
+      <c r="D23" s="42"/>
+      <c r="E23" s="42"/>
+      <c r="F23" s="42"/>
+      <c r="G23" s="42"/>
       <c r="O23" s="12"/>
       <c r="AN23" s="12"/>
-      <c r="AU23" s="49" t="s">
+      <c r="AU23" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AV23" s="49"/>
-      <c r="AW23" s="49"/>
-      <c r="AX23" s="49"/>
-      <c r="AY23" s="49"/>
-      <c r="AZ23" s="49"/>
-      <c r="BA23" s="49"/>
-    </row>
-    <row r="24" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="AV23" s="42"/>
+      <c r="AW23" s="42"/>
+      <c r="AX23" s="42"/>
+      <c r="AY23" s="42"/>
+      <c r="AZ23" s="42"/>
+      <c r="BA23" s="42"/>
+    </row>
+    <row r="24" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="O24" s="12"/>
       <c r="AN24" s="12"/>
     </row>
-    <row r="25" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="49" t="s">
+    <row r="25" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="49"/>
-      <c r="C25" s="49"/>
-      <c r="D25" s="49"/>
-      <c r="E25" s="49"/>
-      <c r="F25" s="49"/>
-      <c r="G25" s="49"/>
+      <c r="B25" s="42"/>
+      <c r="C25" s="42"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="42"/>
+      <c r="F25" s="42"/>
+      <c r="G25" s="42"/>
       <c r="O25" s="12"/>
       <c r="AN25" s="12"/>
-      <c r="AU25" s="49" t="s">
+      <c r="AU25" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="AV25" s="49"/>
-      <c r="AW25" s="49"/>
-      <c r="AX25" s="49"/>
-      <c r="AY25" s="49"/>
-      <c r="AZ25" s="49"/>
-      <c r="BA25" s="49"/>
-    </row>
-    <row r="26" spans="1:53" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AV25" s="42"/>
+      <c r="AW25" s="42"/>
+      <c r="AX25" s="42"/>
+      <c r="AY25" s="42"/>
+      <c r="AZ25" s="42"/>
+      <c r="BA25" s="42"/>
+    </row>
+    <row r="26" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="20" t="s">
         <v>2</v>
       </c>
@@ -2416,24 +2428,24 @@
       <c r="G26" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="O26" s="54"/>
-      <c r="P26" s="50"/>
-      <c r="Q26" s="50"/>
-      <c r="R26" s="50"/>
-      <c r="S26" s="50"/>
-      <c r="T26" s="50"/>
-      <c r="U26" s="50"/>
-      <c r="V26" s="50"/>
-      <c r="W26" s="50"/>
-      <c r="AE26" s="50"/>
-      <c r="AF26" s="50"/>
-      <c r="AG26" s="50"/>
-      <c r="AH26" s="50"/>
-      <c r="AI26" s="50"/>
-      <c r="AJ26" s="50"/>
-      <c r="AK26" s="50"/>
-      <c r="AL26" s="50"/>
-      <c r="AM26" s="58"/>
+      <c r="O26" s="44"/>
+      <c r="P26" s="43"/>
+      <c r="Q26" s="43"/>
+      <c r="R26" s="43"/>
+      <c r="S26" s="43"/>
+      <c r="T26" s="43"/>
+      <c r="U26" s="43"/>
+      <c r="V26" s="43"/>
+      <c r="W26" s="43"/>
+      <c r="AE26" s="43"/>
+      <c r="AF26" s="43"/>
+      <c r="AG26" s="43"/>
+      <c r="AH26" s="43"/>
+      <c r="AI26" s="43"/>
+      <c r="AJ26" s="43"/>
+      <c r="AK26" s="43"/>
+      <c r="AL26" s="43"/>
+      <c r="AM26" s="49"/>
       <c r="AU26" s="20" t="s">
         <v>2</v>
       </c>
@@ -2456,7 +2468,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="7">
         <v>1</v>
       </c>
@@ -2504,7 +2516,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="28" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="8">
         <v>2</v>
       </c>
@@ -2530,26 +2542,26 @@
         <v>54</v>
       </c>
       <c r="O28" s="12"/>
-      <c r="P28" s="42" t="s">
+      <c r="P28" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="Q28" s="43"/>
-      <c r="R28" s="43"/>
-      <c r="S28" s="43"/>
-      <c r="T28" s="43"/>
-      <c r="U28" s="43"/>
-      <c r="V28" s="44"/>
+      <c r="Q28" s="54"/>
+      <c r="R28" s="54"/>
+      <c r="S28" s="54"/>
+      <c r="T28" s="54"/>
+      <c r="U28" s="54"/>
+      <c r="V28" s="55"/>
       <c r="X28" s="12"/>
       <c r="AD28" s="13"/>
-      <c r="AF28" s="49" t="s">
+      <c r="AF28" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="AG28" s="49"/>
-      <c r="AH28" s="49"/>
-      <c r="AI28" s="49"/>
-      <c r="AJ28" s="49"/>
-      <c r="AK28" s="49"/>
-      <c r="AL28" s="49"/>
+      <c r="AG28" s="42"/>
+      <c r="AH28" s="42"/>
+      <c r="AI28" s="42"/>
+      <c r="AJ28" s="42"/>
+      <c r="AK28" s="42"/>
+      <c r="AL28" s="42"/>
       <c r="AN28" s="12"/>
       <c r="AU28" s="8">
         <v>2</v>
@@ -2573,7 +2585,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="29" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="8">
         <v>3</v>
       </c>
@@ -2651,7 +2663,7 @@
       <c r="AZ29" s="13"/>
       <c r="BA29" s="16"/>
     </row>
-    <row r="30" spans="1:53" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A30" s="8">
         <v>4</v>
       </c>
@@ -2667,9 +2679,9 @@
       </c>
       <c r="F30" s="31"/>
       <c r="G30" s="32"/>
-      <c r="I30" s="50"/>
-      <c r="J30" s="50"/>
-      <c r="K30" s="50"/>
+      <c r="I30" s="43"/>
+      <c r="J30" s="43"/>
+      <c r="K30" s="43"/>
       <c r="O30" s="12"/>
       <c r="P30" s="7">
         <v>1</v>
@@ -2692,9 +2704,9 @@
       <c r="AK30" s="24"/>
       <c r="AL30" s="25"/>
       <c r="AN30" s="12"/>
-      <c r="AQ30" s="50"/>
-      <c r="AR30" s="50"/>
-      <c r="AS30" s="50"/>
+      <c r="AQ30" s="43"/>
+      <c r="AR30" s="43"/>
+      <c r="AS30" s="43"/>
       <c r="AU30" s="38">
         <v>4</v>
       </c>
@@ -2711,7 +2723,7 @@
       <c r="AZ30" s="31"/>
       <c r="BA30" s="32"/>
     </row>
-    <row r="31" spans="1:53" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:54" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
         <v>11</v>
       </c>
@@ -2769,7 +2781,7 @@
       <c r="AZ31" s="13"/>
       <c r="BA31" s="16"/>
     </row>
-    <row r="32" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A32" s="8" t="s">
         <v>10</v>
       </c>
@@ -2882,15 +2894,15 @@
       <c r="BA33" s="6"/>
     </row>
     <row r="34" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="49" t="s">
+      <c r="A34" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B34" s="49"/>
-      <c r="C34" s="49"/>
-      <c r="D34" s="49"/>
-      <c r="E34" s="49"/>
-      <c r="F34" s="49"/>
-      <c r="G34" s="49"/>
+      <c r="B34" s="42"/>
+      <c r="C34" s="42"/>
+      <c r="D34" s="42"/>
+      <c r="E34" s="42"/>
+      <c r="F34" s="42"/>
+      <c r="G34" s="42"/>
       <c r="L34" s="12"/>
       <c r="O34" s="12"/>
       <c r="P34" s="8" t="s">
@@ -2915,15 +2927,15 @@
       <c r="AL34" s="16"/>
       <c r="AN34" s="12"/>
       <c r="AQ34" s="12"/>
-      <c r="AU34" s="49" t="s">
+      <c r="AU34" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AV34" s="49"/>
-      <c r="AW34" s="49"/>
-      <c r="AX34" s="49"/>
-      <c r="AY34" s="49"/>
-      <c r="AZ34" s="49"/>
-      <c r="BA34" s="49"/>
+      <c r="AV34" s="42"/>
+      <c r="AW34" s="42"/>
+      <c r="AX34" s="42"/>
+      <c r="AY34" s="42"/>
+      <c r="AZ34" s="42"/>
+      <c r="BA34" s="42"/>
     </row>
     <row r="35" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L35" s="12"/>
@@ -2952,18 +2964,18 @@
       <c r="AQ35" s="12"/>
     </row>
     <row r="36" spans="1:53" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="48" t="s">
+      <c r="A36" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="B36" s="48"/>
-      <c r="C36" s="48"/>
-      <c r="D36" s="48"/>
-      <c r="E36" s="48"/>
-      <c r="F36" s="48"/>
-      <c r="G36" s="48"/>
-      <c r="L36" s="54"/>
-      <c r="M36" s="50"/>
-      <c r="N36" s="50"/>
+      <c r="B36" s="45"/>
+      <c r="C36" s="45"/>
+      <c r="D36" s="45"/>
+      <c r="E36" s="45"/>
+      <c r="F36" s="45"/>
+      <c r="G36" s="45"/>
+      <c r="L36" s="44"/>
+      <c r="M36" s="43"/>
+      <c r="N36" s="43"/>
       <c r="O36" s="12"/>
       <c r="P36" s="8" t="s">
         <v>12</v>
@@ -2985,19 +2997,19 @@
       <c r="AJ36" s="35"/>
       <c r="AK36" s="36"/>
       <c r="AL36" s="37"/>
-      <c r="AN36" s="54"/>
-      <c r="AO36" s="50"/>
-      <c r="AP36" s="50"/>
+      <c r="AN36" s="44"/>
+      <c r="AO36" s="43"/>
+      <c r="AP36" s="43"/>
       <c r="AQ36" s="12"/>
-      <c r="AU36" s="48" t="s">
+      <c r="AU36" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="AV36" s="48"/>
-      <c r="AW36" s="48"/>
-      <c r="AX36" s="48"/>
-      <c r="AY36" s="48"/>
-      <c r="AZ36" s="48"/>
-      <c r="BA36" s="48"/>
+      <c r="AV36" s="45"/>
+      <c r="AW36" s="45"/>
+      <c r="AX36" s="45"/>
+      <c r="AY36" s="45"/>
+      <c r="AZ36" s="45"/>
+      <c r="BA36" s="45"/>
     </row>
     <row r="37" spans="1:53" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37" s="20" t="s">
@@ -3022,31 +3034,31 @@
         <v>9</v>
       </c>
       <c r="L37" s="12"/>
-      <c r="P37" s="45" t="s">
+      <c r="P37" s="56" t="s">
         <v>13</v>
       </c>
-      <c r="Q37" s="46"/>
-      <c r="R37" s="46"/>
-      <c r="S37" s="46"/>
-      <c r="T37" s="46"/>
-      <c r="U37" s="46"/>
-      <c r="V37" s="47"/>
-      <c r="X37" s="54"/>
-      <c r="Y37" s="50"/>
-      <c r="Z37" s="50"/>
-      <c r="AA37" s="50"/>
-      <c r="AB37" s="50"/>
-      <c r="AC37" s="50"/>
-      <c r="AD37" s="58"/>
-      <c r="AF37" s="49" t="s">
+      <c r="Q37" s="57"/>
+      <c r="R37" s="57"/>
+      <c r="S37" s="57"/>
+      <c r="T37" s="57"/>
+      <c r="U37" s="57"/>
+      <c r="V37" s="58"/>
+      <c r="X37" s="44"/>
+      <c r="Y37" s="43"/>
+      <c r="Z37" s="43"/>
+      <c r="AA37" s="43"/>
+      <c r="AB37" s="43"/>
+      <c r="AC37" s="43"/>
+      <c r="AD37" s="49"/>
+      <c r="AF37" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AG37" s="49"/>
-      <c r="AH37" s="49"/>
-      <c r="AI37" s="49"/>
-      <c r="AJ37" s="49"/>
-      <c r="AK37" s="49"/>
-      <c r="AL37" s="49"/>
+      <c r="AG37" s="42"/>
+      <c r="AH37" s="42"/>
+      <c r="AI37" s="42"/>
+      <c r="AJ37" s="42"/>
+      <c r="AK37" s="42"/>
+      <c r="AL37" s="42"/>
       <c r="AQ37" s="12"/>
       <c r="AU37" s="3" t="s">
         <v>2</v>
@@ -3139,33 +3151,33 @@
         <v>53</v>
       </c>
       <c r="L39" s="12"/>
-      <c r="M39" s="42" t="s">
+      <c r="M39" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="N39" s="43"/>
-      <c r="O39" s="43"/>
-      <c r="P39" s="43"/>
-      <c r="Q39" s="43"/>
-      <c r="R39" s="43"/>
-      <c r="S39" s="44"/>
-      <c r="X39" s="49" t="s">
+      <c r="N39" s="54"/>
+      <c r="O39" s="54"/>
+      <c r="P39" s="54"/>
+      <c r="Q39" s="54"/>
+      <c r="R39" s="54"/>
+      <c r="S39" s="55"/>
+      <c r="X39" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="Y39" s="49"/>
-      <c r="Z39" s="49"/>
-      <c r="AA39" s="49"/>
-      <c r="AB39" s="49"/>
-      <c r="AC39" s="49"/>
-      <c r="AD39" s="49"/>
-      <c r="AI39" s="42" t="s">
+      <c r="Y39" s="42"/>
+      <c r="Z39" s="42"/>
+      <c r="AA39" s="42"/>
+      <c r="AB39" s="42"/>
+      <c r="AC39" s="42"/>
+      <c r="AD39" s="42"/>
+      <c r="AI39" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="AJ39" s="43"/>
-      <c r="AK39" s="43"/>
-      <c r="AL39" s="43"/>
-      <c r="AM39" s="43"/>
-      <c r="AN39" s="43"/>
-      <c r="AO39" s="44"/>
+      <c r="AJ39" s="54"/>
+      <c r="AK39" s="54"/>
+      <c r="AL39" s="54"/>
+      <c r="AM39" s="54"/>
+      <c r="AN39" s="54"/>
+      <c r="AO39" s="55"/>
       <c r="AQ39" s="12"/>
       <c r="AU39" s="8">
         <v>2</v>
@@ -3308,9 +3320,9 @@
       </c>
       <c r="F41" s="31"/>
       <c r="G41" s="32"/>
-      <c r="I41" s="50"/>
-      <c r="J41" s="50"/>
-      <c r="K41" s="50"/>
+      <c r="I41" s="43"/>
+      <c r="J41" s="43"/>
+      <c r="K41" s="43"/>
       <c r="L41" s="12"/>
       <c r="M41" s="7">
         <v>1</v>
@@ -3339,9 +3351,9 @@
       <c r="AM41" s="23"/>
       <c r="AN41" s="24"/>
       <c r="AO41" s="25"/>
-      <c r="AQ41" s="54"/>
-      <c r="AR41" s="50"/>
-      <c r="AS41" s="50"/>
+      <c r="AQ41" s="44"/>
+      <c r="AR41" s="43"/>
+      <c r="AS41" s="43"/>
       <c r="AU41" s="38">
         <v>4</v>
       </c>
@@ -3536,15 +3548,15 @@
       <c r="BA44" s="6"/>
     </row>
     <row r="45" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="49" t="s">
+      <c r="A45" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B45" s="49"/>
-      <c r="C45" s="49"/>
-      <c r="D45" s="49"/>
-      <c r="E45" s="49"/>
-      <c r="F45" s="49"/>
-      <c r="G45" s="49"/>
+      <c r="B45" s="42"/>
+      <c r="C45" s="42"/>
+      <c r="D45" s="42"/>
+      <c r="E45" s="42"/>
+      <c r="F45" s="42"/>
+      <c r="G45" s="42"/>
       <c r="M45" s="8" t="s">
         <v>11</v>
       </c>
@@ -3572,15 +3584,15 @@
       <c r="AM45" s="12"/>
       <c r="AN45" s="13"/>
       <c r="AO45" s="16"/>
-      <c r="AU45" s="49" t="s">
+      <c r="AU45" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AV45" s="49"/>
-      <c r="AW45" s="49"/>
-      <c r="AX45" s="49"/>
-      <c r="AY45" s="49"/>
-      <c r="AZ45" s="49"/>
-      <c r="BA45" s="49"/>
+      <c r="AV45" s="42"/>
+      <c r="AW45" s="42"/>
+      <c r="AX45" s="42"/>
+      <c r="AY45" s="42"/>
+      <c r="AZ45" s="42"/>
+      <c r="BA45" s="42"/>
     </row>
     <row r="46" spans="1:53" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="M46" s="8" t="s">
@@ -3641,49 +3653,61 @@
       <c r="AO47" s="6"/>
     </row>
     <row r="48" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="M48" s="42" t="s">
+      <c r="M48" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="N48" s="43"/>
-      <c r="O48" s="43"/>
-      <c r="P48" s="43"/>
-      <c r="Q48" s="43"/>
-      <c r="R48" s="43"/>
-      <c r="S48" s="44"/>
-      <c r="X48" s="49" t="s">
+      <c r="N48" s="54"/>
+      <c r="O48" s="54"/>
+      <c r="P48" s="54"/>
+      <c r="Q48" s="54"/>
+      <c r="R48" s="54"/>
+      <c r="S48" s="55"/>
+      <c r="X48" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="Y48" s="49"/>
-      <c r="Z48" s="49"/>
-      <c r="AA48" s="49"/>
-      <c r="AB48" s="49"/>
-      <c r="AC48" s="49"/>
-      <c r="AD48" s="49"/>
-      <c r="AI48" s="49" t="s">
+      <c r="Y48" s="42"/>
+      <c r="Z48" s="42"/>
+      <c r="AA48" s="42"/>
+      <c r="AB48" s="42"/>
+      <c r="AC48" s="42"/>
+      <c r="AD48" s="42"/>
+      <c r="AI48" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AJ48" s="49"/>
-      <c r="AK48" s="49"/>
-      <c r="AL48" s="49"/>
-      <c r="AM48" s="49"/>
-      <c r="AN48" s="49"/>
-      <c r="AO48" s="49"/>
+      <c r="AJ48" s="42"/>
+      <c r="AK48" s="42"/>
+      <c r="AL48" s="42"/>
+      <c r="AM48" s="42"/>
+      <c r="AN48" s="42"/>
+      <c r="AO48" s="42"/>
     </row>
     <row r="49" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="AU45:BA45"/>
-    <mergeCell ref="AF28:AL28"/>
-    <mergeCell ref="AF37:AL37"/>
-    <mergeCell ref="AQ30:AS30"/>
-    <mergeCell ref="AQ41:AS41"/>
-    <mergeCell ref="AU34:BA34"/>
-    <mergeCell ref="AU36:BA36"/>
-    <mergeCell ref="AU2:BA2"/>
-    <mergeCell ref="AU3:BA3"/>
-    <mergeCell ref="AU12:BA12"/>
-    <mergeCell ref="AU14:BA14"/>
-    <mergeCell ref="AU23:BA23"/>
+    <mergeCell ref="M48:S48"/>
+    <mergeCell ref="M39:S39"/>
+    <mergeCell ref="P37:V37"/>
+    <mergeCell ref="P28:V28"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A1:U1"/>
+    <mergeCell ref="O26:W26"/>
+    <mergeCell ref="I41:K41"/>
+    <mergeCell ref="L14:N14"/>
+    <mergeCell ref="L36:N36"/>
+    <mergeCell ref="M2:R2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="M4:S4"/>
+    <mergeCell ref="M13:S13"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="A25:G25"/>
     <mergeCell ref="X37:AD37"/>
     <mergeCell ref="AE26:AM26"/>
     <mergeCell ref="Z1:AB1"/>
@@ -3700,30 +3724,18 @@
     <mergeCell ref="AN36:AP36"/>
     <mergeCell ref="AQ8:AS8"/>
     <mergeCell ref="AQ19:AS19"/>
-    <mergeCell ref="A1:U1"/>
-    <mergeCell ref="O26:W26"/>
-    <mergeCell ref="I41:K41"/>
-    <mergeCell ref="L14:N14"/>
-    <mergeCell ref="L36:N36"/>
-    <mergeCell ref="M2:R2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="M4:S4"/>
-    <mergeCell ref="M13:S13"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A23:G23"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="M48:S48"/>
-    <mergeCell ref="M39:S39"/>
-    <mergeCell ref="P37:V37"/>
-    <mergeCell ref="P28:V28"/>
-    <mergeCell ref="A36:G36"/>
-    <mergeCell ref="A45:G45"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="AU2:BA2"/>
+    <mergeCell ref="AU3:BA3"/>
+    <mergeCell ref="AU12:BA12"/>
+    <mergeCell ref="AU14:BA14"/>
+    <mergeCell ref="AU23:BA23"/>
+    <mergeCell ref="AU45:BA45"/>
+    <mergeCell ref="AF28:AL28"/>
+    <mergeCell ref="AF37:AL37"/>
+    <mergeCell ref="AQ30:AS30"/>
+    <mergeCell ref="AQ41:AS41"/>
+    <mergeCell ref="AU34:BA34"/>
+    <mergeCell ref="AU36:BA36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/2025_2026/Playoffs/Brackets.xlsx
+++ b/2025_2026/Playoffs/Brackets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\NHLStats\2025_2026\Playoffs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28CB2692-EFA9-4C40-A921-FF7AF51D293C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4934C71-3BB0-43F6-9CCD-55BFE8F36FA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="64">
   <si>
     <t>Eastern Conference Playoff Teams</t>
   </si>
@@ -209,6 +209,15 @@
   </si>
   <si>
     <t>Stars Lead 2-1</t>
+  </si>
+  <si>
+    <t>Sabres Lead 2-1</t>
+  </si>
+  <si>
+    <t>Hurricanes Lead 3-0</t>
+  </si>
+  <si>
+    <t>Avalanche Lead 3-0</t>
   </si>
 </sst>
 </file>
@@ -587,18 +596,45 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -611,40 +647,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1014,18 +1023,18 @@
     </row>
     <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="11" spans="1:7" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="59" t="s">
+      <c r="A11" s="61" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="59"/>
-      <c r="C11" s="59" t="s">
+      <c r="B11" s="61"/>
+      <c r="C11" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="59"/>
-      <c r="E11" s="59" t="s">
+      <c r="D11" s="61"/>
+      <c r="E11" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="59"/>
+      <c r="F11" s="61"/>
       <c r="G11" s="4" t="s">
         <v>18</v>
       </c>
@@ -1054,18 +1063,18 @@
       </c>
     </row>
     <row r="13" spans="1:7" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="60" t="s">
+      <c r="A13" s="59" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="61"/>
-      <c r="C13" s="60" t="s">
+      <c r="B13" s="60"/>
+      <c r="C13" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="D13" s="61"/>
-      <c r="E13" s="60" t="s">
+      <c r="D13" s="60"/>
+      <c r="E13" s="59" t="s">
         <v>17</v>
       </c>
-      <c r="F13" s="61"/>
+      <c r="F13" s="60"/>
       <c r="G13" s="5"/>
     </row>
     <row r="14" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1092,14 +1101,14 @@
       <c r="F15" s="6"/>
     </row>
     <row r="16" spans="1:7" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="60" t="s">
+      <c r="A16" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="61"/>
-      <c r="C16" s="60" t="s">
+      <c r="B16" s="60"/>
+      <c r="C16" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="61"/>
+      <c r="D16" s="60"/>
     </row>
     <row r="17" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
@@ -1121,10 +1130,10 @@
       <c r="D18" s="6"/>
     </row>
     <row r="19" spans="1:4" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="60" t="s">
+      <c r="A19" s="59" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="61"/>
+      <c r="B19" s="60"/>
     </row>
     <row r="20" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
@@ -1143,10 +1152,10 @@
       </c>
     </row>
     <row r="22" spans="1:4" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="60" t="s">
+      <c r="A22" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="61"/>
+      <c r="B22" s="60"/>
     </row>
     <row r="23" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
@@ -1231,16 +1240,16 @@
     <sortCondition ref="B2:B9"/>
   </sortState>
   <mergeCells count="10">
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A16:B16"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A16:B16"/>
   </mergeCells>
   <dataValidations count="16">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C14" xr:uid="{2C3D9587-ABAE-4E3F-8B22-396DF812BF02}">
@@ -1344,124 +1353,124 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:54" ht="27.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
-      <c r="I1" s="51"/>
-      <c r="J1" s="51"/>
-      <c r="K1" s="51"/>
-      <c r="L1" s="51"/>
-      <c r="M1" s="51"/>
-      <c r="N1" s="51"/>
-      <c r="O1" s="51"/>
-      <c r="P1" s="51"/>
-      <c r="Q1" s="51"/>
-      <c r="R1" s="51"/>
-      <c r="S1" s="51"/>
-      <c r="T1" s="51"/>
-      <c r="U1" s="52"/>
-      <c r="Z1" s="50" t="s">
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="52"/>
+      <c r="M1" s="52"/>
+      <c r="N1" s="52"/>
+      <c r="O1" s="52"/>
+      <c r="P1" s="52"/>
+      <c r="Q1" s="52"/>
+      <c r="R1" s="52"/>
+      <c r="S1" s="52"/>
+      <c r="T1" s="52"/>
+      <c r="U1" s="53"/>
+      <c r="Z1" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="AA1" s="51"/>
-      <c r="AB1" s="52"/>
-      <c r="AF1" s="50" t="s">
+      <c r="AA1" s="52"/>
+      <c r="AB1" s="53"/>
+      <c r="AF1" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="AG1" s="51"/>
-      <c r="AH1" s="51"/>
-      <c r="AI1" s="51"/>
-      <c r="AJ1" s="51"/>
-      <c r="AK1" s="51"/>
-      <c r="AL1" s="51"/>
-      <c r="AM1" s="51"/>
-      <c r="AN1" s="51"/>
-      <c r="AO1" s="51"/>
-      <c r="AP1" s="51"/>
-      <c r="AQ1" s="51"/>
-      <c r="AR1" s="51"/>
-      <c r="AS1" s="51"/>
-      <c r="AT1" s="51"/>
-      <c r="AU1" s="51"/>
-      <c r="AV1" s="51"/>
-      <c r="AW1" s="51"/>
-      <c r="AX1" s="51"/>
-      <c r="AY1" s="51"/>
-      <c r="AZ1" s="51"/>
-      <c r="BA1" s="52"/>
+      <c r="AG1" s="52"/>
+      <c r="AH1" s="52"/>
+      <c r="AI1" s="52"/>
+      <c r="AJ1" s="52"/>
+      <c r="AK1" s="52"/>
+      <c r="AL1" s="52"/>
+      <c r="AM1" s="52"/>
+      <c r="AN1" s="52"/>
+      <c r="AO1" s="52"/>
+      <c r="AP1" s="52"/>
+      <c r="AQ1" s="52"/>
+      <c r="AR1" s="52"/>
+      <c r="AS1" s="52"/>
+      <c r="AT1" s="52"/>
+      <c r="AU1" s="52"/>
+      <c r="AV1" s="52"/>
+      <c r="AW1" s="52"/>
+      <c r="AX1" s="52"/>
+      <c r="AY1" s="52"/>
+      <c r="AZ1" s="52"/>
+      <c r="BA1" s="53"/>
     </row>
     <row r="2" spans="1:54" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="48"/>
-      <c r="M2" s="46" t="s">
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="57"/>
+      <c r="M2" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="47"/>
-      <c r="O2" s="47"/>
-      <c r="P2" s="47"/>
-      <c r="Q2" s="47"/>
-      <c r="R2" s="48"/>
-      <c r="AI2" s="46" t="s">
+      <c r="N2" s="56"/>
+      <c r="O2" s="56"/>
+      <c r="P2" s="56"/>
+      <c r="Q2" s="56"/>
+      <c r="R2" s="57"/>
+      <c r="AI2" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="AJ2" s="47"/>
-      <c r="AK2" s="47"/>
-      <c r="AL2" s="47"/>
-      <c r="AM2" s="47"/>
-      <c r="AN2" s="47"/>
-      <c r="AO2" s="48"/>
-      <c r="AU2" s="46" t="s">
+      <c r="AJ2" s="56"/>
+      <c r="AK2" s="56"/>
+      <c r="AL2" s="56"/>
+      <c r="AM2" s="56"/>
+      <c r="AN2" s="56"/>
+      <c r="AO2" s="57"/>
+      <c r="AU2" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="AV2" s="47"/>
-      <c r="AW2" s="47"/>
-      <c r="AX2" s="47"/>
-      <c r="AY2" s="47"/>
-      <c r="AZ2" s="47"/>
-      <c r="BA2" s="48"/>
+      <c r="AV2" s="56"/>
+      <c r="AW2" s="56"/>
+      <c r="AX2" s="56"/>
+      <c r="AY2" s="56"/>
+      <c r="AZ2" s="56"/>
+      <c r="BA2" s="57"/>
     </row>
     <row r="3" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="42" t="s">
+      <c r="A3" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="42"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="42"/>
-      <c r="AI3" s="53" t="s">
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="AI3" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="AJ3" s="54"/>
-      <c r="AK3" s="54"/>
-      <c r="AL3" s="54"/>
-      <c r="AM3" s="54"/>
-      <c r="AN3" s="54"/>
-      <c r="AO3" s="55"/>
-      <c r="AU3" s="42" t="s">
+      <c r="AJ3" s="43"/>
+      <c r="AK3" s="43"/>
+      <c r="AL3" s="43"/>
+      <c r="AM3" s="43"/>
+      <c r="AN3" s="43"/>
+      <c r="AO3" s="44"/>
+      <c r="AU3" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="AV3" s="42"/>
-      <c r="AW3" s="42"/>
-      <c r="AX3" s="42"/>
-      <c r="AY3" s="42"/>
-      <c r="AZ3" s="42"/>
-      <c r="BA3" s="42"/>
+      <c r="AV3" s="49"/>
+      <c r="AW3" s="49"/>
+      <c r="AX3" s="49"/>
+      <c r="AY3" s="49"/>
+      <c r="AZ3" s="49"/>
+      <c r="BA3" s="49"/>
     </row>
     <row r="4" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
@@ -1485,15 +1494,15 @@
       <c r="G4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="53" t="s">
+      <c r="M4" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="N4" s="54"/>
-      <c r="O4" s="54"/>
-      <c r="P4" s="54"/>
-      <c r="Q4" s="54"/>
-      <c r="R4" s="54"/>
-      <c r="S4" s="55"/>
+      <c r="N4" s="43"/>
+      <c r="O4" s="43"/>
+      <c r="P4" s="43"/>
+      <c r="Q4" s="43"/>
+      <c r="R4" s="43"/>
+      <c r="S4" s="44"/>
       <c r="AI4" s="3" t="s">
         <v>2</v>
       </c>
@@ -1686,12 +1695,18 @@
       <c r="C7" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="13"/>
+      <c r="D7" s="13">
+        <v>3</v>
+      </c>
       <c r="E7" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="F7" s="13"/>
-      <c r="G7" s="16"/>
+      <c r="F7" s="13">
+        <v>1</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>61</v>
+      </c>
       <c r="M7" s="8">
         <v>2</v>
       </c>
@@ -1719,12 +1734,18 @@
       <c r="AW7" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="AX7" s="13"/>
+      <c r="AX7" s="13">
+        <v>4</v>
+      </c>
       <c r="AY7" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="AZ7" s="13"/>
-      <c r="BA7" s="16"/>
+      <c r="AZ7" s="13">
+        <v>2</v>
+      </c>
+      <c r="BA7" s="16" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="8" spans="1:54" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="8">
@@ -1742,9 +1763,9 @@
       </c>
       <c r="F8" s="13"/>
       <c r="G8" s="16"/>
-      <c r="I8" s="43"/>
-      <c r="J8" s="43"/>
-      <c r="K8" s="43"/>
+      <c r="I8" s="50"/>
+      <c r="J8" s="50"/>
+      <c r="K8" s="50"/>
       <c r="M8" s="8">
         <v>3</v>
       </c>
@@ -1763,9 +1784,9 @@
       <c r="AM8" s="30"/>
       <c r="AN8" s="31"/>
       <c r="AO8" s="16"/>
-      <c r="AQ8" s="43"/>
-      <c r="AR8" s="43"/>
-      <c r="AS8" s="43"/>
+      <c r="AQ8" s="50"/>
+      <c r="AR8" s="50"/>
+      <c r="AS8" s="50"/>
       <c r="AU8" s="38">
         <v>4</v>
       </c>
@@ -1941,15 +1962,15 @@
       <c r="BA11" s="6"/>
     </row>
     <row r="12" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="42" t="s">
+      <c r="A12" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="42"/>
-      <c r="C12" s="42"/>
-      <c r="D12" s="42"/>
-      <c r="E12" s="42"/>
-      <c r="F12" s="42"/>
-      <c r="G12" s="42"/>
+      <c r="B12" s="49"/>
+      <c r="C12" s="49"/>
+      <c r="D12" s="49"/>
+      <c r="E12" s="49"/>
+      <c r="F12" s="49"/>
+      <c r="G12" s="49"/>
       <c r="L12" s="12"/>
       <c r="M12" s="8" t="s">
         <v>12</v>
@@ -1960,65 +1981,65 @@
       <c r="Q12" s="12"/>
       <c r="R12" s="13"/>
       <c r="S12" s="16"/>
-      <c r="AI12" s="42" t="s">
+      <c r="AI12" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AJ12" s="42"/>
-      <c r="AK12" s="42"/>
-      <c r="AL12" s="42"/>
-      <c r="AM12" s="42"/>
-      <c r="AN12" s="42"/>
-      <c r="AO12" s="42"/>
+      <c r="AJ12" s="49"/>
+      <c r="AK12" s="49"/>
+      <c r="AL12" s="49"/>
+      <c r="AM12" s="49"/>
+      <c r="AN12" s="49"/>
+      <c r="AO12" s="49"/>
       <c r="AQ12" s="12"/>
-      <c r="AU12" s="42" t="s">
+      <c r="AU12" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AV12" s="42"/>
-      <c r="AW12" s="42"/>
-      <c r="AX12" s="42"/>
-      <c r="AY12" s="42"/>
-      <c r="AZ12" s="42"/>
-      <c r="BA12" s="42"/>
+      <c r="AV12" s="49"/>
+      <c r="AW12" s="49"/>
+      <c r="AX12" s="49"/>
+      <c r="AY12" s="49"/>
+      <c r="AZ12" s="49"/>
+      <c r="BA12" s="49"/>
     </row>
     <row r="13" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L13" s="12"/>
-      <c r="M13" s="53" t="s">
+      <c r="M13" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="N13" s="54"/>
-      <c r="O13" s="54"/>
-      <c r="P13" s="54"/>
-      <c r="Q13" s="54"/>
-      <c r="R13" s="54"/>
-      <c r="S13" s="55"/>
+      <c r="N13" s="43"/>
+      <c r="O13" s="43"/>
+      <c r="P13" s="43"/>
+      <c r="Q13" s="43"/>
+      <c r="R13" s="43"/>
+      <c r="S13" s="44"/>
       <c r="AQ13" s="12"/>
     </row>
     <row r="14" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="45" t="s">
+      <c r="A14" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="45"/>
-      <c r="C14" s="45"/>
-      <c r="D14" s="45"/>
-      <c r="E14" s="45"/>
-      <c r="F14" s="45"/>
-      <c r="G14" s="45"/>
-      <c r="L14" s="44"/>
-      <c r="M14" s="43"/>
-      <c r="N14" s="43"/>
-      <c r="AN14" s="43"/>
-      <c r="AO14" s="43"/>
-      <c r="AP14" s="43"/>
+      <c r="B14" s="48"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="48"/>
+      <c r="E14" s="48"/>
+      <c r="F14" s="48"/>
+      <c r="G14" s="48"/>
+      <c r="L14" s="54"/>
+      <c r="M14" s="50"/>
+      <c r="N14" s="50"/>
+      <c r="AN14" s="50"/>
+      <c r="AO14" s="50"/>
+      <c r="AP14" s="50"/>
       <c r="AQ14" s="12"/>
-      <c r="AU14" s="45" t="s">
+      <c r="AU14" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="AV14" s="45"/>
-      <c r="AW14" s="45"/>
-      <c r="AX14" s="45"/>
-      <c r="AY14" s="45"/>
-      <c r="AZ14" s="45"/>
-      <c r="BA14" s="45"/>
+      <c r="AV14" s="48"/>
+      <c r="AW14" s="48"/>
+      <c r="AX14" s="48"/>
+      <c r="AY14" s="48"/>
+      <c r="AZ14" s="48"/>
+      <c r="BA14" s="48"/>
     </row>
     <row r="15" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
@@ -2231,15 +2252,15 @@
       </c>
       <c r="F19" s="31"/>
       <c r="G19" s="32"/>
-      <c r="I19" s="43"/>
-      <c r="J19" s="43"/>
-      <c r="K19" s="43"/>
+      <c r="I19" s="50"/>
+      <c r="J19" s="50"/>
+      <c r="K19" s="50"/>
       <c r="L19" s="12"/>
       <c r="O19" s="12"/>
       <c r="AN19" s="12"/>
-      <c r="AQ19" s="44"/>
-      <c r="AR19" s="43"/>
-      <c r="AS19" s="43"/>
+      <c r="AQ19" s="54"/>
+      <c r="AR19" s="50"/>
+      <c r="AS19" s="50"/>
       <c r="AU19" s="38">
         <v>4</v>
       </c>
@@ -2359,52 +2380,52 @@
       <c r="BA22" s="6"/>
     </row>
     <row r="23" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="42" t="s">
+      <c r="A23" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="B23" s="42"/>
-      <c r="C23" s="42"/>
-      <c r="D23" s="42"/>
-      <c r="E23" s="42"/>
-      <c r="F23" s="42"/>
-      <c r="G23" s="42"/>
+      <c r="B23" s="49"/>
+      <c r="C23" s="49"/>
+      <c r="D23" s="49"/>
+      <c r="E23" s="49"/>
+      <c r="F23" s="49"/>
+      <c r="G23" s="49"/>
       <c r="O23" s="12"/>
       <c r="AN23" s="12"/>
-      <c r="AU23" s="42" t="s">
+      <c r="AU23" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AV23" s="42"/>
-      <c r="AW23" s="42"/>
-      <c r="AX23" s="42"/>
-      <c r="AY23" s="42"/>
-      <c r="AZ23" s="42"/>
-      <c r="BA23" s="42"/>
+      <c r="AV23" s="49"/>
+      <c r="AW23" s="49"/>
+      <c r="AX23" s="49"/>
+      <c r="AY23" s="49"/>
+      <c r="AZ23" s="49"/>
+      <c r="BA23" s="49"/>
     </row>
     <row r="24" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="O24" s="12"/>
       <c r="AN24" s="12"/>
     </row>
     <row r="25" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="42" t="s">
+      <c r="A25" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="42"/>
-      <c r="C25" s="42"/>
-      <c r="D25" s="42"/>
-      <c r="E25" s="42"/>
-      <c r="F25" s="42"/>
-      <c r="G25" s="42"/>
+      <c r="B25" s="49"/>
+      <c r="C25" s="49"/>
+      <c r="D25" s="49"/>
+      <c r="E25" s="49"/>
+      <c r="F25" s="49"/>
+      <c r="G25" s="49"/>
       <c r="O25" s="12"/>
       <c r="AN25" s="12"/>
-      <c r="AU25" s="42" t="s">
+      <c r="AU25" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="AV25" s="42"/>
-      <c r="AW25" s="42"/>
-      <c r="AX25" s="42"/>
-      <c r="AY25" s="42"/>
-      <c r="AZ25" s="42"/>
-      <c r="BA25" s="42"/>
+      <c r="AV25" s="49"/>
+      <c r="AW25" s="49"/>
+      <c r="AX25" s="49"/>
+      <c r="AY25" s="49"/>
+      <c r="AZ25" s="49"/>
+      <c r="BA25" s="49"/>
     </row>
     <row r="26" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="20" t="s">
@@ -2428,24 +2449,24 @@
       <c r="G26" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="O26" s="44"/>
-      <c r="P26" s="43"/>
-      <c r="Q26" s="43"/>
-      <c r="R26" s="43"/>
-      <c r="S26" s="43"/>
-      <c r="T26" s="43"/>
-      <c r="U26" s="43"/>
-      <c r="V26" s="43"/>
-      <c r="W26" s="43"/>
-      <c r="AE26" s="43"/>
-      <c r="AF26" s="43"/>
-      <c r="AG26" s="43"/>
-      <c r="AH26" s="43"/>
-      <c r="AI26" s="43"/>
-      <c r="AJ26" s="43"/>
-      <c r="AK26" s="43"/>
-      <c r="AL26" s="43"/>
-      <c r="AM26" s="49"/>
+      <c r="O26" s="54"/>
+      <c r="P26" s="50"/>
+      <c r="Q26" s="50"/>
+      <c r="R26" s="50"/>
+      <c r="S26" s="50"/>
+      <c r="T26" s="50"/>
+      <c r="U26" s="50"/>
+      <c r="V26" s="50"/>
+      <c r="W26" s="50"/>
+      <c r="AE26" s="50"/>
+      <c r="AF26" s="50"/>
+      <c r="AG26" s="50"/>
+      <c r="AH26" s="50"/>
+      <c r="AI26" s="50"/>
+      <c r="AJ26" s="50"/>
+      <c r="AK26" s="50"/>
+      <c r="AL26" s="50"/>
+      <c r="AM26" s="58"/>
       <c r="AU26" s="20" t="s">
         <v>2</v>
       </c>
@@ -2542,26 +2563,26 @@
         <v>54</v>
       </c>
       <c r="O28" s="12"/>
-      <c r="P28" s="53" t="s">
+      <c r="P28" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="Q28" s="54"/>
-      <c r="R28" s="54"/>
-      <c r="S28" s="54"/>
-      <c r="T28" s="54"/>
-      <c r="U28" s="54"/>
-      <c r="V28" s="55"/>
+      <c r="Q28" s="43"/>
+      <c r="R28" s="43"/>
+      <c r="S28" s="43"/>
+      <c r="T28" s="43"/>
+      <c r="U28" s="43"/>
+      <c r="V28" s="44"/>
       <c r="X28" s="12"/>
       <c r="AD28" s="13"/>
-      <c r="AF28" s="42" t="s">
+      <c r="AF28" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="AG28" s="42"/>
-      <c r="AH28" s="42"/>
-      <c r="AI28" s="42"/>
-      <c r="AJ28" s="42"/>
-      <c r="AK28" s="42"/>
-      <c r="AL28" s="42"/>
+      <c r="AG28" s="49"/>
+      <c r="AH28" s="49"/>
+      <c r="AI28" s="49"/>
+      <c r="AJ28" s="49"/>
+      <c r="AK28" s="49"/>
+      <c r="AL28" s="49"/>
       <c r="AN28" s="12"/>
       <c r="AU28" s="8">
         <v>2</v>
@@ -2595,12 +2616,18 @@
       <c r="C29" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="D29" s="13"/>
+      <c r="D29" s="13">
+        <v>2</v>
+      </c>
       <c r="E29" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="F29" s="13"/>
-      <c r="G29" s="16"/>
+      <c r="F29" s="13">
+        <v>1</v>
+      </c>
+      <c r="G29" s="16" t="s">
+        <v>62</v>
+      </c>
       <c r="O29" s="12"/>
       <c r="P29" s="22" t="s">
         <v>2</v>
@@ -2679,9 +2706,9 @@
       </c>
       <c r="F30" s="31"/>
       <c r="G30" s="32"/>
-      <c r="I30" s="43"/>
-      <c r="J30" s="43"/>
-      <c r="K30" s="43"/>
+      <c r="I30" s="50"/>
+      <c r="J30" s="50"/>
+      <c r="K30" s="50"/>
       <c r="O30" s="12"/>
       <c r="P30" s="7">
         <v>1</v>
@@ -2704,9 +2731,9 @@
       <c r="AK30" s="24"/>
       <c r="AL30" s="25"/>
       <c r="AN30" s="12"/>
-      <c r="AQ30" s="43"/>
-      <c r="AR30" s="43"/>
-      <c r="AS30" s="43"/>
+      <c r="AQ30" s="50"/>
+      <c r="AR30" s="50"/>
+      <c r="AS30" s="50"/>
       <c r="AU30" s="38">
         <v>4</v>
       </c>
@@ -2894,15 +2921,15 @@
       <c r="BA33" s="6"/>
     </row>
     <row r="34" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="42" t="s">
+      <c r="A34" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="B34" s="42"/>
-      <c r="C34" s="42"/>
-      <c r="D34" s="42"/>
-      <c r="E34" s="42"/>
-      <c r="F34" s="42"/>
-      <c r="G34" s="42"/>
+      <c r="B34" s="49"/>
+      <c r="C34" s="49"/>
+      <c r="D34" s="49"/>
+      <c r="E34" s="49"/>
+      <c r="F34" s="49"/>
+      <c r="G34" s="49"/>
       <c r="L34" s="12"/>
       <c r="O34" s="12"/>
       <c r="P34" s="8" t="s">
@@ -2927,15 +2954,15 @@
       <c r="AL34" s="16"/>
       <c r="AN34" s="12"/>
       <c r="AQ34" s="12"/>
-      <c r="AU34" s="42" t="s">
+      <c r="AU34" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AV34" s="42"/>
-      <c r="AW34" s="42"/>
-      <c r="AX34" s="42"/>
-      <c r="AY34" s="42"/>
-      <c r="AZ34" s="42"/>
-      <c r="BA34" s="42"/>
+      <c r="AV34" s="49"/>
+      <c r="AW34" s="49"/>
+      <c r="AX34" s="49"/>
+      <c r="AY34" s="49"/>
+      <c r="AZ34" s="49"/>
+      <c r="BA34" s="49"/>
     </row>
     <row r="35" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L35" s="12"/>
@@ -2964,18 +2991,18 @@
       <c r="AQ35" s="12"/>
     </row>
     <row r="36" spans="1:53" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="45" t="s">
+      <c r="A36" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="B36" s="45"/>
-      <c r="C36" s="45"/>
-      <c r="D36" s="45"/>
-      <c r="E36" s="45"/>
-      <c r="F36" s="45"/>
-      <c r="G36" s="45"/>
-      <c r="L36" s="44"/>
-      <c r="M36" s="43"/>
-      <c r="N36" s="43"/>
+      <c r="B36" s="48"/>
+      <c r="C36" s="48"/>
+      <c r="D36" s="48"/>
+      <c r="E36" s="48"/>
+      <c r="F36" s="48"/>
+      <c r="G36" s="48"/>
+      <c r="L36" s="54"/>
+      <c r="M36" s="50"/>
+      <c r="N36" s="50"/>
       <c r="O36" s="12"/>
       <c r="P36" s="8" t="s">
         <v>12</v>
@@ -2997,19 +3024,19 @@
       <c r="AJ36" s="35"/>
       <c r="AK36" s="36"/>
       <c r="AL36" s="37"/>
-      <c r="AN36" s="44"/>
-      <c r="AO36" s="43"/>
-      <c r="AP36" s="43"/>
+      <c r="AN36" s="54"/>
+      <c r="AO36" s="50"/>
+      <c r="AP36" s="50"/>
       <c r="AQ36" s="12"/>
-      <c r="AU36" s="45" t="s">
+      <c r="AU36" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="AV36" s="45"/>
-      <c r="AW36" s="45"/>
-      <c r="AX36" s="45"/>
-      <c r="AY36" s="45"/>
-      <c r="AZ36" s="45"/>
-      <c r="BA36" s="45"/>
+      <c r="AV36" s="48"/>
+      <c r="AW36" s="48"/>
+      <c r="AX36" s="48"/>
+      <c r="AY36" s="48"/>
+      <c r="AZ36" s="48"/>
+      <c r="BA36" s="48"/>
     </row>
     <row r="37" spans="1:53" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37" s="20" t="s">
@@ -3034,31 +3061,31 @@
         <v>9</v>
       </c>
       <c r="L37" s="12"/>
-      <c r="P37" s="56" t="s">
+      <c r="P37" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="Q37" s="57"/>
-      <c r="R37" s="57"/>
-      <c r="S37" s="57"/>
-      <c r="T37" s="57"/>
-      <c r="U37" s="57"/>
-      <c r="V37" s="58"/>
-      <c r="X37" s="44"/>
-      <c r="Y37" s="43"/>
-      <c r="Z37" s="43"/>
-      <c r="AA37" s="43"/>
-      <c r="AB37" s="43"/>
-      <c r="AC37" s="43"/>
-      <c r="AD37" s="49"/>
-      <c r="AF37" s="42" t="s">
+      <c r="Q37" s="46"/>
+      <c r="R37" s="46"/>
+      <c r="S37" s="46"/>
+      <c r="T37" s="46"/>
+      <c r="U37" s="46"/>
+      <c r="V37" s="47"/>
+      <c r="X37" s="54"/>
+      <c r="Y37" s="50"/>
+      <c r="Z37" s="50"/>
+      <c r="AA37" s="50"/>
+      <c r="AB37" s="50"/>
+      <c r="AC37" s="50"/>
+      <c r="AD37" s="58"/>
+      <c r="AF37" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AG37" s="42"/>
-      <c r="AH37" s="42"/>
-      <c r="AI37" s="42"/>
-      <c r="AJ37" s="42"/>
-      <c r="AK37" s="42"/>
-      <c r="AL37" s="42"/>
+      <c r="AG37" s="49"/>
+      <c r="AH37" s="49"/>
+      <c r="AI37" s="49"/>
+      <c r="AJ37" s="49"/>
+      <c r="AK37" s="49"/>
+      <c r="AL37" s="49"/>
       <c r="AQ37" s="12"/>
       <c r="AU37" s="3" t="s">
         <v>2</v>
@@ -3151,33 +3178,33 @@
         <v>53</v>
       </c>
       <c r="L39" s="12"/>
-      <c r="M39" s="53" t="s">
+      <c r="M39" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="N39" s="54"/>
-      <c r="O39" s="54"/>
-      <c r="P39" s="54"/>
-      <c r="Q39" s="54"/>
-      <c r="R39" s="54"/>
-      <c r="S39" s="55"/>
-      <c r="X39" s="42" t="s">
+      <c r="N39" s="43"/>
+      <c r="O39" s="43"/>
+      <c r="P39" s="43"/>
+      <c r="Q39" s="43"/>
+      <c r="R39" s="43"/>
+      <c r="S39" s="44"/>
+      <c r="X39" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="Y39" s="42"/>
-      <c r="Z39" s="42"/>
-      <c r="AA39" s="42"/>
-      <c r="AB39" s="42"/>
-      <c r="AC39" s="42"/>
-      <c r="AD39" s="42"/>
-      <c r="AI39" s="53" t="s">
+      <c r="Y39" s="49"/>
+      <c r="Z39" s="49"/>
+      <c r="AA39" s="49"/>
+      <c r="AB39" s="49"/>
+      <c r="AC39" s="49"/>
+      <c r="AD39" s="49"/>
+      <c r="AI39" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="AJ39" s="54"/>
-      <c r="AK39" s="54"/>
-      <c r="AL39" s="54"/>
-      <c r="AM39" s="54"/>
-      <c r="AN39" s="54"/>
-      <c r="AO39" s="55"/>
+      <c r="AJ39" s="43"/>
+      <c r="AK39" s="43"/>
+      <c r="AL39" s="43"/>
+      <c r="AM39" s="43"/>
+      <c r="AN39" s="43"/>
+      <c r="AO39" s="44"/>
       <c r="AQ39" s="12"/>
       <c r="AU39" s="8">
         <v>2</v>
@@ -3320,9 +3347,9 @@
       </c>
       <c r="F41" s="31"/>
       <c r="G41" s="32"/>
-      <c r="I41" s="43"/>
-      <c r="J41" s="43"/>
-      <c r="K41" s="43"/>
+      <c r="I41" s="50"/>
+      <c r="J41" s="50"/>
+      <c r="K41" s="50"/>
       <c r="L41" s="12"/>
       <c r="M41" s="7">
         <v>1</v>
@@ -3351,9 +3378,9 @@
       <c r="AM41" s="23"/>
       <c r="AN41" s="24"/>
       <c r="AO41" s="25"/>
-      <c r="AQ41" s="44"/>
-      <c r="AR41" s="43"/>
-      <c r="AS41" s="43"/>
+      <c r="AQ41" s="54"/>
+      <c r="AR41" s="50"/>
+      <c r="AS41" s="50"/>
       <c r="AU41" s="38">
         <v>4</v>
       </c>
@@ -3548,15 +3575,15 @@
       <c r="BA44" s="6"/>
     </row>
     <row r="45" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="42" t="s">
+      <c r="A45" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="B45" s="42"/>
-      <c r="C45" s="42"/>
-      <c r="D45" s="42"/>
-      <c r="E45" s="42"/>
-      <c r="F45" s="42"/>
-      <c r="G45" s="42"/>
+      <c r="B45" s="49"/>
+      <c r="C45" s="49"/>
+      <c r="D45" s="49"/>
+      <c r="E45" s="49"/>
+      <c r="F45" s="49"/>
+      <c r="G45" s="49"/>
       <c r="M45" s="8" t="s">
         <v>11</v>
       </c>
@@ -3584,15 +3611,15 @@
       <c r="AM45" s="12"/>
       <c r="AN45" s="13"/>
       <c r="AO45" s="16"/>
-      <c r="AU45" s="42" t="s">
+      <c r="AU45" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AV45" s="42"/>
-      <c r="AW45" s="42"/>
-      <c r="AX45" s="42"/>
-      <c r="AY45" s="42"/>
-      <c r="AZ45" s="42"/>
-      <c r="BA45" s="42"/>
+      <c r="AV45" s="49"/>
+      <c r="AW45" s="49"/>
+      <c r="AX45" s="49"/>
+      <c r="AY45" s="49"/>
+      <c r="AZ45" s="49"/>
+      <c r="BA45" s="49"/>
     </row>
     <row r="46" spans="1:53" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="M46" s="8" t="s">
@@ -3653,45 +3680,65 @@
       <c r="AO47" s="6"/>
     </row>
     <row r="48" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="M48" s="53" t="s">
+      <c r="M48" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="N48" s="54"/>
-      <c r="O48" s="54"/>
-      <c r="P48" s="54"/>
-      <c r="Q48" s="54"/>
-      <c r="R48" s="54"/>
-      <c r="S48" s="55"/>
-      <c r="X48" s="42" t="s">
+      <c r="N48" s="43"/>
+      <c r="O48" s="43"/>
+      <c r="P48" s="43"/>
+      <c r="Q48" s="43"/>
+      <c r="R48" s="43"/>
+      <c r="S48" s="44"/>
+      <c r="X48" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="Y48" s="42"/>
-      <c r="Z48" s="42"/>
-      <c r="AA48" s="42"/>
-      <c r="AB48" s="42"/>
-      <c r="AC48" s="42"/>
-      <c r="AD48" s="42"/>
-      <c r="AI48" s="42" t="s">
+      <c r="Y48" s="49"/>
+      <c r="Z48" s="49"/>
+      <c r="AA48" s="49"/>
+      <c r="AB48" s="49"/>
+      <c r="AC48" s="49"/>
+      <c r="AD48" s="49"/>
+      <c r="AI48" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AJ48" s="42"/>
-      <c r="AK48" s="42"/>
-      <c r="AL48" s="42"/>
-      <c r="AM48" s="42"/>
-      <c r="AN48" s="42"/>
-      <c r="AO48" s="42"/>
+      <c r="AJ48" s="49"/>
+      <c r="AK48" s="49"/>
+      <c r="AL48" s="49"/>
+      <c r="AM48" s="49"/>
+      <c r="AN48" s="49"/>
+      <c r="AO48" s="49"/>
     </row>
     <row r="49" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="M48:S48"/>
-    <mergeCell ref="M39:S39"/>
-    <mergeCell ref="P37:V37"/>
-    <mergeCell ref="P28:V28"/>
-    <mergeCell ref="A36:G36"/>
-    <mergeCell ref="A45:G45"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="AU45:BA45"/>
+    <mergeCell ref="AF28:AL28"/>
+    <mergeCell ref="AF37:AL37"/>
+    <mergeCell ref="AQ30:AS30"/>
+    <mergeCell ref="AQ41:AS41"/>
+    <mergeCell ref="AU34:BA34"/>
+    <mergeCell ref="AU36:BA36"/>
+    <mergeCell ref="AU2:BA2"/>
+    <mergeCell ref="AU3:BA3"/>
+    <mergeCell ref="AU12:BA12"/>
+    <mergeCell ref="AU14:BA14"/>
+    <mergeCell ref="AU23:BA23"/>
+    <mergeCell ref="X37:AD37"/>
+    <mergeCell ref="AE26:AM26"/>
+    <mergeCell ref="Z1:AB1"/>
+    <mergeCell ref="X39:AD39"/>
+    <mergeCell ref="X48:AD48"/>
+    <mergeCell ref="AF1:BA1"/>
+    <mergeCell ref="AI2:AO2"/>
+    <mergeCell ref="AI3:AO3"/>
+    <mergeCell ref="AI12:AO12"/>
+    <mergeCell ref="AI39:AO39"/>
+    <mergeCell ref="AU25:BA25"/>
+    <mergeCell ref="AI48:AO48"/>
+    <mergeCell ref="AN14:AP14"/>
+    <mergeCell ref="AN36:AP36"/>
+    <mergeCell ref="AQ8:AS8"/>
+    <mergeCell ref="AQ19:AS19"/>
     <mergeCell ref="A1:U1"/>
     <mergeCell ref="O26:W26"/>
     <mergeCell ref="I41:K41"/>
@@ -3708,34 +3755,14 @@
     <mergeCell ref="I8:K8"/>
     <mergeCell ref="I19:K19"/>
     <mergeCell ref="A25:G25"/>
-    <mergeCell ref="X37:AD37"/>
-    <mergeCell ref="AE26:AM26"/>
-    <mergeCell ref="Z1:AB1"/>
-    <mergeCell ref="X39:AD39"/>
-    <mergeCell ref="X48:AD48"/>
-    <mergeCell ref="AF1:BA1"/>
-    <mergeCell ref="AI2:AO2"/>
-    <mergeCell ref="AI3:AO3"/>
-    <mergeCell ref="AI12:AO12"/>
-    <mergeCell ref="AI39:AO39"/>
-    <mergeCell ref="AU25:BA25"/>
-    <mergeCell ref="AI48:AO48"/>
-    <mergeCell ref="AN14:AP14"/>
-    <mergeCell ref="AN36:AP36"/>
-    <mergeCell ref="AQ8:AS8"/>
-    <mergeCell ref="AQ19:AS19"/>
-    <mergeCell ref="AU2:BA2"/>
-    <mergeCell ref="AU3:BA3"/>
-    <mergeCell ref="AU12:BA12"/>
-    <mergeCell ref="AU14:BA14"/>
-    <mergeCell ref="AU23:BA23"/>
-    <mergeCell ref="AU45:BA45"/>
-    <mergeCell ref="AF28:AL28"/>
-    <mergeCell ref="AF37:AL37"/>
-    <mergeCell ref="AQ30:AS30"/>
-    <mergeCell ref="AQ41:AS41"/>
-    <mergeCell ref="AU34:BA34"/>
-    <mergeCell ref="AU36:BA36"/>
+    <mergeCell ref="M48:S48"/>
+    <mergeCell ref="M39:S39"/>
+    <mergeCell ref="P37:V37"/>
+    <mergeCell ref="P28:V28"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="A34:G34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/2025_2026/Playoffs/Brackets.xlsx
+++ b/2025_2026/Playoffs/Brackets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\NHLStats\2025_2026\Playoffs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4934C71-3BB0-43F6-9CCD-55BFE8F36FA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07B6EC2A-D06C-4331-94E7-6078B8574F94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="67">
   <si>
     <t>Eastern Conference Playoff Teams</t>
   </si>
@@ -218,6 +218,15 @@
   </si>
   <si>
     <t>Avalanche Lead 3-0</t>
+  </si>
+  <si>
+    <t>Mammoth Lead 2-1</t>
+  </si>
+  <si>
+    <t>Ducks Lead 2-1</t>
+  </si>
+  <si>
+    <t>Canadiens Lead 2-1</t>
   </si>
 </sst>
 </file>
@@ -596,6 +605,39 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -614,46 +656,13 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1023,18 +1032,18 @@
     </row>
     <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="11" spans="1:7" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="61" t="s">
+      <c r="A11" s="59" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="61"/>
-      <c r="C11" s="61" t="s">
+      <c r="B11" s="59"/>
+      <c r="C11" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="61"/>
-      <c r="E11" s="61" t="s">
+      <c r="D11" s="59"/>
+      <c r="E11" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="61"/>
+      <c r="F11" s="59"/>
       <c r="G11" s="4" t="s">
         <v>18</v>
       </c>
@@ -1063,18 +1072,18 @@
       </c>
     </row>
     <row r="13" spans="1:7" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="59" t="s">
+      <c r="A13" s="60" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="60"/>
-      <c r="C13" s="59" t="s">
+      <c r="B13" s="61"/>
+      <c r="C13" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="D13" s="60"/>
-      <c r="E13" s="59" t="s">
+      <c r="D13" s="61"/>
+      <c r="E13" s="60" t="s">
         <v>17</v>
       </c>
-      <c r="F13" s="60"/>
+      <c r="F13" s="61"/>
       <c r="G13" s="5"/>
     </row>
     <row r="14" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1101,14 +1110,14 @@
       <c r="F15" s="6"/>
     </row>
     <row r="16" spans="1:7" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="59" t="s">
+      <c r="A16" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="60"/>
-      <c r="C16" s="59" t="s">
+      <c r="B16" s="61"/>
+      <c r="C16" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="60"/>
+      <c r="D16" s="61"/>
     </row>
     <row r="17" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
@@ -1130,10 +1139,10 @@
       <c r="D18" s="6"/>
     </row>
     <row r="19" spans="1:4" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="59" t="s">
+      <c r="A19" s="60" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="60"/>
+      <c r="B19" s="61"/>
     </row>
     <row r="20" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
@@ -1152,10 +1161,10 @@
       </c>
     </row>
     <row r="22" spans="1:4" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="59" t="s">
+      <c r="A22" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="60"/>
+      <c r="B22" s="61"/>
     </row>
     <row r="23" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
@@ -1240,16 +1249,16 @@
     <sortCondition ref="B2:B9"/>
   </sortState>
   <mergeCells count="10">
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C16:D16"/>
     <mergeCell ref="E11:F11"/>
     <mergeCell ref="E13:F13"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C16:D16"/>
   </mergeCells>
   <dataValidations count="16">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C14" xr:uid="{2C3D9587-ABAE-4E3F-8B22-396DF812BF02}">
@@ -1353,124 +1362,124 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:54" ht="27.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
-      <c r="M1" s="52"/>
-      <c r="N1" s="52"/>
-      <c r="O1" s="52"/>
-      <c r="P1" s="52"/>
-      <c r="Q1" s="52"/>
-      <c r="R1" s="52"/>
-      <c r="S1" s="52"/>
-      <c r="T1" s="52"/>
-      <c r="U1" s="53"/>
-      <c r="Z1" s="51" t="s">
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
+      <c r="K1" s="51"/>
+      <c r="L1" s="51"/>
+      <c r="M1" s="51"/>
+      <c r="N1" s="51"/>
+      <c r="O1" s="51"/>
+      <c r="P1" s="51"/>
+      <c r="Q1" s="51"/>
+      <c r="R1" s="51"/>
+      <c r="S1" s="51"/>
+      <c r="T1" s="51"/>
+      <c r="U1" s="52"/>
+      <c r="Z1" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="AA1" s="52"/>
-      <c r="AB1" s="53"/>
-      <c r="AF1" s="51" t="s">
+      <c r="AA1" s="51"/>
+      <c r="AB1" s="52"/>
+      <c r="AF1" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="AG1" s="52"/>
-      <c r="AH1" s="52"/>
-      <c r="AI1" s="52"/>
-      <c r="AJ1" s="52"/>
-      <c r="AK1" s="52"/>
-      <c r="AL1" s="52"/>
-      <c r="AM1" s="52"/>
-      <c r="AN1" s="52"/>
-      <c r="AO1" s="52"/>
-      <c r="AP1" s="52"/>
-      <c r="AQ1" s="52"/>
-      <c r="AR1" s="52"/>
-      <c r="AS1" s="52"/>
-      <c r="AT1" s="52"/>
-      <c r="AU1" s="52"/>
-      <c r="AV1" s="52"/>
-      <c r="AW1" s="52"/>
-      <c r="AX1" s="52"/>
-      <c r="AY1" s="52"/>
-      <c r="AZ1" s="52"/>
-      <c r="BA1" s="53"/>
+      <c r="AG1" s="51"/>
+      <c r="AH1" s="51"/>
+      <c r="AI1" s="51"/>
+      <c r="AJ1" s="51"/>
+      <c r="AK1" s="51"/>
+      <c r="AL1" s="51"/>
+      <c r="AM1" s="51"/>
+      <c r="AN1" s="51"/>
+      <c r="AO1" s="51"/>
+      <c r="AP1" s="51"/>
+      <c r="AQ1" s="51"/>
+      <c r="AR1" s="51"/>
+      <c r="AS1" s="51"/>
+      <c r="AT1" s="51"/>
+      <c r="AU1" s="51"/>
+      <c r="AV1" s="51"/>
+      <c r="AW1" s="51"/>
+      <c r="AX1" s="51"/>
+      <c r="AY1" s="51"/>
+      <c r="AZ1" s="51"/>
+      <c r="BA1" s="52"/>
     </row>
     <row r="2" spans="1:54" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="55" t="s">
+      <c r="A2" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="57"/>
-      <c r="M2" s="55" t="s">
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="48"/>
+      <c r="M2" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="56"/>
-      <c r="O2" s="56"/>
-      <c r="P2" s="56"/>
-      <c r="Q2" s="56"/>
-      <c r="R2" s="57"/>
-      <c r="AI2" s="55" t="s">
+      <c r="N2" s="47"/>
+      <c r="O2" s="47"/>
+      <c r="P2" s="47"/>
+      <c r="Q2" s="47"/>
+      <c r="R2" s="48"/>
+      <c r="AI2" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="AJ2" s="56"/>
-      <c r="AK2" s="56"/>
-      <c r="AL2" s="56"/>
-      <c r="AM2" s="56"/>
-      <c r="AN2" s="56"/>
-      <c r="AO2" s="57"/>
-      <c r="AU2" s="55" t="s">
+      <c r="AJ2" s="47"/>
+      <c r="AK2" s="47"/>
+      <c r="AL2" s="47"/>
+      <c r="AM2" s="47"/>
+      <c r="AN2" s="47"/>
+      <c r="AO2" s="48"/>
+      <c r="AU2" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="AV2" s="56"/>
-      <c r="AW2" s="56"/>
-      <c r="AX2" s="56"/>
-      <c r="AY2" s="56"/>
-      <c r="AZ2" s="56"/>
-      <c r="BA2" s="57"/>
+      <c r="AV2" s="47"/>
+      <c r="AW2" s="47"/>
+      <c r="AX2" s="47"/>
+      <c r="AY2" s="47"/>
+      <c r="AZ2" s="47"/>
+      <c r="BA2" s="48"/>
     </row>
     <row r="3" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="49" t="s">
+      <c r="A3" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="49"/>
-      <c r="C3" s="49"/>
-      <c r="D3" s="49"/>
-      <c r="E3" s="49"/>
-      <c r="F3" s="49"/>
-      <c r="G3" s="49"/>
-      <c r="AI3" s="42" t="s">
+      <c r="B3" s="42"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="42"/>
+      <c r="AI3" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="AJ3" s="43"/>
-      <c r="AK3" s="43"/>
-      <c r="AL3" s="43"/>
-      <c r="AM3" s="43"/>
-      <c r="AN3" s="43"/>
-      <c r="AO3" s="44"/>
-      <c r="AU3" s="49" t="s">
+      <c r="AJ3" s="54"/>
+      <c r="AK3" s="54"/>
+      <c r="AL3" s="54"/>
+      <c r="AM3" s="54"/>
+      <c r="AN3" s="54"/>
+      <c r="AO3" s="55"/>
+      <c r="AU3" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="AV3" s="49"/>
-      <c r="AW3" s="49"/>
-      <c r="AX3" s="49"/>
-      <c r="AY3" s="49"/>
-      <c r="AZ3" s="49"/>
-      <c r="BA3" s="49"/>
+      <c r="AV3" s="42"/>
+      <c r="AW3" s="42"/>
+      <c r="AX3" s="42"/>
+      <c r="AY3" s="42"/>
+      <c r="AZ3" s="42"/>
+      <c r="BA3" s="42"/>
     </row>
     <row r="4" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
@@ -1494,15 +1503,15 @@
       <c r="G4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="42" t="s">
+      <c r="M4" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="N4" s="43"/>
-      <c r="O4" s="43"/>
-      <c r="P4" s="43"/>
-      <c r="Q4" s="43"/>
-      <c r="R4" s="43"/>
-      <c r="S4" s="44"/>
+      <c r="N4" s="54"/>
+      <c r="O4" s="54"/>
+      <c r="P4" s="54"/>
+      <c r="Q4" s="54"/>
+      <c r="R4" s="54"/>
+      <c r="S4" s="55"/>
       <c r="AI4" s="3" t="s">
         <v>2</v>
       </c>
@@ -1763,9 +1772,9 @@
       </c>
       <c r="F8" s="13"/>
       <c r="G8" s="16"/>
-      <c r="I8" s="50"/>
-      <c r="J8" s="50"/>
-      <c r="K8" s="50"/>
+      <c r="I8" s="43"/>
+      <c r="J8" s="43"/>
+      <c r="K8" s="43"/>
       <c r="M8" s="8">
         <v>3</v>
       </c>
@@ -1784,9 +1793,9 @@
       <c r="AM8" s="30"/>
       <c r="AN8" s="31"/>
       <c r="AO8" s="16"/>
-      <c r="AQ8" s="50"/>
-      <c r="AR8" s="50"/>
-      <c r="AS8" s="50"/>
+      <c r="AQ8" s="43"/>
+      <c r="AR8" s="43"/>
+      <c r="AS8" s="43"/>
       <c r="AU8" s="38">
         <v>4</v>
       </c>
@@ -1962,15 +1971,15 @@
       <c r="BA11" s="6"/>
     </row>
     <row r="12" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="49" t="s">
+      <c r="A12" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="49"/>
-      <c r="C12" s="49"/>
-      <c r="D12" s="49"/>
-      <c r="E12" s="49"/>
-      <c r="F12" s="49"/>
-      <c r="G12" s="49"/>
+      <c r="B12" s="42"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="42"/>
       <c r="L12" s="12"/>
       <c r="M12" s="8" t="s">
         <v>12</v>
@@ -1981,65 +1990,65 @@
       <c r="Q12" s="12"/>
       <c r="R12" s="13"/>
       <c r="S12" s="16"/>
-      <c r="AI12" s="49" t="s">
+      <c r="AI12" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AJ12" s="49"/>
-      <c r="AK12" s="49"/>
-      <c r="AL12" s="49"/>
-      <c r="AM12" s="49"/>
-      <c r="AN12" s="49"/>
-      <c r="AO12" s="49"/>
+      <c r="AJ12" s="42"/>
+      <c r="AK12" s="42"/>
+      <c r="AL12" s="42"/>
+      <c r="AM12" s="42"/>
+      <c r="AN12" s="42"/>
+      <c r="AO12" s="42"/>
       <c r="AQ12" s="12"/>
-      <c r="AU12" s="49" t="s">
+      <c r="AU12" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AV12" s="49"/>
-      <c r="AW12" s="49"/>
-      <c r="AX12" s="49"/>
-      <c r="AY12" s="49"/>
-      <c r="AZ12" s="49"/>
-      <c r="BA12" s="49"/>
+      <c r="AV12" s="42"/>
+      <c r="AW12" s="42"/>
+      <c r="AX12" s="42"/>
+      <c r="AY12" s="42"/>
+      <c r="AZ12" s="42"/>
+      <c r="BA12" s="42"/>
     </row>
     <row r="13" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L13" s="12"/>
-      <c r="M13" s="42" t="s">
+      <c r="M13" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="N13" s="43"/>
-      <c r="O13" s="43"/>
-      <c r="P13" s="43"/>
-      <c r="Q13" s="43"/>
-      <c r="R13" s="43"/>
-      <c r="S13" s="44"/>
+      <c r="N13" s="54"/>
+      <c r="O13" s="54"/>
+      <c r="P13" s="54"/>
+      <c r="Q13" s="54"/>
+      <c r="R13" s="54"/>
+      <c r="S13" s="55"/>
       <c r="AQ13" s="12"/>
     </row>
     <row r="14" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="48" t="s">
+      <c r="A14" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="48"/>
-      <c r="C14" s="48"/>
-      <c r="D14" s="48"/>
-      <c r="E14" s="48"/>
-      <c r="F14" s="48"/>
-      <c r="G14" s="48"/>
-      <c r="L14" s="54"/>
-      <c r="M14" s="50"/>
-      <c r="N14" s="50"/>
-      <c r="AN14" s="50"/>
-      <c r="AO14" s="50"/>
-      <c r="AP14" s="50"/>
+      <c r="B14" s="45"/>
+      <c r="C14" s="45"/>
+      <c r="D14" s="45"/>
+      <c r="E14" s="45"/>
+      <c r="F14" s="45"/>
+      <c r="G14" s="45"/>
+      <c r="L14" s="44"/>
+      <c r="M14" s="43"/>
+      <c r="N14" s="43"/>
+      <c r="AN14" s="43"/>
+      <c r="AO14" s="43"/>
+      <c r="AP14" s="43"/>
       <c r="AQ14" s="12"/>
-      <c r="AU14" s="48" t="s">
+      <c r="AU14" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="AV14" s="48"/>
-      <c r="AW14" s="48"/>
-      <c r="AX14" s="48"/>
-      <c r="AY14" s="48"/>
-      <c r="AZ14" s="48"/>
-      <c r="BA14" s="48"/>
+      <c r="AV14" s="45"/>
+      <c r="AW14" s="45"/>
+      <c r="AX14" s="45"/>
+      <c r="AY14" s="45"/>
+      <c r="AZ14" s="45"/>
+      <c r="BA14" s="45"/>
     </row>
     <row r="15" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
@@ -2201,12 +2210,21 @@
       <c r="C18" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="D18" s="13"/>
+      <c r="D18" s="13">
+        <v>2</v>
+      </c>
       <c r="E18" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="F18" s="13"/>
-      <c r="G18" s="16"/>
+      <c r="F18" s="13">
+        <v>3</v>
+      </c>
+      <c r="G18" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="L18" s="12"/>
       <c r="O18" s="12"/>
       <c r="AN18" s="12"/>
@@ -2252,15 +2270,15 @@
       </c>
       <c r="F19" s="31"/>
       <c r="G19" s="32"/>
-      <c r="I19" s="50"/>
-      <c r="J19" s="50"/>
-      <c r="K19" s="50"/>
+      <c r="I19" s="43"/>
+      <c r="J19" s="43"/>
+      <c r="K19" s="43"/>
       <c r="L19" s="12"/>
       <c r="O19" s="12"/>
       <c r="AN19" s="12"/>
-      <c r="AQ19" s="54"/>
-      <c r="AR19" s="50"/>
-      <c r="AS19" s="50"/>
+      <c r="AQ19" s="44"/>
+      <c r="AR19" s="43"/>
+      <c r="AS19" s="43"/>
       <c r="AU19" s="38">
         <v>4</v>
       </c>
@@ -2380,52 +2398,52 @@
       <c r="BA22" s="6"/>
     </row>
     <row r="23" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="49" t="s">
+      <c r="A23" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B23" s="49"/>
-      <c r="C23" s="49"/>
-      <c r="D23" s="49"/>
-      <c r="E23" s="49"/>
-      <c r="F23" s="49"/>
-      <c r="G23" s="49"/>
+      <c r="B23" s="42"/>
+      <c r="C23" s="42"/>
+      <c r="D23" s="42"/>
+      <c r="E23" s="42"/>
+      <c r="F23" s="42"/>
+      <c r="G23" s="42"/>
       <c r="O23" s="12"/>
       <c r="AN23" s="12"/>
-      <c r="AU23" s="49" t="s">
+      <c r="AU23" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AV23" s="49"/>
-      <c r="AW23" s="49"/>
-      <c r="AX23" s="49"/>
-      <c r="AY23" s="49"/>
-      <c r="AZ23" s="49"/>
-      <c r="BA23" s="49"/>
+      <c r="AV23" s="42"/>
+      <c r="AW23" s="42"/>
+      <c r="AX23" s="42"/>
+      <c r="AY23" s="42"/>
+      <c r="AZ23" s="42"/>
+      <c r="BA23" s="42"/>
     </row>
     <row r="24" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="O24" s="12"/>
       <c r="AN24" s="12"/>
     </row>
     <row r="25" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="49" t="s">
+      <c r="A25" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="49"/>
-      <c r="C25" s="49"/>
-      <c r="D25" s="49"/>
-      <c r="E25" s="49"/>
-      <c r="F25" s="49"/>
-      <c r="G25" s="49"/>
+      <c r="B25" s="42"/>
+      <c r="C25" s="42"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="42"/>
+      <c r="F25" s="42"/>
+      <c r="G25" s="42"/>
       <c r="O25" s="12"/>
       <c r="AN25" s="12"/>
-      <c r="AU25" s="49" t="s">
+      <c r="AU25" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="AV25" s="49"/>
-      <c r="AW25" s="49"/>
-      <c r="AX25" s="49"/>
-      <c r="AY25" s="49"/>
-      <c r="AZ25" s="49"/>
-      <c r="BA25" s="49"/>
+      <c r="AV25" s="42"/>
+      <c r="AW25" s="42"/>
+      <c r="AX25" s="42"/>
+      <c r="AY25" s="42"/>
+      <c r="AZ25" s="42"/>
+      <c r="BA25" s="42"/>
     </row>
     <row r="26" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="20" t="s">
@@ -2449,24 +2467,24 @@
       <c r="G26" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="O26" s="54"/>
-      <c r="P26" s="50"/>
-      <c r="Q26" s="50"/>
-      <c r="R26" s="50"/>
-      <c r="S26" s="50"/>
-      <c r="T26" s="50"/>
-      <c r="U26" s="50"/>
-      <c r="V26" s="50"/>
-      <c r="W26" s="50"/>
-      <c r="AE26" s="50"/>
-      <c r="AF26" s="50"/>
-      <c r="AG26" s="50"/>
-      <c r="AH26" s="50"/>
-      <c r="AI26" s="50"/>
-      <c r="AJ26" s="50"/>
-      <c r="AK26" s="50"/>
-      <c r="AL26" s="50"/>
-      <c r="AM26" s="58"/>
+      <c r="O26" s="44"/>
+      <c r="P26" s="43"/>
+      <c r="Q26" s="43"/>
+      <c r="R26" s="43"/>
+      <c r="S26" s="43"/>
+      <c r="T26" s="43"/>
+      <c r="U26" s="43"/>
+      <c r="V26" s="43"/>
+      <c r="W26" s="43"/>
+      <c r="AE26" s="43"/>
+      <c r="AF26" s="43"/>
+      <c r="AG26" s="43"/>
+      <c r="AH26" s="43"/>
+      <c r="AI26" s="43"/>
+      <c r="AJ26" s="43"/>
+      <c r="AK26" s="43"/>
+      <c r="AL26" s="43"/>
+      <c r="AM26" s="49"/>
       <c r="AU26" s="20" t="s">
         <v>2</v>
       </c>
@@ -2563,26 +2581,26 @@
         <v>54</v>
       </c>
       <c r="O28" s="12"/>
-      <c r="P28" s="42" t="s">
+      <c r="P28" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="Q28" s="43"/>
-      <c r="R28" s="43"/>
-      <c r="S28" s="43"/>
-      <c r="T28" s="43"/>
-      <c r="U28" s="43"/>
-      <c r="V28" s="44"/>
+      <c r="Q28" s="54"/>
+      <c r="R28" s="54"/>
+      <c r="S28" s="54"/>
+      <c r="T28" s="54"/>
+      <c r="U28" s="54"/>
+      <c r="V28" s="55"/>
       <c r="X28" s="12"/>
       <c r="AD28" s="13"/>
-      <c r="AF28" s="49" t="s">
+      <c r="AF28" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="AG28" s="49"/>
-      <c r="AH28" s="49"/>
-      <c r="AI28" s="49"/>
-      <c r="AJ28" s="49"/>
-      <c r="AK28" s="49"/>
-      <c r="AL28" s="49"/>
+      <c r="AG28" s="42"/>
+      <c r="AH28" s="42"/>
+      <c r="AI28" s="42"/>
+      <c r="AJ28" s="42"/>
+      <c r="AK28" s="42"/>
+      <c r="AL28" s="42"/>
       <c r="AN28" s="12"/>
       <c r="AU28" s="8">
         <v>2</v>
@@ -2683,12 +2701,18 @@
       <c r="AW29" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="AX29" s="13"/>
+      <c r="AX29" s="13">
+        <v>2</v>
+      </c>
       <c r="AY29" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="AZ29" s="13"/>
-      <c r="BA29" s="16"/>
+      <c r="AZ29" s="13">
+        <v>4</v>
+      </c>
+      <c r="BA29" s="16" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="30" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A30" s="8">
@@ -2706,9 +2730,9 @@
       </c>
       <c r="F30" s="31"/>
       <c r="G30" s="32"/>
-      <c r="I30" s="50"/>
-      <c r="J30" s="50"/>
-      <c r="K30" s="50"/>
+      <c r="I30" s="43"/>
+      <c r="J30" s="43"/>
+      <c r="K30" s="43"/>
       <c r="O30" s="12"/>
       <c r="P30" s="7">
         <v>1</v>
@@ -2731,9 +2755,9 @@
       <c r="AK30" s="24"/>
       <c r="AL30" s="25"/>
       <c r="AN30" s="12"/>
-      <c r="AQ30" s="50"/>
-      <c r="AR30" s="50"/>
-      <c r="AS30" s="50"/>
+      <c r="AQ30" s="43"/>
+      <c r="AR30" s="43"/>
+      <c r="AS30" s="43"/>
       <c r="AU30" s="38">
         <v>4</v>
       </c>
@@ -2921,15 +2945,15 @@
       <c r="BA33" s="6"/>
     </row>
     <row r="34" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="49" t="s">
+      <c r="A34" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B34" s="49"/>
-      <c r="C34" s="49"/>
-      <c r="D34" s="49"/>
-      <c r="E34" s="49"/>
-      <c r="F34" s="49"/>
-      <c r="G34" s="49"/>
+      <c r="B34" s="42"/>
+      <c r="C34" s="42"/>
+      <c r="D34" s="42"/>
+      <c r="E34" s="42"/>
+      <c r="F34" s="42"/>
+      <c r="G34" s="42"/>
       <c r="L34" s="12"/>
       <c r="O34" s="12"/>
       <c r="P34" s="8" t="s">
@@ -2954,15 +2978,15 @@
       <c r="AL34" s="16"/>
       <c r="AN34" s="12"/>
       <c r="AQ34" s="12"/>
-      <c r="AU34" s="49" t="s">
+      <c r="AU34" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AV34" s="49"/>
-      <c r="AW34" s="49"/>
-      <c r="AX34" s="49"/>
-      <c r="AY34" s="49"/>
-      <c r="AZ34" s="49"/>
-      <c r="BA34" s="49"/>
+      <c r="AV34" s="42"/>
+      <c r="AW34" s="42"/>
+      <c r="AX34" s="42"/>
+      <c r="AY34" s="42"/>
+      <c r="AZ34" s="42"/>
+      <c r="BA34" s="42"/>
     </row>
     <row r="35" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L35" s="12"/>
@@ -2991,18 +3015,18 @@
       <c r="AQ35" s="12"/>
     </row>
     <row r="36" spans="1:53" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="48" t="s">
+      <c r="A36" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="B36" s="48"/>
-      <c r="C36" s="48"/>
-      <c r="D36" s="48"/>
-      <c r="E36" s="48"/>
-      <c r="F36" s="48"/>
-      <c r="G36" s="48"/>
-      <c r="L36" s="54"/>
-      <c r="M36" s="50"/>
-      <c r="N36" s="50"/>
+      <c r="B36" s="45"/>
+      <c r="C36" s="45"/>
+      <c r="D36" s="45"/>
+      <c r="E36" s="45"/>
+      <c r="F36" s="45"/>
+      <c r="G36" s="45"/>
+      <c r="L36" s="44"/>
+      <c r="M36" s="43"/>
+      <c r="N36" s="43"/>
       <c r="O36" s="12"/>
       <c r="P36" s="8" t="s">
         <v>12</v>
@@ -3024,19 +3048,19 @@
       <c r="AJ36" s="35"/>
       <c r="AK36" s="36"/>
       <c r="AL36" s="37"/>
-      <c r="AN36" s="54"/>
-      <c r="AO36" s="50"/>
-      <c r="AP36" s="50"/>
+      <c r="AN36" s="44"/>
+      <c r="AO36" s="43"/>
+      <c r="AP36" s="43"/>
       <c r="AQ36" s="12"/>
-      <c r="AU36" s="48" t="s">
+      <c r="AU36" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="AV36" s="48"/>
-      <c r="AW36" s="48"/>
-      <c r="AX36" s="48"/>
-      <c r="AY36" s="48"/>
-      <c r="AZ36" s="48"/>
-      <c r="BA36" s="48"/>
+      <c r="AV36" s="45"/>
+      <c r="AW36" s="45"/>
+      <c r="AX36" s="45"/>
+      <c r="AY36" s="45"/>
+      <c r="AZ36" s="45"/>
+      <c r="BA36" s="45"/>
     </row>
     <row r="37" spans="1:53" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37" s="20" t="s">
@@ -3061,31 +3085,31 @@
         <v>9</v>
       </c>
       <c r="L37" s="12"/>
-      <c r="P37" s="45" t="s">
+      <c r="P37" s="56" t="s">
         <v>13</v>
       </c>
-      <c r="Q37" s="46"/>
-      <c r="R37" s="46"/>
-      <c r="S37" s="46"/>
-      <c r="T37" s="46"/>
-      <c r="U37" s="46"/>
-      <c r="V37" s="47"/>
-      <c r="X37" s="54"/>
-      <c r="Y37" s="50"/>
-      <c r="Z37" s="50"/>
-      <c r="AA37" s="50"/>
-      <c r="AB37" s="50"/>
-      <c r="AC37" s="50"/>
-      <c r="AD37" s="58"/>
-      <c r="AF37" s="49" t="s">
+      <c r="Q37" s="57"/>
+      <c r="R37" s="57"/>
+      <c r="S37" s="57"/>
+      <c r="T37" s="57"/>
+      <c r="U37" s="57"/>
+      <c r="V37" s="58"/>
+      <c r="X37" s="44"/>
+      <c r="Y37" s="43"/>
+      <c r="Z37" s="43"/>
+      <c r="AA37" s="43"/>
+      <c r="AB37" s="43"/>
+      <c r="AC37" s="43"/>
+      <c r="AD37" s="49"/>
+      <c r="AF37" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AG37" s="49"/>
-      <c r="AH37" s="49"/>
-      <c r="AI37" s="49"/>
-      <c r="AJ37" s="49"/>
-      <c r="AK37" s="49"/>
-      <c r="AL37" s="49"/>
+      <c r="AG37" s="42"/>
+      <c r="AH37" s="42"/>
+      <c r="AI37" s="42"/>
+      <c r="AJ37" s="42"/>
+      <c r="AK37" s="42"/>
+      <c r="AL37" s="42"/>
       <c r="AQ37" s="12"/>
       <c r="AU37" s="3" t="s">
         <v>2</v>
@@ -3178,33 +3202,33 @@
         <v>53</v>
       </c>
       <c r="L39" s="12"/>
-      <c r="M39" s="42" t="s">
+      <c r="M39" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="N39" s="43"/>
-      <c r="O39" s="43"/>
-      <c r="P39" s="43"/>
-      <c r="Q39" s="43"/>
-      <c r="R39" s="43"/>
-      <c r="S39" s="44"/>
-      <c r="X39" s="49" t="s">
+      <c r="N39" s="54"/>
+      <c r="O39" s="54"/>
+      <c r="P39" s="54"/>
+      <c r="Q39" s="54"/>
+      <c r="R39" s="54"/>
+      <c r="S39" s="55"/>
+      <c r="X39" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="Y39" s="49"/>
-      <c r="Z39" s="49"/>
-      <c r="AA39" s="49"/>
-      <c r="AB39" s="49"/>
-      <c r="AC39" s="49"/>
-      <c r="AD39" s="49"/>
-      <c r="AI39" s="42" t="s">
+      <c r="Y39" s="42"/>
+      <c r="Z39" s="42"/>
+      <c r="AA39" s="42"/>
+      <c r="AB39" s="42"/>
+      <c r="AC39" s="42"/>
+      <c r="AD39" s="42"/>
+      <c r="AI39" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="AJ39" s="43"/>
-      <c r="AK39" s="43"/>
-      <c r="AL39" s="43"/>
-      <c r="AM39" s="43"/>
-      <c r="AN39" s="43"/>
-      <c r="AO39" s="44"/>
+      <c r="AJ39" s="54"/>
+      <c r="AK39" s="54"/>
+      <c r="AL39" s="54"/>
+      <c r="AM39" s="54"/>
+      <c r="AN39" s="54"/>
+      <c r="AO39" s="55"/>
       <c r="AQ39" s="12"/>
       <c r="AU39" s="8">
         <v>2</v>
@@ -3324,12 +3348,18 @@
       <c r="AW40" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="AX40" s="13"/>
+      <c r="AX40" s="13">
+        <v>4</v>
+      </c>
       <c r="AY40" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="AZ40" s="13"/>
-      <c r="BA40" s="16"/>
+      <c r="AZ40" s="13">
+        <v>7</v>
+      </c>
+      <c r="BA40" s="16" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="41" spans="1:53" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A41" s="8">
@@ -3347,9 +3377,9 @@
       </c>
       <c r="F41" s="31"/>
       <c r="G41" s="32"/>
-      <c r="I41" s="50"/>
-      <c r="J41" s="50"/>
-      <c r="K41" s="50"/>
+      <c r="I41" s="43"/>
+      <c r="J41" s="43"/>
+      <c r="K41" s="43"/>
       <c r="L41" s="12"/>
       <c r="M41" s="7">
         <v>1</v>
@@ -3378,9 +3408,9 @@
       <c r="AM41" s="23"/>
       <c r="AN41" s="24"/>
       <c r="AO41" s="25"/>
-      <c r="AQ41" s="54"/>
-      <c r="AR41" s="50"/>
-      <c r="AS41" s="50"/>
+      <c r="AQ41" s="44"/>
+      <c r="AR41" s="43"/>
+      <c r="AS41" s="43"/>
       <c r="AU41" s="38">
         <v>4</v>
       </c>
@@ -3575,15 +3605,15 @@
       <c r="BA44" s="6"/>
     </row>
     <row r="45" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="49" t="s">
+      <c r="A45" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B45" s="49"/>
-      <c r="C45" s="49"/>
-      <c r="D45" s="49"/>
-      <c r="E45" s="49"/>
-      <c r="F45" s="49"/>
-      <c r="G45" s="49"/>
+      <c r="B45" s="42"/>
+      <c r="C45" s="42"/>
+      <c r="D45" s="42"/>
+      <c r="E45" s="42"/>
+      <c r="F45" s="42"/>
+      <c r="G45" s="42"/>
       <c r="M45" s="8" t="s">
         <v>11</v>
       </c>
@@ -3611,15 +3641,15 @@
       <c r="AM45" s="12"/>
       <c r="AN45" s="13"/>
       <c r="AO45" s="16"/>
-      <c r="AU45" s="49" t="s">
+      <c r="AU45" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AV45" s="49"/>
-      <c r="AW45" s="49"/>
-      <c r="AX45" s="49"/>
-      <c r="AY45" s="49"/>
-      <c r="AZ45" s="49"/>
-      <c r="BA45" s="49"/>
+      <c r="AV45" s="42"/>
+      <c r="AW45" s="42"/>
+      <c r="AX45" s="42"/>
+      <c r="AY45" s="42"/>
+      <c r="AZ45" s="42"/>
+      <c r="BA45" s="42"/>
     </row>
     <row r="46" spans="1:53" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="M46" s="8" t="s">
@@ -3680,49 +3710,61 @@
       <c r="AO47" s="6"/>
     </row>
     <row r="48" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="M48" s="42" t="s">
+      <c r="M48" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="N48" s="43"/>
-      <c r="O48" s="43"/>
-      <c r="P48" s="43"/>
-      <c r="Q48" s="43"/>
-      <c r="R48" s="43"/>
-      <c r="S48" s="44"/>
-      <c r="X48" s="49" t="s">
+      <c r="N48" s="54"/>
+      <c r="O48" s="54"/>
+      <c r="P48" s="54"/>
+      <c r="Q48" s="54"/>
+      <c r="R48" s="54"/>
+      <c r="S48" s="55"/>
+      <c r="X48" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="Y48" s="49"/>
-      <c r="Z48" s="49"/>
-      <c r="AA48" s="49"/>
-      <c r="AB48" s="49"/>
-      <c r="AC48" s="49"/>
-      <c r="AD48" s="49"/>
-      <c r="AI48" s="49" t="s">
+      <c r="Y48" s="42"/>
+      <c r="Z48" s="42"/>
+      <c r="AA48" s="42"/>
+      <c r="AB48" s="42"/>
+      <c r="AC48" s="42"/>
+      <c r="AD48" s="42"/>
+      <c r="AI48" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AJ48" s="49"/>
-      <c r="AK48" s="49"/>
-      <c r="AL48" s="49"/>
-      <c r="AM48" s="49"/>
-      <c r="AN48" s="49"/>
-      <c r="AO48" s="49"/>
+      <c r="AJ48" s="42"/>
+      <c r="AK48" s="42"/>
+      <c r="AL48" s="42"/>
+      <c r="AM48" s="42"/>
+      <c r="AN48" s="42"/>
+      <c r="AO48" s="42"/>
     </row>
     <row r="49" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="AU45:BA45"/>
-    <mergeCell ref="AF28:AL28"/>
-    <mergeCell ref="AF37:AL37"/>
-    <mergeCell ref="AQ30:AS30"/>
-    <mergeCell ref="AQ41:AS41"/>
-    <mergeCell ref="AU34:BA34"/>
-    <mergeCell ref="AU36:BA36"/>
-    <mergeCell ref="AU2:BA2"/>
-    <mergeCell ref="AU3:BA3"/>
-    <mergeCell ref="AU12:BA12"/>
-    <mergeCell ref="AU14:BA14"/>
-    <mergeCell ref="AU23:BA23"/>
+    <mergeCell ref="M48:S48"/>
+    <mergeCell ref="M39:S39"/>
+    <mergeCell ref="P37:V37"/>
+    <mergeCell ref="P28:V28"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A1:U1"/>
+    <mergeCell ref="O26:W26"/>
+    <mergeCell ref="I41:K41"/>
+    <mergeCell ref="L14:N14"/>
+    <mergeCell ref="L36:N36"/>
+    <mergeCell ref="M2:R2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="M4:S4"/>
+    <mergeCell ref="M13:S13"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="A25:G25"/>
     <mergeCell ref="X37:AD37"/>
     <mergeCell ref="AE26:AM26"/>
     <mergeCell ref="Z1:AB1"/>
@@ -3739,30 +3781,18 @@
     <mergeCell ref="AN36:AP36"/>
     <mergeCell ref="AQ8:AS8"/>
     <mergeCell ref="AQ19:AS19"/>
-    <mergeCell ref="A1:U1"/>
-    <mergeCell ref="O26:W26"/>
-    <mergeCell ref="I41:K41"/>
-    <mergeCell ref="L14:N14"/>
-    <mergeCell ref="L36:N36"/>
-    <mergeCell ref="M2:R2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="M4:S4"/>
-    <mergeCell ref="M13:S13"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A23:G23"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="M48:S48"/>
-    <mergeCell ref="M39:S39"/>
-    <mergeCell ref="P37:V37"/>
-    <mergeCell ref="P28:V28"/>
-    <mergeCell ref="A36:G36"/>
-    <mergeCell ref="A45:G45"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="AU2:BA2"/>
+    <mergeCell ref="AU3:BA3"/>
+    <mergeCell ref="AU12:BA12"/>
+    <mergeCell ref="AU14:BA14"/>
+    <mergeCell ref="AU23:BA23"/>
+    <mergeCell ref="AU45:BA45"/>
+    <mergeCell ref="AF28:AL28"/>
+    <mergeCell ref="AF37:AL37"/>
+    <mergeCell ref="AQ30:AS30"/>
+    <mergeCell ref="AQ41:AS41"/>
+    <mergeCell ref="AU34:BA34"/>
+    <mergeCell ref="AU36:BA36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/2025_2026/Playoffs/Brackets.xlsx
+++ b/2025_2026/Playoffs/Brackets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\NHLStats\2025_2026\Playoffs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07B6EC2A-D06C-4331-94E7-6078B8574F94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0255A120-D0A2-4EB5-B25D-3CF89B000C06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="70">
   <si>
     <t>Eastern Conference Playoff Teams</t>
   </si>
@@ -227,6 +227,15 @@
   </si>
   <si>
     <t>Canadiens Lead 2-1</t>
+  </si>
+  <si>
+    <t>Hurricanes Win Series 4-0</t>
+  </si>
+  <si>
+    <t>Series Tied 2-2</t>
+  </si>
+  <si>
+    <t>Flyers Lead 3-1</t>
   </si>
 </sst>
 </file>
@@ -605,18 +614,45 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -629,40 +665,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1032,18 +1041,18 @@
     </row>
     <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="11" spans="1:7" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="59" t="s">
+      <c r="A11" s="61" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="59"/>
-      <c r="C11" s="59" t="s">
+      <c r="B11" s="61"/>
+      <c r="C11" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="59"/>
-      <c r="E11" s="59" t="s">
+      <c r="D11" s="61"/>
+      <c r="E11" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="59"/>
+      <c r="F11" s="61"/>
       <c r="G11" s="4" t="s">
         <v>18</v>
       </c>
@@ -1072,18 +1081,18 @@
       </c>
     </row>
     <row r="13" spans="1:7" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="60" t="s">
+      <c r="A13" s="59" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="61"/>
-      <c r="C13" s="60" t="s">
+      <c r="B13" s="60"/>
+      <c r="C13" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="D13" s="61"/>
-      <c r="E13" s="60" t="s">
+      <c r="D13" s="60"/>
+      <c r="E13" s="59" t="s">
         <v>17</v>
       </c>
-      <c r="F13" s="61"/>
+      <c r="F13" s="60"/>
       <c r="G13" s="5"/>
     </row>
     <row r="14" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1110,14 +1119,14 @@
       <c r="F15" s="6"/>
     </row>
     <row r="16" spans="1:7" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="60" t="s">
+      <c r="A16" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="61"/>
-      <c r="C16" s="60" t="s">
+      <c r="B16" s="60"/>
+      <c r="C16" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="61"/>
+      <c r="D16" s="60"/>
     </row>
     <row r="17" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
@@ -1139,10 +1148,10 @@
       <c r="D18" s="6"/>
     </row>
     <row r="19" spans="1:4" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="60" t="s">
+      <c r="A19" s="59" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="61"/>
+      <c r="B19" s="60"/>
     </row>
     <row r="20" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
@@ -1161,10 +1170,10 @@
       </c>
     </row>
     <row r="22" spans="1:4" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="60" t="s">
+      <c r="A22" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="61"/>
+      <c r="B22" s="60"/>
     </row>
     <row r="23" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
@@ -1249,16 +1258,16 @@
     <sortCondition ref="B2:B9"/>
   </sortState>
   <mergeCells count="10">
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A16:B16"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A16:B16"/>
   </mergeCells>
   <dataValidations count="16">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C14" xr:uid="{2C3D9587-ABAE-4E3F-8B22-396DF812BF02}">
@@ -1362,124 +1371,124 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:54" ht="27.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
-      <c r="I1" s="51"/>
-      <c r="J1" s="51"/>
-      <c r="K1" s="51"/>
-      <c r="L1" s="51"/>
-      <c r="M1" s="51"/>
-      <c r="N1" s="51"/>
-      <c r="O1" s="51"/>
-      <c r="P1" s="51"/>
-      <c r="Q1" s="51"/>
-      <c r="R1" s="51"/>
-      <c r="S1" s="51"/>
-      <c r="T1" s="51"/>
-      <c r="U1" s="52"/>
-      <c r="Z1" s="50" t="s">
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="52"/>
+      <c r="M1" s="52"/>
+      <c r="N1" s="52"/>
+      <c r="O1" s="52"/>
+      <c r="P1" s="52"/>
+      <c r="Q1" s="52"/>
+      <c r="R1" s="52"/>
+      <c r="S1" s="52"/>
+      <c r="T1" s="52"/>
+      <c r="U1" s="53"/>
+      <c r="Z1" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="AA1" s="51"/>
-      <c r="AB1" s="52"/>
-      <c r="AF1" s="50" t="s">
+      <c r="AA1" s="52"/>
+      <c r="AB1" s="53"/>
+      <c r="AF1" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="AG1" s="51"/>
-      <c r="AH1" s="51"/>
-      <c r="AI1" s="51"/>
-      <c r="AJ1" s="51"/>
-      <c r="AK1" s="51"/>
-      <c r="AL1" s="51"/>
-      <c r="AM1" s="51"/>
-      <c r="AN1" s="51"/>
-      <c r="AO1" s="51"/>
-      <c r="AP1" s="51"/>
-      <c r="AQ1" s="51"/>
-      <c r="AR1" s="51"/>
-      <c r="AS1" s="51"/>
-      <c r="AT1" s="51"/>
-      <c r="AU1" s="51"/>
-      <c r="AV1" s="51"/>
-      <c r="AW1" s="51"/>
-      <c r="AX1" s="51"/>
-      <c r="AY1" s="51"/>
-      <c r="AZ1" s="51"/>
-      <c r="BA1" s="52"/>
+      <c r="AG1" s="52"/>
+      <c r="AH1" s="52"/>
+      <c r="AI1" s="52"/>
+      <c r="AJ1" s="52"/>
+      <c r="AK1" s="52"/>
+      <c r="AL1" s="52"/>
+      <c r="AM1" s="52"/>
+      <c r="AN1" s="52"/>
+      <c r="AO1" s="52"/>
+      <c r="AP1" s="52"/>
+      <c r="AQ1" s="52"/>
+      <c r="AR1" s="52"/>
+      <c r="AS1" s="52"/>
+      <c r="AT1" s="52"/>
+      <c r="AU1" s="52"/>
+      <c r="AV1" s="52"/>
+      <c r="AW1" s="52"/>
+      <c r="AX1" s="52"/>
+      <c r="AY1" s="52"/>
+      <c r="AZ1" s="52"/>
+      <c r="BA1" s="53"/>
     </row>
     <row r="2" spans="1:54" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="48"/>
-      <c r="M2" s="46" t="s">
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="57"/>
+      <c r="M2" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="47"/>
-      <c r="O2" s="47"/>
-      <c r="P2" s="47"/>
-      <c r="Q2" s="47"/>
-      <c r="R2" s="48"/>
-      <c r="AI2" s="46" t="s">
+      <c r="N2" s="56"/>
+      <c r="O2" s="56"/>
+      <c r="P2" s="56"/>
+      <c r="Q2" s="56"/>
+      <c r="R2" s="57"/>
+      <c r="AI2" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="AJ2" s="47"/>
-      <c r="AK2" s="47"/>
-      <c r="AL2" s="47"/>
-      <c r="AM2" s="47"/>
-      <c r="AN2" s="47"/>
-      <c r="AO2" s="48"/>
-      <c r="AU2" s="46" t="s">
+      <c r="AJ2" s="56"/>
+      <c r="AK2" s="56"/>
+      <c r="AL2" s="56"/>
+      <c r="AM2" s="56"/>
+      <c r="AN2" s="56"/>
+      <c r="AO2" s="57"/>
+      <c r="AU2" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="AV2" s="47"/>
-      <c r="AW2" s="47"/>
-      <c r="AX2" s="47"/>
-      <c r="AY2" s="47"/>
-      <c r="AZ2" s="47"/>
-      <c r="BA2" s="48"/>
+      <c r="AV2" s="56"/>
+      <c r="AW2" s="56"/>
+      <c r="AX2" s="56"/>
+      <c r="AY2" s="56"/>
+      <c r="AZ2" s="56"/>
+      <c r="BA2" s="57"/>
     </row>
     <row r="3" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="42" t="s">
+      <c r="A3" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="42"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="42"/>
-      <c r="AI3" s="53" t="s">
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="AI3" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="AJ3" s="54"/>
-      <c r="AK3" s="54"/>
-      <c r="AL3" s="54"/>
-      <c r="AM3" s="54"/>
-      <c r="AN3" s="54"/>
-      <c r="AO3" s="55"/>
-      <c r="AU3" s="42" t="s">
+      <c r="AJ3" s="43"/>
+      <c r="AK3" s="43"/>
+      <c r="AL3" s="43"/>
+      <c r="AM3" s="43"/>
+      <c r="AN3" s="43"/>
+      <c r="AO3" s="44"/>
+      <c r="AU3" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="AV3" s="42"/>
-      <c r="AW3" s="42"/>
-      <c r="AX3" s="42"/>
-      <c r="AY3" s="42"/>
-      <c r="AZ3" s="42"/>
-      <c r="BA3" s="42"/>
+      <c r="AV3" s="49"/>
+      <c r="AW3" s="49"/>
+      <c r="AX3" s="49"/>
+      <c r="AY3" s="49"/>
+      <c r="AZ3" s="49"/>
+      <c r="BA3" s="49"/>
     </row>
     <row r="4" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
@@ -1503,15 +1512,15 @@
       <c r="G4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="53" t="s">
+      <c r="M4" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="N4" s="54"/>
-      <c r="O4" s="54"/>
-      <c r="P4" s="54"/>
-      <c r="Q4" s="54"/>
-      <c r="R4" s="54"/>
-      <c r="S4" s="55"/>
+      <c r="N4" s="43"/>
+      <c r="O4" s="43"/>
+      <c r="P4" s="43"/>
+      <c r="Q4" s="43"/>
+      <c r="R4" s="43"/>
+      <c r="S4" s="44"/>
       <c r="AI4" s="3" t="s">
         <v>2</v>
       </c>
@@ -1772,9 +1781,9 @@
       </c>
       <c r="F8" s="13"/>
       <c r="G8" s="16"/>
-      <c r="I8" s="43"/>
-      <c r="J8" s="43"/>
-      <c r="K8" s="43"/>
+      <c r="I8" s="50"/>
+      <c r="J8" s="50"/>
+      <c r="K8" s="50"/>
       <c r="M8" s="8">
         <v>3</v>
       </c>
@@ -1793,9 +1802,9 @@
       <c r="AM8" s="30"/>
       <c r="AN8" s="31"/>
       <c r="AO8" s="16"/>
-      <c r="AQ8" s="43"/>
-      <c r="AR8" s="43"/>
-      <c r="AS8" s="43"/>
+      <c r="AQ8" s="50"/>
+      <c r="AR8" s="50"/>
+      <c r="AS8" s="50"/>
       <c r="AU8" s="38">
         <v>4</v>
       </c>
@@ -1971,15 +1980,15 @@
       <c r="BA11" s="6"/>
     </row>
     <row r="12" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="42" t="s">
+      <c r="A12" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="42"/>
-      <c r="C12" s="42"/>
-      <c r="D12" s="42"/>
-      <c r="E12" s="42"/>
-      <c r="F12" s="42"/>
-      <c r="G12" s="42"/>
+      <c r="B12" s="49"/>
+      <c r="C12" s="49"/>
+      <c r="D12" s="49"/>
+      <c r="E12" s="49"/>
+      <c r="F12" s="49"/>
+      <c r="G12" s="49"/>
       <c r="L12" s="12"/>
       <c r="M12" s="8" t="s">
         <v>12</v>
@@ -1990,65 +1999,65 @@
       <c r="Q12" s="12"/>
       <c r="R12" s="13"/>
       <c r="S12" s="16"/>
-      <c r="AI12" s="42" t="s">
+      <c r="AI12" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AJ12" s="42"/>
-      <c r="AK12" s="42"/>
-      <c r="AL12" s="42"/>
-      <c r="AM12" s="42"/>
-      <c r="AN12" s="42"/>
-      <c r="AO12" s="42"/>
+      <c r="AJ12" s="49"/>
+      <c r="AK12" s="49"/>
+      <c r="AL12" s="49"/>
+      <c r="AM12" s="49"/>
+      <c r="AN12" s="49"/>
+      <c r="AO12" s="49"/>
       <c r="AQ12" s="12"/>
-      <c r="AU12" s="42" t="s">
+      <c r="AU12" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AV12" s="42"/>
-      <c r="AW12" s="42"/>
-      <c r="AX12" s="42"/>
-      <c r="AY12" s="42"/>
-      <c r="AZ12" s="42"/>
-      <c r="BA12" s="42"/>
+      <c r="AV12" s="49"/>
+      <c r="AW12" s="49"/>
+      <c r="AX12" s="49"/>
+      <c r="AY12" s="49"/>
+      <c r="AZ12" s="49"/>
+      <c r="BA12" s="49"/>
     </row>
     <row r="13" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L13" s="12"/>
-      <c r="M13" s="53" t="s">
+      <c r="M13" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="N13" s="54"/>
-      <c r="O13" s="54"/>
-      <c r="P13" s="54"/>
-      <c r="Q13" s="54"/>
-      <c r="R13" s="54"/>
-      <c r="S13" s="55"/>
+      <c r="N13" s="43"/>
+      <c r="O13" s="43"/>
+      <c r="P13" s="43"/>
+      <c r="Q13" s="43"/>
+      <c r="R13" s="43"/>
+      <c r="S13" s="44"/>
       <c r="AQ13" s="12"/>
     </row>
     <row r="14" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="45" t="s">
+      <c r="A14" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="45"/>
-      <c r="C14" s="45"/>
-      <c r="D14" s="45"/>
-      <c r="E14" s="45"/>
-      <c r="F14" s="45"/>
-      <c r="G14" s="45"/>
-      <c r="L14" s="44"/>
-      <c r="M14" s="43"/>
-      <c r="N14" s="43"/>
-      <c r="AN14" s="43"/>
-      <c r="AO14" s="43"/>
-      <c r="AP14" s="43"/>
+      <c r="B14" s="48"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="48"/>
+      <c r="E14" s="48"/>
+      <c r="F14" s="48"/>
+      <c r="G14" s="48"/>
+      <c r="L14" s="54"/>
+      <c r="M14" s="50"/>
+      <c r="N14" s="50"/>
+      <c r="AN14" s="50"/>
+      <c r="AO14" s="50"/>
+      <c r="AP14" s="50"/>
       <c r="AQ14" s="12"/>
-      <c r="AU14" s="45" t="s">
+      <c r="AU14" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="AV14" s="45"/>
-      <c r="AW14" s="45"/>
-      <c r="AX14" s="45"/>
-      <c r="AY14" s="45"/>
-      <c r="AZ14" s="45"/>
-      <c r="BA14" s="45"/>
+      <c r="AV14" s="48"/>
+      <c r="AW14" s="48"/>
+      <c r="AX14" s="48"/>
+      <c r="AY14" s="48"/>
+      <c r="AZ14" s="48"/>
+      <c r="BA14" s="48"/>
     </row>
     <row r="15" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
@@ -2270,15 +2279,15 @@
       </c>
       <c r="F19" s="31"/>
       <c r="G19" s="32"/>
-      <c r="I19" s="43"/>
-      <c r="J19" s="43"/>
-      <c r="K19" s="43"/>
+      <c r="I19" s="50"/>
+      <c r="J19" s="50"/>
+      <c r="K19" s="50"/>
       <c r="L19" s="12"/>
       <c r="O19" s="12"/>
       <c r="AN19" s="12"/>
-      <c r="AQ19" s="44"/>
-      <c r="AR19" s="43"/>
-      <c r="AS19" s="43"/>
+      <c r="AQ19" s="54"/>
+      <c r="AR19" s="50"/>
+      <c r="AS19" s="50"/>
       <c r="AU19" s="38">
         <v>4</v>
       </c>
@@ -2288,12 +2297,21 @@
       <c r="AW19" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="AX19" s="31"/>
+      <c r="AX19" s="31">
+        <v>2</v>
+      </c>
       <c r="AY19" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="AZ19" s="31"/>
-      <c r="BA19" s="32"/>
+      <c r="AZ19" s="31">
+        <v>3</v>
+      </c>
+      <c r="BA19" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="BB19" s="1" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="20" spans="1:54" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
@@ -2398,52 +2416,52 @@
       <c r="BA22" s="6"/>
     </row>
     <row r="23" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="42" t="s">
+      <c r="A23" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="B23" s="42"/>
-      <c r="C23" s="42"/>
-      <c r="D23" s="42"/>
-      <c r="E23" s="42"/>
-      <c r="F23" s="42"/>
-      <c r="G23" s="42"/>
+      <c r="B23" s="49"/>
+      <c r="C23" s="49"/>
+      <c r="D23" s="49"/>
+      <c r="E23" s="49"/>
+      <c r="F23" s="49"/>
+      <c r="G23" s="49"/>
       <c r="O23" s="12"/>
       <c r="AN23" s="12"/>
-      <c r="AU23" s="42" t="s">
+      <c r="AU23" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AV23" s="42"/>
-      <c r="AW23" s="42"/>
-      <c r="AX23" s="42"/>
-      <c r="AY23" s="42"/>
-      <c r="AZ23" s="42"/>
-      <c r="BA23" s="42"/>
+      <c r="AV23" s="49"/>
+      <c r="AW23" s="49"/>
+      <c r="AX23" s="49"/>
+      <c r="AY23" s="49"/>
+      <c r="AZ23" s="49"/>
+      <c r="BA23" s="49"/>
     </row>
     <row r="24" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="O24" s="12"/>
       <c r="AN24" s="12"/>
     </row>
     <row r="25" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="42" t="s">
+      <c r="A25" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="42"/>
-      <c r="C25" s="42"/>
-      <c r="D25" s="42"/>
-      <c r="E25" s="42"/>
-      <c r="F25" s="42"/>
-      <c r="G25" s="42"/>
+      <c r="B25" s="49"/>
+      <c r="C25" s="49"/>
+      <c r="D25" s="49"/>
+      <c r="E25" s="49"/>
+      <c r="F25" s="49"/>
+      <c r="G25" s="49"/>
       <c r="O25" s="12"/>
       <c r="AN25" s="12"/>
-      <c r="AU25" s="42" t="s">
+      <c r="AU25" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="AV25" s="42"/>
-      <c r="AW25" s="42"/>
-      <c r="AX25" s="42"/>
-      <c r="AY25" s="42"/>
-      <c r="AZ25" s="42"/>
-      <c r="BA25" s="42"/>
+      <c r="AV25" s="49"/>
+      <c r="AW25" s="49"/>
+      <c r="AX25" s="49"/>
+      <c r="AY25" s="49"/>
+      <c r="AZ25" s="49"/>
+      <c r="BA25" s="49"/>
     </row>
     <row r="26" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="20" t="s">
@@ -2467,24 +2485,24 @@
       <c r="G26" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="O26" s="44"/>
-      <c r="P26" s="43"/>
-      <c r="Q26" s="43"/>
-      <c r="R26" s="43"/>
-      <c r="S26" s="43"/>
-      <c r="T26" s="43"/>
-      <c r="U26" s="43"/>
-      <c r="V26" s="43"/>
-      <c r="W26" s="43"/>
-      <c r="AE26" s="43"/>
-      <c r="AF26" s="43"/>
-      <c r="AG26" s="43"/>
-      <c r="AH26" s="43"/>
-      <c r="AI26" s="43"/>
-      <c r="AJ26" s="43"/>
-      <c r="AK26" s="43"/>
-      <c r="AL26" s="43"/>
-      <c r="AM26" s="49"/>
+      <c r="O26" s="54"/>
+      <c r="P26" s="50"/>
+      <c r="Q26" s="50"/>
+      <c r="R26" s="50"/>
+      <c r="S26" s="50"/>
+      <c r="T26" s="50"/>
+      <c r="U26" s="50"/>
+      <c r="V26" s="50"/>
+      <c r="W26" s="50"/>
+      <c r="AE26" s="50"/>
+      <c r="AF26" s="50"/>
+      <c r="AG26" s="50"/>
+      <c r="AH26" s="50"/>
+      <c r="AI26" s="50"/>
+      <c r="AJ26" s="50"/>
+      <c r="AK26" s="50"/>
+      <c r="AL26" s="50"/>
+      <c r="AM26" s="58"/>
       <c r="AU26" s="20" t="s">
         <v>2</v>
       </c>
@@ -2581,26 +2599,26 @@
         <v>54</v>
       </c>
       <c r="O28" s="12"/>
-      <c r="P28" s="53" t="s">
+      <c r="P28" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="Q28" s="54"/>
-      <c r="R28" s="54"/>
-      <c r="S28" s="54"/>
-      <c r="T28" s="54"/>
-      <c r="U28" s="54"/>
-      <c r="V28" s="55"/>
+      <c r="Q28" s="43"/>
+      <c r="R28" s="43"/>
+      <c r="S28" s="43"/>
+      <c r="T28" s="43"/>
+      <c r="U28" s="43"/>
+      <c r="V28" s="44"/>
       <c r="X28" s="12"/>
       <c r="AD28" s="13"/>
-      <c r="AF28" s="42" t="s">
+      <c r="AF28" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="AG28" s="42"/>
-      <c r="AH28" s="42"/>
-      <c r="AI28" s="42"/>
-      <c r="AJ28" s="42"/>
-      <c r="AK28" s="42"/>
-      <c r="AL28" s="42"/>
+      <c r="AG28" s="49"/>
+      <c r="AH28" s="49"/>
+      <c r="AI28" s="49"/>
+      <c r="AJ28" s="49"/>
+      <c r="AK28" s="49"/>
+      <c r="AL28" s="49"/>
       <c r="AN28" s="12"/>
       <c r="AU28" s="8">
         <v>2</v>
@@ -2724,15 +2742,21 @@
       <c r="C30" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="D30" s="31"/>
+      <c r="D30" s="31">
+        <v>4</v>
+      </c>
       <c r="E30" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="F30" s="31"/>
-      <c r="G30" s="32"/>
-      <c r="I30" s="43"/>
-      <c r="J30" s="43"/>
-      <c r="K30" s="43"/>
+      <c r="F30" s="31">
+        <v>2</v>
+      </c>
+      <c r="G30" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="I30" s="50"/>
+      <c r="J30" s="50"/>
+      <c r="K30" s="50"/>
       <c r="O30" s="12"/>
       <c r="P30" s="7">
         <v>1</v>
@@ -2755,9 +2779,9 @@
       <c r="AK30" s="24"/>
       <c r="AL30" s="25"/>
       <c r="AN30" s="12"/>
-      <c r="AQ30" s="43"/>
-      <c r="AR30" s="43"/>
-      <c r="AS30" s="43"/>
+      <c r="AQ30" s="50"/>
+      <c r="AR30" s="50"/>
+      <c r="AS30" s="50"/>
       <c r="AU30" s="38">
         <v>4</v>
       </c>
@@ -2945,15 +2969,15 @@
       <c r="BA33" s="6"/>
     </row>
     <row r="34" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="42" t="s">
+      <c r="A34" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="B34" s="42"/>
-      <c r="C34" s="42"/>
-      <c r="D34" s="42"/>
-      <c r="E34" s="42"/>
-      <c r="F34" s="42"/>
-      <c r="G34" s="42"/>
+      <c r="B34" s="49"/>
+      <c r="C34" s="49"/>
+      <c r="D34" s="49"/>
+      <c r="E34" s="49"/>
+      <c r="F34" s="49"/>
+      <c r="G34" s="49"/>
       <c r="L34" s="12"/>
       <c r="O34" s="12"/>
       <c r="P34" s="8" t="s">
@@ -2978,15 +3002,15 @@
       <c r="AL34" s="16"/>
       <c r="AN34" s="12"/>
       <c r="AQ34" s="12"/>
-      <c r="AU34" s="42" t="s">
+      <c r="AU34" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AV34" s="42"/>
-      <c r="AW34" s="42"/>
-      <c r="AX34" s="42"/>
-      <c r="AY34" s="42"/>
-      <c r="AZ34" s="42"/>
-      <c r="BA34" s="42"/>
+      <c r="AV34" s="49"/>
+      <c r="AW34" s="49"/>
+      <c r="AX34" s="49"/>
+      <c r="AY34" s="49"/>
+      <c r="AZ34" s="49"/>
+      <c r="BA34" s="49"/>
     </row>
     <row r="35" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L35" s="12"/>
@@ -3015,18 +3039,18 @@
       <c r="AQ35" s="12"/>
     </row>
     <row r="36" spans="1:53" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="45" t="s">
+      <c r="A36" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="B36" s="45"/>
-      <c r="C36" s="45"/>
-      <c r="D36" s="45"/>
-      <c r="E36" s="45"/>
-      <c r="F36" s="45"/>
-      <c r="G36" s="45"/>
-      <c r="L36" s="44"/>
-      <c r="M36" s="43"/>
-      <c r="N36" s="43"/>
+      <c r="B36" s="48"/>
+      <c r="C36" s="48"/>
+      <c r="D36" s="48"/>
+      <c r="E36" s="48"/>
+      <c r="F36" s="48"/>
+      <c r="G36" s="48"/>
+      <c r="L36" s="54"/>
+      <c r="M36" s="50"/>
+      <c r="N36" s="50"/>
       <c r="O36" s="12"/>
       <c r="P36" s="8" t="s">
         <v>12</v>
@@ -3048,19 +3072,19 @@
       <c r="AJ36" s="35"/>
       <c r="AK36" s="36"/>
       <c r="AL36" s="37"/>
-      <c r="AN36" s="44"/>
-      <c r="AO36" s="43"/>
-      <c r="AP36" s="43"/>
+      <c r="AN36" s="54"/>
+      <c r="AO36" s="50"/>
+      <c r="AP36" s="50"/>
       <c r="AQ36" s="12"/>
-      <c r="AU36" s="45" t="s">
+      <c r="AU36" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="AV36" s="45"/>
-      <c r="AW36" s="45"/>
-      <c r="AX36" s="45"/>
-      <c r="AY36" s="45"/>
-      <c r="AZ36" s="45"/>
-      <c r="BA36" s="45"/>
+      <c r="AV36" s="48"/>
+      <c r="AW36" s="48"/>
+      <c r="AX36" s="48"/>
+      <c r="AY36" s="48"/>
+      <c r="AZ36" s="48"/>
+      <c r="BA36" s="48"/>
     </row>
     <row r="37" spans="1:53" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37" s="20" t="s">
@@ -3085,31 +3109,31 @@
         <v>9</v>
       </c>
       <c r="L37" s="12"/>
-      <c r="P37" s="56" t="s">
+      <c r="P37" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="Q37" s="57"/>
-      <c r="R37" s="57"/>
-      <c r="S37" s="57"/>
-      <c r="T37" s="57"/>
-      <c r="U37" s="57"/>
-      <c r="V37" s="58"/>
-      <c r="X37" s="44"/>
-      <c r="Y37" s="43"/>
-      <c r="Z37" s="43"/>
-      <c r="AA37" s="43"/>
-      <c r="AB37" s="43"/>
-      <c r="AC37" s="43"/>
-      <c r="AD37" s="49"/>
-      <c r="AF37" s="42" t="s">
+      <c r="Q37" s="46"/>
+      <c r="R37" s="46"/>
+      <c r="S37" s="46"/>
+      <c r="T37" s="46"/>
+      <c r="U37" s="46"/>
+      <c r="V37" s="47"/>
+      <c r="X37" s="54"/>
+      <c r="Y37" s="50"/>
+      <c r="Z37" s="50"/>
+      <c r="AA37" s="50"/>
+      <c r="AB37" s="50"/>
+      <c r="AC37" s="50"/>
+      <c r="AD37" s="58"/>
+      <c r="AF37" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AG37" s="42"/>
-      <c r="AH37" s="42"/>
-      <c r="AI37" s="42"/>
-      <c r="AJ37" s="42"/>
-      <c r="AK37" s="42"/>
-      <c r="AL37" s="42"/>
+      <c r="AG37" s="49"/>
+      <c r="AH37" s="49"/>
+      <c r="AI37" s="49"/>
+      <c r="AJ37" s="49"/>
+      <c r="AK37" s="49"/>
+      <c r="AL37" s="49"/>
       <c r="AQ37" s="12"/>
       <c r="AU37" s="3" t="s">
         <v>2</v>
@@ -3202,33 +3226,33 @@
         <v>53</v>
       </c>
       <c r="L39" s="12"/>
-      <c r="M39" s="53" t="s">
+      <c r="M39" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="N39" s="54"/>
-      <c r="O39" s="54"/>
-      <c r="P39" s="54"/>
-      <c r="Q39" s="54"/>
-      <c r="R39" s="54"/>
-      <c r="S39" s="55"/>
-      <c r="X39" s="42" t="s">
+      <c r="N39" s="43"/>
+      <c r="O39" s="43"/>
+      <c r="P39" s="43"/>
+      <c r="Q39" s="43"/>
+      <c r="R39" s="43"/>
+      <c r="S39" s="44"/>
+      <c r="X39" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="Y39" s="42"/>
-      <c r="Z39" s="42"/>
-      <c r="AA39" s="42"/>
-      <c r="AB39" s="42"/>
-      <c r="AC39" s="42"/>
-      <c r="AD39" s="42"/>
-      <c r="AI39" s="53" t="s">
+      <c r="Y39" s="49"/>
+      <c r="Z39" s="49"/>
+      <c r="AA39" s="49"/>
+      <c r="AB39" s="49"/>
+      <c r="AC39" s="49"/>
+      <c r="AD39" s="49"/>
+      <c r="AI39" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="AJ39" s="54"/>
-      <c r="AK39" s="54"/>
-      <c r="AL39" s="54"/>
-      <c r="AM39" s="54"/>
-      <c r="AN39" s="54"/>
-      <c r="AO39" s="55"/>
+      <c r="AJ39" s="43"/>
+      <c r="AK39" s="43"/>
+      <c r="AL39" s="43"/>
+      <c r="AM39" s="43"/>
+      <c r="AN39" s="43"/>
+      <c r="AO39" s="44"/>
       <c r="AQ39" s="12"/>
       <c r="AU39" s="8">
         <v>2</v>
@@ -3371,15 +3395,21 @@
       <c r="C41" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="D41" s="31"/>
+      <c r="D41" s="31">
+        <v>4</v>
+      </c>
       <c r="E41" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="F41" s="31"/>
-      <c r="G41" s="32"/>
-      <c r="I41" s="43"/>
-      <c r="J41" s="43"/>
-      <c r="K41" s="43"/>
+      <c r="F41" s="31">
+        <v>2</v>
+      </c>
+      <c r="G41" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="I41" s="50"/>
+      <c r="J41" s="50"/>
+      <c r="K41" s="50"/>
       <c r="L41" s="12"/>
       <c r="M41" s="7">
         <v>1</v>
@@ -3408,9 +3438,9 @@
       <c r="AM41" s="23"/>
       <c r="AN41" s="24"/>
       <c r="AO41" s="25"/>
-      <c r="AQ41" s="44"/>
-      <c r="AR41" s="43"/>
-      <c r="AS41" s="43"/>
+      <c r="AQ41" s="54"/>
+      <c r="AR41" s="50"/>
+      <c r="AS41" s="50"/>
       <c r="AU41" s="38">
         <v>4</v>
       </c>
@@ -3605,15 +3635,15 @@
       <c r="BA44" s="6"/>
     </row>
     <row r="45" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="42" t="s">
+      <c r="A45" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="B45" s="42"/>
-      <c r="C45" s="42"/>
-      <c r="D45" s="42"/>
-      <c r="E45" s="42"/>
-      <c r="F45" s="42"/>
-      <c r="G45" s="42"/>
+      <c r="B45" s="49"/>
+      <c r="C45" s="49"/>
+      <c r="D45" s="49"/>
+      <c r="E45" s="49"/>
+      <c r="F45" s="49"/>
+      <c r="G45" s="49"/>
       <c r="M45" s="8" t="s">
         <v>11</v>
       </c>
@@ -3641,15 +3671,15 @@
       <c r="AM45" s="12"/>
       <c r="AN45" s="13"/>
       <c r="AO45" s="16"/>
-      <c r="AU45" s="42" t="s">
+      <c r="AU45" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AV45" s="42"/>
-      <c r="AW45" s="42"/>
-      <c r="AX45" s="42"/>
-      <c r="AY45" s="42"/>
-      <c r="AZ45" s="42"/>
-      <c r="BA45" s="42"/>
+      <c r="AV45" s="49"/>
+      <c r="AW45" s="49"/>
+      <c r="AX45" s="49"/>
+      <c r="AY45" s="49"/>
+      <c r="AZ45" s="49"/>
+      <c r="BA45" s="49"/>
     </row>
     <row r="46" spans="1:53" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="M46" s="8" t="s">
@@ -3710,45 +3740,65 @@
       <c r="AO47" s="6"/>
     </row>
     <row r="48" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="M48" s="53" t="s">
+      <c r="M48" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="N48" s="54"/>
-      <c r="O48" s="54"/>
-      <c r="P48" s="54"/>
-      <c r="Q48" s="54"/>
-      <c r="R48" s="54"/>
-      <c r="S48" s="55"/>
-      <c r="X48" s="42" t="s">
+      <c r="N48" s="43"/>
+      <c r="O48" s="43"/>
+      <c r="P48" s="43"/>
+      <c r="Q48" s="43"/>
+      <c r="R48" s="43"/>
+      <c r="S48" s="44"/>
+      <c r="X48" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="Y48" s="42"/>
-      <c r="Z48" s="42"/>
-      <c r="AA48" s="42"/>
-      <c r="AB48" s="42"/>
-      <c r="AC48" s="42"/>
-      <c r="AD48" s="42"/>
-      <c r="AI48" s="42" t="s">
+      <c r="Y48" s="49"/>
+      <c r="Z48" s="49"/>
+      <c r="AA48" s="49"/>
+      <c r="AB48" s="49"/>
+      <c r="AC48" s="49"/>
+      <c r="AD48" s="49"/>
+      <c r="AI48" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AJ48" s="42"/>
-      <c r="AK48" s="42"/>
-      <c r="AL48" s="42"/>
-      <c r="AM48" s="42"/>
-      <c r="AN48" s="42"/>
-      <c r="AO48" s="42"/>
+      <c r="AJ48" s="49"/>
+      <c r="AK48" s="49"/>
+      <c r="AL48" s="49"/>
+      <c r="AM48" s="49"/>
+      <c r="AN48" s="49"/>
+      <c r="AO48" s="49"/>
     </row>
     <row r="49" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="M48:S48"/>
-    <mergeCell ref="M39:S39"/>
-    <mergeCell ref="P37:V37"/>
-    <mergeCell ref="P28:V28"/>
-    <mergeCell ref="A36:G36"/>
-    <mergeCell ref="A45:G45"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="AU45:BA45"/>
+    <mergeCell ref="AF28:AL28"/>
+    <mergeCell ref="AF37:AL37"/>
+    <mergeCell ref="AQ30:AS30"/>
+    <mergeCell ref="AQ41:AS41"/>
+    <mergeCell ref="AU34:BA34"/>
+    <mergeCell ref="AU36:BA36"/>
+    <mergeCell ref="AU2:BA2"/>
+    <mergeCell ref="AU3:BA3"/>
+    <mergeCell ref="AU12:BA12"/>
+    <mergeCell ref="AU14:BA14"/>
+    <mergeCell ref="AU23:BA23"/>
+    <mergeCell ref="X37:AD37"/>
+    <mergeCell ref="AE26:AM26"/>
+    <mergeCell ref="Z1:AB1"/>
+    <mergeCell ref="X39:AD39"/>
+    <mergeCell ref="X48:AD48"/>
+    <mergeCell ref="AF1:BA1"/>
+    <mergeCell ref="AI2:AO2"/>
+    <mergeCell ref="AI3:AO3"/>
+    <mergeCell ref="AI12:AO12"/>
+    <mergeCell ref="AI39:AO39"/>
+    <mergeCell ref="AU25:BA25"/>
+    <mergeCell ref="AI48:AO48"/>
+    <mergeCell ref="AN14:AP14"/>
+    <mergeCell ref="AN36:AP36"/>
+    <mergeCell ref="AQ8:AS8"/>
+    <mergeCell ref="AQ19:AS19"/>
     <mergeCell ref="A1:U1"/>
     <mergeCell ref="O26:W26"/>
     <mergeCell ref="I41:K41"/>
@@ -3765,34 +3815,14 @@
     <mergeCell ref="I8:K8"/>
     <mergeCell ref="I19:K19"/>
     <mergeCell ref="A25:G25"/>
-    <mergeCell ref="X37:AD37"/>
-    <mergeCell ref="AE26:AM26"/>
-    <mergeCell ref="Z1:AB1"/>
-    <mergeCell ref="X39:AD39"/>
-    <mergeCell ref="X48:AD48"/>
-    <mergeCell ref="AF1:BA1"/>
-    <mergeCell ref="AI2:AO2"/>
-    <mergeCell ref="AI3:AO3"/>
-    <mergeCell ref="AI12:AO12"/>
-    <mergeCell ref="AI39:AO39"/>
-    <mergeCell ref="AU25:BA25"/>
-    <mergeCell ref="AI48:AO48"/>
-    <mergeCell ref="AN14:AP14"/>
-    <mergeCell ref="AN36:AP36"/>
-    <mergeCell ref="AQ8:AS8"/>
-    <mergeCell ref="AQ19:AS19"/>
-    <mergeCell ref="AU2:BA2"/>
-    <mergeCell ref="AU3:BA3"/>
-    <mergeCell ref="AU12:BA12"/>
-    <mergeCell ref="AU14:BA14"/>
-    <mergeCell ref="AU23:BA23"/>
-    <mergeCell ref="AU45:BA45"/>
-    <mergeCell ref="AF28:AL28"/>
-    <mergeCell ref="AF37:AL37"/>
-    <mergeCell ref="AQ30:AS30"/>
-    <mergeCell ref="AQ41:AS41"/>
-    <mergeCell ref="AU34:BA34"/>
-    <mergeCell ref="AU36:BA36"/>
+    <mergeCell ref="M48:S48"/>
+    <mergeCell ref="M39:S39"/>
+    <mergeCell ref="P37:V37"/>
+    <mergeCell ref="P28:V28"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="A34:G34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/2025_2026/Playoffs/Brackets.xlsx
+++ b/2025_2026/Playoffs/Brackets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\NHLStats\2025_2026\Playoffs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0255A120-D0A2-4EB5-B25D-3CF89B000C06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2A07A79-7EBF-4F71-8690-817F570E3505}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="73">
   <si>
     <t>Eastern Conference Playoff Teams</t>
   </si>
@@ -236,6 +236,15 @@
   </si>
   <si>
     <t>Flyers Lead 3-1</t>
+  </si>
+  <si>
+    <t>Sabres Lead 3-1</t>
+  </si>
+  <si>
+    <t>Avalanche Win Series 4-0</t>
+  </si>
+  <si>
+    <t>Ducks Lead 3-1</t>
   </si>
 </sst>
 </file>
@@ -614,6 +623,39 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -632,46 +674,13 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1041,18 +1050,18 @@
     </row>
     <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="11" spans="1:7" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="61" t="s">
+      <c r="A11" s="59" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="61"/>
-      <c r="C11" s="61" t="s">
+      <c r="B11" s="59"/>
+      <c r="C11" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="61"/>
-      <c r="E11" s="61" t="s">
+      <c r="D11" s="59"/>
+      <c r="E11" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="61"/>
+      <c r="F11" s="59"/>
       <c r="G11" s="4" t="s">
         <v>18</v>
       </c>
@@ -1081,18 +1090,18 @@
       </c>
     </row>
     <row r="13" spans="1:7" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="59" t="s">
+      <c r="A13" s="60" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="60"/>
-      <c r="C13" s="59" t="s">
+      <c r="B13" s="61"/>
+      <c r="C13" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="D13" s="60"/>
-      <c r="E13" s="59" t="s">
+      <c r="D13" s="61"/>
+      <c r="E13" s="60" t="s">
         <v>17</v>
       </c>
-      <c r="F13" s="60"/>
+      <c r="F13" s="61"/>
       <c r="G13" s="5"/>
     </row>
     <row r="14" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1119,14 +1128,14 @@
       <c r="F15" s="6"/>
     </row>
     <row r="16" spans="1:7" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="59" t="s">
+      <c r="A16" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="60"/>
-      <c r="C16" s="59" t="s">
+      <c r="B16" s="61"/>
+      <c r="C16" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="60"/>
+      <c r="D16" s="61"/>
     </row>
     <row r="17" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
@@ -1148,10 +1157,10 @@
       <c r="D18" s="6"/>
     </row>
     <row r="19" spans="1:4" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="59" t="s">
+      <c r="A19" s="60" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="60"/>
+      <c r="B19" s="61"/>
     </row>
     <row r="20" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
@@ -1170,10 +1179,10 @@
       </c>
     </row>
     <row r="22" spans="1:4" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="59" t="s">
+      <c r="A22" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="60"/>
+      <c r="B22" s="61"/>
     </row>
     <row r="23" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
@@ -1258,16 +1267,16 @@
     <sortCondition ref="B2:B9"/>
   </sortState>
   <mergeCells count="10">
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C16:D16"/>
     <mergeCell ref="E11:F11"/>
     <mergeCell ref="E13:F13"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C16:D16"/>
   </mergeCells>
   <dataValidations count="16">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C14" xr:uid="{2C3D9587-ABAE-4E3F-8B22-396DF812BF02}">
@@ -1371,124 +1380,124 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:54" ht="27.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
-      <c r="M1" s="52"/>
-      <c r="N1" s="52"/>
-      <c r="O1" s="52"/>
-      <c r="P1" s="52"/>
-      <c r="Q1" s="52"/>
-      <c r="R1" s="52"/>
-      <c r="S1" s="52"/>
-      <c r="T1" s="52"/>
-      <c r="U1" s="53"/>
-      <c r="Z1" s="51" t="s">
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
+      <c r="K1" s="51"/>
+      <c r="L1" s="51"/>
+      <c r="M1" s="51"/>
+      <c r="N1" s="51"/>
+      <c r="O1" s="51"/>
+      <c r="P1" s="51"/>
+      <c r="Q1" s="51"/>
+      <c r="R1" s="51"/>
+      <c r="S1" s="51"/>
+      <c r="T1" s="51"/>
+      <c r="U1" s="52"/>
+      <c r="Z1" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="AA1" s="52"/>
-      <c r="AB1" s="53"/>
-      <c r="AF1" s="51" t="s">
+      <c r="AA1" s="51"/>
+      <c r="AB1" s="52"/>
+      <c r="AF1" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="AG1" s="52"/>
-      <c r="AH1" s="52"/>
-      <c r="AI1" s="52"/>
-      <c r="AJ1" s="52"/>
-      <c r="AK1" s="52"/>
-      <c r="AL1" s="52"/>
-      <c r="AM1" s="52"/>
-      <c r="AN1" s="52"/>
-      <c r="AO1" s="52"/>
-      <c r="AP1" s="52"/>
-      <c r="AQ1" s="52"/>
-      <c r="AR1" s="52"/>
-      <c r="AS1" s="52"/>
-      <c r="AT1" s="52"/>
-      <c r="AU1" s="52"/>
-      <c r="AV1" s="52"/>
-      <c r="AW1" s="52"/>
-      <c r="AX1" s="52"/>
-      <c r="AY1" s="52"/>
-      <c r="AZ1" s="52"/>
-      <c r="BA1" s="53"/>
+      <c r="AG1" s="51"/>
+      <c r="AH1" s="51"/>
+      <c r="AI1" s="51"/>
+      <c r="AJ1" s="51"/>
+      <c r="AK1" s="51"/>
+      <c r="AL1" s="51"/>
+      <c r="AM1" s="51"/>
+      <c r="AN1" s="51"/>
+      <c r="AO1" s="51"/>
+      <c r="AP1" s="51"/>
+      <c r="AQ1" s="51"/>
+      <c r="AR1" s="51"/>
+      <c r="AS1" s="51"/>
+      <c r="AT1" s="51"/>
+      <c r="AU1" s="51"/>
+      <c r="AV1" s="51"/>
+      <c r="AW1" s="51"/>
+      <c r="AX1" s="51"/>
+      <c r="AY1" s="51"/>
+      <c r="AZ1" s="51"/>
+      <c r="BA1" s="52"/>
     </row>
     <row r="2" spans="1:54" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="55" t="s">
+      <c r="A2" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="57"/>
-      <c r="M2" s="55" t="s">
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="48"/>
+      <c r="M2" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="56"/>
-      <c r="O2" s="56"/>
-      <c r="P2" s="56"/>
-      <c r="Q2" s="56"/>
-      <c r="R2" s="57"/>
-      <c r="AI2" s="55" t="s">
+      <c r="N2" s="47"/>
+      <c r="O2" s="47"/>
+      <c r="P2" s="47"/>
+      <c r="Q2" s="47"/>
+      <c r="R2" s="48"/>
+      <c r="AI2" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="AJ2" s="56"/>
-      <c r="AK2" s="56"/>
-      <c r="AL2" s="56"/>
-      <c r="AM2" s="56"/>
-      <c r="AN2" s="56"/>
-      <c r="AO2" s="57"/>
-      <c r="AU2" s="55" t="s">
+      <c r="AJ2" s="47"/>
+      <c r="AK2" s="47"/>
+      <c r="AL2" s="47"/>
+      <c r="AM2" s="47"/>
+      <c r="AN2" s="47"/>
+      <c r="AO2" s="48"/>
+      <c r="AU2" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="AV2" s="56"/>
-      <c r="AW2" s="56"/>
-      <c r="AX2" s="56"/>
-      <c r="AY2" s="56"/>
-      <c r="AZ2" s="56"/>
-      <c r="BA2" s="57"/>
+      <c r="AV2" s="47"/>
+      <c r="AW2" s="47"/>
+      <c r="AX2" s="47"/>
+      <c r="AY2" s="47"/>
+      <c r="AZ2" s="47"/>
+      <c r="BA2" s="48"/>
     </row>
     <row r="3" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="49" t="s">
+      <c r="A3" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="49"/>
-      <c r="C3" s="49"/>
-      <c r="D3" s="49"/>
-      <c r="E3" s="49"/>
-      <c r="F3" s="49"/>
-      <c r="G3" s="49"/>
-      <c r="AI3" s="42" t="s">
+      <c r="B3" s="42"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="42"/>
+      <c r="AI3" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="AJ3" s="43"/>
-      <c r="AK3" s="43"/>
-      <c r="AL3" s="43"/>
-      <c r="AM3" s="43"/>
-      <c r="AN3" s="43"/>
-      <c r="AO3" s="44"/>
-      <c r="AU3" s="49" t="s">
+      <c r="AJ3" s="54"/>
+      <c r="AK3" s="54"/>
+      <c r="AL3" s="54"/>
+      <c r="AM3" s="54"/>
+      <c r="AN3" s="54"/>
+      <c r="AO3" s="55"/>
+      <c r="AU3" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="AV3" s="49"/>
-      <c r="AW3" s="49"/>
-      <c r="AX3" s="49"/>
-      <c r="AY3" s="49"/>
-      <c r="AZ3" s="49"/>
-      <c r="BA3" s="49"/>
+      <c r="AV3" s="42"/>
+      <c r="AW3" s="42"/>
+      <c r="AX3" s="42"/>
+      <c r="AY3" s="42"/>
+      <c r="AZ3" s="42"/>
+      <c r="BA3" s="42"/>
     </row>
     <row r="4" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
@@ -1512,15 +1521,15 @@
       <c r="G4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="42" t="s">
+      <c r="M4" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="N4" s="43"/>
-      <c r="O4" s="43"/>
-      <c r="P4" s="43"/>
-      <c r="Q4" s="43"/>
-      <c r="R4" s="43"/>
-      <c r="S4" s="44"/>
+      <c r="N4" s="54"/>
+      <c r="O4" s="54"/>
+      <c r="P4" s="54"/>
+      <c r="Q4" s="54"/>
+      <c r="R4" s="54"/>
+      <c r="S4" s="55"/>
       <c r="AI4" s="3" t="s">
         <v>2</v>
       </c>
@@ -1769,21 +1778,27 @@
       <c r="A8" s="8">
         <v>4</v>
       </c>
-      <c r="B8" s="27">
+      <c r="B8" s="33">
         <v>46138</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="13"/>
-      <c r="E8" s="12" t="s">
+      <c r="D8" s="31">
+        <v>6</v>
+      </c>
+      <c r="E8" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="F8" s="13"/>
-      <c r="G8" s="16"/>
-      <c r="I8" s="50"/>
-      <c r="J8" s="50"/>
-      <c r="K8" s="50"/>
+      <c r="F8" s="31">
+        <v>1</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="I8" s="43"/>
+      <c r="J8" s="43"/>
+      <c r="K8" s="43"/>
       <c r="M8" s="8">
         <v>3</v>
       </c>
@@ -1802,9 +1817,9 @@
       <c r="AM8" s="30"/>
       <c r="AN8" s="31"/>
       <c r="AO8" s="16"/>
-      <c r="AQ8" s="50"/>
-      <c r="AR8" s="50"/>
-      <c r="AS8" s="50"/>
+      <c r="AQ8" s="43"/>
+      <c r="AR8" s="43"/>
+      <c r="AS8" s="43"/>
       <c r="AU8" s="38">
         <v>4</v>
       </c>
@@ -1814,12 +1829,18 @@
       <c r="AW8" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="AX8" s="31"/>
+      <c r="AX8" s="31">
+        <v>5</v>
+      </c>
       <c r="AY8" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="AZ8" s="31"/>
-      <c r="BA8" s="32"/>
+      <c r="AZ8" s="31">
+        <v>1</v>
+      </c>
+      <c r="BA8" s="32" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="9" spans="1:54" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
@@ -1980,15 +2001,15 @@
       <c r="BA11" s="6"/>
     </row>
     <row r="12" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="49" t="s">
+      <c r="A12" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="49"/>
-      <c r="C12" s="49"/>
-      <c r="D12" s="49"/>
-      <c r="E12" s="49"/>
-      <c r="F12" s="49"/>
-      <c r="G12" s="49"/>
+      <c r="B12" s="42"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="42"/>
       <c r="L12" s="12"/>
       <c r="M12" s="8" t="s">
         <v>12</v>
@@ -1999,65 +2020,65 @@
       <c r="Q12" s="12"/>
       <c r="R12" s="13"/>
       <c r="S12" s="16"/>
-      <c r="AI12" s="49" t="s">
+      <c r="AI12" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AJ12" s="49"/>
-      <c r="AK12" s="49"/>
-      <c r="AL12" s="49"/>
-      <c r="AM12" s="49"/>
-      <c r="AN12" s="49"/>
-      <c r="AO12" s="49"/>
+      <c r="AJ12" s="42"/>
+      <c r="AK12" s="42"/>
+      <c r="AL12" s="42"/>
+      <c r="AM12" s="42"/>
+      <c r="AN12" s="42"/>
+      <c r="AO12" s="42"/>
       <c r="AQ12" s="12"/>
-      <c r="AU12" s="49" t="s">
+      <c r="AU12" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AV12" s="49"/>
-      <c r="AW12" s="49"/>
-      <c r="AX12" s="49"/>
-      <c r="AY12" s="49"/>
-      <c r="AZ12" s="49"/>
-      <c r="BA12" s="49"/>
+      <c r="AV12" s="42"/>
+      <c r="AW12" s="42"/>
+      <c r="AX12" s="42"/>
+      <c r="AY12" s="42"/>
+      <c r="AZ12" s="42"/>
+      <c r="BA12" s="42"/>
     </row>
     <row r="13" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L13" s="12"/>
-      <c r="M13" s="42" t="s">
+      <c r="M13" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="N13" s="43"/>
-      <c r="O13" s="43"/>
-      <c r="P13" s="43"/>
-      <c r="Q13" s="43"/>
-      <c r="R13" s="43"/>
-      <c r="S13" s="44"/>
+      <c r="N13" s="54"/>
+      <c r="O13" s="54"/>
+      <c r="P13" s="54"/>
+      <c r="Q13" s="54"/>
+      <c r="R13" s="54"/>
+      <c r="S13" s="55"/>
       <c r="AQ13" s="12"/>
     </row>
     <row r="14" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="48" t="s">
+      <c r="A14" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="48"/>
-      <c r="C14" s="48"/>
-      <c r="D14" s="48"/>
-      <c r="E14" s="48"/>
-      <c r="F14" s="48"/>
-      <c r="G14" s="48"/>
-      <c r="L14" s="54"/>
-      <c r="M14" s="50"/>
-      <c r="N14" s="50"/>
-      <c r="AN14" s="50"/>
-      <c r="AO14" s="50"/>
-      <c r="AP14" s="50"/>
+      <c r="B14" s="45"/>
+      <c r="C14" s="45"/>
+      <c r="D14" s="45"/>
+      <c r="E14" s="45"/>
+      <c r="F14" s="45"/>
+      <c r="G14" s="45"/>
+      <c r="L14" s="44"/>
+      <c r="M14" s="43"/>
+      <c r="N14" s="43"/>
+      <c r="AN14" s="43"/>
+      <c r="AO14" s="43"/>
+      <c r="AP14" s="43"/>
       <c r="AQ14" s="12"/>
-      <c r="AU14" s="48" t="s">
+      <c r="AU14" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="AV14" s="48"/>
-      <c r="AW14" s="48"/>
-      <c r="AX14" s="48"/>
-      <c r="AY14" s="48"/>
-      <c r="AZ14" s="48"/>
-      <c r="BA14" s="48"/>
+      <c r="AV14" s="45"/>
+      <c r="AW14" s="45"/>
+      <c r="AX14" s="45"/>
+      <c r="AY14" s="45"/>
+      <c r="AZ14" s="45"/>
+      <c r="BA14" s="45"/>
     </row>
     <row r="15" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
@@ -2273,21 +2294,27 @@
       <c r="C19" s="30" t="s">
         <v>36</v>
       </c>
-      <c r="D19" s="31"/>
+      <c r="D19" s="31">
+        <v>3</v>
+      </c>
       <c r="E19" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="F19" s="31"/>
-      <c r="G19" s="32"/>
-      <c r="I19" s="50"/>
-      <c r="J19" s="50"/>
-      <c r="K19" s="50"/>
+      <c r="F19" s="31">
+        <v>2</v>
+      </c>
+      <c r="G19" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="I19" s="43"/>
+      <c r="J19" s="43"/>
+      <c r="K19" s="43"/>
       <c r="L19" s="12"/>
       <c r="O19" s="12"/>
       <c r="AN19" s="12"/>
-      <c r="AQ19" s="54"/>
-      <c r="AR19" s="50"/>
-      <c r="AS19" s="50"/>
+      <c r="AQ19" s="44"/>
+      <c r="AR19" s="43"/>
+      <c r="AS19" s="43"/>
       <c r="AU19" s="38">
         <v>4</v>
       </c>
@@ -2416,52 +2443,52 @@
       <c r="BA22" s="6"/>
     </row>
     <row r="23" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="49" t="s">
+      <c r="A23" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B23" s="49"/>
-      <c r="C23" s="49"/>
-      <c r="D23" s="49"/>
-      <c r="E23" s="49"/>
-      <c r="F23" s="49"/>
-      <c r="G23" s="49"/>
+      <c r="B23" s="42"/>
+      <c r="C23" s="42"/>
+      <c r="D23" s="42"/>
+      <c r="E23" s="42"/>
+      <c r="F23" s="42"/>
+      <c r="G23" s="42"/>
       <c r="O23" s="12"/>
       <c r="AN23" s="12"/>
-      <c r="AU23" s="49" t="s">
+      <c r="AU23" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AV23" s="49"/>
-      <c r="AW23" s="49"/>
-      <c r="AX23" s="49"/>
-      <c r="AY23" s="49"/>
-      <c r="AZ23" s="49"/>
-      <c r="BA23" s="49"/>
+      <c r="AV23" s="42"/>
+      <c r="AW23" s="42"/>
+      <c r="AX23" s="42"/>
+      <c r="AY23" s="42"/>
+      <c r="AZ23" s="42"/>
+      <c r="BA23" s="42"/>
     </row>
     <row r="24" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="O24" s="12"/>
       <c r="AN24" s="12"/>
     </row>
     <row r="25" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="49" t="s">
+      <c r="A25" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="49"/>
-      <c r="C25" s="49"/>
-      <c r="D25" s="49"/>
-      <c r="E25" s="49"/>
-      <c r="F25" s="49"/>
-      <c r="G25" s="49"/>
+      <c r="B25" s="42"/>
+      <c r="C25" s="42"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="42"/>
+      <c r="F25" s="42"/>
+      <c r="G25" s="42"/>
       <c r="O25" s="12"/>
       <c r="AN25" s="12"/>
-      <c r="AU25" s="49" t="s">
+      <c r="AU25" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="AV25" s="49"/>
-      <c r="AW25" s="49"/>
-      <c r="AX25" s="49"/>
-      <c r="AY25" s="49"/>
-      <c r="AZ25" s="49"/>
-      <c r="BA25" s="49"/>
+      <c r="AV25" s="42"/>
+      <c r="AW25" s="42"/>
+      <c r="AX25" s="42"/>
+      <c r="AY25" s="42"/>
+      <c r="AZ25" s="42"/>
+      <c r="BA25" s="42"/>
     </row>
     <row r="26" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="20" t="s">
@@ -2485,24 +2512,24 @@
       <c r="G26" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="O26" s="54"/>
-      <c r="P26" s="50"/>
-      <c r="Q26" s="50"/>
-      <c r="R26" s="50"/>
-      <c r="S26" s="50"/>
-      <c r="T26" s="50"/>
-      <c r="U26" s="50"/>
-      <c r="V26" s="50"/>
-      <c r="W26" s="50"/>
-      <c r="AE26" s="50"/>
-      <c r="AF26" s="50"/>
-      <c r="AG26" s="50"/>
-      <c r="AH26" s="50"/>
-      <c r="AI26" s="50"/>
-      <c r="AJ26" s="50"/>
-      <c r="AK26" s="50"/>
-      <c r="AL26" s="50"/>
-      <c r="AM26" s="58"/>
+      <c r="O26" s="44"/>
+      <c r="P26" s="43"/>
+      <c r="Q26" s="43"/>
+      <c r="R26" s="43"/>
+      <c r="S26" s="43"/>
+      <c r="T26" s="43"/>
+      <c r="U26" s="43"/>
+      <c r="V26" s="43"/>
+      <c r="W26" s="43"/>
+      <c r="AE26" s="43"/>
+      <c r="AF26" s="43"/>
+      <c r="AG26" s="43"/>
+      <c r="AH26" s="43"/>
+      <c r="AI26" s="43"/>
+      <c r="AJ26" s="43"/>
+      <c r="AK26" s="43"/>
+      <c r="AL26" s="43"/>
+      <c r="AM26" s="49"/>
       <c r="AU26" s="20" t="s">
         <v>2</v>
       </c>
@@ -2599,26 +2626,26 @@
         <v>54</v>
       </c>
       <c r="O28" s="12"/>
-      <c r="P28" s="42" t="s">
+      <c r="P28" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="Q28" s="43"/>
-      <c r="R28" s="43"/>
-      <c r="S28" s="43"/>
-      <c r="T28" s="43"/>
-      <c r="U28" s="43"/>
-      <c r="V28" s="44"/>
+      <c r="Q28" s="54"/>
+      <c r="R28" s="54"/>
+      <c r="S28" s="54"/>
+      <c r="T28" s="54"/>
+      <c r="U28" s="54"/>
+      <c r="V28" s="55"/>
       <c r="X28" s="12"/>
       <c r="AD28" s="13"/>
-      <c r="AF28" s="49" t="s">
+      <c r="AF28" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="AG28" s="49"/>
-      <c r="AH28" s="49"/>
-      <c r="AI28" s="49"/>
-      <c r="AJ28" s="49"/>
-      <c r="AK28" s="49"/>
-      <c r="AL28" s="49"/>
+      <c r="AG28" s="42"/>
+      <c r="AH28" s="42"/>
+      <c r="AI28" s="42"/>
+      <c r="AJ28" s="42"/>
+      <c r="AK28" s="42"/>
+      <c r="AL28" s="42"/>
       <c r="AN28" s="12"/>
       <c r="AU28" s="8">
         <v>2</v>
@@ -2754,9 +2781,9 @@
       <c r="G30" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="I30" s="50"/>
-      <c r="J30" s="50"/>
-      <c r="K30" s="50"/>
+      <c r="I30" s="43"/>
+      <c r="J30" s="43"/>
+      <c r="K30" s="43"/>
       <c r="O30" s="12"/>
       <c r="P30" s="7">
         <v>1</v>
@@ -2779,9 +2806,9 @@
       <c r="AK30" s="24"/>
       <c r="AL30" s="25"/>
       <c r="AN30" s="12"/>
-      <c r="AQ30" s="50"/>
-      <c r="AR30" s="50"/>
-      <c r="AS30" s="50"/>
+      <c r="AQ30" s="43"/>
+      <c r="AR30" s="43"/>
+      <c r="AS30" s="43"/>
       <c r="AU30" s="38">
         <v>4</v>
       </c>
@@ -2912,7 +2939,7 @@
       <c r="AZ32" s="13"/>
       <c r="BA32" s="16"/>
     </row>
-    <row r="33" spans="1:53" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:54" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="9" t="s">
         <v>12</v>
       </c>
@@ -2968,16 +2995,16 @@
       <c r="AZ33" s="15"/>
       <c r="BA33" s="6"/>
     </row>
-    <row r="34" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="49" t="s">
+    <row r="34" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B34" s="49"/>
-      <c r="C34" s="49"/>
-      <c r="D34" s="49"/>
-      <c r="E34" s="49"/>
-      <c r="F34" s="49"/>
-      <c r="G34" s="49"/>
+      <c r="B34" s="42"/>
+      <c r="C34" s="42"/>
+      <c r="D34" s="42"/>
+      <c r="E34" s="42"/>
+      <c r="F34" s="42"/>
+      <c r="G34" s="42"/>
       <c r="L34" s="12"/>
       <c r="O34" s="12"/>
       <c r="P34" s="8" t="s">
@@ -3002,17 +3029,17 @@
       <c r="AL34" s="16"/>
       <c r="AN34" s="12"/>
       <c r="AQ34" s="12"/>
-      <c r="AU34" s="49" t="s">
+      <c r="AU34" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AV34" s="49"/>
-      <c r="AW34" s="49"/>
-      <c r="AX34" s="49"/>
-      <c r="AY34" s="49"/>
-      <c r="AZ34" s="49"/>
-      <c r="BA34" s="49"/>
-    </row>
-    <row r="35" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="AV34" s="42"/>
+      <c r="AW34" s="42"/>
+      <c r="AX34" s="42"/>
+      <c r="AY34" s="42"/>
+      <c r="AZ34" s="42"/>
+      <c r="BA34" s="42"/>
+    </row>
+    <row r="35" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L35" s="12"/>
       <c r="O35" s="12"/>
       <c r="P35" s="8" t="s">
@@ -3038,19 +3065,19 @@
       <c r="AN35" s="12"/>
       <c r="AQ35" s="12"/>
     </row>
-    <row r="36" spans="1:53" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="48" t="s">
+    <row r="36" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="B36" s="48"/>
-      <c r="C36" s="48"/>
-      <c r="D36" s="48"/>
-      <c r="E36" s="48"/>
-      <c r="F36" s="48"/>
-      <c r="G36" s="48"/>
-      <c r="L36" s="54"/>
-      <c r="M36" s="50"/>
-      <c r="N36" s="50"/>
+      <c r="B36" s="45"/>
+      <c r="C36" s="45"/>
+      <c r="D36" s="45"/>
+      <c r="E36" s="45"/>
+      <c r="F36" s="45"/>
+      <c r="G36" s="45"/>
+      <c r="L36" s="44"/>
+      <c r="M36" s="43"/>
+      <c r="N36" s="43"/>
       <c r="O36" s="12"/>
       <c r="P36" s="8" t="s">
         <v>12</v>
@@ -3072,21 +3099,21 @@
       <c r="AJ36" s="35"/>
       <c r="AK36" s="36"/>
       <c r="AL36" s="37"/>
-      <c r="AN36" s="54"/>
-      <c r="AO36" s="50"/>
-      <c r="AP36" s="50"/>
+      <c r="AN36" s="44"/>
+      <c r="AO36" s="43"/>
+      <c r="AP36" s="43"/>
       <c r="AQ36" s="12"/>
-      <c r="AU36" s="48" t="s">
+      <c r="AU36" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="AV36" s="48"/>
-      <c r="AW36" s="48"/>
-      <c r="AX36" s="48"/>
-      <c r="AY36" s="48"/>
-      <c r="AZ36" s="48"/>
-      <c r="BA36" s="48"/>
-    </row>
-    <row r="37" spans="1:53" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AV36" s="45"/>
+      <c r="AW36" s="45"/>
+      <c r="AX36" s="45"/>
+      <c r="AY36" s="45"/>
+      <c r="AZ36" s="45"/>
+      <c r="BA36" s="45"/>
+    </row>
+    <row r="37" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37" s="20" t="s">
         <v>2</v>
       </c>
@@ -3109,31 +3136,31 @@
         <v>9</v>
       </c>
       <c r="L37" s="12"/>
-      <c r="P37" s="45" t="s">
+      <c r="P37" s="56" t="s">
         <v>13</v>
       </c>
-      <c r="Q37" s="46"/>
-      <c r="R37" s="46"/>
-      <c r="S37" s="46"/>
-      <c r="T37" s="46"/>
-      <c r="U37" s="46"/>
-      <c r="V37" s="47"/>
-      <c r="X37" s="54"/>
-      <c r="Y37" s="50"/>
-      <c r="Z37" s="50"/>
-      <c r="AA37" s="50"/>
-      <c r="AB37" s="50"/>
-      <c r="AC37" s="50"/>
-      <c r="AD37" s="58"/>
-      <c r="AF37" s="49" t="s">
+      <c r="Q37" s="57"/>
+      <c r="R37" s="57"/>
+      <c r="S37" s="57"/>
+      <c r="T37" s="57"/>
+      <c r="U37" s="57"/>
+      <c r="V37" s="58"/>
+      <c r="X37" s="44"/>
+      <c r="Y37" s="43"/>
+      <c r="Z37" s="43"/>
+      <c r="AA37" s="43"/>
+      <c r="AB37" s="43"/>
+      <c r="AC37" s="43"/>
+      <c r="AD37" s="49"/>
+      <c r="AF37" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AG37" s="49"/>
-      <c r="AH37" s="49"/>
-      <c r="AI37" s="49"/>
-      <c r="AJ37" s="49"/>
-      <c r="AK37" s="49"/>
-      <c r="AL37" s="49"/>
+      <c r="AG37" s="42"/>
+      <c r="AH37" s="42"/>
+      <c r="AI37" s="42"/>
+      <c r="AJ37" s="42"/>
+      <c r="AK37" s="42"/>
+      <c r="AL37" s="42"/>
       <c r="AQ37" s="12"/>
       <c r="AU37" s="3" t="s">
         <v>2</v>
@@ -3157,7 +3184,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="7">
         <v>1</v>
       </c>
@@ -3203,7 +3230,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="39" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="8">
         <v>2</v>
       </c>
@@ -3226,33 +3253,33 @@
         <v>53</v>
       </c>
       <c r="L39" s="12"/>
-      <c r="M39" s="42" t="s">
+      <c r="M39" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="N39" s="43"/>
-      <c r="O39" s="43"/>
-      <c r="P39" s="43"/>
-      <c r="Q39" s="43"/>
-      <c r="R39" s="43"/>
-      <c r="S39" s="44"/>
-      <c r="X39" s="49" t="s">
+      <c r="N39" s="54"/>
+      <c r="O39" s="54"/>
+      <c r="P39" s="54"/>
+      <c r="Q39" s="54"/>
+      <c r="R39" s="54"/>
+      <c r="S39" s="55"/>
+      <c r="X39" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="Y39" s="49"/>
-      <c r="Z39" s="49"/>
-      <c r="AA39" s="49"/>
-      <c r="AB39" s="49"/>
-      <c r="AC39" s="49"/>
-      <c r="AD39" s="49"/>
-      <c r="AI39" s="42" t="s">
+      <c r="Y39" s="42"/>
+      <c r="Z39" s="42"/>
+      <c r="AA39" s="42"/>
+      <c r="AB39" s="42"/>
+      <c r="AC39" s="42"/>
+      <c r="AD39" s="42"/>
+      <c r="AI39" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="AJ39" s="43"/>
-      <c r="AK39" s="43"/>
-      <c r="AL39" s="43"/>
-      <c r="AM39" s="43"/>
-      <c r="AN39" s="43"/>
-      <c r="AO39" s="44"/>
+      <c r="AJ39" s="54"/>
+      <c r="AK39" s="54"/>
+      <c r="AL39" s="54"/>
+      <c r="AM39" s="54"/>
+      <c r="AN39" s="54"/>
+      <c r="AO39" s="55"/>
       <c r="AQ39" s="12"/>
       <c r="AU39" s="8">
         <v>2</v>
@@ -3276,7 +3303,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="40" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="8">
         <v>3</v>
       </c>
@@ -3385,7 +3412,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="41" spans="1:53" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A41" s="8">
         <v>4</v>
       </c>
@@ -3407,9 +3434,9 @@
       <c r="G41" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="I41" s="50"/>
-      <c r="J41" s="50"/>
-      <c r="K41" s="50"/>
+      <c r="I41" s="43"/>
+      <c r="J41" s="43"/>
+      <c r="K41" s="43"/>
       <c r="L41" s="12"/>
       <c r="M41" s="7">
         <v>1</v>
@@ -3438,9 +3465,9 @@
       <c r="AM41" s="23"/>
       <c r="AN41" s="24"/>
       <c r="AO41" s="25"/>
-      <c r="AQ41" s="54"/>
-      <c r="AR41" s="50"/>
-      <c r="AS41" s="50"/>
+      <c r="AQ41" s="44"/>
+      <c r="AR41" s="43"/>
+      <c r="AS41" s="43"/>
       <c r="AU41" s="38">
         <v>4</v>
       </c>
@@ -3450,14 +3477,23 @@
       <c r="AW41" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="AX41" s="31"/>
+      <c r="AX41" s="31">
+        <v>3</v>
+      </c>
       <c r="AY41" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="AZ41" s="31"/>
-      <c r="BA41" s="32"/>
-    </row>
-    <row r="42" spans="1:53" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="AZ41" s="31">
+        <v>4</v>
+      </c>
+      <c r="BA41" s="32" t="s">
+        <v>72</v>
+      </c>
+      <c r="BB41" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="42" spans="1:54" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A42" s="8" t="s">
         <v>11</v>
       </c>
@@ -3516,7 +3552,7 @@
       <c r="AZ42" s="13"/>
       <c r="BA42" s="16"/>
     </row>
-    <row r="43" spans="1:53" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
         <v>10</v>
       </c>
@@ -3575,7 +3611,7 @@
       <c r="AZ43" s="13"/>
       <c r="BA43" s="32"/>
     </row>
-    <row r="44" spans="1:53" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:54" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
         <v>12</v>
       </c>
@@ -3634,16 +3670,16 @@
       <c r="AZ44" s="15"/>
       <c r="BA44" s="6"/>
     </row>
-    <row r="45" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="49" t="s">
+    <row r="45" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B45" s="49"/>
-      <c r="C45" s="49"/>
-      <c r="D45" s="49"/>
-      <c r="E45" s="49"/>
-      <c r="F45" s="49"/>
-      <c r="G45" s="49"/>
+      <c r="B45" s="42"/>
+      <c r="C45" s="42"/>
+      <c r="D45" s="42"/>
+      <c r="E45" s="42"/>
+      <c r="F45" s="42"/>
+      <c r="G45" s="42"/>
       <c r="M45" s="8" t="s">
         <v>11</v>
       </c>
@@ -3671,17 +3707,17 @@
       <c r="AM45" s="12"/>
       <c r="AN45" s="13"/>
       <c r="AO45" s="16"/>
-      <c r="AU45" s="49" t="s">
+      <c r="AU45" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AV45" s="49"/>
-      <c r="AW45" s="49"/>
-      <c r="AX45" s="49"/>
-      <c r="AY45" s="49"/>
-      <c r="AZ45" s="49"/>
-      <c r="BA45" s="49"/>
-    </row>
-    <row r="46" spans="1:53" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="AV45" s="42"/>
+      <c r="AW45" s="42"/>
+      <c r="AX45" s="42"/>
+      <c r="AY45" s="42"/>
+      <c r="AZ45" s="42"/>
+      <c r="BA45" s="42"/>
+    </row>
+    <row r="46" spans="1:54" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="M46" s="8" t="s">
         <v>10</v>
       </c>
@@ -3710,7 +3746,7 @@
       <c r="AN46" s="13"/>
       <c r="AO46" s="16"/>
     </row>
-    <row r="47" spans="1:53" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:54" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="M47" s="8" t="s">
         <v>12</v>
       </c>
@@ -3739,50 +3775,62 @@
       <c r="AN47" s="15"/>
       <c r="AO47" s="6"/>
     </row>
-    <row r="48" spans="1:53" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="M48" s="42" t="s">
+    <row r="48" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M48" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="N48" s="43"/>
-      <c r="O48" s="43"/>
-      <c r="P48" s="43"/>
-      <c r="Q48" s="43"/>
-      <c r="R48" s="43"/>
-      <c r="S48" s="44"/>
-      <c r="X48" s="49" t="s">
+      <c r="N48" s="54"/>
+      <c r="O48" s="54"/>
+      <c r="P48" s="54"/>
+      <c r="Q48" s="54"/>
+      <c r="R48" s="54"/>
+      <c r="S48" s="55"/>
+      <c r="X48" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="Y48" s="49"/>
-      <c r="Z48" s="49"/>
-      <c r="AA48" s="49"/>
-      <c r="AB48" s="49"/>
-      <c r="AC48" s="49"/>
-      <c r="AD48" s="49"/>
-      <c r="AI48" s="49" t="s">
+      <c r="Y48" s="42"/>
+      <c r="Z48" s="42"/>
+      <c r="AA48" s="42"/>
+      <c r="AB48" s="42"/>
+      <c r="AC48" s="42"/>
+      <c r="AD48" s="42"/>
+      <c r="AI48" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AJ48" s="49"/>
-      <c r="AK48" s="49"/>
-      <c r="AL48" s="49"/>
-      <c r="AM48" s="49"/>
-      <c r="AN48" s="49"/>
-      <c r="AO48" s="49"/>
+      <c r="AJ48" s="42"/>
+      <c r="AK48" s="42"/>
+      <c r="AL48" s="42"/>
+      <c r="AM48" s="42"/>
+      <c r="AN48" s="42"/>
+      <c r="AO48" s="42"/>
     </row>
     <row r="49" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="AU45:BA45"/>
-    <mergeCell ref="AF28:AL28"/>
-    <mergeCell ref="AF37:AL37"/>
-    <mergeCell ref="AQ30:AS30"/>
-    <mergeCell ref="AQ41:AS41"/>
-    <mergeCell ref="AU34:BA34"/>
-    <mergeCell ref="AU36:BA36"/>
-    <mergeCell ref="AU2:BA2"/>
-    <mergeCell ref="AU3:BA3"/>
-    <mergeCell ref="AU12:BA12"/>
-    <mergeCell ref="AU14:BA14"/>
-    <mergeCell ref="AU23:BA23"/>
+    <mergeCell ref="M48:S48"/>
+    <mergeCell ref="M39:S39"/>
+    <mergeCell ref="P37:V37"/>
+    <mergeCell ref="P28:V28"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A1:U1"/>
+    <mergeCell ref="O26:W26"/>
+    <mergeCell ref="I41:K41"/>
+    <mergeCell ref="L14:N14"/>
+    <mergeCell ref="L36:N36"/>
+    <mergeCell ref="M2:R2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="M4:S4"/>
+    <mergeCell ref="M13:S13"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="A25:G25"/>
     <mergeCell ref="X37:AD37"/>
     <mergeCell ref="AE26:AM26"/>
     <mergeCell ref="Z1:AB1"/>
@@ -3799,30 +3847,18 @@
     <mergeCell ref="AN36:AP36"/>
     <mergeCell ref="AQ8:AS8"/>
     <mergeCell ref="AQ19:AS19"/>
-    <mergeCell ref="A1:U1"/>
-    <mergeCell ref="O26:W26"/>
-    <mergeCell ref="I41:K41"/>
-    <mergeCell ref="L14:N14"/>
-    <mergeCell ref="L36:N36"/>
-    <mergeCell ref="M2:R2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="M4:S4"/>
-    <mergeCell ref="M13:S13"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A23:G23"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="M48:S48"/>
-    <mergeCell ref="M39:S39"/>
-    <mergeCell ref="P37:V37"/>
-    <mergeCell ref="P28:V28"/>
-    <mergeCell ref="A36:G36"/>
-    <mergeCell ref="A45:G45"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="AU2:BA2"/>
+    <mergeCell ref="AU3:BA3"/>
+    <mergeCell ref="AU12:BA12"/>
+    <mergeCell ref="AU14:BA14"/>
+    <mergeCell ref="AU23:BA23"/>
+    <mergeCell ref="AU45:BA45"/>
+    <mergeCell ref="AF28:AL28"/>
+    <mergeCell ref="AF37:AL37"/>
+    <mergeCell ref="AQ30:AS30"/>
+    <mergeCell ref="AQ41:AS41"/>
+    <mergeCell ref="AU34:BA34"/>
+    <mergeCell ref="AU36:BA36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/2025_2026/Playoffs/Brackets.xlsx
+++ b/2025_2026/Playoffs/Brackets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\NHLStats\2025_2026\Playoffs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2A07A79-7EBF-4F71-8690-817F570E3505}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CEEF378-AFF0-4417-8A97-53C9B677FB71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="85">
   <si>
     <t>Eastern Conference Playoff Teams</t>
   </si>
@@ -245,6 +245,42 @@
   </si>
   <si>
     <t>Ducks Lead 3-1</t>
+  </si>
+  <si>
+    <t>Series Tied 3-3</t>
+  </si>
+  <si>
+    <t>Flyers Lead 3-2</t>
+  </si>
+  <si>
+    <t>Wild Lead 3-2</t>
+  </si>
+  <si>
+    <t>Ducks Lead 3-2</t>
+  </si>
+  <si>
+    <t>Golden Knights Lead 3-2</t>
+  </si>
+  <si>
+    <t>Flyers Win Series 4-2</t>
+  </si>
+  <si>
+    <t>Canadiens Lead 3-2</t>
+  </si>
+  <si>
+    <t>Wild Win Series 4-2</t>
+  </si>
+  <si>
+    <t>Ducks Win Series 4-2</t>
+  </si>
+  <si>
+    <t>Golden Knights Win Series 4-2</t>
+  </si>
+  <si>
+    <t>Sabres Lead 3-2</t>
+  </si>
+  <si>
+    <t>Sabres Win Series 4-2</t>
   </si>
 </sst>
 </file>
@@ -623,18 +659,45 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -647,40 +710,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1050,18 +1086,18 @@
     </row>
     <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="11" spans="1:7" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="59" t="s">
+      <c r="A11" s="61" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="59"/>
-      <c r="C11" s="59" t="s">
+      <c r="B11" s="61"/>
+      <c r="C11" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="59"/>
-      <c r="E11" s="59" t="s">
+      <c r="D11" s="61"/>
+      <c r="E11" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="59"/>
+      <c r="F11" s="61"/>
       <c r="G11" s="4" t="s">
         <v>18</v>
       </c>
@@ -1090,18 +1126,18 @@
       </c>
     </row>
     <row r="13" spans="1:7" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="60" t="s">
+      <c r="A13" s="59" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="61"/>
-      <c r="C13" s="60" t="s">
+      <c r="B13" s="60"/>
+      <c r="C13" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="D13" s="61"/>
-      <c r="E13" s="60" t="s">
+      <c r="D13" s="60"/>
+      <c r="E13" s="59" t="s">
         <v>17</v>
       </c>
-      <c r="F13" s="61"/>
+      <c r="F13" s="60"/>
       <c r="G13" s="5"/>
     </row>
     <row r="14" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1111,7 +1147,12 @@
       <c r="B14" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D14" s="5"/>
+      <c r="C14" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
       <c r="G14" s="6"/>
@@ -1123,19 +1164,21 @@
       <c r="B15" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D15" s="6"/>
+      <c r="D15" s="6" t="s">
+        <v>31</v>
+      </c>
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
     </row>
     <row r="16" spans="1:7" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="60" t="s">
+      <c r="A16" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="61"/>
-      <c r="C16" s="60" t="s">
+      <c r="B16" s="60"/>
+      <c r="C16" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="61"/>
+      <c r="D16" s="60"/>
     </row>
     <row r="17" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
@@ -1144,7 +1187,12 @@
       <c r="B17" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D17" s="5"/>
+      <c r="C17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="18" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
@@ -1153,14 +1201,18 @@
       <c r="B18" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
+      <c r="C18" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="19" spans="1:4" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="60" t="s">
+      <c r="A19" s="59" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="61"/>
+      <c r="B19" s="60"/>
     </row>
     <row r="20" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
@@ -1179,10 +1231,10 @@
       </c>
     </row>
     <row r="22" spans="1:4" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="60" t="s">
+      <c r="A22" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="61"/>
+      <c r="B22" s="60"/>
     </row>
     <row r="23" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
@@ -1267,16 +1319,16 @@
     <sortCondition ref="B2:B9"/>
   </sortState>
   <mergeCells count="10">
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A16:B16"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A16:B16"/>
   </mergeCells>
   <dataValidations count="16">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C14" xr:uid="{2C3D9587-ABAE-4E3F-8B22-396DF812BF02}">
@@ -1375,129 +1427,129 @@
     <col min="50" max="50" width="9.140625" style="1"/>
     <col min="51" max="51" width="23.140625" style="1" customWidth="1"/>
     <col min="52" max="52" width="9.140625" style="1"/>
-    <col min="53" max="53" width="26.140625" style="1" customWidth="1"/>
+    <col min="53" max="53" width="29.28515625" style="1" customWidth="1"/>
     <col min="54" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:54" ht="27.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
-      <c r="I1" s="51"/>
-      <c r="J1" s="51"/>
-      <c r="K1" s="51"/>
-      <c r="L1" s="51"/>
-      <c r="M1" s="51"/>
-      <c r="N1" s="51"/>
-      <c r="O1" s="51"/>
-      <c r="P1" s="51"/>
-      <c r="Q1" s="51"/>
-      <c r="R1" s="51"/>
-      <c r="S1" s="51"/>
-      <c r="T1" s="51"/>
-      <c r="U1" s="52"/>
-      <c r="Z1" s="50" t="s">
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="52"/>
+      <c r="M1" s="52"/>
+      <c r="N1" s="52"/>
+      <c r="O1" s="52"/>
+      <c r="P1" s="52"/>
+      <c r="Q1" s="52"/>
+      <c r="R1" s="52"/>
+      <c r="S1" s="52"/>
+      <c r="T1" s="52"/>
+      <c r="U1" s="53"/>
+      <c r="Z1" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="AA1" s="51"/>
-      <c r="AB1" s="52"/>
-      <c r="AF1" s="50" t="s">
+      <c r="AA1" s="52"/>
+      <c r="AB1" s="53"/>
+      <c r="AF1" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="AG1" s="51"/>
-      <c r="AH1" s="51"/>
-      <c r="AI1" s="51"/>
-      <c r="AJ1" s="51"/>
-      <c r="AK1" s="51"/>
-      <c r="AL1" s="51"/>
-      <c r="AM1" s="51"/>
-      <c r="AN1" s="51"/>
-      <c r="AO1" s="51"/>
-      <c r="AP1" s="51"/>
-      <c r="AQ1" s="51"/>
-      <c r="AR1" s="51"/>
-      <c r="AS1" s="51"/>
-      <c r="AT1" s="51"/>
-      <c r="AU1" s="51"/>
-      <c r="AV1" s="51"/>
-      <c r="AW1" s="51"/>
-      <c r="AX1" s="51"/>
-      <c r="AY1" s="51"/>
-      <c r="AZ1" s="51"/>
-      <c r="BA1" s="52"/>
+      <c r="AG1" s="52"/>
+      <c r="AH1" s="52"/>
+      <c r="AI1" s="52"/>
+      <c r="AJ1" s="52"/>
+      <c r="AK1" s="52"/>
+      <c r="AL1" s="52"/>
+      <c r="AM1" s="52"/>
+      <c r="AN1" s="52"/>
+      <c r="AO1" s="52"/>
+      <c r="AP1" s="52"/>
+      <c r="AQ1" s="52"/>
+      <c r="AR1" s="52"/>
+      <c r="AS1" s="52"/>
+      <c r="AT1" s="52"/>
+      <c r="AU1" s="52"/>
+      <c r="AV1" s="52"/>
+      <c r="AW1" s="52"/>
+      <c r="AX1" s="52"/>
+      <c r="AY1" s="52"/>
+      <c r="AZ1" s="52"/>
+      <c r="BA1" s="53"/>
     </row>
     <row r="2" spans="1:54" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="48"/>
-      <c r="M2" s="46" t="s">
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="57"/>
+      <c r="M2" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="47"/>
-      <c r="O2" s="47"/>
-      <c r="P2" s="47"/>
-      <c r="Q2" s="47"/>
-      <c r="R2" s="48"/>
-      <c r="AI2" s="46" t="s">
+      <c r="N2" s="56"/>
+      <c r="O2" s="56"/>
+      <c r="P2" s="56"/>
+      <c r="Q2" s="56"/>
+      <c r="R2" s="57"/>
+      <c r="AI2" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="AJ2" s="47"/>
-      <c r="AK2" s="47"/>
-      <c r="AL2" s="47"/>
-      <c r="AM2" s="47"/>
-      <c r="AN2" s="47"/>
-      <c r="AO2" s="48"/>
-      <c r="AU2" s="46" t="s">
+      <c r="AJ2" s="56"/>
+      <c r="AK2" s="56"/>
+      <c r="AL2" s="56"/>
+      <c r="AM2" s="56"/>
+      <c r="AN2" s="56"/>
+      <c r="AO2" s="57"/>
+      <c r="AU2" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="AV2" s="47"/>
-      <c r="AW2" s="47"/>
-      <c r="AX2" s="47"/>
-      <c r="AY2" s="47"/>
-      <c r="AZ2" s="47"/>
-      <c r="BA2" s="48"/>
+      <c r="AV2" s="56"/>
+      <c r="AW2" s="56"/>
+      <c r="AX2" s="56"/>
+      <c r="AY2" s="56"/>
+      <c r="AZ2" s="56"/>
+      <c r="BA2" s="57"/>
     </row>
     <row r="3" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="42" t="s">
+      <c r="A3" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="42"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="42"/>
-      <c r="AI3" s="53" t="s">
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="AI3" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="AJ3" s="54"/>
-      <c r="AK3" s="54"/>
-      <c r="AL3" s="54"/>
-      <c r="AM3" s="54"/>
-      <c r="AN3" s="54"/>
-      <c r="AO3" s="55"/>
-      <c r="AU3" s="42" t="s">
+      <c r="AJ3" s="43"/>
+      <c r="AK3" s="43"/>
+      <c r="AL3" s="43"/>
+      <c r="AM3" s="43"/>
+      <c r="AN3" s="43"/>
+      <c r="AO3" s="44"/>
+      <c r="AU3" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="AV3" s="42"/>
-      <c r="AW3" s="42"/>
-      <c r="AX3" s="42"/>
-      <c r="AY3" s="42"/>
-      <c r="AZ3" s="42"/>
-      <c r="BA3" s="42"/>
+      <c r="AV3" s="49"/>
+      <c r="AW3" s="49"/>
+      <c r="AX3" s="49"/>
+      <c r="AY3" s="49"/>
+      <c r="AZ3" s="49"/>
+      <c r="BA3" s="49"/>
     </row>
     <row r="4" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
@@ -1521,15 +1573,15 @@
       <c r="G4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="53" t="s">
+      <c r="M4" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="N4" s="54"/>
-      <c r="O4" s="54"/>
-      <c r="P4" s="54"/>
-      <c r="Q4" s="54"/>
-      <c r="R4" s="54"/>
-      <c r="S4" s="55"/>
+      <c r="N4" s="43"/>
+      <c r="O4" s="43"/>
+      <c r="P4" s="43"/>
+      <c r="Q4" s="43"/>
+      <c r="R4" s="43"/>
+      <c r="S4" s="44"/>
       <c r="AI4" s="3" t="s">
         <v>2</v>
       </c>
@@ -1619,10 +1671,16 @@
       <c r="AI5" s="7">
         <v>1</v>
       </c>
-      <c r="AJ5" s="26"/>
-      <c r="AK5" s="10"/>
+      <c r="AJ5" s="26">
+        <v>46145</v>
+      </c>
+      <c r="AK5" s="10" t="s">
+        <v>31</v>
+      </c>
       <c r="AL5" s="11"/>
-      <c r="AM5" s="10"/>
+      <c r="AM5" s="10" t="s">
+        <v>27</v>
+      </c>
       <c r="AN5" s="11"/>
       <c r="AO5" s="5"/>
       <c r="AU5" s="7">
@@ -1675,16 +1733,22 @@
       <c r="N6" s="29"/>
       <c r="O6" s="10"/>
       <c r="P6" s="11"/>
-      <c r="Q6" s="10"/>
+      <c r="Q6" s="10" t="s">
+        <v>25</v>
+      </c>
       <c r="R6" s="11"/>
       <c r="S6" s="5"/>
       <c r="AI6" s="8">
         <v>2</v>
       </c>
       <c r="AJ6" s="27"/>
-      <c r="AK6" s="12"/>
+      <c r="AK6" s="12" t="s">
+        <v>31</v>
+      </c>
       <c r="AL6" s="13"/>
-      <c r="AM6" s="12"/>
+      <c r="AM6" s="12" t="s">
+        <v>27</v>
+      </c>
       <c r="AN6" s="13"/>
       <c r="AO6" s="16"/>
       <c r="AU6" s="8">
@@ -1740,16 +1804,22 @@
       <c r="N7" s="33"/>
       <c r="O7" s="12"/>
       <c r="P7" s="13"/>
-      <c r="Q7" s="12"/>
+      <c r="Q7" s="12" t="s">
+        <v>25</v>
+      </c>
       <c r="R7" s="13"/>
       <c r="S7" s="16"/>
       <c r="AI7" s="8">
         <v>3</v>
       </c>
       <c r="AJ7" s="27"/>
-      <c r="AK7" s="12"/>
+      <c r="AK7" s="12" t="s">
+        <v>27</v>
+      </c>
       <c r="AL7" s="13"/>
-      <c r="AM7" s="12"/>
+      <c r="AM7" s="12" t="s">
+        <v>31</v>
+      </c>
       <c r="AN7" s="13"/>
       <c r="AO7" s="16"/>
       <c r="AU7" s="8">
@@ -1796,14 +1866,18 @@
       <c r="G8" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="I8" s="43"/>
-      <c r="J8" s="43"/>
-      <c r="K8" s="43"/>
+      <c r="I8" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="J8" s="50"/>
+      <c r="K8" s="50"/>
       <c r="M8" s="8">
         <v>3</v>
       </c>
       <c r="N8" s="33"/>
-      <c r="O8" s="30"/>
+      <c r="O8" s="30" t="s">
+        <v>25</v>
+      </c>
       <c r="P8" s="31"/>
       <c r="Q8" s="30"/>
       <c r="R8" s="31"/>
@@ -1812,14 +1886,20 @@
         <v>4</v>
       </c>
       <c r="AJ8" s="33"/>
-      <c r="AK8" s="30"/>
+      <c r="AK8" s="30" t="s">
+        <v>27</v>
+      </c>
       <c r="AL8" s="31"/>
-      <c r="AM8" s="30"/>
+      <c r="AM8" s="30" t="s">
+        <v>31</v>
+      </c>
       <c r="AN8" s="31"/>
       <c r="AO8" s="16"/>
-      <c r="AQ8" s="43"/>
-      <c r="AR8" s="43"/>
-      <c r="AS8" s="43"/>
+      <c r="AQ8" s="50" t="s">
+        <v>27</v>
+      </c>
+      <c r="AR8" s="50"/>
+      <c r="AS8" s="50"/>
       <c r="AU8" s="38">
         <v>4</v>
       </c>
@@ -1852,18 +1932,29 @@
       <c r="C9" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="13"/>
+      <c r="D9" s="13">
+        <v>2</v>
+      </c>
       <c r="E9" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="F9" s="13"/>
-      <c r="G9" s="16"/>
+      <c r="F9" s="13">
+        <v>1</v>
+      </c>
+      <c r="G9" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="L9" s="12"/>
       <c r="M9" s="8">
         <v>4</v>
       </c>
       <c r="N9" s="33"/>
-      <c r="O9" s="12"/>
+      <c r="O9" s="12" t="s">
+        <v>25</v>
+      </c>
       <c r="P9" s="13"/>
       <c r="Q9" s="12"/>
       <c r="R9" s="13"/>
@@ -1872,9 +1963,13 @@
         <v>11</v>
       </c>
       <c r="AJ9" s="27"/>
-      <c r="AK9" s="12"/>
+      <c r="AK9" s="12" t="s">
+        <v>31</v>
+      </c>
       <c r="AL9" s="13"/>
-      <c r="AM9" s="12"/>
+      <c r="AM9" s="12" t="s">
+        <v>27</v>
+      </c>
       <c r="AN9" s="13"/>
       <c r="AO9" s="16"/>
       <c r="AQ9" s="10"/>
@@ -1906,12 +2001,18 @@
       <c r="C10" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="13"/>
+      <c r="D10" s="13">
+        <v>4</v>
+      </c>
       <c r="E10" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="F10" s="13"/>
-      <c r="G10" s="16"/>
+      <c r="F10" s="13">
+        <v>1</v>
+      </c>
+      <c r="G10" s="16" t="s">
+        <v>84</v>
+      </c>
       <c r="L10" s="12"/>
       <c r="M10" s="8" t="s">
         <v>11</v>
@@ -1919,16 +2020,22 @@
       <c r="N10" s="33"/>
       <c r="O10" s="12"/>
       <c r="P10" s="13"/>
-      <c r="Q10" s="12"/>
+      <c r="Q10" s="12" t="s">
+        <v>25</v>
+      </c>
       <c r="R10" s="13"/>
       <c r="S10" s="16"/>
       <c r="AI10" s="8" t="s">
         <v>10</v>
       </c>
       <c r="AJ10" s="27"/>
-      <c r="AK10" s="12"/>
+      <c r="AK10" s="12" t="s">
+        <v>27</v>
+      </c>
       <c r="AL10" s="13"/>
-      <c r="AM10" s="12"/>
+      <c r="AM10" s="12" t="s">
+        <v>31</v>
+      </c>
       <c r="AN10" s="13"/>
       <c r="AO10" s="16"/>
       <c r="AQ10" s="12"/>
@@ -1978,9 +2085,13 @@
         <v>12</v>
       </c>
       <c r="AJ11" s="28"/>
-      <c r="AK11" s="14"/>
+      <c r="AK11" s="14" t="s">
+        <v>31</v>
+      </c>
       <c r="AL11" s="15"/>
-      <c r="AM11" s="14"/>
+      <c r="AM11" s="14" t="s">
+        <v>27</v>
+      </c>
       <c r="AN11" s="15"/>
       <c r="AO11" s="6"/>
       <c r="AQ11" s="12"/>
@@ -2001,15 +2112,15 @@
       <c r="BA11" s="6"/>
     </row>
     <row r="12" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="42" t="s">
+      <c r="A12" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="42"/>
-      <c r="C12" s="42"/>
-      <c r="D12" s="42"/>
-      <c r="E12" s="42"/>
-      <c r="F12" s="42"/>
-      <c r="G12" s="42"/>
+      <c r="B12" s="49"/>
+      <c r="C12" s="49"/>
+      <c r="D12" s="49"/>
+      <c r="E12" s="49"/>
+      <c r="F12" s="49"/>
+      <c r="G12" s="49"/>
       <c r="L12" s="12"/>
       <c r="M12" s="8" t="s">
         <v>12</v>
@@ -2017,68 +2128,70 @@
       <c r="N12" s="34"/>
       <c r="O12" s="12"/>
       <c r="P12" s="13"/>
-      <c r="Q12" s="12"/>
+      <c r="Q12" s="12" t="s">
+        <v>25</v>
+      </c>
       <c r="R12" s="13"/>
       <c r="S12" s="16"/>
-      <c r="AI12" s="42" t="s">
+      <c r="AI12" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AJ12" s="42"/>
-      <c r="AK12" s="42"/>
-      <c r="AL12" s="42"/>
-      <c r="AM12" s="42"/>
-      <c r="AN12" s="42"/>
-      <c r="AO12" s="42"/>
+      <c r="AJ12" s="49"/>
+      <c r="AK12" s="49"/>
+      <c r="AL12" s="49"/>
+      <c r="AM12" s="49"/>
+      <c r="AN12" s="49"/>
+      <c r="AO12" s="49"/>
       <c r="AQ12" s="12"/>
-      <c r="AU12" s="42" t="s">
+      <c r="AU12" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AV12" s="42"/>
-      <c r="AW12" s="42"/>
-      <c r="AX12" s="42"/>
-      <c r="AY12" s="42"/>
-      <c r="AZ12" s="42"/>
-      <c r="BA12" s="42"/>
+      <c r="AV12" s="49"/>
+      <c r="AW12" s="49"/>
+      <c r="AX12" s="49"/>
+      <c r="AY12" s="49"/>
+      <c r="AZ12" s="49"/>
+      <c r="BA12" s="49"/>
     </row>
     <row r="13" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L13" s="12"/>
-      <c r="M13" s="53" t="s">
+      <c r="M13" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="N13" s="54"/>
-      <c r="O13" s="54"/>
-      <c r="P13" s="54"/>
-      <c r="Q13" s="54"/>
-      <c r="R13" s="54"/>
-      <c r="S13" s="55"/>
+      <c r="N13" s="43"/>
+      <c r="O13" s="43"/>
+      <c r="P13" s="43"/>
+      <c r="Q13" s="43"/>
+      <c r="R13" s="43"/>
+      <c r="S13" s="44"/>
       <c r="AQ13" s="12"/>
     </row>
     <row r="14" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="45" t="s">
+      <c r="A14" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="45"/>
-      <c r="C14" s="45"/>
-      <c r="D14" s="45"/>
-      <c r="E14" s="45"/>
-      <c r="F14" s="45"/>
-      <c r="G14" s="45"/>
-      <c r="L14" s="44"/>
-      <c r="M14" s="43"/>
-      <c r="N14" s="43"/>
-      <c r="AN14" s="43"/>
-      <c r="AO14" s="43"/>
-      <c r="AP14" s="43"/>
+      <c r="B14" s="48"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="48"/>
+      <c r="E14" s="48"/>
+      <c r="F14" s="48"/>
+      <c r="G14" s="48"/>
+      <c r="L14" s="54"/>
+      <c r="M14" s="50"/>
+      <c r="N14" s="50"/>
+      <c r="AN14" s="50"/>
+      <c r="AO14" s="50"/>
+      <c r="AP14" s="50"/>
       <c r="AQ14" s="12"/>
-      <c r="AU14" s="45" t="s">
+      <c r="AU14" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="AV14" s="45"/>
-      <c r="AW14" s="45"/>
-      <c r="AX14" s="45"/>
-      <c r="AY14" s="45"/>
-      <c r="AZ14" s="45"/>
-      <c r="BA14" s="45"/>
+      <c r="AV14" s="48"/>
+      <c r="AW14" s="48"/>
+      <c r="AX14" s="48"/>
+      <c r="AY14" s="48"/>
+      <c r="AZ14" s="48"/>
+      <c r="BA14" s="48"/>
     </row>
     <row r="15" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
@@ -2306,15 +2419,17 @@
       <c r="G19" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="I19" s="43"/>
-      <c r="J19" s="43"/>
-      <c r="K19" s="43"/>
+      <c r="I19" s="50"/>
+      <c r="J19" s="50"/>
+      <c r="K19" s="50"/>
       <c r="L19" s="12"/>
       <c r="O19" s="12"/>
       <c r="AN19" s="12"/>
-      <c r="AQ19" s="44"/>
-      <c r="AR19" s="43"/>
-      <c r="AS19" s="43"/>
+      <c r="AQ19" s="54" t="s">
+        <v>31</v>
+      </c>
+      <c r="AR19" s="50"/>
+      <c r="AS19" s="50"/>
       <c r="AU19" s="38">
         <v>4</v>
       </c>
@@ -2350,12 +2465,18 @@
       <c r="C20" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="D20" s="13"/>
+      <c r="D20" s="13">
+        <v>3</v>
+      </c>
       <c r="E20" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="F20" s="13"/>
-      <c r="G20" s="16"/>
+      <c r="F20" s="13">
+        <v>2</v>
+      </c>
+      <c r="G20" s="16" t="s">
+        <v>79</v>
+      </c>
       <c r="O20" s="12"/>
       <c r="AN20" s="12"/>
       <c r="AU20" s="8" t="s">
@@ -2367,12 +2488,18 @@
       <c r="AW20" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="AX20" s="13"/>
+      <c r="AX20" s="13">
+        <v>4</v>
+      </c>
       <c r="AY20" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="AZ20" s="13"/>
-      <c r="BA20" s="16"/>
+      <c r="AZ20" s="13">
+        <v>2</v>
+      </c>
+      <c r="BA20" s="16" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="21" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
@@ -2384,12 +2511,21 @@
       <c r="C21" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="D21" s="13"/>
+      <c r="D21" s="13">
+        <v>1</v>
+      </c>
       <c r="E21" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="F21" s="13"/>
-      <c r="G21" s="16"/>
+      <c r="F21" s="13">
+        <v>0</v>
+      </c>
+      <c r="G21" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="O21" s="12"/>
       <c r="AN21" s="12"/>
       <c r="AU21" s="8" t="s">
@@ -2401,12 +2537,18 @@
       <c r="AW21" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="AX21" s="13"/>
+      <c r="AX21" s="13">
+        <v>2</v>
+      </c>
       <c r="AY21" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="AZ21" s="13"/>
-      <c r="BA21" s="16"/>
+      <c r="AZ21" s="13">
+        <v>5</v>
+      </c>
+      <c r="BA21" s="16" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="22" spans="1:54" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
@@ -2443,52 +2585,52 @@
       <c r="BA22" s="6"/>
     </row>
     <row r="23" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="42" t="s">
+      <c r="A23" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="B23" s="42"/>
-      <c r="C23" s="42"/>
-      <c r="D23" s="42"/>
-      <c r="E23" s="42"/>
-      <c r="F23" s="42"/>
-      <c r="G23" s="42"/>
+      <c r="B23" s="49"/>
+      <c r="C23" s="49"/>
+      <c r="D23" s="49"/>
+      <c r="E23" s="49"/>
+      <c r="F23" s="49"/>
+      <c r="G23" s="49"/>
       <c r="O23" s="12"/>
       <c r="AN23" s="12"/>
-      <c r="AU23" s="42" t="s">
+      <c r="AU23" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AV23" s="42"/>
-      <c r="AW23" s="42"/>
-      <c r="AX23" s="42"/>
-      <c r="AY23" s="42"/>
-      <c r="AZ23" s="42"/>
-      <c r="BA23" s="42"/>
+      <c r="AV23" s="49"/>
+      <c r="AW23" s="49"/>
+      <c r="AX23" s="49"/>
+      <c r="AY23" s="49"/>
+      <c r="AZ23" s="49"/>
+      <c r="BA23" s="49"/>
     </row>
     <row r="24" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="O24" s="12"/>
       <c r="AN24" s="12"/>
     </row>
     <row r="25" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="42" t="s">
+      <c r="A25" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="42"/>
-      <c r="C25" s="42"/>
-      <c r="D25" s="42"/>
-      <c r="E25" s="42"/>
-      <c r="F25" s="42"/>
-      <c r="G25" s="42"/>
+      <c r="B25" s="49"/>
+      <c r="C25" s="49"/>
+      <c r="D25" s="49"/>
+      <c r="E25" s="49"/>
+      <c r="F25" s="49"/>
+      <c r="G25" s="49"/>
       <c r="O25" s="12"/>
       <c r="AN25" s="12"/>
-      <c r="AU25" s="42" t="s">
+      <c r="AU25" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="AV25" s="42"/>
-      <c r="AW25" s="42"/>
-      <c r="AX25" s="42"/>
-      <c r="AY25" s="42"/>
-      <c r="AZ25" s="42"/>
-      <c r="BA25" s="42"/>
+      <c r="AV25" s="49"/>
+      <c r="AW25" s="49"/>
+      <c r="AX25" s="49"/>
+      <c r="AY25" s="49"/>
+      <c r="AZ25" s="49"/>
+      <c r="BA25" s="49"/>
     </row>
     <row r="26" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="20" t="s">
@@ -2512,24 +2654,24 @@
       <c r="G26" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="O26" s="44"/>
-      <c r="P26" s="43"/>
-      <c r="Q26" s="43"/>
-      <c r="R26" s="43"/>
-      <c r="S26" s="43"/>
-      <c r="T26" s="43"/>
-      <c r="U26" s="43"/>
-      <c r="V26" s="43"/>
-      <c r="W26" s="43"/>
-      <c r="AE26" s="43"/>
-      <c r="AF26" s="43"/>
-      <c r="AG26" s="43"/>
-      <c r="AH26" s="43"/>
-      <c r="AI26" s="43"/>
-      <c r="AJ26" s="43"/>
-      <c r="AK26" s="43"/>
-      <c r="AL26" s="43"/>
-      <c r="AM26" s="49"/>
+      <c r="O26" s="54"/>
+      <c r="P26" s="50"/>
+      <c r="Q26" s="50"/>
+      <c r="R26" s="50"/>
+      <c r="S26" s="50"/>
+      <c r="T26" s="50"/>
+      <c r="U26" s="50"/>
+      <c r="V26" s="50"/>
+      <c r="W26" s="50"/>
+      <c r="AE26" s="50"/>
+      <c r="AF26" s="50"/>
+      <c r="AG26" s="50"/>
+      <c r="AH26" s="50"/>
+      <c r="AI26" s="50"/>
+      <c r="AJ26" s="50"/>
+      <c r="AK26" s="50"/>
+      <c r="AL26" s="50"/>
+      <c r="AM26" s="58"/>
       <c r="AU26" s="20" t="s">
         <v>2</v>
       </c>
@@ -2626,26 +2768,26 @@
         <v>54</v>
       </c>
       <c r="O28" s="12"/>
-      <c r="P28" s="53" t="s">
+      <c r="P28" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="Q28" s="54"/>
-      <c r="R28" s="54"/>
-      <c r="S28" s="54"/>
-      <c r="T28" s="54"/>
-      <c r="U28" s="54"/>
-      <c r="V28" s="55"/>
+      <c r="Q28" s="43"/>
+      <c r="R28" s="43"/>
+      <c r="S28" s="43"/>
+      <c r="T28" s="43"/>
+      <c r="U28" s="43"/>
+      <c r="V28" s="44"/>
       <c r="X28" s="12"/>
       <c r="AD28" s="13"/>
-      <c r="AF28" s="42" t="s">
+      <c r="AF28" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="AG28" s="42"/>
-      <c r="AH28" s="42"/>
-      <c r="AI28" s="42"/>
-      <c r="AJ28" s="42"/>
-      <c r="AK28" s="42"/>
-      <c r="AL28" s="42"/>
+      <c r="AG28" s="49"/>
+      <c r="AH28" s="49"/>
+      <c r="AI28" s="49"/>
+      <c r="AJ28" s="49"/>
+      <c r="AK28" s="49"/>
+      <c r="AL28" s="49"/>
       <c r="AN28" s="12"/>
       <c r="AU28" s="8">
         <v>2</v>
@@ -2781,9 +2923,11 @@
       <c r="G30" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="I30" s="43"/>
-      <c r="J30" s="43"/>
-      <c r="K30" s="43"/>
+      <c r="I30" s="50" t="s">
+        <v>26</v>
+      </c>
+      <c r="J30" s="50"/>
+      <c r="K30" s="50"/>
       <c r="O30" s="12"/>
       <c r="P30" s="7">
         <v>1</v>
@@ -2806,9 +2950,11 @@
       <c r="AK30" s="24"/>
       <c r="AL30" s="25"/>
       <c r="AN30" s="12"/>
-      <c r="AQ30" s="43"/>
-      <c r="AR30" s="43"/>
-      <c r="AS30" s="43"/>
+      <c r="AQ30" s="50" t="s">
+        <v>38</v>
+      </c>
+      <c r="AR30" s="50"/>
+      <c r="AS30" s="50"/>
       <c r="AU30" s="38">
         <v>4</v>
       </c>
@@ -2818,12 +2964,21 @@
       <c r="AW30" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="AX30" s="31"/>
+      <c r="AX30" s="31">
+        <v>5</v>
+      </c>
       <c r="AY30" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="AZ30" s="31"/>
-      <c r="BA30" s="32"/>
+      <c r="AZ30" s="31">
+        <v>4</v>
+      </c>
+      <c r="BA30" s="32" t="s">
+        <v>68</v>
+      </c>
+      <c r="BB30" s="1" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="31" spans="1:54" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
@@ -2876,12 +3031,21 @@
       <c r="AW31" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="AX31" s="13"/>
+      <c r="AX31" s="13">
+        <v>4</v>
+      </c>
       <c r="AY31" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="AZ31" s="13"/>
-      <c r="BA31" s="16"/>
+      <c r="AZ31" s="13">
+        <v>5</v>
+      </c>
+      <c r="BA31" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="BB31" s="1" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="32" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A32" s="8" t="s">
@@ -2932,12 +3096,18 @@
       <c r="AW32" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="AX32" s="13"/>
+      <c r="AX32" s="13">
+        <v>5</v>
+      </c>
       <c r="AY32" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="AZ32" s="13"/>
-      <c r="BA32" s="16"/>
+      <c r="AZ32" s="13">
+        <v>1</v>
+      </c>
+      <c r="BA32" s="16" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="33" spans="1:54" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="9" t="s">
@@ -2996,15 +3166,15 @@
       <c r="BA33" s="6"/>
     </row>
     <row r="34" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="42" t="s">
+      <c r="A34" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="B34" s="42"/>
-      <c r="C34" s="42"/>
-      <c r="D34" s="42"/>
-      <c r="E34" s="42"/>
-      <c r="F34" s="42"/>
-      <c r="G34" s="42"/>
+      <c r="B34" s="49"/>
+      <c r="C34" s="49"/>
+      <c r="D34" s="49"/>
+      <c r="E34" s="49"/>
+      <c r="F34" s="49"/>
+      <c r="G34" s="49"/>
       <c r="L34" s="12"/>
       <c r="O34" s="12"/>
       <c r="P34" s="8" t="s">
@@ -3029,15 +3199,15 @@
       <c r="AL34" s="16"/>
       <c r="AN34" s="12"/>
       <c r="AQ34" s="12"/>
-      <c r="AU34" s="42" t="s">
+      <c r="AU34" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AV34" s="42"/>
-      <c r="AW34" s="42"/>
-      <c r="AX34" s="42"/>
-      <c r="AY34" s="42"/>
-      <c r="AZ34" s="42"/>
-      <c r="BA34" s="42"/>
+      <c r="AV34" s="49"/>
+      <c r="AW34" s="49"/>
+      <c r="AX34" s="49"/>
+      <c r="AY34" s="49"/>
+      <c r="AZ34" s="49"/>
+      <c r="BA34" s="49"/>
     </row>
     <row r="35" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L35" s="12"/>
@@ -3066,18 +3236,18 @@
       <c r="AQ35" s="12"/>
     </row>
     <row r="36" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="45" t="s">
+      <c r="A36" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="B36" s="45"/>
-      <c r="C36" s="45"/>
-      <c r="D36" s="45"/>
-      <c r="E36" s="45"/>
-      <c r="F36" s="45"/>
-      <c r="G36" s="45"/>
-      <c r="L36" s="44"/>
-      <c r="M36" s="43"/>
-      <c r="N36" s="43"/>
+      <c r="B36" s="48"/>
+      <c r="C36" s="48"/>
+      <c r="D36" s="48"/>
+      <c r="E36" s="48"/>
+      <c r="F36" s="48"/>
+      <c r="G36" s="48"/>
+      <c r="L36" s="54"/>
+      <c r="M36" s="50"/>
+      <c r="N36" s="50"/>
       <c r="O36" s="12"/>
       <c r="P36" s="8" t="s">
         <v>12</v>
@@ -3099,19 +3269,19 @@
       <c r="AJ36" s="35"/>
       <c r="AK36" s="36"/>
       <c r="AL36" s="37"/>
-      <c r="AN36" s="44"/>
-      <c r="AO36" s="43"/>
-      <c r="AP36" s="43"/>
+      <c r="AN36" s="54"/>
+      <c r="AO36" s="50"/>
+      <c r="AP36" s="50"/>
       <c r="AQ36" s="12"/>
-      <c r="AU36" s="45" t="s">
+      <c r="AU36" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="AV36" s="45"/>
-      <c r="AW36" s="45"/>
-      <c r="AX36" s="45"/>
-      <c r="AY36" s="45"/>
-      <c r="AZ36" s="45"/>
-      <c r="BA36" s="45"/>
+      <c r="AV36" s="48"/>
+      <c r="AW36" s="48"/>
+      <c r="AX36" s="48"/>
+      <c r="AY36" s="48"/>
+      <c r="AZ36" s="48"/>
+      <c r="BA36" s="48"/>
     </row>
     <row r="37" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37" s="20" t="s">
@@ -3136,31 +3306,31 @@
         <v>9</v>
       </c>
       <c r="L37" s="12"/>
-      <c r="P37" s="56" t="s">
+      <c r="P37" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="Q37" s="57"/>
-      <c r="R37" s="57"/>
-      <c r="S37" s="57"/>
-      <c r="T37" s="57"/>
-      <c r="U37" s="57"/>
-      <c r="V37" s="58"/>
-      <c r="X37" s="44"/>
-      <c r="Y37" s="43"/>
-      <c r="Z37" s="43"/>
-      <c r="AA37" s="43"/>
-      <c r="AB37" s="43"/>
-      <c r="AC37" s="43"/>
-      <c r="AD37" s="49"/>
-      <c r="AF37" s="42" t="s">
+      <c r="Q37" s="46"/>
+      <c r="R37" s="46"/>
+      <c r="S37" s="46"/>
+      <c r="T37" s="46"/>
+      <c r="U37" s="46"/>
+      <c r="V37" s="47"/>
+      <c r="X37" s="54"/>
+      <c r="Y37" s="50"/>
+      <c r="Z37" s="50"/>
+      <c r="AA37" s="50"/>
+      <c r="AB37" s="50"/>
+      <c r="AC37" s="50"/>
+      <c r="AD37" s="58"/>
+      <c r="AF37" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AG37" s="42"/>
-      <c r="AH37" s="42"/>
-      <c r="AI37" s="42"/>
-      <c r="AJ37" s="42"/>
-      <c r="AK37" s="42"/>
-      <c r="AL37" s="42"/>
+      <c r="AG37" s="49"/>
+      <c r="AH37" s="49"/>
+      <c r="AI37" s="49"/>
+      <c r="AJ37" s="49"/>
+      <c r="AK37" s="49"/>
+      <c r="AL37" s="49"/>
       <c r="AQ37" s="12"/>
       <c r="AU37" s="3" t="s">
         <v>2</v>
@@ -3253,33 +3423,33 @@
         <v>53</v>
       </c>
       <c r="L39" s="12"/>
-      <c r="M39" s="53" t="s">
+      <c r="M39" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="N39" s="54"/>
-      <c r="O39" s="54"/>
-      <c r="P39" s="54"/>
-      <c r="Q39" s="54"/>
-      <c r="R39" s="54"/>
-      <c r="S39" s="55"/>
-      <c r="X39" s="42" t="s">
+      <c r="N39" s="43"/>
+      <c r="O39" s="43"/>
+      <c r="P39" s="43"/>
+      <c r="Q39" s="43"/>
+      <c r="R39" s="43"/>
+      <c r="S39" s="44"/>
+      <c r="X39" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="Y39" s="42"/>
-      <c r="Z39" s="42"/>
-      <c r="AA39" s="42"/>
-      <c r="AB39" s="42"/>
-      <c r="AC39" s="42"/>
-      <c r="AD39" s="42"/>
-      <c r="AI39" s="53" t="s">
+      <c r="Y39" s="49"/>
+      <c r="Z39" s="49"/>
+      <c r="AA39" s="49"/>
+      <c r="AB39" s="49"/>
+      <c r="AC39" s="49"/>
+      <c r="AD39" s="49"/>
+      <c r="AI39" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="AJ39" s="54"/>
-      <c r="AK39" s="54"/>
-      <c r="AL39" s="54"/>
-      <c r="AM39" s="54"/>
-      <c r="AN39" s="54"/>
-      <c r="AO39" s="55"/>
+      <c r="AJ39" s="43"/>
+      <c r="AK39" s="43"/>
+      <c r="AL39" s="43"/>
+      <c r="AM39" s="43"/>
+      <c r="AN39" s="43"/>
+      <c r="AO39" s="44"/>
       <c r="AQ39" s="12"/>
       <c r="AU39" s="8">
         <v>2</v>
@@ -3434,17 +3604,25 @@
       <c r="G41" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="I41" s="43"/>
-      <c r="J41" s="43"/>
-      <c r="K41" s="43"/>
+      <c r="I41" s="50" t="s">
+        <v>34</v>
+      </c>
+      <c r="J41" s="50"/>
+      <c r="K41" s="50"/>
       <c r="L41" s="12"/>
       <c r="M41" s="7">
         <v>1</v>
       </c>
-      <c r="N41" s="29"/>
-      <c r="O41" s="23"/>
+      <c r="N41" s="29">
+        <v>46144</v>
+      </c>
+      <c r="O41" s="23" t="s">
+        <v>34</v>
+      </c>
       <c r="P41" s="24"/>
-      <c r="Q41" s="23"/>
+      <c r="Q41" s="23" t="s">
+        <v>26</v>
+      </c>
       <c r="R41" s="24"/>
       <c r="S41" s="25"/>
       <c r="X41" s="7">
@@ -3460,14 +3638,20 @@
         <v>1</v>
       </c>
       <c r="AJ41" s="29"/>
-      <c r="AK41" s="23"/>
+      <c r="AK41" s="23" t="s">
+        <v>23</v>
+      </c>
       <c r="AL41" s="24"/>
-      <c r="AM41" s="23"/>
+      <c r="AM41" s="23" t="s">
+        <v>38</v>
+      </c>
       <c r="AN41" s="24"/>
       <c r="AO41" s="25"/>
-      <c r="AQ41" s="44"/>
-      <c r="AR41" s="43"/>
-      <c r="AS41" s="43"/>
+      <c r="AQ41" s="54" t="s">
+        <v>23</v>
+      </c>
+      <c r="AR41" s="50"/>
+      <c r="AS41" s="50"/>
       <c r="AU41" s="38">
         <v>4</v>
       </c>
@@ -3503,19 +3687,29 @@
       <c r="C42" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D42" s="13"/>
+      <c r="D42" s="13">
+        <v>2</v>
+      </c>
       <c r="E42" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="F42" s="13"/>
-      <c r="G42" s="16"/>
+      <c r="F42" s="13">
+        <v>3</v>
+      </c>
+      <c r="G42" s="16" t="s">
+        <v>74</v>
+      </c>
       <c r="M42" s="8">
         <v>2</v>
       </c>
       <c r="N42" s="33"/>
-      <c r="O42" s="12"/>
+      <c r="O42" s="12" t="s">
+        <v>34</v>
+      </c>
       <c r="P42" s="13"/>
-      <c r="Q42" s="12"/>
+      <c r="Q42" s="12" t="s">
+        <v>26</v>
+      </c>
       <c r="R42" s="13"/>
       <c r="S42" s="16"/>
       <c r="X42" s="8">
@@ -3531,9 +3725,13 @@
         <v>2</v>
       </c>
       <c r="AJ42" s="27"/>
-      <c r="AK42" s="12"/>
+      <c r="AK42" s="12" t="s">
+        <v>23</v>
+      </c>
       <c r="AL42" s="13"/>
-      <c r="AM42" s="12"/>
+      <c r="AM42" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="AN42" s="13"/>
       <c r="AO42" s="16"/>
       <c r="AU42" s="8" t="s">
@@ -3545,12 +3743,18 @@
       <c r="AW42" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="AX42" s="13"/>
+      <c r="AX42" s="13">
+        <v>1</v>
+      </c>
       <c r="AY42" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="AZ42" s="13"/>
-      <c r="BA42" s="16"/>
+      <c r="AZ42" s="13">
+        <v>4</v>
+      </c>
+      <c r="BA42" s="32" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="43" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
@@ -3562,19 +3766,32 @@
       <c r="C43" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="D43" s="13"/>
+      <c r="D43" s="13">
+        <v>0</v>
+      </c>
       <c r="E43" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="F43" s="13"/>
-      <c r="G43" s="16"/>
+      <c r="F43" s="13">
+        <v>1</v>
+      </c>
+      <c r="G43" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="M43" s="8">
         <v>3</v>
       </c>
       <c r="N43" s="33"/>
-      <c r="O43" s="12"/>
+      <c r="O43" s="12" t="s">
+        <v>26</v>
+      </c>
       <c r="P43" s="13"/>
-      <c r="Q43" s="12"/>
+      <c r="Q43" s="12" t="s">
+        <v>34</v>
+      </c>
       <c r="R43" s="13"/>
       <c r="S43" s="16"/>
       <c r="X43" s="8">
@@ -3590,9 +3807,13 @@
         <v>3</v>
       </c>
       <c r="AJ43" s="27"/>
-      <c r="AK43" s="12"/>
+      <c r="AK43" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="AL43" s="13"/>
-      <c r="AM43" s="12"/>
+      <c r="AM43" s="12" t="s">
+        <v>23</v>
+      </c>
       <c r="AN43" s="13"/>
       <c r="AO43" s="16"/>
       <c r="AU43" s="8" t="s">
@@ -3604,12 +3825,18 @@
       <c r="AW43" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="AX43" s="13"/>
+      <c r="AX43" s="13">
+        <v>2</v>
+      </c>
       <c r="AY43" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="AZ43" s="13"/>
-      <c r="BA43" s="32"/>
+      <c r="AZ43" s="13">
+        <v>5</v>
+      </c>
+      <c r="BA43" s="32" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="44" spans="1:54" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
@@ -3631,9 +3858,13 @@
         <v>4</v>
       </c>
       <c r="N44" s="33"/>
-      <c r="O44" s="12"/>
+      <c r="O44" s="12" t="s">
+        <v>26</v>
+      </c>
       <c r="P44" s="13"/>
-      <c r="Q44" s="12"/>
+      <c r="Q44" s="12" t="s">
+        <v>34</v>
+      </c>
       <c r="R44" s="13"/>
       <c r="S44" s="16"/>
       <c r="X44" s="8">
@@ -3649,9 +3880,13 @@
         <v>4</v>
       </c>
       <c r="AJ44" s="33"/>
-      <c r="AK44" s="12"/>
+      <c r="AK44" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="AL44" s="13"/>
-      <c r="AM44" s="12"/>
+      <c r="AM44" s="12" t="s">
+        <v>23</v>
+      </c>
       <c r="AN44" s="13"/>
       <c r="AO44" s="16"/>
       <c r="AU44" s="9" t="s">
@@ -3671,22 +3906,26 @@
       <c r="BA44" s="6"/>
     </row>
     <row r="45" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="42" t="s">
+      <c r="A45" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="B45" s="42"/>
-      <c r="C45" s="42"/>
-      <c r="D45" s="42"/>
-      <c r="E45" s="42"/>
-      <c r="F45" s="42"/>
-      <c r="G45" s="42"/>
+      <c r="B45" s="49"/>
+      <c r="C45" s="49"/>
+      <c r="D45" s="49"/>
+      <c r="E45" s="49"/>
+      <c r="F45" s="49"/>
+      <c r="G45" s="49"/>
       <c r="M45" s="8" t="s">
         <v>11</v>
       </c>
       <c r="N45" s="33"/>
-      <c r="O45" s="12"/>
+      <c r="O45" s="12" t="s">
+        <v>34</v>
+      </c>
       <c r="P45" s="13"/>
-      <c r="Q45" s="12"/>
+      <c r="Q45" s="12" t="s">
+        <v>26</v>
+      </c>
       <c r="R45" s="13"/>
       <c r="S45" s="16"/>
       <c r="X45" s="8" t="s">
@@ -3702,29 +3941,37 @@
         <v>11</v>
       </c>
       <c r="AJ45" s="27"/>
-      <c r="AK45" s="12"/>
+      <c r="AK45" s="12" t="s">
+        <v>23</v>
+      </c>
       <c r="AL45" s="13"/>
-      <c r="AM45" s="12"/>
+      <c r="AM45" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="AN45" s="13"/>
       <c r="AO45" s="16"/>
-      <c r="AU45" s="42" t="s">
+      <c r="AU45" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AV45" s="42"/>
-      <c r="AW45" s="42"/>
-      <c r="AX45" s="42"/>
-      <c r="AY45" s="42"/>
-      <c r="AZ45" s="42"/>
-      <c r="BA45" s="42"/>
+      <c r="AV45" s="49"/>
+      <c r="AW45" s="49"/>
+      <c r="AX45" s="49"/>
+      <c r="AY45" s="49"/>
+      <c r="AZ45" s="49"/>
+      <c r="BA45" s="49"/>
     </row>
     <row r="46" spans="1:54" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="M46" s="8" t="s">
         <v>10</v>
       </c>
       <c r="N46" s="33"/>
-      <c r="O46" s="12"/>
+      <c r="O46" s="12" t="s">
+        <v>26</v>
+      </c>
       <c r="P46" s="13"/>
-      <c r="Q46" s="12"/>
+      <c r="Q46" s="12" t="s">
+        <v>34</v>
+      </c>
       <c r="R46" s="13"/>
       <c r="S46" s="16"/>
       <c r="X46" s="8" t="s">
@@ -3740,9 +3987,13 @@
         <v>10</v>
       </c>
       <c r="AJ46" s="27"/>
-      <c r="AK46" s="12"/>
+      <c r="AK46" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="AL46" s="13"/>
-      <c r="AM46" s="12"/>
+      <c r="AM46" s="12" t="s">
+        <v>23</v>
+      </c>
       <c r="AN46" s="13"/>
       <c r="AO46" s="16"/>
     </row>
@@ -3751,9 +4002,13 @@
         <v>12</v>
       </c>
       <c r="N47" s="34"/>
-      <c r="O47" s="12"/>
+      <c r="O47" s="12" t="s">
+        <v>34</v>
+      </c>
       <c r="P47" s="13"/>
-      <c r="Q47" s="12"/>
+      <c r="Q47" s="12" t="s">
+        <v>26</v>
+      </c>
       <c r="R47" s="13"/>
       <c r="S47" s="16"/>
       <c r="X47" s="9" t="s">
@@ -3769,52 +4024,76 @@
         <v>12</v>
       </c>
       <c r="AJ47" s="28"/>
-      <c r="AK47" s="14"/>
+      <c r="AK47" s="14" t="s">
+        <v>23</v>
+      </c>
       <c r="AL47" s="15"/>
-      <c r="AM47" s="14"/>
+      <c r="AM47" s="14" t="s">
+        <v>38</v>
+      </c>
       <c r="AN47" s="15"/>
       <c r="AO47" s="6"/>
     </row>
     <row r="48" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="M48" s="53" t="s">
+      <c r="M48" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="N48" s="54"/>
-      <c r="O48" s="54"/>
-      <c r="P48" s="54"/>
-      <c r="Q48" s="54"/>
-      <c r="R48" s="54"/>
-      <c r="S48" s="55"/>
-      <c r="X48" s="42" t="s">
+      <c r="N48" s="43"/>
+      <c r="O48" s="43"/>
+      <c r="P48" s="43"/>
+      <c r="Q48" s="43"/>
+      <c r="R48" s="43"/>
+      <c r="S48" s="44"/>
+      <c r="X48" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="Y48" s="42"/>
-      <c r="Z48" s="42"/>
-      <c r="AA48" s="42"/>
-      <c r="AB48" s="42"/>
-      <c r="AC48" s="42"/>
-      <c r="AD48" s="42"/>
-      <c r="AI48" s="42" t="s">
+      <c r="Y48" s="49"/>
+      <c r="Z48" s="49"/>
+      <c r="AA48" s="49"/>
+      <c r="AB48" s="49"/>
+      <c r="AC48" s="49"/>
+      <c r="AD48" s="49"/>
+      <c r="AI48" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AJ48" s="42"/>
-      <c r="AK48" s="42"/>
-      <c r="AL48" s="42"/>
-      <c r="AM48" s="42"/>
-      <c r="AN48" s="42"/>
-      <c r="AO48" s="42"/>
+      <c r="AJ48" s="49"/>
+      <c r="AK48" s="49"/>
+      <c r="AL48" s="49"/>
+      <c r="AM48" s="49"/>
+      <c r="AN48" s="49"/>
+      <c r="AO48" s="49"/>
     </row>
     <row r="49" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="M48:S48"/>
-    <mergeCell ref="M39:S39"/>
-    <mergeCell ref="P37:V37"/>
-    <mergeCell ref="P28:V28"/>
-    <mergeCell ref="A36:G36"/>
-    <mergeCell ref="A45:G45"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="AU45:BA45"/>
+    <mergeCell ref="AF28:AL28"/>
+    <mergeCell ref="AF37:AL37"/>
+    <mergeCell ref="AQ30:AS30"/>
+    <mergeCell ref="AQ41:AS41"/>
+    <mergeCell ref="AU34:BA34"/>
+    <mergeCell ref="AU36:BA36"/>
+    <mergeCell ref="AU2:BA2"/>
+    <mergeCell ref="AU3:BA3"/>
+    <mergeCell ref="AU12:BA12"/>
+    <mergeCell ref="AU14:BA14"/>
+    <mergeCell ref="AU23:BA23"/>
+    <mergeCell ref="X37:AD37"/>
+    <mergeCell ref="AE26:AM26"/>
+    <mergeCell ref="Z1:AB1"/>
+    <mergeCell ref="X39:AD39"/>
+    <mergeCell ref="X48:AD48"/>
+    <mergeCell ref="AF1:BA1"/>
+    <mergeCell ref="AI2:AO2"/>
+    <mergeCell ref="AI3:AO3"/>
+    <mergeCell ref="AI12:AO12"/>
+    <mergeCell ref="AI39:AO39"/>
+    <mergeCell ref="AU25:BA25"/>
+    <mergeCell ref="AI48:AO48"/>
+    <mergeCell ref="AN14:AP14"/>
+    <mergeCell ref="AN36:AP36"/>
+    <mergeCell ref="AQ8:AS8"/>
+    <mergeCell ref="AQ19:AS19"/>
     <mergeCell ref="A1:U1"/>
     <mergeCell ref="O26:W26"/>
     <mergeCell ref="I41:K41"/>
@@ -3831,34 +4110,14 @@
     <mergeCell ref="I8:K8"/>
     <mergeCell ref="I19:K19"/>
     <mergeCell ref="A25:G25"/>
-    <mergeCell ref="X37:AD37"/>
-    <mergeCell ref="AE26:AM26"/>
-    <mergeCell ref="Z1:AB1"/>
-    <mergeCell ref="X39:AD39"/>
-    <mergeCell ref="X48:AD48"/>
-    <mergeCell ref="AF1:BA1"/>
-    <mergeCell ref="AI2:AO2"/>
-    <mergeCell ref="AI3:AO3"/>
-    <mergeCell ref="AI12:AO12"/>
-    <mergeCell ref="AI39:AO39"/>
-    <mergeCell ref="AU25:BA25"/>
-    <mergeCell ref="AI48:AO48"/>
-    <mergeCell ref="AN14:AP14"/>
-    <mergeCell ref="AN36:AP36"/>
-    <mergeCell ref="AQ8:AS8"/>
-    <mergeCell ref="AQ19:AS19"/>
-    <mergeCell ref="AU2:BA2"/>
-    <mergeCell ref="AU3:BA3"/>
-    <mergeCell ref="AU12:BA12"/>
-    <mergeCell ref="AU14:BA14"/>
-    <mergeCell ref="AU23:BA23"/>
-    <mergeCell ref="AU45:BA45"/>
-    <mergeCell ref="AF28:AL28"/>
-    <mergeCell ref="AF37:AL37"/>
-    <mergeCell ref="AQ30:AS30"/>
-    <mergeCell ref="AQ41:AS41"/>
-    <mergeCell ref="AU34:BA34"/>
-    <mergeCell ref="AU36:BA36"/>
+    <mergeCell ref="M48:S48"/>
+    <mergeCell ref="M39:S39"/>
+    <mergeCell ref="P37:V37"/>
+    <mergeCell ref="P28:V28"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="A34:G34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/2025_2026/Playoffs/Brackets.xlsx
+++ b/2025_2026/Playoffs/Brackets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\NHLStats\2025_2026\Playoffs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CEEF378-AFF0-4417-8A97-53C9B677FB71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBDB60BE-EEBB-4695-9996-2BAF6C553BDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="85">
   <si>
     <t>Eastern Conference Playoff Teams</t>
   </si>
@@ -659,6 +659,39 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -677,46 +710,13 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1086,18 +1086,18 @@
     </row>
     <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="11" spans="1:7" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="61" t="s">
+      <c r="A11" s="59" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="61"/>
-      <c r="C11" s="61" t="s">
+      <c r="B11" s="59"/>
+      <c r="C11" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="61"/>
-      <c r="E11" s="61" t="s">
+      <c r="D11" s="59"/>
+      <c r="E11" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="61"/>
+      <c r="F11" s="59"/>
       <c r="G11" s="4" t="s">
         <v>18</v>
       </c>
@@ -1126,18 +1126,18 @@
       </c>
     </row>
     <row r="13" spans="1:7" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="59" t="s">
+      <c r="A13" s="60" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="60"/>
-      <c r="C13" s="59" t="s">
+      <c r="B13" s="61"/>
+      <c r="C13" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="D13" s="60"/>
-      <c r="E13" s="59" t="s">
+      <c r="D13" s="61"/>
+      <c r="E13" s="60" t="s">
         <v>17</v>
       </c>
-      <c r="F13" s="60"/>
+      <c r="F13" s="61"/>
       <c r="G13" s="5"/>
     </row>
     <row r="14" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1171,14 +1171,14 @@
       <c r="F15" s="6"/>
     </row>
     <row r="16" spans="1:7" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="59" t="s">
+      <c r="A16" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="60"/>
-      <c r="C16" s="59" t="s">
+      <c r="B16" s="61"/>
+      <c r="C16" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="60"/>
+      <c r="D16" s="61"/>
     </row>
     <row r="17" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
@@ -1209,10 +1209,10 @@
       </c>
     </row>
     <row r="19" spans="1:4" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="59" t="s">
+      <c r="A19" s="60" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="60"/>
+      <c r="B19" s="61"/>
     </row>
     <row r="20" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
@@ -1231,10 +1231,10 @@
       </c>
     </row>
     <row r="22" spans="1:4" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="59" t="s">
+      <c r="A22" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="60"/>
+      <c r="B22" s="61"/>
     </row>
     <row r="23" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
@@ -1319,16 +1319,16 @@
     <sortCondition ref="B2:B9"/>
   </sortState>
   <mergeCells count="10">
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C16:D16"/>
     <mergeCell ref="E11:F11"/>
     <mergeCell ref="E13:F13"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C16:D16"/>
   </mergeCells>
   <dataValidations count="16">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C14" xr:uid="{2C3D9587-ABAE-4E3F-8B22-396DF812BF02}">
@@ -1432,124 +1432,124 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:54" ht="27.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
-      <c r="M1" s="52"/>
-      <c r="N1" s="52"/>
-      <c r="O1" s="52"/>
-      <c r="P1" s="52"/>
-      <c r="Q1" s="52"/>
-      <c r="R1" s="52"/>
-      <c r="S1" s="52"/>
-      <c r="T1" s="52"/>
-      <c r="U1" s="53"/>
-      <c r="Z1" s="51" t="s">
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
+      <c r="K1" s="51"/>
+      <c r="L1" s="51"/>
+      <c r="M1" s="51"/>
+      <c r="N1" s="51"/>
+      <c r="O1" s="51"/>
+      <c r="P1" s="51"/>
+      <c r="Q1" s="51"/>
+      <c r="R1" s="51"/>
+      <c r="S1" s="51"/>
+      <c r="T1" s="51"/>
+      <c r="U1" s="52"/>
+      <c r="Z1" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="AA1" s="52"/>
-      <c r="AB1" s="53"/>
-      <c r="AF1" s="51" t="s">
+      <c r="AA1" s="51"/>
+      <c r="AB1" s="52"/>
+      <c r="AF1" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="AG1" s="52"/>
-      <c r="AH1" s="52"/>
-      <c r="AI1" s="52"/>
-      <c r="AJ1" s="52"/>
-      <c r="AK1" s="52"/>
-      <c r="AL1" s="52"/>
-      <c r="AM1" s="52"/>
-      <c r="AN1" s="52"/>
-      <c r="AO1" s="52"/>
-      <c r="AP1" s="52"/>
-      <c r="AQ1" s="52"/>
-      <c r="AR1" s="52"/>
-      <c r="AS1" s="52"/>
-      <c r="AT1" s="52"/>
-      <c r="AU1" s="52"/>
-      <c r="AV1" s="52"/>
-      <c r="AW1" s="52"/>
-      <c r="AX1" s="52"/>
-      <c r="AY1" s="52"/>
-      <c r="AZ1" s="52"/>
-      <c r="BA1" s="53"/>
+      <c r="AG1" s="51"/>
+      <c r="AH1" s="51"/>
+      <c r="AI1" s="51"/>
+      <c r="AJ1" s="51"/>
+      <c r="AK1" s="51"/>
+      <c r="AL1" s="51"/>
+      <c r="AM1" s="51"/>
+      <c r="AN1" s="51"/>
+      <c r="AO1" s="51"/>
+      <c r="AP1" s="51"/>
+      <c r="AQ1" s="51"/>
+      <c r="AR1" s="51"/>
+      <c r="AS1" s="51"/>
+      <c r="AT1" s="51"/>
+      <c r="AU1" s="51"/>
+      <c r="AV1" s="51"/>
+      <c r="AW1" s="51"/>
+      <c r="AX1" s="51"/>
+      <c r="AY1" s="51"/>
+      <c r="AZ1" s="51"/>
+      <c r="BA1" s="52"/>
     </row>
     <row r="2" spans="1:54" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="55" t="s">
+      <c r="A2" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="57"/>
-      <c r="M2" s="55" t="s">
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="48"/>
+      <c r="M2" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="56"/>
-      <c r="O2" s="56"/>
-      <c r="P2" s="56"/>
-      <c r="Q2" s="56"/>
-      <c r="R2" s="57"/>
-      <c r="AI2" s="55" t="s">
+      <c r="N2" s="47"/>
+      <c r="O2" s="47"/>
+      <c r="P2" s="47"/>
+      <c r="Q2" s="47"/>
+      <c r="R2" s="48"/>
+      <c r="AI2" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="AJ2" s="56"/>
-      <c r="AK2" s="56"/>
-      <c r="AL2" s="56"/>
-      <c r="AM2" s="56"/>
-      <c r="AN2" s="56"/>
-      <c r="AO2" s="57"/>
-      <c r="AU2" s="55" t="s">
+      <c r="AJ2" s="47"/>
+      <c r="AK2" s="47"/>
+      <c r="AL2" s="47"/>
+      <c r="AM2" s="47"/>
+      <c r="AN2" s="47"/>
+      <c r="AO2" s="48"/>
+      <c r="AU2" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="AV2" s="56"/>
-      <c r="AW2" s="56"/>
-      <c r="AX2" s="56"/>
-      <c r="AY2" s="56"/>
-      <c r="AZ2" s="56"/>
-      <c r="BA2" s="57"/>
+      <c r="AV2" s="47"/>
+      <c r="AW2" s="47"/>
+      <c r="AX2" s="47"/>
+      <c r="AY2" s="47"/>
+      <c r="AZ2" s="47"/>
+      <c r="BA2" s="48"/>
     </row>
     <row r="3" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="49" t="s">
+      <c r="A3" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="49"/>
-      <c r="C3" s="49"/>
-      <c r="D3" s="49"/>
-      <c r="E3" s="49"/>
-      <c r="F3" s="49"/>
-      <c r="G3" s="49"/>
-      <c r="AI3" s="42" t="s">
+      <c r="B3" s="42"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="42"/>
+      <c r="AI3" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="AJ3" s="43"/>
-      <c r="AK3" s="43"/>
-      <c r="AL3" s="43"/>
-      <c r="AM3" s="43"/>
-      <c r="AN3" s="43"/>
-      <c r="AO3" s="44"/>
-      <c r="AU3" s="49" t="s">
+      <c r="AJ3" s="54"/>
+      <c r="AK3" s="54"/>
+      <c r="AL3" s="54"/>
+      <c r="AM3" s="54"/>
+      <c r="AN3" s="54"/>
+      <c r="AO3" s="55"/>
+      <c r="AU3" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="AV3" s="49"/>
-      <c r="AW3" s="49"/>
-      <c r="AX3" s="49"/>
-      <c r="AY3" s="49"/>
-      <c r="AZ3" s="49"/>
-      <c r="BA3" s="49"/>
+      <c r="AV3" s="42"/>
+      <c r="AW3" s="42"/>
+      <c r="AX3" s="42"/>
+      <c r="AY3" s="42"/>
+      <c r="AZ3" s="42"/>
+      <c r="BA3" s="42"/>
     </row>
     <row r="4" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
@@ -1573,15 +1573,15 @@
       <c r="G4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="42" t="s">
+      <c r="M4" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="N4" s="43"/>
-      <c r="O4" s="43"/>
-      <c r="P4" s="43"/>
-      <c r="Q4" s="43"/>
-      <c r="R4" s="43"/>
-      <c r="S4" s="44"/>
+      <c r="N4" s="54"/>
+      <c r="O4" s="54"/>
+      <c r="P4" s="54"/>
+      <c r="Q4" s="54"/>
+      <c r="R4" s="54"/>
+      <c r="S4" s="55"/>
       <c r="AI4" s="3" t="s">
         <v>2</v>
       </c>
@@ -1730,7 +1730,9 @@
       <c r="M6" s="7">
         <v>1</v>
       </c>
-      <c r="N6" s="29"/>
+      <c r="N6" s="29">
+        <v>46148</v>
+      </c>
       <c r="O6" s="10"/>
       <c r="P6" s="11"/>
       <c r="Q6" s="10" t="s">
@@ -1741,7 +1743,9 @@
       <c r="AI6" s="8">
         <v>2</v>
       </c>
-      <c r="AJ6" s="27"/>
+      <c r="AJ6" s="27">
+        <v>46147</v>
+      </c>
       <c r="AK6" s="12" t="s">
         <v>31</v>
       </c>
@@ -1801,7 +1805,9 @@
       <c r="M7" s="8">
         <v>2</v>
       </c>
-      <c r="N7" s="33"/>
+      <c r="N7" s="33">
+        <v>46150</v>
+      </c>
       <c r="O7" s="12"/>
       <c r="P7" s="13"/>
       <c r="Q7" s="12" t="s">
@@ -1812,7 +1818,9 @@
       <c r="AI7" s="8">
         <v>3</v>
       </c>
-      <c r="AJ7" s="27"/>
+      <c r="AJ7" s="27">
+        <v>46151</v>
+      </c>
       <c r="AK7" s="12" t="s">
         <v>27</v>
       </c>
@@ -1866,15 +1874,17 @@
       <c r="G8" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="I8" s="50" t="s">
+      <c r="I8" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="J8" s="50"/>
-      <c r="K8" s="50"/>
+      <c r="J8" s="43"/>
+      <c r="K8" s="43"/>
       <c r="M8" s="8">
         <v>3</v>
       </c>
-      <c r="N8" s="33"/>
+      <c r="N8" s="33">
+        <v>46152</v>
+      </c>
       <c r="O8" s="30" t="s">
         <v>25</v>
       </c>
@@ -1885,7 +1895,9 @@
       <c r="AI8" s="8">
         <v>4</v>
       </c>
-      <c r="AJ8" s="33"/>
+      <c r="AJ8" s="33">
+        <v>46153</v>
+      </c>
       <c r="AK8" s="30" t="s">
         <v>27</v>
       </c>
@@ -1895,11 +1907,11 @@
       </c>
       <c r="AN8" s="31"/>
       <c r="AO8" s="16"/>
-      <c r="AQ8" s="50" t="s">
+      <c r="AQ8" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="AR8" s="50"/>
-      <c r="AS8" s="50"/>
+      <c r="AR8" s="43"/>
+      <c r="AS8" s="43"/>
       <c r="AU8" s="38">
         <v>4</v>
       </c>
@@ -1951,7 +1963,9 @@
       <c r="M9" s="8">
         <v>4</v>
       </c>
-      <c r="N9" s="33"/>
+      <c r="N9" s="33">
+        <v>46154</v>
+      </c>
       <c r="O9" s="12" t="s">
         <v>25</v>
       </c>
@@ -1962,7 +1976,9 @@
       <c r="AI9" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="AJ9" s="27"/>
+      <c r="AJ9" s="27">
+        <v>46155</v>
+      </c>
       <c r="AK9" s="12" t="s">
         <v>31</v>
       </c>
@@ -2017,7 +2033,9 @@
       <c r="M10" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="N10" s="33"/>
+      <c r="N10" s="33">
+        <v>46156</v>
+      </c>
       <c r="O10" s="12"/>
       <c r="P10" s="13"/>
       <c r="Q10" s="12" t="s">
@@ -2028,7 +2046,9 @@
       <c r="AI10" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="AJ10" s="27"/>
+      <c r="AJ10" s="27">
+        <v>46157</v>
+      </c>
       <c r="AK10" s="12" t="s">
         <v>27</v>
       </c>
@@ -2075,7 +2095,9 @@
       <c r="M11" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="N11" s="33"/>
+      <c r="N11" s="33">
+        <v>46158</v>
+      </c>
       <c r="O11" s="12"/>
       <c r="P11" s="13"/>
       <c r="Q11" s="12"/>
@@ -2084,7 +2106,9 @@
       <c r="AI11" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="AJ11" s="28"/>
+      <c r="AJ11" s="28">
+        <v>46159</v>
+      </c>
       <c r="AK11" s="14" t="s">
         <v>31</v>
       </c>
@@ -2112,20 +2136,22 @@
       <c r="BA11" s="6"/>
     </row>
     <row r="12" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="49" t="s">
+      <c r="A12" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="49"/>
-      <c r="C12" s="49"/>
-      <c r="D12" s="49"/>
-      <c r="E12" s="49"/>
-      <c r="F12" s="49"/>
-      <c r="G12" s="49"/>
+      <c r="B12" s="42"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="42"/>
       <c r="L12" s="12"/>
       <c r="M12" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="N12" s="34"/>
+      <c r="N12" s="34">
+        <v>46160</v>
+      </c>
       <c r="O12" s="12"/>
       <c r="P12" s="13"/>
       <c r="Q12" s="12" t="s">
@@ -2133,65 +2159,65 @@
       </c>
       <c r="R12" s="13"/>
       <c r="S12" s="16"/>
-      <c r="AI12" s="49" t="s">
+      <c r="AI12" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AJ12" s="49"/>
-      <c r="AK12" s="49"/>
-      <c r="AL12" s="49"/>
-      <c r="AM12" s="49"/>
-      <c r="AN12" s="49"/>
-      <c r="AO12" s="49"/>
+      <c r="AJ12" s="42"/>
+      <c r="AK12" s="42"/>
+      <c r="AL12" s="42"/>
+      <c r="AM12" s="42"/>
+      <c r="AN12" s="42"/>
+      <c r="AO12" s="42"/>
       <c r="AQ12" s="12"/>
-      <c r="AU12" s="49" t="s">
+      <c r="AU12" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AV12" s="49"/>
-      <c r="AW12" s="49"/>
-      <c r="AX12" s="49"/>
-      <c r="AY12" s="49"/>
-      <c r="AZ12" s="49"/>
-      <c r="BA12" s="49"/>
+      <c r="AV12" s="42"/>
+      <c r="AW12" s="42"/>
+      <c r="AX12" s="42"/>
+      <c r="AY12" s="42"/>
+      <c r="AZ12" s="42"/>
+      <c r="BA12" s="42"/>
     </row>
     <row r="13" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L13" s="12"/>
-      <c r="M13" s="42" t="s">
+      <c r="M13" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="N13" s="43"/>
-      <c r="O13" s="43"/>
-      <c r="P13" s="43"/>
-      <c r="Q13" s="43"/>
-      <c r="R13" s="43"/>
-      <c r="S13" s="44"/>
+      <c r="N13" s="54"/>
+      <c r="O13" s="54"/>
+      <c r="P13" s="54"/>
+      <c r="Q13" s="54"/>
+      <c r="R13" s="54"/>
+      <c r="S13" s="55"/>
       <c r="AQ13" s="12"/>
     </row>
     <row r="14" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="48" t="s">
+      <c r="A14" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="48"/>
-      <c r="C14" s="48"/>
-      <c r="D14" s="48"/>
-      <c r="E14" s="48"/>
-      <c r="F14" s="48"/>
-      <c r="G14" s="48"/>
-      <c r="L14" s="54"/>
-      <c r="M14" s="50"/>
-      <c r="N14" s="50"/>
-      <c r="AN14" s="50"/>
-      <c r="AO14" s="50"/>
-      <c r="AP14" s="50"/>
+      <c r="B14" s="45"/>
+      <c r="C14" s="45"/>
+      <c r="D14" s="45"/>
+      <c r="E14" s="45"/>
+      <c r="F14" s="45"/>
+      <c r="G14" s="45"/>
+      <c r="L14" s="44"/>
+      <c r="M14" s="43"/>
+      <c r="N14" s="43"/>
+      <c r="AN14" s="43"/>
+      <c r="AO14" s="43"/>
+      <c r="AP14" s="43"/>
       <c r="AQ14" s="12"/>
-      <c r="AU14" s="48" t="s">
+      <c r="AU14" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="AV14" s="48"/>
-      <c r="AW14" s="48"/>
-      <c r="AX14" s="48"/>
-      <c r="AY14" s="48"/>
-      <c r="AZ14" s="48"/>
-      <c r="BA14" s="48"/>
+      <c r="AV14" s="45"/>
+      <c r="AW14" s="45"/>
+      <c r="AX14" s="45"/>
+      <c r="AY14" s="45"/>
+      <c r="AZ14" s="45"/>
+      <c r="BA14" s="45"/>
     </row>
     <row r="15" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
@@ -2419,17 +2445,17 @@
       <c r="G19" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="I19" s="50"/>
-      <c r="J19" s="50"/>
-      <c r="K19" s="50"/>
+      <c r="I19" s="43"/>
+      <c r="J19" s="43"/>
+      <c r="K19" s="43"/>
       <c r="L19" s="12"/>
       <c r="O19" s="12"/>
       <c r="AN19" s="12"/>
-      <c r="AQ19" s="54" t="s">
+      <c r="AQ19" s="44" t="s">
         <v>31</v>
       </c>
-      <c r="AR19" s="50"/>
-      <c r="AS19" s="50"/>
+      <c r="AR19" s="43"/>
+      <c r="AS19" s="43"/>
       <c r="AU19" s="38">
         <v>4</v>
       </c>
@@ -2585,52 +2611,52 @@
       <c r="BA22" s="6"/>
     </row>
     <row r="23" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="49" t="s">
+      <c r="A23" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B23" s="49"/>
-      <c r="C23" s="49"/>
-      <c r="D23" s="49"/>
-      <c r="E23" s="49"/>
-      <c r="F23" s="49"/>
-      <c r="G23" s="49"/>
+      <c r="B23" s="42"/>
+      <c r="C23" s="42"/>
+      <c r="D23" s="42"/>
+      <c r="E23" s="42"/>
+      <c r="F23" s="42"/>
+      <c r="G23" s="42"/>
       <c r="O23" s="12"/>
       <c r="AN23" s="12"/>
-      <c r="AU23" s="49" t="s">
+      <c r="AU23" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AV23" s="49"/>
-      <c r="AW23" s="49"/>
-      <c r="AX23" s="49"/>
-      <c r="AY23" s="49"/>
-      <c r="AZ23" s="49"/>
-      <c r="BA23" s="49"/>
+      <c r="AV23" s="42"/>
+      <c r="AW23" s="42"/>
+      <c r="AX23" s="42"/>
+      <c r="AY23" s="42"/>
+      <c r="AZ23" s="42"/>
+      <c r="BA23" s="42"/>
     </row>
     <row r="24" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="O24" s="12"/>
       <c r="AN24" s="12"/>
     </row>
     <row r="25" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="49" t="s">
+      <c r="A25" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="49"/>
-      <c r="C25" s="49"/>
-      <c r="D25" s="49"/>
-      <c r="E25" s="49"/>
-      <c r="F25" s="49"/>
-      <c r="G25" s="49"/>
+      <c r="B25" s="42"/>
+      <c r="C25" s="42"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="42"/>
+      <c r="F25" s="42"/>
+      <c r="G25" s="42"/>
       <c r="O25" s="12"/>
       <c r="AN25" s="12"/>
-      <c r="AU25" s="49" t="s">
+      <c r="AU25" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="AV25" s="49"/>
-      <c r="AW25" s="49"/>
-      <c r="AX25" s="49"/>
-      <c r="AY25" s="49"/>
-      <c r="AZ25" s="49"/>
-      <c r="BA25" s="49"/>
+      <c r="AV25" s="42"/>
+      <c r="AW25" s="42"/>
+      <c r="AX25" s="42"/>
+      <c r="AY25" s="42"/>
+      <c r="AZ25" s="42"/>
+      <c r="BA25" s="42"/>
     </row>
     <row r="26" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="20" t="s">
@@ -2654,24 +2680,24 @@
       <c r="G26" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="O26" s="54"/>
-      <c r="P26" s="50"/>
-      <c r="Q26" s="50"/>
-      <c r="R26" s="50"/>
-      <c r="S26" s="50"/>
-      <c r="T26" s="50"/>
-      <c r="U26" s="50"/>
-      <c r="V26" s="50"/>
-      <c r="W26" s="50"/>
-      <c r="AE26" s="50"/>
-      <c r="AF26" s="50"/>
-      <c r="AG26" s="50"/>
-      <c r="AH26" s="50"/>
-      <c r="AI26" s="50"/>
-      <c r="AJ26" s="50"/>
-      <c r="AK26" s="50"/>
-      <c r="AL26" s="50"/>
-      <c r="AM26" s="58"/>
+      <c r="O26" s="44"/>
+      <c r="P26" s="43"/>
+      <c r="Q26" s="43"/>
+      <c r="R26" s="43"/>
+      <c r="S26" s="43"/>
+      <c r="T26" s="43"/>
+      <c r="U26" s="43"/>
+      <c r="V26" s="43"/>
+      <c r="W26" s="43"/>
+      <c r="AE26" s="43"/>
+      <c r="AF26" s="43"/>
+      <c r="AG26" s="43"/>
+      <c r="AH26" s="43"/>
+      <c r="AI26" s="43"/>
+      <c r="AJ26" s="43"/>
+      <c r="AK26" s="43"/>
+      <c r="AL26" s="43"/>
+      <c r="AM26" s="49"/>
       <c r="AU26" s="20" t="s">
         <v>2</v>
       </c>
@@ -2768,26 +2794,26 @@
         <v>54</v>
       </c>
       <c r="O28" s="12"/>
-      <c r="P28" s="42" t="s">
+      <c r="P28" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="Q28" s="43"/>
-      <c r="R28" s="43"/>
-      <c r="S28" s="43"/>
-      <c r="T28" s="43"/>
-      <c r="U28" s="43"/>
-      <c r="V28" s="44"/>
+      <c r="Q28" s="54"/>
+      <c r="R28" s="54"/>
+      <c r="S28" s="54"/>
+      <c r="T28" s="54"/>
+      <c r="U28" s="54"/>
+      <c r="V28" s="55"/>
       <c r="X28" s="12"/>
       <c r="AD28" s="13"/>
-      <c r="AF28" s="49" t="s">
+      <c r="AF28" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="AG28" s="49"/>
-      <c r="AH28" s="49"/>
-      <c r="AI28" s="49"/>
-      <c r="AJ28" s="49"/>
-      <c r="AK28" s="49"/>
-      <c r="AL28" s="49"/>
+      <c r="AG28" s="42"/>
+      <c r="AH28" s="42"/>
+      <c r="AI28" s="42"/>
+      <c r="AJ28" s="42"/>
+      <c r="AK28" s="42"/>
+      <c r="AL28" s="42"/>
       <c r="AN28" s="12"/>
       <c r="AU28" s="8">
         <v>2</v>
@@ -2923,11 +2949,11 @@
       <c r="G30" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="I30" s="50" t="s">
+      <c r="I30" s="43" t="s">
         <v>26</v>
       </c>
-      <c r="J30" s="50"/>
-      <c r="K30" s="50"/>
+      <c r="J30" s="43"/>
+      <c r="K30" s="43"/>
       <c r="O30" s="12"/>
       <c r="P30" s="7">
         <v>1</v>
@@ -2950,11 +2976,11 @@
       <c r="AK30" s="24"/>
       <c r="AL30" s="25"/>
       <c r="AN30" s="12"/>
-      <c r="AQ30" s="50" t="s">
+      <c r="AQ30" s="43" t="s">
         <v>38</v>
       </c>
-      <c r="AR30" s="50"/>
-      <c r="AS30" s="50"/>
+      <c r="AR30" s="43"/>
+      <c r="AS30" s="43"/>
       <c r="AU30" s="38">
         <v>4</v>
       </c>
@@ -3166,15 +3192,15 @@
       <c r="BA33" s="6"/>
     </row>
     <row r="34" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="49" t="s">
+      <c r="A34" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B34" s="49"/>
-      <c r="C34" s="49"/>
-      <c r="D34" s="49"/>
-      <c r="E34" s="49"/>
-      <c r="F34" s="49"/>
-      <c r="G34" s="49"/>
+      <c r="B34" s="42"/>
+      <c r="C34" s="42"/>
+      <c r="D34" s="42"/>
+      <c r="E34" s="42"/>
+      <c r="F34" s="42"/>
+      <c r="G34" s="42"/>
       <c r="L34" s="12"/>
       <c r="O34" s="12"/>
       <c r="P34" s="8" t="s">
@@ -3199,15 +3225,15 @@
       <c r="AL34" s="16"/>
       <c r="AN34" s="12"/>
       <c r="AQ34" s="12"/>
-      <c r="AU34" s="49" t="s">
+      <c r="AU34" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AV34" s="49"/>
-      <c r="AW34" s="49"/>
-      <c r="AX34" s="49"/>
-      <c r="AY34" s="49"/>
-      <c r="AZ34" s="49"/>
-      <c r="BA34" s="49"/>
+      <c r="AV34" s="42"/>
+      <c r="AW34" s="42"/>
+      <c r="AX34" s="42"/>
+      <c r="AY34" s="42"/>
+      <c r="AZ34" s="42"/>
+      <c r="BA34" s="42"/>
     </row>
     <row r="35" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L35" s="12"/>
@@ -3236,18 +3262,18 @@
       <c r="AQ35" s="12"/>
     </row>
     <row r="36" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="48" t="s">
+      <c r="A36" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="B36" s="48"/>
-      <c r="C36" s="48"/>
-      <c r="D36" s="48"/>
-      <c r="E36" s="48"/>
-      <c r="F36" s="48"/>
-      <c r="G36" s="48"/>
-      <c r="L36" s="54"/>
-      <c r="M36" s="50"/>
-      <c r="N36" s="50"/>
+      <c r="B36" s="45"/>
+      <c r="C36" s="45"/>
+      <c r="D36" s="45"/>
+      <c r="E36" s="45"/>
+      <c r="F36" s="45"/>
+      <c r="G36" s="45"/>
+      <c r="L36" s="44"/>
+      <c r="M36" s="43"/>
+      <c r="N36" s="43"/>
       <c r="O36" s="12"/>
       <c r="P36" s="8" t="s">
         <v>12</v>
@@ -3269,19 +3295,19 @@
       <c r="AJ36" s="35"/>
       <c r="AK36" s="36"/>
       <c r="AL36" s="37"/>
-      <c r="AN36" s="54"/>
-      <c r="AO36" s="50"/>
-      <c r="AP36" s="50"/>
+      <c r="AN36" s="44"/>
+      <c r="AO36" s="43"/>
+      <c r="AP36" s="43"/>
       <c r="AQ36" s="12"/>
-      <c r="AU36" s="48" t="s">
+      <c r="AU36" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="AV36" s="48"/>
-      <c r="AW36" s="48"/>
-      <c r="AX36" s="48"/>
-      <c r="AY36" s="48"/>
-      <c r="AZ36" s="48"/>
-      <c r="BA36" s="48"/>
+      <c r="AV36" s="45"/>
+      <c r="AW36" s="45"/>
+      <c r="AX36" s="45"/>
+      <c r="AY36" s="45"/>
+      <c r="AZ36" s="45"/>
+      <c r="BA36" s="45"/>
     </row>
     <row r="37" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37" s="20" t="s">
@@ -3306,31 +3332,31 @@
         <v>9</v>
       </c>
       <c r="L37" s="12"/>
-      <c r="P37" s="45" t="s">
+      <c r="P37" s="56" t="s">
         <v>13</v>
       </c>
-      <c r="Q37" s="46"/>
-      <c r="R37" s="46"/>
-      <c r="S37" s="46"/>
-      <c r="T37" s="46"/>
-      <c r="U37" s="46"/>
-      <c r="V37" s="47"/>
-      <c r="X37" s="54"/>
-      <c r="Y37" s="50"/>
-      <c r="Z37" s="50"/>
-      <c r="AA37" s="50"/>
-      <c r="AB37" s="50"/>
-      <c r="AC37" s="50"/>
-      <c r="AD37" s="58"/>
-      <c r="AF37" s="49" t="s">
+      <c r="Q37" s="57"/>
+      <c r="R37" s="57"/>
+      <c r="S37" s="57"/>
+      <c r="T37" s="57"/>
+      <c r="U37" s="57"/>
+      <c r="V37" s="58"/>
+      <c r="X37" s="44"/>
+      <c r="Y37" s="43"/>
+      <c r="Z37" s="43"/>
+      <c r="AA37" s="43"/>
+      <c r="AB37" s="43"/>
+      <c r="AC37" s="43"/>
+      <c r="AD37" s="49"/>
+      <c r="AF37" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AG37" s="49"/>
-      <c r="AH37" s="49"/>
-      <c r="AI37" s="49"/>
-      <c r="AJ37" s="49"/>
-      <c r="AK37" s="49"/>
-      <c r="AL37" s="49"/>
+      <c r="AG37" s="42"/>
+      <c r="AH37" s="42"/>
+      <c r="AI37" s="42"/>
+      <c r="AJ37" s="42"/>
+      <c r="AK37" s="42"/>
+      <c r="AL37" s="42"/>
       <c r="AQ37" s="12"/>
       <c r="AU37" s="3" t="s">
         <v>2</v>
@@ -3423,33 +3449,33 @@
         <v>53</v>
       </c>
       <c r="L39" s="12"/>
-      <c r="M39" s="42" t="s">
+      <c r="M39" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="N39" s="43"/>
-      <c r="O39" s="43"/>
-      <c r="P39" s="43"/>
-      <c r="Q39" s="43"/>
-      <c r="R39" s="43"/>
-      <c r="S39" s="44"/>
-      <c r="X39" s="49" t="s">
+      <c r="N39" s="54"/>
+      <c r="O39" s="54"/>
+      <c r="P39" s="54"/>
+      <c r="Q39" s="54"/>
+      <c r="R39" s="54"/>
+      <c r="S39" s="55"/>
+      <c r="X39" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="Y39" s="49"/>
-      <c r="Z39" s="49"/>
-      <c r="AA39" s="49"/>
-      <c r="AB39" s="49"/>
-      <c r="AC39" s="49"/>
-      <c r="AD39" s="49"/>
-      <c r="AI39" s="42" t="s">
+      <c r="Y39" s="42"/>
+      <c r="Z39" s="42"/>
+      <c r="AA39" s="42"/>
+      <c r="AB39" s="42"/>
+      <c r="AC39" s="42"/>
+      <c r="AD39" s="42"/>
+      <c r="AI39" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="AJ39" s="43"/>
-      <c r="AK39" s="43"/>
-      <c r="AL39" s="43"/>
-      <c r="AM39" s="43"/>
-      <c r="AN39" s="43"/>
-      <c r="AO39" s="44"/>
+      <c r="AJ39" s="54"/>
+      <c r="AK39" s="54"/>
+      <c r="AL39" s="54"/>
+      <c r="AM39" s="54"/>
+      <c r="AN39" s="54"/>
+      <c r="AO39" s="55"/>
       <c r="AQ39" s="12"/>
       <c r="AU39" s="8">
         <v>2</v>
@@ -3604,11 +3630,11 @@
       <c r="G41" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="I41" s="50" t="s">
+      <c r="I41" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="J41" s="50"/>
-      <c r="K41" s="50"/>
+      <c r="J41" s="43"/>
+      <c r="K41" s="43"/>
       <c r="L41" s="12"/>
       <c r="M41" s="7">
         <v>1</v>
@@ -3619,12 +3645,18 @@
       <c r="O41" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="P41" s="24"/>
+      <c r="P41" s="24">
+        <v>0</v>
+      </c>
       <c r="Q41" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="R41" s="24"/>
-      <c r="S41" s="25"/>
+      <c r="R41" s="24">
+        <v>3</v>
+      </c>
+      <c r="S41" s="25" t="s">
+        <v>45</v>
+      </c>
       <c r="X41" s="7">
         <v>1</v>
       </c>
@@ -3637,7 +3669,9 @@
       <c r="AI41" s="7">
         <v>1</v>
       </c>
-      <c r="AJ41" s="29"/>
+      <c r="AJ41" s="29">
+        <v>46146</v>
+      </c>
       <c r="AK41" s="23" t="s">
         <v>23</v>
       </c>
@@ -3647,11 +3681,11 @@
       </c>
       <c r="AN41" s="24"/>
       <c r="AO41" s="25"/>
-      <c r="AQ41" s="54" t="s">
+      <c r="AQ41" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="AR41" s="50"/>
-      <c r="AS41" s="50"/>
+      <c r="AR41" s="43"/>
+      <c r="AS41" s="43"/>
       <c r="AU41" s="38">
         <v>4</v>
       </c>
@@ -3702,7 +3736,9 @@
       <c r="M42" s="8">
         <v>2</v>
       </c>
-      <c r="N42" s="33"/>
+      <c r="N42" s="33">
+        <v>46146</v>
+      </c>
       <c r="O42" s="12" t="s">
         <v>34</v>
       </c>
@@ -3724,7 +3760,9 @@
       <c r="AI42" s="8">
         <v>2</v>
       </c>
-      <c r="AJ42" s="27"/>
+      <c r="AJ42" s="27">
+        <v>46148</v>
+      </c>
       <c r="AK42" s="12" t="s">
         <v>23</v>
       </c>
@@ -3784,7 +3822,9 @@
       <c r="M43" s="8">
         <v>3</v>
       </c>
-      <c r="N43" s="33"/>
+      <c r="N43" s="33">
+        <v>46149</v>
+      </c>
       <c r="O43" s="12" t="s">
         <v>26</v>
       </c>
@@ -3806,7 +3846,9 @@
       <c r="AI43" s="8">
         <v>3</v>
       </c>
-      <c r="AJ43" s="27"/>
+      <c r="AJ43" s="27">
+        <v>46150</v>
+      </c>
       <c r="AK43" s="12" t="s">
         <v>38</v>
       </c>
@@ -3857,7 +3899,9 @@
       <c r="M44" s="8">
         <v>4</v>
       </c>
-      <c r="N44" s="33"/>
+      <c r="N44" s="33">
+        <v>46151</v>
+      </c>
       <c r="O44" s="12" t="s">
         <v>26</v>
       </c>
@@ -3879,7 +3923,9 @@
       <c r="AI44" s="8">
         <v>4</v>
       </c>
-      <c r="AJ44" s="33"/>
+      <c r="AJ44" s="33">
+        <v>46152</v>
+      </c>
       <c r="AK44" s="12" t="s">
         <v>38</v>
       </c>
@@ -3906,19 +3952,21 @@
       <c r="BA44" s="6"/>
     </row>
     <row r="45" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="49" t="s">
+      <c r="A45" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B45" s="49"/>
-      <c r="C45" s="49"/>
-      <c r="D45" s="49"/>
-      <c r="E45" s="49"/>
-      <c r="F45" s="49"/>
-      <c r="G45" s="49"/>
+      <c r="B45" s="42"/>
+      <c r="C45" s="42"/>
+      <c r="D45" s="42"/>
+      <c r="E45" s="42"/>
+      <c r="F45" s="42"/>
+      <c r="G45" s="42"/>
       <c r="M45" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="N45" s="33"/>
+      <c r="N45" s="33">
+        <v>46153</v>
+      </c>
       <c r="O45" s="12" t="s">
         <v>34</v>
       </c>
@@ -3940,7 +3988,9 @@
       <c r="AI45" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="AJ45" s="27"/>
+      <c r="AJ45" s="27">
+        <v>46154</v>
+      </c>
       <c r="AK45" s="12" t="s">
         <v>23</v>
       </c>
@@ -3950,21 +4000,23 @@
       </c>
       <c r="AN45" s="13"/>
       <c r="AO45" s="16"/>
-      <c r="AU45" s="49" t="s">
+      <c r="AU45" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AV45" s="49"/>
-      <c r="AW45" s="49"/>
-      <c r="AX45" s="49"/>
-      <c r="AY45" s="49"/>
-      <c r="AZ45" s="49"/>
-      <c r="BA45" s="49"/>
+      <c r="AV45" s="42"/>
+      <c r="AW45" s="42"/>
+      <c r="AX45" s="42"/>
+      <c r="AY45" s="42"/>
+      <c r="AZ45" s="42"/>
+      <c r="BA45" s="42"/>
     </row>
     <row r="46" spans="1:54" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="M46" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="N46" s="33"/>
+      <c r="N46" s="33">
+        <v>46155</v>
+      </c>
       <c r="O46" s="12" t="s">
         <v>26</v>
       </c>
@@ -3986,7 +4038,9 @@
       <c r="AI46" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="AJ46" s="27"/>
+      <c r="AJ46" s="27">
+        <v>46156</v>
+      </c>
       <c r="AK46" s="12" t="s">
         <v>38</v>
       </c>
@@ -4001,7 +4055,9 @@
       <c r="M47" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="N47" s="34"/>
+      <c r="N47" s="34">
+        <v>46158</v>
+      </c>
       <c r="O47" s="12" t="s">
         <v>34</v>
       </c>
@@ -4023,7 +4079,9 @@
       <c r="AI47" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="AJ47" s="28"/>
+      <c r="AJ47" s="28">
+        <v>46158</v>
+      </c>
       <c r="AK47" s="14" t="s">
         <v>23</v>
       </c>
@@ -4035,49 +4093,61 @@
       <c r="AO47" s="6"/>
     </row>
     <row r="48" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="M48" s="42" t="s">
+      <c r="M48" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="N48" s="43"/>
-      <c r="O48" s="43"/>
-      <c r="P48" s="43"/>
-      <c r="Q48" s="43"/>
-      <c r="R48" s="43"/>
-      <c r="S48" s="44"/>
-      <c r="X48" s="49" t="s">
+      <c r="N48" s="54"/>
+      <c r="O48" s="54"/>
+      <c r="P48" s="54"/>
+      <c r="Q48" s="54"/>
+      <c r="R48" s="54"/>
+      <c r="S48" s="55"/>
+      <c r="X48" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="Y48" s="49"/>
-      <c r="Z48" s="49"/>
-      <c r="AA48" s="49"/>
-      <c r="AB48" s="49"/>
-      <c r="AC48" s="49"/>
-      <c r="AD48" s="49"/>
-      <c r="AI48" s="49" t="s">
+      <c r="Y48" s="42"/>
+      <c r="Z48" s="42"/>
+      <c r="AA48" s="42"/>
+      <c r="AB48" s="42"/>
+      <c r="AC48" s="42"/>
+      <c r="AD48" s="42"/>
+      <c r="AI48" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AJ48" s="49"/>
-      <c r="AK48" s="49"/>
-      <c r="AL48" s="49"/>
-      <c r="AM48" s="49"/>
-      <c r="AN48" s="49"/>
-      <c r="AO48" s="49"/>
+      <c r="AJ48" s="42"/>
+      <c r="AK48" s="42"/>
+      <c r="AL48" s="42"/>
+      <c r="AM48" s="42"/>
+      <c r="AN48" s="42"/>
+      <c r="AO48" s="42"/>
     </row>
     <row r="49" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="AU45:BA45"/>
-    <mergeCell ref="AF28:AL28"/>
-    <mergeCell ref="AF37:AL37"/>
-    <mergeCell ref="AQ30:AS30"/>
-    <mergeCell ref="AQ41:AS41"/>
-    <mergeCell ref="AU34:BA34"/>
-    <mergeCell ref="AU36:BA36"/>
-    <mergeCell ref="AU2:BA2"/>
-    <mergeCell ref="AU3:BA3"/>
-    <mergeCell ref="AU12:BA12"/>
-    <mergeCell ref="AU14:BA14"/>
-    <mergeCell ref="AU23:BA23"/>
+    <mergeCell ref="M48:S48"/>
+    <mergeCell ref="M39:S39"/>
+    <mergeCell ref="P37:V37"/>
+    <mergeCell ref="P28:V28"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A1:U1"/>
+    <mergeCell ref="O26:W26"/>
+    <mergeCell ref="I41:K41"/>
+    <mergeCell ref="L14:N14"/>
+    <mergeCell ref="L36:N36"/>
+    <mergeCell ref="M2:R2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="M4:S4"/>
+    <mergeCell ref="M13:S13"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="A25:G25"/>
     <mergeCell ref="X37:AD37"/>
     <mergeCell ref="AE26:AM26"/>
     <mergeCell ref="Z1:AB1"/>
@@ -4094,30 +4164,18 @@
     <mergeCell ref="AN36:AP36"/>
     <mergeCell ref="AQ8:AS8"/>
     <mergeCell ref="AQ19:AS19"/>
-    <mergeCell ref="A1:U1"/>
-    <mergeCell ref="O26:W26"/>
-    <mergeCell ref="I41:K41"/>
-    <mergeCell ref="L14:N14"/>
-    <mergeCell ref="L36:N36"/>
-    <mergeCell ref="M2:R2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="M4:S4"/>
-    <mergeCell ref="M13:S13"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A23:G23"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="M48:S48"/>
-    <mergeCell ref="M39:S39"/>
-    <mergeCell ref="P37:V37"/>
-    <mergeCell ref="P28:V28"/>
-    <mergeCell ref="A36:G36"/>
-    <mergeCell ref="A45:G45"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="AU2:BA2"/>
+    <mergeCell ref="AU3:BA3"/>
+    <mergeCell ref="AU12:BA12"/>
+    <mergeCell ref="AU14:BA14"/>
+    <mergeCell ref="AU23:BA23"/>
+    <mergeCell ref="AU45:BA45"/>
+    <mergeCell ref="AF28:AL28"/>
+    <mergeCell ref="AF37:AL37"/>
+    <mergeCell ref="AQ30:AS30"/>
+    <mergeCell ref="AQ41:AS41"/>
+    <mergeCell ref="AU34:BA34"/>
+    <mergeCell ref="AU36:BA36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/2025_2026/Playoffs/Brackets.xlsx
+++ b/2025_2026/Playoffs/Brackets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\NHLStats\2025_2026\Playoffs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBDB60BE-EEBB-4695-9996-2BAF6C553BDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECDE848D-4AF9-497E-8296-236E347C6533}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="87">
   <si>
     <t>Eastern Conference Playoff Teams</t>
   </si>
@@ -281,6 +281,12 @@
   </si>
   <si>
     <t>Sabres Win Series 4-2</t>
+  </si>
+  <si>
+    <t>Canadiens Win Series 4-3</t>
+  </si>
+  <si>
+    <t>Avalanche Leads 1-0</t>
   </si>
 </sst>
 </file>
@@ -659,18 +665,45 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -683,40 +716,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1086,18 +1092,18 @@
     </row>
     <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="11" spans="1:7" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="59" t="s">
+      <c r="A11" s="61" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="59"/>
-      <c r="C11" s="59" t="s">
+      <c r="B11" s="61"/>
+      <c r="C11" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="59"/>
-      <c r="E11" s="59" t="s">
+      <c r="D11" s="61"/>
+      <c r="E11" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="59"/>
+      <c r="F11" s="61"/>
       <c r="G11" s="4" t="s">
         <v>18</v>
       </c>
@@ -1126,18 +1132,18 @@
       </c>
     </row>
     <row r="13" spans="1:7" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="60" t="s">
+      <c r="A13" s="59" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="61"/>
-      <c r="C13" s="60" t="s">
+      <c r="B13" s="60"/>
+      <c r="C13" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="D13" s="61"/>
-      <c r="E13" s="60" t="s">
+      <c r="D13" s="60"/>
+      <c r="E13" s="59" t="s">
         <v>17</v>
       </c>
-      <c r="F13" s="61"/>
+      <c r="F13" s="60"/>
       <c r="G13" s="5"/>
     </row>
     <row r="14" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1164,6 +1170,9 @@
       <c r="B15" s="6" t="s">
         <v>30</v>
       </c>
+      <c r="C15" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="D15" s="6" t="s">
         <v>31</v>
       </c>
@@ -1171,14 +1180,14 @@
       <c r="F15" s="6"/>
     </row>
     <row r="16" spans="1:7" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="60" t="s">
+      <c r="A16" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="61"/>
-      <c r="C16" s="60" t="s">
+      <c r="B16" s="60"/>
+      <c r="C16" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="61"/>
+      <c r="D16" s="60"/>
     </row>
     <row r="17" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
@@ -1209,10 +1218,10 @@
       </c>
     </row>
     <row r="19" spans="1:4" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="60" t="s">
+      <c r="A19" s="59" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="61"/>
+      <c r="B19" s="60"/>
     </row>
     <row r="20" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
@@ -1231,10 +1240,10 @@
       </c>
     </row>
     <row r="22" spans="1:4" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="60" t="s">
+      <c r="A22" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="61"/>
+      <c r="B22" s="60"/>
     </row>
     <row r="23" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
@@ -1319,16 +1328,16 @@
     <sortCondition ref="B2:B9"/>
   </sortState>
   <mergeCells count="10">
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A16:B16"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A16:B16"/>
   </mergeCells>
   <dataValidations count="16">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C14" xr:uid="{2C3D9587-ABAE-4E3F-8B22-396DF812BF02}">
@@ -1432,124 +1441,124 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:54" ht="27.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
-      <c r="I1" s="51"/>
-      <c r="J1" s="51"/>
-      <c r="K1" s="51"/>
-      <c r="L1" s="51"/>
-      <c r="M1" s="51"/>
-      <c r="N1" s="51"/>
-      <c r="O1" s="51"/>
-      <c r="P1" s="51"/>
-      <c r="Q1" s="51"/>
-      <c r="R1" s="51"/>
-      <c r="S1" s="51"/>
-      <c r="T1" s="51"/>
-      <c r="U1" s="52"/>
-      <c r="Z1" s="50" t="s">
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="52"/>
+      <c r="M1" s="52"/>
+      <c r="N1" s="52"/>
+      <c r="O1" s="52"/>
+      <c r="P1" s="52"/>
+      <c r="Q1" s="52"/>
+      <c r="R1" s="52"/>
+      <c r="S1" s="52"/>
+      <c r="T1" s="52"/>
+      <c r="U1" s="53"/>
+      <c r="Z1" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="AA1" s="51"/>
-      <c r="AB1" s="52"/>
-      <c r="AF1" s="50" t="s">
+      <c r="AA1" s="52"/>
+      <c r="AB1" s="53"/>
+      <c r="AF1" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="AG1" s="51"/>
-      <c r="AH1" s="51"/>
-      <c r="AI1" s="51"/>
-      <c r="AJ1" s="51"/>
-      <c r="AK1" s="51"/>
-      <c r="AL1" s="51"/>
-      <c r="AM1" s="51"/>
-      <c r="AN1" s="51"/>
-      <c r="AO1" s="51"/>
-      <c r="AP1" s="51"/>
-      <c r="AQ1" s="51"/>
-      <c r="AR1" s="51"/>
-      <c r="AS1" s="51"/>
-      <c r="AT1" s="51"/>
-      <c r="AU1" s="51"/>
-      <c r="AV1" s="51"/>
-      <c r="AW1" s="51"/>
-      <c r="AX1" s="51"/>
-      <c r="AY1" s="51"/>
-      <c r="AZ1" s="51"/>
-      <c r="BA1" s="52"/>
+      <c r="AG1" s="52"/>
+      <c r="AH1" s="52"/>
+      <c r="AI1" s="52"/>
+      <c r="AJ1" s="52"/>
+      <c r="AK1" s="52"/>
+      <c r="AL1" s="52"/>
+      <c r="AM1" s="52"/>
+      <c r="AN1" s="52"/>
+      <c r="AO1" s="52"/>
+      <c r="AP1" s="52"/>
+      <c r="AQ1" s="52"/>
+      <c r="AR1" s="52"/>
+      <c r="AS1" s="52"/>
+      <c r="AT1" s="52"/>
+      <c r="AU1" s="52"/>
+      <c r="AV1" s="52"/>
+      <c r="AW1" s="52"/>
+      <c r="AX1" s="52"/>
+      <c r="AY1" s="52"/>
+      <c r="AZ1" s="52"/>
+      <c r="BA1" s="53"/>
     </row>
     <row r="2" spans="1:54" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="48"/>
-      <c r="M2" s="46" t="s">
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="57"/>
+      <c r="M2" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="47"/>
-      <c r="O2" s="47"/>
-      <c r="P2" s="47"/>
-      <c r="Q2" s="47"/>
-      <c r="R2" s="48"/>
-      <c r="AI2" s="46" t="s">
+      <c r="N2" s="56"/>
+      <c r="O2" s="56"/>
+      <c r="P2" s="56"/>
+      <c r="Q2" s="56"/>
+      <c r="R2" s="57"/>
+      <c r="AI2" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="AJ2" s="47"/>
-      <c r="AK2" s="47"/>
-      <c r="AL2" s="47"/>
-      <c r="AM2" s="47"/>
-      <c r="AN2" s="47"/>
-      <c r="AO2" s="48"/>
-      <c r="AU2" s="46" t="s">
+      <c r="AJ2" s="56"/>
+      <c r="AK2" s="56"/>
+      <c r="AL2" s="56"/>
+      <c r="AM2" s="56"/>
+      <c r="AN2" s="56"/>
+      <c r="AO2" s="57"/>
+      <c r="AU2" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="AV2" s="47"/>
-      <c r="AW2" s="47"/>
-      <c r="AX2" s="47"/>
-      <c r="AY2" s="47"/>
-      <c r="AZ2" s="47"/>
-      <c r="BA2" s="48"/>
+      <c r="AV2" s="56"/>
+      <c r="AW2" s="56"/>
+      <c r="AX2" s="56"/>
+      <c r="AY2" s="56"/>
+      <c r="AZ2" s="56"/>
+      <c r="BA2" s="57"/>
     </row>
     <row r="3" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="42" t="s">
+      <c r="A3" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="42"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="42"/>
-      <c r="AI3" s="53" t="s">
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="AI3" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="AJ3" s="54"/>
-      <c r="AK3" s="54"/>
-      <c r="AL3" s="54"/>
-      <c r="AM3" s="54"/>
-      <c r="AN3" s="54"/>
-      <c r="AO3" s="55"/>
-      <c r="AU3" s="42" t="s">
+      <c r="AJ3" s="43"/>
+      <c r="AK3" s="43"/>
+      <c r="AL3" s="43"/>
+      <c r="AM3" s="43"/>
+      <c r="AN3" s="43"/>
+      <c r="AO3" s="44"/>
+      <c r="AU3" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="AV3" s="42"/>
-      <c r="AW3" s="42"/>
-      <c r="AX3" s="42"/>
-      <c r="AY3" s="42"/>
-      <c r="AZ3" s="42"/>
-      <c r="BA3" s="42"/>
+      <c r="AV3" s="49"/>
+      <c r="AW3" s="49"/>
+      <c r="AX3" s="49"/>
+      <c r="AY3" s="49"/>
+      <c r="AZ3" s="49"/>
+      <c r="BA3" s="49"/>
     </row>
     <row r="4" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
@@ -1573,15 +1582,15 @@
       <c r="G4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="53" t="s">
+      <c r="M4" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="N4" s="54"/>
-      <c r="O4" s="54"/>
-      <c r="P4" s="54"/>
-      <c r="Q4" s="54"/>
-      <c r="R4" s="54"/>
-      <c r="S4" s="55"/>
+      <c r="N4" s="43"/>
+      <c r="O4" s="43"/>
+      <c r="P4" s="43"/>
+      <c r="Q4" s="43"/>
+      <c r="R4" s="43"/>
+      <c r="S4" s="44"/>
       <c r="AI4" s="3" t="s">
         <v>2</v>
       </c>
@@ -1677,12 +1686,18 @@
       <c r="AK5" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="AL5" s="11"/>
+      <c r="AL5" s="11">
+        <v>6</v>
+      </c>
       <c r="AM5" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="AN5" s="11"/>
-      <c r="AO5" s="5"/>
+      <c r="AN5" s="11">
+        <v>9</v>
+      </c>
+      <c r="AO5" s="5" t="s">
+        <v>86</v>
+      </c>
       <c r="AU5" s="7">
         <v>1</v>
       </c>
@@ -1733,7 +1748,9 @@
       <c r="N6" s="29">
         <v>46148</v>
       </c>
-      <c r="O6" s="10"/>
+      <c r="O6" s="10" t="s">
+        <v>32</v>
+      </c>
       <c r="P6" s="11"/>
       <c r="Q6" s="10" t="s">
         <v>25</v>
@@ -1808,7 +1825,9 @@
       <c r="N7" s="33">
         <v>46150</v>
       </c>
-      <c r="O7" s="12"/>
+      <c r="O7" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="P7" s="13"/>
       <c r="Q7" s="12" t="s">
         <v>25</v>
@@ -1874,11 +1893,11 @@
       <c r="G8" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="I8" s="43" t="s">
+      <c r="I8" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="J8" s="43"/>
-      <c r="K8" s="43"/>
+      <c r="J8" s="50"/>
+      <c r="K8" s="50"/>
       <c r="M8" s="8">
         <v>3</v>
       </c>
@@ -1889,7 +1908,9 @@
         <v>25</v>
       </c>
       <c r="P8" s="31"/>
-      <c r="Q8" s="30"/>
+      <c r="Q8" s="30" t="s">
+        <v>32</v>
+      </c>
       <c r="R8" s="31"/>
       <c r="S8" s="16"/>
       <c r="AI8" s="8">
@@ -1907,11 +1928,11 @@
       </c>
       <c r="AN8" s="31"/>
       <c r="AO8" s="16"/>
-      <c r="AQ8" s="43" t="s">
+      <c r="AQ8" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="AR8" s="43"/>
-      <c r="AS8" s="43"/>
+      <c r="AR8" s="50"/>
+      <c r="AS8" s="50"/>
       <c r="AU8" s="38">
         <v>4</v>
       </c>
@@ -1970,7 +1991,9 @@
         <v>25</v>
       </c>
       <c r="P9" s="13"/>
-      <c r="Q9" s="12"/>
+      <c r="Q9" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="R9" s="13"/>
       <c r="S9" s="16"/>
       <c r="AI9" s="8" t="s">
@@ -2036,7 +2059,9 @@
       <c r="N10" s="33">
         <v>46156</v>
       </c>
-      <c r="O10" s="12"/>
+      <c r="O10" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="P10" s="13"/>
       <c r="Q10" s="12" t="s">
         <v>25</v>
@@ -2098,9 +2123,13 @@
       <c r="N11" s="33">
         <v>46158</v>
       </c>
-      <c r="O11" s="12"/>
+      <c r="O11" s="12" t="s">
+        <v>25</v>
+      </c>
       <c r="P11" s="13"/>
-      <c r="Q11" s="12"/>
+      <c r="Q11" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="R11" s="13"/>
       <c r="S11" s="16"/>
       <c r="AI11" s="9" t="s">
@@ -2136,15 +2165,15 @@
       <c r="BA11" s="6"/>
     </row>
     <row r="12" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="42" t="s">
+      <c r="A12" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="42"/>
-      <c r="C12" s="42"/>
-      <c r="D12" s="42"/>
-      <c r="E12" s="42"/>
-      <c r="F12" s="42"/>
-      <c r="G12" s="42"/>
+      <c r="B12" s="49"/>
+      <c r="C12" s="49"/>
+      <c r="D12" s="49"/>
+      <c r="E12" s="49"/>
+      <c r="F12" s="49"/>
+      <c r="G12" s="49"/>
       <c r="L12" s="12"/>
       <c r="M12" s="8" t="s">
         <v>12</v>
@@ -2152,72 +2181,74 @@
       <c r="N12" s="34">
         <v>46160</v>
       </c>
-      <c r="O12" s="12"/>
+      <c r="O12" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="P12" s="13"/>
       <c r="Q12" s="12" t="s">
         <v>25</v>
       </c>
       <c r="R12" s="13"/>
       <c r="S12" s="16"/>
-      <c r="AI12" s="42" t="s">
+      <c r="AI12" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AJ12" s="42"/>
-      <c r="AK12" s="42"/>
-      <c r="AL12" s="42"/>
-      <c r="AM12" s="42"/>
-      <c r="AN12" s="42"/>
-      <c r="AO12" s="42"/>
+      <c r="AJ12" s="49"/>
+      <c r="AK12" s="49"/>
+      <c r="AL12" s="49"/>
+      <c r="AM12" s="49"/>
+      <c r="AN12" s="49"/>
+      <c r="AO12" s="49"/>
       <c r="AQ12" s="12"/>
-      <c r="AU12" s="42" t="s">
+      <c r="AU12" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AV12" s="42"/>
-      <c r="AW12" s="42"/>
-      <c r="AX12" s="42"/>
-      <c r="AY12" s="42"/>
-      <c r="AZ12" s="42"/>
-      <c r="BA12" s="42"/>
+      <c r="AV12" s="49"/>
+      <c r="AW12" s="49"/>
+      <c r="AX12" s="49"/>
+      <c r="AY12" s="49"/>
+      <c r="AZ12" s="49"/>
+      <c r="BA12" s="49"/>
     </row>
     <row r="13" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L13" s="12"/>
-      <c r="M13" s="53" t="s">
+      <c r="M13" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="N13" s="54"/>
-      <c r="O13" s="54"/>
-      <c r="P13" s="54"/>
-      <c r="Q13" s="54"/>
-      <c r="R13" s="54"/>
-      <c r="S13" s="55"/>
+      <c r="N13" s="43"/>
+      <c r="O13" s="43"/>
+      <c r="P13" s="43"/>
+      <c r="Q13" s="43"/>
+      <c r="R13" s="43"/>
+      <c r="S13" s="44"/>
       <c r="AQ13" s="12"/>
     </row>
     <row r="14" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="45" t="s">
+      <c r="A14" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="45"/>
-      <c r="C14" s="45"/>
-      <c r="D14" s="45"/>
-      <c r="E14" s="45"/>
-      <c r="F14" s="45"/>
-      <c r="G14" s="45"/>
-      <c r="L14" s="44"/>
-      <c r="M14" s="43"/>
-      <c r="N14" s="43"/>
-      <c r="AN14" s="43"/>
-      <c r="AO14" s="43"/>
-      <c r="AP14" s="43"/>
+      <c r="B14" s="48"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="48"/>
+      <c r="E14" s="48"/>
+      <c r="F14" s="48"/>
+      <c r="G14" s="48"/>
+      <c r="L14" s="54"/>
+      <c r="M14" s="50"/>
+      <c r="N14" s="50"/>
+      <c r="AN14" s="50"/>
+      <c r="AO14" s="50"/>
+      <c r="AP14" s="50"/>
       <c r="AQ14" s="12"/>
-      <c r="AU14" s="45" t="s">
+      <c r="AU14" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="AV14" s="45"/>
-      <c r="AW14" s="45"/>
-      <c r="AX14" s="45"/>
-      <c r="AY14" s="45"/>
-      <c r="AZ14" s="45"/>
-      <c r="BA14" s="45"/>
+      <c r="AV14" s="48"/>
+      <c r="AW14" s="48"/>
+      <c r="AX14" s="48"/>
+      <c r="AY14" s="48"/>
+      <c r="AZ14" s="48"/>
+      <c r="BA14" s="48"/>
     </row>
     <row r="15" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
@@ -2445,17 +2476,19 @@
       <c r="G19" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="I19" s="43"/>
-      <c r="J19" s="43"/>
-      <c r="K19" s="43"/>
+      <c r="I19" s="50" t="s">
+        <v>32</v>
+      </c>
+      <c r="J19" s="50"/>
+      <c r="K19" s="50"/>
       <c r="L19" s="12"/>
       <c r="O19" s="12"/>
       <c r="AN19" s="12"/>
-      <c r="AQ19" s="44" t="s">
+      <c r="AQ19" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="AR19" s="43"/>
-      <c r="AS19" s="43"/>
+      <c r="AR19" s="50"/>
+      <c r="AS19" s="50"/>
       <c r="AU19" s="38">
         <v>4</v>
       </c>
@@ -2586,12 +2619,18 @@
       <c r="C22" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="D22" s="15"/>
+      <c r="D22" s="15">
+        <v>2</v>
+      </c>
       <c r="E22" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="F22" s="15"/>
-      <c r="G22" s="6"/>
+      <c r="F22" s="15">
+        <v>1</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>85</v>
+      </c>
       <c r="O22" s="12"/>
       <c r="AN22" s="12"/>
       <c r="AU22" s="9" t="s">
@@ -2611,52 +2650,52 @@
       <c r="BA22" s="6"/>
     </row>
     <row r="23" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="42" t="s">
+      <c r="A23" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="B23" s="42"/>
-      <c r="C23" s="42"/>
-      <c r="D23" s="42"/>
-      <c r="E23" s="42"/>
-      <c r="F23" s="42"/>
-      <c r="G23" s="42"/>
+      <c r="B23" s="49"/>
+      <c r="C23" s="49"/>
+      <c r="D23" s="49"/>
+      <c r="E23" s="49"/>
+      <c r="F23" s="49"/>
+      <c r="G23" s="49"/>
       <c r="O23" s="12"/>
       <c r="AN23" s="12"/>
-      <c r="AU23" s="42" t="s">
+      <c r="AU23" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AV23" s="42"/>
-      <c r="AW23" s="42"/>
-      <c r="AX23" s="42"/>
-      <c r="AY23" s="42"/>
-      <c r="AZ23" s="42"/>
-      <c r="BA23" s="42"/>
+      <c r="AV23" s="49"/>
+      <c r="AW23" s="49"/>
+      <c r="AX23" s="49"/>
+      <c r="AY23" s="49"/>
+      <c r="AZ23" s="49"/>
+      <c r="BA23" s="49"/>
     </row>
     <row r="24" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="O24" s="12"/>
       <c r="AN24" s="12"/>
     </row>
     <row r="25" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="42" t="s">
+      <c r="A25" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="42"/>
-      <c r="C25" s="42"/>
-      <c r="D25" s="42"/>
-      <c r="E25" s="42"/>
-      <c r="F25" s="42"/>
-      <c r="G25" s="42"/>
+      <c r="B25" s="49"/>
+      <c r="C25" s="49"/>
+      <c r="D25" s="49"/>
+      <c r="E25" s="49"/>
+      <c r="F25" s="49"/>
+      <c r="G25" s="49"/>
       <c r="O25" s="12"/>
       <c r="AN25" s="12"/>
-      <c r="AU25" s="42" t="s">
+      <c r="AU25" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="AV25" s="42"/>
-      <c r="AW25" s="42"/>
-      <c r="AX25" s="42"/>
-      <c r="AY25" s="42"/>
-      <c r="AZ25" s="42"/>
-      <c r="BA25" s="42"/>
+      <c r="AV25" s="49"/>
+      <c r="AW25" s="49"/>
+      <c r="AX25" s="49"/>
+      <c r="AY25" s="49"/>
+      <c r="AZ25" s="49"/>
+      <c r="BA25" s="49"/>
     </row>
     <row r="26" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="20" t="s">
@@ -2680,24 +2719,24 @@
       <c r="G26" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="O26" s="44"/>
-      <c r="P26" s="43"/>
-      <c r="Q26" s="43"/>
-      <c r="R26" s="43"/>
-      <c r="S26" s="43"/>
-      <c r="T26" s="43"/>
-      <c r="U26" s="43"/>
-      <c r="V26" s="43"/>
-      <c r="W26" s="43"/>
-      <c r="AE26" s="43"/>
-      <c r="AF26" s="43"/>
-      <c r="AG26" s="43"/>
-      <c r="AH26" s="43"/>
-      <c r="AI26" s="43"/>
-      <c r="AJ26" s="43"/>
-      <c r="AK26" s="43"/>
-      <c r="AL26" s="43"/>
-      <c r="AM26" s="49"/>
+      <c r="O26" s="54"/>
+      <c r="P26" s="50"/>
+      <c r="Q26" s="50"/>
+      <c r="R26" s="50"/>
+      <c r="S26" s="50"/>
+      <c r="T26" s="50"/>
+      <c r="U26" s="50"/>
+      <c r="V26" s="50"/>
+      <c r="W26" s="50"/>
+      <c r="AE26" s="50"/>
+      <c r="AF26" s="50"/>
+      <c r="AG26" s="50"/>
+      <c r="AH26" s="50"/>
+      <c r="AI26" s="50"/>
+      <c r="AJ26" s="50"/>
+      <c r="AK26" s="50"/>
+      <c r="AL26" s="50"/>
+      <c r="AM26" s="58"/>
       <c r="AU26" s="20" t="s">
         <v>2</v>
       </c>
@@ -2794,26 +2833,26 @@
         <v>54</v>
       </c>
       <c r="O28" s="12"/>
-      <c r="P28" s="53" t="s">
+      <c r="P28" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="Q28" s="54"/>
-      <c r="R28" s="54"/>
-      <c r="S28" s="54"/>
-      <c r="T28" s="54"/>
-      <c r="U28" s="54"/>
-      <c r="V28" s="55"/>
+      <c r="Q28" s="43"/>
+      <c r="R28" s="43"/>
+      <c r="S28" s="43"/>
+      <c r="T28" s="43"/>
+      <c r="U28" s="43"/>
+      <c r="V28" s="44"/>
       <c r="X28" s="12"/>
       <c r="AD28" s="13"/>
-      <c r="AF28" s="42" t="s">
+      <c r="AF28" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="AG28" s="42"/>
-      <c r="AH28" s="42"/>
-      <c r="AI28" s="42"/>
-      <c r="AJ28" s="42"/>
-      <c r="AK28" s="42"/>
-      <c r="AL28" s="42"/>
+      <c r="AG28" s="49"/>
+      <c r="AH28" s="49"/>
+      <c r="AI28" s="49"/>
+      <c r="AJ28" s="49"/>
+      <c r="AK28" s="49"/>
+      <c r="AL28" s="49"/>
       <c r="AN28" s="12"/>
       <c r="AU28" s="8">
         <v>2</v>
@@ -2949,11 +2988,11 @@
       <c r="G30" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="I30" s="43" t="s">
+      <c r="I30" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="J30" s="43"/>
-      <c r="K30" s="43"/>
+      <c r="J30" s="50"/>
+      <c r="K30" s="50"/>
       <c r="O30" s="12"/>
       <c r="P30" s="7">
         <v>1</v>
@@ -2976,11 +3015,11 @@
       <c r="AK30" s="24"/>
       <c r="AL30" s="25"/>
       <c r="AN30" s="12"/>
-      <c r="AQ30" s="43" t="s">
+      <c r="AQ30" s="50" t="s">
         <v>38</v>
       </c>
-      <c r="AR30" s="43"/>
-      <c r="AS30" s="43"/>
+      <c r="AR30" s="50"/>
+      <c r="AS30" s="50"/>
       <c r="AU30" s="38">
         <v>4</v>
       </c>
@@ -3192,15 +3231,15 @@
       <c r="BA33" s="6"/>
     </row>
     <row r="34" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="42" t="s">
+      <c r="A34" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="B34" s="42"/>
-      <c r="C34" s="42"/>
-      <c r="D34" s="42"/>
-      <c r="E34" s="42"/>
-      <c r="F34" s="42"/>
-      <c r="G34" s="42"/>
+      <c r="B34" s="49"/>
+      <c r="C34" s="49"/>
+      <c r="D34" s="49"/>
+      <c r="E34" s="49"/>
+      <c r="F34" s="49"/>
+      <c r="G34" s="49"/>
       <c r="L34" s="12"/>
       <c r="O34" s="12"/>
       <c r="P34" s="8" t="s">
@@ -3225,15 +3264,15 @@
       <c r="AL34" s="16"/>
       <c r="AN34" s="12"/>
       <c r="AQ34" s="12"/>
-      <c r="AU34" s="42" t="s">
+      <c r="AU34" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AV34" s="42"/>
-      <c r="AW34" s="42"/>
-      <c r="AX34" s="42"/>
-      <c r="AY34" s="42"/>
-      <c r="AZ34" s="42"/>
-      <c r="BA34" s="42"/>
+      <c r="AV34" s="49"/>
+      <c r="AW34" s="49"/>
+      <c r="AX34" s="49"/>
+      <c r="AY34" s="49"/>
+      <c r="AZ34" s="49"/>
+      <c r="BA34" s="49"/>
     </row>
     <row r="35" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L35" s="12"/>
@@ -3262,18 +3301,18 @@
       <c r="AQ35" s="12"/>
     </row>
     <row r="36" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="45" t="s">
+      <c r="A36" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="B36" s="45"/>
-      <c r="C36" s="45"/>
-      <c r="D36" s="45"/>
-      <c r="E36" s="45"/>
-      <c r="F36" s="45"/>
-      <c r="G36" s="45"/>
-      <c r="L36" s="44"/>
-      <c r="M36" s="43"/>
-      <c r="N36" s="43"/>
+      <c r="B36" s="48"/>
+      <c r="C36" s="48"/>
+      <c r="D36" s="48"/>
+      <c r="E36" s="48"/>
+      <c r="F36" s="48"/>
+      <c r="G36" s="48"/>
+      <c r="L36" s="54"/>
+      <c r="M36" s="50"/>
+      <c r="N36" s="50"/>
       <c r="O36" s="12"/>
       <c r="P36" s="8" t="s">
         <v>12</v>
@@ -3295,19 +3334,19 @@
       <c r="AJ36" s="35"/>
       <c r="AK36" s="36"/>
       <c r="AL36" s="37"/>
-      <c r="AN36" s="44"/>
-      <c r="AO36" s="43"/>
-      <c r="AP36" s="43"/>
+      <c r="AN36" s="54"/>
+      <c r="AO36" s="50"/>
+      <c r="AP36" s="50"/>
       <c r="AQ36" s="12"/>
-      <c r="AU36" s="45" t="s">
+      <c r="AU36" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="AV36" s="45"/>
-      <c r="AW36" s="45"/>
-      <c r="AX36" s="45"/>
-      <c r="AY36" s="45"/>
-      <c r="AZ36" s="45"/>
-      <c r="BA36" s="45"/>
+      <c r="AV36" s="48"/>
+      <c r="AW36" s="48"/>
+      <c r="AX36" s="48"/>
+      <c r="AY36" s="48"/>
+      <c r="AZ36" s="48"/>
+      <c r="BA36" s="48"/>
     </row>
     <row r="37" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37" s="20" t="s">
@@ -3332,31 +3371,31 @@
         <v>9</v>
       </c>
       <c r="L37" s="12"/>
-      <c r="P37" s="56" t="s">
+      <c r="P37" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="Q37" s="57"/>
-      <c r="R37" s="57"/>
-      <c r="S37" s="57"/>
-      <c r="T37" s="57"/>
-      <c r="U37" s="57"/>
-      <c r="V37" s="58"/>
-      <c r="X37" s="44"/>
-      <c r="Y37" s="43"/>
-      <c r="Z37" s="43"/>
-      <c r="AA37" s="43"/>
-      <c r="AB37" s="43"/>
-      <c r="AC37" s="43"/>
-      <c r="AD37" s="49"/>
-      <c r="AF37" s="42" t="s">
+      <c r="Q37" s="46"/>
+      <c r="R37" s="46"/>
+      <c r="S37" s="46"/>
+      <c r="T37" s="46"/>
+      <c r="U37" s="46"/>
+      <c r="V37" s="47"/>
+      <c r="X37" s="54"/>
+      <c r="Y37" s="50"/>
+      <c r="Z37" s="50"/>
+      <c r="AA37" s="50"/>
+      <c r="AB37" s="50"/>
+      <c r="AC37" s="50"/>
+      <c r="AD37" s="58"/>
+      <c r="AF37" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AG37" s="42"/>
-      <c r="AH37" s="42"/>
-      <c r="AI37" s="42"/>
-      <c r="AJ37" s="42"/>
-      <c r="AK37" s="42"/>
-      <c r="AL37" s="42"/>
+      <c r="AG37" s="49"/>
+      <c r="AH37" s="49"/>
+      <c r="AI37" s="49"/>
+      <c r="AJ37" s="49"/>
+      <c r="AK37" s="49"/>
+      <c r="AL37" s="49"/>
       <c r="AQ37" s="12"/>
       <c r="AU37" s="3" t="s">
         <v>2</v>
@@ -3449,33 +3488,33 @@
         <v>53</v>
       </c>
       <c r="L39" s="12"/>
-      <c r="M39" s="53" t="s">
+      <c r="M39" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="N39" s="54"/>
-      <c r="O39" s="54"/>
-      <c r="P39" s="54"/>
-      <c r="Q39" s="54"/>
-      <c r="R39" s="54"/>
-      <c r="S39" s="55"/>
-      <c r="X39" s="42" t="s">
+      <c r="N39" s="43"/>
+      <c r="O39" s="43"/>
+      <c r="P39" s="43"/>
+      <c r="Q39" s="43"/>
+      <c r="R39" s="43"/>
+      <c r="S39" s="44"/>
+      <c r="X39" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="Y39" s="42"/>
-      <c r="Z39" s="42"/>
-      <c r="AA39" s="42"/>
-      <c r="AB39" s="42"/>
-      <c r="AC39" s="42"/>
-      <c r="AD39" s="42"/>
-      <c r="AI39" s="53" t="s">
+      <c r="Y39" s="49"/>
+      <c r="Z39" s="49"/>
+      <c r="AA39" s="49"/>
+      <c r="AB39" s="49"/>
+      <c r="AC39" s="49"/>
+      <c r="AD39" s="49"/>
+      <c r="AI39" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="AJ39" s="54"/>
-      <c r="AK39" s="54"/>
-      <c r="AL39" s="54"/>
-      <c r="AM39" s="54"/>
-      <c r="AN39" s="54"/>
-      <c r="AO39" s="55"/>
+      <c r="AJ39" s="43"/>
+      <c r="AK39" s="43"/>
+      <c r="AL39" s="43"/>
+      <c r="AM39" s="43"/>
+      <c r="AN39" s="43"/>
+      <c r="AO39" s="44"/>
       <c r="AQ39" s="12"/>
       <c r="AU39" s="8">
         <v>2</v>
@@ -3630,11 +3669,11 @@
       <c r="G41" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="I41" s="43" t="s">
+      <c r="I41" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="J41" s="43"/>
-      <c r="K41" s="43"/>
+      <c r="J41" s="50"/>
+      <c r="K41" s="50"/>
       <c r="L41" s="12"/>
       <c r="M41" s="7">
         <v>1</v>
@@ -3681,11 +3720,11 @@
       </c>
       <c r="AN41" s="24"/>
       <c r="AO41" s="25"/>
-      <c r="AQ41" s="44" t="s">
+      <c r="AQ41" s="54" t="s">
         <v>23</v>
       </c>
-      <c r="AR41" s="43"/>
-      <c r="AS41" s="43"/>
+      <c r="AR41" s="50"/>
+      <c r="AS41" s="50"/>
       <c r="AU41" s="38">
         <v>4</v>
       </c>
@@ -3952,15 +3991,15 @@
       <c r="BA44" s="6"/>
     </row>
     <row r="45" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="42" t="s">
+      <c r="A45" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="B45" s="42"/>
-      <c r="C45" s="42"/>
-      <c r="D45" s="42"/>
-      <c r="E45" s="42"/>
-      <c r="F45" s="42"/>
-      <c r="G45" s="42"/>
+      <c r="B45" s="49"/>
+      <c r="C45" s="49"/>
+      <c r="D45" s="49"/>
+      <c r="E45" s="49"/>
+      <c r="F45" s="49"/>
+      <c r="G45" s="49"/>
       <c r="M45" s="8" t="s">
         <v>11</v>
       </c>
@@ -4000,15 +4039,15 @@
       </c>
       <c r="AN45" s="13"/>
       <c r="AO45" s="16"/>
-      <c r="AU45" s="42" t="s">
+      <c r="AU45" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AV45" s="42"/>
-      <c r="AW45" s="42"/>
-      <c r="AX45" s="42"/>
-      <c r="AY45" s="42"/>
-      <c r="AZ45" s="42"/>
-      <c r="BA45" s="42"/>
+      <c r="AV45" s="49"/>
+      <c r="AW45" s="49"/>
+      <c r="AX45" s="49"/>
+      <c r="AY45" s="49"/>
+      <c r="AZ45" s="49"/>
+      <c r="BA45" s="49"/>
     </row>
     <row r="46" spans="1:54" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="M46" s="8" t="s">
@@ -4093,45 +4132,65 @@
       <c r="AO47" s="6"/>
     </row>
     <row r="48" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="M48" s="53" t="s">
+      <c r="M48" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="N48" s="54"/>
-      <c r="O48" s="54"/>
-      <c r="P48" s="54"/>
-      <c r="Q48" s="54"/>
-      <c r="R48" s="54"/>
-      <c r="S48" s="55"/>
-      <c r="X48" s="42" t="s">
+      <c r="N48" s="43"/>
+      <c r="O48" s="43"/>
+      <c r="P48" s="43"/>
+      <c r="Q48" s="43"/>
+      <c r="R48" s="43"/>
+      <c r="S48" s="44"/>
+      <c r="X48" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="Y48" s="42"/>
-      <c r="Z48" s="42"/>
-      <c r="AA48" s="42"/>
-      <c r="AB48" s="42"/>
-      <c r="AC48" s="42"/>
-      <c r="AD48" s="42"/>
-      <c r="AI48" s="42" t="s">
+      <c r="Y48" s="49"/>
+      <c r="Z48" s="49"/>
+      <c r="AA48" s="49"/>
+      <c r="AB48" s="49"/>
+      <c r="AC48" s="49"/>
+      <c r="AD48" s="49"/>
+      <c r="AI48" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AJ48" s="42"/>
-      <c r="AK48" s="42"/>
-      <c r="AL48" s="42"/>
-      <c r="AM48" s="42"/>
-      <c r="AN48" s="42"/>
-      <c r="AO48" s="42"/>
+      <c r="AJ48" s="49"/>
+      <c r="AK48" s="49"/>
+      <c r="AL48" s="49"/>
+      <c r="AM48" s="49"/>
+      <c r="AN48" s="49"/>
+      <c r="AO48" s="49"/>
     </row>
     <row r="49" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="M48:S48"/>
-    <mergeCell ref="M39:S39"/>
-    <mergeCell ref="P37:V37"/>
-    <mergeCell ref="P28:V28"/>
-    <mergeCell ref="A36:G36"/>
-    <mergeCell ref="A45:G45"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="AU45:BA45"/>
+    <mergeCell ref="AF28:AL28"/>
+    <mergeCell ref="AF37:AL37"/>
+    <mergeCell ref="AQ30:AS30"/>
+    <mergeCell ref="AQ41:AS41"/>
+    <mergeCell ref="AU34:BA34"/>
+    <mergeCell ref="AU36:BA36"/>
+    <mergeCell ref="AU2:BA2"/>
+    <mergeCell ref="AU3:BA3"/>
+    <mergeCell ref="AU12:BA12"/>
+    <mergeCell ref="AU14:BA14"/>
+    <mergeCell ref="AU23:BA23"/>
+    <mergeCell ref="X37:AD37"/>
+    <mergeCell ref="AE26:AM26"/>
+    <mergeCell ref="Z1:AB1"/>
+    <mergeCell ref="X39:AD39"/>
+    <mergeCell ref="X48:AD48"/>
+    <mergeCell ref="AF1:BA1"/>
+    <mergeCell ref="AI2:AO2"/>
+    <mergeCell ref="AI3:AO3"/>
+    <mergeCell ref="AI12:AO12"/>
+    <mergeCell ref="AI39:AO39"/>
+    <mergeCell ref="AU25:BA25"/>
+    <mergeCell ref="AI48:AO48"/>
+    <mergeCell ref="AN14:AP14"/>
+    <mergeCell ref="AN36:AP36"/>
+    <mergeCell ref="AQ8:AS8"/>
+    <mergeCell ref="AQ19:AS19"/>
     <mergeCell ref="A1:U1"/>
     <mergeCell ref="O26:W26"/>
     <mergeCell ref="I41:K41"/>
@@ -4148,34 +4207,14 @@
     <mergeCell ref="I8:K8"/>
     <mergeCell ref="I19:K19"/>
     <mergeCell ref="A25:G25"/>
-    <mergeCell ref="X37:AD37"/>
-    <mergeCell ref="AE26:AM26"/>
-    <mergeCell ref="Z1:AB1"/>
-    <mergeCell ref="X39:AD39"/>
-    <mergeCell ref="X48:AD48"/>
-    <mergeCell ref="AF1:BA1"/>
-    <mergeCell ref="AI2:AO2"/>
-    <mergeCell ref="AI3:AO3"/>
-    <mergeCell ref="AI12:AO12"/>
-    <mergeCell ref="AI39:AO39"/>
-    <mergeCell ref="AU25:BA25"/>
-    <mergeCell ref="AI48:AO48"/>
-    <mergeCell ref="AN14:AP14"/>
-    <mergeCell ref="AN36:AP36"/>
-    <mergeCell ref="AQ8:AS8"/>
-    <mergeCell ref="AQ19:AS19"/>
-    <mergeCell ref="AU2:BA2"/>
-    <mergeCell ref="AU3:BA3"/>
-    <mergeCell ref="AU12:BA12"/>
-    <mergeCell ref="AU14:BA14"/>
-    <mergeCell ref="AU23:BA23"/>
-    <mergeCell ref="AU45:BA45"/>
-    <mergeCell ref="AF28:AL28"/>
-    <mergeCell ref="AF37:AL37"/>
-    <mergeCell ref="AQ30:AS30"/>
-    <mergeCell ref="AQ41:AS41"/>
-    <mergeCell ref="AU34:BA34"/>
-    <mergeCell ref="AU36:BA36"/>
+    <mergeCell ref="M48:S48"/>
+    <mergeCell ref="M39:S39"/>
+    <mergeCell ref="P37:V37"/>
+    <mergeCell ref="P28:V28"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="A34:G34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/2025_2026/Playoffs/Brackets.xlsx
+++ b/2025_2026/Playoffs/Brackets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\NHLStats\2025_2026\Playoffs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECDE848D-4AF9-497E-8296-236E347C6533}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B0D6E11-EB0C-40A7-8F93-C171D9065C51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="88">
   <si>
     <t>Eastern Conference Playoff Teams</t>
   </si>
@@ -287,6 +287,9 @@
   </si>
   <si>
     <t>Avalanche Leads 1-0</t>
+  </si>
+  <si>
+    <t>Golden Knights lead 1-0</t>
   </si>
 </sst>
 </file>
@@ -665,6 +668,39 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -683,46 +719,13 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1092,18 +1095,18 @@
     </row>
     <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="11" spans="1:7" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="61" t="s">
+      <c r="A11" s="59" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="61"/>
-      <c r="C11" s="61" t="s">
+      <c r="B11" s="59"/>
+      <c r="C11" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="61"/>
-      <c r="E11" s="61" t="s">
+      <c r="D11" s="59"/>
+      <c r="E11" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="61"/>
+      <c r="F11" s="59"/>
       <c r="G11" s="4" t="s">
         <v>18</v>
       </c>
@@ -1132,18 +1135,18 @@
       </c>
     </row>
     <row r="13" spans="1:7" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="59" t="s">
+      <c r="A13" s="60" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="60"/>
-      <c r="C13" s="59" t="s">
+      <c r="B13" s="61"/>
+      <c r="C13" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="D13" s="60"/>
-      <c r="E13" s="59" t="s">
+      <c r="D13" s="61"/>
+      <c r="E13" s="60" t="s">
         <v>17</v>
       </c>
-      <c r="F13" s="60"/>
+      <c r="F13" s="61"/>
       <c r="G13" s="5"/>
     </row>
     <row r="14" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1180,14 +1183,14 @@
       <c r="F15" s="6"/>
     </row>
     <row r="16" spans="1:7" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="59" t="s">
+      <c r="A16" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="60"/>
-      <c r="C16" s="59" t="s">
+      <c r="B16" s="61"/>
+      <c r="C16" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="60"/>
+      <c r="D16" s="61"/>
     </row>
     <row r="17" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
@@ -1218,10 +1221,10 @@
       </c>
     </row>
     <row r="19" spans="1:4" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="59" t="s">
+      <c r="A19" s="60" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="60"/>
+      <c r="B19" s="61"/>
     </row>
     <row r="20" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
@@ -1240,10 +1243,10 @@
       </c>
     </row>
     <row r="22" spans="1:4" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="59" t="s">
+      <c r="A22" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="60"/>
+      <c r="B22" s="61"/>
     </row>
     <row r="23" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
@@ -1328,16 +1331,16 @@
     <sortCondition ref="B2:B9"/>
   </sortState>
   <mergeCells count="10">
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C16:D16"/>
     <mergeCell ref="E11:F11"/>
     <mergeCell ref="E13:F13"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C16:D16"/>
   </mergeCells>
   <dataValidations count="16">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C14" xr:uid="{2C3D9587-ABAE-4E3F-8B22-396DF812BF02}">
@@ -1429,7 +1432,7 @@
     <col min="38" max="38" width="20.7109375" style="1" customWidth="1"/>
     <col min="39" max="39" width="22.140625" style="1" customWidth="1"/>
     <col min="40" max="40" width="9.140625" style="1"/>
-    <col min="41" max="41" width="22.140625" style="1" customWidth="1"/>
+    <col min="41" max="41" width="24.7109375" style="1" customWidth="1"/>
     <col min="42" max="47" width="9.140625" style="1"/>
     <col min="48" max="48" width="10.28515625" style="1" customWidth="1"/>
     <col min="49" max="49" width="23.140625" style="1" customWidth="1"/>
@@ -1441,124 +1444,124 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:54" ht="27.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
-      <c r="M1" s="52"/>
-      <c r="N1" s="52"/>
-      <c r="O1" s="52"/>
-      <c r="P1" s="52"/>
-      <c r="Q1" s="52"/>
-      <c r="R1" s="52"/>
-      <c r="S1" s="52"/>
-      <c r="T1" s="52"/>
-      <c r="U1" s="53"/>
-      <c r="Z1" s="51" t="s">
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
+      <c r="K1" s="51"/>
+      <c r="L1" s="51"/>
+      <c r="M1" s="51"/>
+      <c r="N1" s="51"/>
+      <c r="O1" s="51"/>
+      <c r="P1" s="51"/>
+      <c r="Q1" s="51"/>
+      <c r="R1" s="51"/>
+      <c r="S1" s="51"/>
+      <c r="T1" s="51"/>
+      <c r="U1" s="52"/>
+      <c r="Z1" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="AA1" s="52"/>
-      <c r="AB1" s="53"/>
-      <c r="AF1" s="51" t="s">
+      <c r="AA1" s="51"/>
+      <c r="AB1" s="52"/>
+      <c r="AF1" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="AG1" s="52"/>
-      <c r="AH1" s="52"/>
-      <c r="AI1" s="52"/>
-      <c r="AJ1" s="52"/>
-      <c r="AK1" s="52"/>
-      <c r="AL1" s="52"/>
-      <c r="AM1" s="52"/>
-      <c r="AN1" s="52"/>
-      <c r="AO1" s="52"/>
-      <c r="AP1" s="52"/>
-      <c r="AQ1" s="52"/>
-      <c r="AR1" s="52"/>
-      <c r="AS1" s="52"/>
-      <c r="AT1" s="52"/>
-      <c r="AU1" s="52"/>
-      <c r="AV1" s="52"/>
-      <c r="AW1" s="52"/>
-      <c r="AX1" s="52"/>
-      <c r="AY1" s="52"/>
-      <c r="AZ1" s="52"/>
-      <c r="BA1" s="53"/>
+      <c r="AG1" s="51"/>
+      <c r="AH1" s="51"/>
+      <c r="AI1" s="51"/>
+      <c r="AJ1" s="51"/>
+      <c r="AK1" s="51"/>
+      <c r="AL1" s="51"/>
+      <c r="AM1" s="51"/>
+      <c r="AN1" s="51"/>
+      <c r="AO1" s="51"/>
+      <c r="AP1" s="51"/>
+      <c r="AQ1" s="51"/>
+      <c r="AR1" s="51"/>
+      <c r="AS1" s="51"/>
+      <c r="AT1" s="51"/>
+      <c r="AU1" s="51"/>
+      <c r="AV1" s="51"/>
+      <c r="AW1" s="51"/>
+      <c r="AX1" s="51"/>
+      <c r="AY1" s="51"/>
+      <c r="AZ1" s="51"/>
+      <c r="BA1" s="52"/>
     </row>
     <row r="2" spans="1:54" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="55" t="s">
+      <c r="A2" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="57"/>
-      <c r="M2" s="55" t="s">
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="48"/>
+      <c r="M2" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="56"/>
-      <c r="O2" s="56"/>
-      <c r="P2" s="56"/>
-      <c r="Q2" s="56"/>
-      <c r="R2" s="57"/>
-      <c r="AI2" s="55" t="s">
+      <c r="N2" s="47"/>
+      <c r="O2" s="47"/>
+      <c r="P2" s="47"/>
+      <c r="Q2" s="47"/>
+      <c r="R2" s="48"/>
+      <c r="AI2" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="AJ2" s="56"/>
-      <c r="AK2" s="56"/>
-      <c r="AL2" s="56"/>
-      <c r="AM2" s="56"/>
-      <c r="AN2" s="56"/>
-      <c r="AO2" s="57"/>
-      <c r="AU2" s="55" t="s">
+      <c r="AJ2" s="47"/>
+      <c r="AK2" s="47"/>
+      <c r="AL2" s="47"/>
+      <c r="AM2" s="47"/>
+      <c r="AN2" s="47"/>
+      <c r="AO2" s="48"/>
+      <c r="AU2" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="AV2" s="56"/>
-      <c r="AW2" s="56"/>
-      <c r="AX2" s="56"/>
-      <c r="AY2" s="56"/>
-      <c r="AZ2" s="56"/>
-      <c r="BA2" s="57"/>
+      <c r="AV2" s="47"/>
+      <c r="AW2" s="47"/>
+      <c r="AX2" s="47"/>
+      <c r="AY2" s="47"/>
+      <c r="AZ2" s="47"/>
+      <c r="BA2" s="48"/>
     </row>
     <row r="3" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="49" t="s">
+      <c r="A3" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="49"/>
-      <c r="C3" s="49"/>
-      <c r="D3" s="49"/>
-      <c r="E3" s="49"/>
-      <c r="F3" s="49"/>
-      <c r="G3" s="49"/>
-      <c r="AI3" s="42" t="s">
+      <c r="B3" s="42"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="42"/>
+      <c r="AI3" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="AJ3" s="43"/>
-      <c r="AK3" s="43"/>
-      <c r="AL3" s="43"/>
-      <c r="AM3" s="43"/>
-      <c r="AN3" s="43"/>
-      <c r="AO3" s="44"/>
-      <c r="AU3" s="49" t="s">
+      <c r="AJ3" s="54"/>
+      <c r="AK3" s="54"/>
+      <c r="AL3" s="54"/>
+      <c r="AM3" s="54"/>
+      <c r="AN3" s="54"/>
+      <c r="AO3" s="55"/>
+      <c r="AU3" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="AV3" s="49"/>
-      <c r="AW3" s="49"/>
-      <c r="AX3" s="49"/>
-      <c r="AY3" s="49"/>
-      <c r="AZ3" s="49"/>
-      <c r="BA3" s="49"/>
+      <c r="AV3" s="42"/>
+      <c r="AW3" s="42"/>
+      <c r="AX3" s="42"/>
+      <c r="AY3" s="42"/>
+      <c r="AZ3" s="42"/>
+      <c r="BA3" s="42"/>
     </row>
     <row r="4" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
@@ -1582,15 +1585,15 @@
       <c r="G4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="42" t="s">
+      <c r="M4" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="N4" s="43"/>
-      <c r="O4" s="43"/>
-      <c r="P4" s="43"/>
-      <c r="Q4" s="43"/>
-      <c r="R4" s="43"/>
-      <c r="S4" s="44"/>
+      <c r="N4" s="54"/>
+      <c r="O4" s="54"/>
+      <c r="P4" s="54"/>
+      <c r="Q4" s="54"/>
+      <c r="R4" s="54"/>
+      <c r="S4" s="55"/>
       <c r="AI4" s="3" t="s">
         <v>2</v>
       </c>
@@ -1893,11 +1896,11 @@
       <c r="G8" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="I8" s="50" t="s">
+      <c r="I8" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="J8" s="50"/>
-      <c r="K8" s="50"/>
+      <c r="J8" s="43"/>
+      <c r="K8" s="43"/>
       <c r="M8" s="8">
         <v>3</v>
       </c>
@@ -1928,11 +1931,11 @@
       </c>
       <c r="AN8" s="31"/>
       <c r="AO8" s="16"/>
-      <c r="AQ8" s="50" t="s">
+      <c r="AQ8" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="AR8" s="50"/>
-      <c r="AS8" s="50"/>
+      <c r="AR8" s="43"/>
+      <c r="AS8" s="43"/>
       <c r="AU8" s="38">
         <v>4</v>
       </c>
@@ -2165,15 +2168,15 @@
       <c r="BA11" s="6"/>
     </row>
     <row r="12" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="49" t="s">
+      <c r="A12" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="49"/>
-      <c r="C12" s="49"/>
-      <c r="D12" s="49"/>
-      <c r="E12" s="49"/>
-      <c r="F12" s="49"/>
-      <c r="G12" s="49"/>
+      <c r="B12" s="42"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="42"/>
       <c r="L12" s="12"/>
       <c r="M12" s="8" t="s">
         <v>12</v>
@@ -2190,65 +2193,65 @@
       </c>
       <c r="R12" s="13"/>
       <c r="S12" s="16"/>
-      <c r="AI12" s="49" t="s">
+      <c r="AI12" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AJ12" s="49"/>
-      <c r="AK12" s="49"/>
-      <c r="AL12" s="49"/>
-      <c r="AM12" s="49"/>
-      <c r="AN12" s="49"/>
-      <c r="AO12" s="49"/>
+      <c r="AJ12" s="42"/>
+      <c r="AK12" s="42"/>
+      <c r="AL12" s="42"/>
+      <c r="AM12" s="42"/>
+      <c r="AN12" s="42"/>
+      <c r="AO12" s="42"/>
       <c r="AQ12" s="12"/>
-      <c r="AU12" s="49" t="s">
+      <c r="AU12" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AV12" s="49"/>
-      <c r="AW12" s="49"/>
-      <c r="AX12" s="49"/>
-      <c r="AY12" s="49"/>
-      <c r="AZ12" s="49"/>
-      <c r="BA12" s="49"/>
+      <c r="AV12" s="42"/>
+      <c r="AW12" s="42"/>
+      <c r="AX12" s="42"/>
+      <c r="AY12" s="42"/>
+      <c r="AZ12" s="42"/>
+      <c r="BA12" s="42"/>
     </row>
     <row r="13" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L13" s="12"/>
-      <c r="M13" s="42" t="s">
+      <c r="M13" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="N13" s="43"/>
-      <c r="O13" s="43"/>
-      <c r="P13" s="43"/>
-      <c r="Q13" s="43"/>
-      <c r="R13" s="43"/>
-      <c r="S13" s="44"/>
+      <c r="N13" s="54"/>
+      <c r="O13" s="54"/>
+      <c r="P13" s="54"/>
+      <c r="Q13" s="54"/>
+      <c r="R13" s="54"/>
+      <c r="S13" s="55"/>
       <c r="AQ13" s="12"/>
     </row>
     <row r="14" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="48" t="s">
+      <c r="A14" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="48"/>
-      <c r="C14" s="48"/>
-      <c r="D14" s="48"/>
-      <c r="E14" s="48"/>
-      <c r="F14" s="48"/>
-      <c r="G14" s="48"/>
-      <c r="L14" s="54"/>
-      <c r="M14" s="50"/>
-      <c r="N14" s="50"/>
-      <c r="AN14" s="50"/>
-      <c r="AO14" s="50"/>
-      <c r="AP14" s="50"/>
+      <c r="B14" s="45"/>
+      <c r="C14" s="45"/>
+      <c r="D14" s="45"/>
+      <c r="E14" s="45"/>
+      <c r="F14" s="45"/>
+      <c r="G14" s="45"/>
+      <c r="L14" s="44"/>
+      <c r="M14" s="43"/>
+      <c r="N14" s="43"/>
+      <c r="AN14" s="43"/>
+      <c r="AO14" s="43"/>
+      <c r="AP14" s="43"/>
       <c r="AQ14" s="12"/>
-      <c r="AU14" s="48" t="s">
+      <c r="AU14" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="AV14" s="48"/>
-      <c r="AW14" s="48"/>
-      <c r="AX14" s="48"/>
-      <c r="AY14" s="48"/>
-      <c r="AZ14" s="48"/>
-      <c r="BA14" s="48"/>
+      <c r="AV14" s="45"/>
+      <c r="AW14" s="45"/>
+      <c r="AX14" s="45"/>
+      <c r="AY14" s="45"/>
+      <c r="AZ14" s="45"/>
+      <c r="BA14" s="45"/>
     </row>
     <row r="15" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
@@ -2476,19 +2479,19 @@
       <c r="G19" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="I19" s="50" t="s">
+      <c r="I19" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="J19" s="50"/>
-      <c r="K19" s="50"/>
+      <c r="J19" s="43"/>
+      <c r="K19" s="43"/>
       <c r="L19" s="12"/>
       <c r="O19" s="12"/>
       <c r="AN19" s="12"/>
-      <c r="AQ19" s="54" t="s">
+      <c r="AQ19" s="44" t="s">
         <v>31</v>
       </c>
-      <c r="AR19" s="50"/>
-      <c r="AS19" s="50"/>
+      <c r="AR19" s="43"/>
+      <c r="AS19" s="43"/>
       <c r="AU19" s="38">
         <v>4</v>
       </c>
@@ -2650,52 +2653,52 @@
       <c r="BA22" s="6"/>
     </row>
     <row r="23" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="49" t="s">
+      <c r="A23" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B23" s="49"/>
-      <c r="C23" s="49"/>
-      <c r="D23" s="49"/>
-      <c r="E23" s="49"/>
-      <c r="F23" s="49"/>
-      <c r="G23" s="49"/>
+      <c r="B23" s="42"/>
+      <c r="C23" s="42"/>
+      <c r="D23" s="42"/>
+      <c r="E23" s="42"/>
+      <c r="F23" s="42"/>
+      <c r="G23" s="42"/>
       <c r="O23" s="12"/>
       <c r="AN23" s="12"/>
-      <c r="AU23" s="49" t="s">
+      <c r="AU23" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AV23" s="49"/>
-      <c r="AW23" s="49"/>
-      <c r="AX23" s="49"/>
-      <c r="AY23" s="49"/>
-      <c r="AZ23" s="49"/>
-      <c r="BA23" s="49"/>
+      <c r="AV23" s="42"/>
+      <c r="AW23" s="42"/>
+      <c r="AX23" s="42"/>
+      <c r="AY23" s="42"/>
+      <c r="AZ23" s="42"/>
+      <c r="BA23" s="42"/>
     </row>
     <row r="24" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="O24" s="12"/>
       <c r="AN24" s="12"/>
     </row>
     <row r="25" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="49" t="s">
+      <c r="A25" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="49"/>
-      <c r="C25" s="49"/>
-      <c r="D25" s="49"/>
-      <c r="E25" s="49"/>
-      <c r="F25" s="49"/>
-      <c r="G25" s="49"/>
+      <c r="B25" s="42"/>
+      <c r="C25" s="42"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="42"/>
+      <c r="F25" s="42"/>
+      <c r="G25" s="42"/>
       <c r="O25" s="12"/>
       <c r="AN25" s="12"/>
-      <c r="AU25" s="49" t="s">
+      <c r="AU25" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="AV25" s="49"/>
-      <c r="AW25" s="49"/>
-      <c r="AX25" s="49"/>
-      <c r="AY25" s="49"/>
-      <c r="AZ25" s="49"/>
-      <c r="BA25" s="49"/>
+      <c r="AV25" s="42"/>
+      <c r="AW25" s="42"/>
+      <c r="AX25" s="42"/>
+      <c r="AY25" s="42"/>
+      <c r="AZ25" s="42"/>
+      <c r="BA25" s="42"/>
     </row>
     <row r="26" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="20" t="s">
@@ -2719,24 +2722,24 @@
       <c r="G26" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="O26" s="54"/>
-      <c r="P26" s="50"/>
-      <c r="Q26" s="50"/>
-      <c r="R26" s="50"/>
-      <c r="S26" s="50"/>
-      <c r="T26" s="50"/>
-      <c r="U26" s="50"/>
-      <c r="V26" s="50"/>
-      <c r="W26" s="50"/>
-      <c r="AE26" s="50"/>
-      <c r="AF26" s="50"/>
-      <c r="AG26" s="50"/>
-      <c r="AH26" s="50"/>
-      <c r="AI26" s="50"/>
-      <c r="AJ26" s="50"/>
-      <c r="AK26" s="50"/>
-      <c r="AL26" s="50"/>
-      <c r="AM26" s="58"/>
+      <c r="O26" s="44"/>
+      <c r="P26" s="43"/>
+      <c r="Q26" s="43"/>
+      <c r="R26" s="43"/>
+      <c r="S26" s="43"/>
+      <c r="T26" s="43"/>
+      <c r="U26" s="43"/>
+      <c r="V26" s="43"/>
+      <c r="W26" s="43"/>
+      <c r="AE26" s="43"/>
+      <c r="AF26" s="43"/>
+      <c r="AG26" s="43"/>
+      <c r="AH26" s="43"/>
+      <c r="AI26" s="43"/>
+      <c r="AJ26" s="43"/>
+      <c r="AK26" s="43"/>
+      <c r="AL26" s="43"/>
+      <c r="AM26" s="49"/>
       <c r="AU26" s="20" t="s">
         <v>2</v>
       </c>
@@ -2833,26 +2836,26 @@
         <v>54</v>
       </c>
       <c r="O28" s="12"/>
-      <c r="P28" s="42" t="s">
+      <c r="P28" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="Q28" s="43"/>
-      <c r="R28" s="43"/>
-      <c r="S28" s="43"/>
-      <c r="T28" s="43"/>
-      <c r="U28" s="43"/>
-      <c r="V28" s="44"/>
+      <c r="Q28" s="54"/>
+      <c r="R28" s="54"/>
+      <c r="S28" s="54"/>
+      <c r="T28" s="54"/>
+      <c r="U28" s="54"/>
+      <c r="V28" s="55"/>
       <c r="X28" s="12"/>
       <c r="AD28" s="13"/>
-      <c r="AF28" s="49" t="s">
+      <c r="AF28" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="AG28" s="49"/>
-      <c r="AH28" s="49"/>
-      <c r="AI28" s="49"/>
-      <c r="AJ28" s="49"/>
-      <c r="AK28" s="49"/>
-      <c r="AL28" s="49"/>
+      <c r="AG28" s="42"/>
+      <c r="AH28" s="42"/>
+      <c r="AI28" s="42"/>
+      <c r="AJ28" s="42"/>
+      <c r="AK28" s="42"/>
+      <c r="AL28" s="42"/>
       <c r="AN28" s="12"/>
       <c r="AU28" s="8">
         <v>2</v>
@@ -2988,11 +2991,11 @@
       <c r="G30" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="I30" s="50" t="s">
+      <c r="I30" s="43" t="s">
         <v>26</v>
       </c>
-      <c r="J30" s="50"/>
-      <c r="K30" s="50"/>
+      <c r="J30" s="43"/>
+      <c r="K30" s="43"/>
       <c r="O30" s="12"/>
       <c r="P30" s="7">
         <v>1</v>
@@ -3015,11 +3018,11 @@
       <c r="AK30" s="24"/>
       <c r="AL30" s="25"/>
       <c r="AN30" s="12"/>
-      <c r="AQ30" s="50" t="s">
+      <c r="AQ30" s="43" t="s">
         <v>38</v>
       </c>
-      <c r="AR30" s="50"/>
-      <c r="AS30" s="50"/>
+      <c r="AR30" s="43"/>
+      <c r="AS30" s="43"/>
       <c r="AU30" s="38">
         <v>4</v>
       </c>
@@ -3231,15 +3234,15 @@
       <c r="BA33" s="6"/>
     </row>
     <row r="34" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="49" t="s">
+      <c r="A34" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B34" s="49"/>
-      <c r="C34" s="49"/>
-      <c r="D34" s="49"/>
-      <c r="E34" s="49"/>
-      <c r="F34" s="49"/>
-      <c r="G34" s="49"/>
+      <c r="B34" s="42"/>
+      <c r="C34" s="42"/>
+      <c r="D34" s="42"/>
+      <c r="E34" s="42"/>
+      <c r="F34" s="42"/>
+      <c r="G34" s="42"/>
       <c r="L34" s="12"/>
       <c r="O34" s="12"/>
       <c r="P34" s="8" t="s">
@@ -3264,15 +3267,15 @@
       <c r="AL34" s="16"/>
       <c r="AN34" s="12"/>
       <c r="AQ34" s="12"/>
-      <c r="AU34" s="49" t="s">
+      <c r="AU34" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AV34" s="49"/>
-      <c r="AW34" s="49"/>
-      <c r="AX34" s="49"/>
-      <c r="AY34" s="49"/>
-      <c r="AZ34" s="49"/>
-      <c r="BA34" s="49"/>
+      <c r="AV34" s="42"/>
+      <c r="AW34" s="42"/>
+      <c r="AX34" s="42"/>
+      <c r="AY34" s="42"/>
+      <c r="AZ34" s="42"/>
+      <c r="BA34" s="42"/>
     </row>
     <row r="35" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L35" s="12"/>
@@ -3301,18 +3304,18 @@
       <c r="AQ35" s="12"/>
     </row>
     <row r="36" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="48" t="s">
+      <c r="A36" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="B36" s="48"/>
-      <c r="C36" s="48"/>
-      <c r="D36" s="48"/>
-      <c r="E36" s="48"/>
-      <c r="F36" s="48"/>
-      <c r="G36" s="48"/>
-      <c r="L36" s="54"/>
-      <c r="M36" s="50"/>
-      <c r="N36" s="50"/>
+      <c r="B36" s="45"/>
+      <c r="C36" s="45"/>
+      <c r="D36" s="45"/>
+      <c r="E36" s="45"/>
+      <c r="F36" s="45"/>
+      <c r="G36" s="45"/>
+      <c r="L36" s="44"/>
+      <c r="M36" s="43"/>
+      <c r="N36" s="43"/>
       <c r="O36" s="12"/>
       <c r="P36" s="8" t="s">
         <v>12</v>
@@ -3334,19 +3337,19 @@
       <c r="AJ36" s="35"/>
       <c r="AK36" s="36"/>
       <c r="AL36" s="37"/>
-      <c r="AN36" s="54"/>
-      <c r="AO36" s="50"/>
-      <c r="AP36" s="50"/>
+      <c r="AN36" s="44"/>
+      <c r="AO36" s="43"/>
+      <c r="AP36" s="43"/>
       <c r="AQ36" s="12"/>
-      <c r="AU36" s="48" t="s">
+      <c r="AU36" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="AV36" s="48"/>
-      <c r="AW36" s="48"/>
-      <c r="AX36" s="48"/>
-      <c r="AY36" s="48"/>
-      <c r="AZ36" s="48"/>
-      <c r="BA36" s="48"/>
+      <c r="AV36" s="45"/>
+      <c r="AW36" s="45"/>
+      <c r="AX36" s="45"/>
+      <c r="AY36" s="45"/>
+      <c r="AZ36" s="45"/>
+      <c r="BA36" s="45"/>
     </row>
     <row r="37" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37" s="20" t="s">
@@ -3371,31 +3374,31 @@
         <v>9</v>
       </c>
       <c r="L37" s="12"/>
-      <c r="P37" s="45" t="s">
+      <c r="P37" s="56" t="s">
         <v>13</v>
       </c>
-      <c r="Q37" s="46"/>
-      <c r="R37" s="46"/>
-      <c r="S37" s="46"/>
-      <c r="T37" s="46"/>
-      <c r="U37" s="46"/>
-      <c r="V37" s="47"/>
-      <c r="X37" s="54"/>
-      <c r="Y37" s="50"/>
-      <c r="Z37" s="50"/>
-      <c r="AA37" s="50"/>
-      <c r="AB37" s="50"/>
-      <c r="AC37" s="50"/>
-      <c r="AD37" s="58"/>
-      <c r="AF37" s="49" t="s">
+      <c r="Q37" s="57"/>
+      <c r="R37" s="57"/>
+      <c r="S37" s="57"/>
+      <c r="T37" s="57"/>
+      <c r="U37" s="57"/>
+      <c r="V37" s="58"/>
+      <c r="X37" s="44"/>
+      <c r="Y37" s="43"/>
+      <c r="Z37" s="43"/>
+      <c r="AA37" s="43"/>
+      <c r="AB37" s="43"/>
+      <c r="AC37" s="43"/>
+      <c r="AD37" s="49"/>
+      <c r="AF37" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AG37" s="49"/>
-      <c r="AH37" s="49"/>
-      <c r="AI37" s="49"/>
-      <c r="AJ37" s="49"/>
-      <c r="AK37" s="49"/>
-      <c r="AL37" s="49"/>
+      <c r="AG37" s="42"/>
+      <c r="AH37" s="42"/>
+      <c r="AI37" s="42"/>
+      <c r="AJ37" s="42"/>
+      <c r="AK37" s="42"/>
+      <c r="AL37" s="42"/>
       <c r="AQ37" s="12"/>
       <c r="AU37" s="3" t="s">
         <v>2</v>
@@ -3488,33 +3491,33 @@
         <v>53</v>
       </c>
       <c r="L39" s="12"/>
-      <c r="M39" s="42" t="s">
+      <c r="M39" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="N39" s="43"/>
-      <c r="O39" s="43"/>
-      <c r="P39" s="43"/>
-      <c r="Q39" s="43"/>
-      <c r="R39" s="43"/>
-      <c r="S39" s="44"/>
-      <c r="X39" s="49" t="s">
+      <c r="N39" s="54"/>
+      <c r="O39" s="54"/>
+      <c r="P39" s="54"/>
+      <c r="Q39" s="54"/>
+      <c r="R39" s="54"/>
+      <c r="S39" s="55"/>
+      <c r="X39" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="Y39" s="49"/>
-      <c r="Z39" s="49"/>
-      <c r="AA39" s="49"/>
-      <c r="AB39" s="49"/>
-      <c r="AC39" s="49"/>
-      <c r="AD39" s="49"/>
-      <c r="AI39" s="42" t="s">
+      <c r="Y39" s="42"/>
+      <c r="Z39" s="42"/>
+      <c r="AA39" s="42"/>
+      <c r="AB39" s="42"/>
+      <c r="AC39" s="42"/>
+      <c r="AD39" s="42"/>
+      <c r="AI39" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="AJ39" s="43"/>
-      <c r="AK39" s="43"/>
-      <c r="AL39" s="43"/>
-      <c r="AM39" s="43"/>
-      <c r="AN39" s="43"/>
-      <c r="AO39" s="44"/>
+      <c r="AJ39" s="54"/>
+      <c r="AK39" s="54"/>
+      <c r="AL39" s="54"/>
+      <c r="AM39" s="54"/>
+      <c r="AN39" s="54"/>
+      <c r="AO39" s="55"/>
       <c r="AQ39" s="12"/>
       <c r="AU39" s="8">
         <v>2</v>
@@ -3669,11 +3672,11 @@
       <c r="G41" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="I41" s="50" t="s">
+      <c r="I41" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="J41" s="50"/>
-      <c r="K41" s="50"/>
+      <c r="J41" s="43"/>
+      <c r="K41" s="43"/>
       <c r="L41" s="12"/>
       <c r="M41" s="7">
         <v>1</v>
@@ -3714,17 +3717,23 @@
       <c r="AK41" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="AL41" s="24"/>
+      <c r="AL41" s="24">
+        <v>1</v>
+      </c>
       <c r="AM41" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="AN41" s="24"/>
-      <c r="AO41" s="25"/>
-      <c r="AQ41" s="54" t="s">
+      <c r="AN41" s="24">
+        <v>3</v>
+      </c>
+      <c r="AO41" s="25" t="s">
+        <v>87</v>
+      </c>
+      <c r="AQ41" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="AR41" s="50"/>
-      <c r="AS41" s="50"/>
+      <c r="AR41" s="43"/>
+      <c r="AS41" s="43"/>
       <c r="AU41" s="38">
         <v>4</v>
       </c>
@@ -3781,12 +3790,18 @@
       <c r="O42" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="P42" s="13"/>
+      <c r="P42" s="13">
+        <v>2</v>
+      </c>
       <c r="Q42" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="R42" s="13"/>
-      <c r="S42" s="16"/>
+      <c r="R42" s="13">
+        <v>3</v>
+      </c>
+      <c r="S42" s="16" t="s">
+        <v>55</v>
+      </c>
       <c r="X42" s="8">
         <v>2</v>
       </c>
@@ -3991,15 +4006,15 @@
       <c r="BA44" s="6"/>
     </row>
     <row r="45" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="49" t="s">
+      <c r="A45" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B45" s="49"/>
-      <c r="C45" s="49"/>
-      <c r="D45" s="49"/>
-      <c r="E45" s="49"/>
-      <c r="F45" s="49"/>
-      <c r="G45" s="49"/>
+      <c r="B45" s="42"/>
+      <c r="C45" s="42"/>
+      <c r="D45" s="42"/>
+      <c r="E45" s="42"/>
+      <c r="F45" s="42"/>
+      <c r="G45" s="42"/>
       <c r="M45" s="8" t="s">
         <v>11</v>
       </c>
@@ -4039,15 +4054,15 @@
       </c>
       <c r="AN45" s="13"/>
       <c r="AO45" s="16"/>
-      <c r="AU45" s="49" t="s">
+      <c r="AU45" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AV45" s="49"/>
-      <c r="AW45" s="49"/>
-      <c r="AX45" s="49"/>
-      <c r="AY45" s="49"/>
-      <c r="AZ45" s="49"/>
-      <c r="BA45" s="49"/>
+      <c r="AV45" s="42"/>
+      <c r="AW45" s="42"/>
+      <c r="AX45" s="42"/>
+      <c r="AY45" s="42"/>
+      <c r="AZ45" s="42"/>
+      <c r="BA45" s="42"/>
     </row>
     <row r="46" spans="1:54" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="M46" s="8" t="s">
@@ -4132,49 +4147,61 @@
       <c r="AO47" s="6"/>
     </row>
     <row r="48" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="M48" s="42" t="s">
+      <c r="M48" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="N48" s="43"/>
-      <c r="O48" s="43"/>
-      <c r="P48" s="43"/>
-      <c r="Q48" s="43"/>
-      <c r="R48" s="43"/>
-      <c r="S48" s="44"/>
-      <c r="X48" s="49" t="s">
+      <c r="N48" s="54"/>
+      <c r="O48" s="54"/>
+      <c r="P48" s="54"/>
+      <c r="Q48" s="54"/>
+      <c r="R48" s="54"/>
+      <c r="S48" s="55"/>
+      <c r="X48" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="Y48" s="49"/>
-      <c r="Z48" s="49"/>
-      <c r="AA48" s="49"/>
-      <c r="AB48" s="49"/>
-      <c r="AC48" s="49"/>
-      <c r="AD48" s="49"/>
-      <c r="AI48" s="49" t="s">
+      <c r="Y48" s="42"/>
+      <c r="Z48" s="42"/>
+      <c r="AA48" s="42"/>
+      <c r="AB48" s="42"/>
+      <c r="AC48" s="42"/>
+      <c r="AD48" s="42"/>
+      <c r="AI48" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AJ48" s="49"/>
-      <c r="AK48" s="49"/>
-      <c r="AL48" s="49"/>
-      <c r="AM48" s="49"/>
-      <c r="AN48" s="49"/>
-      <c r="AO48" s="49"/>
+      <c r="AJ48" s="42"/>
+      <c r="AK48" s="42"/>
+      <c r="AL48" s="42"/>
+      <c r="AM48" s="42"/>
+      <c r="AN48" s="42"/>
+      <c r="AO48" s="42"/>
     </row>
     <row r="49" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="AU45:BA45"/>
-    <mergeCell ref="AF28:AL28"/>
-    <mergeCell ref="AF37:AL37"/>
-    <mergeCell ref="AQ30:AS30"/>
-    <mergeCell ref="AQ41:AS41"/>
-    <mergeCell ref="AU34:BA34"/>
-    <mergeCell ref="AU36:BA36"/>
-    <mergeCell ref="AU2:BA2"/>
-    <mergeCell ref="AU3:BA3"/>
-    <mergeCell ref="AU12:BA12"/>
-    <mergeCell ref="AU14:BA14"/>
-    <mergeCell ref="AU23:BA23"/>
+    <mergeCell ref="M48:S48"/>
+    <mergeCell ref="M39:S39"/>
+    <mergeCell ref="P37:V37"/>
+    <mergeCell ref="P28:V28"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A1:U1"/>
+    <mergeCell ref="O26:W26"/>
+    <mergeCell ref="I41:K41"/>
+    <mergeCell ref="L14:N14"/>
+    <mergeCell ref="L36:N36"/>
+    <mergeCell ref="M2:R2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="M4:S4"/>
+    <mergeCell ref="M13:S13"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="A25:G25"/>
     <mergeCell ref="X37:AD37"/>
     <mergeCell ref="AE26:AM26"/>
     <mergeCell ref="Z1:AB1"/>
@@ -4191,30 +4218,18 @@
     <mergeCell ref="AN36:AP36"/>
     <mergeCell ref="AQ8:AS8"/>
     <mergeCell ref="AQ19:AS19"/>
-    <mergeCell ref="A1:U1"/>
-    <mergeCell ref="O26:W26"/>
-    <mergeCell ref="I41:K41"/>
-    <mergeCell ref="L14:N14"/>
-    <mergeCell ref="L36:N36"/>
-    <mergeCell ref="M2:R2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="M4:S4"/>
-    <mergeCell ref="M13:S13"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A23:G23"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="M48:S48"/>
-    <mergeCell ref="M39:S39"/>
-    <mergeCell ref="P37:V37"/>
-    <mergeCell ref="P28:V28"/>
-    <mergeCell ref="A36:G36"/>
-    <mergeCell ref="A45:G45"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="AU2:BA2"/>
+    <mergeCell ref="AU3:BA3"/>
+    <mergeCell ref="AU12:BA12"/>
+    <mergeCell ref="AU14:BA14"/>
+    <mergeCell ref="AU23:BA23"/>
+    <mergeCell ref="AU45:BA45"/>
+    <mergeCell ref="AF28:AL28"/>
+    <mergeCell ref="AF37:AL37"/>
+    <mergeCell ref="AQ30:AS30"/>
+    <mergeCell ref="AQ41:AS41"/>
+    <mergeCell ref="AU34:BA34"/>
+    <mergeCell ref="AU36:BA36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/2025_2026/Playoffs/Brackets.xlsx
+++ b/2025_2026/Playoffs/Brackets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\NHLStats\2025_2026\Playoffs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B0D6E11-EB0C-40A7-8F93-C171D9065C51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{061F8F85-DEE7-4620-89B4-4CC9304B9511}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="89">
   <si>
     <t>Eastern Conference Playoff Teams</t>
   </si>
@@ -290,6 +290,9 @@
   </si>
   <si>
     <t>Golden Knights lead 1-0</t>
+  </si>
+  <si>
+    <t>Avalanche Leads 2-0</t>
   </si>
 </sst>
 </file>
@@ -668,18 +671,45 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -692,40 +722,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1095,18 +1098,18 @@
     </row>
     <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="11" spans="1:7" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="59" t="s">
+      <c r="A11" s="61" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="59"/>
-      <c r="C11" s="59" t="s">
+      <c r="B11" s="61"/>
+      <c r="C11" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="59"/>
-      <c r="E11" s="59" t="s">
+      <c r="D11" s="61"/>
+      <c r="E11" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="59"/>
+      <c r="F11" s="61"/>
       <c r="G11" s="4" t="s">
         <v>18</v>
       </c>
@@ -1135,18 +1138,18 @@
       </c>
     </row>
     <row r="13" spans="1:7" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="60" t="s">
+      <c r="A13" s="59" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="61"/>
-      <c r="C13" s="60" t="s">
+      <c r="B13" s="60"/>
+      <c r="C13" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="D13" s="61"/>
-      <c r="E13" s="60" t="s">
+      <c r="D13" s="60"/>
+      <c r="E13" s="59" t="s">
         <v>17</v>
       </c>
-      <c r="F13" s="61"/>
+      <c r="F13" s="60"/>
       <c r="G13" s="5"/>
     </row>
     <row r="14" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1183,14 +1186,14 @@
       <c r="F15" s="6"/>
     </row>
     <row r="16" spans="1:7" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="60" t="s">
+      <c r="A16" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="61"/>
-      <c r="C16" s="60" t="s">
+      <c r="B16" s="60"/>
+      <c r="C16" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="61"/>
+      <c r="D16" s="60"/>
     </row>
     <row r="17" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
@@ -1221,10 +1224,10 @@
       </c>
     </row>
     <row r="19" spans="1:4" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="60" t="s">
+      <c r="A19" s="59" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="61"/>
+      <c r="B19" s="60"/>
     </row>
     <row r="20" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
@@ -1243,10 +1246,10 @@
       </c>
     </row>
     <row r="22" spans="1:4" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="60" t="s">
+      <c r="A22" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="61"/>
+      <c r="B22" s="60"/>
     </row>
     <row r="23" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
@@ -1331,16 +1334,16 @@
     <sortCondition ref="B2:B9"/>
   </sortState>
   <mergeCells count="10">
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A16:B16"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A16:B16"/>
   </mergeCells>
   <dataValidations count="16">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C14" xr:uid="{2C3D9587-ABAE-4E3F-8B22-396DF812BF02}">
@@ -1444,124 +1447,124 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:54" ht="27.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
-      <c r="I1" s="51"/>
-      <c r="J1" s="51"/>
-      <c r="K1" s="51"/>
-      <c r="L1" s="51"/>
-      <c r="M1" s="51"/>
-      <c r="N1" s="51"/>
-      <c r="O1" s="51"/>
-      <c r="P1" s="51"/>
-      <c r="Q1" s="51"/>
-      <c r="R1" s="51"/>
-      <c r="S1" s="51"/>
-      <c r="T1" s="51"/>
-      <c r="U1" s="52"/>
-      <c r="Z1" s="50" t="s">
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="52"/>
+      <c r="M1" s="52"/>
+      <c r="N1" s="52"/>
+      <c r="O1" s="52"/>
+      <c r="P1" s="52"/>
+      <c r="Q1" s="52"/>
+      <c r="R1" s="52"/>
+      <c r="S1" s="52"/>
+      <c r="T1" s="52"/>
+      <c r="U1" s="53"/>
+      <c r="Z1" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="AA1" s="51"/>
-      <c r="AB1" s="52"/>
-      <c r="AF1" s="50" t="s">
+      <c r="AA1" s="52"/>
+      <c r="AB1" s="53"/>
+      <c r="AF1" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="AG1" s="51"/>
-      <c r="AH1" s="51"/>
-      <c r="AI1" s="51"/>
-      <c r="AJ1" s="51"/>
-      <c r="AK1" s="51"/>
-      <c r="AL1" s="51"/>
-      <c r="AM1" s="51"/>
-      <c r="AN1" s="51"/>
-      <c r="AO1" s="51"/>
-      <c r="AP1" s="51"/>
-      <c r="AQ1" s="51"/>
-      <c r="AR1" s="51"/>
-      <c r="AS1" s="51"/>
-      <c r="AT1" s="51"/>
-      <c r="AU1" s="51"/>
-      <c r="AV1" s="51"/>
-      <c r="AW1" s="51"/>
-      <c r="AX1" s="51"/>
-      <c r="AY1" s="51"/>
-      <c r="AZ1" s="51"/>
-      <c r="BA1" s="52"/>
+      <c r="AG1" s="52"/>
+      <c r="AH1" s="52"/>
+      <c r="AI1" s="52"/>
+      <c r="AJ1" s="52"/>
+      <c r="AK1" s="52"/>
+      <c r="AL1" s="52"/>
+      <c r="AM1" s="52"/>
+      <c r="AN1" s="52"/>
+      <c r="AO1" s="52"/>
+      <c r="AP1" s="52"/>
+      <c r="AQ1" s="52"/>
+      <c r="AR1" s="52"/>
+      <c r="AS1" s="52"/>
+      <c r="AT1" s="52"/>
+      <c r="AU1" s="52"/>
+      <c r="AV1" s="52"/>
+      <c r="AW1" s="52"/>
+      <c r="AX1" s="52"/>
+      <c r="AY1" s="52"/>
+      <c r="AZ1" s="52"/>
+      <c r="BA1" s="53"/>
     </row>
     <row r="2" spans="1:54" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="48"/>
-      <c r="M2" s="46" t="s">
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="57"/>
+      <c r="M2" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="47"/>
-      <c r="O2" s="47"/>
-      <c r="P2" s="47"/>
-      <c r="Q2" s="47"/>
-      <c r="R2" s="48"/>
-      <c r="AI2" s="46" t="s">
+      <c r="N2" s="56"/>
+      <c r="O2" s="56"/>
+      <c r="P2" s="56"/>
+      <c r="Q2" s="56"/>
+      <c r="R2" s="57"/>
+      <c r="AI2" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="AJ2" s="47"/>
-      <c r="AK2" s="47"/>
-      <c r="AL2" s="47"/>
-      <c r="AM2" s="47"/>
-      <c r="AN2" s="47"/>
-      <c r="AO2" s="48"/>
-      <c r="AU2" s="46" t="s">
+      <c r="AJ2" s="56"/>
+      <c r="AK2" s="56"/>
+      <c r="AL2" s="56"/>
+      <c r="AM2" s="56"/>
+      <c r="AN2" s="56"/>
+      <c r="AO2" s="57"/>
+      <c r="AU2" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="AV2" s="47"/>
-      <c r="AW2" s="47"/>
-      <c r="AX2" s="47"/>
-      <c r="AY2" s="47"/>
-      <c r="AZ2" s="47"/>
-      <c r="BA2" s="48"/>
+      <c r="AV2" s="56"/>
+      <c r="AW2" s="56"/>
+      <c r="AX2" s="56"/>
+      <c r="AY2" s="56"/>
+      <c r="AZ2" s="56"/>
+      <c r="BA2" s="57"/>
     </row>
     <row r="3" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="42" t="s">
+      <c r="A3" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="42"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="42"/>
-      <c r="AI3" s="53" t="s">
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="AI3" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="AJ3" s="54"/>
-      <c r="AK3" s="54"/>
-      <c r="AL3" s="54"/>
-      <c r="AM3" s="54"/>
-      <c r="AN3" s="54"/>
-      <c r="AO3" s="55"/>
-      <c r="AU3" s="42" t="s">
+      <c r="AJ3" s="43"/>
+      <c r="AK3" s="43"/>
+      <c r="AL3" s="43"/>
+      <c r="AM3" s="43"/>
+      <c r="AN3" s="43"/>
+      <c r="AO3" s="44"/>
+      <c r="AU3" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="AV3" s="42"/>
-      <c r="AW3" s="42"/>
-      <c r="AX3" s="42"/>
-      <c r="AY3" s="42"/>
-      <c r="AZ3" s="42"/>
-      <c r="BA3" s="42"/>
+      <c r="AV3" s="49"/>
+      <c r="AW3" s="49"/>
+      <c r="AX3" s="49"/>
+      <c r="AY3" s="49"/>
+      <c r="AZ3" s="49"/>
+      <c r="BA3" s="49"/>
     </row>
     <row r="4" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
@@ -1585,15 +1588,15 @@
       <c r="G4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="53" t="s">
+      <c r="M4" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="N4" s="54"/>
-      <c r="O4" s="54"/>
-      <c r="P4" s="54"/>
-      <c r="Q4" s="54"/>
-      <c r="R4" s="54"/>
-      <c r="S4" s="55"/>
+      <c r="N4" s="43"/>
+      <c r="O4" s="43"/>
+      <c r="P4" s="43"/>
+      <c r="Q4" s="43"/>
+      <c r="R4" s="43"/>
+      <c r="S4" s="44"/>
       <c r="AI4" s="3" t="s">
         <v>2</v>
       </c>
@@ -1769,12 +1772,18 @@
       <c r="AK6" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="AL6" s="13"/>
+      <c r="AL6" s="13">
+        <v>2</v>
+      </c>
       <c r="AM6" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="AN6" s="13"/>
-      <c r="AO6" s="16"/>
+      <c r="AN6" s="13">
+        <v>5</v>
+      </c>
+      <c r="AO6" s="16" t="s">
+        <v>88</v>
+      </c>
       <c r="AU6" s="8">
         <v>2</v>
       </c>
@@ -1896,11 +1905,11 @@
       <c r="G8" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="I8" s="43" t="s">
+      <c r="I8" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="J8" s="43"/>
-      <c r="K8" s="43"/>
+      <c r="J8" s="50"/>
+      <c r="K8" s="50"/>
       <c r="M8" s="8">
         <v>3</v>
       </c>
@@ -1931,11 +1940,11 @@
       </c>
       <c r="AN8" s="31"/>
       <c r="AO8" s="16"/>
-      <c r="AQ8" s="43" t="s">
+      <c r="AQ8" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="AR8" s="43"/>
-      <c r="AS8" s="43"/>
+      <c r="AR8" s="50"/>
+      <c r="AS8" s="50"/>
       <c r="AU8" s="38">
         <v>4</v>
       </c>
@@ -2168,15 +2177,15 @@
       <c r="BA11" s="6"/>
     </row>
     <row r="12" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="42" t="s">
+      <c r="A12" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="42"/>
-      <c r="C12" s="42"/>
-      <c r="D12" s="42"/>
-      <c r="E12" s="42"/>
-      <c r="F12" s="42"/>
-      <c r="G12" s="42"/>
+      <c r="B12" s="49"/>
+      <c r="C12" s="49"/>
+      <c r="D12" s="49"/>
+      <c r="E12" s="49"/>
+      <c r="F12" s="49"/>
+      <c r="G12" s="49"/>
       <c r="L12" s="12"/>
       <c r="M12" s="8" t="s">
         <v>12</v>
@@ -2193,65 +2202,65 @@
       </c>
       <c r="R12" s="13"/>
       <c r="S12" s="16"/>
-      <c r="AI12" s="42" t="s">
+      <c r="AI12" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AJ12" s="42"/>
-      <c r="AK12" s="42"/>
-      <c r="AL12" s="42"/>
-      <c r="AM12" s="42"/>
-      <c r="AN12" s="42"/>
-      <c r="AO12" s="42"/>
+      <c r="AJ12" s="49"/>
+      <c r="AK12" s="49"/>
+      <c r="AL12" s="49"/>
+      <c r="AM12" s="49"/>
+      <c r="AN12" s="49"/>
+      <c r="AO12" s="49"/>
       <c r="AQ12" s="12"/>
-      <c r="AU12" s="42" t="s">
+      <c r="AU12" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AV12" s="42"/>
-      <c r="AW12" s="42"/>
-      <c r="AX12" s="42"/>
-      <c r="AY12" s="42"/>
-      <c r="AZ12" s="42"/>
-      <c r="BA12" s="42"/>
+      <c r="AV12" s="49"/>
+      <c r="AW12" s="49"/>
+      <c r="AX12" s="49"/>
+      <c r="AY12" s="49"/>
+      <c r="AZ12" s="49"/>
+      <c r="BA12" s="49"/>
     </row>
     <row r="13" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L13" s="12"/>
-      <c r="M13" s="53" t="s">
+      <c r="M13" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="N13" s="54"/>
-      <c r="O13" s="54"/>
-      <c r="P13" s="54"/>
-      <c r="Q13" s="54"/>
-      <c r="R13" s="54"/>
-      <c r="S13" s="55"/>
+      <c r="N13" s="43"/>
+      <c r="O13" s="43"/>
+      <c r="P13" s="43"/>
+      <c r="Q13" s="43"/>
+      <c r="R13" s="43"/>
+      <c r="S13" s="44"/>
       <c r="AQ13" s="12"/>
     </row>
     <row r="14" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="45" t="s">
+      <c r="A14" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="45"/>
-      <c r="C14" s="45"/>
-      <c r="D14" s="45"/>
-      <c r="E14" s="45"/>
-      <c r="F14" s="45"/>
-      <c r="G14" s="45"/>
-      <c r="L14" s="44"/>
-      <c r="M14" s="43"/>
-      <c r="N14" s="43"/>
-      <c r="AN14" s="43"/>
-      <c r="AO14" s="43"/>
-      <c r="AP14" s="43"/>
+      <c r="B14" s="48"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="48"/>
+      <c r="E14" s="48"/>
+      <c r="F14" s="48"/>
+      <c r="G14" s="48"/>
+      <c r="L14" s="54"/>
+      <c r="M14" s="50"/>
+      <c r="N14" s="50"/>
+      <c r="AN14" s="50"/>
+      <c r="AO14" s="50"/>
+      <c r="AP14" s="50"/>
       <c r="AQ14" s="12"/>
-      <c r="AU14" s="45" t="s">
+      <c r="AU14" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="AV14" s="45"/>
-      <c r="AW14" s="45"/>
-      <c r="AX14" s="45"/>
-      <c r="AY14" s="45"/>
-      <c r="AZ14" s="45"/>
-      <c r="BA14" s="45"/>
+      <c r="AV14" s="48"/>
+      <c r="AW14" s="48"/>
+      <c r="AX14" s="48"/>
+      <c r="AY14" s="48"/>
+      <c r="AZ14" s="48"/>
+      <c r="BA14" s="48"/>
     </row>
     <row r="15" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
@@ -2479,19 +2488,19 @@
       <c r="G19" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="I19" s="43" t="s">
+      <c r="I19" s="50" t="s">
         <v>32</v>
       </c>
-      <c r="J19" s="43"/>
-      <c r="K19" s="43"/>
+      <c r="J19" s="50"/>
+      <c r="K19" s="50"/>
       <c r="L19" s="12"/>
       <c r="O19" s="12"/>
       <c r="AN19" s="12"/>
-      <c r="AQ19" s="44" t="s">
+      <c r="AQ19" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="AR19" s="43"/>
-      <c r="AS19" s="43"/>
+      <c r="AR19" s="50"/>
+      <c r="AS19" s="50"/>
       <c r="AU19" s="38">
         <v>4</v>
       </c>
@@ -2653,52 +2662,52 @@
       <c r="BA22" s="6"/>
     </row>
     <row r="23" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="42" t="s">
+      <c r="A23" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="B23" s="42"/>
-      <c r="C23" s="42"/>
-      <c r="D23" s="42"/>
-      <c r="E23" s="42"/>
-      <c r="F23" s="42"/>
-      <c r="G23" s="42"/>
+      <c r="B23" s="49"/>
+      <c r="C23" s="49"/>
+      <c r="D23" s="49"/>
+      <c r="E23" s="49"/>
+      <c r="F23" s="49"/>
+      <c r="G23" s="49"/>
       <c r="O23" s="12"/>
       <c r="AN23" s="12"/>
-      <c r="AU23" s="42" t="s">
+      <c r="AU23" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AV23" s="42"/>
-      <c r="AW23" s="42"/>
-      <c r="AX23" s="42"/>
-      <c r="AY23" s="42"/>
-      <c r="AZ23" s="42"/>
-      <c r="BA23" s="42"/>
+      <c r="AV23" s="49"/>
+      <c r="AW23" s="49"/>
+      <c r="AX23" s="49"/>
+      <c r="AY23" s="49"/>
+      <c r="AZ23" s="49"/>
+      <c r="BA23" s="49"/>
     </row>
     <row r="24" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="O24" s="12"/>
       <c r="AN24" s="12"/>
     </row>
     <row r="25" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="42" t="s">
+      <c r="A25" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="42"/>
-      <c r="C25" s="42"/>
-      <c r="D25" s="42"/>
-      <c r="E25" s="42"/>
-      <c r="F25" s="42"/>
-      <c r="G25" s="42"/>
+      <c r="B25" s="49"/>
+      <c r="C25" s="49"/>
+      <c r="D25" s="49"/>
+      <c r="E25" s="49"/>
+      <c r="F25" s="49"/>
+      <c r="G25" s="49"/>
       <c r="O25" s="12"/>
       <c r="AN25" s="12"/>
-      <c r="AU25" s="42" t="s">
+      <c r="AU25" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="AV25" s="42"/>
-      <c r="AW25" s="42"/>
-      <c r="AX25" s="42"/>
-      <c r="AY25" s="42"/>
-      <c r="AZ25" s="42"/>
-      <c r="BA25" s="42"/>
+      <c r="AV25" s="49"/>
+      <c r="AW25" s="49"/>
+      <c r="AX25" s="49"/>
+      <c r="AY25" s="49"/>
+      <c r="AZ25" s="49"/>
+      <c r="BA25" s="49"/>
     </row>
     <row r="26" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="20" t="s">
@@ -2722,24 +2731,24 @@
       <c r="G26" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="O26" s="44"/>
-      <c r="P26" s="43"/>
-      <c r="Q26" s="43"/>
-      <c r="R26" s="43"/>
-      <c r="S26" s="43"/>
-      <c r="T26" s="43"/>
-      <c r="U26" s="43"/>
-      <c r="V26" s="43"/>
-      <c r="W26" s="43"/>
-      <c r="AE26" s="43"/>
-      <c r="AF26" s="43"/>
-      <c r="AG26" s="43"/>
-      <c r="AH26" s="43"/>
-      <c r="AI26" s="43"/>
-      <c r="AJ26" s="43"/>
-      <c r="AK26" s="43"/>
-      <c r="AL26" s="43"/>
-      <c r="AM26" s="49"/>
+      <c r="O26" s="54"/>
+      <c r="P26" s="50"/>
+      <c r="Q26" s="50"/>
+      <c r="R26" s="50"/>
+      <c r="S26" s="50"/>
+      <c r="T26" s="50"/>
+      <c r="U26" s="50"/>
+      <c r="V26" s="50"/>
+      <c r="W26" s="50"/>
+      <c r="AE26" s="50"/>
+      <c r="AF26" s="50"/>
+      <c r="AG26" s="50"/>
+      <c r="AH26" s="50"/>
+      <c r="AI26" s="50"/>
+      <c r="AJ26" s="50"/>
+      <c r="AK26" s="50"/>
+      <c r="AL26" s="50"/>
+      <c r="AM26" s="58"/>
       <c r="AU26" s="20" t="s">
         <v>2</v>
       </c>
@@ -2836,26 +2845,26 @@
         <v>54</v>
       </c>
       <c r="O28" s="12"/>
-      <c r="P28" s="53" t="s">
+      <c r="P28" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="Q28" s="54"/>
-      <c r="R28" s="54"/>
-      <c r="S28" s="54"/>
-      <c r="T28" s="54"/>
-      <c r="U28" s="54"/>
-      <c r="V28" s="55"/>
+      <c r="Q28" s="43"/>
+      <c r="R28" s="43"/>
+      <c r="S28" s="43"/>
+      <c r="T28" s="43"/>
+      <c r="U28" s="43"/>
+      <c r="V28" s="44"/>
       <c r="X28" s="12"/>
       <c r="AD28" s="13"/>
-      <c r="AF28" s="42" t="s">
+      <c r="AF28" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="AG28" s="42"/>
-      <c r="AH28" s="42"/>
-      <c r="AI28" s="42"/>
-      <c r="AJ28" s="42"/>
-      <c r="AK28" s="42"/>
-      <c r="AL28" s="42"/>
+      <c r="AG28" s="49"/>
+      <c r="AH28" s="49"/>
+      <c r="AI28" s="49"/>
+      <c r="AJ28" s="49"/>
+      <c r="AK28" s="49"/>
+      <c r="AL28" s="49"/>
       <c r="AN28" s="12"/>
       <c r="AU28" s="8">
         <v>2</v>
@@ -2991,11 +3000,11 @@
       <c r="G30" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="I30" s="43" t="s">
+      <c r="I30" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="J30" s="43"/>
-      <c r="K30" s="43"/>
+      <c r="J30" s="50"/>
+      <c r="K30" s="50"/>
       <c r="O30" s="12"/>
       <c r="P30" s="7">
         <v>1</v>
@@ -3018,11 +3027,11 @@
       <c r="AK30" s="24"/>
       <c r="AL30" s="25"/>
       <c r="AN30" s="12"/>
-      <c r="AQ30" s="43" t="s">
+      <c r="AQ30" s="50" t="s">
         <v>38</v>
       </c>
-      <c r="AR30" s="43"/>
-      <c r="AS30" s="43"/>
+      <c r="AR30" s="50"/>
+      <c r="AS30" s="50"/>
       <c r="AU30" s="38">
         <v>4</v>
       </c>
@@ -3234,15 +3243,15 @@
       <c r="BA33" s="6"/>
     </row>
     <row r="34" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="42" t="s">
+      <c r="A34" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="B34" s="42"/>
-      <c r="C34" s="42"/>
-      <c r="D34" s="42"/>
-      <c r="E34" s="42"/>
-      <c r="F34" s="42"/>
-      <c r="G34" s="42"/>
+      <c r="B34" s="49"/>
+      <c r="C34" s="49"/>
+      <c r="D34" s="49"/>
+      <c r="E34" s="49"/>
+      <c r="F34" s="49"/>
+      <c r="G34" s="49"/>
       <c r="L34" s="12"/>
       <c r="O34" s="12"/>
       <c r="P34" s="8" t="s">
@@ -3267,15 +3276,15 @@
       <c r="AL34" s="16"/>
       <c r="AN34" s="12"/>
       <c r="AQ34" s="12"/>
-      <c r="AU34" s="42" t="s">
+      <c r="AU34" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AV34" s="42"/>
-      <c r="AW34" s="42"/>
-      <c r="AX34" s="42"/>
-      <c r="AY34" s="42"/>
-      <c r="AZ34" s="42"/>
-      <c r="BA34" s="42"/>
+      <c r="AV34" s="49"/>
+      <c r="AW34" s="49"/>
+      <c r="AX34" s="49"/>
+      <c r="AY34" s="49"/>
+      <c r="AZ34" s="49"/>
+      <c r="BA34" s="49"/>
     </row>
     <row r="35" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L35" s="12"/>
@@ -3304,18 +3313,18 @@
       <c r="AQ35" s="12"/>
     </row>
     <row r="36" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="45" t="s">
+      <c r="A36" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="B36" s="45"/>
-      <c r="C36" s="45"/>
-      <c r="D36" s="45"/>
-      <c r="E36" s="45"/>
-      <c r="F36" s="45"/>
-      <c r="G36" s="45"/>
-      <c r="L36" s="44"/>
-      <c r="M36" s="43"/>
-      <c r="N36" s="43"/>
+      <c r="B36" s="48"/>
+      <c r="C36" s="48"/>
+      <c r="D36" s="48"/>
+      <c r="E36" s="48"/>
+      <c r="F36" s="48"/>
+      <c r="G36" s="48"/>
+      <c r="L36" s="54"/>
+      <c r="M36" s="50"/>
+      <c r="N36" s="50"/>
       <c r="O36" s="12"/>
       <c r="P36" s="8" t="s">
         <v>12</v>
@@ -3337,19 +3346,19 @@
       <c r="AJ36" s="35"/>
       <c r="AK36" s="36"/>
       <c r="AL36" s="37"/>
-      <c r="AN36" s="44"/>
-      <c r="AO36" s="43"/>
-      <c r="AP36" s="43"/>
+      <c r="AN36" s="54"/>
+      <c r="AO36" s="50"/>
+      <c r="AP36" s="50"/>
       <c r="AQ36" s="12"/>
-      <c r="AU36" s="45" t="s">
+      <c r="AU36" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="AV36" s="45"/>
-      <c r="AW36" s="45"/>
-      <c r="AX36" s="45"/>
-      <c r="AY36" s="45"/>
-      <c r="AZ36" s="45"/>
-      <c r="BA36" s="45"/>
+      <c r="AV36" s="48"/>
+      <c r="AW36" s="48"/>
+      <c r="AX36" s="48"/>
+      <c r="AY36" s="48"/>
+      <c r="AZ36" s="48"/>
+      <c r="BA36" s="48"/>
     </row>
     <row r="37" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37" s="20" t="s">
@@ -3374,31 +3383,31 @@
         <v>9</v>
       </c>
       <c r="L37" s="12"/>
-      <c r="P37" s="56" t="s">
+      <c r="P37" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="Q37" s="57"/>
-      <c r="R37" s="57"/>
-      <c r="S37" s="57"/>
-      <c r="T37" s="57"/>
-      <c r="U37" s="57"/>
-      <c r="V37" s="58"/>
-      <c r="X37" s="44"/>
-      <c r="Y37" s="43"/>
-      <c r="Z37" s="43"/>
-      <c r="AA37" s="43"/>
-      <c r="AB37" s="43"/>
-      <c r="AC37" s="43"/>
-      <c r="AD37" s="49"/>
-      <c r="AF37" s="42" t="s">
+      <c r="Q37" s="46"/>
+      <c r="R37" s="46"/>
+      <c r="S37" s="46"/>
+      <c r="T37" s="46"/>
+      <c r="U37" s="46"/>
+      <c r="V37" s="47"/>
+      <c r="X37" s="54"/>
+      <c r="Y37" s="50"/>
+      <c r="Z37" s="50"/>
+      <c r="AA37" s="50"/>
+      <c r="AB37" s="50"/>
+      <c r="AC37" s="50"/>
+      <c r="AD37" s="58"/>
+      <c r="AF37" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AG37" s="42"/>
-      <c r="AH37" s="42"/>
-      <c r="AI37" s="42"/>
-      <c r="AJ37" s="42"/>
-      <c r="AK37" s="42"/>
-      <c r="AL37" s="42"/>
+      <c r="AG37" s="49"/>
+      <c r="AH37" s="49"/>
+      <c r="AI37" s="49"/>
+      <c r="AJ37" s="49"/>
+      <c r="AK37" s="49"/>
+      <c r="AL37" s="49"/>
       <c r="AQ37" s="12"/>
       <c r="AU37" s="3" t="s">
         <v>2</v>
@@ -3491,33 +3500,33 @@
         <v>53</v>
       </c>
       <c r="L39" s="12"/>
-      <c r="M39" s="53" t="s">
+      <c r="M39" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="N39" s="54"/>
-      <c r="O39" s="54"/>
-      <c r="P39" s="54"/>
-      <c r="Q39" s="54"/>
-      <c r="R39" s="54"/>
-      <c r="S39" s="55"/>
-      <c r="X39" s="42" t="s">
+      <c r="N39" s="43"/>
+      <c r="O39" s="43"/>
+      <c r="P39" s="43"/>
+      <c r="Q39" s="43"/>
+      <c r="R39" s="43"/>
+      <c r="S39" s="44"/>
+      <c r="X39" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="Y39" s="42"/>
-      <c r="Z39" s="42"/>
-      <c r="AA39" s="42"/>
-      <c r="AB39" s="42"/>
-      <c r="AC39" s="42"/>
-      <c r="AD39" s="42"/>
-      <c r="AI39" s="53" t="s">
+      <c r="Y39" s="49"/>
+      <c r="Z39" s="49"/>
+      <c r="AA39" s="49"/>
+      <c r="AB39" s="49"/>
+      <c r="AC39" s="49"/>
+      <c r="AD39" s="49"/>
+      <c r="AI39" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="AJ39" s="54"/>
-      <c r="AK39" s="54"/>
-      <c r="AL39" s="54"/>
-      <c r="AM39" s="54"/>
-      <c r="AN39" s="54"/>
-      <c r="AO39" s="55"/>
+      <c r="AJ39" s="43"/>
+      <c r="AK39" s="43"/>
+      <c r="AL39" s="43"/>
+      <c r="AM39" s="43"/>
+      <c r="AN39" s="43"/>
+      <c r="AO39" s="44"/>
       <c r="AQ39" s="12"/>
       <c r="AU39" s="8">
         <v>2</v>
@@ -3672,11 +3681,11 @@
       <c r="G41" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="I41" s="43" t="s">
+      <c r="I41" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="J41" s="43"/>
-      <c r="K41" s="43"/>
+      <c r="J41" s="50"/>
+      <c r="K41" s="50"/>
       <c r="L41" s="12"/>
       <c r="M41" s="7">
         <v>1</v>
@@ -3729,11 +3738,11 @@
       <c r="AO41" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="AQ41" s="44" t="s">
+      <c r="AQ41" s="54" t="s">
         <v>23</v>
       </c>
-      <c r="AR41" s="43"/>
-      <c r="AS41" s="43"/>
+      <c r="AR41" s="50"/>
+      <c r="AS41" s="50"/>
       <c r="AU41" s="38">
         <v>4</v>
       </c>
@@ -4006,15 +4015,15 @@
       <c r="BA44" s="6"/>
     </row>
     <row r="45" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="42" t="s">
+      <c r="A45" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="B45" s="42"/>
-      <c r="C45" s="42"/>
-      <c r="D45" s="42"/>
-      <c r="E45" s="42"/>
-      <c r="F45" s="42"/>
-      <c r="G45" s="42"/>
+      <c r="B45" s="49"/>
+      <c r="C45" s="49"/>
+      <c r="D45" s="49"/>
+      <c r="E45" s="49"/>
+      <c r="F45" s="49"/>
+      <c r="G45" s="49"/>
       <c r="M45" s="8" t="s">
         <v>11</v>
       </c>
@@ -4054,15 +4063,15 @@
       </c>
       <c r="AN45" s="13"/>
       <c r="AO45" s="16"/>
-      <c r="AU45" s="42" t="s">
+      <c r="AU45" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AV45" s="42"/>
-      <c r="AW45" s="42"/>
-      <c r="AX45" s="42"/>
-      <c r="AY45" s="42"/>
-      <c r="AZ45" s="42"/>
-      <c r="BA45" s="42"/>
+      <c r="AV45" s="49"/>
+      <c r="AW45" s="49"/>
+      <c r="AX45" s="49"/>
+      <c r="AY45" s="49"/>
+      <c r="AZ45" s="49"/>
+      <c r="BA45" s="49"/>
     </row>
     <row r="46" spans="1:54" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="M46" s="8" t="s">
@@ -4147,45 +4156,65 @@
       <c r="AO47" s="6"/>
     </row>
     <row r="48" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="M48" s="53" t="s">
+      <c r="M48" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="N48" s="54"/>
-      <c r="O48" s="54"/>
-      <c r="P48" s="54"/>
-      <c r="Q48" s="54"/>
-      <c r="R48" s="54"/>
-      <c r="S48" s="55"/>
-      <c r="X48" s="42" t="s">
+      <c r="N48" s="43"/>
+      <c r="O48" s="43"/>
+      <c r="P48" s="43"/>
+      <c r="Q48" s="43"/>
+      <c r="R48" s="43"/>
+      <c r="S48" s="44"/>
+      <c r="X48" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="Y48" s="42"/>
-      <c r="Z48" s="42"/>
-      <c r="AA48" s="42"/>
-      <c r="AB48" s="42"/>
-      <c r="AC48" s="42"/>
-      <c r="AD48" s="42"/>
-      <c r="AI48" s="42" t="s">
+      <c r="Y48" s="49"/>
+      <c r="Z48" s="49"/>
+      <c r="AA48" s="49"/>
+      <c r="AB48" s="49"/>
+      <c r="AC48" s="49"/>
+      <c r="AD48" s="49"/>
+      <c r="AI48" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AJ48" s="42"/>
-      <c r="AK48" s="42"/>
-      <c r="AL48" s="42"/>
-      <c r="AM48" s="42"/>
-      <c r="AN48" s="42"/>
-      <c r="AO48" s="42"/>
+      <c r="AJ48" s="49"/>
+      <c r="AK48" s="49"/>
+      <c r="AL48" s="49"/>
+      <c r="AM48" s="49"/>
+      <c r="AN48" s="49"/>
+      <c r="AO48" s="49"/>
     </row>
     <row r="49" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="M48:S48"/>
-    <mergeCell ref="M39:S39"/>
-    <mergeCell ref="P37:V37"/>
-    <mergeCell ref="P28:V28"/>
-    <mergeCell ref="A36:G36"/>
-    <mergeCell ref="A45:G45"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="AU45:BA45"/>
+    <mergeCell ref="AF28:AL28"/>
+    <mergeCell ref="AF37:AL37"/>
+    <mergeCell ref="AQ30:AS30"/>
+    <mergeCell ref="AQ41:AS41"/>
+    <mergeCell ref="AU34:BA34"/>
+    <mergeCell ref="AU36:BA36"/>
+    <mergeCell ref="AU2:BA2"/>
+    <mergeCell ref="AU3:BA3"/>
+    <mergeCell ref="AU12:BA12"/>
+    <mergeCell ref="AU14:BA14"/>
+    <mergeCell ref="AU23:BA23"/>
+    <mergeCell ref="X37:AD37"/>
+    <mergeCell ref="AE26:AM26"/>
+    <mergeCell ref="Z1:AB1"/>
+    <mergeCell ref="X39:AD39"/>
+    <mergeCell ref="X48:AD48"/>
+    <mergeCell ref="AF1:BA1"/>
+    <mergeCell ref="AI2:AO2"/>
+    <mergeCell ref="AI3:AO3"/>
+    <mergeCell ref="AI12:AO12"/>
+    <mergeCell ref="AI39:AO39"/>
+    <mergeCell ref="AU25:BA25"/>
+    <mergeCell ref="AI48:AO48"/>
+    <mergeCell ref="AN14:AP14"/>
+    <mergeCell ref="AN36:AP36"/>
+    <mergeCell ref="AQ8:AS8"/>
+    <mergeCell ref="AQ19:AS19"/>
     <mergeCell ref="A1:U1"/>
     <mergeCell ref="O26:W26"/>
     <mergeCell ref="I41:K41"/>
@@ -4202,34 +4231,14 @@
     <mergeCell ref="I8:K8"/>
     <mergeCell ref="I19:K19"/>
     <mergeCell ref="A25:G25"/>
-    <mergeCell ref="X37:AD37"/>
-    <mergeCell ref="AE26:AM26"/>
-    <mergeCell ref="Z1:AB1"/>
-    <mergeCell ref="X39:AD39"/>
-    <mergeCell ref="X48:AD48"/>
-    <mergeCell ref="AF1:BA1"/>
-    <mergeCell ref="AI2:AO2"/>
-    <mergeCell ref="AI3:AO3"/>
-    <mergeCell ref="AI12:AO12"/>
-    <mergeCell ref="AI39:AO39"/>
-    <mergeCell ref="AU25:BA25"/>
-    <mergeCell ref="AI48:AO48"/>
-    <mergeCell ref="AN14:AP14"/>
-    <mergeCell ref="AN36:AP36"/>
-    <mergeCell ref="AQ8:AS8"/>
-    <mergeCell ref="AQ19:AS19"/>
-    <mergeCell ref="AU2:BA2"/>
-    <mergeCell ref="AU3:BA3"/>
-    <mergeCell ref="AU12:BA12"/>
-    <mergeCell ref="AU14:BA14"/>
-    <mergeCell ref="AU23:BA23"/>
-    <mergeCell ref="AU45:BA45"/>
-    <mergeCell ref="AF28:AL28"/>
-    <mergeCell ref="AF37:AL37"/>
-    <mergeCell ref="AQ30:AS30"/>
-    <mergeCell ref="AQ41:AS41"/>
-    <mergeCell ref="AU34:BA34"/>
-    <mergeCell ref="AU36:BA36"/>
+    <mergeCell ref="M48:S48"/>
+    <mergeCell ref="M39:S39"/>
+    <mergeCell ref="P37:V37"/>
+    <mergeCell ref="P28:V28"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="A34:G34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/2025_2026/Playoffs/Brackets.xlsx
+++ b/2025_2026/Playoffs/Brackets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\NHLStats\2025_2026\Playoffs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{061F8F85-DEE7-4620-89B4-4CC9304B9511}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF8E2276-1AEF-4DE4-937C-E8594DC990C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="90">
   <si>
     <t>Eastern Conference Playoff Teams</t>
   </si>
@@ -293,6 +293,9 @@
   </si>
   <si>
     <t>Avalanche Leads 2-0</t>
+  </si>
+  <si>
+    <t>Golden Knights lead 2-1</t>
   </si>
 </sst>
 </file>
@@ -671,6 +674,39 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -689,46 +725,13 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1098,18 +1101,18 @@
     </row>
     <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="11" spans="1:7" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="61" t="s">
+      <c r="A11" s="59" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="61"/>
-      <c r="C11" s="61" t="s">
+      <c r="B11" s="59"/>
+      <c r="C11" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="61"/>
-      <c r="E11" s="61" t="s">
+      <c r="D11" s="59"/>
+      <c r="E11" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="61"/>
+      <c r="F11" s="59"/>
       <c r="G11" s="4" t="s">
         <v>18</v>
       </c>
@@ -1138,18 +1141,18 @@
       </c>
     </row>
     <row r="13" spans="1:7" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="59" t="s">
+      <c r="A13" s="60" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="60"/>
-      <c r="C13" s="59" t="s">
+      <c r="B13" s="61"/>
+      <c r="C13" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="D13" s="60"/>
-      <c r="E13" s="59" t="s">
+      <c r="D13" s="61"/>
+      <c r="E13" s="60" t="s">
         <v>17</v>
       </c>
-      <c r="F13" s="60"/>
+      <c r="F13" s="61"/>
       <c r="G13" s="5"/>
     </row>
     <row r="14" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1186,14 +1189,14 @@
       <c r="F15" s="6"/>
     </row>
     <row r="16" spans="1:7" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="59" t="s">
+      <c r="A16" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="60"/>
-      <c r="C16" s="59" t="s">
+      <c r="B16" s="61"/>
+      <c r="C16" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="60"/>
+      <c r="D16" s="61"/>
     </row>
     <row r="17" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
@@ -1224,10 +1227,10 @@
       </c>
     </row>
     <row r="19" spans="1:4" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="59" t="s">
+      <c r="A19" s="60" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="60"/>
+      <c r="B19" s="61"/>
     </row>
     <row r="20" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
@@ -1246,10 +1249,10 @@
       </c>
     </row>
     <row r="22" spans="1:4" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="59" t="s">
+      <c r="A22" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="60"/>
+      <c r="B22" s="61"/>
     </row>
     <row r="23" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
@@ -1334,16 +1337,16 @@
     <sortCondition ref="B2:B9"/>
   </sortState>
   <mergeCells count="10">
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C16:D16"/>
     <mergeCell ref="E11:F11"/>
     <mergeCell ref="E13:F13"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C16:D16"/>
   </mergeCells>
   <dataValidations count="16">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C14" xr:uid="{2C3D9587-ABAE-4E3F-8B22-396DF812BF02}">
@@ -1447,124 +1450,124 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:54" ht="27.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
-      <c r="M1" s="52"/>
-      <c r="N1" s="52"/>
-      <c r="O1" s="52"/>
-      <c r="P1" s="52"/>
-      <c r="Q1" s="52"/>
-      <c r="R1" s="52"/>
-      <c r="S1" s="52"/>
-      <c r="T1" s="52"/>
-      <c r="U1" s="53"/>
-      <c r="Z1" s="51" t="s">
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
+      <c r="K1" s="51"/>
+      <c r="L1" s="51"/>
+      <c r="M1" s="51"/>
+      <c r="N1" s="51"/>
+      <c r="O1" s="51"/>
+      <c r="P1" s="51"/>
+      <c r="Q1" s="51"/>
+      <c r="R1" s="51"/>
+      <c r="S1" s="51"/>
+      <c r="T1" s="51"/>
+      <c r="U1" s="52"/>
+      <c r="Z1" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="AA1" s="52"/>
-      <c r="AB1" s="53"/>
-      <c r="AF1" s="51" t="s">
+      <c r="AA1" s="51"/>
+      <c r="AB1" s="52"/>
+      <c r="AF1" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="AG1" s="52"/>
-      <c r="AH1" s="52"/>
-      <c r="AI1" s="52"/>
-      <c r="AJ1" s="52"/>
-      <c r="AK1" s="52"/>
-      <c r="AL1" s="52"/>
-      <c r="AM1" s="52"/>
-      <c r="AN1" s="52"/>
-      <c r="AO1" s="52"/>
-      <c r="AP1" s="52"/>
-      <c r="AQ1" s="52"/>
-      <c r="AR1" s="52"/>
-      <c r="AS1" s="52"/>
-      <c r="AT1" s="52"/>
-      <c r="AU1" s="52"/>
-      <c r="AV1" s="52"/>
-      <c r="AW1" s="52"/>
-      <c r="AX1" s="52"/>
-      <c r="AY1" s="52"/>
-      <c r="AZ1" s="52"/>
-      <c r="BA1" s="53"/>
+      <c r="AG1" s="51"/>
+      <c r="AH1" s="51"/>
+      <c r="AI1" s="51"/>
+      <c r="AJ1" s="51"/>
+      <c r="AK1" s="51"/>
+      <c r="AL1" s="51"/>
+      <c r="AM1" s="51"/>
+      <c r="AN1" s="51"/>
+      <c r="AO1" s="51"/>
+      <c r="AP1" s="51"/>
+      <c r="AQ1" s="51"/>
+      <c r="AR1" s="51"/>
+      <c r="AS1" s="51"/>
+      <c r="AT1" s="51"/>
+      <c r="AU1" s="51"/>
+      <c r="AV1" s="51"/>
+      <c r="AW1" s="51"/>
+      <c r="AX1" s="51"/>
+      <c r="AY1" s="51"/>
+      <c r="AZ1" s="51"/>
+      <c r="BA1" s="52"/>
     </row>
     <row r="2" spans="1:54" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="55" t="s">
+      <c r="A2" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="57"/>
-      <c r="M2" s="55" t="s">
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="48"/>
+      <c r="M2" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="56"/>
-      <c r="O2" s="56"/>
-      <c r="P2" s="56"/>
-      <c r="Q2" s="56"/>
-      <c r="R2" s="57"/>
-      <c r="AI2" s="55" t="s">
+      <c r="N2" s="47"/>
+      <c r="O2" s="47"/>
+      <c r="P2" s="47"/>
+      <c r="Q2" s="47"/>
+      <c r="R2" s="48"/>
+      <c r="AI2" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="AJ2" s="56"/>
-      <c r="AK2" s="56"/>
-      <c r="AL2" s="56"/>
-      <c r="AM2" s="56"/>
-      <c r="AN2" s="56"/>
-      <c r="AO2" s="57"/>
-      <c r="AU2" s="55" t="s">
+      <c r="AJ2" s="47"/>
+      <c r="AK2" s="47"/>
+      <c r="AL2" s="47"/>
+      <c r="AM2" s="47"/>
+      <c r="AN2" s="47"/>
+      <c r="AO2" s="48"/>
+      <c r="AU2" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="AV2" s="56"/>
-      <c r="AW2" s="56"/>
-      <c r="AX2" s="56"/>
-      <c r="AY2" s="56"/>
-      <c r="AZ2" s="56"/>
-      <c r="BA2" s="57"/>
+      <c r="AV2" s="47"/>
+      <c r="AW2" s="47"/>
+      <c r="AX2" s="47"/>
+      <c r="AY2" s="47"/>
+      <c r="AZ2" s="47"/>
+      <c r="BA2" s="48"/>
     </row>
     <row r="3" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="49" t="s">
+      <c r="A3" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="49"/>
-      <c r="C3" s="49"/>
-      <c r="D3" s="49"/>
-      <c r="E3" s="49"/>
-      <c r="F3" s="49"/>
-      <c r="G3" s="49"/>
-      <c r="AI3" s="42" t="s">
+      <c r="B3" s="42"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="42"/>
+      <c r="AI3" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="AJ3" s="43"/>
-      <c r="AK3" s="43"/>
-      <c r="AL3" s="43"/>
-      <c r="AM3" s="43"/>
-      <c r="AN3" s="43"/>
-      <c r="AO3" s="44"/>
-      <c r="AU3" s="49" t="s">
+      <c r="AJ3" s="54"/>
+      <c r="AK3" s="54"/>
+      <c r="AL3" s="54"/>
+      <c r="AM3" s="54"/>
+      <c r="AN3" s="54"/>
+      <c r="AO3" s="55"/>
+      <c r="AU3" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="AV3" s="49"/>
-      <c r="AW3" s="49"/>
-      <c r="AX3" s="49"/>
-      <c r="AY3" s="49"/>
-      <c r="AZ3" s="49"/>
-      <c r="BA3" s="49"/>
+      <c r="AV3" s="42"/>
+      <c r="AW3" s="42"/>
+      <c r="AX3" s="42"/>
+      <c r="AY3" s="42"/>
+      <c r="AZ3" s="42"/>
+      <c r="BA3" s="42"/>
     </row>
     <row r="4" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
@@ -1588,15 +1591,15 @@
       <c r="G4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="42" t="s">
+      <c r="M4" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="N4" s="43"/>
-      <c r="O4" s="43"/>
-      <c r="P4" s="43"/>
-      <c r="Q4" s="43"/>
-      <c r="R4" s="43"/>
-      <c r="S4" s="44"/>
+      <c r="N4" s="54"/>
+      <c r="O4" s="54"/>
+      <c r="P4" s="54"/>
+      <c r="Q4" s="54"/>
+      <c r="R4" s="54"/>
+      <c r="S4" s="55"/>
       <c r="AI4" s="3" t="s">
         <v>2</v>
       </c>
@@ -1757,12 +1760,18 @@
       <c r="O6" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="P6" s="11"/>
+      <c r="P6" s="11">
+        <v>2</v>
+      </c>
       <c r="Q6" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="R6" s="11"/>
-      <c r="S6" s="5"/>
+      <c r="R6" s="11">
+        <v>4</v>
+      </c>
+      <c r="S6" s="5" t="s">
+        <v>51</v>
+      </c>
       <c r="AI6" s="8">
         <v>2</v>
       </c>
@@ -1840,12 +1849,18 @@
       <c r="O7" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="P7" s="13"/>
+      <c r="P7" s="13">
+        <v>5</v>
+      </c>
       <c r="Q7" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="R7" s="13"/>
-      <c r="S7" s="16"/>
+      <c r="R7" s="13">
+        <v>1</v>
+      </c>
+      <c r="S7" s="16" t="s">
+        <v>56</v>
+      </c>
       <c r="AI7" s="8">
         <v>3</v>
       </c>
@@ -1905,11 +1920,11 @@
       <c r="G8" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="I8" s="50" t="s">
+      <c r="I8" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="J8" s="50"/>
-      <c r="K8" s="50"/>
+      <c r="J8" s="43"/>
+      <c r="K8" s="43"/>
       <c r="M8" s="8">
         <v>3</v>
       </c>
@@ -1940,11 +1955,11 @@
       </c>
       <c r="AN8" s="31"/>
       <c r="AO8" s="16"/>
-      <c r="AQ8" s="50" t="s">
+      <c r="AQ8" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="AR8" s="50"/>
-      <c r="AS8" s="50"/>
+      <c r="AR8" s="43"/>
+      <c r="AS8" s="43"/>
       <c r="AU8" s="38">
         <v>4</v>
       </c>
@@ -2177,15 +2192,15 @@
       <c r="BA11" s="6"/>
     </row>
     <row r="12" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="49" t="s">
+      <c r="A12" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="49"/>
-      <c r="C12" s="49"/>
-      <c r="D12" s="49"/>
-      <c r="E12" s="49"/>
-      <c r="F12" s="49"/>
-      <c r="G12" s="49"/>
+      <c r="B12" s="42"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="42"/>
       <c r="L12" s="12"/>
       <c r="M12" s="8" t="s">
         <v>12</v>
@@ -2202,65 +2217,65 @@
       </c>
       <c r="R12" s="13"/>
       <c r="S12" s="16"/>
-      <c r="AI12" s="49" t="s">
+      <c r="AI12" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AJ12" s="49"/>
-      <c r="AK12" s="49"/>
-      <c r="AL12" s="49"/>
-      <c r="AM12" s="49"/>
-      <c r="AN12" s="49"/>
-      <c r="AO12" s="49"/>
+      <c r="AJ12" s="42"/>
+      <c r="AK12" s="42"/>
+      <c r="AL12" s="42"/>
+      <c r="AM12" s="42"/>
+      <c r="AN12" s="42"/>
+      <c r="AO12" s="42"/>
       <c r="AQ12" s="12"/>
-      <c r="AU12" s="49" t="s">
+      <c r="AU12" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AV12" s="49"/>
-      <c r="AW12" s="49"/>
-      <c r="AX12" s="49"/>
-      <c r="AY12" s="49"/>
-      <c r="AZ12" s="49"/>
-      <c r="BA12" s="49"/>
+      <c r="AV12" s="42"/>
+      <c r="AW12" s="42"/>
+      <c r="AX12" s="42"/>
+      <c r="AY12" s="42"/>
+      <c r="AZ12" s="42"/>
+      <c r="BA12" s="42"/>
     </row>
     <row r="13" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L13" s="12"/>
-      <c r="M13" s="42" t="s">
+      <c r="M13" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="N13" s="43"/>
-      <c r="O13" s="43"/>
-      <c r="P13" s="43"/>
-      <c r="Q13" s="43"/>
-      <c r="R13" s="43"/>
-      <c r="S13" s="44"/>
+      <c r="N13" s="54"/>
+      <c r="O13" s="54"/>
+      <c r="P13" s="54"/>
+      <c r="Q13" s="54"/>
+      <c r="R13" s="54"/>
+      <c r="S13" s="55"/>
       <c r="AQ13" s="12"/>
     </row>
     <row r="14" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="48" t="s">
+      <c r="A14" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="48"/>
-      <c r="C14" s="48"/>
-      <c r="D14" s="48"/>
-      <c r="E14" s="48"/>
-      <c r="F14" s="48"/>
-      <c r="G14" s="48"/>
-      <c r="L14" s="54"/>
-      <c r="M14" s="50"/>
-      <c r="N14" s="50"/>
-      <c r="AN14" s="50"/>
-      <c r="AO14" s="50"/>
-      <c r="AP14" s="50"/>
+      <c r="B14" s="45"/>
+      <c r="C14" s="45"/>
+      <c r="D14" s="45"/>
+      <c r="E14" s="45"/>
+      <c r="F14" s="45"/>
+      <c r="G14" s="45"/>
+      <c r="L14" s="44"/>
+      <c r="M14" s="43"/>
+      <c r="N14" s="43"/>
+      <c r="AN14" s="43"/>
+      <c r="AO14" s="43"/>
+      <c r="AP14" s="43"/>
       <c r="AQ14" s="12"/>
-      <c r="AU14" s="48" t="s">
+      <c r="AU14" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="AV14" s="48"/>
-      <c r="AW14" s="48"/>
-      <c r="AX14" s="48"/>
-      <c r="AY14" s="48"/>
-      <c r="AZ14" s="48"/>
-      <c r="BA14" s="48"/>
+      <c r="AV14" s="45"/>
+      <c r="AW14" s="45"/>
+      <c r="AX14" s="45"/>
+      <c r="AY14" s="45"/>
+      <c r="AZ14" s="45"/>
+      <c r="BA14" s="45"/>
     </row>
     <row r="15" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
@@ -2488,19 +2503,19 @@
       <c r="G19" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="I19" s="50" t="s">
+      <c r="I19" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="J19" s="50"/>
-      <c r="K19" s="50"/>
+      <c r="J19" s="43"/>
+      <c r="K19" s="43"/>
       <c r="L19" s="12"/>
       <c r="O19" s="12"/>
       <c r="AN19" s="12"/>
-      <c r="AQ19" s="54" t="s">
+      <c r="AQ19" s="44" t="s">
         <v>31</v>
       </c>
-      <c r="AR19" s="50"/>
-      <c r="AS19" s="50"/>
+      <c r="AR19" s="43"/>
+      <c r="AS19" s="43"/>
       <c r="AU19" s="38">
         <v>4</v>
       </c>
@@ -2662,52 +2677,52 @@
       <c r="BA22" s="6"/>
     </row>
     <row r="23" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="49" t="s">
+      <c r="A23" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B23" s="49"/>
-      <c r="C23" s="49"/>
-      <c r="D23" s="49"/>
-      <c r="E23" s="49"/>
-      <c r="F23" s="49"/>
-      <c r="G23" s="49"/>
+      <c r="B23" s="42"/>
+      <c r="C23" s="42"/>
+      <c r="D23" s="42"/>
+      <c r="E23" s="42"/>
+      <c r="F23" s="42"/>
+      <c r="G23" s="42"/>
       <c r="O23" s="12"/>
       <c r="AN23" s="12"/>
-      <c r="AU23" s="49" t="s">
+      <c r="AU23" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AV23" s="49"/>
-      <c r="AW23" s="49"/>
-      <c r="AX23" s="49"/>
-      <c r="AY23" s="49"/>
-      <c r="AZ23" s="49"/>
-      <c r="BA23" s="49"/>
+      <c r="AV23" s="42"/>
+      <c r="AW23" s="42"/>
+      <c r="AX23" s="42"/>
+      <c r="AY23" s="42"/>
+      <c r="AZ23" s="42"/>
+      <c r="BA23" s="42"/>
     </row>
     <row r="24" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="O24" s="12"/>
       <c r="AN24" s="12"/>
     </row>
     <row r="25" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="49" t="s">
+      <c r="A25" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="49"/>
-      <c r="C25" s="49"/>
-      <c r="D25" s="49"/>
-      <c r="E25" s="49"/>
-      <c r="F25" s="49"/>
-      <c r="G25" s="49"/>
+      <c r="B25" s="42"/>
+      <c r="C25" s="42"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="42"/>
+      <c r="F25" s="42"/>
+      <c r="G25" s="42"/>
       <c r="O25" s="12"/>
       <c r="AN25" s="12"/>
-      <c r="AU25" s="49" t="s">
+      <c r="AU25" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="AV25" s="49"/>
-      <c r="AW25" s="49"/>
-      <c r="AX25" s="49"/>
-      <c r="AY25" s="49"/>
-      <c r="AZ25" s="49"/>
-      <c r="BA25" s="49"/>
+      <c r="AV25" s="42"/>
+      <c r="AW25" s="42"/>
+      <c r="AX25" s="42"/>
+      <c r="AY25" s="42"/>
+      <c r="AZ25" s="42"/>
+      <c r="BA25" s="42"/>
     </row>
     <row r="26" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="20" t="s">
@@ -2731,24 +2746,24 @@
       <c r="G26" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="O26" s="54"/>
-      <c r="P26" s="50"/>
-      <c r="Q26" s="50"/>
-      <c r="R26" s="50"/>
-      <c r="S26" s="50"/>
-      <c r="T26" s="50"/>
-      <c r="U26" s="50"/>
-      <c r="V26" s="50"/>
-      <c r="W26" s="50"/>
-      <c r="AE26" s="50"/>
-      <c r="AF26" s="50"/>
-      <c r="AG26" s="50"/>
-      <c r="AH26" s="50"/>
-      <c r="AI26" s="50"/>
-      <c r="AJ26" s="50"/>
-      <c r="AK26" s="50"/>
-      <c r="AL26" s="50"/>
-      <c r="AM26" s="58"/>
+      <c r="O26" s="44"/>
+      <c r="P26" s="43"/>
+      <c r="Q26" s="43"/>
+      <c r="R26" s="43"/>
+      <c r="S26" s="43"/>
+      <c r="T26" s="43"/>
+      <c r="U26" s="43"/>
+      <c r="V26" s="43"/>
+      <c r="W26" s="43"/>
+      <c r="AE26" s="43"/>
+      <c r="AF26" s="43"/>
+      <c r="AG26" s="43"/>
+      <c r="AH26" s="43"/>
+      <c r="AI26" s="43"/>
+      <c r="AJ26" s="43"/>
+      <c r="AK26" s="43"/>
+      <c r="AL26" s="43"/>
+      <c r="AM26" s="49"/>
       <c r="AU26" s="20" t="s">
         <v>2</v>
       </c>
@@ -2845,26 +2860,26 @@
         <v>54</v>
       </c>
       <c r="O28" s="12"/>
-      <c r="P28" s="42" t="s">
+      <c r="P28" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="Q28" s="43"/>
-      <c r="R28" s="43"/>
-      <c r="S28" s="43"/>
-      <c r="T28" s="43"/>
-      <c r="U28" s="43"/>
-      <c r="V28" s="44"/>
+      <c r="Q28" s="54"/>
+      <c r="R28" s="54"/>
+      <c r="S28" s="54"/>
+      <c r="T28" s="54"/>
+      <c r="U28" s="54"/>
+      <c r="V28" s="55"/>
       <c r="X28" s="12"/>
       <c r="AD28" s="13"/>
-      <c r="AF28" s="49" t="s">
+      <c r="AF28" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="AG28" s="49"/>
-      <c r="AH28" s="49"/>
-      <c r="AI28" s="49"/>
-      <c r="AJ28" s="49"/>
-      <c r="AK28" s="49"/>
-      <c r="AL28" s="49"/>
+      <c r="AG28" s="42"/>
+      <c r="AH28" s="42"/>
+      <c r="AI28" s="42"/>
+      <c r="AJ28" s="42"/>
+      <c r="AK28" s="42"/>
+      <c r="AL28" s="42"/>
       <c r="AN28" s="12"/>
       <c r="AU28" s="8">
         <v>2</v>
@@ -3000,11 +3015,11 @@
       <c r="G30" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="I30" s="50" t="s">
+      <c r="I30" s="43" t="s">
         <v>26</v>
       </c>
-      <c r="J30" s="50"/>
-      <c r="K30" s="50"/>
+      <c r="J30" s="43"/>
+      <c r="K30" s="43"/>
       <c r="O30" s="12"/>
       <c r="P30" s="7">
         <v>1</v>
@@ -3027,11 +3042,11 @@
       <c r="AK30" s="24"/>
       <c r="AL30" s="25"/>
       <c r="AN30" s="12"/>
-      <c r="AQ30" s="50" t="s">
+      <c r="AQ30" s="43" t="s">
         <v>38</v>
       </c>
-      <c r="AR30" s="50"/>
-      <c r="AS30" s="50"/>
+      <c r="AR30" s="43"/>
+      <c r="AS30" s="43"/>
       <c r="AU30" s="38">
         <v>4</v>
       </c>
@@ -3243,15 +3258,15 @@
       <c r="BA33" s="6"/>
     </row>
     <row r="34" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="49" t="s">
+      <c r="A34" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B34" s="49"/>
-      <c r="C34" s="49"/>
-      <c r="D34" s="49"/>
-      <c r="E34" s="49"/>
-      <c r="F34" s="49"/>
-      <c r="G34" s="49"/>
+      <c r="B34" s="42"/>
+      <c r="C34" s="42"/>
+      <c r="D34" s="42"/>
+      <c r="E34" s="42"/>
+      <c r="F34" s="42"/>
+      <c r="G34" s="42"/>
       <c r="L34" s="12"/>
       <c r="O34" s="12"/>
       <c r="P34" s="8" t="s">
@@ -3276,15 +3291,15 @@
       <c r="AL34" s="16"/>
       <c r="AN34" s="12"/>
       <c r="AQ34" s="12"/>
-      <c r="AU34" s="49" t="s">
+      <c r="AU34" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AV34" s="49"/>
-      <c r="AW34" s="49"/>
-      <c r="AX34" s="49"/>
-      <c r="AY34" s="49"/>
-      <c r="AZ34" s="49"/>
-      <c r="BA34" s="49"/>
+      <c r="AV34" s="42"/>
+      <c r="AW34" s="42"/>
+      <c r="AX34" s="42"/>
+      <c r="AY34" s="42"/>
+      <c r="AZ34" s="42"/>
+      <c r="BA34" s="42"/>
     </row>
     <row r="35" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L35" s="12"/>
@@ -3313,18 +3328,18 @@
       <c r="AQ35" s="12"/>
     </row>
     <row r="36" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="48" t="s">
+      <c r="A36" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="B36" s="48"/>
-      <c r="C36" s="48"/>
-      <c r="D36" s="48"/>
-      <c r="E36" s="48"/>
-      <c r="F36" s="48"/>
-      <c r="G36" s="48"/>
-      <c r="L36" s="54"/>
-      <c r="M36" s="50"/>
-      <c r="N36" s="50"/>
+      <c r="B36" s="45"/>
+      <c r="C36" s="45"/>
+      <c r="D36" s="45"/>
+      <c r="E36" s="45"/>
+      <c r="F36" s="45"/>
+      <c r="G36" s="45"/>
+      <c r="L36" s="44"/>
+      <c r="M36" s="43"/>
+      <c r="N36" s="43"/>
       <c r="O36" s="12"/>
       <c r="P36" s="8" t="s">
         <v>12</v>
@@ -3346,19 +3361,19 @@
       <c r="AJ36" s="35"/>
       <c r="AK36" s="36"/>
       <c r="AL36" s="37"/>
-      <c r="AN36" s="54"/>
-      <c r="AO36" s="50"/>
-      <c r="AP36" s="50"/>
+      <c r="AN36" s="44"/>
+      <c r="AO36" s="43"/>
+      <c r="AP36" s="43"/>
       <c r="AQ36" s="12"/>
-      <c r="AU36" s="48" t="s">
+      <c r="AU36" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="AV36" s="48"/>
-      <c r="AW36" s="48"/>
-      <c r="AX36" s="48"/>
-      <c r="AY36" s="48"/>
-      <c r="AZ36" s="48"/>
-      <c r="BA36" s="48"/>
+      <c r="AV36" s="45"/>
+      <c r="AW36" s="45"/>
+      <c r="AX36" s="45"/>
+      <c r="AY36" s="45"/>
+      <c r="AZ36" s="45"/>
+      <c r="BA36" s="45"/>
     </row>
     <row r="37" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37" s="20" t="s">
@@ -3383,31 +3398,31 @@
         <v>9</v>
       </c>
       <c r="L37" s="12"/>
-      <c r="P37" s="45" t="s">
+      <c r="P37" s="56" t="s">
         <v>13</v>
       </c>
-      <c r="Q37" s="46"/>
-      <c r="R37" s="46"/>
-      <c r="S37" s="46"/>
-      <c r="T37" s="46"/>
-      <c r="U37" s="46"/>
-      <c r="V37" s="47"/>
-      <c r="X37" s="54"/>
-      <c r="Y37" s="50"/>
-      <c r="Z37" s="50"/>
-      <c r="AA37" s="50"/>
-      <c r="AB37" s="50"/>
-      <c r="AC37" s="50"/>
-      <c r="AD37" s="58"/>
-      <c r="AF37" s="49" t="s">
+      <c r="Q37" s="57"/>
+      <c r="R37" s="57"/>
+      <c r="S37" s="57"/>
+      <c r="T37" s="57"/>
+      <c r="U37" s="57"/>
+      <c r="V37" s="58"/>
+      <c r="X37" s="44"/>
+      <c r="Y37" s="43"/>
+      <c r="Z37" s="43"/>
+      <c r="AA37" s="43"/>
+      <c r="AB37" s="43"/>
+      <c r="AC37" s="43"/>
+      <c r="AD37" s="49"/>
+      <c r="AF37" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AG37" s="49"/>
-      <c r="AH37" s="49"/>
-      <c r="AI37" s="49"/>
-      <c r="AJ37" s="49"/>
-      <c r="AK37" s="49"/>
-      <c r="AL37" s="49"/>
+      <c r="AG37" s="42"/>
+      <c r="AH37" s="42"/>
+      <c r="AI37" s="42"/>
+      <c r="AJ37" s="42"/>
+      <c r="AK37" s="42"/>
+      <c r="AL37" s="42"/>
       <c r="AQ37" s="12"/>
       <c r="AU37" s="3" t="s">
         <v>2</v>
@@ -3500,33 +3515,33 @@
         <v>53</v>
       </c>
       <c r="L39" s="12"/>
-      <c r="M39" s="42" t="s">
+      <c r="M39" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="N39" s="43"/>
-      <c r="O39" s="43"/>
-      <c r="P39" s="43"/>
-      <c r="Q39" s="43"/>
-      <c r="R39" s="43"/>
-      <c r="S39" s="44"/>
-      <c r="X39" s="49" t="s">
+      <c r="N39" s="54"/>
+      <c r="O39" s="54"/>
+      <c r="P39" s="54"/>
+      <c r="Q39" s="54"/>
+      <c r="R39" s="54"/>
+      <c r="S39" s="55"/>
+      <c r="X39" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="Y39" s="49"/>
-      <c r="Z39" s="49"/>
-      <c r="AA39" s="49"/>
-      <c r="AB39" s="49"/>
-      <c r="AC39" s="49"/>
-      <c r="AD39" s="49"/>
-      <c r="AI39" s="42" t="s">
+      <c r="Y39" s="42"/>
+      <c r="Z39" s="42"/>
+      <c r="AA39" s="42"/>
+      <c r="AB39" s="42"/>
+      <c r="AC39" s="42"/>
+      <c r="AD39" s="42"/>
+      <c r="AI39" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="AJ39" s="43"/>
-      <c r="AK39" s="43"/>
-      <c r="AL39" s="43"/>
-      <c r="AM39" s="43"/>
-      <c r="AN39" s="43"/>
-      <c r="AO39" s="44"/>
+      <c r="AJ39" s="54"/>
+      <c r="AK39" s="54"/>
+      <c r="AL39" s="54"/>
+      <c r="AM39" s="54"/>
+      <c r="AN39" s="54"/>
+      <c r="AO39" s="55"/>
       <c r="AQ39" s="12"/>
       <c r="AU39" s="8">
         <v>2</v>
@@ -3681,11 +3696,11 @@
       <c r="G41" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="I41" s="50" t="s">
+      <c r="I41" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="J41" s="50"/>
-      <c r="K41" s="50"/>
+      <c r="J41" s="43"/>
+      <c r="K41" s="43"/>
       <c r="L41" s="12"/>
       <c r="M41" s="7">
         <v>1</v>
@@ -3738,11 +3753,11 @@
       <c r="AO41" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="AQ41" s="54" t="s">
+      <c r="AQ41" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="AR41" s="50"/>
-      <c r="AS41" s="50"/>
+      <c r="AR41" s="43"/>
+      <c r="AS41" s="43"/>
       <c r="AU41" s="38">
         <v>4</v>
       </c>
@@ -3829,12 +3844,18 @@
       <c r="AK42" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="AL42" s="13"/>
+      <c r="AL42" s="13">
+        <v>3</v>
+      </c>
       <c r="AM42" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="AN42" s="13"/>
-      <c r="AO42" s="16"/>
+      <c r="AN42" s="13">
+        <v>1</v>
+      </c>
+      <c r="AO42" s="16" t="s">
+        <v>56</v>
+      </c>
       <c r="AU42" s="8" t="s">
         <v>11</v>
       </c>
@@ -3891,12 +3912,18 @@
       <c r="O43" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="P43" s="13"/>
+      <c r="P43" s="13">
+        <v>4</v>
+      </c>
       <c r="Q43" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="R43" s="13"/>
-      <c r="S43" s="16"/>
+      <c r="R43" s="13">
+        <v>1</v>
+      </c>
+      <c r="S43" s="16" t="s">
+        <v>62</v>
+      </c>
       <c r="X43" s="8">
         <v>3</v>
       </c>
@@ -3915,12 +3942,18 @@
       <c r="AK43" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="AL43" s="13"/>
+      <c r="AL43" s="13">
+        <v>6</v>
+      </c>
       <c r="AM43" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="AN43" s="13"/>
-      <c r="AO43" s="16"/>
+      <c r="AN43" s="13">
+        <v>2</v>
+      </c>
+      <c r="AO43" s="16" t="s">
+        <v>89</v>
+      </c>
       <c r="AU43" s="8" t="s">
         <v>10</v>
       </c>
@@ -4015,15 +4048,15 @@
       <c r="BA44" s="6"/>
     </row>
     <row r="45" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="49" t="s">
+      <c r="A45" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B45" s="49"/>
-      <c r="C45" s="49"/>
-      <c r="D45" s="49"/>
-      <c r="E45" s="49"/>
-      <c r="F45" s="49"/>
-      <c r="G45" s="49"/>
+      <c r="B45" s="42"/>
+      <c r="C45" s="42"/>
+      <c r="D45" s="42"/>
+      <c r="E45" s="42"/>
+      <c r="F45" s="42"/>
+      <c r="G45" s="42"/>
       <c r="M45" s="8" t="s">
         <v>11</v>
       </c>
@@ -4063,15 +4096,15 @@
       </c>
       <c r="AN45" s="13"/>
       <c r="AO45" s="16"/>
-      <c r="AU45" s="49" t="s">
+      <c r="AU45" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AV45" s="49"/>
-      <c r="AW45" s="49"/>
-      <c r="AX45" s="49"/>
-      <c r="AY45" s="49"/>
-      <c r="AZ45" s="49"/>
-      <c r="BA45" s="49"/>
+      <c r="AV45" s="42"/>
+      <c r="AW45" s="42"/>
+      <c r="AX45" s="42"/>
+      <c r="AY45" s="42"/>
+      <c r="AZ45" s="42"/>
+      <c r="BA45" s="42"/>
     </row>
     <row r="46" spans="1:54" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="M46" s="8" t="s">
@@ -4156,49 +4189,61 @@
       <c r="AO47" s="6"/>
     </row>
     <row r="48" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="M48" s="42" t="s">
+      <c r="M48" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="N48" s="43"/>
-      <c r="O48" s="43"/>
-      <c r="P48" s="43"/>
-      <c r="Q48" s="43"/>
-      <c r="R48" s="43"/>
-      <c r="S48" s="44"/>
-      <c r="X48" s="49" t="s">
+      <c r="N48" s="54"/>
+      <c r="O48" s="54"/>
+      <c r="P48" s="54"/>
+      <c r="Q48" s="54"/>
+      <c r="R48" s="54"/>
+      <c r="S48" s="55"/>
+      <c r="X48" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="Y48" s="49"/>
-      <c r="Z48" s="49"/>
-      <c r="AA48" s="49"/>
-      <c r="AB48" s="49"/>
-      <c r="AC48" s="49"/>
-      <c r="AD48" s="49"/>
-      <c r="AI48" s="49" t="s">
+      <c r="Y48" s="42"/>
+      <c r="Z48" s="42"/>
+      <c r="AA48" s="42"/>
+      <c r="AB48" s="42"/>
+      <c r="AC48" s="42"/>
+      <c r="AD48" s="42"/>
+      <c r="AI48" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AJ48" s="49"/>
-      <c r="AK48" s="49"/>
-      <c r="AL48" s="49"/>
-      <c r="AM48" s="49"/>
-      <c r="AN48" s="49"/>
-      <c r="AO48" s="49"/>
+      <c r="AJ48" s="42"/>
+      <c r="AK48" s="42"/>
+      <c r="AL48" s="42"/>
+      <c r="AM48" s="42"/>
+      <c r="AN48" s="42"/>
+      <c r="AO48" s="42"/>
     </row>
     <row r="49" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="AU45:BA45"/>
-    <mergeCell ref="AF28:AL28"/>
-    <mergeCell ref="AF37:AL37"/>
-    <mergeCell ref="AQ30:AS30"/>
-    <mergeCell ref="AQ41:AS41"/>
-    <mergeCell ref="AU34:BA34"/>
-    <mergeCell ref="AU36:BA36"/>
-    <mergeCell ref="AU2:BA2"/>
-    <mergeCell ref="AU3:BA3"/>
-    <mergeCell ref="AU12:BA12"/>
-    <mergeCell ref="AU14:BA14"/>
-    <mergeCell ref="AU23:BA23"/>
+    <mergeCell ref="M48:S48"/>
+    <mergeCell ref="M39:S39"/>
+    <mergeCell ref="P37:V37"/>
+    <mergeCell ref="P28:V28"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A1:U1"/>
+    <mergeCell ref="O26:W26"/>
+    <mergeCell ref="I41:K41"/>
+    <mergeCell ref="L14:N14"/>
+    <mergeCell ref="L36:N36"/>
+    <mergeCell ref="M2:R2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="M4:S4"/>
+    <mergeCell ref="M13:S13"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="A25:G25"/>
     <mergeCell ref="X37:AD37"/>
     <mergeCell ref="AE26:AM26"/>
     <mergeCell ref="Z1:AB1"/>
@@ -4215,30 +4260,18 @@
     <mergeCell ref="AN36:AP36"/>
     <mergeCell ref="AQ8:AS8"/>
     <mergeCell ref="AQ19:AS19"/>
-    <mergeCell ref="A1:U1"/>
-    <mergeCell ref="O26:W26"/>
-    <mergeCell ref="I41:K41"/>
-    <mergeCell ref="L14:N14"/>
-    <mergeCell ref="L36:N36"/>
-    <mergeCell ref="M2:R2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="M4:S4"/>
-    <mergeCell ref="M13:S13"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A23:G23"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="M48:S48"/>
-    <mergeCell ref="M39:S39"/>
-    <mergeCell ref="P37:V37"/>
-    <mergeCell ref="P28:V28"/>
-    <mergeCell ref="A36:G36"/>
-    <mergeCell ref="A45:G45"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="AU2:BA2"/>
+    <mergeCell ref="AU3:BA3"/>
+    <mergeCell ref="AU12:BA12"/>
+    <mergeCell ref="AU14:BA14"/>
+    <mergeCell ref="AU23:BA23"/>
+    <mergeCell ref="AU45:BA45"/>
+    <mergeCell ref="AF28:AL28"/>
+    <mergeCell ref="AF37:AL37"/>
+    <mergeCell ref="AQ30:AS30"/>
+    <mergeCell ref="AQ41:AS41"/>
+    <mergeCell ref="AU34:BA34"/>
+    <mergeCell ref="AU36:BA36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/2025_2026/Playoffs/Brackets.xlsx
+++ b/2025_2026/Playoffs/Brackets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\NHLStats\2025_2026\Playoffs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF8E2276-1AEF-4DE4-937C-E8594DC990C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A2B8032-0259-4ECC-ADC4-CF0862A518EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="91">
   <si>
     <t>Eastern Conference Playoff Teams</t>
   </si>
@@ -296,6 +296,9 @@
   </si>
   <si>
     <t>Golden Knights lead 2-1</t>
+  </si>
+  <si>
+    <t>Avalanche Leads 2-1</t>
   </si>
 </sst>
 </file>
@@ -674,18 +677,45 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -698,40 +728,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1101,18 +1104,18 @@
     </row>
     <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="11" spans="1:7" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="59" t="s">
+      <c r="A11" s="61" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="59"/>
-      <c r="C11" s="59" t="s">
+      <c r="B11" s="61"/>
+      <c r="C11" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="59"/>
-      <c r="E11" s="59" t="s">
+      <c r="D11" s="61"/>
+      <c r="E11" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="59"/>
+      <c r="F11" s="61"/>
       <c r="G11" s="4" t="s">
         <v>18</v>
       </c>
@@ -1141,18 +1144,18 @@
       </c>
     </row>
     <row r="13" spans="1:7" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="60" t="s">
+      <c r="A13" s="59" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="61"/>
-      <c r="C13" s="60" t="s">
+      <c r="B13" s="60"/>
+      <c r="C13" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="D13" s="61"/>
-      <c r="E13" s="60" t="s">
+      <c r="D13" s="60"/>
+      <c r="E13" s="59" t="s">
         <v>17</v>
       </c>
-      <c r="F13" s="61"/>
+      <c r="F13" s="60"/>
       <c r="G13" s="5"/>
     </row>
     <row r="14" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1185,18 +1188,20 @@
       <c r="D15" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E15" s="6"/>
+      <c r="E15" s="6" t="s">
+        <v>26</v>
+      </c>
       <c r="F15" s="6"/>
     </row>
     <row r="16" spans="1:7" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="60" t="s">
+      <c r="A16" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="61"/>
-      <c r="C16" s="60" t="s">
+      <c r="B16" s="60"/>
+      <c r="C16" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="61"/>
+      <c r="D16" s="60"/>
     </row>
     <row r="17" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
@@ -1227,10 +1232,10 @@
       </c>
     </row>
     <row r="19" spans="1:4" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="60" t="s">
+      <c r="A19" s="59" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="61"/>
+      <c r="B19" s="60"/>
     </row>
     <row r="20" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
@@ -1249,10 +1254,10 @@
       </c>
     </row>
     <row r="22" spans="1:4" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="60" t="s">
+      <c r="A22" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="61"/>
+      <c r="B22" s="60"/>
     </row>
     <row r="23" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
@@ -1337,16 +1342,16 @@
     <sortCondition ref="B2:B9"/>
   </sortState>
   <mergeCells count="10">
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A16:B16"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A16:B16"/>
   </mergeCells>
   <dataValidations count="16">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C14" xr:uid="{2C3D9587-ABAE-4E3F-8B22-396DF812BF02}">
@@ -1421,7 +1426,7 @@
     <col min="16" max="16" width="17" style="1" customWidth="1"/>
     <col min="17" max="17" width="20.140625" style="1" customWidth="1"/>
     <col min="18" max="18" width="20.28515625" style="1" customWidth="1"/>
-    <col min="19" max="19" width="23.85546875" style="1" customWidth="1"/>
+    <col min="19" max="19" width="24.7109375" style="1" customWidth="1"/>
     <col min="20" max="20" width="23.42578125" style="1" customWidth="1"/>
     <col min="21" max="21" width="9.140625" style="1"/>
     <col min="22" max="22" width="26" style="1" customWidth="1"/>
@@ -1450,124 +1455,124 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:54" ht="27.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
-      <c r="I1" s="51"/>
-      <c r="J1" s="51"/>
-      <c r="K1" s="51"/>
-      <c r="L1" s="51"/>
-      <c r="M1" s="51"/>
-      <c r="N1" s="51"/>
-      <c r="O1" s="51"/>
-      <c r="P1" s="51"/>
-      <c r="Q1" s="51"/>
-      <c r="R1" s="51"/>
-      <c r="S1" s="51"/>
-      <c r="T1" s="51"/>
-      <c r="U1" s="52"/>
-      <c r="Z1" s="50" t="s">
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="52"/>
+      <c r="M1" s="52"/>
+      <c r="N1" s="52"/>
+      <c r="O1" s="52"/>
+      <c r="P1" s="52"/>
+      <c r="Q1" s="52"/>
+      <c r="R1" s="52"/>
+      <c r="S1" s="52"/>
+      <c r="T1" s="52"/>
+      <c r="U1" s="53"/>
+      <c r="Z1" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="AA1" s="51"/>
-      <c r="AB1" s="52"/>
-      <c r="AF1" s="50" t="s">
+      <c r="AA1" s="52"/>
+      <c r="AB1" s="53"/>
+      <c r="AF1" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="AG1" s="51"/>
-      <c r="AH1" s="51"/>
-      <c r="AI1" s="51"/>
-      <c r="AJ1" s="51"/>
-      <c r="AK1" s="51"/>
-      <c r="AL1" s="51"/>
-      <c r="AM1" s="51"/>
-      <c r="AN1" s="51"/>
-      <c r="AO1" s="51"/>
-      <c r="AP1" s="51"/>
-      <c r="AQ1" s="51"/>
-      <c r="AR1" s="51"/>
-      <c r="AS1" s="51"/>
-      <c r="AT1" s="51"/>
-      <c r="AU1" s="51"/>
-      <c r="AV1" s="51"/>
-      <c r="AW1" s="51"/>
-      <c r="AX1" s="51"/>
-      <c r="AY1" s="51"/>
-      <c r="AZ1" s="51"/>
-      <c r="BA1" s="52"/>
+      <c r="AG1" s="52"/>
+      <c r="AH1" s="52"/>
+      <c r="AI1" s="52"/>
+      <c r="AJ1" s="52"/>
+      <c r="AK1" s="52"/>
+      <c r="AL1" s="52"/>
+      <c r="AM1" s="52"/>
+      <c r="AN1" s="52"/>
+      <c r="AO1" s="52"/>
+      <c r="AP1" s="52"/>
+      <c r="AQ1" s="52"/>
+      <c r="AR1" s="52"/>
+      <c r="AS1" s="52"/>
+      <c r="AT1" s="52"/>
+      <c r="AU1" s="52"/>
+      <c r="AV1" s="52"/>
+      <c r="AW1" s="52"/>
+      <c r="AX1" s="52"/>
+      <c r="AY1" s="52"/>
+      <c r="AZ1" s="52"/>
+      <c r="BA1" s="53"/>
     </row>
     <row r="2" spans="1:54" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="48"/>
-      <c r="M2" s="46" t="s">
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="57"/>
+      <c r="M2" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="47"/>
-      <c r="O2" s="47"/>
-      <c r="P2" s="47"/>
-      <c r="Q2" s="47"/>
-      <c r="R2" s="48"/>
-      <c r="AI2" s="46" t="s">
+      <c r="N2" s="56"/>
+      <c r="O2" s="56"/>
+      <c r="P2" s="56"/>
+      <c r="Q2" s="56"/>
+      <c r="R2" s="57"/>
+      <c r="AI2" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="AJ2" s="47"/>
-      <c r="AK2" s="47"/>
-      <c r="AL2" s="47"/>
-      <c r="AM2" s="47"/>
-      <c r="AN2" s="47"/>
-      <c r="AO2" s="48"/>
-      <c r="AU2" s="46" t="s">
+      <c r="AJ2" s="56"/>
+      <c r="AK2" s="56"/>
+      <c r="AL2" s="56"/>
+      <c r="AM2" s="56"/>
+      <c r="AN2" s="56"/>
+      <c r="AO2" s="57"/>
+      <c r="AU2" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="AV2" s="47"/>
-      <c r="AW2" s="47"/>
-      <c r="AX2" s="47"/>
-      <c r="AY2" s="47"/>
-      <c r="AZ2" s="47"/>
-      <c r="BA2" s="48"/>
+      <c r="AV2" s="56"/>
+      <c r="AW2" s="56"/>
+      <c r="AX2" s="56"/>
+      <c r="AY2" s="56"/>
+      <c r="AZ2" s="56"/>
+      <c r="BA2" s="57"/>
     </row>
     <row r="3" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="42" t="s">
+      <c r="A3" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="42"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="42"/>
-      <c r="AI3" s="53" t="s">
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="AI3" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="AJ3" s="54"/>
-      <c r="AK3" s="54"/>
-      <c r="AL3" s="54"/>
-      <c r="AM3" s="54"/>
-      <c r="AN3" s="54"/>
-      <c r="AO3" s="55"/>
-      <c r="AU3" s="42" t="s">
+      <c r="AJ3" s="43"/>
+      <c r="AK3" s="43"/>
+      <c r="AL3" s="43"/>
+      <c r="AM3" s="43"/>
+      <c r="AN3" s="43"/>
+      <c r="AO3" s="44"/>
+      <c r="AU3" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="AV3" s="42"/>
-      <c r="AW3" s="42"/>
-      <c r="AX3" s="42"/>
-      <c r="AY3" s="42"/>
-      <c r="AZ3" s="42"/>
-      <c r="BA3" s="42"/>
+      <c r="AV3" s="49"/>
+      <c r="AW3" s="49"/>
+      <c r="AX3" s="49"/>
+      <c r="AY3" s="49"/>
+      <c r="AZ3" s="49"/>
+      <c r="BA3" s="49"/>
     </row>
     <row r="4" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
@@ -1591,15 +1596,15 @@
       <c r="G4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="53" t="s">
+      <c r="M4" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="N4" s="54"/>
-      <c r="O4" s="54"/>
-      <c r="P4" s="54"/>
-      <c r="Q4" s="54"/>
-      <c r="R4" s="54"/>
-      <c r="S4" s="55"/>
+      <c r="N4" s="43"/>
+      <c r="O4" s="43"/>
+      <c r="P4" s="43"/>
+      <c r="Q4" s="43"/>
+      <c r="R4" s="43"/>
+      <c r="S4" s="44"/>
       <c r="AI4" s="3" t="s">
         <v>2</v>
       </c>
@@ -1870,12 +1875,18 @@
       <c r="AK7" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="AL7" s="13"/>
+      <c r="AL7" s="13">
+        <v>1</v>
+      </c>
       <c r="AM7" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="AN7" s="13"/>
-      <c r="AO7" s="16"/>
+      <c r="AN7" s="13">
+        <v>5</v>
+      </c>
+      <c r="AO7" s="16" t="s">
+        <v>90</v>
+      </c>
       <c r="AU7" s="8">
         <v>3</v>
       </c>
@@ -1920,11 +1931,11 @@
       <c r="G8" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="I8" s="43" t="s">
+      <c r="I8" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="J8" s="43"/>
-      <c r="K8" s="43"/>
+      <c r="J8" s="50"/>
+      <c r="K8" s="50"/>
       <c r="M8" s="8">
         <v>3</v>
       </c>
@@ -1955,11 +1966,11 @@
       </c>
       <c r="AN8" s="31"/>
       <c r="AO8" s="16"/>
-      <c r="AQ8" s="43" t="s">
+      <c r="AQ8" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="AR8" s="43"/>
-      <c r="AS8" s="43"/>
+      <c r="AR8" s="50"/>
+      <c r="AS8" s="50"/>
       <c r="AU8" s="38">
         <v>4</v>
       </c>
@@ -2192,15 +2203,15 @@
       <c r="BA11" s="6"/>
     </row>
     <row r="12" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="42" t="s">
+      <c r="A12" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="42"/>
-      <c r="C12" s="42"/>
-      <c r="D12" s="42"/>
-      <c r="E12" s="42"/>
-      <c r="F12" s="42"/>
-      <c r="G12" s="42"/>
+      <c r="B12" s="49"/>
+      <c r="C12" s="49"/>
+      <c r="D12" s="49"/>
+      <c r="E12" s="49"/>
+      <c r="F12" s="49"/>
+      <c r="G12" s="49"/>
       <c r="L12" s="12"/>
       <c r="M12" s="8" t="s">
         <v>12</v>
@@ -2217,65 +2228,65 @@
       </c>
       <c r="R12" s="13"/>
       <c r="S12" s="16"/>
-      <c r="AI12" s="42" t="s">
+      <c r="AI12" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AJ12" s="42"/>
-      <c r="AK12" s="42"/>
-      <c r="AL12" s="42"/>
-      <c r="AM12" s="42"/>
-      <c r="AN12" s="42"/>
-      <c r="AO12" s="42"/>
+      <c r="AJ12" s="49"/>
+      <c r="AK12" s="49"/>
+      <c r="AL12" s="49"/>
+      <c r="AM12" s="49"/>
+      <c r="AN12" s="49"/>
+      <c r="AO12" s="49"/>
       <c r="AQ12" s="12"/>
-      <c r="AU12" s="42" t="s">
+      <c r="AU12" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AV12" s="42"/>
-      <c r="AW12" s="42"/>
-      <c r="AX12" s="42"/>
-      <c r="AY12" s="42"/>
-      <c r="AZ12" s="42"/>
-      <c r="BA12" s="42"/>
+      <c r="AV12" s="49"/>
+      <c r="AW12" s="49"/>
+      <c r="AX12" s="49"/>
+      <c r="AY12" s="49"/>
+      <c r="AZ12" s="49"/>
+      <c r="BA12" s="49"/>
     </row>
     <row r="13" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L13" s="12"/>
-      <c r="M13" s="53" t="s">
+      <c r="M13" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="N13" s="54"/>
-      <c r="O13" s="54"/>
-      <c r="P13" s="54"/>
-      <c r="Q13" s="54"/>
-      <c r="R13" s="54"/>
-      <c r="S13" s="55"/>
+      <c r="N13" s="43"/>
+      <c r="O13" s="43"/>
+      <c r="P13" s="43"/>
+      <c r="Q13" s="43"/>
+      <c r="R13" s="43"/>
+      <c r="S13" s="44"/>
       <c r="AQ13" s="12"/>
     </row>
     <row r="14" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="45" t="s">
+      <c r="A14" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="45"/>
-      <c r="C14" s="45"/>
-      <c r="D14" s="45"/>
-      <c r="E14" s="45"/>
-      <c r="F14" s="45"/>
-      <c r="G14" s="45"/>
-      <c r="L14" s="44"/>
-      <c r="M14" s="43"/>
-      <c r="N14" s="43"/>
-      <c r="AN14" s="43"/>
-      <c r="AO14" s="43"/>
-      <c r="AP14" s="43"/>
+      <c r="B14" s="48"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="48"/>
+      <c r="E14" s="48"/>
+      <c r="F14" s="48"/>
+      <c r="G14" s="48"/>
+      <c r="L14" s="54"/>
+      <c r="M14" s="50"/>
+      <c r="N14" s="50"/>
+      <c r="AN14" s="50"/>
+      <c r="AO14" s="50"/>
+      <c r="AP14" s="50"/>
       <c r="AQ14" s="12"/>
-      <c r="AU14" s="45" t="s">
+      <c r="AU14" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="AV14" s="45"/>
-      <c r="AW14" s="45"/>
-      <c r="AX14" s="45"/>
-      <c r="AY14" s="45"/>
-      <c r="AZ14" s="45"/>
-      <c r="BA14" s="45"/>
+      <c r="AV14" s="48"/>
+      <c r="AW14" s="48"/>
+      <c r="AX14" s="48"/>
+      <c r="AY14" s="48"/>
+      <c r="AZ14" s="48"/>
+      <c r="BA14" s="48"/>
     </row>
     <row r="15" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
@@ -2503,19 +2514,19 @@
       <c r="G19" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="I19" s="43" t="s">
+      <c r="I19" s="50" t="s">
         <v>32</v>
       </c>
-      <c r="J19" s="43"/>
-      <c r="K19" s="43"/>
+      <c r="J19" s="50"/>
+      <c r="K19" s="50"/>
       <c r="L19" s="12"/>
       <c r="O19" s="12"/>
       <c r="AN19" s="12"/>
-      <c r="AQ19" s="44" t="s">
+      <c r="AQ19" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="AR19" s="43"/>
-      <c r="AS19" s="43"/>
+      <c r="AR19" s="50"/>
+      <c r="AS19" s="50"/>
       <c r="AU19" s="38">
         <v>4</v>
       </c>
@@ -2677,52 +2688,52 @@
       <c r="BA22" s="6"/>
     </row>
     <row r="23" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="42" t="s">
+      <c r="A23" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="B23" s="42"/>
-      <c r="C23" s="42"/>
-      <c r="D23" s="42"/>
-      <c r="E23" s="42"/>
-      <c r="F23" s="42"/>
-      <c r="G23" s="42"/>
+      <c r="B23" s="49"/>
+      <c r="C23" s="49"/>
+      <c r="D23" s="49"/>
+      <c r="E23" s="49"/>
+      <c r="F23" s="49"/>
+      <c r="G23" s="49"/>
       <c r="O23" s="12"/>
       <c r="AN23" s="12"/>
-      <c r="AU23" s="42" t="s">
+      <c r="AU23" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AV23" s="42"/>
-      <c r="AW23" s="42"/>
-      <c r="AX23" s="42"/>
-      <c r="AY23" s="42"/>
-      <c r="AZ23" s="42"/>
-      <c r="BA23" s="42"/>
+      <c r="AV23" s="49"/>
+      <c r="AW23" s="49"/>
+      <c r="AX23" s="49"/>
+      <c r="AY23" s="49"/>
+      <c r="AZ23" s="49"/>
+      <c r="BA23" s="49"/>
     </row>
     <row r="24" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="O24" s="12"/>
       <c r="AN24" s="12"/>
     </row>
     <row r="25" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="42" t="s">
+      <c r="A25" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="42"/>
-      <c r="C25" s="42"/>
-      <c r="D25" s="42"/>
-      <c r="E25" s="42"/>
-      <c r="F25" s="42"/>
-      <c r="G25" s="42"/>
+      <c r="B25" s="49"/>
+      <c r="C25" s="49"/>
+      <c r="D25" s="49"/>
+      <c r="E25" s="49"/>
+      <c r="F25" s="49"/>
+      <c r="G25" s="49"/>
       <c r="O25" s="12"/>
       <c r="AN25" s="12"/>
-      <c r="AU25" s="42" t="s">
+      <c r="AU25" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="AV25" s="42"/>
-      <c r="AW25" s="42"/>
-      <c r="AX25" s="42"/>
-      <c r="AY25" s="42"/>
-      <c r="AZ25" s="42"/>
-      <c r="BA25" s="42"/>
+      <c r="AV25" s="49"/>
+      <c r="AW25" s="49"/>
+      <c r="AX25" s="49"/>
+      <c r="AY25" s="49"/>
+      <c r="AZ25" s="49"/>
+      <c r="BA25" s="49"/>
     </row>
     <row r="26" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="20" t="s">
@@ -2746,24 +2757,24 @@
       <c r="G26" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="O26" s="44"/>
-      <c r="P26" s="43"/>
-      <c r="Q26" s="43"/>
-      <c r="R26" s="43"/>
-      <c r="S26" s="43"/>
-      <c r="T26" s="43"/>
-      <c r="U26" s="43"/>
-      <c r="V26" s="43"/>
-      <c r="W26" s="43"/>
-      <c r="AE26" s="43"/>
-      <c r="AF26" s="43"/>
-      <c r="AG26" s="43"/>
-      <c r="AH26" s="43"/>
-      <c r="AI26" s="43"/>
-      <c r="AJ26" s="43"/>
-      <c r="AK26" s="43"/>
-      <c r="AL26" s="43"/>
-      <c r="AM26" s="49"/>
+      <c r="O26" s="54"/>
+      <c r="P26" s="50"/>
+      <c r="Q26" s="50"/>
+      <c r="R26" s="50"/>
+      <c r="S26" s="50"/>
+      <c r="T26" s="50"/>
+      <c r="U26" s="50"/>
+      <c r="V26" s="50"/>
+      <c r="W26" s="50"/>
+      <c r="AE26" s="50"/>
+      <c r="AF26" s="50"/>
+      <c r="AG26" s="50"/>
+      <c r="AH26" s="50"/>
+      <c r="AI26" s="50"/>
+      <c r="AJ26" s="50"/>
+      <c r="AK26" s="50"/>
+      <c r="AL26" s="50"/>
+      <c r="AM26" s="58"/>
       <c r="AU26" s="20" t="s">
         <v>2</v>
       </c>
@@ -2860,26 +2871,26 @@
         <v>54</v>
       </c>
       <c r="O28" s="12"/>
-      <c r="P28" s="53" t="s">
+      <c r="P28" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="Q28" s="54"/>
-      <c r="R28" s="54"/>
-      <c r="S28" s="54"/>
-      <c r="T28" s="54"/>
-      <c r="U28" s="54"/>
-      <c r="V28" s="55"/>
+      <c r="Q28" s="43"/>
+      <c r="R28" s="43"/>
+      <c r="S28" s="43"/>
+      <c r="T28" s="43"/>
+      <c r="U28" s="43"/>
+      <c r="V28" s="44"/>
       <c r="X28" s="12"/>
       <c r="AD28" s="13"/>
-      <c r="AF28" s="42" t="s">
+      <c r="AF28" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="AG28" s="42"/>
-      <c r="AH28" s="42"/>
-      <c r="AI28" s="42"/>
-      <c r="AJ28" s="42"/>
-      <c r="AK28" s="42"/>
-      <c r="AL28" s="42"/>
+      <c r="AG28" s="49"/>
+      <c r="AH28" s="49"/>
+      <c r="AI28" s="49"/>
+      <c r="AJ28" s="49"/>
+      <c r="AK28" s="49"/>
+      <c r="AL28" s="49"/>
       <c r="AN28" s="12"/>
       <c r="AU28" s="8">
         <v>2</v>
@@ -3015,11 +3026,11 @@
       <c r="G30" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="I30" s="43" t="s">
+      <c r="I30" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="J30" s="43"/>
-      <c r="K30" s="43"/>
+      <c r="J30" s="50"/>
+      <c r="K30" s="50"/>
       <c r="O30" s="12"/>
       <c r="P30" s="7">
         <v>1</v>
@@ -3042,11 +3053,11 @@
       <c r="AK30" s="24"/>
       <c r="AL30" s="25"/>
       <c r="AN30" s="12"/>
-      <c r="AQ30" s="43" t="s">
+      <c r="AQ30" s="50" t="s">
         <v>38</v>
       </c>
-      <c r="AR30" s="43"/>
-      <c r="AS30" s="43"/>
+      <c r="AR30" s="50"/>
+      <c r="AS30" s="50"/>
       <c r="AU30" s="38">
         <v>4</v>
       </c>
@@ -3258,15 +3269,15 @@
       <c r="BA33" s="6"/>
     </row>
     <row r="34" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="42" t="s">
+      <c r="A34" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="B34" s="42"/>
-      <c r="C34" s="42"/>
-      <c r="D34" s="42"/>
-      <c r="E34" s="42"/>
-      <c r="F34" s="42"/>
-      <c r="G34" s="42"/>
+      <c r="B34" s="49"/>
+      <c r="C34" s="49"/>
+      <c r="D34" s="49"/>
+      <c r="E34" s="49"/>
+      <c r="F34" s="49"/>
+      <c r="G34" s="49"/>
       <c r="L34" s="12"/>
       <c r="O34" s="12"/>
       <c r="P34" s="8" t="s">
@@ -3291,15 +3302,15 @@
       <c r="AL34" s="16"/>
       <c r="AN34" s="12"/>
       <c r="AQ34" s="12"/>
-      <c r="AU34" s="42" t="s">
+      <c r="AU34" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AV34" s="42"/>
-      <c r="AW34" s="42"/>
-      <c r="AX34" s="42"/>
-      <c r="AY34" s="42"/>
-      <c r="AZ34" s="42"/>
-      <c r="BA34" s="42"/>
+      <c r="AV34" s="49"/>
+      <c r="AW34" s="49"/>
+      <c r="AX34" s="49"/>
+      <c r="AY34" s="49"/>
+      <c r="AZ34" s="49"/>
+      <c r="BA34" s="49"/>
     </row>
     <row r="35" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L35" s="12"/>
@@ -3328,18 +3339,20 @@
       <c r="AQ35" s="12"/>
     </row>
     <row r="36" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="45" t="s">
+      <c r="A36" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="B36" s="45"/>
-      <c r="C36" s="45"/>
-      <c r="D36" s="45"/>
-      <c r="E36" s="45"/>
-      <c r="F36" s="45"/>
-      <c r="G36" s="45"/>
-      <c r="L36" s="44"/>
-      <c r="M36" s="43"/>
-      <c r="N36" s="43"/>
+      <c r="B36" s="48"/>
+      <c r="C36" s="48"/>
+      <c r="D36" s="48"/>
+      <c r="E36" s="48"/>
+      <c r="F36" s="48"/>
+      <c r="G36" s="48"/>
+      <c r="L36" s="54" t="s">
+        <v>26</v>
+      </c>
+      <c r="M36" s="50"/>
+      <c r="N36" s="50"/>
       <c r="O36" s="12"/>
       <c r="P36" s="8" t="s">
         <v>12</v>
@@ -3361,19 +3374,19 @@
       <c r="AJ36" s="35"/>
       <c r="AK36" s="36"/>
       <c r="AL36" s="37"/>
-      <c r="AN36" s="44"/>
-      <c r="AO36" s="43"/>
-      <c r="AP36" s="43"/>
+      <c r="AN36" s="54"/>
+      <c r="AO36" s="50"/>
+      <c r="AP36" s="50"/>
       <c r="AQ36" s="12"/>
-      <c r="AU36" s="45" t="s">
+      <c r="AU36" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="AV36" s="45"/>
-      <c r="AW36" s="45"/>
-      <c r="AX36" s="45"/>
-      <c r="AY36" s="45"/>
-      <c r="AZ36" s="45"/>
-      <c r="BA36" s="45"/>
+      <c r="AV36" s="48"/>
+      <c r="AW36" s="48"/>
+      <c r="AX36" s="48"/>
+      <c r="AY36" s="48"/>
+      <c r="AZ36" s="48"/>
+      <c r="BA36" s="48"/>
     </row>
     <row r="37" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37" s="20" t="s">
@@ -3398,31 +3411,31 @@
         <v>9</v>
       </c>
       <c r="L37" s="12"/>
-      <c r="P37" s="56" t="s">
+      <c r="P37" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="Q37" s="57"/>
-      <c r="R37" s="57"/>
-      <c r="S37" s="57"/>
-      <c r="T37" s="57"/>
-      <c r="U37" s="57"/>
-      <c r="V37" s="58"/>
-      <c r="X37" s="44"/>
-      <c r="Y37" s="43"/>
-      <c r="Z37" s="43"/>
-      <c r="AA37" s="43"/>
-      <c r="AB37" s="43"/>
-      <c r="AC37" s="43"/>
-      <c r="AD37" s="49"/>
-      <c r="AF37" s="42" t="s">
+      <c r="Q37" s="46"/>
+      <c r="R37" s="46"/>
+      <c r="S37" s="46"/>
+      <c r="T37" s="46"/>
+      <c r="U37" s="46"/>
+      <c r="V37" s="47"/>
+      <c r="X37" s="54"/>
+      <c r="Y37" s="50"/>
+      <c r="Z37" s="50"/>
+      <c r="AA37" s="50"/>
+      <c r="AB37" s="50"/>
+      <c r="AC37" s="50"/>
+      <c r="AD37" s="58"/>
+      <c r="AF37" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AG37" s="42"/>
-      <c r="AH37" s="42"/>
-      <c r="AI37" s="42"/>
-      <c r="AJ37" s="42"/>
-      <c r="AK37" s="42"/>
-      <c r="AL37" s="42"/>
+      <c r="AG37" s="49"/>
+      <c r="AH37" s="49"/>
+      <c r="AI37" s="49"/>
+      <c r="AJ37" s="49"/>
+      <c r="AK37" s="49"/>
+      <c r="AL37" s="49"/>
       <c r="AQ37" s="12"/>
       <c r="AU37" s="3" t="s">
         <v>2</v>
@@ -3515,33 +3528,33 @@
         <v>53</v>
       </c>
       <c r="L39" s="12"/>
-      <c r="M39" s="53" t="s">
+      <c r="M39" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="N39" s="54"/>
-      <c r="O39" s="54"/>
-      <c r="P39" s="54"/>
-      <c r="Q39" s="54"/>
-      <c r="R39" s="54"/>
-      <c r="S39" s="55"/>
-      <c r="X39" s="42" t="s">
+      <c r="N39" s="43"/>
+      <c r="O39" s="43"/>
+      <c r="P39" s="43"/>
+      <c r="Q39" s="43"/>
+      <c r="R39" s="43"/>
+      <c r="S39" s="44"/>
+      <c r="X39" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="Y39" s="42"/>
-      <c r="Z39" s="42"/>
-      <c r="AA39" s="42"/>
-      <c r="AB39" s="42"/>
-      <c r="AC39" s="42"/>
-      <c r="AD39" s="42"/>
-      <c r="AI39" s="53" t="s">
+      <c r="Y39" s="49"/>
+      <c r="Z39" s="49"/>
+      <c r="AA39" s="49"/>
+      <c r="AB39" s="49"/>
+      <c r="AC39" s="49"/>
+      <c r="AD39" s="49"/>
+      <c r="AI39" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="AJ39" s="54"/>
-      <c r="AK39" s="54"/>
-      <c r="AL39" s="54"/>
-      <c r="AM39" s="54"/>
-      <c r="AN39" s="54"/>
-      <c r="AO39" s="55"/>
+      <c r="AJ39" s="43"/>
+      <c r="AK39" s="43"/>
+      <c r="AL39" s="43"/>
+      <c r="AM39" s="43"/>
+      <c r="AN39" s="43"/>
+      <c r="AO39" s="44"/>
       <c r="AQ39" s="12"/>
       <c r="AU39" s="8">
         <v>2</v>
@@ -3696,11 +3709,11 @@
       <c r="G41" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="I41" s="43" t="s">
+      <c r="I41" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="J41" s="43"/>
-      <c r="K41" s="43"/>
+      <c r="J41" s="50"/>
+      <c r="K41" s="50"/>
       <c r="L41" s="12"/>
       <c r="M41" s="7">
         <v>1</v>
@@ -3753,11 +3766,11 @@
       <c r="AO41" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="AQ41" s="44" t="s">
+      <c r="AQ41" s="54" t="s">
         <v>23</v>
       </c>
-      <c r="AR41" s="43"/>
-      <c r="AS41" s="43"/>
+      <c r="AR41" s="50"/>
+      <c r="AS41" s="50"/>
       <c r="AU41" s="38">
         <v>4</v>
       </c>
@@ -4001,12 +4014,21 @@
       <c r="O44" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="P44" s="13"/>
+      <c r="P44" s="13">
+        <v>3</v>
+      </c>
       <c r="Q44" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="R44" s="13"/>
-      <c r="S44" s="16"/>
+      <c r="R44" s="13">
+        <v>2</v>
+      </c>
+      <c r="S44" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="T44" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="X44" s="8">
         <v>4</v>
       </c>
@@ -4048,15 +4070,15 @@
       <c r="BA44" s="6"/>
     </row>
     <row r="45" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="42" t="s">
+      <c r="A45" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="B45" s="42"/>
-      <c r="C45" s="42"/>
-      <c r="D45" s="42"/>
-      <c r="E45" s="42"/>
-      <c r="F45" s="42"/>
-      <c r="G45" s="42"/>
+      <c r="B45" s="49"/>
+      <c r="C45" s="49"/>
+      <c r="D45" s="49"/>
+      <c r="E45" s="49"/>
+      <c r="F45" s="49"/>
+      <c r="G45" s="49"/>
       <c r="M45" s="8" t="s">
         <v>11</v>
       </c>
@@ -4096,15 +4118,15 @@
       </c>
       <c r="AN45" s="13"/>
       <c r="AO45" s="16"/>
-      <c r="AU45" s="42" t="s">
+      <c r="AU45" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AV45" s="42"/>
-      <c r="AW45" s="42"/>
-      <c r="AX45" s="42"/>
-      <c r="AY45" s="42"/>
-      <c r="AZ45" s="42"/>
-      <c r="BA45" s="42"/>
+      <c r="AV45" s="49"/>
+      <c r="AW45" s="49"/>
+      <c r="AX45" s="49"/>
+      <c r="AY45" s="49"/>
+      <c r="AZ45" s="49"/>
+      <c r="BA45" s="49"/>
     </row>
     <row r="46" spans="1:54" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="M46" s="8" t="s">
@@ -4189,45 +4211,65 @@
       <c r="AO47" s="6"/>
     </row>
     <row r="48" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="M48" s="53" t="s">
+      <c r="M48" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="N48" s="54"/>
-      <c r="O48" s="54"/>
-      <c r="P48" s="54"/>
-      <c r="Q48" s="54"/>
-      <c r="R48" s="54"/>
-      <c r="S48" s="55"/>
-      <c r="X48" s="42" t="s">
+      <c r="N48" s="43"/>
+      <c r="O48" s="43"/>
+      <c r="P48" s="43"/>
+      <c r="Q48" s="43"/>
+      <c r="R48" s="43"/>
+      <c r="S48" s="44"/>
+      <c r="X48" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="Y48" s="42"/>
-      <c r="Z48" s="42"/>
-      <c r="AA48" s="42"/>
-      <c r="AB48" s="42"/>
-      <c r="AC48" s="42"/>
-      <c r="AD48" s="42"/>
-      <c r="AI48" s="42" t="s">
+      <c r="Y48" s="49"/>
+      <c r="Z48" s="49"/>
+      <c r="AA48" s="49"/>
+      <c r="AB48" s="49"/>
+      <c r="AC48" s="49"/>
+      <c r="AD48" s="49"/>
+      <c r="AI48" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AJ48" s="42"/>
-      <c r="AK48" s="42"/>
-      <c r="AL48" s="42"/>
-      <c r="AM48" s="42"/>
-      <c r="AN48" s="42"/>
-      <c r="AO48" s="42"/>
+      <c r="AJ48" s="49"/>
+      <c r="AK48" s="49"/>
+      <c r="AL48" s="49"/>
+      <c r="AM48" s="49"/>
+      <c r="AN48" s="49"/>
+      <c r="AO48" s="49"/>
     </row>
     <row r="49" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="M48:S48"/>
-    <mergeCell ref="M39:S39"/>
-    <mergeCell ref="P37:V37"/>
-    <mergeCell ref="P28:V28"/>
-    <mergeCell ref="A36:G36"/>
-    <mergeCell ref="A45:G45"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="AU45:BA45"/>
+    <mergeCell ref="AF28:AL28"/>
+    <mergeCell ref="AF37:AL37"/>
+    <mergeCell ref="AQ30:AS30"/>
+    <mergeCell ref="AQ41:AS41"/>
+    <mergeCell ref="AU34:BA34"/>
+    <mergeCell ref="AU36:BA36"/>
+    <mergeCell ref="AU2:BA2"/>
+    <mergeCell ref="AU3:BA3"/>
+    <mergeCell ref="AU12:BA12"/>
+    <mergeCell ref="AU14:BA14"/>
+    <mergeCell ref="AU23:BA23"/>
+    <mergeCell ref="X37:AD37"/>
+    <mergeCell ref="AE26:AM26"/>
+    <mergeCell ref="Z1:AB1"/>
+    <mergeCell ref="X39:AD39"/>
+    <mergeCell ref="X48:AD48"/>
+    <mergeCell ref="AF1:BA1"/>
+    <mergeCell ref="AI2:AO2"/>
+    <mergeCell ref="AI3:AO3"/>
+    <mergeCell ref="AI12:AO12"/>
+    <mergeCell ref="AI39:AO39"/>
+    <mergeCell ref="AU25:BA25"/>
+    <mergeCell ref="AI48:AO48"/>
+    <mergeCell ref="AN14:AP14"/>
+    <mergeCell ref="AN36:AP36"/>
+    <mergeCell ref="AQ8:AS8"/>
+    <mergeCell ref="AQ19:AS19"/>
     <mergeCell ref="A1:U1"/>
     <mergeCell ref="O26:W26"/>
     <mergeCell ref="I41:K41"/>
@@ -4244,34 +4286,14 @@
     <mergeCell ref="I8:K8"/>
     <mergeCell ref="I19:K19"/>
     <mergeCell ref="A25:G25"/>
-    <mergeCell ref="X37:AD37"/>
-    <mergeCell ref="AE26:AM26"/>
-    <mergeCell ref="Z1:AB1"/>
-    <mergeCell ref="X39:AD39"/>
-    <mergeCell ref="X48:AD48"/>
-    <mergeCell ref="AF1:BA1"/>
-    <mergeCell ref="AI2:AO2"/>
-    <mergeCell ref="AI3:AO3"/>
-    <mergeCell ref="AI12:AO12"/>
-    <mergeCell ref="AI39:AO39"/>
-    <mergeCell ref="AU25:BA25"/>
-    <mergeCell ref="AI48:AO48"/>
-    <mergeCell ref="AN14:AP14"/>
-    <mergeCell ref="AN36:AP36"/>
-    <mergeCell ref="AQ8:AS8"/>
-    <mergeCell ref="AQ19:AS19"/>
-    <mergeCell ref="AU2:BA2"/>
-    <mergeCell ref="AU3:BA3"/>
-    <mergeCell ref="AU12:BA12"/>
-    <mergeCell ref="AU14:BA14"/>
-    <mergeCell ref="AU23:BA23"/>
-    <mergeCell ref="AU45:BA45"/>
-    <mergeCell ref="AF28:AL28"/>
-    <mergeCell ref="AF37:AL37"/>
-    <mergeCell ref="AQ30:AS30"/>
-    <mergeCell ref="AQ41:AS41"/>
-    <mergeCell ref="AU34:BA34"/>
-    <mergeCell ref="AU36:BA36"/>
+    <mergeCell ref="M48:S48"/>
+    <mergeCell ref="M39:S39"/>
+    <mergeCell ref="P37:V37"/>
+    <mergeCell ref="P28:V28"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="A34:G34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/2025_2026/Playoffs/Brackets.xlsx
+++ b/2025_2026/Playoffs/Brackets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\NHLStats\2025_2026\Playoffs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A2B8032-0259-4ECC-ADC4-CF0862A518EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9797A1B-BEFD-4824-824C-F64C080DFCF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="91">
   <si>
     <t>Eastern Conference Playoff Teams</t>
   </si>
@@ -677,6 +677,39 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -695,46 +728,13 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1104,18 +1104,18 @@
     </row>
     <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="11" spans="1:7" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="61" t="s">
+      <c r="A11" s="59" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="61"/>
-      <c r="C11" s="61" t="s">
+      <c r="B11" s="59"/>
+      <c r="C11" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="61"/>
-      <c r="E11" s="61" t="s">
+      <c r="D11" s="59"/>
+      <c r="E11" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="61"/>
+      <c r="F11" s="59"/>
       <c r="G11" s="4" t="s">
         <v>18</v>
       </c>
@@ -1144,18 +1144,18 @@
       </c>
     </row>
     <row r="13" spans="1:7" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="59" t="s">
+      <c r="A13" s="60" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="60"/>
-      <c r="C13" s="59" t="s">
+      <c r="B13" s="61"/>
+      <c r="C13" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="D13" s="60"/>
-      <c r="E13" s="59" t="s">
+      <c r="D13" s="61"/>
+      <c r="E13" s="60" t="s">
         <v>17</v>
       </c>
-      <c r="F13" s="60"/>
+      <c r="F13" s="61"/>
       <c r="G13" s="5"/>
     </row>
     <row r="14" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1194,14 +1194,14 @@
       <c r="F15" s="6"/>
     </row>
     <row r="16" spans="1:7" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="59" t="s">
+      <c r="A16" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="60"/>
-      <c r="C16" s="59" t="s">
+      <c r="B16" s="61"/>
+      <c r="C16" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="60"/>
+      <c r="D16" s="61"/>
     </row>
     <row r="17" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
@@ -1232,10 +1232,10 @@
       </c>
     </row>
     <row r="19" spans="1:4" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="59" t="s">
+      <c r="A19" s="60" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="60"/>
+      <c r="B19" s="61"/>
     </row>
     <row r="20" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
@@ -1254,10 +1254,10 @@
       </c>
     </row>
     <row r="22" spans="1:4" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="59" t="s">
+      <c r="A22" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="60"/>
+      <c r="B22" s="61"/>
     </row>
     <row r="23" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
@@ -1342,16 +1342,16 @@
     <sortCondition ref="B2:B9"/>
   </sortState>
   <mergeCells count="10">
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C16:D16"/>
     <mergeCell ref="E11:F11"/>
     <mergeCell ref="E13:F13"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C16:D16"/>
   </mergeCells>
   <dataValidations count="16">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C14" xr:uid="{2C3D9587-ABAE-4E3F-8B22-396DF812BF02}">
@@ -1455,124 +1455,124 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:54" ht="27.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
-      <c r="M1" s="52"/>
-      <c r="N1" s="52"/>
-      <c r="O1" s="52"/>
-      <c r="P1" s="52"/>
-      <c r="Q1" s="52"/>
-      <c r="R1" s="52"/>
-      <c r="S1" s="52"/>
-      <c r="T1" s="52"/>
-      <c r="U1" s="53"/>
-      <c r="Z1" s="51" t="s">
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
+      <c r="K1" s="51"/>
+      <c r="L1" s="51"/>
+      <c r="M1" s="51"/>
+      <c r="N1" s="51"/>
+      <c r="O1" s="51"/>
+      <c r="P1" s="51"/>
+      <c r="Q1" s="51"/>
+      <c r="R1" s="51"/>
+      <c r="S1" s="51"/>
+      <c r="T1" s="51"/>
+      <c r="U1" s="52"/>
+      <c r="Z1" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="AA1" s="52"/>
-      <c r="AB1" s="53"/>
-      <c r="AF1" s="51" t="s">
+      <c r="AA1" s="51"/>
+      <c r="AB1" s="52"/>
+      <c r="AF1" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="AG1" s="52"/>
-      <c r="AH1" s="52"/>
-      <c r="AI1" s="52"/>
-      <c r="AJ1" s="52"/>
-      <c r="AK1" s="52"/>
-      <c r="AL1" s="52"/>
-      <c r="AM1" s="52"/>
-      <c r="AN1" s="52"/>
-      <c r="AO1" s="52"/>
-      <c r="AP1" s="52"/>
-      <c r="AQ1" s="52"/>
-      <c r="AR1" s="52"/>
-      <c r="AS1" s="52"/>
-      <c r="AT1" s="52"/>
-      <c r="AU1" s="52"/>
-      <c r="AV1" s="52"/>
-      <c r="AW1" s="52"/>
-      <c r="AX1" s="52"/>
-      <c r="AY1" s="52"/>
-      <c r="AZ1" s="52"/>
-      <c r="BA1" s="53"/>
+      <c r="AG1" s="51"/>
+      <c r="AH1" s="51"/>
+      <c r="AI1" s="51"/>
+      <c r="AJ1" s="51"/>
+      <c r="AK1" s="51"/>
+      <c r="AL1" s="51"/>
+      <c r="AM1" s="51"/>
+      <c r="AN1" s="51"/>
+      <c r="AO1" s="51"/>
+      <c r="AP1" s="51"/>
+      <c r="AQ1" s="51"/>
+      <c r="AR1" s="51"/>
+      <c r="AS1" s="51"/>
+      <c r="AT1" s="51"/>
+      <c r="AU1" s="51"/>
+      <c r="AV1" s="51"/>
+      <c r="AW1" s="51"/>
+      <c r="AX1" s="51"/>
+      <c r="AY1" s="51"/>
+      <c r="AZ1" s="51"/>
+      <c r="BA1" s="52"/>
     </row>
     <row r="2" spans="1:54" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="55" t="s">
+      <c r="A2" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="57"/>
-      <c r="M2" s="55" t="s">
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="48"/>
+      <c r="M2" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="56"/>
-      <c r="O2" s="56"/>
-      <c r="P2" s="56"/>
-      <c r="Q2" s="56"/>
-      <c r="R2" s="57"/>
-      <c r="AI2" s="55" t="s">
+      <c r="N2" s="47"/>
+      <c r="O2" s="47"/>
+      <c r="P2" s="47"/>
+      <c r="Q2" s="47"/>
+      <c r="R2" s="48"/>
+      <c r="AI2" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="AJ2" s="56"/>
-      <c r="AK2" s="56"/>
-      <c r="AL2" s="56"/>
-      <c r="AM2" s="56"/>
-      <c r="AN2" s="56"/>
-      <c r="AO2" s="57"/>
-      <c r="AU2" s="55" t="s">
+      <c r="AJ2" s="47"/>
+      <c r="AK2" s="47"/>
+      <c r="AL2" s="47"/>
+      <c r="AM2" s="47"/>
+      <c r="AN2" s="47"/>
+      <c r="AO2" s="48"/>
+      <c r="AU2" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="AV2" s="56"/>
-      <c r="AW2" s="56"/>
-      <c r="AX2" s="56"/>
-      <c r="AY2" s="56"/>
-      <c r="AZ2" s="56"/>
-      <c r="BA2" s="57"/>
+      <c r="AV2" s="47"/>
+      <c r="AW2" s="47"/>
+      <c r="AX2" s="47"/>
+      <c r="AY2" s="47"/>
+      <c r="AZ2" s="47"/>
+      <c r="BA2" s="48"/>
     </row>
     <row r="3" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="49" t="s">
+      <c r="A3" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="49"/>
-      <c r="C3" s="49"/>
-      <c r="D3" s="49"/>
-      <c r="E3" s="49"/>
-      <c r="F3" s="49"/>
-      <c r="G3" s="49"/>
-      <c r="AI3" s="42" t="s">
+      <c r="B3" s="42"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="42"/>
+      <c r="AI3" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="AJ3" s="43"/>
-      <c r="AK3" s="43"/>
-      <c r="AL3" s="43"/>
-      <c r="AM3" s="43"/>
-      <c r="AN3" s="43"/>
-      <c r="AO3" s="44"/>
-      <c r="AU3" s="49" t="s">
+      <c r="AJ3" s="54"/>
+      <c r="AK3" s="54"/>
+      <c r="AL3" s="54"/>
+      <c r="AM3" s="54"/>
+      <c r="AN3" s="54"/>
+      <c r="AO3" s="55"/>
+      <c r="AU3" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="AV3" s="49"/>
-      <c r="AW3" s="49"/>
-      <c r="AX3" s="49"/>
-      <c r="AY3" s="49"/>
-      <c r="AZ3" s="49"/>
-      <c r="BA3" s="49"/>
+      <c r="AV3" s="42"/>
+      <c r="AW3" s="42"/>
+      <c r="AX3" s="42"/>
+      <c r="AY3" s="42"/>
+      <c r="AZ3" s="42"/>
+      <c r="BA3" s="42"/>
     </row>
     <row r="4" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
@@ -1596,15 +1596,15 @@
       <c r="G4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="42" t="s">
+      <c r="M4" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="N4" s="43"/>
-      <c r="O4" s="43"/>
-      <c r="P4" s="43"/>
-      <c r="Q4" s="43"/>
-      <c r="R4" s="43"/>
-      <c r="S4" s="44"/>
+      <c r="N4" s="54"/>
+      <c r="O4" s="54"/>
+      <c r="P4" s="54"/>
+      <c r="Q4" s="54"/>
+      <c r="R4" s="54"/>
+      <c r="S4" s="55"/>
       <c r="AI4" s="3" t="s">
         <v>2</v>
       </c>
@@ -1931,11 +1931,11 @@
       <c r="G8" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="I8" s="50" t="s">
+      <c r="I8" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="J8" s="50"/>
-      <c r="K8" s="50"/>
+      <c r="J8" s="43"/>
+      <c r="K8" s="43"/>
       <c r="M8" s="8">
         <v>3</v>
       </c>
@@ -1945,12 +1945,18 @@
       <c r="O8" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="P8" s="31"/>
+      <c r="P8" s="31">
+        <v>2</v>
+      </c>
       <c r="Q8" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="R8" s="31"/>
-      <c r="S8" s="16"/>
+      <c r="R8" s="31">
+        <v>6</v>
+      </c>
+      <c r="S8" s="16" t="s">
+        <v>66</v>
+      </c>
       <c r="AI8" s="8">
         <v>4</v>
       </c>
@@ -1966,11 +1972,11 @@
       </c>
       <c r="AN8" s="31"/>
       <c r="AO8" s="16"/>
-      <c r="AQ8" s="50" t="s">
+      <c r="AQ8" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="AR8" s="50"/>
-      <c r="AS8" s="50"/>
+      <c r="AR8" s="43"/>
+      <c r="AS8" s="43"/>
       <c r="AU8" s="38">
         <v>4</v>
       </c>
@@ -2203,15 +2209,15 @@
       <c r="BA11" s="6"/>
     </row>
     <row r="12" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="49" t="s">
+      <c r="A12" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="49"/>
-      <c r="C12" s="49"/>
-      <c r="D12" s="49"/>
-      <c r="E12" s="49"/>
-      <c r="F12" s="49"/>
-      <c r="G12" s="49"/>
+      <c r="B12" s="42"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="42"/>
       <c r="L12" s="12"/>
       <c r="M12" s="8" t="s">
         <v>12</v>
@@ -2228,65 +2234,65 @@
       </c>
       <c r="R12" s="13"/>
       <c r="S12" s="16"/>
-      <c r="AI12" s="49" t="s">
+      <c r="AI12" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AJ12" s="49"/>
-      <c r="AK12" s="49"/>
-      <c r="AL12" s="49"/>
-      <c r="AM12" s="49"/>
-      <c r="AN12" s="49"/>
-      <c r="AO12" s="49"/>
+      <c r="AJ12" s="42"/>
+      <c r="AK12" s="42"/>
+      <c r="AL12" s="42"/>
+      <c r="AM12" s="42"/>
+      <c r="AN12" s="42"/>
+      <c r="AO12" s="42"/>
       <c r="AQ12" s="12"/>
-      <c r="AU12" s="49" t="s">
+      <c r="AU12" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AV12" s="49"/>
-      <c r="AW12" s="49"/>
-      <c r="AX12" s="49"/>
-      <c r="AY12" s="49"/>
-      <c r="AZ12" s="49"/>
-      <c r="BA12" s="49"/>
+      <c r="AV12" s="42"/>
+      <c r="AW12" s="42"/>
+      <c r="AX12" s="42"/>
+      <c r="AY12" s="42"/>
+      <c r="AZ12" s="42"/>
+      <c r="BA12" s="42"/>
     </row>
     <row r="13" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L13" s="12"/>
-      <c r="M13" s="42" t="s">
+      <c r="M13" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="N13" s="43"/>
-      <c r="O13" s="43"/>
-      <c r="P13" s="43"/>
-      <c r="Q13" s="43"/>
-      <c r="R13" s="43"/>
-      <c r="S13" s="44"/>
+      <c r="N13" s="54"/>
+      <c r="O13" s="54"/>
+      <c r="P13" s="54"/>
+      <c r="Q13" s="54"/>
+      <c r="R13" s="54"/>
+      <c r="S13" s="55"/>
       <c r="AQ13" s="12"/>
     </row>
     <row r="14" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="48" t="s">
+      <c r="A14" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="48"/>
-      <c r="C14" s="48"/>
-      <c r="D14" s="48"/>
-      <c r="E14" s="48"/>
-      <c r="F14" s="48"/>
-      <c r="G14" s="48"/>
-      <c r="L14" s="54"/>
-      <c r="M14" s="50"/>
-      <c r="N14" s="50"/>
-      <c r="AN14" s="50"/>
-      <c r="AO14" s="50"/>
-      <c r="AP14" s="50"/>
+      <c r="B14" s="45"/>
+      <c r="C14" s="45"/>
+      <c r="D14" s="45"/>
+      <c r="E14" s="45"/>
+      <c r="F14" s="45"/>
+      <c r="G14" s="45"/>
+      <c r="L14" s="44"/>
+      <c r="M14" s="43"/>
+      <c r="N14" s="43"/>
+      <c r="AN14" s="43"/>
+      <c r="AO14" s="43"/>
+      <c r="AP14" s="43"/>
       <c r="AQ14" s="12"/>
-      <c r="AU14" s="48" t="s">
+      <c r="AU14" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="AV14" s="48"/>
-      <c r="AW14" s="48"/>
-      <c r="AX14" s="48"/>
-      <c r="AY14" s="48"/>
-      <c r="AZ14" s="48"/>
-      <c r="BA14" s="48"/>
+      <c r="AV14" s="45"/>
+      <c r="AW14" s="45"/>
+      <c r="AX14" s="45"/>
+      <c r="AY14" s="45"/>
+      <c r="AZ14" s="45"/>
+      <c r="BA14" s="45"/>
     </row>
     <row r="15" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
@@ -2514,19 +2520,19 @@
       <c r="G19" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="I19" s="50" t="s">
+      <c r="I19" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="J19" s="50"/>
-      <c r="K19" s="50"/>
+      <c r="J19" s="43"/>
+      <c r="K19" s="43"/>
       <c r="L19" s="12"/>
       <c r="O19" s="12"/>
       <c r="AN19" s="12"/>
-      <c r="AQ19" s="54" t="s">
+      <c r="AQ19" s="44" t="s">
         <v>31</v>
       </c>
-      <c r="AR19" s="50"/>
-      <c r="AS19" s="50"/>
+      <c r="AR19" s="43"/>
+      <c r="AS19" s="43"/>
       <c r="AU19" s="38">
         <v>4</v>
       </c>
@@ -2688,52 +2694,52 @@
       <c r="BA22" s="6"/>
     </row>
     <row r="23" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="49" t="s">
+      <c r="A23" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B23" s="49"/>
-      <c r="C23" s="49"/>
-      <c r="D23" s="49"/>
-      <c r="E23" s="49"/>
-      <c r="F23" s="49"/>
-      <c r="G23" s="49"/>
+      <c r="B23" s="42"/>
+      <c r="C23" s="42"/>
+      <c r="D23" s="42"/>
+      <c r="E23" s="42"/>
+      <c r="F23" s="42"/>
+      <c r="G23" s="42"/>
       <c r="O23" s="12"/>
       <c r="AN23" s="12"/>
-      <c r="AU23" s="49" t="s">
+      <c r="AU23" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AV23" s="49"/>
-      <c r="AW23" s="49"/>
-      <c r="AX23" s="49"/>
-      <c r="AY23" s="49"/>
-      <c r="AZ23" s="49"/>
-      <c r="BA23" s="49"/>
+      <c r="AV23" s="42"/>
+      <c r="AW23" s="42"/>
+      <c r="AX23" s="42"/>
+      <c r="AY23" s="42"/>
+      <c r="AZ23" s="42"/>
+      <c r="BA23" s="42"/>
     </row>
     <row r="24" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="O24" s="12"/>
       <c r="AN24" s="12"/>
     </row>
     <row r="25" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="49" t="s">
+      <c r="A25" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="49"/>
-      <c r="C25" s="49"/>
-      <c r="D25" s="49"/>
-      <c r="E25" s="49"/>
-      <c r="F25" s="49"/>
-      <c r="G25" s="49"/>
+      <c r="B25" s="42"/>
+      <c r="C25" s="42"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="42"/>
+      <c r="F25" s="42"/>
+      <c r="G25" s="42"/>
       <c r="O25" s="12"/>
       <c r="AN25" s="12"/>
-      <c r="AU25" s="49" t="s">
+      <c r="AU25" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="AV25" s="49"/>
-      <c r="AW25" s="49"/>
-      <c r="AX25" s="49"/>
-      <c r="AY25" s="49"/>
-      <c r="AZ25" s="49"/>
-      <c r="BA25" s="49"/>
+      <c r="AV25" s="42"/>
+      <c r="AW25" s="42"/>
+      <c r="AX25" s="42"/>
+      <c r="AY25" s="42"/>
+      <c r="AZ25" s="42"/>
+      <c r="BA25" s="42"/>
     </row>
     <row r="26" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="20" t="s">
@@ -2757,24 +2763,24 @@
       <c r="G26" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="O26" s="54"/>
-      <c r="P26" s="50"/>
-      <c r="Q26" s="50"/>
-      <c r="R26" s="50"/>
-      <c r="S26" s="50"/>
-      <c r="T26" s="50"/>
-      <c r="U26" s="50"/>
-      <c r="V26" s="50"/>
-      <c r="W26" s="50"/>
-      <c r="AE26" s="50"/>
-      <c r="AF26" s="50"/>
-      <c r="AG26" s="50"/>
-      <c r="AH26" s="50"/>
-      <c r="AI26" s="50"/>
-      <c r="AJ26" s="50"/>
-      <c r="AK26" s="50"/>
-      <c r="AL26" s="50"/>
-      <c r="AM26" s="58"/>
+      <c r="O26" s="44"/>
+      <c r="P26" s="43"/>
+      <c r="Q26" s="43"/>
+      <c r="R26" s="43"/>
+      <c r="S26" s="43"/>
+      <c r="T26" s="43"/>
+      <c r="U26" s="43"/>
+      <c r="V26" s="43"/>
+      <c r="W26" s="43"/>
+      <c r="AE26" s="43"/>
+      <c r="AF26" s="43"/>
+      <c r="AG26" s="43"/>
+      <c r="AH26" s="43"/>
+      <c r="AI26" s="43"/>
+      <c r="AJ26" s="43"/>
+      <c r="AK26" s="43"/>
+      <c r="AL26" s="43"/>
+      <c r="AM26" s="49"/>
       <c r="AU26" s="20" t="s">
         <v>2</v>
       </c>
@@ -2871,26 +2877,26 @@
         <v>54</v>
       </c>
       <c r="O28" s="12"/>
-      <c r="P28" s="42" t="s">
+      <c r="P28" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="Q28" s="43"/>
-      <c r="R28" s="43"/>
-      <c r="S28" s="43"/>
-      <c r="T28" s="43"/>
-      <c r="U28" s="43"/>
-      <c r="V28" s="44"/>
+      <c r="Q28" s="54"/>
+      <c r="R28" s="54"/>
+      <c r="S28" s="54"/>
+      <c r="T28" s="54"/>
+      <c r="U28" s="54"/>
+      <c r="V28" s="55"/>
       <c r="X28" s="12"/>
       <c r="AD28" s="13"/>
-      <c r="AF28" s="49" t="s">
+      <c r="AF28" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="AG28" s="49"/>
-      <c r="AH28" s="49"/>
-      <c r="AI28" s="49"/>
-      <c r="AJ28" s="49"/>
-      <c r="AK28" s="49"/>
-      <c r="AL28" s="49"/>
+      <c r="AG28" s="42"/>
+      <c r="AH28" s="42"/>
+      <c r="AI28" s="42"/>
+      <c r="AJ28" s="42"/>
+      <c r="AK28" s="42"/>
+      <c r="AL28" s="42"/>
       <c r="AN28" s="12"/>
       <c r="AU28" s="8">
         <v>2</v>
@@ -3026,11 +3032,11 @@
       <c r="G30" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="I30" s="50" t="s">
+      <c r="I30" s="43" t="s">
         <v>26</v>
       </c>
-      <c r="J30" s="50"/>
-      <c r="K30" s="50"/>
+      <c r="J30" s="43"/>
+      <c r="K30" s="43"/>
       <c r="O30" s="12"/>
       <c r="P30" s="7">
         <v>1</v>
@@ -3053,11 +3059,11 @@
       <c r="AK30" s="24"/>
       <c r="AL30" s="25"/>
       <c r="AN30" s="12"/>
-      <c r="AQ30" s="50" t="s">
+      <c r="AQ30" s="43" t="s">
         <v>38</v>
       </c>
-      <c r="AR30" s="50"/>
-      <c r="AS30" s="50"/>
+      <c r="AR30" s="43"/>
+      <c r="AS30" s="43"/>
       <c r="AU30" s="38">
         <v>4</v>
       </c>
@@ -3269,15 +3275,15 @@
       <c r="BA33" s="6"/>
     </row>
     <row r="34" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="49" t="s">
+      <c r="A34" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B34" s="49"/>
-      <c r="C34" s="49"/>
-      <c r="D34" s="49"/>
-      <c r="E34" s="49"/>
-      <c r="F34" s="49"/>
-      <c r="G34" s="49"/>
+      <c r="B34" s="42"/>
+      <c r="C34" s="42"/>
+      <c r="D34" s="42"/>
+      <c r="E34" s="42"/>
+      <c r="F34" s="42"/>
+      <c r="G34" s="42"/>
       <c r="L34" s="12"/>
       <c r="O34" s="12"/>
       <c r="P34" s="8" t="s">
@@ -3302,15 +3308,15 @@
       <c r="AL34" s="16"/>
       <c r="AN34" s="12"/>
       <c r="AQ34" s="12"/>
-      <c r="AU34" s="49" t="s">
+      <c r="AU34" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AV34" s="49"/>
-      <c r="AW34" s="49"/>
-      <c r="AX34" s="49"/>
-      <c r="AY34" s="49"/>
-      <c r="AZ34" s="49"/>
-      <c r="BA34" s="49"/>
+      <c r="AV34" s="42"/>
+      <c r="AW34" s="42"/>
+      <c r="AX34" s="42"/>
+      <c r="AY34" s="42"/>
+      <c r="AZ34" s="42"/>
+      <c r="BA34" s="42"/>
     </row>
     <row r="35" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L35" s="12"/>
@@ -3339,20 +3345,20 @@
       <c r="AQ35" s="12"/>
     </row>
     <row r="36" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="48" t="s">
+      <c r="A36" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="B36" s="48"/>
-      <c r="C36" s="48"/>
-      <c r="D36" s="48"/>
-      <c r="E36" s="48"/>
-      <c r="F36" s="48"/>
-      <c r="G36" s="48"/>
-      <c r="L36" s="54" t="s">
+      <c r="B36" s="45"/>
+      <c r="C36" s="45"/>
+      <c r="D36" s="45"/>
+      <c r="E36" s="45"/>
+      <c r="F36" s="45"/>
+      <c r="G36" s="45"/>
+      <c r="L36" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="M36" s="50"/>
-      <c r="N36" s="50"/>
+      <c r="M36" s="43"/>
+      <c r="N36" s="43"/>
       <c r="O36" s="12"/>
       <c r="P36" s="8" t="s">
         <v>12</v>
@@ -3374,19 +3380,19 @@
       <c r="AJ36" s="35"/>
       <c r="AK36" s="36"/>
       <c r="AL36" s="37"/>
-      <c r="AN36" s="54"/>
-      <c r="AO36" s="50"/>
-      <c r="AP36" s="50"/>
+      <c r="AN36" s="44"/>
+      <c r="AO36" s="43"/>
+      <c r="AP36" s="43"/>
       <c r="AQ36" s="12"/>
-      <c r="AU36" s="48" t="s">
+      <c r="AU36" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="AV36" s="48"/>
-      <c r="AW36" s="48"/>
-      <c r="AX36" s="48"/>
-      <c r="AY36" s="48"/>
-      <c r="AZ36" s="48"/>
-      <c r="BA36" s="48"/>
+      <c r="AV36" s="45"/>
+      <c r="AW36" s="45"/>
+      <c r="AX36" s="45"/>
+      <c r="AY36" s="45"/>
+      <c r="AZ36" s="45"/>
+      <c r="BA36" s="45"/>
     </row>
     <row r="37" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37" s="20" t="s">
@@ -3411,31 +3417,31 @@
         <v>9</v>
       </c>
       <c r="L37" s="12"/>
-      <c r="P37" s="45" t="s">
+      <c r="P37" s="56" t="s">
         <v>13</v>
       </c>
-      <c r="Q37" s="46"/>
-      <c r="R37" s="46"/>
-      <c r="S37" s="46"/>
-      <c r="T37" s="46"/>
-      <c r="U37" s="46"/>
-      <c r="V37" s="47"/>
-      <c r="X37" s="54"/>
-      <c r="Y37" s="50"/>
-      <c r="Z37" s="50"/>
-      <c r="AA37" s="50"/>
-      <c r="AB37" s="50"/>
-      <c r="AC37" s="50"/>
-      <c r="AD37" s="58"/>
-      <c r="AF37" s="49" t="s">
+      <c r="Q37" s="57"/>
+      <c r="R37" s="57"/>
+      <c r="S37" s="57"/>
+      <c r="T37" s="57"/>
+      <c r="U37" s="57"/>
+      <c r="V37" s="58"/>
+      <c r="X37" s="44"/>
+      <c r="Y37" s="43"/>
+      <c r="Z37" s="43"/>
+      <c r="AA37" s="43"/>
+      <c r="AB37" s="43"/>
+      <c r="AC37" s="43"/>
+      <c r="AD37" s="49"/>
+      <c r="AF37" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AG37" s="49"/>
-      <c r="AH37" s="49"/>
-      <c r="AI37" s="49"/>
-      <c r="AJ37" s="49"/>
-      <c r="AK37" s="49"/>
-      <c r="AL37" s="49"/>
+      <c r="AG37" s="42"/>
+      <c r="AH37" s="42"/>
+      <c r="AI37" s="42"/>
+      <c r="AJ37" s="42"/>
+      <c r="AK37" s="42"/>
+      <c r="AL37" s="42"/>
       <c r="AQ37" s="12"/>
       <c r="AU37" s="3" t="s">
         <v>2</v>
@@ -3528,33 +3534,33 @@
         <v>53</v>
       </c>
       <c r="L39" s="12"/>
-      <c r="M39" s="42" t="s">
+      <c r="M39" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="N39" s="43"/>
-      <c r="O39" s="43"/>
-      <c r="P39" s="43"/>
-      <c r="Q39" s="43"/>
-      <c r="R39" s="43"/>
-      <c r="S39" s="44"/>
-      <c r="X39" s="49" t="s">
+      <c r="N39" s="54"/>
+      <c r="O39" s="54"/>
+      <c r="P39" s="54"/>
+      <c r="Q39" s="54"/>
+      <c r="R39" s="54"/>
+      <c r="S39" s="55"/>
+      <c r="X39" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="Y39" s="49"/>
-      <c r="Z39" s="49"/>
-      <c r="AA39" s="49"/>
-      <c r="AB39" s="49"/>
-      <c r="AC39" s="49"/>
-      <c r="AD39" s="49"/>
-      <c r="AI39" s="42" t="s">
+      <c r="Y39" s="42"/>
+      <c r="Z39" s="42"/>
+      <c r="AA39" s="42"/>
+      <c r="AB39" s="42"/>
+      <c r="AC39" s="42"/>
+      <c r="AD39" s="42"/>
+      <c r="AI39" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="AJ39" s="43"/>
-      <c r="AK39" s="43"/>
-      <c r="AL39" s="43"/>
-      <c r="AM39" s="43"/>
-      <c r="AN39" s="43"/>
-      <c r="AO39" s="44"/>
+      <c r="AJ39" s="54"/>
+      <c r="AK39" s="54"/>
+      <c r="AL39" s="54"/>
+      <c r="AM39" s="54"/>
+      <c r="AN39" s="54"/>
+      <c r="AO39" s="55"/>
       <c r="AQ39" s="12"/>
       <c r="AU39" s="8">
         <v>2</v>
@@ -3709,11 +3715,11 @@
       <c r="G41" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="I41" s="50" t="s">
+      <c r="I41" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="J41" s="50"/>
-      <c r="K41" s="50"/>
+      <c r="J41" s="43"/>
+      <c r="K41" s="43"/>
       <c r="L41" s="12"/>
       <c r="M41" s="7">
         <v>1</v>
@@ -3766,11 +3772,11 @@
       <c r="AO41" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="AQ41" s="54" t="s">
+      <c r="AQ41" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="AR41" s="50"/>
-      <c r="AS41" s="50"/>
+      <c r="AR41" s="43"/>
+      <c r="AS41" s="43"/>
       <c r="AU41" s="38">
         <v>4</v>
       </c>
@@ -4047,12 +4053,18 @@
       <c r="AK44" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="AL44" s="13"/>
+      <c r="AL44" s="13">
+        <v>3</v>
+      </c>
       <c r="AM44" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="AN44" s="13"/>
-      <c r="AO44" s="16"/>
+      <c r="AN44" s="13">
+        <v>4</v>
+      </c>
+      <c r="AO44" s="16" t="s">
+        <v>68</v>
+      </c>
       <c r="AU44" s="9" t="s">
         <v>12</v>
       </c>
@@ -4070,15 +4082,15 @@
       <c r="BA44" s="6"/>
     </row>
     <row r="45" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="49" t="s">
+      <c r="A45" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B45" s="49"/>
-      <c r="C45" s="49"/>
-      <c r="D45" s="49"/>
-      <c r="E45" s="49"/>
-      <c r="F45" s="49"/>
-      <c r="G45" s="49"/>
+      <c r="B45" s="42"/>
+      <c r="C45" s="42"/>
+      <c r="D45" s="42"/>
+      <c r="E45" s="42"/>
+      <c r="F45" s="42"/>
+      <c r="G45" s="42"/>
       <c r="M45" s="8" t="s">
         <v>11</v>
       </c>
@@ -4118,15 +4130,15 @@
       </c>
       <c r="AN45" s="13"/>
       <c r="AO45" s="16"/>
-      <c r="AU45" s="49" t="s">
+      <c r="AU45" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AV45" s="49"/>
-      <c r="AW45" s="49"/>
-      <c r="AX45" s="49"/>
-      <c r="AY45" s="49"/>
-      <c r="AZ45" s="49"/>
-      <c r="BA45" s="49"/>
+      <c r="AV45" s="42"/>
+      <c r="AW45" s="42"/>
+      <c r="AX45" s="42"/>
+      <c r="AY45" s="42"/>
+      <c r="AZ45" s="42"/>
+      <c r="BA45" s="42"/>
     </row>
     <row r="46" spans="1:54" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="M46" s="8" t="s">
@@ -4211,49 +4223,61 @@
       <c r="AO47" s="6"/>
     </row>
     <row r="48" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="M48" s="42" t="s">
+      <c r="M48" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="N48" s="43"/>
-      <c r="O48" s="43"/>
-      <c r="P48" s="43"/>
-      <c r="Q48" s="43"/>
-      <c r="R48" s="43"/>
-      <c r="S48" s="44"/>
-      <c r="X48" s="49" t="s">
+      <c r="N48" s="54"/>
+      <c r="O48" s="54"/>
+      <c r="P48" s="54"/>
+      <c r="Q48" s="54"/>
+      <c r="R48" s="54"/>
+      <c r="S48" s="55"/>
+      <c r="X48" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="Y48" s="49"/>
-      <c r="Z48" s="49"/>
-      <c r="AA48" s="49"/>
-      <c r="AB48" s="49"/>
-      <c r="AC48" s="49"/>
-      <c r="AD48" s="49"/>
-      <c r="AI48" s="49" t="s">
+      <c r="Y48" s="42"/>
+      <c r="Z48" s="42"/>
+      <c r="AA48" s="42"/>
+      <c r="AB48" s="42"/>
+      <c r="AC48" s="42"/>
+      <c r="AD48" s="42"/>
+      <c r="AI48" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AJ48" s="49"/>
-      <c r="AK48" s="49"/>
-      <c r="AL48" s="49"/>
-      <c r="AM48" s="49"/>
-      <c r="AN48" s="49"/>
-      <c r="AO48" s="49"/>
+      <c r="AJ48" s="42"/>
+      <c r="AK48" s="42"/>
+      <c r="AL48" s="42"/>
+      <c r="AM48" s="42"/>
+      <c r="AN48" s="42"/>
+      <c r="AO48" s="42"/>
     </row>
     <row r="49" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="AU45:BA45"/>
-    <mergeCell ref="AF28:AL28"/>
-    <mergeCell ref="AF37:AL37"/>
-    <mergeCell ref="AQ30:AS30"/>
-    <mergeCell ref="AQ41:AS41"/>
-    <mergeCell ref="AU34:BA34"/>
-    <mergeCell ref="AU36:BA36"/>
-    <mergeCell ref="AU2:BA2"/>
-    <mergeCell ref="AU3:BA3"/>
-    <mergeCell ref="AU12:BA12"/>
-    <mergeCell ref="AU14:BA14"/>
-    <mergeCell ref="AU23:BA23"/>
+    <mergeCell ref="M48:S48"/>
+    <mergeCell ref="M39:S39"/>
+    <mergeCell ref="P37:V37"/>
+    <mergeCell ref="P28:V28"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A1:U1"/>
+    <mergeCell ref="O26:W26"/>
+    <mergeCell ref="I41:K41"/>
+    <mergeCell ref="L14:N14"/>
+    <mergeCell ref="L36:N36"/>
+    <mergeCell ref="M2:R2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="M4:S4"/>
+    <mergeCell ref="M13:S13"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="A25:G25"/>
     <mergeCell ref="X37:AD37"/>
     <mergeCell ref="AE26:AM26"/>
     <mergeCell ref="Z1:AB1"/>
@@ -4270,30 +4294,18 @@
     <mergeCell ref="AN36:AP36"/>
     <mergeCell ref="AQ8:AS8"/>
     <mergeCell ref="AQ19:AS19"/>
-    <mergeCell ref="A1:U1"/>
-    <mergeCell ref="O26:W26"/>
-    <mergeCell ref="I41:K41"/>
-    <mergeCell ref="L14:N14"/>
-    <mergeCell ref="L36:N36"/>
-    <mergeCell ref="M2:R2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="M4:S4"/>
-    <mergeCell ref="M13:S13"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A23:G23"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="M48:S48"/>
-    <mergeCell ref="M39:S39"/>
-    <mergeCell ref="P37:V37"/>
-    <mergeCell ref="P28:V28"/>
-    <mergeCell ref="A36:G36"/>
-    <mergeCell ref="A45:G45"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="AU2:BA2"/>
+    <mergeCell ref="AU3:BA3"/>
+    <mergeCell ref="AU12:BA12"/>
+    <mergeCell ref="AU14:BA14"/>
+    <mergeCell ref="AU23:BA23"/>
+    <mergeCell ref="AU45:BA45"/>
+    <mergeCell ref="AF28:AL28"/>
+    <mergeCell ref="AF37:AL37"/>
+    <mergeCell ref="AQ30:AS30"/>
+    <mergeCell ref="AQ41:AS41"/>
+    <mergeCell ref="AU34:BA34"/>
+    <mergeCell ref="AU36:BA36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/2025_2026/Playoffs/Brackets.xlsx
+++ b/2025_2026/Playoffs/Brackets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\NHLStats\2025_2026\Playoffs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9797A1B-BEFD-4824-824C-F64C080DFCF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B49304A1-9EDE-42AE-96D9-B013E05D902F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="94">
   <si>
     <t>Eastern Conference Playoff Teams</t>
   </si>
@@ -299,6 +299,15 @@
   </si>
   <si>
     <t>Avalanche Leads 2-1</t>
+  </si>
+  <si>
+    <t>Avalanche Leads 3-1</t>
+  </si>
+  <si>
+    <t>Golden Knights lead 3-2</t>
+  </si>
+  <si>
+    <t>Avalanche Win Series 4-1</t>
   </si>
 </sst>
 </file>
@@ -677,18 +686,45 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -701,40 +737,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1104,18 +1113,18 @@
     </row>
     <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="11" spans="1:7" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="59" t="s">
+      <c r="A11" s="61" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="59"/>
-      <c r="C11" s="59" t="s">
+      <c r="B11" s="61"/>
+      <c r="C11" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="59"/>
-      <c r="E11" s="59" t="s">
+      <c r="D11" s="61"/>
+      <c r="E11" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="59"/>
+      <c r="F11" s="61"/>
       <c r="G11" s="4" t="s">
         <v>18</v>
       </c>
@@ -1144,18 +1153,18 @@
       </c>
     </row>
     <row r="13" spans="1:7" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="60" t="s">
+      <c r="A13" s="59" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="61"/>
-      <c r="C13" s="60" t="s">
+      <c r="B13" s="60"/>
+      <c r="C13" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="D13" s="61"/>
-      <c r="E13" s="60" t="s">
+      <c r="D13" s="60"/>
+      <c r="E13" s="59" t="s">
         <v>17</v>
       </c>
-      <c r="F13" s="61"/>
+      <c r="F13" s="60"/>
       <c r="G13" s="5"/>
     </row>
     <row r="14" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1172,7 +1181,9 @@
         <v>27</v>
       </c>
       <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
+      <c r="F14" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="G14" s="6"/>
     </row>
     <row r="15" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1191,17 +1202,19 @@
       <c r="E15" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="F15" s="6"/>
+      <c r="F15" s="6" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="16" spans="1:7" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="60" t="s">
+      <c r="A16" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="61"/>
-      <c r="C16" s="60" t="s">
+      <c r="B16" s="60"/>
+      <c r="C16" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="61"/>
+      <c r="D16" s="60"/>
     </row>
     <row r="17" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
@@ -1232,10 +1245,10 @@
       </c>
     </row>
     <row r="19" spans="1:4" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="60" t="s">
+      <c r="A19" s="59" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="61"/>
+      <c r="B19" s="60"/>
     </row>
     <row r="20" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
@@ -1254,10 +1267,10 @@
       </c>
     </row>
     <row r="22" spans="1:4" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="60" t="s">
+      <c r="A22" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="61"/>
+      <c r="B22" s="60"/>
     </row>
     <row r="23" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
@@ -1342,16 +1355,16 @@
     <sortCondition ref="B2:B9"/>
   </sortState>
   <mergeCells count="10">
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A16:B16"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A16:B16"/>
   </mergeCells>
   <dataValidations count="16">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C14" xr:uid="{2C3D9587-ABAE-4E3F-8B22-396DF812BF02}">
@@ -1443,7 +1456,7 @@
     <col min="38" max="38" width="20.7109375" style="1" customWidth="1"/>
     <col min="39" max="39" width="22.140625" style="1" customWidth="1"/>
     <col min="40" max="40" width="9.140625" style="1"/>
-    <col min="41" max="41" width="24.7109375" style="1" customWidth="1"/>
+    <col min="41" max="41" width="29.42578125" style="1" customWidth="1"/>
     <col min="42" max="47" width="9.140625" style="1"/>
     <col min="48" max="48" width="10.28515625" style="1" customWidth="1"/>
     <col min="49" max="49" width="23.140625" style="1" customWidth="1"/>
@@ -1455,124 +1468,124 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:54" ht="27.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
-      <c r="I1" s="51"/>
-      <c r="J1" s="51"/>
-      <c r="K1" s="51"/>
-      <c r="L1" s="51"/>
-      <c r="M1" s="51"/>
-      <c r="N1" s="51"/>
-      <c r="O1" s="51"/>
-      <c r="P1" s="51"/>
-      <c r="Q1" s="51"/>
-      <c r="R1" s="51"/>
-      <c r="S1" s="51"/>
-      <c r="T1" s="51"/>
-      <c r="U1" s="52"/>
-      <c r="Z1" s="50" t="s">
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="52"/>
+      <c r="M1" s="52"/>
+      <c r="N1" s="52"/>
+      <c r="O1" s="52"/>
+      <c r="P1" s="52"/>
+      <c r="Q1" s="52"/>
+      <c r="R1" s="52"/>
+      <c r="S1" s="52"/>
+      <c r="T1" s="52"/>
+      <c r="U1" s="53"/>
+      <c r="Z1" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="AA1" s="51"/>
-      <c r="AB1" s="52"/>
-      <c r="AF1" s="50" t="s">
+      <c r="AA1" s="52"/>
+      <c r="AB1" s="53"/>
+      <c r="AF1" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="AG1" s="51"/>
-      <c r="AH1" s="51"/>
-      <c r="AI1" s="51"/>
-      <c r="AJ1" s="51"/>
-      <c r="AK1" s="51"/>
-      <c r="AL1" s="51"/>
-      <c r="AM1" s="51"/>
-      <c r="AN1" s="51"/>
-      <c r="AO1" s="51"/>
-      <c r="AP1" s="51"/>
-      <c r="AQ1" s="51"/>
-      <c r="AR1" s="51"/>
-      <c r="AS1" s="51"/>
-      <c r="AT1" s="51"/>
-      <c r="AU1" s="51"/>
-      <c r="AV1" s="51"/>
-      <c r="AW1" s="51"/>
-      <c r="AX1" s="51"/>
-      <c r="AY1" s="51"/>
-      <c r="AZ1" s="51"/>
-      <c r="BA1" s="52"/>
+      <c r="AG1" s="52"/>
+      <c r="AH1" s="52"/>
+      <c r="AI1" s="52"/>
+      <c r="AJ1" s="52"/>
+      <c r="AK1" s="52"/>
+      <c r="AL1" s="52"/>
+      <c r="AM1" s="52"/>
+      <c r="AN1" s="52"/>
+      <c r="AO1" s="52"/>
+      <c r="AP1" s="52"/>
+      <c r="AQ1" s="52"/>
+      <c r="AR1" s="52"/>
+      <c r="AS1" s="52"/>
+      <c r="AT1" s="52"/>
+      <c r="AU1" s="52"/>
+      <c r="AV1" s="52"/>
+      <c r="AW1" s="52"/>
+      <c r="AX1" s="52"/>
+      <c r="AY1" s="52"/>
+      <c r="AZ1" s="52"/>
+      <c r="BA1" s="53"/>
     </row>
     <row r="2" spans="1:54" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="48"/>
-      <c r="M2" s="46" t="s">
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="57"/>
+      <c r="M2" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="47"/>
-      <c r="O2" s="47"/>
-      <c r="P2" s="47"/>
-      <c r="Q2" s="47"/>
-      <c r="R2" s="48"/>
-      <c r="AI2" s="46" t="s">
+      <c r="N2" s="56"/>
+      <c r="O2" s="56"/>
+      <c r="P2" s="56"/>
+      <c r="Q2" s="56"/>
+      <c r="R2" s="57"/>
+      <c r="AI2" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="AJ2" s="47"/>
-      <c r="AK2" s="47"/>
-      <c r="AL2" s="47"/>
-      <c r="AM2" s="47"/>
-      <c r="AN2" s="47"/>
-      <c r="AO2" s="48"/>
-      <c r="AU2" s="46" t="s">
+      <c r="AJ2" s="56"/>
+      <c r="AK2" s="56"/>
+      <c r="AL2" s="56"/>
+      <c r="AM2" s="56"/>
+      <c r="AN2" s="56"/>
+      <c r="AO2" s="57"/>
+      <c r="AU2" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="AV2" s="47"/>
-      <c r="AW2" s="47"/>
-      <c r="AX2" s="47"/>
-      <c r="AY2" s="47"/>
-      <c r="AZ2" s="47"/>
-      <c r="BA2" s="48"/>
+      <c r="AV2" s="56"/>
+      <c r="AW2" s="56"/>
+      <c r="AX2" s="56"/>
+      <c r="AY2" s="56"/>
+      <c r="AZ2" s="56"/>
+      <c r="BA2" s="57"/>
     </row>
     <row r="3" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="42" t="s">
+      <c r="A3" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="42"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="42"/>
-      <c r="AI3" s="53" t="s">
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="AI3" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="AJ3" s="54"/>
-      <c r="AK3" s="54"/>
-      <c r="AL3" s="54"/>
-      <c r="AM3" s="54"/>
-      <c r="AN3" s="54"/>
-      <c r="AO3" s="55"/>
-      <c r="AU3" s="42" t="s">
+      <c r="AJ3" s="43"/>
+      <c r="AK3" s="43"/>
+      <c r="AL3" s="43"/>
+      <c r="AM3" s="43"/>
+      <c r="AN3" s="43"/>
+      <c r="AO3" s="44"/>
+      <c r="AU3" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="AV3" s="42"/>
-      <c r="AW3" s="42"/>
-      <c r="AX3" s="42"/>
-      <c r="AY3" s="42"/>
-      <c r="AZ3" s="42"/>
-      <c r="BA3" s="42"/>
+      <c r="AV3" s="49"/>
+      <c r="AW3" s="49"/>
+      <c r="AX3" s="49"/>
+      <c r="AY3" s="49"/>
+      <c r="AZ3" s="49"/>
+      <c r="BA3" s="49"/>
     </row>
     <row r="4" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
@@ -1596,15 +1609,15 @@
       <c r="G4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="53" t="s">
+      <c r="M4" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="N4" s="54"/>
-      <c r="O4" s="54"/>
-      <c r="P4" s="54"/>
-      <c r="Q4" s="54"/>
-      <c r="R4" s="54"/>
-      <c r="S4" s="55"/>
+      <c r="N4" s="43"/>
+      <c r="O4" s="43"/>
+      <c r="P4" s="43"/>
+      <c r="Q4" s="43"/>
+      <c r="R4" s="43"/>
+      <c r="S4" s="44"/>
       <c r="AI4" s="3" t="s">
         <v>2</v>
       </c>
@@ -1931,11 +1944,11 @@
       <c r="G8" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="I8" s="43" t="s">
+      <c r="I8" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="J8" s="43"/>
-      <c r="K8" s="43"/>
+      <c r="J8" s="50"/>
+      <c r="K8" s="50"/>
       <c r="M8" s="8">
         <v>3</v>
       </c>
@@ -1966,17 +1979,23 @@
       <c r="AK8" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="AL8" s="31"/>
+      <c r="AL8" s="31">
+        <v>5</v>
+      </c>
       <c r="AM8" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="AN8" s="31"/>
-      <c r="AO8" s="16"/>
-      <c r="AQ8" s="43" t="s">
+      <c r="AN8" s="31">
+        <v>2</v>
+      </c>
+      <c r="AO8" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="AQ8" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="AR8" s="43"/>
-      <c r="AS8" s="43"/>
+      <c r="AR8" s="50"/>
+      <c r="AS8" s="50"/>
       <c r="AU8" s="38">
         <v>4</v>
       </c>
@@ -2034,12 +2053,18 @@
       <c r="O9" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="P9" s="13"/>
+      <c r="P9" s="13">
+        <v>3</v>
+      </c>
       <c r="Q9" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="R9" s="13"/>
-      <c r="S9" s="16"/>
+      <c r="R9" s="13">
+        <v>2</v>
+      </c>
+      <c r="S9" s="16" t="s">
+        <v>68</v>
+      </c>
       <c r="AI9" s="8" t="s">
         <v>11</v>
       </c>
@@ -2049,12 +2074,21 @@
       <c r="AK9" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="AL9" s="13"/>
+      <c r="AL9" s="13">
+        <v>3</v>
+      </c>
       <c r="AM9" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="AN9" s="13"/>
-      <c r="AO9" s="16"/>
+      <c r="AN9" s="13">
+        <v>4</v>
+      </c>
+      <c r="AO9" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="AP9" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="AQ9" s="10"/>
       <c r="AR9" s="17"/>
       <c r="AS9" s="17"/>
@@ -2106,12 +2140,18 @@
       <c r="O10" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="P10" s="13"/>
+      <c r="P10" s="13">
+        <v>6</v>
+      </c>
       <c r="Q10" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="R10" s="13"/>
-      <c r="S10" s="16"/>
+      <c r="R10" s="13">
+        <v>3</v>
+      </c>
+      <c r="S10" s="16" t="s">
+        <v>79</v>
+      </c>
       <c r="AI10" s="8" t="s">
         <v>10</v>
       </c>
@@ -2209,15 +2249,15 @@
       <c r="BA11" s="6"/>
     </row>
     <row r="12" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="42" t="s">
+      <c r="A12" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="42"/>
-      <c r="C12" s="42"/>
-      <c r="D12" s="42"/>
-      <c r="E12" s="42"/>
-      <c r="F12" s="42"/>
-      <c r="G12" s="42"/>
+      <c r="B12" s="49"/>
+      <c r="C12" s="49"/>
+      <c r="D12" s="49"/>
+      <c r="E12" s="49"/>
+      <c r="F12" s="49"/>
+      <c r="G12" s="49"/>
       <c r="L12" s="12"/>
       <c r="M12" s="8" t="s">
         <v>12</v>
@@ -2234,65 +2274,65 @@
       </c>
       <c r="R12" s="13"/>
       <c r="S12" s="16"/>
-      <c r="AI12" s="42" t="s">
+      <c r="AI12" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AJ12" s="42"/>
-      <c r="AK12" s="42"/>
-      <c r="AL12" s="42"/>
-      <c r="AM12" s="42"/>
-      <c r="AN12" s="42"/>
-      <c r="AO12" s="42"/>
+      <c r="AJ12" s="49"/>
+      <c r="AK12" s="49"/>
+      <c r="AL12" s="49"/>
+      <c r="AM12" s="49"/>
+      <c r="AN12" s="49"/>
+      <c r="AO12" s="49"/>
       <c r="AQ12" s="12"/>
-      <c r="AU12" s="42" t="s">
+      <c r="AU12" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AV12" s="42"/>
-      <c r="AW12" s="42"/>
-      <c r="AX12" s="42"/>
-      <c r="AY12" s="42"/>
-      <c r="AZ12" s="42"/>
-      <c r="BA12" s="42"/>
+      <c r="AV12" s="49"/>
+      <c r="AW12" s="49"/>
+      <c r="AX12" s="49"/>
+      <c r="AY12" s="49"/>
+      <c r="AZ12" s="49"/>
+      <c r="BA12" s="49"/>
     </row>
     <row r="13" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L13" s="12"/>
-      <c r="M13" s="53" t="s">
+      <c r="M13" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="N13" s="54"/>
-      <c r="O13" s="54"/>
-      <c r="P13" s="54"/>
-      <c r="Q13" s="54"/>
-      <c r="R13" s="54"/>
-      <c r="S13" s="55"/>
+      <c r="N13" s="43"/>
+      <c r="O13" s="43"/>
+      <c r="P13" s="43"/>
+      <c r="Q13" s="43"/>
+      <c r="R13" s="43"/>
+      <c r="S13" s="44"/>
       <c r="AQ13" s="12"/>
     </row>
     <row r="14" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="45" t="s">
+      <c r="A14" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="45"/>
-      <c r="C14" s="45"/>
-      <c r="D14" s="45"/>
-      <c r="E14" s="45"/>
-      <c r="F14" s="45"/>
-      <c r="G14" s="45"/>
-      <c r="L14" s="44"/>
-      <c r="M14" s="43"/>
-      <c r="N14" s="43"/>
-      <c r="AN14" s="43"/>
-      <c r="AO14" s="43"/>
-      <c r="AP14" s="43"/>
+      <c r="B14" s="48"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="48"/>
+      <c r="E14" s="48"/>
+      <c r="F14" s="48"/>
+      <c r="G14" s="48"/>
+      <c r="L14" s="54"/>
+      <c r="M14" s="50"/>
+      <c r="N14" s="50"/>
+      <c r="AN14" s="50"/>
+      <c r="AO14" s="50"/>
+      <c r="AP14" s="50"/>
       <c r="AQ14" s="12"/>
-      <c r="AU14" s="45" t="s">
+      <c r="AU14" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="AV14" s="45"/>
-      <c r="AW14" s="45"/>
-      <c r="AX14" s="45"/>
-      <c r="AY14" s="45"/>
-      <c r="AZ14" s="45"/>
-      <c r="BA14" s="45"/>
+      <c r="AV14" s="48"/>
+      <c r="AW14" s="48"/>
+      <c r="AX14" s="48"/>
+      <c r="AY14" s="48"/>
+      <c r="AZ14" s="48"/>
+      <c r="BA14" s="48"/>
     </row>
     <row r="15" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
@@ -2520,19 +2560,19 @@
       <c r="G19" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="I19" s="43" t="s">
+      <c r="I19" s="50" t="s">
         <v>32</v>
       </c>
-      <c r="J19" s="43"/>
-      <c r="K19" s="43"/>
+      <c r="J19" s="50"/>
+      <c r="K19" s="50"/>
       <c r="L19" s="12"/>
       <c r="O19" s="12"/>
       <c r="AN19" s="12"/>
-      <c r="AQ19" s="44" t="s">
+      <c r="AQ19" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="AR19" s="43"/>
-      <c r="AS19" s="43"/>
+      <c r="AR19" s="50"/>
+      <c r="AS19" s="50"/>
       <c r="AU19" s="38">
         <v>4</v>
       </c>
@@ -2694,52 +2734,52 @@
       <c r="BA22" s="6"/>
     </row>
     <row r="23" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="42" t="s">
+      <c r="A23" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="B23" s="42"/>
-      <c r="C23" s="42"/>
-      <c r="D23" s="42"/>
-      <c r="E23" s="42"/>
-      <c r="F23" s="42"/>
-      <c r="G23" s="42"/>
+      <c r="B23" s="49"/>
+      <c r="C23" s="49"/>
+      <c r="D23" s="49"/>
+      <c r="E23" s="49"/>
+      <c r="F23" s="49"/>
+      <c r="G23" s="49"/>
       <c r="O23" s="12"/>
       <c r="AN23" s="12"/>
-      <c r="AU23" s="42" t="s">
+      <c r="AU23" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AV23" s="42"/>
-      <c r="AW23" s="42"/>
-      <c r="AX23" s="42"/>
-      <c r="AY23" s="42"/>
-      <c r="AZ23" s="42"/>
-      <c r="BA23" s="42"/>
+      <c r="AV23" s="49"/>
+      <c r="AW23" s="49"/>
+      <c r="AX23" s="49"/>
+      <c r="AY23" s="49"/>
+      <c r="AZ23" s="49"/>
+      <c r="BA23" s="49"/>
     </row>
     <row r="24" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="O24" s="12"/>
       <c r="AN24" s="12"/>
     </row>
     <row r="25" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="42" t="s">
+      <c r="A25" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="42"/>
-      <c r="C25" s="42"/>
-      <c r="D25" s="42"/>
-      <c r="E25" s="42"/>
-      <c r="F25" s="42"/>
-      <c r="G25" s="42"/>
+      <c r="B25" s="49"/>
+      <c r="C25" s="49"/>
+      <c r="D25" s="49"/>
+      <c r="E25" s="49"/>
+      <c r="F25" s="49"/>
+      <c r="G25" s="49"/>
       <c r="O25" s="12"/>
       <c r="AN25" s="12"/>
-      <c r="AU25" s="42" t="s">
+      <c r="AU25" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="AV25" s="42"/>
-      <c r="AW25" s="42"/>
-      <c r="AX25" s="42"/>
-      <c r="AY25" s="42"/>
-      <c r="AZ25" s="42"/>
-      <c r="BA25" s="42"/>
+      <c r="AV25" s="49"/>
+      <c r="AW25" s="49"/>
+      <c r="AX25" s="49"/>
+      <c r="AY25" s="49"/>
+      <c r="AZ25" s="49"/>
+      <c r="BA25" s="49"/>
     </row>
     <row r="26" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="20" t="s">
@@ -2763,24 +2803,24 @@
       <c r="G26" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="O26" s="44"/>
-      <c r="P26" s="43"/>
-      <c r="Q26" s="43"/>
-      <c r="R26" s="43"/>
-      <c r="S26" s="43"/>
-      <c r="T26" s="43"/>
-      <c r="U26" s="43"/>
-      <c r="V26" s="43"/>
-      <c r="W26" s="43"/>
-      <c r="AE26" s="43"/>
-      <c r="AF26" s="43"/>
-      <c r="AG26" s="43"/>
-      <c r="AH26" s="43"/>
-      <c r="AI26" s="43"/>
-      <c r="AJ26" s="43"/>
-      <c r="AK26" s="43"/>
-      <c r="AL26" s="43"/>
-      <c r="AM26" s="49"/>
+      <c r="O26" s="54"/>
+      <c r="P26" s="50"/>
+      <c r="Q26" s="50"/>
+      <c r="R26" s="50"/>
+      <c r="S26" s="50"/>
+      <c r="T26" s="50"/>
+      <c r="U26" s="50"/>
+      <c r="V26" s="50"/>
+      <c r="W26" s="50"/>
+      <c r="AE26" s="50"/>
+      <c r="AF26" s="50"/>
+      <c r="AG26" s="50"/>
+      <c r="AH26" s="50"/>
+      <c r="AI26" s="50"/>
+      <c r="AJ26" s="50"/>
+      <c r="AK26" s="50"/>
+      <c r="AL26" s="50"/>
+      <c r="AM26" s="58"/>
       <c r="AU26" s="20" t="s">
         <v>2</v>
       </c>
@@ -2877,26 +2917,26 @@
         <v>54</v>
       </c>
       <c r="O28" s="12"/>
-      <c r="P28" s="53" t="s">
+      <c r="P28" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="Q28" s="54"/>
-      <c r="R28" s="54"/>
-      <c r="S28" s="54"/>
-      <c r="T28" s="54"/>
-      <c r="U28" s="54"/>
-      <c r="V28" s="55"/>
+      <c r="Q28" s="43"/>
+      <c r="R28" s="43"/>
+      <c r="S28" s="43"/>
+      <c r="T28" s="43"/>
+      <c r="U28" s="43"/>
+      <c r="V28" s="44"/>
       <c r="X28" s="12"/>
       <c r="AD28" s="13"/>
-      <c r="AF28" s="42" t="s">
+      <c r="AF28" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="AG28" s="42"/>
-      <c r="AH28" s="42"/>
-      <c r="AI28" s="42"/>
-      <c r="AJ28" s="42"/>
-      <c r="AK28" s="42"/>
-      <c r="AL28" s="42"/>
+      <c r="AG28" s="49"/>
+      <c r="AH28" s="49"/>
+      <c r="AI28" s="49"/>
+      <c r="AJ28" s="49"/>
+      <c r="AK28" s="49"/>
+      <c r="AL28" s="49"/>
       <c r="AN28" s="12"/>
       <c r="AU28" s="8">
         <v>2</v>
@@ -3032,11 +3072,11 @@
       <c r="G30" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="I30" s="43" t="s">
+      <c r="I30" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="J30" s="43"/>
-      <c r="K30" s="43"/>
+      <c r="J30" s="50"/>
+      <c r="K30" s="50"/>
       <c r="O30" s="12"/>
       <c r="P30" s="7">
         <v>1</v>
@@ -3059,11 +3099,11 @@
       <c r="AK30" s="24"/>
       <c r="AL30" s="25"/>
       <c r="AN30" s="12"/>
-      <c r="AQ30" s="43" t="s">
+      <c r="AQ30" s="50" t="s">
         <v>38</v>
       </c>
-      <c r="AR30" s="43"/>
-      <c r="AS30" s="43"/>
+      <c r="AR30" s="50"/>
+      <c r="AS30" s="50"/>
       <c r="AU30" s="38">
         <v>4</v>
       </c>
@@ -3275,15 +3315,15 @@
       <c r="BA33" s="6"/>
     </row>
     <row r="34" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="42" t="s">
+      <c r="A34" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="B34" s="42"/>
-      <c r="C34" s="42"/>
-      <c r="D34" s="42"/>
-      <c r="E34" s="42"/>
-      <c r="F34" s="42"/>
-      <c r="G34" s="42"/>
+      <c r="B34" s="49"/>
+      <c r="C34" s="49"/>
+      <c r="D34" s="49"/>
+      <c r="E34" s="49"/>
+      <c r="F34" s="49"/>
+      <c r="G34" s="49"/>
       <c r="L34" s="12"/>
       <c r="O34" s="12"/>
       <c r="P34" s="8" t="s">
@@ -3308,15 +3348,15 @@
       <c r="AL34" s="16"/>
       <c r="AN34" s="12"/>
       <c r="AQ34" s="12"/>
-      <c r="AU34" s="42" t="s">
+      <c r="AU34" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AV34" s="42"/>
-      <c r="AW34" s="42"/>
-      <c r="AX34" s="42"/>
-      <c r="AY34" s="42"/>
-      <c r="AZ34" s="42"/>
-      <c r="BA34" s="42"/>
+      <c r="AV34" s="49"/>
+      <c r="AW34" s="49"/>
+      <c r="AX34" s="49"/>
+      <c r="AY34" s="49"/>
+      <c r="AZ34" s="49"/>
+      <c r="BA34" s="49"/>
     </row>
     <row r="35" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L35" s="12"/>
@@ -3345,20 +3385,20 @@
       <c r="AQ35" s="12"/>
     </row>
     <row r="36" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="45" t="s">
+      <c r="A36" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="B36" s="45"/>
-      <c r="C36" s="45"/>
-      <c r="D36" s="45"/>
-      <c r="E36" s="45"/>
-      <c r="F36" s="45"/>
-      <c r="G36" s="45"/>
-      <c r="L36" s="44" t="s">
+      <c r="B36" s="48"/>
+      <c r="C36" s="48"/>
+      <c r="D36" s="48"/>
+      <c r="E36" s="48"/>
+      <c r="F36" s="48"/>
+      <c r="G36" s="48"/>
+      <c r="L36" s="54" t="s">
         <v>26</v>
       </c>
-      <c r="M36" s="43"/>
-      <c r="N36" s="43"/>
+      <c r="M36" s="50"/>
+      <c r="N36" s="50"/>
       <c r="O36" s="12"/>
       <c r="P36" s="8" t="s">
         <v>12</v>
@@ -3380,19 +3420,19 @@
       <c r="AJ36" s="35"/>
       <c r="AK36" s="36"/>
       <c r="AL36" s="37"/>
-      <c r="AN36" s="44"/>
-      <c r="AO36" s="43"/>
-      <c r="AP36" s="43"/>
+      <c r="AN36" s="54"/>
+      <c r="AO36" s="50"/>
+      <c r="AP36" s="50"/>
       <c r="AQ36" s="12"/>
-      <c r="AU36" s="45" t="s">
+      <c r="AU36" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="AV36" s="45"/>
-      <c r="AW36" s="45"/>
-      <c r="AX36" s="45"/>
-      <c r="AY36" s="45"/>
-      <c r="AZ36" s="45"/>
-      <c r="BA36" s="45"/>
+      <c r="AV36" s="48"/>
+      <c r="AW36" s="48"/>
+      <c r="AX36" s="48"/>
+      <c r="AY36" s="48"/>
+      <c r="AZ36" s="48"/>
+      <c r="BA36" s="48"/>
     </row>
     <row r="37" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37" s="20" t="s">
@@ -3417,31 +3457,31 @@
         <v>9</v>
       </c>
       <c r="L37" s="12"/>
-      <c r="P37" s="56" t="s">
+      <c r="P37" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="Q37" s="57"/>
-      <c r="R37" s="57"/>
-      <c r="S37" s="57"/>
-      <c r="T37" s="57"/>
-      <c r="U37" s="57"/>
-      <c r="V37" s="58"/>
-      <c r="X37" s="44"/>
-      <c r="Y37" s="43"/>
-      <c r="Z37" s="43"/>
-      <c r="AA37" s="43"/>
-      <c r="AB37" s="43"/>
-      <c r="AC37" s="43"/>
-      <c r="AD37" s="49"/>
-      <c r="AF37" s="42" t="s">
+      <c r="Q37" s="46"/>
+      <c r="R37" s="46"/>
+      <c r="S37" s="46"/>
+      <c r="T37" s="46"/>
+      <c r="U37" s="46"/>
+      <c r="V37" s="47"/>
+      <c r="X37" s="54"/>
+      <c r="Y37" s="50"/>
+      <c r="Z37" s="50"/>
+      <c r="AA37" s="50"/>
+      <c r="AB37" s="50"/>
+      <c r="AC37" s="50"/>
+      <c r="AD37" s="58"/>
+      <c r="AF37" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AG37" s="42"/>
-      <c r="AH37" s="42"/>
-      <c r="AI37" s="42"/>
-      <c r="AJ37" s="42"/>
-      <c r="AK37" s="42"/>
-      <c r="AL37" s="42"/>
+      <c r="AG37" s="49"/>
+      <c r="AH37" s="49"/>
+      <c r="AI37" s="49"/>
+      <c r="AJ37" s="49"/>
+      <c r="AK37" s="49"/>
+      <c r="AL37" s="49"/>
       <c r="AQ37" s="12"/>
       <c r="AU37" s="3" t="s">
         <v>2</v>
@@ -3534,33 +3574,33 @@
         <v>53</v>
       </c>
       <c r="L39" s="12"/>
-      <c r="M39" s="53" t="s">
+      <c r="M39" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="N39" s="54"/>
-      <c r="O39" s="54"/>
-      <c r="P39" s="54"/>
-      <c r="Q39" s="54"/>
-      <c r="R39" s="54"/>
-      <c r="S39" s="55"/>
-      <c r="X39" s="42" t="s">
+      <c r="N39" s="43"/>
+      <c r="O39" s="43"/>
+      <c r="P39" s="43"/>
+      <c r="Q39" s="43"/>
+      <c r="R39" s="43"/>
+      <c r="S39" s="44"/>
+      <c r="X39" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="Y39" s="42"/>
-      <c r="Z39" s="42"/>
-      <c r="AA39" s="42"/>
-      <c r="AB39" s="42"/>
-      <c r="AC39" s="42"/>
-      <c r="AD39" s="42"/>
-      <c r="AI39" s="53" t="s">
+      <c r="Y39" s="49"/>
+      <c r="Z39" s="49"/>
+      <c r="AA39" s="49"/>
+      <c r="AB39" s="49"/>
+      <c r="AC39" s="49"/>
+      <c r="AD39" s="49"/>
+      <c r="AI39" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="AJ39" s="54"/>
-      <c r="AK39" s="54"/>
-      <c r="AL39" s="54"/>
-      <c r="AM39" s="54"/>
-      <c r="AN39" s="54"/>
-      <c r="AO39" s="55"/>
+      <c r="AJ39" s="43"/>
+      <c r="AK39" s="43"/>
+      <c r="AL39" s="43"/>
+      <c r="AM39" s="43"/>
+      <c r="AN39" s="43"/>
+      <c r="AO39" s="44"/>
       <c r="AQ39" s="12"/>
       <c r="AU39" s="8">
         <v>2</v>
@@ -3715,11 +3755,11 @@
       <c r="G41" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="I41" s="43" t="s">
+      <c r="I41" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="J41" s="43"/>
-      <c r="K41" s="43"/>
+      <c r="J41" s="50"/>
+      <c r="K41" s="50"/>
       <c r="L41" s="12"/>
       <c r="M41" s="7">
         <v>1</v>
@@ -3772,11 +3812,11 @@
       <c r="AO41" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="AQ41" s="44" t="s">
+      <c r="AQ41" s="54" t="s">
         <v>23</v>
       </c>
-      <c r="AR41" s="43"/>
-      <c r="AS41" s="43"/>
+      <c r="AR41" s="50"/>
+      <c r="AS41" s="50"/>
       <c r="AU41" s="38">
         <v>4</v>
       </c>
@@ -4082,15 +4122,15 @@
       <c r="BA44" s="6"/>
     </row>
     <row r="45" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="42" t="s">
+      <c r="A45" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="B45" s="42"/>
-      <c r="C45" s="42"/>
-      <c r="D45" s="42"/>
-      <c r="E45" s="42"/>
-      <c r="F45" s="42"/>
-      <c r="G45" s="42"/>
+      <c r="B45" s="49"/>
+      <c r="C45" s="49"/>
+      <c r="D45" s="49"/>
+      <c r="E45" s="49"/>
+      <c r="F45" s="49"/>
+      <c r="G45" s="49"/>
       <c r="M45" s="8" t="s">
         <v>11</v>
       </c>
@@ -4124,21 +4164,30 @@
       <c r="AK45" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="AL45" s="13"/>
+      <c r="AL45" s="13">
+        <v>2</v>
+      </c>
       <c r="AM45" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="AN45" s="13"/>
-      <c r="AO45" s="16"/>
-      <c r="AU45" s="42" t="s">
+      <c r="AN45" s="13">
+        <v>3</v>
+      </c>
+      <c r="AO45" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="AP45" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AU45" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AV45" s="42"/>
-      <c r="AW45" s="42"/>
-      <c r="AX45" s="42"/>
-      <c r="AY45" s="42"/>
-      <c r="AZ45" s="42"/>
-      <c r="BA45" s="42"/>
+      <c r="AV45" s="49"/>
+      <c r="AW45" s="49"/>
+      <c r="AX45" s="49"/>
+      <c r="AY45" s="49"/>
+      <c r="AZ45" s="49"/>
+      <c r="BA45" s="49"/>
     </row>
     <row r="46" spans="1:54" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="M46" s="8" t="s">
@@ -4174,12 +4223,18 @@
       <c r="AK46" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="AL46" s="13"/>
+      <c r="AL46" s="13">
+        <v>5</v>
+      </c>
       <c r="AM46" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="AN46" s="13"/>
-      <c r="AO46" s="16"/>
+      <c r="AN46" s="13">
+        <v>1</v>
+      </c>
+      <c r="AO46" s="16" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="47" spans="1:54" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="M47" s="8" t="s">
@@ -4223,45 +4278,65 @@
       <c r="AO47" s="6"/>
     </row>
     <row r="48" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="M48" s="53" t="s">
+      <c r="M48" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="N48" s="54"/>
-      <c r="O48" s="54"/>
-      <c r="P48" s="54"/>
-      <c r="Q48" s="54"/>
-      <c r="R48" s="54"/>
-      <c r="S48" s="55"/>
-      <c r="X48" s="42" t="s">
+      <c r="N48" s="43"/>
+      <c r="O48" s="43"/>
+      <c r="P48" s="43"/>
+      <c r="Q48" s="43"/>
+      <c r="R48" s="43"/>
+      <c r="S48" s="44"/>
+      <c r="X48" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="Y48" s="42"/>
-      <c r="Z48" s="42"/>
-      <c r="AA48" s="42"/>
-      <c r="AB48" s="42"/>
-      <c r="AC48" s="42"/>
-      <c r="AD48" s="42"/>
-      <c r="AI48" s="42" t="s">
+      <c r="Y48" s="49"/>
+      <c r="Z48" s="49"/>
+      <c r="AA48" s="49"/>
+      <c r="AB48" s="49"/>
+      <c r="AC48" s="49"/>
+      <c r="AD48" s="49"/>
+      <c r="AI48" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AJ48" s="42"/>
-      <c r="AK48" s="42"/>
-      <c r="AL48" s="42"/>
-      <c r="AM48" s="42"/>
-      <c r="AN48" s="42"/>
-      <c r="AO48" s="42"/>
+      <c r="AJ48" s="49"/>
+      <c r="AK48" s="49"/>
+      <c r="AL48" s="49"/>
+      <c r="AM48" s="49"/>
+      <c r="AN48" s="49"/>
+      <c r="AO48" s="49"/>
     </row>
     <row r="49" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="M48:S48"/>
-    <mergeCell ref="M39:S39"/>
-    <mergeCell ref="P37:V37"/>
-    <mergeCell ref="P28:V28"/>
-    <mergeCell ref="A36:G36"/>
-    <mergeCell ref="A45:G45"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="AU45:BA45"/>
+    <mergeCell ref="AF28:AL28"/>
+    <mergeCell ref="AF37:AL37"/>
+    <mergeCell ref="AQ30:AS30"/>
+    <mergeCell ref="AQ41:AS41"/>
+    <mergeCell ref="AU34:BA34"/>
+    <mergeCell ref="AU36:BA36"/>
+    <mergeCell ref="AU2:BA2"/>
+    <mergeCell ref="AU3:BA3"/>
+    <mergeCell ref="AU12:BA12"/>
+    <mergeCell ref="AU14:BA14"/>
+    <mergeCell ref="AU23:BA23"/>
+    <mergeCell ref="X37:AD37"/>
+    <mergeCell ref="AE26:AM26"/>
+    <mergeCell ref="Z1:AB1"/>
+    <mergeCell ref="X39:AD39"/>
+    <mergeCell ref="X48:AD48"/>
+    <mergeCell ref="AF1:BA1"/>
+    <mergeCell ref="AI2:AO2"/>
+    <mergeCell ref="AI3:AO3"/>
+    <mergeCell ref="AI12:AO12"/>
+    <mergeCell ref="AI39:AO39"/>
+    <mergeCell ref="AU25:BA25"/>
+    <mergeCell ref="AI48:AO48"/>
+    <mergeCell ref="AN14:AP14"/>
+    <mergeCell ref="AN36:AP36"/>
+    <mergeCell ref="AQ8:AS8"/>
+    <mergeCell ref="AQ19:AS19"/>
     <mergeCell ref="A1:U1"/>
     <mergeCell ref="O26:W26"/>
     <mergeCell ref="I41:K41"/>
@@ -4278,34 +4353,14 @@
     <mergeCell ref="I8:K8"/>
     <mergeCell ref="I19:K19"/>
     <mergeCell ref="A25:G25"/>
-    <mergeCell ref="X37:AD37"/>
-    <mergeCell ref="AE26:AM26"/>
-    <mergeCell ref="Z1:AB1"/>
-    <mergeCell ref="X39:AD39"/>
-    <mergeCell ref="X48:AD48"/>
-    <mergeCell ref="AF1:BA1"/>
-    <mergeCell ref="AI2:AO2"/>
-    <mergeCell ref="AI3:AO3"/>
-    <mergeCell ref="AI12:AO12"/>
-    <mergeCell ref="AI39:AO39"/>
-    <mergeCell ref="AU25:BA25"/>
-    <mergeCell ref="AI48:AO48"/>
-    <mergeCell ref="AN14:AP14"/>
-    <mergeCell ref="AN36:AP36"/>
-    <mergeCell ref="AQ8:AS8"/>
-    <mergeCell ref="AQ19:AS19"/>
-    <mergeCell ref="AU2:BA2"/>
-    <mergeCell ref="AU3:BA3"/>
-    <mergeCell ref="AU12:BA12"/>
-    <mergeCell ref="AU14:BA14"/>
-    <mergeCell ref="AU23:BA23"/>
-    <mergeCell ref="AU45:BA45"/>
-    <mergeCell ref="AF28:AL28"/>
-    <mergeCell ref="AF37:AL37"/>
-    <mergeCell ref="AQ30:AS30"/>
-    <mergeCell ref="AQ41:AS41"/>
-    <mergeCell ref="AU34:BA34"/>
-    <mergeCell ref="AU36:BA36"/>
+    <mergeCell ref="M48:S48"/>
+    <mergeCell ref="M39:S39"/>
+    <mergeCell ref="P37:V37"/>
+    <mergeCell ref="P28:V28"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="A34:G34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/2025_2026/Playoffs/Brackets.xlsx
+++ b/2025_2026/Playoffs/Brackets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\NHLStats\2025_2026\Playoffs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B49304A1-9EDE-42AE-96D9-B013E05D902F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1355B02C-725B-4CE4-88DC-63E802BFCC37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="94">
   <si>
     <t>Eastern Conference Playoff Teams</t>
   </si>
@@ -686,6 +686,39 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -704,46 +737,13 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1113,18 +1113,18 @@
     </row>
     <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="11" spans="1:7" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="61" t="s">
+      <c r="A11" s="59" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="61"/>
-      <c r="C11" s="61" t="s">
+      <c r="B11" s="59"/>
+      <c r="C11" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="61"/>
-      <c r="E11" s="61" t="s">
+      <c r="D11" s="59"/>
+      <c r="E11" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="61"/>
+      <c r="F11" s="59"/>
       <c r="G11" s="4" t="s">
         <v>18</v>
       </c>
@@ -1153,18 +1153,18 @@
       </c>
     </row>
     <row r="13" spans="1:7" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="59" t="s">
+      <c r="A13" s="60" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="60"/>
-      <c r="C13" s="59" t="s">
+      <c r="B13" s="61"/>
+      <c r="C13" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="D13" s="60"/>
-      <c r="E13" s="59" t="s">
+      <c r="D13" s="61"/>
+      <c r="E13" s="60" t="s">
         <v>17</v>
       </c>
-      <c r="F13" s="60"/>
+      <c r="F13" s="61"/>
       <c r="G13" s="5"/>
     </row>
     <row r="14" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1207,14 +1207,14 @@
       </c>
     </row>
     <row r="16" spans="1:7" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="59" t="s">
+      <c r="A16" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="60"/>
-      <c r="C16" s="59" t="s">
+      <c r="B16" s="61"/>
+      <c r="C16" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="60"/>
+      <c r="D16" s="61"/>
     </row>
     <row r="17" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
@@ -1245,10 +1245,10 @@
       </c>
     </row>
     <row r="19" spans="1:4" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="59" t="s">
+      <c r="A19" s="60" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="60"/>
+      <c r="B19" s="61"/>
     </row>
     <row r="20" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
@@ -1267,10 +1267,10 @@
       </c>
     </row>
     <row r="22" spans="1:4" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="59" t="s">
+      <c r="A22" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="60"/>
+      <c r="B22" s="61"/>
     </row>
     <row r="23" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
@@ -1355,16 +1355,16 @@
     <sortCondition ref="B2:B9"/>
   </sortState>
   <mergeCells count="10">
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C16:D16"/>
     <mergeCell ref="E11:F11"/>
     <mergeCell ref="E13:F13"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C16:D16"/>
   </mergeCells>
   <dataValidations count="16">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C14" xr:uid="{2C3D9587-ABAE-4E3F-8B22-396DF812BF02}">
@@ -1468,124 +1468,124 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:54" ht="27.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
-      <c r="M1" s="52"/>
-      <c r="N1" s="52"/>
-      <c r="O1" s="52"/>
-      <c r="P1" s="52"/>
-      <c r="Q1" s="52"/>
-      <c r="R1" s="52"/>
-      <c r="S1" s="52"/>
-      <c r="T1" s="52"/>
-      <c r="U1" s="53"/>
-      <c r="Z1" s="51" t="s">
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
+      <c r="K1" s="51"/>
+      <c r="L1" s="51"/>
+      <c r="M1" s="51"/>
+      <c r="N1" s="51"/>
+      <c r="O1" s="51"/>
+      <c r="P1" s="51"/>
+      <c r="Q1" s="51"/>
+      <c r="R1" s="51"/>
+      <c r="S1" s="51"/>
+      <c r="T1" s="51"/>
+      <c r="U1" s="52"/>
+      <c r="Z1" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="AA1" s="52"/>
-      <c r="AB1" s="53"/>
-      <c r="AF1" s="51" t="s">
+      <c r="AA1" s="51"/>
+      <c r="AB1" s="52"/>
+      <c r="AF1" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="AG1" s="52"/>
-      <c r="AH1" s="52"/>
-      <c r="AI1" s="52"/>
-      <c r="AJ1" s="52"/>
-      <c r="AK1" s="52"/>
-      <c r="AL1" s="52"/>
-      <c r="AM1" s="52"/>
-      <c r="AN1" s="52"/>
-      <c r="AO1" s="52"/>
-      <c r="AP1" s="52"/>
-      <c r="AQ1" s="52"/>
-      <c r="AR1" s="52"/>
-      <c r="AS1" s="52"/>
-      <c r="AT1" s="52"/>
-      <c r="AU1" s="52"/>
-      <c r="AV1" s="52"/>
-      <c r="AW1" s="52"/>
-      <c r="AX1" s="52"/>
-      <c r="AY1" s="52"/>
-      <c r="AZ1" s="52"/>
-      <c r="BA1" s="53"/>
+      <c r="AG1" s="51"/>
+      <c r="AH1" s="51"/>
+      <c r="AI1" s="51"/>
+      <c r="AJ1" s="51"/>
+      <c r="AK1" s="51"/>
+      <c r="AL1" s="51"/>
+      <c r="AM1" s="51"/>
+      <c r="AN1" s="51"/>
+      <c r="AO1" s="51"/>
+      <c r="AP1" s="51"/>
+      <c r="AQ1" s="51"/>
+      <c r="AR1" s="51"/>
+      <c r="AS1" s="51"/>
+      <c r="AT1" s="51"/>
+      <c r="AU1" s="51"/>
+      <c r="AV1" s="51"/>
+      <c r="AW1" s="51"/>
+      <c r="AX1" s="51"/>
+      <c r="AY1" s="51"/>
+      <c r="AZ1" s="51"/>
+      <c r="BA1" s="52"/>
     </row>
     <row r="2" spans="1:54" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="55" t="s">
+      <c r="A2" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="57"/>
-      <c r="M2" s="55" t="s">
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="48"/>
+      <c r="M2" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="56"/>
-      <c r="O2" s="56"/>
-      <c r="P2" s="56"/>
-      <c r="Q2" s="56"/>
-      <c r="R2" s="57"/>
-      <c r="AI2" s="55" t="s">
+      <c r="N2" s="47"/>
+      <c r="O2" s="47"/>
+      <c r="P2" s="47"/>
+      <c r="Q2" s="47"/>
+      <c r="R2" s="48"/>
+      <c r="AI2" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="AJ2" s="56"/>
-      <c r="AK2" s="56"/>
-      <c r="AL2" s="56"/>
-      <c r="AM2" s="56"/>
-      <c r="AN2" s="56"/>
-      <c r="AO2" s="57"/>
-      <c r="AU2" s="55" t="s">
+      <c r="AJ2" s="47"/>
+      <c r="AK2" s="47"/>
+      <c r="AL2" s="47"/>
+      <c r="AM2" s="47"/>
+      <c r="AN2" s="47"/>
+      <c r="AO2" s="48"/>
+      <c r="AU2" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="AV2" s="56"/>
-      <c r="AW2" s="56"/>
-      <c r="AX2" s="56"/>
-      <c r="AY2" s="56"/>
-      <c r="AZ2" s="56"/>
-      <c r="BA2" s="57"/>
+      <c r="AV2" s="47"/>
+      <c r="AW2" s="47"/>
+      <c r="AX2" s="47"/>
+      <c r="AY2" s="47"/>
+      <c r="AZ2" s="47"/>
+      <c r="BA2" s="48"/>
     </row>
     <row r="3" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="49" t="s">
+      <c r="A3" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="49"/>
-      <c r="C3" s="49"/>
-      <c r="D3" s="49"/>
-      <c r="E3" s="49"/>
-      <c r="F3" s="49"/>
-      <c r="G3" s="49"/>
-      <c r="AI3" s="42" t="s">
+      <c r="B3" s="42"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="42"/>
+      <c r="AI3" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="AJ3" s="43"/>
-      <c r="AK3" s="43"/>
-      <c r="AL3" s="43"/>
-      <c r="AM3" s="43"/>
-      <c r="AN3" s="43"/>
-      <c r="AO3" s="44"/>
-      <c r="AU3" s="49" t="s">
+      <c r="AJ3" s="54"/>
+      <c r="AK3" s="54"/>
+      <c r="AL3" s="54"/>
+      <c r="AM3" s="54"/>
+      <c r="AN3" s="54"/>
+      <c r="AO3" s="55"/>
+      <c r="AU3" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="AV3" s="49"/>
-      <c r="AW3" s="49"/>
-      <c r="AX3" s="49"/>
-      <c r="AY3" s="49"/>
-      <c r="AZ3" s="49"/>
-      <c r="BA3" s="49"/>
+      <c r="AV3" s="42"/>
+      <c r="AW3" s="42"/>
+      <c r="AX3" s="42"/>
+      <c r="AY3" s="42"/>
+      <c r="AZ3" s="42"/>
+      <c r="BA3" s="42"/>
     </row>
     <row r="4" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
@@ -1609,15 +1609,15 @@
       <c r="G4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="42" t="s">
+      <c r="M4" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="N4" s="43"/>
-      <c r="O4" s="43"/>
-      <c r="P4" s="43"/>
-      <c r="Q4" s="43"/>
-      <c r="R4" s="43"/>
-      <c r="S4" s="44"/>
+      <c r="N4" s="54"/>
+      <c r="O4" s="54"/>
+      <c r="P4" s="54"/>
+      <c r="Q4" s="54"/>
+      <c r="R4" s="54"/>
+      <c r="S4" s="55"/>
       <c r="AI4" s="3" t="s">
         <v>2</v>
       </c>
@@ -1944,11 +1944,11 @@
       <c r="G8" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="I8" s="50" t="s">
+      <c r="I8" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="J8" s="50"/>
-      <c r="K8" s="50"/>
+      <c r="J8" s="43"/>
+      <c r="K8" s="43"/>
       <c r="M8" s="8">
         <v>3</v>
       </c>
@@ -1991,11 +1991,11 @@
       <c r="AO8" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="AQ8" s="50" t="s">
+      <c r="AQ8" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="AR8" s="50"/>
-      <c r="AS8" s="50"/>
+      <c r="AR8" s="43"/>
+      <c r="AS8" s="43"/>
       <c r="AU8" s="38">
         <v>4</v>
       </c>
@@ -2210,12 +2210,18 @@
       <c r="O11" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="P11" s="13"/>
+      <c r="P11" s="13">
+        <v>8</v>
+      </c>
       <c r="Q11" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="R11" s="13"/>
-      <c r="S11" s="16"/>
+      <c r="R11" s="13">
+        <v>3</v>
+      </c>
+      <c r="S11" s="16" t="s">
+        <v>73</v>
+      </c>
       <c r="AI11" s="9" t="s">
         <v>12</v>
       </c>
@@ -2249,15 +2255,15 @@
       <c r="BA11" s="6"/>
     </row>
     <row r="12" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="49" t="s">
+      <c r="A12" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="49"/>
-      <c r="C12" s="49"/>
-      <c r="D12" s="49"/>
-      <c r="E12" s="49"/>
-      <c r="F12" s="49"/>
-      <c r="G12" s="49"/>
+      <c r="B12" s="42"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="42"/>
       <c r="L12" s="12"/>
       <c r="M12" s="8" t="s">
         <v>12</v>
@@ -2274,65 +2280,65 @@
       </c>
       <c r="R12" s="13"/>
       <c r="S12" s="16"/>
-      <c r="AI12" s="49" t="s">
+      <c r="AI12" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AJ12" s="49"/>
-      <c r="AK12" s="49"/>
-      <c r="AL12" s="49"/>
-      <c r="AM12" s="49"/>
-      <c r="AN12" s="49"/>
-      <c r="AO12" s="49"/>
+      <c r="AJ12" s="42"/>
+      <c r="AK12" s="42"/>
+      <c r="AL12" s="42"/>
+      <c r="AM12" s="42"/>
+      <c r="AN12" s="42"/>
+      <c r="AO12" s="42"/>
       <c r="AQ12" s="12"/>
-      <c r="AU12" s="49" t="s">
+      <c r="AU12" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AV12" s="49"/>
-      <c r="AW12" s="49"/>
-      <c r="AX12" s="49"/>
-      <c r="AY12" s="49"/>
-      <c r="AZ12" s="49"/>
-      <c r="BA12" s="49"/>
+      <c r="AV12" s="42"/>
+      <c r="AW12" s="42"/>
+      <c r="AX12" s="42"/>
+      <c r="AY12" s="42"/>
+      <c r="AZ12" s="42"/>
+      <c r="BA12" s="42"/>
     </row>
     <row r="13" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L13" s="12"/>
-      <c r="M13" s="42" t="s">
+      <c r="M13" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="N13" s="43"/>
-      <c r="O13" s="43"/>
-      <c r="P13" s="43"/>
-      <c r="Q13" s="43"/>
-      <c r="R13" s="43"/>
-      <c r="S13" s="44"/>
+      <c r="N13" s="54"/>
+      <c r="O13" s="54"/>
+      <c r="P13" s="54"/>
+      <c r="Q13" s="54"/>
+      <c r="R13" s="54"/>
+      <c r="S13" s="55"/>
       <c r="AQ13" s="12"/>
     </row>
     <row r="14" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="48" t="s">
+      <c r="A14" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="48"/>
-      <c r="C14" s="48"/>
-      <c r="D14" s="48"/>
-      <c r="E14" s="48"/>
-      <c r="F14" s="48"/>
-      <c r="G14" s="48"/>
-      <c r="L14" s="54"/>
-      <c r="M14" s="50"/>
-      <c r="N14" s="50"/>
-      <c r="AN14" s="50"/>
-      <c r="AO14" s="50"/>
-      <c r="AP14" s="50"/>
+      <c r="B14" s="45"/>
+      <c r="C14" s="45"/>
+      <c r="D14" s="45"/>
+      <c r="E14" s="45"/>
+      <c r="F14" s="45"/>
+      <c r="G14" s="45"/>
+      <c r="L14" s="44"/>
+      <c r="M14" s="43"/>
+      <c r="N14" s="43"/>
+      <c r="AN14" s="43"/>
+      <c r="AO14" s="43"/>
+      <c r="AP14" s="43"/>
       <c r="AQ14" s="12"/>
-      <c r="AU14" s="48" t="s">
+      <c r="AU14" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="AV14" s="48"/>
-      <c r="AW14" s="48"/>
-      <c r="AX14" s="48"/>
-      <c r="AY14" s="48"/>
-      <c r="AZ14" s="48"/>
-      <c r="BA14" s="48"/>
+      <c r="AV14" s="45"/>
+      <c r="AW14" s="45"/>
+      <c r="AX14" s="45"/>
+      <c r="AY14" s="45"/>
+      <c r="AZ14" s="45"/>
+      <c r="BA14" s="45"/>
     </row>
     <row r="15" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
@@ -2560,19 +2566,19 @@
       <c r="G19" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="I19" s="50" t="s">
+      <c r="I19" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="J19" s="50"/>
-      <c r="K19" s="50"/>
+      <c r="J19" s="43"/>
+      <c r="K19" s="43"/>
       <c r="L19" s="12"/>
       <c r="O19" s="12"/>
       <c r="AN19" s="12"/>
-      <c r="AQ19" s="54" t="s">
+      <c r="AQ19" s="44" t="s">
         <v>31</v>
       </c>
-      <c r="AR19" s="50"/>
-      <c r="AS19" s="50"/>
+      <c r="AR19" s="43"/>
+      <c r="AS19" s="43"/>
       <c r="AU19" s="38">
         <v>4</v>
       </c>
@@ -2734,52 +2740,52 @@
       <c r="BA22" s="6"/>
     </row>
     <row r="23" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="49" t="s">
+      <c r="A23" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B23" s="49"/>
-      <c r="C23" s="49"/>
-      <c r="D23" s="49"/>
-      <c r="E23" s="49"/>
-      <c r="F23" s="49"/>
-      <c r="G23" s="49"/>
+      <c r="B23" s="42"/>
+      <c r="C23" s="42"/>
+      <c r="D23" s="42"/>
+      <c r="E23" s="42"/>
+      <c r="F23" s="42"/>
+      <c r="G23" s="42"/>
       <c r="O23" s="12"/>
       <c r="AN23" s="12"/>
-      <c r="AU23" s="49" t="s">
+      <c r="AU23" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AV23" s="49"/>
-      <c r="AW23" s="49"/>
-      <c r="AX23" s="49"/>
-      <c r="AY23" s="49"/>
-      <c r="AZ23" s="49"/>
-      <c r="BA23" s="49"/>
+      <c r="AV23" s="42"/>
+      <c r="AW23" s="42"/>
+      <c r="AX23" s="42"/>
+      <c r="AY23" s="42"/>
+      <c r="AZ23" s="42"/>
+      <c r="BA23" s="42"/>
     </row>
     <row r="24" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="O24" s="12"/>
       <c r="AN24" s="12"/>
     </row>
     <row r="25" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="49" t="s">
+      <c r="A25" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="49"/>
-      <c r="C25" s="49"/>
-      <c r="D25" s="49"/>
-      <c r="E25" s="49"/>
-      <c r="F25" s="49"/>
-      <c r="G25" s="49"/>
+      <c r="B25" s="42"/>
+      <c r="C25" s="42"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="42"/>
+      <c r="F25" s="42"/>
+      <c r="G25" s="42"/>
       <c r="O25" s="12"/>
       <c r="AN25" s="12"/>
-      <c r="AU25" s="49" t="s">
+      <c r="AU25" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="AV25" s="49"/>
-      <c r="AW25" s="49"/>
-      <c r="AX25" s="49"/>
-      <c r="AY25" s="49"/>
-      <c r="AZ25" s="49"/>
-      <c r="BA25" s="49"/>
+      <c r="AV25" s="42"/>
+      <c r="AW25" s="42"/>
+      <c r="AX25" s="42"/>
+      <c r="AY25" s="42"/>
+      <c r="AZ25" s="42"/>
+      <c r="BA25" s="42"/>
     </row>
     <row r="26" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="20" t="s">
@@ -2803,24 +2809,24 @@
       <c r="G26" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="O26" s="54"/>
-      <c r="P26" s="50"/>
-      <c r="Q26" s="50"/>
-      <c r="R26" s="50"/>
-      <c r="S26" s="50"/>
-      <c r="T26" s="50"/>
-      <c r="U26" s="50"/>
-      <c r="V26" s="50"/>
-      <c r="W26" s="50"/>
-      <c r="AE26" s="50"/>
-      <c r="AF26" s="50"/>
-      <c r="AG26" s="50"/>
-      <c r="AH26" s="50"/>
-      <c r="AI26" s="50"/>
-      <c r="AJ26" s="50"/>
-      <c r="AK26" s="50"/>
-      <c r="AL26" s="50"/>
-      <c r="AM26" s="58"/>
+      <c r="O26" s="44"/>
+      <c r="P26" s="43"/>
+      <c r="Q26" s="43"/>
+      <c r="R26" s="43"/>
+      <c r="S26" s="43"/>
+      <c r="T26" s="43"/>
+      <c r="U26" s="43"/>
+      <c r="V26" s="43"/>
+      <c r="W26" s="43"/>
+      <c r="AE26" s="43"/>
+      <c r="AF26" s="43"/>
+      <c r="AG26" s="43"/>
+      <c r="AH26" s="43"/>
+      <c r="AI26" s="43"/>
+      <c r="AJ26" s="43"/>
+      <c r="AK26" s="43"/>
+      <c r="AL26" s="43"/>
+      <c r="AM26" s="49"/>
       <c r="AU26" s="20" t="s">
         <v>2</v>
       </c>
@@ -2917,26 +2923,26 @@
         <v>54</v>
       </c>
       <c r="O28" s="12"/>
-      <c r="P28" s="42" t="s">
+      <c r="P28" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="Q28" s="43"/>
-      <c r="R28" s="43"/>
-      <c r="S28" s="43"/>
-      <c r="T28" s="43"/>
-      <c r="U28" s="43"/>
-      <c r="V28" s="44"/>
+      <c r="Q28" s="54"/>
+      <c r="R28" s="54"/>
+      <c r="S28" s="54"/>
+      <c r="T28" s="54"/>
+      <c r="U28" s="54"/>
+      <c r="V28" s="55"/>
       <c r="X28" s="12"/>
       <c r="AD28" s="13"/>
-      <c r="AF28" s="49" t="s">
+      <c r="AF28" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="AG28" s="49"/>
-      <c r="AH28" s="49"/>
-      <c r="AI28" s="49"/>
-      <c r="AJ28" s="49"/>
-      <c r="AK28" s="49"/>
-      <c r="AL28" s="49"/>
+      <c r="AG28" s="42"/>
+      <c r="AH28" s="42"/>
+      <c r="AI28" s="42"/>
+      <c r="AJ28" s="42"/>
+      <c r="AK28" s="42"/>
+      <c r="AL28" s="42"/>
       <c r="AN28" s="12"/>
       <c r="AU28" s="8">
         <v>2</v>
@@ -3072,11 +3078,11 @@
       <c r="G30" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="I30" s="50" t="s">
+      <c r="I30" s="43" t="s">
         <v>26</v>
       </c>
-      <c r="J30" s="50"/>
-      <c r="K30" s="50"/>
+      <c r="J30" s="43"/>
+      <c r="K30" s="43"/>
       <c r="O30" s="12"/>
       <c r="P30" s="7">
         <v>1</v>
@@ -3099,11 +3105,11 @@
       <c r="AK30" s="24"/>
       <c r="AL30" s="25"/>
       <c r="AN30" s="12"/>
-      <c r="AQ30" s="50" t="s">
+      <c r="AQ30" s="43" t="s">
         <v>38</v>
       </c>
-      <c r="AR30" s="50"/>
-      <c r="AS30" s="50"/>
+      <c r="AR30" s="43"/>
+      <c r="AS30" s="43"/>
       <c r="AU30" s="38">
         <v>4</v>
       </c>
@@ -3315,15 +3321,15 @@
       <c r="BA33" s="6"/>
     </row>
     <row r="34" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="49" t="s">
+      <c r="A34" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B34" s="49"/>
-      <c r="C34" s="49"/>
-      <c r="D34" s="49"/>
-      <c r="E34" s="49"/>
-      <c r="F34" s="49"/>
-      <c r="G34" s="49"/>
+      <c r="B34" s="42"/>
+      <c r="C34" s="42"/>
+      <c r="D34" s="42"/>
+      <c r="E34" s="42"/>
+      <c r="F34" s="42"/>
+      <c r="G34" s="42"/>
       <c r="L34" s="12"/>
       <c r="O34" s="12"/>
       <c r="P34" s="8" t="s">
@@ -3348,15 +3354,15 @@
       <c r="AL34" s="16"/>
       <c r="AN34" s="12"/>
       <c r="AQ34" s="12"/>
-      <c r="AU34" s="49" t="s">
+      <c r="AU34" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AV34" s="49"/>
-      <c r="AW34" s="49"/>
-      <c r="AX34" s="49"/>
-      <c r="AY34" s="49"/>
-      <c r="AZ34" s="49"/>
-      <c r="BA34" s="49"/>
+      <c r="AV34" s="42"/>
+      <c r="AW34" s="42"/>
+      <c r="AX34" s="42"/>
+      <c r="AY34" s="42"/>
+      <c r="AZ34" s="42"/>
+      <c r="BA34" s="42"/>
     </row>
     <row r="35" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L35" s="12"/>
@@ -3385,20 +3391,20 @@
       <c r="AQ35" s="12"/>
     </row>
     <row r="36" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="48" t="s">
+      <c r="A36" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="B36" s="48"/>
-      <c r="C36" s="48"/>
-      <c r="D36" s="48"/>
-      <c r="E36" s="48"/>
-      <c r="F36" s="48"/>
-      <c r="G36" s="48"/>
-      <c r="L36" s="54" t="s">
+      <c r="B36" s="45"/>
+      <c r="C36" s="45"/>
+      <c r="D36" s="45"/>
+      <c r="E36" s="45"/>
+      <c r="F36" s="45"/>
+      <c r="G36" s="45"/>
+      <c r="L36" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="M36" s="50"/>
-      <c r="N36" s="50"/>
+      <c r="M36" s="43"/>
+      <c r="N36" s="43"/>
       <c r="O36" s="12"/>
       <c r="P36" s="8" t="s">
         <v>12</v>
@@ -3420,19 +3426,19 @@
       <c r="AJ36" s="35"/>
       <c r="AK36" s="36"/>
       <c r="AL36" s="37"/>
-      <c r="AN36" s="54"/>
-      <c r="AO36" s="50"/>
-      <c r="AP36" s="50"/>
+      <c r="AN36" s="44"/>
+      <c r="AO36" s="43"/>
+      <c r="AP36" s="43"/>
       <c r="AQ36" s="12"/>
-      <c r="AU36" s="48" t="s">
+      <c r="AU36" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="AV36" s="48"/>
-      <c r="AW36" s="48"/>
-      <c r="AX36" s="48"/>
-      <c r="AY36" s="48"/>
-      <c r="AZ36" s="48"/>
-      <c r="BA36" s="48"/>
+      <c r="AV36" s="45"/>
+      <c r="AW36" s="45"/>
+      <c r="AX36" s="45"/>
+      <c r="AY36" s="45"/>
+      <c r="AZ36" s="45"/>
+      <c r="BA36" s="45"/>
     </row>
     <row r="37" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37" s="20" t="s">
@@ -3457,31 +3463,31 @@
         <v>9</v>
       </c>
       <c r="L37" s="12"/>
-      <c r="P37" s="45" t="s">
+      <c r="P37" s="56" t="s">
         <v>13</v>
       </c>
-      <c r="Q37" s="46"/>
-      <c r="R37" s="46"/>
-      <c r="S37" s="46"/>
-      <c r="T37" s="46"/>
-      <c r="U37" s="46"/>
-      <c r="V37" s="47"/>
-      <c r="X37" s="54"/>
-      <c r="Y37" s="50"/>
-      <c r="Z37" s="50"/>
-      <c r="AA37" s="50"/>
-      <c r="AB37" s="50"/>
-      <c r="AC37" s="50"/>
-      <c r="AD37" s="58"/>
-      <c r="AF37" s="49" t="s">
+      <c r="Q37" s="57"/>
+      <c r="R37" s="57"/>
+      <c r="S37" s="57"/>
+      <c r="T37" s="57"/>
+      <c r="U37" s="57"/>
+      <c r="V37" s="58"/>
+      <c r="X37" s="44"/>
+      <c r="Y37" s="43"/>
+      <c r="Z37" s="43"/>
+      <c r="AA37" s="43"/>
+      <c r="AB37" s="43"/>
+      <c r="AC37" s="43"/>
+      <c r="AD37" s="49"/>
+      <c r="AF37" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AG37" s="49"/>
-      <c r="AH37" s="49"/>
-      <c r="AI37" s="49"/>
-      <c r="AJ37" s="49"/>
-      <c r="AK37" s="49"/>
-      <c r="AL37" s="49"/>
+      <c r="AG37" s="42"/>
+      <c r="AH37" s="42"/>
+      <c r="AI37" s="42"/>
+      <c r="AJ37" s="42"/>
+      <c r="AK37" s="42"/>
+      <c r="AL37" s="42"/>
       <c r="AQ37" s="12"/>
       <c r="AU37" s="3" t="s">
         <v>2</v>
@@ -3574,33 +3580,33 @@
         <v>53</v>
       </c>
       <c r="L39" s="12"/>
-      <c r="M39" s="42" t="s">
+      <c r="M39" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="N39" s="43"/>
-      <c r="O39" s="43"/>
-      <c r="P39" s="43"/>
-      <c r="Q39" s="43"/>
-      <c r="R39" s="43"/>
-      <c r="S39" s="44"/>
-      <c r="X39" s="49" t="s">
+      <c r="N39" s="54"/>
+      <c r="O39" s="54"/>
+      <c r="P39" s="54"/>
+      <c r="Q39" s="54"/>
+      <c r="R39" s="54"/>
+      <c r="S39" s="55"/>
+      <c r="X39" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="Y39" s="49"/>
-      <c r="Z39" s="49"/>
-      <c r="AA39" s="49"/>
-      <c r="AB39" s="49"/>
-      <c r="AC39" s="49"/>
-      <c r="AD39" s="49"/>
-      <c r="AI39" s="42" t="s">
+      <c r="Y39" s="42"/>
+      <c r="Z39" s="42"/>
+      <c r="AA39" s="42"/>
+      <c r="AB39" s="42"/>
+      <c r="AC39" s="42"/>
+      <c r="AD39" s="42"/>
+      <c r="AI39" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="AJ39" s="43"/>
-      <c r="AK39" s="43"/>
-      <c r="AL39" s="43"/>
-      <c r="AM39" s="43"/>
-      <c r="AN39" s="43"/>
-      <c r="AO39" s="44"/>
+      <c r="AJ39" s="54"/>
+      <c r="AK39" s="54"/>
+      <c r="AL39" s="54"/>
+      <c r="AM39" s="54"/>
+      <c r="AN39" s="54"/>
+      <c r="AO39" s="55"/>
       <c r="AQ39" s="12"/>
       <c r="AU39" s="8">
         <v>2</v>
@@ -3755,11 +3761,11 @@
       <c r="G41" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="I41" s="50" t="s">
+      <c r="I41" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="J41" s="50"/>
-      <c r="K41" s="50"/>
+      <c r="J41" s="43"/>
+      <c r="K41" s="43"/>
       <c r="L41" s="12"/>
       <c r="M41" s="7">
         <v>1</v>
@@ -3812,11 +3818,11 @@
       <c r="AO41" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="AQ41" s="54" t="s">
+      <c r="AQ41" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="AR41" s="50"/>
-      <c r="AS41" s="50"/>
+      <c r="AR41" s="43"/>
+      <c r="AS41" s="43"/>
       <c r="AU41" s="38">
         <v>4</v>
       </c>
@@ -4122,15 +4128,15 @@
       <c r="BA44" s="6"/>
     </row>
     <row r="45" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="49" t="s">
+      <c r="A45" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B45" s="49"/>
-      <c r="C45" s="49"/>
-      <c r="D45" s="49"/>
-      <c r="E45" s="49"/>
-      <c r="F45" s="49"/>
-      <c r="G45" s="49"/>
+      <c r="B45" s="42"/>
+      <c r="C45" s="42"/>
+      <c r="D45" s="42"/>
+      <c r="E45" s="42"/>
+      <c r="F45" s="42"/>
+      <c r="G45" s="42"/>
       <c r="M45" s="8" t="s">
         <v>11</v>
       </c>
@@ -4179,15 +4185,15 @@
       <c r="AP45" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AU45" s="49" t="s">
+      <c r="AU45" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AV45" s="49"/>
-      <c r="AW45" s="49"/>
-      <c r="AX45" s="49"/>
-      <c r="AY45" s="49"/>
-      <c r="AZ45" s="49"/>
-      <c r="BA45" s="49"/>
+      <c r="AV45" s="42"/>
+      <c r="AW45" s="42"/>
+      <c r="AX45" s="42"/>
+      <c r="AY45" s="42"/>
+      <c r="AZ45" s="42"/>
+      <c r="BA45" s="42"/>
     </row>
     <row r="46" spans="1:54" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="M46" s="8" t="s">
@@ -4278,49 +4284,61 @@
       <c r="AO47" s="6"/>
     </row>
     <row r="48" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="M48" s="42" t="s">
+      <c r="M48" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="N48" s="43"/>
-      <c r="O48" s="43"/>
-      <c r="P48" s="43"/>
-      <c r="Q48" s="43"/>
-      <c r="R48" s="43"/>
-      <c r="S48" s="44"/>
-      <c r="X48" s="49" t="s">
+      <c r="N48" s="54"/>
+      <c r="O48" s="54"/>
+      <c r="P48" s="54"/>
+      <c r="Q48" s="54"/>
+      <c r="R48" s="54"/>
+      <c r="S48" s="55"/>
+      <c r="X48" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="Y48" s="49"/>
-      <c r="Z48" s="49"/>
-      <c r="AA48" s="49"/>
-      <c r="AB48" s="49"/>
-      <c r="AC48" s="49"/>
-      <c r="AD48" s="49"/>
-      <c r="AI48" s="49" t="s">
+      <c r="Y48" s="42"/>
+      <c r="Z48" s="42"/>
+      <c r="AA48" s="42"/>
+      <c r="AB48" s="42"/>
+      <c r="AC48" s="42"/>
+      <c r="AD48" s="42"/>
+      <c r="AI48" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AJ48" s="49"/>
-      <c r="AK48" s="49"/>
-      <c r="AL48" s="49"/>
-      <c r="AM48" s="49"/>
-      <c r="AN48" s="49"/>
-      <c r="AO48" s="49"/>
+      <c r="AJ48" s="42"/>
+      <c r="AK48" s="42"/>
+      <c r="AL48" s="42"/>
+      <c r="AM48" s="42"/>
+      <c r="AN48" s="42"/>
+      <c r="AO48" s="42"/>
     </row>
     <row r="49" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="AU45:BA45"/>
-    <mergeCell ref="AF28:AL28"/>
-    <mergeCell ref="AF37:AL37"/>
-    <mergeCell ref="AQ30:AS30"/>
-    <mergeCell ref="AQ41:AS41"/>
-    <mergeCell ref="AU34:BA34"/>
-    <mergeCell ref="AU36:BA36"/>
-    <mergeCell ref="AU2:BA2"/>
-    <mergeCell ref="AU3:BA3"/>
-    <mergeCell ref="AU12:BA12"/>
-    <mergeCell ref="AU14:BA14"/>
-    <mergeCell ref="AU23:BA23"/>
+    <mergeCell ref="M48:S48"/>
+    <mergeCell ref="M39:S39"/>
+    <mergeCell ref="P37:V37"/>
+    <mergeCell ref="P28:V28"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A1:U1"/>
+    <mergeCell ref="O26:W26"/>
+    <mergeCell ref="I41:K41"/>
+    <mergeCell ref="L14:N14"/>
+    <mergeCell ref="L36:N36"/>
+    <mergeCell ref="M2:R2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="M4:S4"/>
+    <mergeCell ref="M13:S13"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="A25:G25"/>
     <mergeCell ref="X37:AD37"/>
     <mergeCell ref="AE26:AM26"/>
     <mergeCell ref="Z1:AB1"/>
@@ -4337,30 +4355,18 @@
     <mergeCell ref="AN36:AP36"/>
     <mergeCell ref="AQ8:AS8"/>
     <mergeCell ref="AQ19:AS19"/>
-    <mergeCell ref="A1:U1"/>
-    <mergeCell ref="O26:W26"/>
-    <mergeCell ref="I41:K41"/>
-    <mergeCell ref="L14:N14"/>
-    <mergeCell ref="L36:N36"/>
-    <mergeCell ref="M2:R2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="M4:S4"/>
-    <mergeCell ref="M13:S13"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A23:G23"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="M48:S48"/>
-    <mergeCell ref="M39:S39"/>
-    <mergeCell ref="P37:V37"/>
-    <mergeCell ref="P28:V28"/>
-    <mergeCell ref="A36:G36"/>
-    <mergeCell ref="A45:G45"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="AU2:BA2"/>
+    <mergeCell ref="AU3:BA3"/>
+    <mergeCell ref="AU12:BA12"/>
+    <mergeCell ref="AU14:BA14"/>
+    <mergeCell ref="AU23:BA23"/>
+    <mergeCell ref="AU45:BA45"/>
+    <mergeCell ref="AF28:AL28"/>
+    <mergeCell ref="AF37:AL37"/>
+    <mergeCell ref="AQ30:AS30"/>
+    <mergeCell ref="AQ41:AS41"/>
+    <mergeCell ref="AU34:BA34"/>
+    <mergeCell ref="AU36:BA36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/2025_2026/Playoffs/Brackets.xlsx
+++ b/2025_2026/Playoffs/Brackets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\NHLStats\2025_2026\Playoffs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1355B02C-725B-4CE4-88DC-63E802BFCC37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01DE515A-AFA9-4C79-AFD1-700FAC672FC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="94">
   <si>
     <t>Eastern Conference Playoff Teams</t>
   </si>
@@ -683,8 +683,26 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -692,12 +710,18 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -710,41 +734,17 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1113,18 +1113,18 @@
     </row>
     <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="11" spans="1:7" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="59" t="s">
+      <c r="A11" s="60" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="59"/>
-      <c r="C11" s="59" t="s">
+      <c r="B11" s="60"/>
+      <c r="C11" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="59"/>
-      <c r="E11" s="59" t="s">
+      <c r="D11" s="60"/>
+      <c r="E11" s="60" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="59"/>
+      <c r="F11" s="60"/>
       <c r="G11" s="4" t="s">
         <v>18</v>
       </c>
@@ -1153,18 +1153,18 @@
       </c>
     </row>
     <row r="13" spans="1:7" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="60" t="s">
+      <c r="A13" s="58" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="61"/>
-      <c r="C13" s="60" t="s">
+      <c r="B13" s="59"/>
+      <c r="C13" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="D13" s="61"/>
-      <c r="E13" s="60" t="s">
+      <c r="D13" s="59"/>
+      <c r="E13" s="58" t="s">
         <v>17</v>
       </c>
-      <c r="F13" s="61"/>
+      <c r="F13" s="59"/>
       <c r="G13" s="5"/>
     </row>
     <row r="14" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1180,7 +1180,9 @@
       <c r="D14" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E14" s="5"/>
+      <c r="E14" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="F14" s="5" t="s">
         <v>27</v>
       </c>
@@ -1207,14 +1209,14 @@
       </c>
     </row>
     <row r="16" spans="1:7" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="60" t="s">
+      <c r="A16" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="61"/>
-      <c r="C16" s="60" t="s">
+      <c r="B16" s="59"/>
+      <c r="C16" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="61"/>
+      <c r="D16" s="59"/>
     </row>
     <row r="17" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
@@ -1245,10 +1247,10 @@
       </c>
     </row>
     <row r="19" spans="1:4" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="60" t="s">
+      <c r="A19" s="58" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="61"/>
+      <c r="B19" s="59"/>
     </row>
     <row r="20" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
@@ -1267,10 +1269,10 @@
       </c>
     </row>
     <row r="22" spans="1:4" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="60" t="s">
+      <c r="A22" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="61"/>
+      <c r="B22" s="59"/>
     </row>
     <row r="23" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
@@ -1355,16 +1357,16 @@
     <sortCondition ref="B2:B9"/>
   </sortState>
   <mergeCells count="10">
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A16:B16"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A16:B16"/>
   </mergeCells>
   <dataValidations count="16">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C14" xr:uid="{2C3D9587-ABAE-4E3F-8B22-396DF812BF02}">
@@ -1522,70 +1524,70 @@
       <c r="BA1" s="52"/>
     </row>
     <row r="2" spans="1:54" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="48"/>
-      <c r="M2" s="46" t="s">
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="56"/>
+      <c r="M2" s="54" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="47"/>
-      <c r="O2" s="47"/>
-      <c r="P2" s="47"/>
-      <c r="Q2" s="47"/>
-      <c r="R2" s="48"/>
-      <c r="AI2" s="46" t="s">
+      <c r="N2" s="55"/>
+      <c r="O2" s="55"/>
+      <c r="P2" s="55"/>
+      <c r="Q2" s="55"/>
+      <c r="R2" s="56"/>
+      <c r="AI2" s="54" t="s">
         <v>20</v>
       </c>
-      <c r="AJ2" s="47"/>
-      <c r="AK2" s="47"/>
-      <c r="AL2" s="47"/>
-      <c r="AM2" s="47"/>
-      <c r="AN2" s="47"/>
-      <c r="AO2" s="48"/>
-      <c r="AU2" s="46" t="s">
+      <c r="AJ2" s="55"/>
+      <c r="AK2" s="55"/>
+      <c r="AL2" s="55"/>
+      <c r="AM2" s="55"/>
+      <c r="AN2" s="55"/>
+      <c r="AO2" s="56"/>
+      <c r="AU2" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="AV2" s="47"/>
-      <c r="AW2" s="47"/>
-      <c r="AX2" s="47"/>
-      <c r="AY2" s="47"/>
-      <c r="AZ2" s="47"/>
-      <c r="BA2" s="48"/>
+      <c r="AV2" s="55"/>
+      <c r="AW2" s="55"/>
+      <c r="AX2" s="55"/>
+      <c r="AY2" s="55"/>
+      <c r="AZ2" s="55"/>
+      <c r="BA2" s="56"/>
     </row>
     <row r="3" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="42" t="s">
+      <c r="A3" s="48" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="42"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="42"/>
-      <c r="AI3" s="53" t="s">
+      <c r="B3" s="48"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="AI3" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="AJ3" s="54"/>
-      <c r="AK3" s="54"/>
-      <c r="AL3" s="54"/>
-      <c r="AM3" s="54"/>
-      <c r="AN3" s="54"/>
-      <c r="AO3" s="55"/>
-      <c r="AU3" s="42" t="s">
+      <c r="AJ3" s="42"/>
+      <c r="AK3" s="42"/>
+      <c r="AL3" s="42"/>
+      <c r="AM3" s="42"/>
+      <c r="AN3" s="42"/>
+      <c r="AO3" s="43"/>
+      <c r="AU3" s="48" t="s">
         <v>42</v>
       </c>
-      <c r="AV3" s="42"/>
-      <c r="AW3" s="42"/>
-      <c r="AX3" s="42"/>
-      <c r="AY3" s="42"/>
-      <c r="AZ3" s="42"/>
-      <c r="BA3" s="42"/>
+      <c r="AV3" s="48"/>
+      <c r="AW3" s="48"/>
+      <c r="AX3" s="48"/>
+      <c r="AY3" s="48"/>
+      <c r="AZ3" s="48"/>
+      <c r="BA3" s="48"/>
     </row>
     <row r="4" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
@@ -1609,15 +1611,15 @@
       <c r="G4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="53" t="s">
+      <c r="M4" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="N4" s="54"/>
-      <c r="O4" s="54"/>
-      <c r="P4" s="54"/>
-      <c r="Q4" s="54"/>
-      <c r="R4" s="54"/>
-      <c r="S4" s="55"/>
+      <c r="N4" s="42"/>
+      <c r="O4" s="42"/>
+      <c r="P4" s="42"/>
+      <c r="Q4" s="42"/>
+      <c r="R4" s="42"/>
+      <c r="S4" s="43"/>
       <c r="AI4" s="3" t="s">
         <v>2</v>
       </c>
@@ -1944,11 +1946,11 @@
       <c r="G8" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="I8" s="43" t="s">
+      <c r="I8" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="J8" s="43"/>
-      <c r="K8" s="43"/>
+      <c r="J8" s="49"/>
+      <c r="K8" s="49"/>
       <c r="M8" s="8">
         <v>3</v>
       </c>
@@ -1991,11 +1993,11 @@
       <c r="AO8" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="AQ8" s="43" t="s">
+      <c r="AQ8" s="49" t="s">
         <v>27</v>
       </c>
-      <c r="AR8" s="43"/>
-      <c r="AS8" s="43"/>
+      <c r="AR8" s="49"/>
+      <c r="AS8" s="49"/>
       <c r="AU8" s="38">
         <v>4</v>
       </c>
@@ -2255,15 +2257,15 @@
       <c r="BA11" s="6"/>
     </row>
     <row r="12" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="42" t="s">
+      <c r="A12" s="48" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="42"/>
-      <c r="C12" s="42"/>
-      <c r="D12" s="42"/>
-      <c r="E12" s="42"/>
-      <c r="F12" s="42"/>
-      <c r="G12" s="42"/>
+      <c r="B12" s="48"/>
+      <c r="C12" s="48"/>
+      <c r="D12" s="48"/>
+      <c r="E12" s="48"/>
+      <c r="F12" s="48"/>
+      <c r="G12" s="48"/>
       <c r="L12" s="12"/>
       <c r="M12" s="8" t="s">
         <v>12</v>
@@ -2274,71 +2276,84 @@
       <c r="O12" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="P12" s="13"/>
+      <c r="P12" s="13">
+        <v>3</v>
+      </c>
       <c r="Q12" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="R12" s="13"/>
-      <c r="S12" s="16"/>
-      <c r="AI12" s="42" t="s">
+      <c r="R12" s="13">
+        <v>2</v>
+      </c>
+      <c r="S12" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="T12" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AI12" s="48" t="s">
         <v>13</v>
       </c>
-      <c r="AJ12" s="42"/>
-      <c r="AK12" s="42"/>
-      <c r="AL12" s="42"/>
-      <c r="AM12" s="42"/>
-      <c r="AN12" s="42"/>
-      <c r="AO12" s="42"/>
+      <c r="AJ12" s="48"/>
+      <c r="AK12" s="48"/>
+      <c r="AL12" s="48"/>
+      <c r="AM12" s="48"/>
+      <c r="AN12" s="48"/>
+      <c r="AO12" s="48"/>
       <c r="AQ12" s="12"/>
-      <c r="AU12" s="42" t="s">
+      <c r="AU12" s="48" t="s">
         <v>13</v>
       </c>
-      <c r="AV12" s="42"/>
-      <c r="AW12" s="42"/>
-      <c r="AX12" s="42"/>
-      <c r="AY12" s="42"/>
-      <c r="AZ12" s="42"/>
-      <c r="BA12" s="42"/>
+      <c r="AV12" s="48"/>
+      <c r="AW12" s="48"/>
+      <c r="AX12" s="48"/>
+      <c r="AY12" s="48"/>
+      <c r="AZ12" s="48"/>
+      <c r="BA12" s="48"/>
     </row>
     <row r="13" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L13" s="12"/>
-      <c r="M13" s="53" t="s">
+      <c r="M13" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="N13" s="54"/>
-      <c r="O13" s="54"/>
-      <c r="P13" s="54"/>
-      <c r="Q13" s="54"/>
-      <c r="R13" s="54"/>
-      <c r="S13" s="55"/>
+      <c r="N13" s="42"/>
+      <c r="O13" s="42"/>
+      <c r="P13" s="42"/>
+      <c r="Q13" s="42"/>
+      <c r="R13" s="42"/>
+      <c r="S13" s="43"/>
       <c r="AQ13" s="12"/>
     </row>
     <row r="14" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="45" t="s">
+      <c r="A14" s="47" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="45"/>
-      <c r="C14" s="45"/>
-      <c r="D14" s="45"/>
-      <c r="E14" s="45"/>
-      <c r="F14" s="45"/>
-      <c r="G14" s="45"/>
-      <c r="L14" s="44"/>
-      <c r="M14" s="43"/>
-      <c r="N14" s="43"/>
-      <c r="AN14" s="43"/>
-      <c r="AO14" s="43"/>
-      <c r="AP14" s="43"/>
+      <c r="B14" s="47"/>
+      <c r="C14" s="47"/>
+      <c r="D14" s="47"/>
+      <c r="E14" s="47"/>
+      <c r="F14" s="47"/>
+      <c r="G14" s="47"/>
+      <c r="L14" s="53" t="s">
+        <v>32</v>
+      </c>
+      <c r="M14" s="49"/>
+      <c r="N14" s="49"/>
+      <c r="AN14" s="49" t="s">
+        <v>27</v>
+      </c>
+      <c r="AO14" s="49"/>
+      <c r="AP14" s="49"/>
       <c r="AQ14" s="12"/>
-      <c r="AU14" s="45" t="s">
+      <c r="AU14" s="47" t="s">
         <v>43</v>
       </c>
-      <c r="AV14" s="45"/>
-      <c r="AW14" s="45"/>
-      <c r="AX14" s="45"/>
-      <c r="AY14" s="45"/>
-      <c r="AZ14" s="45"/>
-      <c r="BA14" s="45"/>
+      <c r="AV14" s="47"/>
+      <c r="AW14" s="47"/>
+      <c r="AX14" s="47"/>
+      <c r="AY14" s="47"/>
+      <c r="AZ14" s="47"/>
+      <c r="BA14" s="47"/>
     </row>
     <row r="15" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
@@ -2566,19 +2581,19 @@
       <c r="G19" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="I19" s="43" t="s">
+      <c r="I19" s="49" t="s">
         <v>32</v>
       </c>
-      <c r="J19" s="43"/>
-      <c r="K19" s="43"/>
+      <c r="J19" s="49"/>
+      <c r="K19" s="49"/>
       <c r="L19" s="12"/>
       <c r="O19" s="12"/>
       <c r="AN19" s="12"/>
-      <c r="AQ19" s="44" t="s">
+      <c r="AQ19" s="53" t="s">
         <v>31</v>
       </c>
-      <c r="AR19" s="43"/>
-      <c r="AS19" s="43"/>
+      <c r="AR19" s="49"/>
+      <c r="AS19" s="49"/>
       <c r="AU19" s="38">
         <v>4</v>
       </c>
@@ -2740,52 +2755,52 @@
       <c r="BA22" s="6"/>
     </row>
     <row r="23" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="42" t="s">
+      <c r="A23" s="48" t="s">
         <v>13</v>
       </c>
-      <c r="B23" s="42"/>
-      <c r="C23" s="42"/>
-      <c r="D23" s="42"/>
-      <c r="E23" s="42"/>
-      <c r="F23" s="42"/>
-      <c r="G23" s="42"/>
+      <c r="B23" s="48"/>
+      <c r="C23" s="48"/>
+      <c r="D23" s="48"/>
+      <c r="E23" s="48"/>
+      <c r="F23" s="48"/>
+      <c r="G23" s="48"/>
       <c r="O23" s="12"/>
       <c r="AN23" s="12"/>
-      <c r="AU23" s="42" t="s">
+      <c r="AU23" s="48" t="s">
         <v>13</v>
       </c>
-      <c r="AV23" s="42"/>
-      <c r="AW23" s="42"/>
-      <c r="AX23" s="42"/>
-      <c r="AY23" s="42"/>
-      <c r="AZ23" s="42"/>
-      <c r="BA23" s="42"/>
+      <c r="AV23" s="48"/>
+      <c r="AW23" s="48"/>
+      <c r="AX23" s="48"/>
+      <c r="AY23" s="48"/>
+      <c r="AZ23" s="48"/>
+      <c r="BA23" s="48"/>
     </row>
     <row r="24" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="O24" s="12"/>
       <c r="AN24" s="12"/>
     </row>
     <row r="25" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="42" t="s">
+      <c r="A25" s="48" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="42"/>
-      <c r="C25" s="42"/>
-      <c r="D25" s="42"/>
-      <c r="E25" s="42"/>
-      <c r="F25" s="42"/>
-      <c r="G25" s="42"/>
+      <c r="B25" s="48"/>
+      <c r="C25" s="48"/>
+      <c r="D25" s="48"/>
+      <c r="E25" s="48"/>
+      <c r="F25" s="48"/>
+      <c r="G25" s="48"/>
       <c r="O25" s="12"/>
       <c r="AN25" s="12"/>
-      <c r="AU25" s="42" t="s">
+      <c r="AU25" s="48" t="s">
         <v>42</v>
       </c>
-      <c r="AV25" s="42"/>
-      <c r="AW25" s="42"/>
-      <c r="AX25" s="42"/>
-      <c r="AY25" s="42"/>
-      <c r="AZ25" s="42"/>
-      <c r="BA25" s="42"/>
+      <c r="AV25" s="48"/>
+      <c r="AW25" s="48"/>
+      <c r="AX25" s="48"/>
+      <c r="AY25" s="48"/>
+      <c r="AZ25" s="48"/>
+      <c r="BA25" s="48"/>
     </row>
     <row r="26" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="20" t="s">
@@ -2809,24 +2824,24 @@
       <c r="G26" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="O26" s="44"/>
-      <c r="P26" s="43"/>
-      <c r="Q26" s="43"/>
-      <c r="R26" s="43"/>
-      <c r="S26" s="43"/>
-      <c r="T26" s="43"/>
-      <c r="U26" s="43"/>
-      <c r="V26" s="43"/>
-      <c r="W26" s="43"/>
-      <c r="AE26" s="43"/>
-      <c r="AF26" s="43"/>
-      <c r="AG26" s="43"/>
-      <c r="AH26" s="43"/>
-      <c r="AI26" s="43"/>
-      <c r="AJ26" s="43"/>
-      <c r="AK26" s="43"/>
-      <c r="AL26" s="43"/>
-      <c r="AM26" s="49"/>
+      <c r="O26" s="53"/>
+      <c r="P26" s="49"/>
+      <c r="Q26" s="49"/>
+      <c r="R26" s="49"/>
+      <c r="S26" s="49"/>
+      <c r="T26" s="49"/>
+      <c r="U26" s="49"/>
+      <c r="V26" s="49"/>
+      <c r="W26" s="49"/>
+      <c r="AE26" s="49"/>
+      <c r="AF26" s="49"/>
+      <c r="AG26" s="49"/>
+      <c r="AH26" s="49"/>
+      <c r="AI26" s="49"/>
+      <c r="AJ26" s="49"/>
+      <c r="AK26" s="49"/>
+      <c r="AL26" s="49"/>
+      <c r="AM26" s="57"/>
       <c r="AU26" s="20" t="s">
         <v>2</v>
       </c>
@@ -2923,26 +2938,26 @@
         <v>54</v>
       </c>
       <c r="O28" s="12"/>
-      <c r="P28" s="53" t="s">
+      <c r="P28" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="Q28" s="54"/>
-      <c r="R28" s="54"/>
-      <c r="S28" s="54"/>
-      <c r="T28" s="54"/>
-      <c r="U28" s="54"/>
-      <c r="V28" s="55"/>
+      <c r="Q28" s="42"/>
+      <c r="R28" s="42"/>
+      <c r="S28" s="42"/>
+      <c r="T28" s="42"/>
+      <c r="U28" s="42"/>
+      <c r="V28" s="43"/>
       <c r="X28" s="12"/>
       <c r="AD28" s="13"/>
-      <c r="AF28" s="42" t="s">
+      <c r="AF28" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="AG28" s="42"/>
-      <c r="AH28" s="42"/>
-      <c r="AI28" s="42"/>
-      <c r="AJ28" s="42"/>
-      <c r="AK28" s="42"/>
-      <c r="AL28" s="42"/>
+      <c r="AG28" s="48"/>
+      <c r="AH28" s="48"/>
+      <c r="AI28" s="48"/>
+      <c r="AJ28" s="48"/>
+      <c r="AK28" s="48"/>
+      <c r="AL28" s="48"/>
       <c r="AN28" s="12"/>
       <c r="AU28" s="8">
         <v>2</v>
@@ -3078,19 +3093,25 @@
       <c r="G30" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="I30" s="43" t="s">
+      <c r="I30" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="J30" s="43"/>
-      <c r="K30" s="43"/>
+      <c r="J30" s="49"/>
+      <c r="K30" s="49"/>
       <c r="O30" s="12"/>
       <c r="P30" s="7">
         <v>1</v>
       </c>
-      <c r="Q30" s="39"/>
-      <c r="R30" s="23"/>
+      <c r="Q30" s="39">
+        <v>46163</v>
+      </c>
+      <c r="R30" s="23" t="s">
+        <v>32</v>
+      </c>
       <c r="S30" s="24"/>
-      <c r="T30" s="23"/>
+      <c r="T30" s="23" t="s">
+        <v>26</v>
+      </c>
       <c r="U30" s="24"/>
       <c r="V30" s="25"/>
       <c r="X30" s="12"/>
@@ -3098,18 +3119,24 @@
       <c r="AF30" s="7">
         <v>1</v>
       </c>
-      <c r="AG30" s="29"/>
-      <c r="AH30" s="23"/>
+      <c r="AG30" s="29">
+        <v>46162</v>
+      </c>
+      <c r="AH30" s="23" t="s">
+        <v>38</v>
+      </c>
       <c r="AI30" s="24"/>
-      <c r="AJ30" s="23"/>
+      <c r="AJ30" s="23" t="s">
+        <v>27</v>
+      </c>
       <c r="AK30" s="24"/>
       <c r="AL30" s="25"/>
       <c r="AN30" s="12"/>
-      <c r="AQ30" s="43" t="s">
+      <c r="AQ30" s="49" t="s">
         <v>38</v>
       </c>
-      <c r="AR30" s="43"/>
-      <c r="AS30" s="43"/>
+      <c r="AR30" s="49"/>
+      <c r="AS30" s="49"/>
       <c r="AU30" s="38">
         <v>4</v>
       </c>
@@ -3156,10 +3183,16 @@
       <c r="P31" s="8">
         <v>2</v>
       </c>
-      <c r="Q31" s="40"/>
-      <c r="R31" s="12"/>
+      <c r="Q31" s="40">
+        <v>46165</v>
+      </c>
+      <c r="R31" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="S31" s="13"/>
-      <c r="T31" s="12"/>
+      <c r="T31" s="12" t="s">
+        <v>26</v>
+      </c>
       <c r="U31" s="13"/>
       <c r="V31" s="16"/>
       <c r="X31" s="12"/>
@@ -3167,10 +3200,16 @@
       <c r="AF31" s="8">
         <v>2</v>
       </c>
-      <c r="AG31" s="27"/>
-      <c r="AH31" s="12"/>
+      <c r="AG31" s="27">
+        <v>46164</v>
+      </c>
+      <c r="AH31" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="AI31" s="13"/>
-      <c r="AJ31" s="12"/>
+      <c r="AJ31" s="12" t="s">
+        <v>27</v>
+      </c>
       <c r="AK31" s="13"/>
       <c r="AL31" s="16"/>
       <c r="AN31" s="12"/>
@@ -3223,10 +3262,16 @@
       <c r="P32" s="8">
         <v>3</v>
       </c>
-      <c r="Q32" s="40"/>
-      <c r="R32" s="12"/>
+      <c r="Q32" s="40">
+        <v>46167</v>
+      </c>
+      <c r="R32" s="12" t="s">
+        <v>26</v>
+      </c>
       <c r="S32" s="13"/>
-      <c r="T32" s="12"/>
+      <c r="T32" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="U32" s="13"/>
       <c r="V32" s="16"/>
       <c r="X32" s="12"/>
@@ -3234,10 +3279,16 @@
       <c r="AF32" s="8">
         <v>3</v>
       </c>
-      <c r="AG32" s="27"/>
-      <c r="AH32" s="12"/>
+      <c r="AG32" s="27">
+        <v>46166</v>
+      </c>
+      <c r="AH32" s="12" t="s">
+        <v>27</v>
+      </c>
       <c r="AI32" s="13"/>
-      <c r="AJ32" s="12"/>
+      <c r="AJ32" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="AK32" s="13"/>
       <c r="AL32" s="16"/>
       <c r="AN32" s="12"/>
@@ -3285,10 +3336,16 @@
       <c r="P33" s="8">
         <v>4</v>
       </c>
-      <c r="Q33" s="40"/>
-      <c r="R33" s="12"/>
+      <c r="Q33" s="40">
+        <v>46169</v>
+      </c>
+      <c r="R33" s="12" t="s">
+        <v>26</v>
+      </c>
       <c r="S33" s="13"/>
-      <c r="T33" s="12"/>
+      <c r="T33" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="U33" s="13"/>
       <c r="V33" s="16"/>
       <c r="X33" s="12"/>
@@ -3296,10 +3353,16 @@
       <c r="AF33" s="8">
         <v>4</v>
       </c>
-      <c r="AG33" s="33"/>
-      <c r="AH33" s="12"/>
+      <c r="AG33" s="33">
+        <v>46168</v>
+      </c>
+      <c r="AH33" s="12" t="s">
+        <v>27</v>
+      </c>
       <c r="AI33" s="13"/>
-      <c r="AJ33" s="12"/>
+      <c r="AJ33" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="AK33" s="13"/>
       <c r="AL33" s="16"/>
       <c r="AN33" s="12"/>
@@ -3321,24 +3384,30 @@
       <c r="BA33" s="6"/>
     </row>
     <row r="34" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="42" t="s">
+      <c r="A34" s="48" t="s">
         <v>13</v>
       </c>
-      <c r="B34" s="42"/>
-      <c r="C34" s="42"/>
-      <c r="D34" s="42"/>
-      <c r="E34" s="42"/>
-      <c r="F34" s="42"/>
-      <c r="G34" s="42"/>
+      <c r="B34" s="48"/>
+      <c r="C34" s="48"/>
+      <c r="D34" s="48"/>
+      <c r="E34" s="48"/>
+      <c r="F34" s="48"/>
+      <c r="G34" s="48"/>
       <c r="L34" s="12"/>
       <c r="O34" s="12"/>
       <c r="P34" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="Q34" s="40"/>
-      <c r="R34" s="12"/>
+      <c r="Q34" s="40">
+        <v>46171</v>
+      </c>
+      <c r="R34" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="S34" s="13"/>
-      <c r="T34" s="12"/>
+      <c r="T34" s="12" t="s">
+        <v>26</v>
+      </c>
       <c r="U34" s="13"/>
       <c r="V34" s="16"/>
       <c r="X34" s="12"/>
@@ -3346,23 +3415,29 @@
       <c r="AF34" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="AG34" s="27"/>
-      <c r="AH34" s="12"/>
+      <c r="AG34" s="27">
+        <v>46170</v>
+      </c>
+      <c r="AH34" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="AI34" s="13"/>
-      <c r="AJ34" s="12"/>
+      <c r="AJ34" s="12" t="s">
+        <v>27</v>
+      </c>
       <c r="AK34" s="13"/>
       <c r="AL34" s="16"/>
       <c r="AN34" s="12"/>
       <c r="AQ34" s="12"/>
-      <c r="AU34" s="42" t="s">
+      <c r="AU34" s="48" t="s">
         <v>13</v>
       </c>
-      <c r="AV34" s="42"/>
-      <c r="AW34" s="42"/>
-      <c r="AX34" s="42"/>
-      <c r="AY34" s="42"/>
-      <c r="AZ34" s="42"/>
-      <c r="BA34" s="42"/>
+      <c r="AV34" s="48"/>
+      <c r="AW34" s="48"/>
+      <c r="AX34" s="48"/>
+      <c r="AY34" s="48"/>
+      <c r="AZ34" s="48"/>
+      <c r="BA34" s="48"/>
     </row>
     <row r="35" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L35" s="12"/>
@@ -3370,10 +3445,16 @@
       <c r="P35" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="Q35" s="40"/>
-      <c r="R35" s="12"/>
+      <c r="Q35" s="40">
+        <v>46173</v>
+      </c>
+      <c r="R35" s="12" t="s">
+        <v>26</v>
+      </c>
       <c r="S35" s="13"/>
-      <c r="T35" s="12"/>
+      <c r="T35" s="12" t="s">
+        <v>32</v>
+      </c>
       <c r="U35" s="13"/>
       <c r="V35" s="16"/>
       <c r="X35" s="12"/>
@@ -3381,64 +3462,84 @@
       <c r="AF35" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="AG35" s="27"/>
-      <c r="AH35" s="12"/>
+      <c r="AG35" s="27">
+        <v>46172</v>
+      </c>
+      <c r="AH35" s="12" t="s">
+        <v>27</v>
+      </c>
       <c r="AI35" s="13"/>
-      <c r="AJ35" s="12"/>
+      <c r="AJ35" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="AK35" s="13"/>
       <c r="AL35" s="16"/>
       <c r="AN35" s="12"/>
       <c r="AQ35" s="12"/>
     </row>
     <row r="36" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="45" t="s">
+      <c r="A36" s="47" t="s">
         <v>43</v>
       </c>
-      <c r="B36" s="45"/>
-      <c r="C36" s="45"/>
-      <c r="D36" s="45"/>
-      <c r="E36" s="45"/>
-      <c r="F36" s="45"/>
-      <c r="G36" s="45"/>
-      <c r="L36" s="44" t="s">
+      <c r="B36" s="47"/>
+      <c r="C36" s="47"/>
+      <c r="D36" s="47"/>
+      <c r="E36" s="47"/>
+      <c r="F36" s="47"/>
+      <c r="G36" s="47"/>
+      <c r="L36" s="53" t="s">
         <v>26</v>
       </c>
-      <c r="M36" s="43"/>
-      <c r="N36" s="43"/>
+      <c r="M36" s="49"/>
+      <c r="N36" s="49"/>
       <c r="O36" s="12"/>
       <c r="P36" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="Q36" s="41"/>
-      <c r="R36" s="12"/>
-      <c r="S36" s="13"/>
-      <c r="T36" s="12"/>
-      <c r="U36" s="13"/>
-      <c r="V36" s="16"/>
+      <c r="Q36" s="61">
+        <v>46175</v>
+      </c>
+      <c r="R36" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="S36" s="31"/>
+      <c r="T36" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="U36" s="31"/>
+      <c r="V36" s="32"/>
       <c r="X36" s="12"/>
       <c r="AD36" s="13"/>
       <c r="AF36" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="AG36" s="34"/>
-      <c r="AH36" s="35"/>
+      <c r="AG36" s="34">
+        <v>46174</v>
+      </c>
+      <c r="AH36" s="35" t="s">
+        <v>38</v>
+      </c>
       <c r="AI36" s="36"/>
-      <c r="AJ36" s="35"/>
+      <c r="AJ36" s="35" t="s">
+        <v>27</v>
+      </c>
       <c r="AK36" s="36"/>
       <c r="AL36" s="37"/>
-      <c r="AN36" s="44"/>
-      <c r="AO36" s="43"/>
-      <c r="AP36" s="43"/>
+      <c r="AN36" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="AO36" s="49"/>
+      <c r="AP36" s="49"/>
       <c r="AQ36" s="12"/>
-      <c r="AU36" s="45" t="s">
+      <c r="AU36" s="47" t="s">
         <v>43</v>
       </c>
-      <c r="AV36" s="45"/>
-      <c r="AW36" s="45"/>
-      <c r="AX36" s="45"/>
-      <c r="AY36" s="45"/>
-      <c r="AZ36" s="45"/>
-      <c r="BA36" s="45"/>
+      <c r="AV36" s="47"/>
+      <c r="AW36" s="47"/>
+      <c r="AX36" s="47"/>
+      <c r="AY36" s="47"/>
+      <c r="AZ36" s="47"/>
+      <c r="BA36" s="47"/>
     </row>
     <row r="37" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37" s="20" t="s">
@@ -3463,31 +3564,31 @@
         <v>9</v>
       </c>
       <c r="L37" s="12"/>
-      <c r="P37" s="56" t="s">
+      <c r="P37" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="Q37" s="57"/>
-      <c r="R37" s="57"/>
-      <c r="S37" s="57"/>
-      <c r="T37" s="57"/>
-      <c r="U37" s="57"/>
-      <c r="V37" s="58"/>
-      <c r="X37" s="44"/>
-      <c r="Y37" s="43"/>
-      <c r="Z37" s="43"/>
-      <c r="AA37" s="43"/>
-      <c r="AB37" s="43"/>
-      <c r="AC37" s="43"/>
-      <c r="AD37" s="49"/>
-      <c r="AF37" s="42" t="s">
+      <c r="Q37" s="45"/>
+      <c r="R37" s="45"/>
+      <c r="S37" s="45"/>
+      <c r="T37" s="45"/>
+      <c r="U37" s="45"/>
+      <c r="V37" s="46"/>
+      <c r="X37" s="53"/>
+      <c r="Y37" s="49"/>
+      <c r="Z37" s="49"/>
+      <c r="AA37" s="49"/>
+      <c r="AB37" s="49"/>
+      <c r="AC37" s="49"/>
+      <c r="AD37" s="57"/>
+      <c r="AF37" s="48" t="s">
         <v>13</v>
       </c>
-      <c r="AG37" s="42"/>
-      <c r="AH37" s="42"/>
-      <c r="AI37" s="42"/>
-      <c r="AJ37" s="42"/>
-      <c r="AK37" s="42"/>
-      <c r="AL37" s="42"/>
+      <c r="AG37" s="48"/>
+      <c r="AH37" s="48"/>
+      <c r="AI37" s="48"/>
+      <c r="AJ37" s="48"/>
+      <c r="AK37" s="48"/>
+      <c r="AL37" s="48"/>
       <c r="AQ37" s="12"/>
       <c r="AU37" s="3" t="s">
         <v>2</v>
@@ -3580,33 +3681,33 @@
         <v>53</v>
       </c>
       <c r="L39" s="12"/>
-      <c r="M39" s="53" t="s">
+      <c r="M39" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="N39" s="54"/>
-      <c r="O39" s="54"/>
-      <c r="P39" s="54"/>
-      <c r="Q39" s="54"/>
-      <c r="R39" s="54"/>
-      <c r="S39" s="55"/>
-      <c r="X39" s="42" t="s">
+      <c r="N39" s="42"/>
+      <c r="O39" s="42"/>
+      <c r="P39" s="42"/>
+      <c r="Q39" s="42"/>
+      <c r="R39" s="42"/>
+      <c r="S39" s="43"/>
+      <c r="X39" s="48" t="s">
         <v>21</v>
       </c>
-      <c r="Y39" s="42"/>
-      <c r="Z39" s="42"/>
-      <c r="AA39" s="42"/>
-      <c r="AB39" s="42"/>
-      <c r="AC39" s="42"/>
-      <c r="AD39" s="42"/>
-      <c r="AI39" s="53" t="s">
+      <c r="Y39" s="48"/>
+      <c r="Z39" s="48"/>
+      <c r="AA39" s="48"/>
+      <c r="AB39" s="48"/>
+      <c r="AC39" s="48"/>
+      <c r="AD39" s="48"/>
+      <c r="AI39" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="AJ39" s="54"/>
-      <c r="AK39" s="54"/>
-      <c r="AL39" s="54"/>
-      <c r="AM39" s="54"/>
-      <c r="AN39" s="54"/>
-      <c r="AO39" s="55"/>
+      <c r="AJ39" s="42"/>
+      <c r="AK39" s="42"/>
+      <c r="AL39" s="42"/>
+      <c r="AM39" s="42"/>
+      <c r="AN39" s="42"/>
+      <c r="AO39" s="43"/>
       <c r="AQ39" s="12"/>
       <c r="AU39" s="8">
         <v>2</v>
@@ -3761,11 +3862,11 @@
       <c r="G41" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="I41" s="43" t="s">
+      <c r="I41" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="J41" s="43"/>
-      <c r="K41" s="43"/>
+      <c r="J41" s="49"/>
+      <c r="K41" s="49"/>
       <c r="L41" s="12"/>
       <c r="M41" s="7">
         <v>1</v>
@@ -3818,11 +3919,11 @@
       <c r="AO41" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="AQ41" s="44" t="s">
+      <c r="AQ41" s="53" t="s">
         <v>23</v>
       </c>
-      <c r="AR41" s="43"/>
-      <c r="AS41" s="43"/>
+      <c r="AR41" s="49"/>
+      <c r="AS41" s="49"/>
       <c r="AU41" s="38">
         <v>4</v>
       </c>
@@ -4128,15 +4229,15 @@
       <c r="BA44" s="6"/>
     </row>
     <row r="45" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="42" t="s">
+      <c r="A45" s="48" t="s">
         <v>13</v>
       </c>
-      <c r="B45" s="42"/>
-      <c r="C45" s="42"/>
-      <c r="D45" s="42"/>
-      <c r="E45" s="42"/>
-      <c r="F45" s="42"/>
-      <c r="G45" s="42"/>
+      <c r="B45" s="48"/>
+      <c r="C45" s="48"/>
+      <c r="D45" s="48"/>
+      <c r="E45" s="48"/>
+      <c r="F45" s="48"/>
+      <c r="G45" s="48"/>
       <c r="M45" s="8" t="s">
         <v>11</v>
       </c>
@@ -4185,15 +4286,15 @@
       <c r="AP45" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AU45" s="42" t="s">
+      <c r="AU45" s="48" t="s">
         <v>13</v>
       </c>
-      <c r="AV45" s="42"/>
-      <c r="AW45" s="42"/>
-      <c r="AX45" s="42"/>
-      <c r="AY45" s="42"/>
-      <c r="AZ45" s="42"/>
-      <c r="BA45" s="42"/>
+      <c r="AV45" s="48"/>
+      <c r="AW45" s="48"/>
+      <c r="AX45" s="48"/>
+      <c r="AY45" s="48"/>
+      <c r="AZ45" s="48"/>
+      <c r="BA45" s="48"/>
     </row>
     <row r="46" spans="1:54" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="M46" s="8" t="s">
@@ -4284,45 +4385,65 @@
       <c r="AO47" s="6"/>
     </row>
     <row r="48" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="M48" s="53" t="s">
+      <c r="M48" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="N48" s="54"/>
-      <c r="O48" s="54"/>
-      <c r="P48" s="54"/>
-      <c r="Q48" s="54"/>
-      <c r="R48" s="54"/>
-      <c r="S48" s="55"/>
-      <c r="X48" s="42" t="s">
+      <c r="N48" s="42"/>
+      <c r="O48" s="42"/>
+      <c r="P48" s="42"/>
+      <c r="Q48" s="42"/>
+      <c r="R48" s="42"/>
+      <c r="S48" s="43"/>
+      <c r="X48" s="48" t="s">
         <v>13</v>
       </c>
-      <c r="Y48" s="42"/>
-      <c r="Z48" s="42"/>
-      <c r="AA48" s="42"/>
-      <c r="AB48" s="42"/>
-      <c r="AC48" s="42"/>
-      <c r="AD48" s="42"/>
-      <c r="AI48" s="42" t="s">
+      <c r="Y48" s="48"/>
+      <c r="Z48" s="48"/>
+      <c r="AA48" s="48"/>
+      <c r="AB48" s="48"/>
+      <c r="AC48" s="48"/>
+      <c r="AD48" s="48"/>
+      <c r="AI48" s="48" t="s">
         <v>13</v>
       </c>
-      <c r="AJ48" s="42"/>
-      <c r="AK48" s="42"/>
-      <c r="AL48" s="42"/>
-      <c r="AM48" s="42"/>
-      <c r="AN48" s="42"/>
-      <c r="AO48" s="42"/>
+      <c r="AJ48" s="48"/>
+      <c r="AK48" s="48"/>
+      <c r="AL48" s="48"/>
+      <c r="AM48" s="48"/>
+      <c r="AN48" s="48"/>
+      <c r="AO48" s="48"/>
     </row>
     <row r="49" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="M48:S48"/>
-    <mergeCell ref="M39:S39"/>
-    <mergeCell ref="P37:V37"/>
-    <mergeCell ref="P28:V28"/>
-    <mergeCell ref="A36:G36"/>
-    <mergeCell ref="A45:G45"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="AU45:BA45"/>
+    <mergeCell ref="AF28:AL28"/>
+    <mergeCell ref="AF37:AL37"/>
+    <mergeCell ref="AQ30:AS30"/>
+    <mergeCell ref="AQ41:AS41"/>
+    <mergeCell ref="AU34:BA34"/>
+    <mergeCell ref="AU36:BA36"/>
+    <mergeCell ref="AU2:BA2"/>
+    <mergeCell ref="AU3:BA3"/>
+    <mergeCell ref="AU12:BA12"/>
+    <mergeCell ref="AU14:BA14"/>
+    <mergeCell ref="AU23:BA23"/>
+    <mergeCell ref="X37:AD37"/>
+    <mergeCell ref="AE26:AM26"/>
+    <mergeCell ref="Z1:AB1"/>
+    <mergeCell ref="X39:AD39"/>
+    <mergeCell ref="X48:AD48"/>
+    <mergeCell ref="AF1:BA1"/>
+    <mergeCell ref="AI2:AO2"/>
+    <mergeCell ref="AI3:AO3"/>
+    <mergeCell ref="AI12:AO12"/>
+    <mergeCell ref="AI39:AO39"/>
+    <mergeCell ref="AU25:BA25"/>
+    <mergeCell ref="AI48:AO48"/>
+    <mergeCell ref="AN14:AP14"/>
+    <mergeCell ref="AN36:AP36"/>
+    <mergeCell ref="AQ8:AS8"/>
+    <mergeCell ref="AQ19:AS19"/>
     <mergeCell ref="A1:U1"/>
     <mergeCell ref="O26:W26"/>
     <mergeCell ref="I41:K41"/>
@@ -4339,34 +4460,14 @@
     <mergeCell ref="I8:K8"/>
     <mergeCell ref="I19:K19"/>
     <mergeCell ref="A25:G25"/>
-    <mergeCell ref="X37:AD37"/>
-    <mergeCell ref="AE26:AM26"/>
-    <mergeCell ref="Z1:AB1"/>
-    <mergeCell ref="X39:AD39"/>
-    <mergeCell ref="X48:AD48"/>
-    <mergeCell ref="AF1:BA1"/>
-    <mergeCell ref="AI2:AO2"/>
-    <mergeCell ref="AI3:AO3"/>
-    <mergeCell ref="AI12:AO12"/>
-    <mergeCell ref="AI39:AO39"/>
-    <mergeCell ref="AU25:BA25"/>
-    <mergeCell ref="AI48:AO48"/>
-    <mergeCell ref="AN14:AP14"/>
-    <mergeCell ref="AN36:AP36"/>
-    <mergeCell ref="AQ8:AS8"/>
-    <mergeCell ref="AQ19:AS19"/>
-    <mergeCell ref="AU2:BA2"/>
-    <mergeCell ref="AU3:BA3"/>
-    <mergeCell ref="AU12:BA12"/>
-    <mergeCell ref="AU14:BA14"/>
-    <mergeCell ref="AU23:BA23"/>
-    <mergeCell ref="AU45:BA45"/>
-    <mergeCell ref="AF28:AL28"/>
-    <mergeCell ref="AF37:AL37"/>
-    <mergeCell ref="AQ30:AS30"/>
-    <mergeCell ref="AQ41:AS41"/>
-    <mergeCell ref="AU34:BA34"/>
-    <mergeCell ref="AU36:BA36"/>
+    <mergeCell ref="M48:S48"/>
+    <mergeCell ref="M39:S39"/>
+    <mergeCell ref="P37:V37"/>
+    <mergeCell ref="P28:V28"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="A34:G34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/2025_2026/Playoffs/Brackets.xlsx
+++ b/2025_2026/Playoffs/Brackets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\NHLStats\2025_2026\Playoffs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01DE515A-AFA9-4C79-AFD1-700FAC672FC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA1AACC5-88CA-4FBF-8F8D-542C621AB781}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="94">
   <si>
     <t>Eastern Conference Playoff Teams</t>
   </si>
@@ -683,6 +683,42 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -701,37 +737,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -739,12 +745,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1113,18 +1113,18 @@
     </row>
     <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="11" spans="1:7" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="60" t="s">
+      <c r="A11" s="59" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="60"/>
-      <c r="C11" s="60" t="s">
+      <c r="B11" s="59"/>
+      <c r="C11" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="60"/>
-      <c r="E11" s="60" t="s">
+      <c r="D11" s="59"/>
+      <c r="E11" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="60"/>
+      <c r="F11" s="59"/>
       <c r="G11" s="4" t="s">
         <v>18</v>
       </c>
@@ -1153,18 +1153,18 @@
       </c>
     </row>
     <row r="13" spans="1:7" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="58" t="s">
+      <c r="A13" s="60" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="59"/>
-      <c r="C13" s="58" t="s">
+      <c r="B13" s="61"/>
+      <c r="C13" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="D13" s="59"/>
-      <c r="E13" s="58" t="s">
+      <c r="D13" s="61"/>
+      <c r="E13" s="60" t="s">
         <v>17</v>
       </c>
-      <c r="F13" s="59"/>
+      <c r="F13" s="61"/>
       <c r="G13" s="5"/>
     </row>
     <row r="14" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1209,14 +1209,14 @@
       </c>
     </row>
     <row r="16" spans="1:7" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="58" t="s">
+      <c r="A16" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="59"/>
-      <c r="C16" s="58" t="s">
+      <c r="B16" s="61"/>
+      <c r="C16" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="59"/>
+      <c r="D16" s="61"/>
     </row>
     <row r="17" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
@@ -1247,10 +1247,10 @@
       </c>
     </row>
     <row r="19" spans="1:4" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="58" t="s">
+      <c r="A19" s="60" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="59"/>
+      <c r="B19" s="61"/>
     </row>
     <row r="20" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
@@ -1269,10 +1269,10 @@
       </c>
     </row>
     <row r="22" spans="1:4" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="58" t="s">
+      <c r="A22" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="59"/>
+      <c r="B22" s="61"/>
     </row>
     <row r="23" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
@@ -1357,16 +1357,16 @@
     <sortCondition ref="B2:B9"/>
   </sortState>
   <mergeCells count="10">
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C16:D16"/>
     <mergeCell ref="E11:F11"/>
     <mergeCell ref="E13:F13"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C16:D16"/>
   </mergeCells>
   <dataValidations count="16">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C14" xr:uid="{2C3D9587-ABAE-4E3F-8B22-396DF812BF02}">
@@ -1455,7 +1455,7 @@
     <col min="34" max="34" width="22.85546875" style="1" customWidth="1"/>
     <col min="35" max="36" width="21.7109375" style="1" customWidth="1"/>
     <col min="37" max="37" width="22.28515625" style="1" customWidth="1"/>
-    <col min="38" max="38" width="20.7109375" style="1" customWidth="1"/>
+    <col min="38" max="38" width="25.85546875" style="1" customWidth="1"/>
     <col min="39" max="39" width="22.140625" style="1" customWidth="1"/>
     <col min="40" max="40" width="9.140625" style="1"/>
     <col min="41" max="41" width="29.42578125" style="1" customWidth="1"/>
@@ -1524,70 +1524,70 @@
       <c r="BA1" s="52"/>
     </row>
     <row r="2" spans="1:54" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="54" t="s">
+      <c r="A2" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="55"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="56"/>
-      <c r="M2" s="54" t="s">
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="48"/>
+      <c r="M2" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="55"/>
-      <c r="O2" s="55"/>
-      <c r="P2" s="55"/>
-      <c r="Q2" s="55"/>
-      <c r="R2" s="56"/>
-      <c r="AI2" s="54" t="s">
+      <c r="N2" s="47"/>
+      <c r="O2" s="47"/>
+      <c r="P2" s="47"/>
+      <c r="Q2" s="47"/>
+      <c r="R2" s="48"/>
+      <c r="AI2" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="AJ2" s="55"/>
-      <c r="AK2" s="55"/>
-      <c r="AL2" s="55"/>
-      <c r="AM2" s="55"/>
-      <c r="AN2" s="55"/>
-      <c r="AO2" s="56"/>
-      <c r="AU2" s="54" t="s">
+      <c r="AJ2" s="47"/>
+      <c r="AK2" s="47"/>
+      <c r="AL2" s="47"/>
+      <c r="AM2" s="47"/>
+      <c r="AN2" s="47"/>
+      <c r="AO2" s="48"/>
+      <c r="AU2" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="AV2" s="55"/>
-      <c r="AW2" s="55"/>
-      <c r="AX2" s="55"/>
-      <c r="AY2" s="55"/>
-      <c r="AZ2" s="55"/>
-      <c r="BA2" s="56"/>
+      <c r="AV2" s="47"/>
+      <c r="AW2" s="47"/>
+      <c r="AX2" s="47"/>
+      <c r="AY2" s="47"/>
+      <c r="AZ2" s="47"/>
+      <c r="BA2" s="48"/>
     </row>
     <row r="3" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="48" t="s">
+      <c r="A3" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="48"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="AI3" s="41" t="s">
+      <c r="B3" s="42"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="42"/>
+      <c r="AI3" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="AJ3" s="42"/>
-      <c r="AK3" s="42"/>
-      <c r="AL3" s="42"/>
-      <c r="AM3" s="42"/>
-      <c r="AN3" s="42"/>
-      <c r="AO3" s="43"/>
-      <c r="AU3" s="48" t="s">
+      <c r="AJ3" s="54"/>
+      <c r="AK3" s="54"/>
+      <c r="AL3" s="54"/>
+      <c r="AM3" s="54"/>
+      <c r="AN3" s="54"/>
+      <c r="AO3" s="55"/>
+      <c r="AU3" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="AV3" s="48"/>
-      <c r="AW3" s="48"/>
-      <c r="AX3" s="48"/>
-      <c r="AY3" s="48"/>
-      <c r="AZ3" s="48"/>
-      <c r="BA3" s="48"/>
+      <c r="AV3" s="42"/>
+      <c r="AW3" s="42"/>
+      <c r="AX3" s="42"/>
+      <c r="AY3" s="42"/>
+      <c r="AZ3" s="42"/>
+      <c r="BA3" s="42"/>
     </row>
     <row r="4" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
@@ -1611,15 +1611,15 @@
       <c r="G4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="41" t="s">
+      <c r="M4" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="N4" s="42"/>
-      <c r="O4" s="42"/>
-      <c r="P4" s="42"/>
-      <c r="Q4" s="42"/>
-      <c r="R4" s="42"/>
-      <c r="S4" s="43"/>
+      <c r="N4" s="54"/>
+      <c r="O4" s="54"/>
+      <c r="P4" s="54"/>
+      <c r="Q4" s="54"/>
+      <c r="R4" s="54"/>
+      <c r="S4" s="55"/>
       <c r="AI4" s="3" t="s">
         <v>2</v>
       </c>
@@ -1946,11 +1946,11 @@
       <c r="G8" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="I8" s="49" t="s">
+      <c r="I8" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="J8" s="49"/>
-      <c r="K8" s="49"/>
+      <c r="J8" s="43"/>
+      <c r="K8" s="43"/>
       <c r="M8" s="8">
         <v>3</v>
       </c>
@@ -1993,11 +1993,11 @@
       <c r="AO8" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="AQ8" s="49" t="s">
+      <c r="AQ8" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="AR8" s="49"/>
-      <c r="AS8" s="49"/>
+      <c r="AR8" s="43"/>
+      <c r="AS8" s="43"/>
       <c r="AU8" s="38">
         <v>4</v>
       </c>
@@ -2257,15 +2257,15 @@
       <c r="BA11" s="6"/>
     </row>
     <row r="12" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="48" t="s">
+      <c r="A12" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="48"/>
-      <c r="C12" s="48"/>
-      <c r="D12" s="48"/>
-      <c r="E12" s="48"/>
-      <c r="F12" s="48"/>
-      <c r="G12" s="48"/>
+      <c r="B12" s="42"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="42"/>
       <c r="L12" s="12"/>
       <c r="M12" s="8" t="s">
         <v>12</v>
@@ -2291,69 +2291,69 @@
       <c r="T12" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AI12" s="48" t="s">
+      <c r="AI12" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AJ12" s="48"/>
-      <c r="AK12" s="48"/>
-      <c r="AL12" s="48"/>
-      <c r="AM12" s="48"/>
-      <c r="AN12" s="48"/>
-      <c r="AO12" s="48"/>
+      <c r="AJ12" s="42"/>
+      <c r="AK12" s="42"/>
+      <c r="AL12" s="42"/>
+      <c r="AM12" s="42"/>
+      <c r="AN12" s="42"/>
+      <c r="AO12" s="42"/>
       <c r="AQ12" s="12"/>
-      <c r="AU12" s="48" t="s">
+      <c r="AU12" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AV12" s="48"/>
-      <c r="AW12" s="48"/>
-      <c r="AX12" s="48"/>
-      <c r="AY12" s="48"/>
-      <c r="AZ12" s="48"/>
-      <c r="BA12" s="48"/>
+      <c r="AV12" s="42"/>
+      <c r="AW12" s="42"/>
+      <c r="AX12" s="42"/>
+      <c r="AY12" s="42"/>
+      <c r="AZ12" s="42"/>
+      <c r="BA12" s="42"/>
     </row>
     <row r="13" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L13" s="12"/>
-      <c r="M13" s="41" t="s">
+      <c r="M13" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="N13" s="42"/>
-      <c r="O13" s="42"/>
-      <c r="P13" s="42"/>
-      <c r="Q13" s="42"/>
-      <c r="R13" s="42"/>
-      <c r="S13" s="43"/>
+      <c r="N13" s="54"/>
+      <c r="O13" s="54"/>
+      <c r="P13" s="54"/>
+      <c r="Q13" s="54"/>
+      <c r="R13" s="54"/>
+      <c r="S13" s="55"/>
       <c r="AQ13" s="12"/>
     </row>
     <row r="14" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="47" t="s">
+      <c r="A14" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="47"/>
-      <c r="C14" s="47"/>
-      <c r="D14" s="47"/>
-      <c r="E14" s="47"/>
-      <c r="F14" s="47"/>
-      <c r="G14" s="47"/>
-      <c r="L14" s="53" t="s">
+      <c r="B14" s="45"/>
+      <c r="C14" s="45"/>
+      <c r="D14" s="45"/>
+      <c r="E14" s="45"/>
+      <c r="F14" s="45"/>
+      <c r="G14" s="45"/>
+      <c r="L14" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="M14" s="49"/>
-      <c r="N14" s="49"/>
-      <c r="AN14" s="49" t="s">
+      <c r="M14" s="43"/>
+      <c r="N14" s="43"/>
+      <c r="AN14" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="AO14" s="49"/>
-      <c r="AP14" s="49"/>
+      <c r="AO14" s="43"/>
+      <c r="AP14" s="43"/>
       <c r="AQ14" s="12"/>
-      <c r="AU14" s="47" t="s">
+      <c r="AU14" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="AV14" s="47"/>
-      <c r="AW14" s="47"/>
-      <c r="AX14" s="47"/>
-      <c r="AY14" s="47"/>
-      <c r="AZ14" s="47"/>
-      <c r="BA14" s="47"/>
+      <c r="AV14" s="45"/>
+      <c r="AW14" s="45"/>
+      <c r="AX14" s="45"/>
+      <c r="AY14" s="45"/>
+      <c r="AZ14" s="45"/>
+      <c r="BA14" s="45"/>
     </row>
     <row r="15" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
@@ -2581,19 +2581,19 @@
       <c r="G19" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="I19" s="49" t="s">
+      <c r="I19" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="J19" s="49"/>
-      <c r="K19" s="49"/>
+      <c r="J19" s="43"/>
+      <c r="K19" s="43"/>
       <c r="L19" s="12"/>
       <c r="O19" s="12"/>
       <c r="AN19" s="12"/>
-      <c r="AQ19" s="53" t="s">
+      <c r="AQ19" s="44" t="s">
         <v>31</v>
       </c>
-      <c r="AR19" s="49"/>
-      <c r="AS19" s="49"/>
+      <c r="AR19" s="43"/>
+      <c r="AS19" s="43"/>
       <c r="AU19" s="38">
         <v>4</v>
       </c>
@@ -2755,52 +2755,52 @@
       <c r="BA22" s="6"/>
     </row>
     <row r="23" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="48" t="s">
+      <c r="A23" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B23" s="48"/>
-      <c r="C23" s="48"/>
-      <c r="D23" s="48"/>
-      <c r="E23" s="48"/>
-      <c r="F23" s="48"/>
-      <c r="G23" s="48"/>
+      <c r="B23" s="42"/>
+      <c r="C23" s="42"/>
+      <c r="D23" s="42"/>
+      <c r="E23" s="42"/>
+      <c r="F23" s="42"/>
+      <c r="G23" s="42"/>
       <c r="O23" s="12"/>
       <c r="AN23" s="12"/>
-      <c r="AU23" s="48" t="s">
+      <c r="AU23" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AV23" s="48"/>
-      <c r="AW23" s="48"/>
-      <c r="AX23" s="48"/>
-      <c r="AY23" s="48"/>
-      <c r="AZ23" s="48"/>
-      <c r="BA23" s="48"/>
+      <c r="AV23" s="42"/>
+      <c r="AW23" s="42"/>
+      <c r="AX23" s="42"/>
+      <c r="AY23" s="42"/>
+      <c r="AZ23" s="42"/>
+      <c r="BA23" s="42"/>
     </row>
     <row r="24" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="O24" s="12"/>
       <c r="AN24" s="12"/>
     </row>
     <row r="25" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="48" t="s">
+      <c r="A25" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="48"/>
-      <c r="C25" s="48"/>
-      <c r="D25" s="48"/>
-      <c r="E25" s="48"/>
-      <c r="F25" s="48"/>
-      <c r="G25" s="48"/>
+      <c r="B25" s="42"/>
+      <c r="C25" s="42"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="42"/>
+      <c r="F25" s="42"/>
+      <c r="G25" s="42"/>
       <c r="O25" s="12"/>
       <c r="AN25" s="12"/>
-      <c r="AU25" s="48" t="s">
+      <c r="AU25" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="AV25" s="48"/>
-      <c r="AW25" s="48"/>
-      <c r="AX25" s="48"/>
-      <c r="AY25" s="48"/>
-      <c r="AZ25" s="48"/>
-      <c r="BA25" s="48"/>
+      <c r="AV25" s="42"/>
+      <c r="AW25" s="42"/>
+      <c r="AX25" s="42"/>
+      <c r="AY25" s="42"/>
+      <c r="AZ25" s="42"/>
+      <c r="BA25" s="42"/>
     </row>
     <row r="26" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="20" t="s">
@@ -2824,24 +2824,24 @@
       <c r="G26" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="O26" s="53"/>
-      <c r="P26" s="49"/>
-      <c r="Q26" s="49"/>
-      <c r="R26" s="49"/>
-      <c r="S26" s="49"/>
-      <c r="T26" s="49"/>
-      <c r="U26" s="49"/>
-      <c r="V26" s="49"/>
-      <c r="W26" s="49"/>
-      <c r="AE26" s="49"/>
-      <c r="AF26" s="49"/>
-      <c r="AG26" s="49"/>
-      <c r="AH26" s="49"/>
-      <c r="AI26" s="49"/>
-      <c r="AJ26" s="49"/>
-      <c r="AK26" s="49"/>
-      <c r="AL26" s="49"/>
-      <c r="AM26" s="57"/>
+      <c r="O26" s="44"/>
+      <c r="P26" s="43"/>
+      <c r="Q26" s="43"/>
+      <c r="R26" s="43"/>
+      <c r="S26" s="43"/>
+      <c r="T26" s="43"/>
+      <c r="U26" s="43"/>
+      <c r="V26" s="43"/>
+      <c r="W26" s="43"/>
+      <c r="AE26" s="43"/>
+      <c r="AF26" s="43"/>
+      <c r="AG26" s="43"/>
+      <c r="AH26" s="43"/>
+      <c r="AI26" s="43"/>
+      <c r="AJ26" s="43"/>
+      <c r="AK26" s="43"/>
+      <c r="AL26" s="43"/>
+      <c r="AM26" s="49"/>
       <c r="AU26" s="20" t="s">
         <v>2</v>
       </c>
@@ -2938,26 +2938,26 @@
         <v>54</v>
       </c>
       <c r="O28" s="12"/>
-      <c r="P28" s="41" t="s">
+      <c r="P28" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="Q28" s="42"/>
-      <c r="R28" s="42"/>
-      <c r="S28" s="42"/>
-      <c r="T28" s="42"/>
-      <c r="U28" s="42"/>
-      <c r="V28" s="43"/>
+      <c r="Q28" s="54"/>
+      <c r="R28" s="54"/>
+      <c r="S28" s="54"/>
+      <c r="T28" s="54"/>
+      <c r="U28" s="54"/>
+      <c r="V28" s="55"/>
       <c r="X28" s="12"/>
       <c r="AD28" s="13"/>
-      <c r="AF28" s="48" t="s">
+      <c r="AF28" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="AG28" s="48"/>
-      <c r="AH28" s="48"/>
-      <c r="AI28" s="48"/>
-      <c r="AJ28" s="48"/>
-      <c r="AK28" s="48"/>
-      <c r="AL28" s="48"/>
+      <c r="AG28" s="42"/>
+      <c r="AH28" s="42"/>
+      <c r="AI28" s="42"/>
+      <c r="AJ28" s="42"/>
+      <c r="AK28" s="42"/>
+      <c r="AL28" s="42"/>
       <c r="AN28" s="12"/>
       <c r="AU28" s="8">
         <v>2</v>
@@ -3093,11 +3093,11 @@
       <c r="G30" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="I30" s="49" t="s">
+      <c r="I30" s="43" t="s">
         <v>26</v>
       </c>
-      <c r="J30" s="49"/>
-      <c r="K30" s="49"/>
+      <c r="J30" s="43"/>
+      <c r="K30" s="43"/>
       <c r="O30" s="12"/>
       <c r="P30" s="7">
         <v>1</v>
@@ -3108,12 +3108,18 @@
       <c r="R30" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="S30" s="24"/>
+      <c r="S30" s="24">
+        <v>6</v>
+      </c>
       <c r="T30" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="U30" s="24"/>
-      <c r="V30" s="25"/>
+      <c r="U30" s="24">
+        <v>2</v>
+      </c>
+      <c r="V30" s="25" t="s">
+        <v>50</v>
+      </c>
       <c r="X30" s="12"/>
       <c r="AD30" s="13"/>
       <c r="AF30" s="7">
@@ -3125,18 +3131,24 @@
       <c r="AH30" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="AI30" s="24"/>
+      <c r="AI30" s="24">
+        <v>4</v>
+      </c>
       <c r="AJ30" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="AK30" s="24"/>
-      <c r="AL30" s="25"/>
+      <c r="AK30" s="24">
+        <v>2</v>
+      </c>
+      <c r="AL30" s="25" t="s">
+        <v>52</v>
+      </c>
       <c r="AN30" s="12"/>
-      <c r="AQ30" s="49" t="s">
+      <c r="AQ30" s="43" t="s">
         <v>38</v>
       </c>
-      <c r="AR30" s="49"/>
-      <c r="AS30" s="49"/>
+      <c r="AR30" s="43"/>
+      <c r="AS30" s="43"/>
       <c r="AU30" s="38">
         <v>4</v>
       </c>
@@ -3384,15 +3396,15 @@
       <c r="BA33" s="6"/>
     </row>
     <row r="34" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="48" t="s">
+      <c r="A34" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B34" s="48"/>
-      <c r="C34" s="48"/>
-      <c r="D34" s="48"/>
-      <c r="E34" s="48"/>
-      <c r="F34" s="48"/>
-      <c r="G34" s="48"/>
+      <c r="B34" s="42"/>
+      <c r="C34" s="42"/>
+      <c r="D34" s="42"/>
+      <c r="E34" s="42"/>
+      <c r="F34" s="42"/>
+      <c r="G34" s="42"/>
       <c r="L34" s="12"/>
       <c r="O34" s="12"/>
       <c r="P34" s="8" t="s">
@@ -3429,15 +3441,15 @@
       <c r="AL34" s="16"/>
       <c r="AN34" s="12"/>
       <c r="AQ34" s="12"/>
-      <c r="AU34" s="48" t="s">
+      <c r="AU34" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AV34" s="48"/>
-      <c r="AW34" s="48"/>
-      <c r="AX34" s="48"/>
-      <c r="AY34" s="48"/>
-      <c r="AZ34" s="48"/>
-      <c r="BA34" s="48"/>
+      <c r="AV34" s="42"/>
+      <c r="AW34" s="42"/>
+      <c r="AX34" s="42"/>
+      <c r="AY34" s="42"/>
+      <c r="AZ34" s="42"/>
+      <c r="BA34" s="42"/>
     </row>
     <row r="35" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L35" s="12"/>
@@ -3478,25 +3490,25 @@
       <c r="AQ35" s="12"/>
     </row>
     <row r="36" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="47" t="s">
+      <c r="A36" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="B36" s="47"/>
-      <c r="C36" s="47"/>
-      <c r="D36" s="47"/>
-      <c r="E36" s="47"/>
-      <c r="F36" s="47"/>
-      <c r="G36" s="47"/>
-      <c r="L36" s="53" t="s">
+      <c r="B36" s="45"/>
+      <c r="C36" s="45"/>
+      <c r="D36" s="45"/>
+      <c r="E36" s="45"/>
+      <c r="F36" s="45"/>
+      <c r="G36" s="45"/>
+      <c r="L36" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="M36" s="49"/>
-      <c r="N36" s="49"/>
+      <c r="M36" s="43"/>
+      <c r="N36" s="43"/>
       <c r="O36" s="12"/>
       <c r="P36" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="Q36" s="61">
+      <c r="Q36" s="41">
         <v>46175</v>
       </c>
       <c r="R36" s="30" t="s">
@@ -3525,21 +3537,21 @@
       </c>
       <c r="AK36" s="36"/>
       <c r="AL36" s="37"/>
-      <c r="AN36" s="53" t="s">
+      <c r="AN36" s="44" t="s">
         <v>38</v>
       </c>
-      <c r="AO36" s="49"/>
-      <c r="AP36" s="49"/>
+      <c r="AO36" s="43"/>
+      <c r="AP36" s="43"/>
       <c r="AQ36" s="12"/>
-      <c r="AU36" s="47" t="s">
+      <c r="AU36" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="AV36" s="47"/>
-      <c r="AW36" s="47"/>
-      <c r="AX36" s="47"/>
-      <c r="AY36" s="47"/>
-      <c r="AZ36" s="47"/>
-      <c r="BA36" s="47"/>
+      <c r="AV36" s="45"/>
+      <c r="AW36" s="45"/>
+      <c r="AX36" s="45"/>
+      <c r="AY36" s="45"/>
+      <c r="AZ36" s="45"/>
+      <c r="BA36" s="45"/>
     </row>
     <row r="37" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37" s="20" t="s">
@@ -3564,31 +3576,31 @@
         <v>9</v>
       </c>
       <c r="L37" s="12"/>
-      <c r="P37" s="44" t="s">
+      <c r="P37" s="56" t="s">
         <v>13</v>
       </c>
-      <c r="Q37" s="45"/>
-      <c r="R37" s="45"/>
-      <c r="S37" s="45"/>
-      <c r="T37" s="45"/>
-      <c r="U37" s="45"/>
-      <c r="V37" s="46"/>
-      <c r="X37" s="53"/>
-      <c r="Y37" s="49"/>
-      <c r="Z37" s="49"/>
-      <c r="AA37" s="49"/>
-      <c r="AB37" s="49"/>
-      <c r="AC37" s="49"/>
-      <c r="AD37" s="57"/>
-      <c r="AF37" s="48" t="s">
+      <c r="Q37" s="57"/>
+      <c r="R37" s="57"/>
+      <c r="S37" s="57"/>
+      <c r="T37" s="57"/>
+      <c r="U37" s="57"/>
+      <c r="V37" s="58"/>
+      <c r="X37" s="44"/>
+      <c r="Y37" s="43"/>
+      <c r="Z37" s="43"/>
+      <c r="AA37" s="43"/>
+      <c r="AB37" s="43"/>
+      <c r="AC37" s="43"/>
+      <c r="AD37" s="49"/>
+      <c r="AF37" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AG37" s="48"/>
-      <c r="AH37" s="48"/>
-      <c r="AI37" s="48"/>
-      <c r="AJ37" s="48"/>
-      <c r="AK37" s="48"/>
-      <c r="AL37" s="48"/>
+      <c r="AG37" s="42"/>
+      <c r="AH37" s="42"/>
+      <c r="AI37" s="42"/>
+      <c r="AJ37" s="42"/>
+      <c r="AK37" s="42"/>
+      <c r="AL37" s="42"/>
       <c r="AQ37" s="12"/>
       <c r="AU37" s="3" t="s">
         <v>2</v>
@@ -3681,33 +3693,33 @@
         <v>53</v>
       </c>
       <c r="L39" s="12"/>
-      <c r="M39" s="41" t="s">
+      <c r="M39" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="N39" s="42"/>
-      <c r="O39" s="42"/>
-      <c r="P39" s="42"/>
-      <c r="Q39" s="42"/>
-      <c r="R39" s="42"/>
-      <c r="S39" s="43"/>
-      <c r="X39" s="48" t="s">
+      <c r="N39" s="54"/>
+      <c r="O39" s="54"/>
+      <c r="P39" s="54"/>
+      <c r="Q39" s="54"/>
+      <c r="R39" s="54"/>
+      <c r="S39" s="55"/>
+      <c r="X39" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="Y39" s="48"/>
-      <c r="Z39" s="48"/>
-      <c r="AA39" s="48"/>
-      <c r="AB39" s="48"/>
-      <c r="AC39" s="48"/>
-      <c r="AD39" s="48"/>
-      <c r="AI39" s="41" t="s">
+      <c r="Y39" s="42"/>
+      <c r="Z39" s="42"/>
+      <c r="AA39" s="42"/>
+      <c r="AB39" s="42"/>
+      <c r="AC39" s="42"/>
+      <c r="AD39" s="42"/>
+      <c r="AI39" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="AJ39" s="42"/>
-      <c r="AK39" s="42"/>
-      <c r="AL39" s="42"/>
-      <c r="AM39" s="42"/>
-      <c r="AN39" s="42"/>
-      <c r="AO39" s="43"/>
+      <c r="AJ39" s="54"/>
+      <c r="AK39" s="54"/>
+      <c r="AL39" s="54"/>
+      <c r="AM39" s="54"/>
+      <c r="AN39" s="54"/>
+      <c r="AO39" s="55"/>
       <c r="AQ39" s="12"/>
       <c r="AU39" s="8">
         <v>2</v>
@@ -3862,11 +3874,11 @@
       <c r="G41" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="I41" s="49" t="s">
+      <c r="I41" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="J41" s="49"/>
-      <c r="K41" s="49"/>
+      <c r="J41" s="43"/>
+      <c r="K41" s="43"/>
       <c r="L41" s="12"/>
       <c r="M41" s="7">
         <v>1</v>
@@ -3919,11 +3931,11 @@
       <c r="AO41" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="AQ41" s="53" t="s">
+      <c r="AQ41" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="AR41" s="49"/>
-      <c r="AS41" s="49"/>
+      <c r="AR41" s="43"/>
+      <c r="AS41" s="43"/>
       <c r="AU41" s="38">
         <v>4</v>
       </c>
@@ -4229,15 +4241,15 @@
       <c r="BA44" s="6"/>
     </row>
     <row r="45" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="48" t="s">
+      <c r="A45" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B45" s="48"/>
-      <c r="C45" s="48"/>
-      <c r="D45" s="48"/>
-      <c r="E45" s="48"/>
-      <c r="F45" s="48"/>
-      <c r="G45" s="48"/>
+      <c r="B45" s="42"/>
+      <c r="C45" s="42"/>
+      <c r="D45" s="42"/>
+      <c r="E45" s="42"/>
+      <c r="F45" s="42"/>
+      <c r="G45" s="42"/>
       <c r="M45" s="8" t="s">
         <v>11</v>
       </c>
@@ -4286,15 +4298,15 @@
       <c r="AP45" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AU45" s="48" t="s">
+      <c r="AU45" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AV45" s="48"/>
-      <c r="AW45" s="48"/>
-      <c r="AX45" s="48"/>
-      <c r="AY45" s="48"/>
-      <c r="AZ45" s="48"/>
-      <c r="BA45" s="48"/>
+      <c r="AV45" s="42"/>
+      <c r="AW45" s="42"/>
+      <c r="AX45" s="42"/>
+      <c r="AY45" s="42"/>
+      <c r="AZ45" s="42"/>
+      <c r="BA45" s="42"/>
     </row>
     <row r="46" spans="1:54" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="M46" s="8" t="s">
@@ -4385,49 +4397,61 @@
       <c r="AO47" s="6"/>
     </row>
     <row r="48" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="M48" s="41" t="s">
+      <c r="M48" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="N48" s="42"/>
-      <c r="O48" s="42"/>
-      <c r="P48" s="42"/>
-      <c r="Q48" s="42"/>
-      <c r="R48" s="42"/>
-      <c r="S48" s="43"/>
-      <c r="X48" s="48" t="s">
+      <c r="N48" s="54"/>
+      <c r="O48" s="54"/>
+      <c r="P48" s="54"/>
+      <c r="Q48" s="54"/>
+      <c r="R48" s="54"/>
+      <c r="S48" s="55"/>
+      <c r="X48" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="Y48" s="48"/>
-      <c r="Z48" s="48"/>
-      <c r="AA48" s="48"/>
-      <c r="AB48" s="48"/>
-      <c r="AC48" s="48"/>
-      <c r="AD48" s="48"/>
-      <c r="AI48" s="48" t="s">
+      <c r="Y48" s="42"/>
+      <c r="Z48" s="42"/>
+      <c r="AA48" s="42"/>
+      <c r="AB48" s="42"/>
+      <c r="AC48" s="42"/>
+      <c r="AD48" s="42"/>
+      <c r="AI48" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AJ48" s="48"/>
-      <c r="AK48" s="48"/>
-      <c r="AL48" s="48"/>
-      <c r="AM48" s="48"/>
-      <c r="AN48" s="48"/>
-      <c r="AO48" s="48"/>
+      <c r="AJ48" s="42"/>
+      <c r="AK48" s="42"/>
+      <c r="AL48" s="42"/>
+      <c r="AM48" s="42"/>
+      <c r="AN48" s="42"/>
+      <c r="AO48" s="42"/>
     </row>
     <row r="49" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="AU45:BA45"/>
-    <mergeCell ref="AF28:AL28"/>
-    <mergeCell ref="AF37:AL37"/>
-    <mergeCell ref="AQ30:AS30"/>
-    <mergeCell ref="AQ41:AS41"/>
-    <mergeCell ref="AU34:BA34"/>
-    <mergeCell ref="AU36:BA36"/>
-    <mergeCell ref="AU2:BA2"/>
-    <mergeCell ref="AU3:BA3"/>
-    <mergeCell ref="AU12:BA12"/>
-    <mergeCell ref="AU14:BA14"/>
-    <mergeCell ref="AU23:BA23"/>
+    <mergeCell ref="M48:S48"/>
+    <mergeCell ref="M39:S39"/>
+    <mergeCell ref="P37:V37"/>
+    <mergeCell ref="P28:V28"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A1:U1"/>
+    <mergeCell ref="O26:W26"/>
+    <mergeCell ref="I41:K41"/>
+    <mergeCell ref="L14:N14"/>
+    <mergeCell ref="L36:N36"/>
+    <mergeCell ref="M2:R2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="M4:S4"/>
+    <mergeCell ref="M13:S13"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="A25:G25"/>
     <mergeCell ref="X37:AD37"/>
     <mergeCell ref="AE26:AM26"/>
     <mergeCell ref="Z1:AB1"/>
@@ -4444,30 +4468,18 @@
     <mergeCell ref="AN36:AP36"/>
     <mergeCell ref="AQ8:AS8"/>
     <mergeCell ref="AQ19:AS19"/>
-    <mergeCell ref="A1:U1"/>
-    <mergeCell ref="O26:W26"/>
-    <mergeCell ref="I41:K41"/>
-    <mergeCell ref="L14:N14"/>
-    <mergeCell ref="L36:N36"/>
-    <mergeCell ref="M2:R2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="M4:S4"/>
-    <mergeCell ref="M13:S13"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A23:G23"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="M48:S48"/>
-    <mergeCell ref="M39:S39"/>
-    <mergeCell ref="P37:V37"/>
-    <mergeCell ref="P28:V28"/>
-    <mergeCell ref="A36:G36"/>
-    <mergeCell ref="A45:G45"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="AU2:BA2"/>
+    <mergeCell ref="AU3:BA3"/>
+    <mergeCell ref="AU12:BA12"/>
+    <mergeCell ref="AU14:BA14"/>
+    <mergeCell ref="AU23:BA23"/>
+    <mergeCell ref="AU45:BA45"/>
+    <mergeCell ref="AF28:AL28"/>
+    <mergeCell ref="AF37:AL37"/>
+    <mergeCell ref="AQ30:AS30"/>
+    <mergeCell ref="AQ41:AS41"/>
+    <mergeCell ref="AU34:BA34"/>
+    <mergeCell ref="AU36:BA36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/2025_2026/Playoffs/Brackets.xlsx
+++ b/2025_2026/Playoffs/Brackets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\NHLStats\2025_2026\Playoffs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA1AACC5-88CA-4FBF-8F8D-542C621AB781}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8291B30E-E627-4FE0-845D-B530C932551F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="95">
   <si>
     <t>Eastern Conference Playoff Teams</t>
   </si>
@@ -308,6 +308,9 @@
   </si>
   <si>
     <t>Avalanche Win Series 4-1</t>
+  </si>
+  <si>
+    <t>Golden Knights Lead 2-0</t>
   </si>
 </sst>
 </file>
@@ -686,18 +689,45 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -710,40 +740,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1113,18 +1116,18 @@
     </row>
     <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="11" spans="1:7" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="59" t="s">
+      <c r="A11" s="61" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="59"/>
-      <c r="C11" s="59" t="s">
+      <c r="B11" s="61"/>
+      <c r="C11" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="59"/>
-      <c r="E11" s="59" t="s">
+      <c r="D11" s="61"/>
+      <c r="E11" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="59"/>
+      <c r="F11" s="61"/>
       <c r="G11" s="4" t="s">
         <v>18</v>
       </c>
@@ -1153,18 +1156,18 @@
       </c>
     </row>
     <row r="13" spans="1:7" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="60" t="s">
+      <c r="A13" s="59" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="61"/>
-      <c r="C13" s="60" t="s">
+      <c r="B13" s="60"/>
+      <c r="C13" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="D13" s="61"/>
-      <c r="E13" s="60" t="s">
+      <c r="D13" s="60"/>
+      <c r="E13" s="59" t="s">
         <v>17</v>
       </c>
-      <c r="F13" s="61"/>
+      <c r="F13" s="60"/>
       <c r="G13" s="5"/>
     </row>
     <row r="14" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1209,14 +1212,14 @@
       </c>
     </row>
     <row r="16" spans="1:7" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="60" t="s">
+      <c r="A16" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="61"/>
-      <c r="C16" s="60" t="s">
+      <c r="B16" s="60"/>
+      <c r="C16" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="61"/>
+      <c r="D16" s="60"/>
     </row>
     <row r="17" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
@@ -1247,10 +1250,10 @@
       </c>
     </row>
     <row r="19" spans="1:4" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="60" t="s">
+      <c r="A19" s="59" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="61"/>
+      <c r="B19" s="60"/>
     </row>
     <row r="20" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
@@ -1269,10 +1272,10 @@
       </c>
     </row>
     <row r="22" spans="1:4" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="60" t="s">
+      <c r="A22" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="61"/>
+      <c r="B22" s="60"/>
     </row>
     <row r="23" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
@@ -1357,16 +1360,16 @@
     <sortCondition ref="B2:B9"/>
   </sortState>
   <mergeCells count="10">
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A16:B16"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A16:B16"/>
   </mergeCells>
   <dataValidations count="16">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C14" xr:uid="{2C3D9587-ABAE-4E3F-8B22-396DF812BF02}">
@@ -1470,124 +1473,124 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:54" ht="27.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
-      <c r="I1" s="51"/>
-      <c r="J1" s="51"/>
-      <c r="K1" s="51"/>
-      <c r="L1" s="51"/>
-      <c r="M1" s="51"/>
-      <c r="N1" s="51"/>
-      <c r="O1" s="51"/>
-      <c r="P1" s="51"/>
-      <c r="Q1" s="51"/>
-      <c r="R1" s="51"/>
-      <c r="S1" s="51"/>
-      <c r="T1" s="51"/>
-      <c r="U1" s="52"/>
-      <c r="Z1" s="50" t="s">
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="52"/>
+      <c r="M1" s="52"/>
+      <c r="N1" s="52"/>
+      <c r="O1" s="52"/>
+      <c r="P1" s="52"/>
+      <c r="Q1" s="52"/>
+      <c r="R1" s="52"/>
+      <c r="S1" s="52"/>
+      <c r="T1" s="52"/>
+      <c r="U1" s="53"/>
+      <c r="Z1" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="AA1" s="51"/>
-      <c r="AB1" s="52"/>
-      <c r="AF1" s="50" t="s">
+      <c r="AA1" s="52"/>
+      <c r="AB1" s="53"/>
+      <c r="AF1" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="AG1" s="51"/>
-      <c r="AH1" s="51"/>
-      <c r="AI1" s="51"/>
-      <c r="AJ1" s="51"/>
-      <c r="AK1" s="51"/>
-      <c r="AL1" s="51"/>
-      <c r="AM1" s="51"/>
-      <c r="AN1" s="51"/>
-      <c r="AO1" s="51"/>
-      <c r="AP1" s="51"/>
-      <c r="AQ1" s="51"/>
-      <c r="AR1" s="51"/>
-      <c r="AS1" s="51"/>
-      <c r="AT1" s="51"/>
-      <c r="AU1" s="51"/>
-      <c r="AV1" s="51"/>
-      <c r="AW1" s="51"/>
-      <c r="AX1" s="51"/>
-      <c r="AY1" s="51"/>
-      <c r="AZ1" s="51"/>
-      <c r="BA1" s="52"/>
+      <c r="AG1" s="52"/>
+      <c r="AH1" s="52"/>
+      <c r="AI1" s="52"/>
+      <c r="AJ1" s="52"/>
+      <c r="AK1" s="52"/>
+      <c r="AL1" s="52"/>
+      <c r="AM1" s="52"/>
+      <c r="AN1" s="52"/>
+      <c r="AO1" s="52"/>
+      <c r="AP1" s="52"/>
+      <c r="AQ1" s="52"/>
+      <c r="AR1" s="52"/>
+      <c r="AS1" s="52"/>
+      <c r="AT1" s="52"/>
+      <c r="AU1" s="52"/>
+      <c r="AV1" s="52"/>
+      <c r="AW1" s="52"/>
+      <c r="AX1" s="52"/>
+      <c r="AY1" s="52"/>
+      <c r="AZ1" s="52"/>
+      <c r="BA1" s="53"/>
     </row>
     <row r="2" spans="1:54" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="48"/>
-      <c r="M2" s="46" t="s">
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="57"/>
+      <c r="M2" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="47"/>
-      <c r="O2" s="47"/>
-      <c r="P2" s="47"/>
-      <c r="Q2" s="47"/>
-      <c r="R2" s="48"/>
-      <c r="AI2" s="46" t="s">
+      <c r="N2" s="56"/>
+      <c r="O2" s="56"/>
+      <c r="P2" s="56"/>
+      <c r="Q2" s="56"/>
+      <c r="R2" s="57"/>
+      <c r="AI2" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="AJ2" s="47"/>
-      <c r="AK2" s="47"/>
-      <c r="AL2" s="47"/>
-      <c r="AM2" s="47"/>
-      <c r="AN2" s="47"/>
-      <c r="AO2" s="48"/>
-      <c r="AU2" s="46" t="s">
+      <c r="AJ2" s="56"/>
+      <c r="AK2" s="56"/>
+      <c r="AL2" s="56"/>
+      <c r="AM2" s="56"/>
+      <c r="AN2" s="56"/>
+      <c r="AO2" s="57"/>
+      <c r="AU2" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="AV2" s="47"/>
-      <c r="AW2" s="47"/>
-      <c r="AX2" s="47"/>
-      <c r="AY2" s="47"/>
-      <c r="AZ2" s="47"/>
-      <c r="BA2" s="48"/>
+      <c r="AV2" s="56"/>
+      <c r="AW2" s="56"/>
+      <c r="AX2" s="56"/>
+      <c r="AY2" s="56"/>
+      <c r="AZ2" s="56"/>
+      <c r="BA2" s="57"/>
     </row>
     <row r="3" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="42" t="s">
+      <c r="A3" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="42"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="42"/>
-      <c r="AI3" s="53" t="s">
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="AI3" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="AJ3" s="54"/>
-      <c r="AK3" s="54"/>
-      <c r="AL3" s="54"/>
-      <c r="AM3" s="54"/>
-      <c r="AN3" s="54"/>
-      <c r="AO3" s="55"/>
-      <c r="AU3" s="42" t="s">
+      <c r="AJ3" s="43"/>
+      <c r="AK3" s="43"/>
+      <c r="AL3" s="43"/>
+      <c r="AM3" s="43"/>
+      <c r="AN3" s="43"/>
+      <c r="AO3" s="44"/>
+      <c r="AU3" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="AV3" s="42"/>
-      <c r="AW3" s="42"/>
-      <c r="AX3" s="42"/>
-      <c r="AY3" s="42"/>
-      <c r="AZ3" s="42"/>
-      <c r="BA3" s="42"/>
+      <c r="AV3" s="49"/>
+      <c r="AW3" s="49"/>
+      <c r="AX3" s="49"/>
+      <c r="AY3" s="49"/>
+      <c r="AZ3" s="49"/>
+      <c r="BA3" s="49"/>
     </row>
     <row r="4" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
@@ -1611,15 +1614,15 @@
       <c r="G4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="53" t="s">
+      <c r="M4" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="N4" s="54"/>
-      <c r="O4" s="54"/>
-      <c r="P4" s="54"/>
-      <c r="Q4" s="54"/>
-      <c r="R4" s="54"/>
-      <c r="S4" s="55"/>
+      <c r="N4" s="43"/>
+      <c r="O4" s="43"/>
+      <c r="P4" s="43"/>
+      <c r="Q4" s="43"/>
+      <c r="R4" s="43"/>
+      <c r="S4" s="44"/>
       <c r="AI4" s="3" t="s">
         <v>2</v>
       </c>
@@ -1946,11 +1949,11 @@
       <c r="G8" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="I8" s="43" t="s">
+      <c r="I8" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="J8" s="43"/>
-      <c r="K8" s="43"/>
+      <c r="J8" s="50"/>
+      <c r="K8" s="50"/>
       <c r="M8" s="8">
         <v>3</v>
       </c>
@@ -1993,11 +1996,11 @@
       <c r="AO8" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="AQ8" s="43" t="s">
+      <c r="AQ8" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="AR8" s="43"/>
-      <c r="AS8" s="43"/>
+      <c r="AR8" s="50"/>
+      <c r="AS8" s="50"/>
       <c r="AU8" s="38">
         <v>4</v>
       </c>
@@ -2257,15 +2260,15 @@
       <c r="BA11" s="6"/>
     </row>
     <row r="12" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="42" t="s">
+      <c r="A12" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="42"/>
-      <c r="C12" s="42"/>
-      <c r="D12" s="42"/>
-      <c r="E12" s="42"/>
-      <c r="F12" s="42"/>
-      <c r="G12" s="42"/>
+      <c r="B12" s="49"/>
+      <c r="C12" s="49"/>
+      <c r="D12" s="49"/>
+      <c r="E12" s="49"/>
+      <c r="F12" s="49"/>
+      <c r="G12" s="49"/>
       <c r="L12" s="12"/>
       <c r="M12" s="8" t="s">
         <v>12</v>
@@ -2291,69 +2294,69 @@
       <c r="T12" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AI12" s="42" t="s">
+      <c r="AI12" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AJ12" s="42"/>
-      <c r="AK12" s="42"/>
-      <c r="AL12" s="42"/>
-      <c r="AM12" s="42"/>
-      <c r="AN12" s="42"/>
-      <c r="AO12" s="42"/>
+      <c r="AJ12" s="49"/>
+      <c r="AK12" s="49"/>
+      <c r="AL12" s="49"/>
+      <c r="AM12" s="49"/>
+      <c r="AN12" s="49"/>
+      <c r="AO12" s="49"/>
       <c r="AQ12" s="12"/>
-      <c r="AU12" s="42" t="s">
+      <c r="AU12" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AV12" s="42"/>
-      <c r="AW12" s="42"/>
-      <c r="AX12" s="42"/>
-      <c r="AY12" s="42"/>
-      <c r="AZ12" s="42"/>
-      <c r="BA12" s="42"/>
+      <c r="AV12" s="49"/>
+      <c r="AW12" s="49"/>
+      <c r="AX12" s="49"/>
+      <c r="AY12" s="49"/>
+      <c r="AZ12" s="49"/>
+      <c r="BA12" s="49"/>
     </row>
     <row r="13" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L13" s="12"/>
-      <c r="M13" s="53" t="s">
+      <c r="M13" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="N13" s="54"/>
-      <c r="O13" s="54"/>
-      <c r="P13" s="54"/>
-      <c r="Q13" s="54"/>
-      <c r="R13" s="54"/>
-      <c r="S13" s="55"/>
+      <c r="N13" s="43"/>
+      <c r="O13" s="43"/>
+      <c r="P13" s="43"/>
+      <c r="Q13" s="43"/>
+      <c r="R13" s="43"/>
+      <c r="S13" s="44"/>
       <c r="AQ13" s="12"/>
     </row>
     <row r="14" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="45" t="s">
+      <c r="A14" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="45"/>
-      <c r="C14" s="45"/>
-      <c r="D14" s="45"/>
-      <c r="E14" s="45"/>
-      <c r="F14" s="45"/>
-      <c r="G14" s="45"/>
-      <c r="L14" s="44" t="s">
+      <c r="B14" s="48"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="48"/>
+      <c r="E14" s="48"/>
+      <c r="F14" s="48"/>
+      <c r="G14" s="48"/>
+      <c r="L14" s="54" t="s">
         <v>32</v>
       </c>
-      <c r="M14" s="43"/>
-      <c r="N14" s="43"/>
-      <c r="AN14" s="43" t="s">
+      <c r="M14" s="50"/>
+      <c r="N14" s="50"/>
+      <c r="AN14" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="AO14" s="43"/>
-      <c r="AP14" s="43"/>
+      <c r="AO14" s="50"/>
+      <c r="AP14" s="50"/>
       <c r="AQ14" s="12"/>
-      <c r="AU14" s="45" t="s">
+      <c r="AU14" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="AV14" s="45"/>
-      <c r="AW14" s="45"/>
-      <c r="AX14" s="45"/>
-      <c r="AY14" s="45"/>
-      <c r="AZ14" s="45"/>
-      <c r="BA14" s="45"/>
+      <c r="AV14" s="48"/>
+      <c r="AW14" s="48"/>
+      <c r="AX14" s="48"/>
+      <c r="AY14" s="48"/>
+      <c r="AZ14" s="48"/>
+      <c r="BA14" s="48"/>
     </row>
     <row r="15" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
@@ -2581,19 +2584,19 @@
       <c r="G19" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="I19" s="43" t="s">
+      <c r="I19" s="50" t="s">
         <v>32</v>
       </c>
-      <c r="J19" s="43"/>
-      <c r="K19" s="43"/>
+      <c r="J19" s="50"/>
+      <c r="K19" s="50"/>
       <c r="L19" s="12"/>
       <c r="O19" s="12"/>
       <c r="AN19" s="12"/>
-      <c r="AQ19" s="44" t="s">
+      <c r="AQ19" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="AR19" s="43"/>
-      <c r="AS19" s="43"/>
+      <c r="AR19" s="50"/>
+      <c r="AS19" s="50"/>
       <c r="AU19" s="38">
         <v>4</v>
       </c>
@@ -2755,52 +2758,52 @@
       <c r="BA22" s="6"/>
     </row>
     <row r="23" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="42" t="s">
+      <c r="A23" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="B23" s="42"/>
-      <c r="C23" s="42"/>
-      <c r="D23" s="42"/>
-      <c r="E23" s="42"/>
-      <c r="F23" s="42"/>
-      <c r="G23" s="42"/>
+      <c r="B23" s="49"/>
+      <c r="C23" s="49"/>
+      <c r="D23" s="49"/>
+      <c r="E23" s="49"/>
+      <c r="F23" s="49"/>
+      <c r="G23" s="49"/>
       <c r="O23" s="12"/>
       <c r="AN23" s="12"/>
-      <c r="AU23" s="42" t="s">
+      <c r="AU23" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AV23" s="42"/>
-      <c r="AW23" s="42"/>
-      <c r="AX23" s="42"/>
-      <c r="AY23" s="42"/>
-      <c r="AZ23" s="42"/>
-      <c r="BA23" s="42"/>
+      <c r="AV23" s="49"/>
+      <c r="AW23" s="49"/>
+      <c r="AX23" s="49"/>
+      <c r="AY23" s="49"/>
+      <c r="AZ23" s="49"/>
+      <c r="BA23" s="49"/>
     </row>
     <row r="24" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="O24" s="12"/>
       <c r="AN24" s="12"/>
     </row>
     <row r="25" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="42" t="s">
+      <c r="A25" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="42"/>
-      <c r="C25" s="42"/>
-      <c r="D25" s="42"/>
-      <c r="E25" s="42"/>
-      <c r="F25" s="42"/>
-      <c r="G25" s="42"/>
+      <c r="B25" s="49"/>
+      <c r="C25" s="49"/>
+      <c r="D25" s="49"/>
+      <c r="E25" s="49"/>
+      <c r="F25" s="49"/>
+      <c r="G25" s="49"/>
       <c r="O25" s="12"/>
       <c r="AN25" s="12"/>
-      <c r="AU25" s="42" t="s">
+      <c r="AU25" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="AV25" s="42"/>
-      <c r="AW25" s="42"/>
-      <c r="AX25" s="42"/>
-      <c r="AY25" s="42"/>
-      <c r="AZ25" s="42"/>
-      <c r="BA25" s="42"/>
+      <c r="AV25" s="49"/>
+      <c r="AW25" s="49"/>
+      <c r="AX25" s="49"/>
+      <c r="AY25" s="49"/>
+      <c r="AZ25" s="49"/>
+      <c r="BA25" s="49"/>
     </row>
     <row r="26" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="20" t="s">
@@ -2824,24 +2827,24 @@
       <c r="G26" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="O26" s="44"/>
-      <c r="P26" s="43"/>
-      <c r="Q26" s="43"/>
-      <c r="R26" s="43"/>
-      <c r="S26" s="43"/>
-      <c r="T26" s="43"/>
-      <c r="U26" s="43"/>
-      <c r="V26" s="43"/>
-      <c r="W26" s="43"/>
-      <c r="AE26" s="43"/>
-      <c r="AF26" s="43"/>
-      <c r="AG26" s="43"/>
-      <c r="AH26" s="43"/>
-      <c r="AI26" s="43"/>
-      <c r="AJ26" s="43"/>
-      <c r="AK26" s="43"/>
-      <c r="AL26" s="43"/>
-      <c r="AM26" s="49"/>
+      <c r="O26" s="54"/>
+      <c r="P26" s="50"/>
+      <c r="Q26" s="50"/>
+      <c r="R26" s="50"/>
+      <c r="S26" s="50"/>
+      <c r="T26" s="50"/>
+      <c r="U26" s="50"/>
+      <c r="V26" s="50"/>
+      <c r="W26" s="50"/>
+      <c r="AE26" s="50"/>
+      <c r="AF26" s="50"/>
+      <c r="AG26" s="50"/>
+      <c r="AH26" s="50"/>
+      <c r="AI26" s="50"/>
+      <c r="AJ26" s="50"/>
+      <c r="AK26" s="50"/>
+      <c r="AL26" s="50"/>
+      <c r="AM26" s="58"/>
       <c r="AU26" s="20" t="s">
         <v>2</v>
       </c>
@@ -2938,26 +2941,26 @@
         <v>54</v>
       </c>
       <c r="O28" s="12"/>
-      <c r="P28" s="53" t="s">
+      <c r="P28" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="Q28" s="54"/>
-      <c r="R28" s="54"/>
-      <c r="S28" s="54"/>
-      <c r="T28" s="54"/>
-      <c r="U28" s="54"/>
-      <c r="V28" s="55"/>
+      <c r="Q28" s="43"/>
+      <c r="R28" s="43"/>
+      <c r="S28" s="43"/>
+      <c r="T28" s="43"/>
+      <c r="U28" s="43"/>
+      <c r="V28" s="44"/>
       <c r="X28" s="12"/>
       <c r="AD28" s="13"/>
-      <c r="AF28" s="42" t="s">
+      <c r="AF28" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="AG28" s="42"/>
-      <c r="AH28" s="42"/>
-      <c r="AI28" s="42"/>
-      <c r="AJ28" s="42"/>
-      <c r="AK28" s="42"/>
-      <c r="AL28" s="42"/>
+      <c r="AG28" s="49"/>
+      <c r="AH28" s="49"/>
+      <c r="AI28" s="49"/>
+      <c r="AJ28" s="49"/>
+      <c r="AK28" s="49"/>
+      <c r="AL28" s="49"/>
       <c r="AN28" s="12"/>
       <c r="AU28" s="8">
         <v>2</v>
@@ -3093,11 +3096,11 @@
       <c r="G30" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="I30" s="43" t="s">
+      <c r="I30" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="J30" s="43"/>
-      <c r="K30" s="43"/>
+      <c r="J30" s="50"/>
+      <c r="K30" s="50"/>
       <c r="O30" s="12"/>
       <c r="P30" s="7">
         <v>1</v>
@@ -3144,11 +3147,11 @@
         <v>52</v>
       </c>
       <c r="AN30" s="12"/>
-      <c r="AQ30" s="43" t="s">
+      <c r="AQ30" s="50" t="s">
         <v>38</v>
       </c>
-      <c r="AR30" s="43"/>
-      <c r="AS30" s="43"/>
+      <c r="AR30" s="50"/>
+      <c r="AS30" s="50"/>
       <c r="AU30" s="38">
         <v>4</v>
       </c>
@@ -3218,12 +3221,18 @@
       <c r="AH31" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="AI31" s="13"/>
+      <c r="AI31" s="13">
+        <v>3</v>
+      </c>
       <c r="AJ31" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="AK31" s="13"/>
-      <c r="AL31" s="16"/>
+      <c r="AK31" s="13">
+        <v>1</v>
+      </c>
+      <c r="AL31" s="16" t="s">
+        <v>94</v>
+      </c>
       <c r="AN31" s="12"/>
       <c r="AQ31" s="10"/>
       <c r="AR31" s="17"/>
@@ -3396,15 +3405,15 @@
       <c r="BA33" s="6"/>
     </row>
     <row r="34" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="42" t="s">
+      <c r="A34" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="B34" s="42"/>
-      <c r="C34" s="42"/>
-      <c r="D34" s="42"/>
-      <c r="E34" s="42"/>
-      <c r="F34" s="42"/>
-      <c r="G34" s="42"/>
+      <c r="B34" s="49"/>
+      <c r="C34" s="49"/>
+      <c r="D34" s="49"/>
+      <c r="E34" s="49"/>
+      <c r="F34" s="49"/>
+      <c r="G34" s="49"/>
       <c r="L34" s="12"/>
       <c r="O34" s="12"/>
       <c r="P34" s="8" t="s">
@@ -3441,15 +3450,15 @@
       <c r="AL34" s="16"/>
       <c r="AN34" s="12"/>
       <c r="AQ34" s="12"/>
-      <c r="AU34" s="42" t="s">
+      <c r="AU34" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AV34" s="42"/>
-      <c r="AW34" s="42"/>
-      <c r="AX34" s="42"/>
-      <c r="AY34" s="42"/>
-      <c r="AZ34" s="42"/>
-      <c r="BA34" s="42"/>
+      <c r="AV34" s="49"/>
+      <c r="AW34" s="49"/>
+      <c r="AX34" s="49"/>
+      <c r="AY34" s="49"/>
+      <c r="AZ34" s="49"/>
+      <c r="BA34" s="49"/>
     </row>
     <row r="35" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L35" s="12"/>
@@ -3490,20 +3499,20 @@
       <c r="AQ35" s="12"/>
     </row>
     <row r="36" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="45" t="s">
+      <c r="A36" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="B36" s="45"/>
-      <c r="C36" s="45"/>
-      <c r="D36" s="45"/>
-      <c r="E36" s="45"/>
-      <c r="F36" s="45"/>
-      <c r="G36" s="45"/>
-      <c r="L36" s="44" t="s">
+      <c r="B36" s="48"/>
+      <c r="C36" s="48"/>
+      <c r="D36" s="48"/>
+      <c r="E36" s="48"/>
+      <c r="F36" s="48"/>
+      <c r="G36" s="48"/>
+      <c r="L36" s="54" t="s">
         <v>26</v>
       </c>
-      <c r="M36" s="43"/>
-      <c r="N36" s="43"/>
+      <c r="M36" s="50"/>
+      <c r="N36" s="50"/>
       <c r="O36" s="12"/>
       <c r="P36" s="8" t="s">
         <v>12</v>
@@ -3537,21 +3546,21 @@
       </c>
       <c r="AK36" s="36"/>
       <c r="AL36" s="37"/>
-      <c r="AN36" s="44" t="s">
+      <c r="AN36" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="AO36" s="43"/>
-      <c r="AP36" s="43"/>
+      <c r="AO36" s="50"/>
+      <c r="AP36" s="50"/>
       <c r="AQ36" s="12"/>
-      <c r="AU36" s="45" t="s">
+      <c r="AU36" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="AV36" s="45"/>
-      <c r="AW36" s="45"/>
-      <c r="AX36" s="45"/>
-      <c r="AY36" s="45"/>
-      <c r="AZ36" s="45"/>
-      <c r="BA36" s="45"/>
+      <c r="AV36" s="48"/>
+      <c r="AW36" s="48"/>
+      <c r="AX36" s="48"/>
+      <c r="AY36" s="48"/>
+      <c r="AZ36" s="48"/>
+      <c r="BA36" s="48"/>
     </row>
     <row r="37" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37" s="20" t="s">
@@ -3576,31 +3585,31 @@
         <v>9</v>
       </c>
       <c r="L37" s="12"/>
-      <c r="P37" s="56" t="s">
+      <c r="P37" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="Q37" s="57"/>
-      <c r="R37" s="57"/>
-      <c r="S37" s="57"/>
-      <c r="T37" s="57"/>
-      <c r="U37" s="57"/>
-      <c r="V37" s="58"/>
-      <c r="X37" s="44"/>
-      <c r="Y37" s="43"/>
-      <c r="Z37" s="43"/>
-      <c r="AA37" s="43"/>
-      <c r="AB37" s="43"/>
-      <c r="AC37" s="43"/>
-      <c r="AD37" s="49"/>
-      <c r="AF37" s="42" t="s">
+      <c r="Q37" s="46"/>
+      <c r="R37" s="46"/>
+      <c r="S37" s="46"/>
+      <c r="T37" s="46"/>
+      <c r="U37" s="46"/>
+      <c r="V37" s="47"/>
+      <c r="X37" s="54"/>
+      <c r="Y37" s="50"/>
+      <c r="Z37" s="50"/>
+      <c r="AA37" s="50"/>
+      <c r="AB37" s="50"/>
+      <c r="AC37" s="50"/>
+      <c r="AD37" s="58"/>
+      <c r="AF37" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AG37" s="42"/>
-      <c r="AH37" s="42"/>
-      <c r="AI37" s="42"/>
-      <c r="AJ37" s="42"/>
-      <c r="AK37" s="42"/>
-      <c r="AL37" s="42"/>
+      <c r="AG37" s="49"/>
+      <c r="AH37" s="49"/>
+      <c r="AI37" s="49"/>
+      <c r="AJ37" s="49"/>
+      <c r="AK37" s="49"/>
+      <c r="AL37" s="49"/>
       <c r="AQ37" s="12"/>
       <c r="AU37" s="3" t="s">
         <v>2</v>
@@ -3693,33 +3702,33 @@
         <v>53</v>
       </c>
       <c r="L39" s="12"/>
-      <c r="M39" s="53" t="s">
+      <c r="M39" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="N39" s="54"/>
-      <c r="O39" s="54"/>
-      <c r="P39" s="54"/>
-      <c r="Q39" s="54"/>
-      <c r="R39" s="54"/>
-      <c r="S39" s="55"/>
-      <c r="X39" s="42" t="s">
+      <c r="N39" s="43"/>
+      <c r="O39" s="43"/>
+      <c r="P39" s="43"/>
+      <c r="Q39" s="43"/>
+      <c r="R39" s="43"/>
+      <c r="S39" s="44"/>
+      <c r="X39" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="Y39" s="42"/>
-      <c r="Z39" s="42"/>
-      <c r="AA39" s="42"/>
-      <c r="AB39" s="42"/>
-      <c r="AC39" s="42"/>
-      <c r="AD39" s="42"/>
-      <c r="AI39" s="53" t="s">
+      <c r="Y39" s="49"/>
+      <c r="Z39" s="49"/>
+      <c r="AA39" s="49"/>
+      <c r="AB39" s="49"/>
+      <c r="AC39" s="49"/>
+      <c r="AD39" s="49"/>
+      <c r="AI39" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="AJ39" s="54"/>
-      <c r="AK39" s="54"/>
-      <c r="AL39" s="54"/>
-      <c r="AM39" s="54"/>
-      <c r="AN39" s="54"/>
-      <c r="AO39" s="55"/>
+      <c r="AJ39" s="43"/>
+      <c r="AK39" s="43"/>
+      <c r="AL39" s="43"/>
+      <c r="AM39" s="43"/>
+      <c r="AN39" s="43"/>
+      <c r="AO39" s="44"/>
       <c r="AQ39" s="12"/>
       <c r="AU39" s="8">
         <v>2</v>
@@ -3874,11 +3883,11 @@
       <c r="G41" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="I41" s="43" t="s">
+      <c r="I41" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="J41" s="43"/>
-      <c r="K41" s="43"/>
+      <c r="J41" s="50"/>
+      <c r="K41" s="50"/>
       <c r="L41" s="12"/>
       <c r="M41" s="7">
         <v>1</v>
@@ -3931,11 +3940,11 @@
       <c r="AO41" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="AQ41" s="44" t="s">
+      <c r="AQ41" s="54" t="s">
         <v>23</v>
       </c>
-      <c r="AR41" s="43"/>
-      <c r="AS41" s="43"/>
+      <c r="AR41" s="50"/>
+      <c r="AS41" s="50"/>
       <c r="AU41" s="38">
         <v>4</v>
       </c>
@@ -4241,15 +4250,15 @@
       <c r="BA44" s="6"/>
     </row>
     <row r="45" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="42" t="s">
+      <c r="A45" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="B45" s="42"/>
-      <c r="C45" s="42"/>
-      <c r="D45" s="42"/>
-      <c r="E45" s="42"/>
-      <c r="F45" s="42"/>
-      <c r="G45" s="42"/>
+      <c r="B45" s="49"/>
+      <c r="C45" s="49"/>
+      <c r="D45" s="49"/>
+      <c r="E45" s="49"/>
+      <c r="F45" s="49"/>
+      <c r="G45" s="49"/>
       <c r="M45" s="8" t="s">
         <v>11</v>
       </c>
@@ -4298,15 +4307,15 @@
       <c r="AP45" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AU45" s="42" t="s">
+      <c r="AU45" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AV45" s="42"/>
-      <c r="AW45" s="42"/>
-      <c r="AX45" s="42"/>
-      <c r="AY45" s="42"/>
-      <c r="AZ45" s="42"/>
-      <c r="BA45" s="42"/>
+      <c r="AV45" s="49"/>
+      <c r="AW45" s="49"/>
+      <c r="AX45" s="49"/>
+      <c r="AY45" s="49"/>
+      <c r="AZ45" s="49"/>
+      <c r="BA45" s="49"/>
     </row>
     <row r="46" spans="1:54" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="M46" s="8" t="s">
@@ -4397,45 +4406,65 @@
       <c r="AO47" s="6"/>
     </row>
     <row r="48" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="M48" s="53" t="s">
+      <c r="M48" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="N48" s="54"/>
-      <c r="O48" s="54"/>
-      <c r="P48" s="54"/>
-      <c r="Q48" s="54"/>
-      <c r="R48" s="54"/>
-      <c r="S48" s="55"/>
-      <c r="X48" s="42" t="s">
+      <c r="N48" s="43"/>
+      <c r="O48" s="43"/>
+      <c r="P48" s="43"/>
+      <c r="Q48" s="43"/>
+      <c r="R48" s="43"/>
+      <c r="S48" s="44"/>
+      <c r="X48" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="Y48" s="42"/>
-      <c r="Z48" s="42"/>
-      <c r="AA48" s="42"/>
-      <c r="AB48" s="42"/>
-      <c r="AC48" s="42"/>
-      <c r="AD48" s="42"/>
-      <c r="AI48" s="42" t="s">
+      <c r="Y48" s="49"/>
+      <c r="Z48" s="49"/>
+      <c r="AA48" s="49"/>
+      <c r="AB48" s="49"/>
+      <c r="AC48" s="49"/>
+      <c r="AD48" s="49"/>
+      <c r="AI48" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AJ48" s="42"/>
-      <c r="AK48" s="42"/>
-      <c r="AL48" s="42"/>
-      <c r="AM48" s="42"/>
-      <c r="AN48" s="42"/>
-      <c r="AO48" s="42"/>
+      <c r="AJ48" s="49"/>
+      <c r="AK48" s="49"/>
+      <c r="AL48" s="49"/>
+      <c r="AM48" s="49"/>
+      <c r="AN48" s="49"/>
+      <c r="AO48" s="49"/>
     </row>
     <row r="49" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="M48:S48"/>
-    <mergeCell ref="M39:S39"/>
-    <mergeCell ref="P37:V37"/>
-    <mergeCell ref="P28:V28"/>
-    <mergeCell ref="A36:G36"/>
-    <mergeCell ref="A45:G45"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="AU45:BA45"/>
+    <mergeCell ref="AF28:AL28"/>
+    <mergeCell ref="AF37:AL37"/>
+    <mergeCell ref="AQ30:AS30"/>
+    <mergeCell ref="AQ41:AS41"/>
+    <mergeCell ref="AU34:BA34"/>
+    <mergeCell ref="AU36:BA36"/>
+    <mergeCell ref="AU2:BA2"/>
+    <mergeCell ref="AU3:BA3"/>
+    <mergeCell ref="AU12:BA12"/>
+    <mergeCell ref="AU14:BA14"/>
+    <mergeCell ref="AU23:BA23"/>
+    <mergeCell ref="X37:AD37"/>
+    <mergeCell ref="AE26:AM26"/>
+    <mergeCell ref="Z1:AB1"/>
+    <mergeCell ref="X39:AD39"/>
+    <mergeCell ref="X48:AD48"/>
+    <mergeCell ref="AF1:BA1"/>
+    <mergeCell ref="AI2:AO2"/>
+    <mergeCell ref="AI3:AO3"/>
+    <mergeCell ref="AI12:AO12"/>
+    <mergeCell ref="AI39:AO39"/>
+    <mergeCell ref="AU25:BA25"/>
+    <mergeCell ref="AI48:AO48"/>
+    <mergeCell ref="AN14:AP14"/>
+    <mergeCell ref="AN36:AP36"/>
+    <mergeCell ref="AQ8:AS8"/>
+    <mergeCell ref="AQ19:AS19"/>
     <mergeCell ref="A1:U1"/>
     <mergeCell ref="O26:W26"/>
     <mergeCell ref="I41:K41"/>
@@ -4452,34 +4481,14 @@
     <mergeCell ref="I8:K8"/>
     <mergeCell ref="I19:K19"/>
     <mergeCell ref="A25:G25"/>
-    <mergeCell ref="X37:AD37"/>
-    <mergeCell ref="AE26:AM26"/>
-    <mergeCell ref="Z1:AB1"/>
-    <mergeCell ref="X39:AD39"/>
-    <mergeCell ref="X48:AD48"/>
-    <mergeCell ref="AF1:BA1"/>
-    <mergeCell ref="AI2:AO2"/>
-    <mergeCell ref="AI3:AO3"/>
-    <mergeCell ref="AI12:AO12"/>
-    <mergeCell ref="AI39:AO39"/>
-    <mergeCell ref="AU25:BA25"/>
-    <mergeCell ref="AI48:AO48"/>
-    <mergeCell ref="AN14:AP14"/>
-    <mergeCell ref="AN36:AP36"/>
-    <mergeCell ref="AQ8:AS8"/>
-    <mergeCell ref="AQ19:AS19"/>
-    <mergeCell ref="AU2:BA2"/>
-    <mergeCell ref="AU3:BA3"/>
-    <mergeCell ref="AU12:BA12"/>
-    <mergeCell ref="AU14:BA14"/>
-    <mergeCell ref="AU23:BA23"/>
-    <mergeCell ref="AU45:BA45"/>
-    <mergeCell ref="AF28:AL28"/>
-    <mergeCell ref="AF37:AL37"/>
-    <mergeCell ref="AQ30:AS30"/>
-    <mergeCell ref="AQ41:AS41"/>
-    <mergeCell ref="AU34:BA34"/>
-    <mergeCell ref="AU36:BA36"/>
+    <mergeCell ref="M48:S48"/>
+    <mergeCell ref="M39:S39"/>
+    <mergeCell ref="P37:V37"/>
+    <mergeCell ref="P28:V28"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="A34:G34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/2025_2026/Playoffs/Brackets.xlsx
+++ b/2025_2026/Playoffs/Brackets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\NHLStats\2025_2026\Playoffs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8291B30E-E627-4FE0-845D-B530C932551F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BE52E77-5CC1-493F-8276-9151F301F71D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="95">
   <si>
     <t>Eastern Conference Playoff Teams</t>
   </si>
@@ -689,6 +689,39 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -707,46 +740,13 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1116,18 +1116,18 @@
     </row>
     <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="11" spans="1:7" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="61" t="s">
+      <c r="A11" s="59" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="61"/>
-      <c r="C11" s="61" t="s">
+      <c r="B11" s="59"/>
+      <c r="C11" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="61"/>
-      <c r="E11" s="61" t="s">
+      <c r="D11" s="59"/>
+      <c r="E11" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="61"/>
+      <c r="F11" s="59"/>
       <c r="G11" s="4" t="s">
         <v>18</v>
       </c>
@@ -1156,18 +1156,18 @@
       </c>
     </row>
     <row r="13" spans="1:7" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="59" t="s">
+      <c r="A13" s="60" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="60"/>
-      <c r="C13" s="59" t="s">
+      <c r="B13" s="61"/>
+      <c r="C13" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="D13" s="60"/>
-      <c r="E13" s="59" t="s">
+      <c r="D13" s="61"/>
+      <c r="E13" s="60" t="s">
         <v>17</v>
       </c>
-      <c r="F13" s="60"/>
+      <c r="F13" s="61"/>
       <c r="G13" s="5"/>
     </row>
     <row r="14" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1212,14 +1212,14 @@
       </c>
     </row>
     <row r="16" spans="1:7" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="59" t="s">
+      <c r="A16" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="60"/>
-      <c r="C16" s="59" t="s">
+      <c r="B16" s="61"/>
+      <c r="C16" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="60"/>
+      <c r="D16" s="61"/>
     </row>
     <row r="17" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
@@ -1250,10 +1250,10 @@
       </c>
     </row>
     <row r="19" spans="1:4" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="59" t="s">
+      <c r="A19" s="60" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="60"/>
+      <c r="B19" s="61"/>
     </row>
     <row r="20" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
@@ -1272,10 +1272,10 @@
       </c>
     </row>
     <row r="22" spans="1:4" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="59" t="s">
+      <c r="A22" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="60"/>
+      <c r="B22" s="61"/>
     </row>
     <row r="23" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
@@ -1360,16 +1360,16 @@
     <sortCondition ref="B2:B9"/>
   </sortState>
   <mergeCells count="10">
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C16:D16"/>
     <mergeCell ref="E11:F11"/>
     <mergeCell ref="E13:F13"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C16:D16"/>
   </mergeCells>
   <dataValidations count="16">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C14" xr:uid="{2C3D9587-ABAE-4E3F-8B22-396DF812BF02}">
@@ -1473,124 +1473,124 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:54" ht="27.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
-      <c r="M1" s="52"/>
-      <c r="N1" s="52"/>
-      <c r="O1" s="52"/>
-      <c r="P1" s="52"/>
-      <c r="Q1" s="52"/>
-      <c r="R1" s="52"/>
-      <c r="S1" s="52"/>
-      <c r="T1" s="52"/>
-      <c r="U1" s="53"/>
-      <c r="Z1" s="51" t="s">
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
+      <c r="K1" s="51"/>
+      <c r="L1" s="51"/>
+      <c r="M1" s="51"/>
+      <c r="N1" s="51"/>
+      <c r="O1" s="51"/>
+      <c r="P1" s="51"/>
+      <c r="Q1" s="51"/>
+      <c r="R1" s="51"/>
+      <c r="S1" s="51"/>
+      <c r="T1" s="51"/>
+      <c r="U1" s="52"/>
+      <c r="Z1" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="AA1" s="52"/>
-      <c r="AB1" s="53"/>
-      <c r="AF1" s="51" t="s">
+      <c r="AA1" s="51"/>
+      <c r="AB1" s="52"/>
+      <c r="AF1" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="AG1" s="52"/>
-      <c r="AH1" s="52"/>
-      <c r="AI1" s="52"/>
-      <c r="AJ1" s="52"/>
-      <c r="AK1" s="52"/>
-      <c r="AL1" s="52"/>
-      <c r="AM1" s="52"/>
-      <c r="AN1" s="52"/>
-      <c r="AO1" s="52"/>
-      <c r="AP1" s="52"/>
-      <c r="AQ1" s="52"/>
-      <c r="AR1" s="52"/>
-      <c r="AS1" s="52"/>
-      <c r="AT1" s="52"/>
-      <c r="AU1" s="52"/>
-      <c r="AV1" s="52"/>
-      <c r="AW1" s="52"/>
-      <c r="AX1" s="52"/>
-      <c r="AY1" s="52"/>
-      <c r="AZ1" s="52"/>
-      <c r="BA1" s="53"/>
+      <c r="AG1" s="51"/>
+      <c r="AH1" s="51"/>
+      <c r="AI1" s="51"/>
+      <c r="AJ1" s="51"/>
+      <c r="AK1" s="51"/>
+      <c r="AL1" s="51"/>
+      <c r="AM1" s="51"/>
+      <c r="AN1" s="51"/>
+      <c r="AO1" s="51"/>
+      <c r="AP1" s="51"/>
+      <c r="AQ1" s="51"/>
+      <c r="AR1" s="51"/>
+      <c r="AS1" s="51"/>
+      <c r="AT1" s="51"/>
+      <c r="AU1" s="51"/>
+      <c r="AV1" s="51"/>
+      <c r="AW1" s="51"/>
+      <c r="AX1" s="51"/>
+      <c r="AY1" s="51"/>
+      <c r="AZ1" s="51"/>
+      <c r="BA1" s="52"/>
     </row>
     <row r="2" spans="1:54" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="55" t="s">
+      <c r="A2" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="57"/>
-      <c r="M2" s="55" t="s">
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="48"/>
+      <c r="M2" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="56"/>
-      <c r="O2" s="56"/>
-      <c r="P2" s="56"/>
-      <c r="Q2" s="56"/>
-      <c r="R2" s="57"/>
-      <c r="AI2" s="55" t="s">
+      <c r="N2" s="47"/>
+      <c r="O2" s="47"/>
+      <c r="P2" s="47"/>
+      <c r="Q2" s="47"/>
+      <c r="R2" s="48"/>
+      <c r="AI2" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="AJ2" s="56"/>
-      <c r="AK2" s="56"/>
-      <c r="AL2" s="56"/>
-      <c r="AM2" s="56"/>
-      <c r="AN2" s="56"/>
-      <c r="AO2" s="57"/>
-      <c r="AU2" s="55" t="s">
+      <c r="AJ2" s="47"/>
+      <c r="AK2" s="47"/>
+      <c r="AL2" s="47"/>
+      <c r="AM2" s="47"/>
+      <c r="AN2" s="47"/>
+      <c r="AO2" s="48"/>
+      <c r="AU2" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="AV2" s="56"/>
-      <c r="AW2" s="56"/>
-      <c r="AX2" s="56"/>
-      <c r="AY2" s="56"/>
-      <c r="AZ2" s="56"/>
-      <c r="BA2" s="57"/>
+      <c r="AV2" s="47"/>
+      <c r="AW2" s="47"/>
+      <c r="AX2" s="47"/>
+      <c r="AY2" s="47"/>
+      <c r="AZ2" s="47"/>
+      <c r="BA2" s="48"/>
     </row>
     <row r="3" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="49" t="s">
+      <c r="A3" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="49"/>
-      <c r="C3" s="49"/>
-      <c r="D3" s="49"/>
-      <c r="E3" s="49"/>
-      <c r="F3" s="49"/>
-      <c r="G3" s="49"/>
-      <c r="AI3" s="42" t="s">
+      <c r="B3" s="42"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="42"/>
+      <c r="AI3" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="AJ3" s="43"/>
-      <c r="AK3" s="43"/>
-      <c r="AL3" s="43"/>
-      <c r="AM3" s="43"/>
-      <c r="AN3" s="43"/>
-      <c r="AO3" s="44"/>
-      <c r="AU3" s="49" t="s">
+      <c r="AJ3" s="54"/>
+      <c r="AK3" s="54"/>
+      <c r="AL3" s="54"/>
+      <c r="AM3" s="54"/>
+      <c r="AN3" s="54"/>
+      <c r="AO3" s="55"/>
+      <c r="AU3" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="AV3" s="49"/>
-      <c r="AW3" s="49"/>
-      <c r="AX3" s="49"/>
-      <c r="AY3" s="49"/>
-      <c r="AZ3" s="49"/>
-      <c r="BA3" s="49"/>
+      <c r="AV3" s="42"/>
+      <c r="AW3" s="42"/>
+      <c r="AX3" s="42"/>
+      <c r="AY3" s="42"/>
+      <c r="AZ3" s="42"/>
+      <c r="BA3" s="42"/>
     </row>
     <row r="4" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
@@ -1614,15 +1614,15 @@
       <c r="G4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="42" t="s">
+      <c r="M4" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="N4" s="43"/>
-      <c r="O4" s="43"/>
-      <c r="P4" s="43"/>
-      <c r="Q4" s="43"/>
-      <c r="R4" s="43"/>
-      <c r="S4" s="44"/>
+      <c r="N4" s="54"/>
+      <c r="O4" s="54"/>
+      <c r="P4" s="54"/>
+      <c r="Q4" s="54"/>
+      <c r="R4" s="54"/>
+      <c r="S4" s="55"/>
       <c r="AI4" s="3" t="s">
         <v>2</v>
       </c>
@@ -1949,11 +1949,11 @@
       <c r="G8" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="I8" s="50" t="s">
+      <c r="I8" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="J8" s="50"/>
-      <c r="K8" s="50"/>
+      <c r="J8" s="43"/>
+      <c r="K8" s="43"/>
       <c r="M8" s="8">
         <v>3</v>
       </c>
@@ -1996,11 +1996,11 @@
       <c r="AO8" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="AQ8" s="50" t="s">
+      <c r="AQ8" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="AR8" s="50"/>
-      <c r="AS8" s="50"/>
+      <c r="AR8" s="43"/>
+      <c r="AS8" s="43"/>
       <c r="AU8" s="38">
         <v>4</v>
       </c>
@@ -2260,15 +2260,15 @@
       <c r="BA11" s="6"/>
     </row>
     <row r="12" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="49" t="s">
+      <c r="A12" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="49"/>
-      <c r="C12" s="49"/>
-      <c r="D12" s="49"/>
-      <c r="E12" s="49"/>
-      <c r="F12" s="49"/>
-      <c r="G12" s="49"/>
+      <c r="B12" s="42"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="42"/>
       <c r="L12" s="12"/>
       <c r="M12" s="8" t="s">
         <v>12</v>
@@ -2294,69 +2294,69 @@
       <c r="T12" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AI12" s="49" t="s">
+      <c r="AI12" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AJ12" s="49"/>
-      <c r="AK12" s="49"/>
-      <c r="AL12" s="49"/>
-      <c r="AM12" s="49"/>
-      <c r="AN12" s="49"/>
-      <c r="AO12" s="49"/>
+      <c r="AJ12" s="42"/>
+      <c r="AK12" s="42"/>
+      <c r="AL12" s="42"/>
+      <c r="AM12" s="42"/>
+      <c r="AN12" s="42"/>
+      <c r="AO12" s="42"/>
       <c r="AQ12" s="12"/>
-      <c r="AU12" s="49" t="s">
+      <c r="AU12" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AV12" s="49"/>
-      <c r="AW12" s="49"/>
-      <c r="AX12" s="49"/>
-      <c r="AY12" s="49"/>
-      <c r="AZ12" s="49"/>
-      <c r="BA12" s="49"/>
+      <c r="AV12" s="42"/>
+      <c r="AW12" s="42"/>
+      <c r="AX12" s="42"/>
+      <c r="AY12" s="42"/>
+      <c r="AZ12" s="42"/>
+      <c r="BA12" s="42"/>
     </row>
     <row r="13" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L13" s="12"/>
-      <c r="M13" s="42" t="s">
+      <c r="M13" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="N13" s="43"/>
-      <c r="O13" s="43"/>
-      <c r="P13" s="43"/>
-      <c r="Q13" s="43"/>
-      <c r="R13" s="43"/>
-      <c r="S13" s="44"/>
+      <c r="N13" s="54"/>
+      <c r="O13" s="54"/>
+      <c r="P13" s="54"/>
+      <c r="Q13" s="54"/>
+      <c r="R13" s="54"/>
+      <c r="S13" s="55"/>
       <c r="AQ13" s="12"/>
     </row>
     <row r="14" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="48" t="s">
+      <c r="A14" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="48"/>
-      <c r="C14" s="48"/>
-      <c r="D14" s="48"/>
-      <c r="E14" s="48"/>
-      <c r="F14" s="48"/>
-      <c r="G14" s="48"/>
-      <c r="L14" s="54" t="s">
+      <c r="B14" s="45"/>
+      <c r="C14" s="45"/>
+      <c r="D14" s="45"/>
+      <c r="E14" s="45"/>
+      <c r="F14" s="45"/>
+      <c r="G14" s="45"/>
+      <c r="L14" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="M14" s="50"/>
-      <c r="N14" s="50"/>
-      <c r="AN14" s="50" t="s">
+      <c r="M14" s="43"/>
+      <c r="N14" s="43"/>
+      <c r="AN14" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="AO14" s="50"/>
-      <c r="AP14" s="50"/>
+      <c r="AO14" s="43"/>
+      <c r="AP14" s="43"/>
       <c r="AQ14" s="12"/>
-      <c r="AU14" s="48" t="s">
+      <c r="AU14" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="AV14" s="48"/>
-      <c r="AW14" s="48"/>
-      <c r="AX14" s="48"/>
-      <c r="AY14" s="48"/>
-      <c r="AZ14" s="48"/>
-      <c r="BA14" s="48"/>
+      <c r="AV14" s="45"/>
+      <c r="AW14" s="45"/>
+      <c r="AX14" s="45"/>
+      <c r="AY14" s="45"/>
+      <c r="AZ14" s="45"/>
+      <c r="BA14" s="45"/>
     </row>
     <row r="15" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
@@ -2584,19 +2584,19 @@
       <c r="G19" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="I19" s="50" t="s">
+      <c r="I19" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="J19" s="50"/>
-      <c r="K19" s="50"/>
+      <c r="J19" s="43"/>
+      <c r="K19" s="43"/>
       <c r="L19" s="12"/>
       <c r="O19" s="12"/>
       <c r="AN19" s="12"/>
-      <c r="AQ19" s="54" t="s">
+      <c r="AQ19" s="44" t="s">
         <v>31</v>
       </c>
-      <c r="AR19" s="50"/>
-      <c r="AS19" s="50"/>
+      <c r="AR19" s="43"/>
+      <c r="AS19" s="43"/>
       <c r="AU19" s="38">
         <v>4</v>
       </c>
@@ -2758,52 +2758,52 @@
       <c r="BA22" s="6"/>
     </row>
     <row r="23" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="49" t="s">
+      <c r="A23" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B23" s="49"/>
-      <c r="C23" s="49"/>
-      <c r="D23" s="49"/>
-      <c r="E23" s="49"/>
-      <c r="F23" s="49"/>
-      <c r="G23" s="49"/>
+      <c r="B23" s="42"/>
+      <c r="C23" s="42"/>
+      <c r="D23" s="42"/>
+      <c r="E23" s="42"/>
+      <c r="F23" s="42"/>
+      <c r="G23" s="42"/>
       <c r="O23" s="12"/>
       <c r="AN23" s="12"/>
-      <c r="AU23" s="49" t="s">
+      <c r="AU23" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AV23" s="49"/>
-      <c r="AW23" s="49"/>
-      <c r="AX23" s="49"/>
-      <c r="AY23" s="49"/>
-      <c r="AZ23" s="49"/>
-      <c r="BA23" s="49"/>
+      <c r="AV23" s="42"/>
+      <c r="AW23" s="42"/>
+      <c r="AX23" s="42"/>
+      <c r="AY23" s="42"/>
+      <c r="AZ23" s="42"/>
+      <c r="BA23" s="42"/>
     </row>
     <row r="24" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="O24" s="12"/>
       <c r="AN24" s="12"/>
     </row>
     <row r="25" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="49" t="s">
+      <c r="A25" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="49"/>
-      <c r="C25" s="49"/>
-      <c r="D25" s="49"/>
-      <c r="E25" s="49"/>
-      <c r="F25" s="49"/>
-      <c r="G25" s="49"/>
+      <c r="B25" s="42"/>
+      <c r="C25" s="42"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="42"/>
+      <c r="F25" s="42"/>
+      <c r="G25" s="42"/>
       <c r="O25" s="12"/>
       <c r="AN25" s="12"/>
-      <c r="AU25" s="49" t="s">
+      <c r="AU25" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="AV25" s="49"/>
-      <c r="AW25" s="49"/>
-      <c r="AX25" s="49"/>
-      <c r="AY25" s="49"/>
-      <c r="AZ25" s="49"/>
-      <c r="BA25" s="49"/>
+      <c r="AV25" s="42"/>
+      <c r="AW25" s="42"/>
+      <c r="AX25" s="42"/>
+      <c r="AY25" s="42"/>
+      <c r="AZ25" s="42"/>
+      <c r="BA25" s="42"/>
     </row>
     <row r="26" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="20" t="s">
@@ -2827,24 +2827,24 @@
       <c r="G26" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="O26" s="54"/>
-      <c r="P26" s="50"/>
-      <c r="Q26" s="50"/>
-      <c r="R26" s="50"/>
-      <c r="S26" s="50"/>
-      <c r="T26" s="50"/>
-      <c r="U26" s="50"/>
-      <c r="V26" s="50"/>
-      <c r="W26" s="50"/>
-      <c r="AE26" s="50"/>
-      <c r="AF26" s="50"/>
-      <c r="AG26" s="50"/>
-      <c r="AH26" s="50"/>
-      <c r="AI26" s="50"/>
-      <c r="AJ26" s="50"/>
-      <c r="AK26" s="50"/>
-      <c r="AL26" s="50"/>
-      <c r="AM26" s="58"/>
+      <c r="O26" s="44"/>
+      <c r="P26" s="43"/>
+      <c r="Q26" s="43"/>
+      <c r="R26" s="43"/>
+      <c r="S26" s="43"/>
+      <c r="T26" s="43"/>
+      <c r="U26" s="43"/>
+      <c r="V26" s="43"/>
+      <c r="W26" s="43"/>
+      <c r="AE26" s="43"/>
+      <c r="AF26" s="43"/>
+      <c r="AG26" s="43"/>
+      <c r="AH26" s="43"/>
+      <c r="AI26" s="43"/>
+      <c r="AJ26" s="43"/>
+      <c r="AK26" s="43"/>
+      <c r="AL26" s="43"/>
+      <c r="AM26" s="49"/>
       <c r="AU26" s="20" t="s">
         <v>2</v>
       </c>
@@ -2941,26 +2941,26 @@
         <v>54</v>
       </c>
       <c r="O28" s="12"/>
-      <c r="P28" s="42" t="s">
+      <c r="P28" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="Q28" s="43"/>
-      <c r="R28" s="43"/>
-      <c r="S28" s="43"/>
-      <c r="T28" s="43"/>
-      <c r="U28" s="43"/>
-      <c r="V28" s="44"/>
+      <c r="Q28" s="54"/>
+      <c r="R28" s="54"/>
+      <c r="S28" s="54"/>
+      <c r="T28" s="54"/>
+      <c r="U28" s="54"/>
+      <c r="V28" s="55"/>
       <c r="X28" s="12"/>
       <c r="AD28" s="13"/>
-      <c r="AF28" s="49" t="s">
+      <c r="AF28" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="AG28" s="49"/>
-      <c r="AH28" s="49"/>
-      <c r="AI28" s="49"/>
-      <c r="AJ28" s="49"/>
-      <c r="AK28" s="49"/>
-      <c r="AL28" s="49"/>
+      <c r="AG28" s="42"/>
+      <c r="AH28" s="42"/>
+      <c r="AI28" s="42"/>
+      <c r="AJ28" s="42"/>
+      <c r="AK28" s="42"/>
+      <c r="AL28" s="42"/>
       <c r="AN28" s="12"/>
       <c r="AU28" s="8">
         <v>2</v>
@@ -3096,11 +3096,11 @@
       <c r="G30" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="I30" s="50" t="s">
+      <c r="I30" s="43" t="s">
         <v>26</v>
       </c>
-      <c r="J30" s="50"/>
-      <c r="K30" s="50"/>
+      <c r="J30" s="43"/>
+      <c r="K30" s="43"/>
       <c r="O30" s="12"/>
       <c r="P30" s="7">
         <v>1</v>
@@ -3147,11 +3147,11 @@
         <v>52</v>
       </c>
       <c r="AN30" s="12"/>
-      <c r="AQ30" s="50" t="s">
+      <c r="AQ30" s="43" t="s">
         <v>38</v>
       </c>
-      <c r="AR30" s="50"/>
-      <c r="AS30" s="50"/>
+      <c r="AR30" s="43"/>
+      <c r="AS30" s="43"/>
       <c r="AU30" s="38">
         <v>4</v>
       </c>
@@ -3204,12 +3204,18 @@
       <c r="R31" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="S31" s="13"/>
+      <c r="S31" s="13">
+        <v>2</v>
+      </c>
       <c r="T31" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="U31" s="13"/>
-      <c r="V31" s="16"/>
+      <c r="U31" s="13">
+        <v>3</v>
+      </c>
+      <c r="V31" s="16" t="s">
+        <v>56</v>
+      </c>
       <c r="X31" s="12"/>
       <c r="AD31" s="13"/>
       <c r="AF31" s="8">
@@ -3405,15 +3411,15 @@
       <c r="BA33" s="6"/>
     </row>
     <row r="34" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="49" t="s">
+      <c r="A34" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B34" s="49"/>
-      <c r="C34" s="49"/>
-      <c r="D34" s="49"/>
-      <c r="E34" s="49"/>
-      <c r="F34" s="49"/>
-      <c r="G34" s="49"/>
+      <c r="B34" s="42"/>
+      <c r="C34" s="42"/>
+      <c r="D34" s="42"/>
+      <c r="E34" s="42"/>
+      <c r="F34" s="42"/>
+      <c r="G34" s="42"/>
       <c r="L34" s="12"/>
       <c r="O34" s="12"/>
       <c r="P34" s="8" t="s">
@@ -3450,15 +3456,15 @@
       <c r="AL34" s="16"/>
       <c r="AN34" s="12"/>
       <c r="AQ34" s="12"/>
-      <c r="AU34" s="49" t="s">
+      <c r="AU34" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AV34" s="49"/>
-      <c r="AW34" s="49"/>
-      <c r="AX34" s="49"/>
-      <c r="AY34" s="49"/>
-      <c r="AZ34" s="49"/>
-      <c r="BA34" s="49"/>
+      <c r="AV34" s="42"/>
+      <c r="AW34" s="42"/>
+      <c r="AX34" s="42"/>
+      <c r="AY34" s="42"/>
+      <c r="AZ34" s="42"/>
+      <c r="BA34" s="42"/>
     </row>
     <row r="35" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L35" s="12"/>
@@ -3499,20 +3505,20 @@
       <c r="AQ35" s="12"/>
     </row>
     <row r="36" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="48" t="s">
+      <c r="A36" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="B36" s="48"/>
-      <c r="C36" s="48"/>
-      <c r="D36" s="48"/>
-      <c r="E36" s="48"/>
-      <c r="F36" s="48"/>
-      <c r="G36" s="48"/>
-      <c r="L36" s="54" t="s">
+      <c r="B36" s="45"/>
+      <c r="C36" s="45"/>
+      <c r="D36" s="45"/>
+      <c r="E36" s="45"/>
+      <c r="F36" s="45"/>
+      <c r="G36" s="45"/>
+      <c r="L36" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="M36" s="50"/>
-      <c r="N36" s="50"/>
+      <c r="M36" s="43"/>
+      <c r="N36" s="43"/>
       <c r="O36" s="12"/>
       <c r="P36" s="8" t="s">
         <v>12</v>
@@ -3546,21 +3552,21 @@
       </c>
       <c r="AK36" s="36"/>
       <c r="AL36" s="37"/>
-      <c r="AN36" s="54" t="s">
+      <c r="AN36" s="44" t="s">
         <v>38</v>
       </c>
-      <c r="AO36" s="50"/>
-      <c r="AP36" s="50"/>
+      <c r="AO36" s="43"/>
+      <c r="AP36" s="43"/>
       <c r="AQ36" s="12"/>
-      <c r="AU36" s="48" t="s">
+      <c r="AU36" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="AV36" s="48"/>
-      <c r="AW36" s="48"/>
-      <c r="AX36" s="48"/>
-      <c r="AY36" s="48"/>
-      <c r="AZ36" s="48"/>
-      <c r="BA36" s="48"/>
+      <c r="AV36" s="45"/>
+      <c r="AW36" s="45"/>
+      <c r="AX36" s="45"/>
+      <c r="AY36" s="45"/>
+      <c r="AZ36" s="45"/>
+      <c r="BA36" s="45"/>
     </row>
     <row r="37" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37" s="20" t="s">
@@ -3585,31 +3591,31 @@
         <v>9</v>
       </c>
       <c r="L37" s="12"/>
-      <c r="P37" s="45" t="s">
+      <c r="P37" s="56" t="s">
         <v>13</v>
       </c>
-      <c r="Q37" s="46"/>
-      <c r="R37" s="46"/>
-      <c r="S37" s="46"/>
-      <c r="T37" s="46"/>
-      <c r="U37" s="46"/>
-      <c r="V37" s="47"/>
-      <c r="X37" s="54"/>
-      <c r="Y37" s="50"/>
-      <c r="Z37" s="50"/>
-      <c r="AA37" s="50"/>
-      <c r="AB37" s="50"/>
-      <c r="AC37" s="50"/>
-      <c r="AD37" s="58"/>
-      <c r="AF37" s="49" t="s">
+      <c r="Q37" s="57"/>
+      <c r="R37" s="57"/>
+      <c r="S37" s="57"/>
+      <c r="T37" s="57"/>
+      <c r="U37" s="57"/>
+      <c r="V37" s="58"/>
+      <c r="X37" s="44"/>
+      <c r="Y37" s="43"/>
+      <c r="Z37" s="43"/>
+      <c r="AA37" s="43"/>
+      <c r="AB37" s="43"/>
+      <c r="AC37" s="43"/>
+      <c r="AD37" s="49"/>
+      <c r="AF37" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AG37" s="49"/>
-      <c r="AH37" s="49"/>
-      <c r="AI37" s="49"/>
-      <c r="AJ37" s="49"/>
-      <c r="AK37" s="49"/>
-      <c r="AL37" s="49"/>
+      <c r="AG37" s="42"/>
+      <c r="AH37" s="42"/>
+      <c r="AI37" s="42"/>
+      <c r="AJ37" s="42"/>
+      <c r="AK37" s="42"/>
+      <c r="AL37" s="42"/>
       <c r="AQ37" s="12"/>
       <c r="AU37" s="3" t="s">
         <v>2</v>
@@ -3702,33 +3708,33 @@
         <v>53</v>
       </c>
       <c r="L39" s="12"/>
-      <c r="M39" s="42" t="s">
+      <c r="M39" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="N39" s="43"/>
-      <c r="O39" s="43"/>
-      <c r="P39" s="43"/>
-      <c r="Q39" s="43"/>
-      <c r="R39" s="43"/>
-      <c r="S39" s="44"/>
-      <c r="X39" s="49" t="s">
+      <c r="N39" s="54"/>
+      <c r="O39" s="54"/>
+      <c r="P39" s="54"/>
+      <c r="Q39" s="54"/>
+      <c r="R39" s="54"/>
+      <c r="S39" s="55"/>
+      <c r="X39" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="Y39" s="49"/>
-      <c r="Z39" s="49"/>
-      <c r="AA39" s="49"/>
-      <c r="AB39" s="49"/>
-      <c r="AC39" s="49"/>
-      <c r="AD39" s="49"/>
-      <c r="AI39" s="42" t="s">
+      <c r="Y39" s="42"/>
+      <c r="Z39" s="42"/>
+      <c r="AA39" s="42"/>
+      <c r="AB39" s="42"/>
+      <c r="AC39" s="42"/>
+      <c r="AD39" s="42"/>
+      <c r="AI39" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="AJ39" s="43"/>
-      <c r="AK39" s="43"/>
-      <c r="AL39" s="43"/>
-      <c r="AM39" s="43"/>
-      <c r="AN39" s="43"/>
-      <c r="AO39" s="44"/>
+      <c r="AJ39" s="54"/>
+      <c r="AK39" s="54"/>
+      <c r="AL39" s="54"/>
+      <c r="AM39" s="54"/>
+      <c r="AN39" s="54"/>
+      <c r="AO39" s="55"/>
       <c r="AQ39" s="12"/>
       <c r="AU39" s="8">
         <v>2</v>
@@ -3883,11 +3889,11 @@
       <c r="G41" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="I41" s="50" t="s">
+      <c r="I41" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="J41" s="50"/>
-      <c r="K41" s="50"/>
+      <c r="J41" s="43"/>
+      <c r="K41" s="43"/>
       <c r="L41" s="12"/>
       <c r="M41" s="7">
         <v>1</v>
@@ -3940,11 +3946,11 @@
       <c r="AO41" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="AQ41" s="54" t="s">
+      <c r="AQ41" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="AR41" s="50"/>
-      <c r="AS41" s="50"/>
+      <c r="AR41" s="43"/>
+      <c r="AS41" s="43"/>
       <c r="AU41" s="38">
         <v>4</v>
       </c>
@@ -4250,15 +4256,15 @@
       <c r="BA44" s="6"/>
     </row>
     <row r="45" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="49" t="s">
+      <c r="A45" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B45" s="49"/>
-      <c r="C45" s="49"/>
-      <c r="D45" s="49"/>
-      <c r="E45" s="49"/>
-      <c r="F45" s="49"/>
-      <c r="G45" s="49"/>
+      <c r="B45" s="42"/>
+      <c r="C45" s="42"/>
+      <c r="D45" s="42"/>
+      <c r="E45" s="42"/>
+      <c r="F45" s="42"/>
+      <c r="G45" s="42"/>
       <c r="M45" s="8" t="s">
         <v>11</v>
       </c>
@@ -4307,15 +4313,15 @@
       <c r="AP45" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AU45" s="49" t="s">
+      <c r="AU45" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AV45" s="49"/>
-      <c r="AW45" s="49"/>
-      <c r="AX45" s="49"/>
-      <c r="AY45" s="49"/>
-      <c r="AZ45" s="49"/>
-      <c r="BA45" s="49"/>
+      <c r="AV45" s="42"/>
+      <c r="AW45" s="42"/>
+      <c r="AX45" s="42"/>
+      <c r="AY45" s="42"/>
+      <c r="AZ45" s="42"/>
+      <c r="BA45" s="42"/>
     </row>
     <row r="46" spans="1:54" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="M46" s="8" t="s">
@@ -4406,49 +4412,61 @@
       <c r="AO47" s="6"/>
     </row>
     <row r="48" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="M48" s="42" t="s">
+      <c r="M48" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="N48" s="43"/>
-      <c r="O48" s="43"/>
-      <c r="P48" s="43"/>
-      <c r="Q48" s="43"/>
-      <c r="R48" s="43"/>
-      <c r="S48" s="44"/>
-      <c r="X48" s="49" t="s">
+      <c r="N48" s="54"/>
+      <c r="O48" s="54"/>
+      <c r="P48" s="54"/>
+      <c r="Q48" s="54"/>
+      <c r="R48" s="54"/>
+      <c r="S48" s="55"/>
+      <c r="X48" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="Y48" s="49"/>
-      <c r="Z48" s="49"/>
-      <c r="AA48" s="49"/>
-      <c r="AB48" s="49"/>
-      <c r="AC48" s="49"/>
-      <c r="AD48" s="49"/>
-      <c r="AI48" s="49" t="s">
+      <c r="Y48" s="42"/>
+      <c r="Z48" s="42"/>
+      <c r="AA48" s="42"/>
+      <c r="AB48" s="42"/>
+      <c r="AC48" s="42"/>
+      <c r="AD48" s="42"/>
+      <c r="AI48" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AJ48" s="49"/>
-      <c r="AK48" s="49"/>
-      <c r="AL48" s="49"/>
-      <c r="AM48" s="49"/>
-      <c r="AN48" s="49"/>
-      <c r="AO48" s="49"/>
+      <c r="AJ48" s="42"/>
+      <c r="AK48" s="42"/>
+      <c r="AL48" s="42"/>
+      <c r="AM48" s="42"/>
+      <c r="AN48" s="42"/>
+      <c r="AO48" s="42"/>
     </row>
     <row r="49" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="AU45:BA45"/>
-    <mergeCell ref="AF28:AL28"/>
-    <mergeCell ref="AF37:AL37"/>
-    <mergeCell ref="AQ30:AS30"/>
-    <mergeCell ref="AQ41:AS41"/>
-    <mergeCell ref="AU34:BA34"/>
-    <mergeCell ref="AU36:BA36"/>
-    <mergeCell ref="AU2:BA2"/>
-    <mergeCell ref="AU3:BA3"/>
-    <mergeCell ref="AU12:BA12"/>
-    <mergeCell ref="AU14:BA14"/>
-    <mergeCell ref="AU23:BA23"/>
+    <mergeCell ref="M48:S48"/>
+    <mergeCell ref="M39:S39"/>
+    <mergeCell ref="P37:V37"/>
+    <mergeCell ref="P28:V28"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A1:U1"/>
+    <mergeCell ref="O26:W26"/>
+    <mergeCell ref="I41:K41"/>
+    <mergeCell ref="L14:N14"/>
+    <mergeCell ref="L36:N36"/>
+    <mergeCell ref="M2:R2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="M4:S4"/>
+    <mergeCell ref="M13:S13"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="A25:G25"/>
     <mergeCell ref="X37:AD37"/>
     <mergeCell ref="AE26:AM26"/>
     <mergeCell ref="Z1:AB1"/>
@@ -4465,30 +4483,18 @@
     <mergeCell ref="AN36:AP36"/>
     <mergeCell ref="AQ8:AS8"/>
     <mergeCell ref="AQ19:AS19"/>
-    <mergeCell ref="A1:U1"/>
-    <mergeCell ref="O26:W26"/>
-    <mergeCell ref="I41:K41"/>
-    <mergeCell ref="L14:N14"/>
-    <mergeCell ref="L36:N36"/>
-    <mergeCell ref="M2:R2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="M4:S4"/>
-    <mergeCell ref="M13:S13"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A23:G23"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="M48:S48"/>
-    <mergeCell ref="M39:S39"/>
-    <mergeCell ref="P37:V37"/>
-    <mergeCell ref="P28:V28"/>
-    <mergeCell ref="A36:G36"/>
-    <mergeCell ref="A45:G45"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="AU2:BA2"/>
+    <mergeCell ref="AU3:BA3"/>
+    <mergeCell ref="AU12:BA12"/>
+    <mergeCell ref="AU14:BA14"/>
+    <mergeCell ref="AU23:BA23"/>
+    <mergeCell ref="AU45:BA45"/>
+    <mergeCell ref="AF28:AL28"/>
+    <mergeCell ref="AF37:AL37"/>
+    <mergeCell ref="AQ30:AS30"/>
+    <mergeCell ref="AQ41:AS41"/>
+    <mergeCell ref="AU34:BA34"/>
+    <mergeCell ref="AU36:BA36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/2025_2026/Playoffs/Brackets.xlsx
+++ b/2025_2026/Playoffs/Brackets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\NHLStats\2025_2026\Playoffs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BE52E77-5CC1-493F-8276-9151F301F71D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A043C336-6EC7-4B2C-96F1-9BAF76A87790}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="96">
   <si>
     <t>Eastern Conference Playoff Teams</t>
   </si>
@@ -311,6 +311,9 @@
   </si>
   <si>
     <t>Golden Knights Lead 2-0</t>
+  </si>
+  <si>
+    <t>Golden Knights Lead 3-0</t>
   </si>
 </sst>
 </file>
@@ -689,18 +692,45 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -713,40 +743,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1116,18 +1119,18 @@
     </row>
     <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="11" spans="1:7" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="59" t="s">
+      <c r="A11" s="61" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="59"/>
-      <c r="C11" s="59" t="s">
+      <c r="B11" s="61"/>
+      <c r="C11" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="59"/>
-      <c r="E11" s="59" t="s">
+      <c r="D11" s="61"/>
+      <c r="E11" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="59"/>
+      <c r="F11" s="61"/>
       <c r="G11" s="4" t="s">
         <v>18</v>
       </c>
@@ -1156,18 +1159,18 @@
       </c>
     </row>
     <row r="13" spans="1:7" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="60" t="s">
+      <c r="A13" s="59" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="61"/>
-      <c r="C13" s="60" t="s">
+      <c r="B13" s="60"/>
+      <c r="C13" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="D13" s="61"/>
-      <c r="E13" s="60" t="s">
+      <c r="D13" s="60"/>
+      <c r="E13" s="59" t="s">
         <v>17</v>
       </c>
-      <c r="F13" s="61"/>
+      <c r="F13" s="60"/>
       <c r="G13" s="5"/>
     </row>
     <row r="14" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1212,14 +1215,14 @@
       </c>
     </row>
     <row r="16" spans="1:7" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="60" t="s">
+      <c r="A16" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="61"/>
-      <c r="C16" s="60" t="s">
+      <c r="B16" s="60"/>
+      <c r="C16" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="61"/>
+      <c r="D16" s="60"/>
     </row>
     <row r="17" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
@@ -1250,10 +1253,10 @@
       </c>
     </row>
     <row r="19" spans="1:4" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="60" t="s">
+      <c r="A19" s="59" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="61"/>
+      <c r="B19" s="60"/>
     </row>
     <row r="20" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
@@ -1272,10 +1275,10 @@
       </c>
     </row>
     <row r="22" spans="1:4" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="60" t="s">
+      <c r="A22" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="61"/>
+      <c r="B22" s="60"/>
     </row>
     <row r="23" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
@@ -1360,16 +1363,16 @@
     <sortCondition ref="B2:B9"/>
   </sortState>
   <mergeCells count="10">
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A16:B16"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A16:B16"/>
   </mergeCells>
   <dataValidations count="16">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C14" xr:uid="{2C3D9587-ABAE-4E3F-8B22-396DF812BF02}">
@@ -1473,124 +1476,124 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:54" ht="27.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
-      <c r="I1" s="51"/>
-      <c r="J1" s="51"/>
-      <c r="K1" s="51"/>
-      <c r="L1" s="51"/>
-      <c r="M1" s="51"/>
-      <c r="N1" s="51"/>
-      <c r="O1" s="51"/>
-      <c r="P1" s="51"/>
-      <c r="Q1" s="51"/>
-      <c r="R1" s="51"/>
-      <c r="S1" s="51"/>
-      <c r="T1" s="51"/>
-      <c r="U1" s="52"/>
-      <c r="Z1" s="50" t="s">
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="52"/>
+      <c r="M1" s="52"/>
+      <c r="N1" s="52"/>
+      <c r="O1" s="52"/>
+      <c r="P1" s="52"/>
+      <c r="Q1" s="52"/>
+      <c r="R1" s="52"/>
+      <c r="S1" s="52"/>
+      <c r="T1" s="52"/>
+      <c r="U1" s="53"/>
+      <c r="Z1" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="AA1" s="51"/>
-      <c r="AB1" s="52"/>
-      <c r="AF1" s="50" t="s">
+      <c r="AA1" s="52"/>
+      <c r="AB1" s="53"/>
+      <c r="AF1" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="AG1" s="51"/>
-      <c r="AH1" s="51"/>
-      <c r="AI1" s="51"/>
-      <c r="AJ1" s="51"/>
-      <c r="AK1" s="51"/>
-      <c r="AL1" s="51"/>
-      <c r="AM1" s="51"/>
-      <c r="AN1" s="51"/>
-      <c r="AO1" s="51"/>
-      <c r="AP1" s="51"/>
-      <c r="AQ1" s="51"/>
-      <c r="AR1" s="51"/>
-      <c r="AS1" s="51"/>
-      <c r="AT1" s="51"/>
-      <c r="AU1" s="51"/>
-      <c r="AV1" s="51"/>
-      <c r="AW1" s="51"/>
-      <c r="AX1" s="51"/>
-      <c r="AY1" s="51"/>
-      <c r="AZ1" s="51"/>
-      <c r="BA1" s="52"/>
+      <c r="AG1" s="52"/>
+      <c r="AH1" s="52"/>
+      <c r="AI1" s="52"/>
+      <c r="AJ1" s="52"/>
+      <c r="AK1" s="52"/>
+      <c r="AL1" s="52"/>
+      <c r="AM1" s="52"/>
+      <c r="AN1" s="52"/>
+      <c r="AO1" s="52"/>
+      <c r="AP1" s="52"/>
+      <c r="AQ1" s="52"/>
+      <c r="AR1" s="52"/>
+      <c r="AS1" s="52"/>
+      <c r="AT1" s="52"/>
+      <c r="AU1" s="52"/>
+      <c r="AV1" s="52"/>
+      <c r="AW1" s="52"/>
+      <c r="AX1" s="52"/>
+      <c r="AY1" s="52"/>
+      <c r="AZ1" s="52"/>
+      <c r="BA1" s="53"/>
     </row>
     <row r="2" spans="1:54" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="48"/>
-      <c r="M2" s="46" t="s">
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="57"/>
+      <c r="M2" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="47"/>
-      <c r="O2" s="47"/>
-      <c r="P2" s="47"/>
-      <c r="Q2" s="47"/>
-      <c r="R2" s="48"/>
-      <c r="AI2" s="46" t="s">
+      <c r="N2" s="56"/>
+      <c r="O2" s="56"/>
+      <c r="P2" s="56"/>
+      <c r="Q2" s="56"/>
+      <c r="R2" s="57"/>
+      <c r="AI2" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="AJ2" s="47"/>
-      <c r="AK2" s="47"/>
-      <c r="AL2" s="47"/>
-      <c r="AM2" s="47"/>
-      <c r="AN2" s="47"/>
-      <c r="AO2" s="48"/>
-      <c r="AU2" s="46" t="s">
+      <c r="AJ2" s="56"/>
+      <c r="AK2" s="56"/>
+      <c r="AL2" s="56"/>
+      <c r="AM2" s="56"/>
+      <c r="AN2" s="56"/>
+      <c r="AO2" s="57"/>
+      <c r="AU2" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="AV2" s="47"/>
-      <c r="AW2" s="47"/>
-      <c r="AX2" s="47"/>
-      <c r="AY2" s="47"/>
-      <c r="AZ2" s="47"/>
-      <c r="BA2" s="48"/>
+      <c r="AV2" s="56"/>
+      <c r="AW2" s="56"/>
+      <c r="AX2" s="56"/>
+      <c r="AY2" s="56"/>
+      <c r="AZ2" s="56"/>
+      <c r="BA2" s="57"/>
     </row>
     <row r="3" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="42" t="s">
+      <c r="A3" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="42"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="42"/>
-      <c r="AI3" s="53" t="s">
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="AI3" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="AJ3" s="54"/>
-      <c r="AK3" s="54"/>
-      <c r="AL3" s="54"/>
-      <c r="AM3" s="54"/>
-      <c r="AN3" s="54"/>
-      <c r="AO3" s="55"/>
-      <c r="AU3" s="42" t="s">
+      <c r="AJ3" s="43"/>
+      <c r="AK3" s="43"/>
+      <c r="AL3" s="43"/>
+      <c r="AM3" s="43"/>
+      <c r="AN3" s="43"/>
+      <c r="AO3" s="44"/>
+      <c r="AU3" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="AV3" s="42"/>
-      <c r="AW3" s="42"/>
-      <c r="AX3" s="42"/>
-      <c r="AY3" s="42"/>
-      <c r="AZ3" s="42"/>
-      <c r="BA3" s="42"/>
+      <c r="AV3" s="49"/>
+      <c r="AW3" s="49"/>
+      <c r="AX3" s="49"/>
+      <c r="AY3" s="49"/>
+      <c r="AZ3" s="49"/>
+      <c r="BA3" s="49"/>
     </row>
     <row r="4" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
@@ -1614,15 +1617,15 @@
       <c r="G4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="53" t="s">
+      <c r="M4" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="N4" s="54"/>
-      <c r="O4" s="54"/>
-      <c r="P4" s="54"/>
-      <c r="Q4" s="54"/>
-      <c r="R4" s="54"/>
-      <c r="S4" s="55"/>
+      <c r="N4" s="43"/>
+      <c r="O4" s="43"/>
+      <c r="P4" s="43"/>
+      <c r="Q4" s="43"/>
+      <c r="R4" s="43"/>
+      <c r="S4" s="44"/>
       <c r="AI4" s="3" t="s">
         <v>2</v>
       </c>
@@ -1949,11 +1952,11 @@
       <c r="G8" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="I8" s="43" t="s">
+      <c r="I8" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="J8" s="43"/>
-      <c r="K8" s="43"/>
+      <c r="J8" s="50"/>
+      <c r="K8" s="50"/>
       <c r="M8" s="8">
         <v>3</v>
       </c>
@@ -1996,11 +1999,11 @@
       <c r="AO8" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="AQ8" s="43" t="s">
+      <c r="AQ8" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="AR8" s="43"/>
-      <c r="AS8" s="43"/>
+      <c r="AR8" s="50"/>
+      <c r="AS8" s="50"/>
       <c r="AU8" s="38">
         <v>4</v>
       </c>
@@ -2260,15 +2263,15 @@
       <c r="BA11" s="6"/>
     </row>
     <row r="12" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="42" t="s">
+      <c r="A12" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="42"/>
-      <c r="C12" s="42"/>
-      <c r="D12" s="42"/>
-      <c r="E12" s="42"/>
-      <c r="F12" s="42"/>
-      <c r="G12" s="42"/>
+      <c r="B12" s="49"/>
+      <c r="C12" s="49"/>
+      <c r="D12" s="49"/>
+      <c r="E12" s="49"/>
+      <c r="F12" s="49"/>
+      <c r="G12" s="49"/>
       <c r="L12" s="12"/>
       <c r="M12" s="8" t="s">
         <v>12</v>
@@ -2294,69 +2297,69 @@
       <c r="T12" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AI12" s="42" t="s">
+      <c r="AI12" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AJ12" s="42"/>
-      <c r="AK12" s="42"/>
-      <c r="AL12" s="42"/>
-      <c r="AM12" s="42"/>
-      <c r="AN12" s="42"/>
-      <c r="AO12" s="42"/>
+      <c r="AJ12" s="49"/>
+      <c r="AK12" s="49"/>
+      <c r="AL12" s="49"/>
+      <c r="AM12" s="49"/>
+      <c r="AN12" s="49"/>
+      <c r="AO12" s="49"/>
       <c r="AQ12" s="12"/>
-      <c r="AU12" s="42" t="s">
+      <c r="AU12" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AV12" s="42"/>
-      <c r="AW12" s="42"/>
-      <c r="AX12" s="42"/>
-      <c r="AY12" s="42"/>
-      <c r="AZ12" s="42"/>
-      <c r="BA12" s="42"/>
+      <c r="AV12" s="49"/>
+      <c r="AW12" s="49"/>
+      <c r="AX12" s="49"/>
+      <c r="AY12" s="49"/>
+      <c r="AZ12" s="49"/>
+      <c r="BA12" s="49"/>
     </row>
     <row r="13" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L13" s="12"/>
-      <c r="M13" s="53" t="s">
+      <c r="M13" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="N13" s="54"/>
-      <c r="O13" s="54"/>
-      <c r="P13" s="54"/>
-      <c r="Q13" s="54"/>
-      <c r="R13" s="54"/>
-      <c r="S13" s="55"/>
+      <c r="N13" s="43"/>
+      <c r="O13" s="43"/>
+      <c r="P13" s="43"/>
+      <c r="Q13" s="43"/>
+      <c r="R13" s="43"/>
+      <c r="S13" s="44"/>
       <c r="AQ13" s="12"/>
     </row>
     <row r="14" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="45" t="s">
+      <c r="A14" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="45"/>
-      <c r="C14" s="45"/>
-      <c r="D14" s="45"/>
-      <c r="E14" s="45"/>
-      <c r="F14" s="45"/>
-      <c r="G14" s="45"/>
-      <c r="L14" s="44" t="s">
+      <c r="B14" s="48"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="48"/>
+      <c r="E14" s="48"/>
+      <c r="F14" s="48"/>
+      <c r="G14" s="48"/>
+      <c r="L14" s="54" t="s">
         <v>32</v>
       </c>
-      <c r="M14" s="43"/>
-      <c r="N14" s="43"/>
-      <c r="AN14" s="43" t="s">
+      <c r="M14" s="50"/>
+      <c r="N14" s="50"/>
+      <c r="AN14" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="AO14" s="43"/>
-      <c r="AP14" s="43"/>
+      <c r="AO14" s="50"/>
+      <c r="AP14" s="50"/>
       <c r="AQ14" s="12"/>
-      <c r="AU14" s="45" t="s">
+      <c r="AU14" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="AV14" s="45"/>
-      <c r="AW14" s="45"/>
-      <c r="AX14" s="45"/>
-      <c r="AY14" s="45"/>
-      <c r="AZ14" s="45"/>
-      <c r="BA14" s="45"/>
+      <c r="AV14" s="48"/>
+      <c r="AW14" s="48"/>
+      <c r="AX14" s="48"/>
+      <c r="AY14" s="48"/>
+      <c r="AZ14" s="48"/>
+      <c r="BA14" s="48"/>
     </row>
     <row r="15" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
@@ -2584,19 +2587,19 @@
       <c r="G19" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="I19" s="43" t="s">
+      <c r="I19" s="50" t="s">
         <v>32</v>
       </c>
-      <c r="J19" s="43"/>
-      <c r="K19" s="43"/>
+      <c r="J19" s="50"/>
+      <c r="K19" s="50"/>
       <c r="L19" s="12"/>
       <c r="O19" s="12"/>
       <c r="AN19" s="12"/>
-      <c r="AQ19" s="44" t="s">
+      <c r="AQ19" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="AR19" s="43"/>
-      <c r="AS19" s="43"/>
+      <c r="AR19" s="50"/>
+      <c r="AS19" s="50"/>
       <c r="AU19" s="38">
         <v>4</v>
       </c>
@@ -2758,52 +2761,52 @@
       <c r="BA22" s="6"/>
     </row>
     <row r="23" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="42" t="s">
+      <c r="A23" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="B23" s="42"/>
-      <c r="C23" s="42"/>
-      <c r="D23" s="42"/>
-      <c r="E23" s="42"/>
-      <c r="F23" s="42"/>
-      <c r="G23" s="42"/>
+      <c r="B23" s="49"/>
+      <c r="C23" s="49"/>
+      <c r="D23" s="49"/>
+      <c r="E23" s="49"/>
+      <c r="F23" s="49"/>
+      <c r="G23" s="49"/>
       <c r="O23" s="12"/>
       <c r="AN23" s="12"/>
-      <c r="AU23" s="42" t="s">
+      <c r="AU23" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AV23" s="42"/>
-      <c r="AW23" s="42"/>
-      <c r="AX23" s="42"/>
-      <c r="AY23" s="42"/>
-      <c r="AZ23" s="42"/>
-      <c r="BA23" s="42"/>
+      <c r="AV23" s="49"/>
+      <c r="AW23" s="49"/>
+      <c r="AX23" s="49"/>
+      <c r="AY23" s="49"/>
+      <c r="AZ23" s="49"/>
+      <c r="BA23" s="49"/>
     </row>
     <row r="24" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="O24" s="12"/>
       <c r="AN24" s="12"/>
     </row>
     <row r="25" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="42" t="s">
+      <c r="A25" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="42"/>
-      <c r="C25" s="42"/>
-      <c r="D25" s="42"/>
-      <c r="E25" s="42"/>
-      <c r="F25" s="42"/>
-      <c r="G25" s="42"/>
+      <c r="B25" s="49"/>
+      <c r="C25" s="49"/>
+      <c r="D25" s="49"/>
+      <c r="E25" s="49"/>
+      <c r="F25" s="49"/>
+      <c r="G25" s="49"/>
       <c r="O25" s="12"/>
       <c r="AN25" s="12"/>
-      <c r="AU25" s="42" t="s">
+      <c r="AU25" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="AV25" s="42"/>
-      <c r="AW25" s="42"/>
-      <c r="AX25" s="42"/>
-      <c r="AY25" s="42"/>
-      <c r="AZ25" s="42"/>
-      <c r="BA25" s="42"/>
+      <c r="AV25" s="49"/>
+      <c r="AW25" s="49"/>
+      <c r="AX25" s="49"/>
+      <c r="AY25" s="49"/>
+      <c r="AZ25" s="49"/>
+      <c r="BA25" s="49"/>
     </row>
     <row r="26" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="20" t="s">
@@ -2827,24 +2830,24 @@
       <c r="G26" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="O26" s="44"/>
-      <c r="P26" s="43"/>
-      <c r="Q26" s="43"/>
-      <c r="R26" s="43"/>
-      <c r="S26" s="43"/>
-      <c r="T26" s="43"/>
-      <c r="U26" s="43"/>
-      <c r="V26" s="43"/>
-      <c r="W26" s="43"/>
-      <c r="AE26" s="43"/>
-      <c r="AF26" s="43"/>
-      <c r="AG26" s="43"/>
-      <c r="AH26" s="43"/>
-      <c r="AI26" s="43"/>
-      <c r="AJ26" s="43"/>
-      <c r="AK26" s="43"/>
-      <c r="AL26" s="43"/>
-      <c r="AM26" s="49"/>
+      <c r="O26" s="54"/>
+      <c r="P26" s="50"/>
+      <c r="Q26" s="50"/>
+      <c r="R26" s="50"/>
+      <c r="S26" s="50"/>
+      <c r="T26" s="50"/>
+      <c r="U26" s="50"/>
+      <c r="V26" s="50"/>
+      <c r="W26" s="50"/>
+      <c r="AE26" s="50"/>
+      <c r="AF26" s="50"/>
+      <c r="AG26" s="50"/>
+      <c r="AH26" s="50"/>
+      <c r="AI26" s="50"/>
+      <c r="AJ26" s="50"/>
+      <c r="AK26" s="50"/>
+      <c r="AL26" s="50"/>
+      <c r="AM26" s="58"/>
       <c r="AU26" s="20" t="s">
         <v>2</v>
       </c>
@@ -2941,26 +2944,26 @@
         <v>54</v>
       </c>
       <c r="O28" s="12"/>
-      <c r="P28" s="53" t="s">
+      <c r="P28" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="Q28" s="54"/>
-      <c r="R28" s="54"/>
-      <c r="S28" s="54"/>
-      <c r="T28" s="54"/>
-      <c r="U28" s="54"/>
-      <c r="V28" s="55"/>
+      <c r="Q28" s="43"/>
+      <c r="R28" s="43"/>
+      <c r="S28" s="43"/>
+      <c r="T28" s="43"/>
+      <c r="U28" s="43"/>
+      <c r="V28" s="44"/>
       <c r="X28" s="12"/>
       <c r="AD28" s="13"/>
-      <c r="AF28" s="42" t="s">
+      <c r="AF28" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="AG28" s="42"/>
-      <c r="AH28" s="42"/>
-      <c r="AI28" s="42"/>
-      <c r="AJ28" s="42"/>
-      <c r="AK28" s="42"/>
-      <c r="AL28" s="42"/>
+      <c r="AG28" s="49"/>
+      <c r="AH28" s="49"/>
+      <c r="AI28" s="49"/>
+      <c r="AJ28" s="49"/>
+      <c r="AK28" s="49"/>
+      <c r="AL28" s="49"/>
       <c r="AN28" s="12"/>
       <c r="AU28" s="8">
         <v>2</v>
@@ -3096,11 +3099,11 @@
       <c r="G30" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="I30" s="43" t="s">
+      <c r="I30" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="J30" s="43"/>
-      <c r="K30" s="43"/>
+      <c r="J30" s="50"/>
+      <c r="K30" s="50"/>
       <c r="O30" s="12"/>
       <c r="P30" s="7">
         <v>1</v>
@@ -3147,11 +3150,11 @@
         <v>52</v>
       </c>
       <c r="AN30" s="12"/>
-      <c r="AQ30" s="43" t="s">
+      <c r="AQ30" s="50" t="s">
         <v>38</v>
       </c>
-      <c r="AR30" s="43"/>
-      <c r="AS30" s="43"/>
+      <c r="AR30" s="50"/>
+      <c r="AS30" s="50"/>
       <c r="AU30" s="38">
         <v>4</v>
       </c>
@@ -3312,12 +3315,18 @@
       <c r="AH32" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="AI32" s="13"/>
+      <c r="AI32" s="13">
+        <v>3</v>
+      </c>
       <c r="AJ32" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="AK32" s="13"/>
-      <c r="AL32" s="16"/>
+      <c r="AK32" s="13">
+        <v>5</v>
+      </c>
+      <c r="AL32" s="16" t="s">
+        <v>95</v>
+      </c>
       <c r="AN32" s="12"/>
       <c r="AQ32" s="12"/>
       <c r="AU32" s="8" t="s">
@@ -3411,15 +3420,15 @@
       <c r="BA33" s="6"/>
     </row>
     <row r="34" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="42" t="s">
+      <c r="A34" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="B34" s="42"/>
-      <c r="C34" s="42"/>
-      <c r="D34" s="42"/>
-      <c r="E34" s="42"/>
-      <c r="F34" s="42"/>
-      <c r="G34" s="42"/>
+      <c r="B34" s="49"/>
+      <c r="C34" s="49"/>
+      <c r="D34" s="49"/>
+      <c r="E34" s="49"/>
+      <c r="F34" s="49"/>
+      <c r="G34" s="49"/>
       <c r="L34" s="12"/>
       <c r="O34" s="12"/>
       <c r="P34" s="8" t="s">
@@ -3456,15 +3465,15 @@
       <c r="AL34" s="16"/>
       <c r="AN34" s="12"/>
       <c r="AQ34" s="12"/>
-      <c r="AU34" s="42" t="s">
+      <c r="AU34" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AV34" s="42"/>
-      <c r="AW34" s="42"/>
-      <c r="AX34" s="42"/>
-      <c r="AY34" s="42"/>
-      <c r="AZ34" s="42"/>
-      <c r="BA34" s="42"/>
+      <c r="AV34" s="49"/>
+      <c r="AW34" s="49"/>
+      <c r="AX34" s="49"/>
+      <c r="AY34" s="49"/>
+      <c r="AZ34" s="49"/>
+      <c r="BA34" s="49"/>
     </row>
     <row r="35" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L35" s="12"/>
@@ -3505,20 +3514,20 @@
       <c r="AQ35" s="12"/>
     </row>
     <row r="36" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="45" t="s">
+      <c r="A36" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="B36" s="45"/>
-      <c r="C36" s="45"/>
-      <c r="D36" s="45"/>
-      <c r="E36" s="45"/>
-      <c r="F36" s="45"/>
-      <c r="G36" s="45"/>
-      <c r="L36" s="44" t="s">
+      <c r="B36" s="48"/>
+      <c r="C36" s="48"/>
+      <c r="D36" s="48"/>
+      <c r="E36" s="48"/>
+      <c r="F36" s="48"/>
+      <c r="G36" s="48"/>
+      <c r="L36" s="54" t="s">
         <v>26</v>
       </c>
-      <c r="M36" s="43"/>
-      <c r="N36" s="43"/>
+      <c r="M36" s="50"/>
+      <c r="N36" s="50"/>
       <c r="O36" s="12"/>
       <c r="P36" s="8" t="s">
         <v>12</v>
@@ -3552,21 +3561,21 @@
       </c>
       <c r="AK36" s="36"/>
       <c r="AL36" s="37"/>
-      <c r="AN36" s="44" t="s">
+      <c r="AN36" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="AO36" s="43"/>
-      <c r="AP36" s="43"/>
+      <c r="AO36" s="50"/>
+      <c r="AP36" s="50"/>
       <c r="AQ36" s="12"/>
-      <c r="AU36" s="45" t="s">
+      <c r="AU36" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="AV36" s="45"/>
-      <c r="AW36" s="45"/>
-      <c r="AX36" s="45"/>
-      <c r="AY36" s="45"/>
-      <c r="AZ36" s="45"/>
-      <c r="BA36" s="45"/>
+      <c r="AV36" s="48"/>
+      <c r="AW36" s="48"/>
+      <c r="AX36" s="48"/>
+      <c r="AY36" s="48"/>
+      <c r="AZ36" s="48"/>
+      <c r="BA36" s="48"/>
     </row>
     <row r="37" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37" s="20" t="s">
@@ -3591,31 +3600,31 @@
         <v>9</v>
       </c>
       <c r="L37" s="12"/>
-      <c r="P37" s="56" t="s">
+      <c r="P37" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="Q37" s="57"/>
-      <c r="R37" s="57"/>
-      <c r="S37" s="57"/>
-      <c r="T37" s="57"/>
-      <c r="U37" s="57"/>
-      <c r="V37" s="58"/>
-      <c r="X37" s="44"/>
-      <c r="Y37" s="43"/>
-      <c r="Z37" s="43"/>
-      <c r="AA37" s="43"/>
-      <c r="AB37" s="43"/>
-      <c r="AC37" s="43"/>
-      <c r="AD37" s="49"/>
-      <c r="AF37" s="42" t="s">
+      <c r="Q37" s="46"/>
+      <c r="R37" s="46"/>
+      <c r="S37" s="46"/>
+      <c r="T37" s="46"/>
+      <c r="U37" s="46"/>
+      <c r="V37" s="47"/>
+      <c r="X37" s="54"/>
+      <c r="Y37" s="50"/>
+      <c r="Z37" s="50"/>
+      <c r="AA37" s="50"/>
+      <c r="AB37" s="50"/>
+      <c r="AC37" s="50"/>
+      <c r="AD37" s="58"/>
+      <c r="AF37" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AG37" s="42"/>
-      <c r="AH37" s="42"/>
-      <c r="AI37" s="42"/>
-      <c r="AJ37" s="42"/>
-      <c r="AK37" s="42"/>
-      <c r="AL37" s="42"/>
+      <c r="AG37" s="49"/>
+      <c r="AH37" s="49"/>
+      <c r="AI37" s="49"/>
+      <c r="AJ37" s="49"/>
+      <c r="AK37" s="49"/>
+      <c r="AL37" s="49"/>
       <c r="AQ37" s="12"/>
       <c r="AU37" s="3" t="s">
         <v>2</v>
@@ -3708,33 +3717,33 @@
         <v>53</v>
       </c>
       <c r="L39" s="12"/>
-      <c r="M39" s="53" t="s">
+      <c r="M39" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="N39" s="54"/>
-      <c r="O39" s="54"/>
-      <c r="P39" s="54"/>
-      <c r="Q39" s="54"/>
-      <c r="R39" s="54"/>
-      <c r="S39" s="55"/>
-      <c r="X39" s="42" t="s">
+      <c r="N39" s="43"/>
+      <c r="O39" s="43"/>
+      <c r="P39" s="43"/>
+      <c r="Q39" s="43"/>
+      <c r="R39" s="43"/>
+      <c r="S39" s="44"/>
+      <c r="X39" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="Y39" s="42"/>
-      <c r="Z39" s="42"/>
-      <c r="AA39" s="42"/>
-      <c r="AB39" s="42"/>
-      <c r="AC39" s="42"/>
-      <c r="AD39" s="42"/>
-      <c r="AI39" s="53" t="s">
+      <c r="Y39" s="49"/>
+      <c r="Z39" s="49"/>
+      <c r="AA39" s="49"/>
+      <c r="AB39" s="49"/>
+      <c r="AC39" s="49"/>
+      <c r="AD39" s="49"/>
+      <c r="AI39" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="AJ39" s="54"/>
-      <c r="AK39" s="54"/>
-      <c r="AL39" s="54"/>
-      <c r="AM39" s="54"/>
-      <c r="AN39" s="54"/>
-      <c r="AO39" s="55"/>
+      <c r="AJ39" s="43"/>
+      <c r="AK39" s="43"/>
+      <c r="AL39" s="43"/>
+      <c r="AM39" s="43"/>
+      <c r="AN39" s="43"/>
+      <c r="AO39" s="44"/>
       <c r="AQ39" s="12"/>
       <c r="AU39" s="8">
         <v>2</v>
@@ -3889,11 +3898,11 @@
       <c r="G41" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="I41" s="43" t="s">
+      <c r="I41" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="J41" s="43"/>
-      <c r="K41" s="43"/>
+      <c r="J41" s="50"/>
+      <c r="K41" s="50"/>
       <c r="L41" s="12"/>
       <c r="M41" s="7">
         <v>1</v>
@@ -3946,11 +3955,11 @@
       <c r="AO41" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="AQ41" s="44" t="s">
+      <c r="AQ41" s="54" t="s">
         <v>23</v>
       </c>
-      <c r="AR41" s="43"/>
-      <c r="AS41" s="43"/>
+      <c r="AR41" s="50"/>
+      <c r="AS41" s="50"/>
       <c r="AU41" s="38">
         <v>4</v>
       </c>
@@ -4256,15 +4265,15 @@
       <c r="BA44" s="6"/>
     </row>
     <row r="45" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="42" t="s">
+      <c r="A45" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="B45" s="42"/>
-      <c r="C45" s="42"/>
-      <c r="D45" s="42"/>
-      <c r="E45" s="42"/>
-      <c r="F45" s="42"/>
-      <c r="G45" s="42"/>
+      <c r="B45" s="49"/>
+      <c r="C45" s="49"/>
+      <c r="D45" s="49"/>
+      <c r="E45" s="49"/>
+      <c r="F45" s="49"/>
+      <c r="G45" s="49"/>
       <c r="M45" s="8" t="s">
         <v>11</v>
       </c>
@@ -4313,15 +4322,15 @@
       <c r="AP45" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AU45" s="42" t="s">
+      <c r="AU45" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AV45" s="42"/>
-      <c r="AW45" s="42"/>
-      <c r="AX45" s="42"/>
-      <c r="AY45" s="42"/>
-      <c r="AZ45" s="42"/>
-      <c r="BA45" s="42"/>
+      <c r="AV45" s="49"/>
+      <c r="AW45" s="49"/>
+      <c r="AX45" s="49"/>
+      <c r="AY45" s="49"/>
+      <c r="AZ45" s="49"/>
+      <c r="BA45" s="49"/>
     </row>
     <row r="46" spans="1:54" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="M46" s="8" t="s">
@@ -4412,45 +4421,65 @@
       <c r="AO47" s="6"/>
     </row>
     <row r="48" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="M48" s="53" t="s">
+      <c r="M48" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="N48" s="54"/>
-      <c r="O48" s="54"/>
-      <c r="P48" s="54"/>
-      <c r="Q48" s="54"/>
-      <c r="R48" s="54"/>
-      <c r="S48" s="55"/>
-      <c r="X48" s="42" t="s">
+      <c r="N48" s="43"/>
+      <c r="O48" s="43"/>
+      <c r="P48" s="43"/>
+      <c r="Q48" s="43"/>
+      <c r="R48" s="43"/>
+      <c r="S48" s="44"/>
+      <c r="X48" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="Y48" s="42"/>
-      <c r="Z48" s="42"/>
-      <c r="AA48" s="42"/>
-      <c r="AB48" s="42"/>
-      <c r="AC48" s="42"/>
-      <c r="AD48" s="42"/>
-      <c r="AI48" s="42" t="s">
+      <c r="Y48" s="49"/>
+      <c r="Z48" s="49"/>
+      <c r="AA48" s="49"/>
+      <c r="AB48" s="49"/>
+      <c r="AC48" s="49"/>
+      <c r="AD48" s="49"/>
+      <c r="AI48" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AJ48" s="42"/>
-      <c r="AK48" s="42"/>
-      <c r="AL48" s="42"/>
-      <c r="AM48" s="42"/>
-      <c r="AN48" s="42"/>
-      <c r="AO48" s="42"/>
+      <c r="AJ48" s="49"/>
+      <c r="AK48" s="49"/>
+      <c r="AL48" s="49"/>
+      <c r="AM48" s="49"/>
+      <c r="AN48" s="49"/>
+      <c r="AO48" s="49"/>
     </row>
     <row r="49" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="M48:S48"/>
-    <mergeCell ref="M39:S39"/>
-    <mergeCell ref="P37:V37"/>
-    <mergeCell ref="P28:V28"/>
-    <mergeCell ref="A36:G36"/>
-    <mergeCell ref="A45:G45"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="AU45:BA45"/>
+    <mergeCell ref="AF28:AL28"/>
+    <mergeCell ref="AF37:AL37"/>
+    <mergeCell ref="AQ30:AS30"/>
+    <mergeCell ref="AQ41:AS41"/>
+    <mergeCell ref="AU34:BA34"/>
+    <mergeCell ref="AU36:BA36"/>
+    <mergeCell ref="AU2:BA2"/>
+    <mergeCell ref="AU3:BA3"/>
+    <mergeCell ref="AU12:BA12"/>
+    <mergeCell ref="AU14:BA14"/>
+    <mergeCell ref="AU23:BA23"/>
+    <mergeCell ref="X37:AD37"/>
+    <mergeCell ref="AE26:AM26"/>
+    <mergeCell ref="Z1:AB1"/>
+    <mergeCell ref="X39:AD39"/>
+    <mergeCell ref="X48:AD48"/>
+    <mergeCell ref="AF1:BA1"/>
+    <mergeCell ref="AI2:AO2"/>
+    <mergeCell ref="AI3:AO3"/>
+    <mergeCell ref="AI12:AO12"/>
+    <mergeCell ref="AI39:AO39"/>
+    <mergeCell ref="AU25:BA25"/>
+    <mergeCell ref="AI48:AO48"/>
+    <mergeCell ref="AN14:AP14"/>
+    <mergeCell ref="AN36:AP36"/>
+    <mergeCell ref="AQ8:AS8"/>
+    <mergeCell ref="AQ19:AS19"/>
     <mergeCell ref="A1:U1"/>
     <mergeCell ref="O26:W26"/>
     <mergeCell ref="I41:K41"/>
@@ -4467,34 +4496,14 @@
     <mergeCell ref="I8:K8"/>
     <mergeCell ref="I19:K19"/>
     <mergeCell ref="A25:G25"/>
-    <mergeCell ref="X37:AD37"/>
-    <mergeCell ref="AE26:AM26"/>
-    <mergeCell ref="Z1:AB1"/>
-    <mergeCell ref="X39:AD39"/>
-    <mergeCell ref="X48:AD48"/>
-    <mergeCell ref="AF1:BA1"/>
-    <mergeCell ref="AI2:AO2"/>
-    <mergeCell ref="AI3:AO3"/>
-    <mergeCell ref="AI12:AO12"/>
-    <mergeCell ref="AI39:AO39"/>
-    <mergeCell ref="AU25:BA25"/>
-    <mergeCell ref="AI48:AO48"/>
-    <mergeCell ref="AN14:AP14"/>
-    <mergeCell ref="AN36:AP36"/>
-    <mergeCell ref="AQ8:AS8"/>
-    <mergeCell ref="AQ19:AS19"/>
-    <mergeCell ref="AU2:BA2"/>
-    <mergeCell ref="AU3:BA3"/>
-    <mergeCell ref="AU12:BA12"/>
-    <mergeCell ref="AU14:BA14"/>
-    <mergeCell ref="AU23:BA23"/>
-    <mergeCell ref="AU45:BA45"/>
-    <mergeCell ref="AF28:AL28"/>
-    <mergeCell ref="AF37:AL37"/>
-    <mergeCell ref="AQ30:AS30"/>
-    <mergeCell ref="AQ41:AS41"/>
-    <mergeCell ref="AU34:BA34"/>
-    <mergeCell ref="AU36:BA36"/>
+    <mergeCell ref="M48:S48"/>
+    <mergeCell ref="M39:S39"/>
+    <mergeCell ref="P37:V37"/>
+    <mergeCell ref="P28:V28"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="A34:G34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/2025_2026/Playoffs/Brackets.xlsx
+++ b/2025_2026/Playoffs/Brackets.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\NHLStats\2025_2026\Playoffs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A043C336-6EC7-4B2C-96F1-9BAF76A87790}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2B1DA5E-BDF2-482E-A38C-270B347717DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="1590" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Matchups" sheetId="3" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="98">
   <si>
     <t>Eastern Conference Playoff Teams</t>
   </si>
@@ -314,6 +314,12 @@
   </si>
   <si>
     <t>Golden Knights Lead 3-0</t>
+  </si>
+  <si>
+    <t>Hurricanes Lead 2-1</t>
+  </si>
+  <si>
+    <t>Golden Knights Win Series 4-0</t>
   </si>
 </sst>
 </file>
@@ -692,6 +698,39 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -710,46 +749,13 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1033,19 +1039,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J55"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="31.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.7109375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="31.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.6640625" style="1" customWidth="1"/>
     <col min="4" max="4" width="29" style="1" customWidth="1"/>
-    <col min="5" max="5" width="24.28515625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="26.140625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="37.42578125" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="1"/>
+    <col min="5" max="5" width="24.33203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="26.109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="37.44140625" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1053,7 +1059,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>24</v>
       </c>
@@ -1061,7 +1067,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>25</v>
       </c>
@@ -1069,7 +1075,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>26</v>
       </c>
@@ -1077,7 +1083,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>32</v>
       </c>
@@ -1085,7 +1091,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>33</v>
       </c>
@@ -1093,7 +1099,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>34</v>
       </c>
@@ -1101,7 +1107,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>35</v>
       </c>
@@ -1109,7 +1115,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>36</v>
       </c>
@@ -1117,25 +1123,25 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="11" spans="1:7" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="61" t="s">
+    <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="11" spans="1:7" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="59" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="61"/>
-      <c r="C11" s="61" t="s">
+      <c r="B11" s="59"/>
+      <c r="C11" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="61"/>
-      <c r="E11" s="61" t="s">
+      <c r="D11" s="59"/>
+      <c r="E11" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="61"/>
+      <c r="F11" s="59"/>
       <c r="G11" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="4" t="s">
         <v>4</v>
       </c>
@@ -1158,22 +1164,22 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="59" t="s">
+    <row r="13" spans="1:7" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="60" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="60"/>
-      <c r="C13" s="59" t="s">
+      <c r="B13" s="61"/>
+      <c r="C13" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="D13" s="60"/>
-      <c r="E13" s="59" t="s">
+      <c r="D13" s="61"/>
+      <c r="E13" s="60" t="s">
         <v>17</v>
       </c>
-      <c r="F13" s="60"/>
+      <c r="F13" s="61"/>
       <c r="G13" s="5"/>
     </row>
-    <row r="14" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
         <v>25</v>
       </c>
@@ -1192,9 +1198,11 @@
       <c r="F14" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="G14" s="6"/>
-    </row>
-    <row r="15" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G14" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
         <v>24</v>
       </c>
@@ -1214,17 +1222,17 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="59" t="s">
+    <row r="16" spans="1:7" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="60"/>
-      <c r="C16" s="59" t="s">
+      <c r="B16" s="61"/>
+      <c r="C16" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="60"/>
-    </row>
-    <row r="17" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="D16" s="61"/>
+    </row>
+    <row r="17" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>36</v>
       </c>
@@ -1238,7 +1246,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="6" t="s">
         <v>32</v>
       </c>
@@ -1252,13 +1260,13 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="59" t="s">
+    <row r="19" spans="1:4" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="60" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="60"/>
-    </row>
-    <row r="20" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="61"/>
+    </row>
+    <row r="20" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>26</v>
       </c>
@@ -1266,7 +1274,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="6" t="s">
         <v>33</v>
       </c>
@@ -1274,13 +1282,13 @@
         <v>37</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="59" t="s">
+    <row r="22" spans="1:4" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="60"/>
-    </row>
-    <row r="23" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="61"/>
+    </row>
+    <row r="23" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>35</v>
       </c>
@@ -1288,7 +1296,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="6" t="s">
         <v>34</v>
       </c>
@@ -1296,64 +1304,64 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
-    <row r="39" spans="7:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="39" spans="7:10" x14ac:dyDescent="0.3">
       <c r="J39" s="2"/>
     </row>
-    <row r="40" spans="7:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="7:10" x14ac:dyDescent="0.3">
       <c r="J40" s="2"/>
     </row>
-    <row r="41" spans="7:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="7:10" x14ac:dyDescent="0.3">
       <c r="J41" s="2"/>
     </row>
-    <row r="42" spans="7:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="7:10" x14ac:dyDescent="0.3">
       <c r="J42" s="2"/>
     </row>
-    <row r="43" spans="7:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="7:10" x14ac:dyDescent="0.3">
       <c r="J43" s="2"/>
     </row>
-    <row r="44" spans="7:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="7:10" x14ac:dyDescent="0.3">
       <c r="H44" s="2"/>
       <c r="J44" s="2"/>
     </row>
-    <row r="45" spans="7:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="7:10" x14ac:dyDescent="0.3">
       <c r="H45" s="2"/>
       <c r="J45" s="2"/>
     </row>
-    <row r="46" spans="7:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="7:10" x14ac:dyDescent="0.3">
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
       <c r="J46" s="2"/>
     </row>
-    <row r="48" spans="7:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="7:10" x14ac:dyDescent="0.3">
       <c r="J48" s="2"/>
     </row>
-    <row r="49" spans="7:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="7:10" x14ac:dyDescent="0.3">
       <c r="H49" s="2"/>
       <c r="J49" s="2"/>
     </row>
-    <row r="50" spans="7:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="7:10" x14ac:dyDescent="0.3">
       <c r="J50" s="2"/>
     </row>
-    <row r="51" spans="7:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="7:10" x14ac:dyDescent="0.3">
       <c r="G51" s="2"/>
       <c r="J51" s="2"/>
     </row>
-    <row r="52" spans="7:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="7:10" x14ac:dyDescent="0.3">
       <c r="G52" s="2"/>
       <c r="H52" s="2"/>
       <c r="J52" s="2"/>
     </row>
-    <row r="53" spans="7:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="7:10" x14ac:dyDescent="0.3">
       <c r="G53" s="2"/>
       <c r="J53" s="2"/>
     </row>
-    <row r="54" spans="7:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="7:10" x14ac:dyDescent="0.3">
       <c r="G54" s="2"/>
       <c r="H54" s="2"/>
       <c r="J54" s="2"/>
     </row>
-    <row r="55" spans="7:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="7:10" x14ac:dyDescent="0.3">
       <c r="G55" s="2"/>
       <c r="H55" s="2"/>
       <c r="J55" s="2"/>
@@ -1363,16 +1371,16 @@
     <sortCondition ref="B2:B9"/>
   </sortState>
   <mergeCells count="10">
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C16:D16"/>
     <mergeCell ref="E11:F11"/>
     <mergeCell ref="E13:F13"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C16:D16"/>
   </mergeCells>
   <dataValidations count="16">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C14" xr:uid="{2C3D9587-ABAE-4E3F-8B22-396DF812BF02}">
@@ -1432,170 +1440,170 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:BB49"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="1"/>
-    <col min="2" max="2" width="12.7109375" style="19" customWidth="1"/>
-    <col min="3" max="3" width="28.5703125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" style="1"/>
-    <col min="5" max="5" width="22.5703125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" style="1"/>
-    <col min="7" max="7" width="30.5703125" style="1" customWidth="1"/>
-    <col min="8" max="13" width="9.140625" style="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="9.109375" style="1"/>
+    <col min="2" max="2" width="12.6640625" style="19" customWidth="1"/>
+    <col min="3" max="3" width="28.5546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" style="1"/>
+    <col min="5" max="5" width="22.5546875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9.109375" style="1"/>
+    <col min="7" max="7" width="30.5546875" style="1" customWidth="1"/>
+    <col min="8" max="13" width="9.109375" style="1"/>
+    <col min="14" max="14" width="14.88671875" style="1" customWidth="1"/>
     <col min="15" max="15" width="26" style="1" customWidth="1"/>
     <col min="16" max="16" width="17" style="1" customWidth="1"/>
-    <col min="17" max="17" width="20.140625" style="1" customWidth="1"/>
-    <col min="18" max="18" width="20.28515625" style="1" customWidth="1"/>
-    <col min="19" max="19" width="24.7109375" style="1" customWidth="1"/>
-    <col min="20" max="20" width="23.42578125" style="1" customWidth="1"/>
-    <col min="21" max="21" width="9.140625" style="1"/>
+    <col min="17" max="17" width="20.109375" style="1" customWidth="1"/>
+    <col min="18" max="18" width="20.33203125" style="1" customWidth="1"/>
+    <col min="19" max="19" width="24.6640625" style="1" customWidth="1"/>
+    <col min="20" max="20" width="23.44140625" style="1" customWidth="1"/>
+    <col min="21" max="21" width="9.109375" style="1"/>
     <col min="22" max="22" width="26" style="1" customWidth="1"/>
-    <col min="23" max="23" width="9.140625" style="1"/>
-    <col min="24" max="24" width="21.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="28" width="21.42578125" style="1" customWidth="1"/>
-    <col min="29" max="29" width="9.140625" style="1"/>
-    <col min="30" max="30" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="9.140625" style="1"/>
-    <col min="33" max="33" width="23.7109375" style="1" customWidth="1"/>
-    <col min="34" max="34" width="22.85546875" style="1" customWidth="1"/>
-    <col min="35" max="36" width="21.7109375" style="1" customWidth="1"/>
-    <col min="37" max="37" width="22.28515625" style="1" customWidth="1"/>
-    <col min="38" max="38" width="25.85546875" style="1" customWidth="1"/>
-    <col min="39" max="39" width="22.140625" style="1" customWidth="1"/>
-    <col min="40" max="40" width="9.140625" style="1"/>
-    <col min="41" max="41" width="29.42578125" style="1" customWidth="1"/>
-    <col min="42" max="47" width="9.140625" style="1"/>
-    <col min="48" max="48" width="10.28515625" style="1" customWidth="1"/>
-    <col min="49" max="49" width="23.140625" style="1" customWidth="1"/>
-    <col min="50" max="50" width="9.140625" style="1"/>
-    <col min="51" max="51" width="23.140625" style="1" customWidth="1"/>
-    <col min="52" max="52" width="9.140625" style="1"/>
-    <col min="53" max="53" width="29.28515625" style="1" customWidth="1"/>
-    <col min="54" max="16384" width="9.140625" style="1"/>
+    <col min="23" max="23" width="9.109375" style="1"/>
+    <col min="24" max="24" width="21.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="28" width="21.44140625" style="1" customWidth="1"/>
+    <col min="29" max="29" width="9.109375" style="1"/>
+    <col min="30" max="30" width="22.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="9.109375" style="1"/>
+    <col min="33" max="33" width="23.6640625" style="1" customWidth="1"/>
+    <col min="34" max="34" width="22.88671875" style="1" customWidth="1"/>
+    <col min="35" max="36" width="21.6640625" style="1" customWidth="1"/>
+    <col min="37" max="37" width="22.33203125" style="1" customWidth="1"/>
+    <col min="38" max="38" width="29.21875" style="1" customWidth="1"/>
+    <col min="39" max="39" width="22.109375" style="1" customWidth="1"/>
+    <col min="40" max="40" width="9.109375" style="1"/>
+    <col min="41" max="41" width="29.44140625" style="1" customWidth="1"/>
+    <col min="42" max="47" width="9.109375" style="1"/>
+    <col min="48" max="48" width="10.33203125" style="1" customWidth="1"/>
+    <col min="49" max="49" width="23.109375" style="1" customWidth="1"/>
+    <col min="50" max="50" width="9.109375" style="1"/>
+    <col min="51" max="51" width="23.109375" style="1" customWidth="1"/>
+    <col min="52" max="52" width="9.109375" style="1"/>
+    <col min="53" max="53" width="29.33203125" style="1" customWidth="1"/>
+    <col min="54" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:54" ht="27.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="51" t="s">
+    <row r="1" spans="1:54" ht="27" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
-      <c r="M1" s="52"/>
-      <c r="N1" s="52"/>
-      <c r="O1" s="52"/>
-      <c r="P1" s="52"/>
-      <c r="Q1" s="52"/>
-      <c r="R1" s="52"/>
-      <c r="S1" s="52"/>
-      <c r="T1" s="52"/>
-      <c r="U1" s="53"/>
-      <c r="Z1" s="51" t="s">
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
+      <c r="K1" s="51"/>
+      <c r="L1" s="51"/>
+      <c r="M1" s="51"/>
+      <c r="N1" s="51"/>
+      <c r="O1" s="51"/>
+      <c r="P1" s="51"/>
+      <c r="Q1" s="51"/>
+      <c r="R1" s="51"/>
+      <c r="S1" s="51"/>
+      <c r="T1" s="51"/>
+      <c r="U1" s="52"/>
+      <c r="Z1" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="AA1" s="52"/>
-      <c r="AB1" s="53"/>
-      <c r="AF1" s="51" t="s">
+      <c r="AA1" s="51"/>
+      <c r="AB1" s="52"/>
+      <c r="AF1" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="AG1" s="52"/>
-      <c r="AH1" s="52"/>
-      <c r="AI1" s="52"/>
-      <c r="AJ1" s="52"/>
-      <c r="AK1" s="52"/>
-      <c r="AL1" s="52"/>
-      <c r="AM1" s="52"/>
-      <c r="AN1" s="52"/>
-      <c r="AO1" s="52"/>
-      <c r="AP1" s="52"/>
-      <c r="AQ1" s="52"/>
-      <c r="AR1" s="52"/>
-      <c r="AS1" s="52"/>
-      <c r="AT1" s="52"/>
-      <c r="AU1" s="52"/>
-      <c r="AV1" s="52"/>
-      <c r="AW1" s="52"/>
-      <c r="AX1" s="52"/>
-      <c r="AY1" s="52"/>
-      <c r="AZ1" s="52"/>
-      <c r="BA1" s="53"/>
-    </row>
-    <row r="2" spans="1:54" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="55" t="s">
+      <c r="AG1" s="51"/>
+      <c r="AH1" s="51"/>
+      <c r="AI1" s="51"/>
+      <c r="AJ1" s="51"/>
+      <c r="AK1" s="51"/>
+      <c r="AL1" s="51"/>
+      <c r="AM1" s="51"/>
+      <c r="AN1" s="51"/>
+      <c r="AO1" s="51"/>
+      <c r="AP1" s="51"/>
+      <c r="AQ1" s="51"/>
+      <c r="AR1" s="51"/>
+      <c r="AS1" s="51"/>
+      <c r="AT1" s="51"/>
+      <c r="AU1" s="51"/>
+      <c r="AV1" s="51"/>
+      <c r="AW1" s="51"/>
+      <c r="AX1" s="51"/>
+      <c r="AY1" s="51"/>
+      <c r="AZ1" s="51"/>
+      <c r="BA1" s="52"/>
+    </row>
+    <row r="2" spans="1:54" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="57"/>
-      <c r="M2" s="55" t="s">
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="48"/>
+      <c r="M2" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="56"/>
-      <c r="O2" s="56"/>
-      <c r="P2" s="56"/>
-      <c r="Q2" s="56"/>
-      <c r="R2" s="57"/>
-      <c r="AI2" s="55" t="s">
+      <c r="N2" s="47"/>
+      <c r="O2" s="47"/>
+      <c r="P2" s="47"/>
+      <c r="Q2" s="47"/>
+      <c r="R2" s="48"/>
+      <c r="AI2" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="AJ2" s="56"/>
-      <c r="AK2" s="56"/>
-      <c r="AL2" s="56"/>
-      <c r="AM2" s="56"/>
-      <c r="AN2" s="56"/>
-      <c r="AO2" s="57"/>
-      <c r="AU2" s="55" t="s">
+      <c r="AJ2" s="47"/>
+      <c r="AK2" s="47"/>
+      <c r="AL2" s="47"/>
+      <c r="AM2" s="47"/>
+      <c r="AN2" s="47"/>
+      <c r="AO2" s="48"/>
+      <c r="AU2" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="AV2" s="56"/>
-      <c r="AW2" s="56"/>
-      <c r="AX2" s="56"/>
-      <c r="AY2" s="56"/>
-      <c r="AZ2" s="56"/>
-      <c r="BA2" s="57"/>
-    </row>
-    <row r="3" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="49" t="s">
+      <c r="AV2" s="47"/>
+      <c r="AW2" s="47"/>
+      <c r="AX2" s="47"/>
+      <c r="AY2" s="47"/>
+      <c r="AZ2" s="47"/>
+      <c r="BA2" s="48"/>
+    </row>
+    <row r="3" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="49"/>
-      <c r="C3" s="49"/>
-      <c r="D3" s="49"/>
-      <c r="E3" s="49"/>
-      <c r="F3" s="49"/>
-      <c r="G3" s="49"/>
-      <c r="AI3" s="42" t="s">
+      <c r="B3" s="42"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="42"/>
+      <c r="AI3" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="AJ3" s="43"/>
-      <c r="AK3" s="43"/>
-      <c r="AL3" s="43"/>
-      <c r="AM3" s="43"/>
-      <c r="AN3" s="43"/>
-      <c r="AO3" s="44"/>
-      <c r="AU3" s="49" t="s">
+      <c r="AJ3" s="54"/>
+      <c r="AK3" s="54"/>
+      <c r="AL3" s="54"/>
+      <c r="AM3" s="54"/>
+      <c r="AN3" s="54"/>
+      <c r="AO3" s="55"/>
+      <c r="AU3" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="AV3" s="49"/>
-      <c r="AW3" s="49"/>
-      <c r="AX3" s="49"/>
-      <c r="AY3" s="49"/>
-      <c r="AZ3" s="49"/>
-      <c r="BA3" s="49"/>
-    </row>
-    <row r="4" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="AV3" s="42"/>
+      <c r="AW3" s="42"/>
+      <c r="AX3" s="42"/>
+      <c r="AY3" s="42"/>
+      <c r="AZ3" s="42"/>
+      <c r="BA3" s="42"/>
+    </row>
+    <row r="4" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
@@ -1617,15 +1625,15 @@
       <c r="G4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="42" t="s">
+      <c r="M4" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="N4" s="43"/>
-      <c r="O4" s="43"/>
-      <c r="P4" s="43"/>
-      <c r="Q4" s="43"/>
-      <c r="R4" s="43"/>
-      <c r="S4" s="44"/>
+      <c r="N4" s="54"/>
+      <c r="O4" s="54"/>
+      <c r="P4" s="54"/>
+      <c r="Q4" s="54"/>
+      <c r="R4" s="54"/>
+      <c r="S4" s="55"/>
       <c r="AI4" s="3" t="s">
         <v>2</v>
       </c>
@@ -1669,7 +1677,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="7">
         <v>1</v>
       </c>
@@ -1755,7 +1763,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:54" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:54" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
         <v>2</v>
       </c>
@@ -1844,7 +1852,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A7" s="8">
         <v>3</v>
       </c>
@@ -1930,7 +1938,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="8" spans="1:54" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:54" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="8">
         <v>4</v>
       </c>
@@ -1952,11 +1960,11 @@
       <c r="G8" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="I8" s="50" t="s">
+      <c r="I8" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="J8" s="50"/>
-      <c r="K8" s="50"/>
+      <c r="J8" s="43"/>
+      <c r="K8" s="43"/>
       <c r="M8" s="8">
         <v>3</v>
       </c>
@@ -1999,11 +2007,11 @@
       <c r="AO8" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="AQ8" s="50" t="s">
+      <c r="AQ8" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="AR8" s="50"/>
-      <c r="AS8" s="50"/>
+      <c r="AR8" s="43"/>
+      <c r="AS8" s="43"/>
       <c r="AU8" s="38">
         <v>4</v>
       </c>
@@ -2026,7 +2034,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="9" spans="1:54" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:54" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
         <v>11</v>
       </c>
@@ -2116,7 +2124,7 @@
       <c r="AZ9" s="13"/>
       <c r="BA9" s="32"/>
     </row>
-    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
         <v>10</v>
       </c>
@@ -2192,7 +2200,7 @@
       <c r="AZ10" s="13"/>
       <c r="BA10" s="16"/>
     </row>
-    <row r="11" spans="1:54" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="9" t="s">
         <v>12</v>
       </c>
@@ -2262,16 +2270,16 @@
       <c r="AZ11" s="15"/>
       <c r="BA11" s="6"/>
     </row>
-    <row r="12" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="49" t="s">
+    <row r="12" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="49"/>
-      <c r="C12" s="49"/>
-      <c r="D12" s="49"/>
-      <c r="E12" s="49"/>
-      <c r="F12" s="49"/>
-      <c r="G12" s="49"/>
+      <c r="B12" s="42"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="42"/>
       <c r="L12" s="12"/>
       <c r="M12" s="8" t="s">
         <v>12</v>
@@ -2297,71 +2305,71 @@
       <c r="T12" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AI12" s="49" t="s">
+      <c r="AI12" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AJ12" s="49"/>
-      <c r="AK12" s="49"/>
-      <c r="AL12" s="49"/>
-      <c r="AM12" s="49"/>
-      <c r="AN12" s="49"/>
-      <c r="AO12" s="49"/>
+      <c r="AJ12" s="42"/>
+      <c r="AK12" s="42"/>
+      <c r="AL12" s="42"/>
+      <c r="AM12" s="42"/>
+      <c r="AN12" s="42"/>
+      <c r="AO12" s="42"/>
       <c r="AQ12" s="12"/>
-      <c r="AU12" s="49" t="s">
+      <c r="AU12" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AV12" s="49"/>
-      <c r="AW12" s="49"/>
-      <c r="AX12" s="49"/>
-      <c r="AY12" s="49"/>
-      <c r="AZ12" s="49"/>
-      <c r="BA12" s="49"/>
-    </row>
-    <row r="13" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="AV12" s="42"/>
+      <c r="AW12" s="42"/>
+      <c r="AX12" s="42"/>
+      <c r="AY12" s="42"/>
+      <c r="AZ12" s="42"/>
+      <c r="BA12" s="42"/>
+    </row>
+    <row r="13" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="L13" s="12"/>
-      <c r="M13" s="42" t="s">
+      <c r="M13" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="N13" s="43"/>
-      <c r="O13" s="43"/>
-      <c r="P13" s="43"/>
-      <c r="Q13" s="43"/>
-      <c r="R13" s="43"/>
-      <c r="S13" s="44"/>
+      <c r="N13" s="54"/>
+      <c r="O13" s="54"/>
+      <c r="P13" s="54"/>
+      <c r="Q13" s="54"/>
+      <c r="R13" s="54"/>
+      <c r="S13" s="55"/>
       <c r="AQ13" s="12"/>
     </row>
-    <row r="14" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="48" t="s">
+    <row r="14" spans="1:54" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="48"/>
-      <c r="C14" s="48"/>
-      <c r="D14" s="48"/>
-      <c r="E14" s="48"/>
-      <c r="F14" s="48"/>
-      <c r="G14" s="48"/>
-      <c r="L14" s="54" t="s">
+      <c r="B14" s="45"/>
+      <c r="C14" s="45"/>
+      <c r="D14" s="45"/>
+      <c r="E14" s="45"/>
+      <c r="F14" s="45"/>
+      <c r="G14" s="45"/>
+      <c r="L14" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="M14" s="50"/>
-      <c r="N14" s="50"/>
-      <c r="AN14" s="50" t="s">
+      <c r="M14" s="43"/>
+      <c r="N14" s="43"/>
+      <c r="AN14" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="AO14" s="50"/>
-      <c r="AP14" s="50"/>
+      <c r="AO14" s="43"/>
+      <c r="AP14" s="43"/>
       <c r="AQ14" s="12"/>
-      <c r="AU14" s="48" t="s">
+      <c r="AU14" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="AV14" s="48"/>
-      <c r="AW14" s="48"/>
-      <c r="AX14" s="48"/>
-      <c r="AY14" s="48"/>
-      <c r="AZ14" s="48"/>
-      <c r="BA14" s="48"/>
-    </row>
-    <row r="15" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="AV14" s="45"/>
+      <c r="AW14" s="45"/>
+      <c r="AX14" s="45"/>
+      <c r="AY14" s="45"/>
+      <c r="AZ14" s="45"/>
+      <c r="BA14" s="45"/>
+    </row>
+    <row r="15" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>2</v>
       </c>
@@ -2409,7 +2417,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:54" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:54" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7">
         <v>1</v>
       </c>
@@ -2460,7 +2468,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A17" s="8">
         <v>2</v>
       </c>
@@ -2511,7 +2519,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="18" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A18" s="8">
         <v>3</v>
       </c>
@@ -2565,7 +2573,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="19" spans="1:54" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:54" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A19" s="8">
         <v>4</v>
       </c>
@@ -2587,19 +2595,19 @@
       <c r="G19" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="I19" s="50" t="s">
+      <c r="I19" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="J19" s="50"/>
-      <c r="K19" s="50"/>
+      <c r="J19" s="43"/>
+      <c r="K19" s="43"/>
       <c r="L19" s="12"/>
       <c r="O19" s="12"/>
       <c r="AN19" s="12"/>
-      <c r="AQ19" s="54" t="s">
+      <c r="AQ19" s="44" t="s">
         <v>31</v>
       </c>
-      <c r="AR19" s="50"/>
-      <c r="AS19" s="50"/>
+      <c r="AR19" s="43"/>
+      <c r="AS19" s="43"/>
       <c r="AU19" s="38">
         <v>4</v>
       </c>
@@ -2625,7 +2633,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="20" spans="1:54" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:54" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
         <v>11</v>
       </c>
@@ -2671,7 +2679,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
         <v>10</v>
       </c>
@@ -2720,7 +2728,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="22" spans="1:54" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="9" t="s">
         <v>12</v>
       </c>
@@ -2760,55 +2768,55 @@
       <c r="AZ22" s="15"/>
       <c r="BA22" s="6"/>
     </row>
-    <row r="23" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="49" t="s">
+    <row r="23" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B23" s="49"/>
-      <c r="C23" s="49"/>
-      <c r="D23" s="49"/>
-      <c r="E23" s="49"/>
-      <c r="F23" s="49"/>
-      <c r="G23" s="49"/>
+      <c r="B23" s="42"/>
+      <c r="C23" s="42"/>
+      <c r="D23" s="42"/>
+      <c r="E23" s="42"/>
+      <c r="F23" s="42"/>
+      <c r="G23" s="42"/>
       <c r="O23" s="12"/>
       <c r="AN23" s="12"/>
-      <c r="AU23" s="49" t="s">
+      <c r="AU23" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AV23" s="49"/>
-      <c r="AW23" s="49"/>
-      <c r="AX23" s="49"/>
-      <c r="AY23" s="49"/>
-      <c r="AZ23" s="49"/>
-      <c r="BA23" s="49"/>
-    </row>
-    <row r="24" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="AV23" s="42"/>
+      <c r="AW23" s="42"/>
+      <c r="AX23" s="42"/>
+      <c r="AY23" s="42"/>
+      <c r="AZ23" s="42"/>
+      <c r="BA23" s="42"/>
+    </row>
+    <row r="24" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="O24" s="12"/>
       <c r="AN24" s="12"/>
     </row>
-    <row r="25" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="49" t="s">
+    <row r="25" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="49"/>
-      <c r="C25" s="49"/>
-      <c r="D25" s="49"/>
-      <c r="E25" s="49"/>
-      <c r="F25" s="49"/>
-      <c r="G25" s="49"/>
+      <c r="B25" s="42"/>
+      <c r="C25" s="42"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="42"/>
+      <c r="F25" s="42"/>
+      <c r="G25" s="42"/>
       <c r="O25" s="12"/>
       <c r="AN25" s="12"/>
-      <c r="AU25" s="49" t="s">
+      <c r="AU25" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="AV25" s="49"/>
-      <c r="AW25" s="49"/>
-      <c r="AX25" s="49"/>
-      <c r="AY25" s="49"/>
-      <c r="AZ25" s="49"/>
-      <c r="BA25" s="49"/>
-    </row>
-    <row r="26" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AV25" s="42"/>
+      <c r="AW25" s="42"/>
+      <c r="AX25" s="42"/>
+      <c r="AY25" s="42"/>
+      <c r="AZ25" s="42"/>
+      <c r="BA25" s="42"/>
+    </row>
+    <row r="26" spans="1:54" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A26" s="20" t="s">
         <v>2</v>
       </c>
@@ -2830,24 +2838,26 @@
       <c r="G26" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="O26" s="54"/>
-      <c r="P26" s="50"/>
-      <c r="Q26" s="50"/>
-      <c r="R26" s="50"/>
-      <c r="S26" s="50"/>
-      <c r="T26" s="50"/>
-      <c r="U26" s="50"/>
-      <c r="V26" s="50"/>
-      <c r="W26" s="50"/>
-      <c r="AE26" s="50"/>
-      <c r="AF26" s="50"/>
-      <c r="AG26" s="50"/>
-      <c r="AH26" s="50"/>
-      <c r="AI26" s="50"/>
-      <c r="AJ26" s="50"/>
-      <c r="AK26" s="50"/>
-      <c r="AL26" s="50"/>
-      <c r="AM26" s="58"/>
+      <c r="O26" s="44"/>
+      <c r="P26" s="43"/>
+      <c r="Q26" s="43"/>
+      <c r="R26" s="43"/>
+      <c r="S26" s="43"/>
+      <c r="T26" s="43"/>
+      <c r="U26" s="43"/>
+      <c r="V26" s="43"/>
+      <c r="W26" s="43"/>
+      <c r="AE26" s="43" t="s">
+        <v>38</v>
+      </c>
+      <c r="AF26" s="43"/>
+      <c r="AG26" s="43"/>
+      <c r="AH26" s="43"/>
+      <c r="AI26" s="43"/>
+      <c r="AJ26" s="43"/>
+      <c r="AK26" s="43"/>
+      <c r="AL26" s="43"/>
+      <c r="AM26" s="49"/>
       <c r="AU26" s="20" t="s">
         <v>2</v>
       </c>
@@ -2870,7 +2880,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="7">
         <v>1</v>
       </c>
@@ -2918,7 +2928,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="28" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="8">
         <v>2</v>
       </c>
@@ -2944,26 +2954,26 @@
         <v>54</v>
       </c>
       <c r="O28" s="12"/>
-      <c r="P28" s="42" t="s">
+      <c r="P28" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="Q28" s="43"/>
-      <c r="R28" s="43"/>
-      <c r="S28" s="43"/>
-      <c r="T28" s="43"/>
-      <c r="U28" s="43"/>
-      <c r="V28" s="44"/>
+      <c r="Q28" s="54"/>
+      <c r="R28" s="54"/>
+      <c r="S28" s="54"/>
+      <c r="T28" s="54"/>
+      <c r="U28" s="54"/>
+      <c r="V28" s="55"/>
       <c r="X28" s="12"/>
       <c r="AD28" s="13"/>
-      <c r="AF28" s="49" t="s">
+      <c r="AF28" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="AG28" s="49"/>
-      <c r="AH28" s="49"/>
-      <c r="AI28" s="49"/>
-      <c r="AJ28" s="49"/>
-      <c r="AK28" s="49"/>
-      <c r="AL28" s="49"/>
+      <c r="AG28" s="42"/>
+      <c r="AH28" s="42"/>
+      <c r="AI28" s="42"/>
+      <c r="AJ28" s="42"/>
+      <c r="AK28" s="42"/>
+      <c r="AL28" s="42"/>
       <c r="AN28" s="12"/>
       <c r="AU28" s="8">
         <v>2</v>
@@ -2987,7 +2997,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="29" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="8">
         <v>3</v>
       </c>
@@ -3077,7 +3087,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="30" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:54" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A30" s="8">
         <v>4</v>
       </c>
@@ -3099,11 +3109,11 @@
       <c r="G30" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="I30" s="50" t="s">
+      <c r="I30" s="43" t="s">
         <v>26</v>
       </c>
-      <c r="J30" s="50"/>
-      <c r="K30" s="50"/>
+      <c r="J30" s="43"/>
+      <c r="K30" s="43"/>
       <c r="O30" s="12"/>
       <c r="P30" s="7">
         <v>1</v>
@@ -3150,11 +3160,11 @@
         <v>52</v>
       </c>
       <c r="AN30" s="12"/>
-      <c r="AQ30" s="50" t="s">
+      <c r="AQ30" s="43" t="s">
         <v>38</v>
       </c>
-      <c r="AR30" s="50"/>
-      <c r="AS30" s="50"/>
+      <c r="AR30" s="43"/>
+      <c r="AS30" s="43"/>
       <c r="AU30" s="38">
         <v>4</v>
       </c>
@@ -3180,7 +3190,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="31" spans="1:54" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:54" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A31" s="8" t="s">
         <v>11</v>
       </c>
@@ -3271,7 +3281,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="32" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A32" s="8" t="s">
         <v>10</v>
       </c>
@@ -3298,12 +3308,21 @@
       <c r="R32" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="S32" s="13"/>
+      <c r="S32" s="13">
+        <v>3</v>
+      </c>
       <c r="T32" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="U32" s="13"/>
-      <c r="V32" s="16"/>
+      <c r="U32" s="13">
+        <v>2</v>
+      </c>
+      <c r="V32" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="W32" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="X32" s="12"/>
       <c r="AD32" s="13"/>
       <c r="AF32" s="8">
@@ -3351,7 +3370,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="33" spans="1:54" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="9" t="s">
         <v>12</v>
       </c>
@@ -3395,12 +3414,18 @@
       <c r="AH33" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="AI33" s="13"/>
+      <c r="AI33" s="13">
+        <v>1</v>
+      </c>
       <c r="AJ33" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="AK33" s="13"/>
-      <c r="AL33" s="16"/>
+      <c r="AK33" s="13">
+        <v>2</v>
+      </c>
+      <c r="AL33" s="16" t="s">
+        <v>97</v>
+      </c>
       <c r="AN33" s="12"/>
       <c r="AQ33" s="12"/>
       <c r="AU33" s="9" t="s">
@@ -3419,16 +3444,16 @@
       <c r="AZ33" s="15"/>
       <c r="BA33" s="6"/>
     </row>
-    <row r="34" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="49" t="s">
+    <row r="34" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B34" s="49"/>
-      <c r="C34" s="49"/>
-      <c r="D34" s="49"/>
-      <c r="E34" s="49"/>
-      <c r="F34" s="49"/>
-      <c r="G34" s="49"/>
+      <c r="B34" s="42"/>
+      <c r="C34" s="42"/>
+      <c r="D34" s="42"/>
+      <c r="E34" s="42"/>
+      <c r="F34" s="42"/>
+      <c r="G34" s="42"/>
       <c r="L34" s="12"/>
       <c r="O34" s="12"/>
       <c r="P34" s="8" t="s">
@@ -3465,17 +3490,17 @@
       <c r="AL34" s="16"/>
       <c r="AN34" s="12"/>
       <c r="AQ34" s="12"/>
-      <c r="AU34" s="49" t="s">
+      <c r="AU34" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AV34" s="49"/>
-      <c r="AW34" s="49"/>
-      <c r="AX34" s="49"/>
-      <c r="AY34" s="49"/>
-      <c r="AZ34" s="49"/>
-      <c r="BA34" s="49"/>
-    </row>
-    <row r="35" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="AV34" s="42"/>
+      <c r="AW34" s="42"/>
+      <c r="AX34" s="42"/>
+      <c r="AY34" s="42"/>
+      <c r="AZ34" s="42"/>
+      <c r="BA34" s="42"/>
+    </row>
+    <row r="35" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="L35" s="12"/>
       <c r="O35" s="12"/>
       <c r="P35" s="8" t="s">
@@ -3513,21 +3538,21 @@
       <c r="AN35" s="12"/>
       <c r="AQ35" s="12"/>
     </row>
-    <row r="36" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="48" t="s">
+    <row r="36" spans="1:54" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A36" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="B36" s="48"/>
-      <c r="C36" s="48"/>
-      <c r="D36" s="48"/>
-      <c r="E36" s="48"/>
-      <c r="F36" s="48"/>
-      <c r="G36" s="48"/>
-      <c r="L36" s="54" t="s">
+      <c r="B36" s="45"/>
+      <c r="C36" s="45"/>
+      <c r="D36" s="45"/>
+      <c r="E36" s="45"/>
+      <c r="F36" s="45"/>
+      <c r="G36" s="45"/>
+      <c r="L36" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="M36" s="50"/>
-      <c r="N36" s="50"/>
+      <c r="M36" s="43"/>
+      <c r="N36" s="43"/>
       <c r="O36" s="12"/>
       <c r="P36" s="8" t="s">
         <v>12</v>
@@ -3561,23 +3586,23 @@
       </c>
       <c r="AK36" s="36"/>
       <c r="AL36" s="37"/>
-      <c r="AN36" s="54" t="s">
+      <c r="AN36" s="44" t="s">
         <v>38</v>
       </c>
-      <c r="AO36" s="50"/>
-      <c r="AP36" s="50"/>
+      <c r="AO36" s="43"/>
+      <c r="AP36" s="43"/>
       <c r="AQ36" s="12"/>
-      <c r="AU36" s="48" t="s">
+      <c r="AU36" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="AV36" s="48"/>
-      <c r="AW36" s="48"/>
-      <c r="AX36" s="48"/>
-      <c r="AY36" s="48"/>
-      <c r="AZ36" s="48"/>
-      <c r="BA36" s="48"/>
-    </row>
-    <row r="37" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="AV36" s="45"/>
+      <c r="AW36" s="45"/>
+      <c r="AX36" s="45"/>
+      <c r="AY36" s="45"/>
+      <c r="AZ36" s="45"/>
+      <c r="BA36" s="45"/>
+    </row>
+    <row r="37" spans="1:54" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A37" s="20" t="s">
         <v>2</v>
       </c>
@@ -3600,31 +3625,31 @@
         <v>9</v>
       </c>
       <c r="L37" s="12"/>
-      <c r="P37" s="45" t="s">
+      <c r="P37" s="56" t="s">
         <v>13</v>
       </c>
-      <c r="Q37" s="46"/>
-      <c r="R37" s="46"/>
-      <c r="S37" s="46"/>
-      <c r="T37" s="46"/>
-      <c r="U37" s="46"/>
-      <c r="V37" s="47"/>
-      <c r="X37" s="54"/>
-      <c r="Y37" s="50"/>
-      <c r="Z37" s="50"/>
-      <c r="AA37" s="50"/>
-      <c r="AB37" s="50"/>
-      <c r="AC37" s="50"/>
-      <c r="AD37" s="58"/>
-      <c r="AF37" s="49" t="s">
+      <c r="Q37" s="57"/>
+      <c r="R37" s="57"/>
+      <c r="S37" s="57"/>
+      <c r="T37" s="57"/>
+      <c r="U37" s="57"/>
+      <c r="V37" s="58"/>
+      <c r="X37" s="44"/>
+      <c r="Y37" s="43"/>
+      <c r="Z37" s="43"/>
+      <c r="AA37" s="43"/>
+      <c r="AB37" s="43"/>
+      <c r="AC37" s="43"/>
+      <c r="AD37" s="49"/>
+      <c r="AF37" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AG37" s="49"/>
-      <c r="AH37" s="49"/>
-      <c r="AI37" s="49"/>
-      <c r="AJ37" s="49"/>
-      <c r="AK37" s="49"/>
-      <c r="AL37" s="49"/>
+      <c r="AG37" s="42"/>
+      <c r="AH37" s="42"/>
+      <c r="AI37" s="42"/>
+      <c r="AJ37" s="42"/>
+      <c r="AK37" s="42"/>
+      <c r="AL37" s="42"/>
       <c r="AQ37" s="12"/>
       <c r="AU37" s="3" t="s">
         <v>2</v>
@@ -3648,7 +3673,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="7">
         <v>1</v>
       </c>
@@ -3694,7 +3719,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="39" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="8">
         <v>2</v>
       </c>
@@ -3717,33 +3742,33 @@
         <v>53</v>
       </c>
       <c r="L39" s="12"/>
-      <c r="M39" s="42" t="s">
+      <c r="M39" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="N39" s="43"/>
-      <c r="O39" s="43"/>
-      <c r="P39" s="43"/>
-      <c r="Q39" s="43"/>
-      <c r="R39" s="43"/>
-      <c r="S39" s="44"/>
-      <c r="X39" s="49" t="s">
+      <c r="N39" s="54"/>
+      <c r="O39" s="54"/>
+      <c r="P39" s="54"/>
+      <c r="Q39" s="54"/>
+      <c r="R39" s="54"/>
+      <c r="S39" s="55"/>
+      <c r="X39" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="Y39" s="49"/>
-      <c r="Z39" s="49"/>
-      <c r="AA39" s="49"/>
-      <c r="AB39" s="49"/>
-      <c r="AC39" s="49"/>
-      <c r="AD39" s="49"/>
-      <c r="AI39" s="42" t="s">
+      <c r="Y39" s="42"/>
+      <c r="Z39" s="42"/>
+      <c r="AA39" s="42"/>
+      <c r="AB39" s="42"/>
+      <c r="AC39" s="42"/>
+      <c r="AD39" s="42"/>
+      <c r="AI39" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="AJ39" s="43"/>
-      <c r="AK39" s="43"/>
-      <c r="AL39" s="43"/>
-      <c r="AM39" s="43"/>
-      <c r="AN39" s="43"/>
-      <c r="AO39" s="44"/>
+      <c r="AJ39" s="54"/>
+      <c r="AK39" s="54"/>
+      <c r="AL39" s="54"/>
+      <c r="AM39" s="54"/>
+      <c r="AN39" s="54"/>
+      <c r="AO39" s="55"/>
       <c r="AQ39" s="12"/>
       <c r="AU39" s="8">
         <v>2</v>
@@ -3767,7 +3792,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="40" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="8">
         <v>3</v>
       </c>
@@ -3876,7 +3901,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="41" spans="1:54" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:54" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A41" s="8">
         <v>4</v>
       </c>
@@ -3898,11 +3923,11 @@
       <c r="G41" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="I41" s="50" t="s">
+      <c r="I41" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="J41" s="50"/>
-      <c r="K41" s="50"/>
+      <c r="J41" s="43"/>
+      <c r="K41" s="43"/>
       <c r="L41" s="12"/>
       <c r="M41" s="7">
         <v>1</v>
@@ -3955,11 +3980,11 @@
       <c r="AO41" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="AQ41" s="54" t="s">
+      <c r="AQ41" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="AR41" s="50"/>
-      <c r="AS41" s="50"/>
+      <c r="AR41" s="43"/>
+      <c r="AS41" s="43"/>
       <c r="AU41" s="38">
         <v>4</v>
       </c>
@@ -3985,7 +4010,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="42" spans="1:54" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:54" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A42" s="8" t="s">
         <v>11</v>
       </c>
@@ -4080,7 +4105,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="43" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A43" s="8" t="s">
         <v>10</v>
       </c>
@@ -4178,7 +4203,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="44" spans="1:54" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="9" t="s">
         <v>12</v>
       </c>
@@ -4264,16 +4289,16 @@
       <c r="AZ44" s="15"/>
       <c r="BA44" s="6"/>
     </row>
-    <row r="45" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="49" t="s">
+    <row r="45" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B45" s="49"/>
-      <c r="C45" s="49"/>
-      <c r="D45" s="49"/>
-      <c r="E45" s="49"/>
-      <c r="F45" s="49"/>
-      <c r="G45" s="49"/>
+      <c r="B45" s="42"/>
+      <c r="C45" s="42"/>
+      <c r="D45" s="42"/>
+      <c r="E45" s="42"/>
+      <c r="F45" s="42"/>
+      <c r="G45" s="42"/>
       <c r="M45" s="8" t="s">
         <v>11</v>
       </c>
@@ -4322,17 +4347,17 @@
       <c r="AP45" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AU45" s="49" t="s">
+      <c r="AU45" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AV45" s="49"/>
-      <c r="AW45" s="49"/>
-      <c r="AX45" s="49"/>
-      <c r="AY45" s="49"/>
-      <c r="AZ45" s="49"/>
-      <c r="BA45" s="49"/>
-    </row>
-    <row r="46" spans="1:54" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="AV45" s="42"/>
+      <c r="AW45" s="42"/>
+      <c r="AX45" s="42"/>
+      <c r="AY45" s="42"/>
+      <c r="AZ45" s="42"/>
+      <c r="BA45" s="42"/>
+    </row>
+    <row r="46" spans="1:54" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="M46" s="8" t="s">
         <v>10</v>
       </c>
@@ -4379,7 +4404,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="47" spans="1:54" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:54" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="M47" s="8" t="s">
         <v>12</v>
       </c>
@@ -4420,50 +4445,62 @@
       <c r="AN47" s="15"/>
       <c r="AO47" s="6"/>
     </row>
-    <row r="48" spans="1:54" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="M48" s="42" t="s">
+    <row r="48" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M48" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="N48" s="43"/>
-      <c r="O48" s="43"/>
-      <c r="P48" s="43"/>
-      <c r="Q48" s="43"/>
-      <c r="R48" s="43"/>
-      <c r="S48" s="44"/>
-      <c r="X48" s="49" t="s">
+      <c r="N48" s="54"/>
+      <c r="O48" s="54"/>
+      <c r="P48" s="54"/>
+      <c r="Q48" s="54"/>
+      <c r="R48" s="54"/>
+      <c r="S48" s="55"/>
+      <c r="X48" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="Y48" s="49"/>
-      <c r="Z48" s="49"/>
-      <c r="AA48" s="49"/>
-      <c r="AB48" s="49"/>
-      <c r="AC48" s="49"/>
-      <c r="AD48" s="49"/>
-      <c r="AI48" s="49" t="s">
+      <c r="Y48" s="42"/>
+      <c r="Z48" s="42"/>
+      <c r="AA48" s="42"/>
+      <c r="AB48" s="42"/>
+      <c r="AC48" s="42"/>
+      <c r="AD48" s="42"/>
+      <c r="AI48" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AJ48" s="49"/>
-      <c r="AK48" s="49"/>
-      <c r="AL48" s="49"/>
-      <c r="AM48" s="49"/>
-      <c r="AN48" s="49"/>
-      <c r="AO48" s="49"/>
-    </row>
-    <row r="49" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+      <c r="AJ48" s="42"/>
+      <c r="AK48" s="42"/>
+      <c r="AL48" s="42"/>
+      <c r="AM48" s="42"/>
+      <c r="AN48" s="42"/>
+      <c r="AO48" s="42"/>
+    </row>
+    <row r="49" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="AU45:BA45"/>
-    <mergeCell ref="AF28:AL28"/>
-    <mergeCell ref="AF37:AL37"/>
-    <mergeCell ref="AQ30:AS30"/>
-    <mergeCell ref="AQ41:AS41"/>
-    <mergeCell ref="AU34:BA34"/>
-    <mergeCell ref="AU36:BA36"/>
-    <mergeCell ref="AU2:BA2"/>
-    <mergeCell ref="AU3:BA3"/>
-    <mergeCell ref="AU12:BA12"/>
-    <mergeCell ref="AU14:BA14"/>
-    <mergeCell ref="AU23:BA23"/>
+    <mergeCell ref="M48:S48"/>
+    <mergeCell ref="M39:S39"/>
+    <mergeCell ref="P37:V37"/>
+    <mergeCell ref="P28:V28"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A1:U1"/>
+    <mergeCell ref="O26:W26"/>
+    <mergeCell ref="I41:K41"/>
+    <mergeCell ref="L14:N14"/>
+    <mergeCell ref="L36:N36"/>
+    <mergeCell ref="M2:R2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="M4:S4"/>
+    <mergeCell ref="M13:S13"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="A25:G25"/>
     <mergeCell ref="X37:AD37"/>
     <mergeCell ref="AE26:AM26"/>
     <mergeCell ref="Z1:AB1"/>
@@ -4480,30 +4517,18 @@
     <mergeCell ref="AN36:AP36"/>
     <mergeCell ref="AQ8:AS8"/>
     <mergeCell ref="AQ19:AS19"/>
-    <mergeCell ref="A1:U1"/>
-    <mergeCell ref="O26:W26"/>
-    <mergeCell ref="I41:K41"/>
-    <mergeCell ref="L14:N14"/>
-    <mergeCell ref="L36:N36"/>
-    <mergeCell ref="M2:R2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="M4:S4"/>
-    <mergeCell ref="M13:S13"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A23:G23"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="M48:S48"/>
-    <mergeCell ref="M39:S39"/>
-    <mergeCell ref="P37:V37"/>
-    <mergeCell ref="P28:V28"/>
-    <mergeCell ref="A36:G36"/>
-    <mergeCell ref="A45:G45"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="AU2:BA2"/>
+    <mergeCell ref="AU3:BA3"/>
+    <mergeCell ref="AU12:BA12"/>
+    <mergeCell ref="AU14:BA14"/>
+    <mergeCell ref="AU23:BA23"/>
+    <mergeCell ref="AU45:BA45"/>
+    <mergeCell ref="AF28:AL28"/>
+    <mergeCell ref="AF37:AL37"/>
+    <mergeCell ref="AQ30:AS30"/>
+    <mergeCell ref="AQ41:AS41"/>
+    <mergeCell ref="AU34:BA34"/>
+    <mergeCell ref="AU36:BA36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/2025_2026/Playoffs/Brackets.xlsx
+++ b/2025_2026/Playoffs/Brackets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\NHLStats\2025_2026\Playoffs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2B1DA5E-BDF2-482E-A38C-270B347717DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16A5E15C-97CE-48D0-86BD-B509DAA46DBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="1590" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="100">
   <si>
     <t>Eastern Conference Playoff Teams</t>
   </si>
@@ -320,6 +320,12 @@
   </si>
   <si>
     <t>Golden Knights Win Series 4-0</t>
+  </si>
+  <si>
+    <t>Hurricanes Lead 3-1</t>
+  </si>
+  <si>
+    <t>Hurricanes Win Series 4-1</t>
   </si>
 </sst>
 </file>
@@ -698,18 +704,45 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -722,40 +755,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1125,18 +1131,18 @@
     </row>
     <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="11" spans="1:7" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="59" t="s">
+      <c r="A11" s="61" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="59"/>
-      <c r="C11" s="59" t="s">
+      <c r="B11" s="61"/>
+      <c r="C11" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="59"/>
-      <c r="E11" s="59" t="s">
+      <c r="D11" s="61"/>
+      <c r="E11" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="59"/>
+      <c r="F11" s="61"/>
       <c r="G11" s="4" t="s">
         <v>18</v>
       </c>
@@ -1165,19 +1171,21 @@
       </c>
     </row>
     <row r="13" spans="1:7" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="60" t="s">
+      <c r="A13" s="59" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="61"/>
-      <c r="C13" s="60" t="s">
+      <c r="B13" s="60"/>
+      <c r="C13" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="D13" s="61"/>
-      <c r="E13" s="60" t="s">
+      <c r="D13" s="60"/>
+      <c r="E13" s="59" t="s">
         <v>17</v>
       </c>
-      <c r="F13" s="61"/>
-      <c r="G13" s="5"/>
+      <c r="F13" s="60"/>
+      <c r="G13" s="5" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="14" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
@@ -1223,14 +1231,14 @@
       </c>
     </row>
     <row r="16" spans="1:7" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="60" t="s">
+      <c r="A16" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="61"/>
-      <c r="C16" s="60" t="s">
+      <c r="B16" s="60"/>
+      <c r="C16" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="61"/>
+      <c r="D16" s="60"/>
     </row>
     <row r="17" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
@@ -1261,10 +1269,10 @@
       </c>
     </row>
     <row r="19" spans="1:4" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="60" t="s">
+      <c r="A19" s="59" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="61"/>
+      <c r="B19" s="60"/>
     </row>
     <row r="20" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
@@ -1283,10 +1291,10 @@
       </c>
     </row>
     <row r="22" spans="1:4" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="60" t="s">
+      <c r="A22" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="61"/>
+      <c r="B22" s="60"/>
     </row>
     <row r="23" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
@@ -1371,16 +1379,16 @@
     <sortCondition ref="B2:B9"/>
   </sortState>
   <mergeCells count="10">
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A16:B16"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A16:B16"/>
   </mergeCells>
   <dataValidations count="16">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C14" xr:uid="{2C3D9587-ABAE-4E3F-8B22-396DF812BF02}">
@@ -1484,124 +1492,124 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:54" ht="27" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
-      <c r="I1" s="51"/>
-      <c r="J1" s="51"/>
-      <c r="K1" s="51"/>
-      <c r="L1" s="51"/>
-      <c r="M1" s="51"/>
-      <c r="N1" s="51"/>
-      <c r="O1" s="51"/>
-      <c r="P1" s="51"/>
-      <c r="Q1" s="51"/>
-      <c r="R1" s="51"/>
-      <c r="S1" s="51"/>
-      <c r="T1" s="51"/>
-      <c r="U1" s="52"/>
-      <c r="Z1" s="50" t="s">
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="52"/>
+      <c r="M1" s="52"/>
+      <c r="N1" s="52"/>
+      <c r="O1" s="52"/>
+      <c r="P1" s="52"/>
+      <c r="Q1" s="52"/>
+      <c r="R1" s="52"/>
+      <c r="S1" s="52"/>
+      <c r="T1" s="52"/>
+      <c r="U1" s="53"/>
+      <c r="Z1" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="AA1" s="51"/>
-      <c r="AB1" s="52"/>
-      <c r="AF1" s="50" t="s">
+      <c r="AA1" s="52"/>
+      <c r="AB1" s="53"/>
+      <c r="AF1" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="AG1" s="51"/>
-      <c r="AH1" s="51"/>
-      <c r="AI1" s="51"/>
-      <c r="AJ1" s="51"/>
-      <c r="AK1" s="51"/>
-      <c r="AL1" s="51"/>
-      <c r="AM1" s="51"/>
-      <c r="AN1" s="51"/>
-      <c r="AO1" s="51"/>
-      <c r="AP1" s="51"/>
-      <c r="AQ1" s="51"/>
-      <c r="AR1" s="51"/>
-      <c r="AS1" s="51"/>
-      <c r="AT1" s="51"/>
-      <c r="AU1" s="51"/>
-      <c r="AV1" s="51"/>
-      <c r="AW1" s="51"/>
-      <c r="AX1" s="51"/>
-      <c r="AY1" s="51"/>
-      <c r="AZ1" s="51"/>
-      <c r="BA1" s="52"/>
+      <c r="AG1" s="52"/>
+      <c r="AH1" s="52"/>
+      <c r="AI1" s="52"/>
+      <c r="AJ1" s="52"/>
+      <c r="AK1" s="52"/>
+      <c r="AL1" s="52"/>
+      <c r="AM1" s="52"/>
+      <c r="AN1" s="52"/>
+      <c r="AO1" s="52"/>
+      <c r="AP1" s="52"/>
+      <c r="AQ1" s="52"/>
+      <c r="AR1" s="52"/>
+      <c r="AS1" s="52"/>
+      <c r="AT1" s="52"/>
+      <c r="AU1" s="52"/>
+      <c r="AV1" s="52"/>
+      <c r="AW1" s="52"/>
+      <c r="AX1" s="52"/>
+      <c r="AY1" s="52"/>
+      <c r="AZ1" s="52"/>
+      <c r="BA1" s="53"/>
     </row>
     <row r="2" spans="1:54" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="48"/>
-      <c r="M2" s="46" t="s">
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="57"/>
+      <c r="M2" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="47"/>
-      <c r="O2" s="47"/>
-      <c r="P2" s="47"/>
-      <c r="Q2" s="47"/>
-      <c r="R2" s="48"/>
-      <c r="AI2" s="46" t="s">
+      <c r="N2" s="56"/>
+      <c r="O2" s="56"/>
+      <c r="P2" s="56"/>
+      <c r="Q2" s="56"/>
+      <c r="R2" s="57"/>
+      <c r="AI2" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="AJ2" s="47"/>
-      <c r="AK2" s="47"/>
-      <c r="AL2" s="47"/>
-      <c r="AM2" s="47"/>
-      <c r="AN2" s="47"/>
-      <c r="AO2" s="48"/>
-      <c r="AU2" s="46" t="s">
+      <c r="AJ2" s="56"/>
+      <c r="AK2" s="56"/>
+      <c r="AL2" s="56"/>
+      <c r="AM2" s="56"/>
+      <c r="AN2" s="56"/>
+      <c r="AO2" s="57"/>
+      <c r="AU2" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="AV2" s="47"/>
-      <c r="AW2" s="47"/>
-      <c r="AX2" s="47"/>
-      <c r="AY2" s="47"/>
-      <c r="AZ2" s="47"/>
-      <c r="BA2" s="48"/>
+      <c r="AV2" s="56"/>
+      <c r="AW2" s="56"/>
+      <c r="AX2" s="56"/>
+      <c r="AY2" s="56"/>
+      <c r="AZ2" s="56"/>
+      <c r="BA2" s="57"/>
     </row>
     <row r="3" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="42" t="s">
+      <c r="A3" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="42"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="42"/>
-      <c r="AI3" s="53" t="s">
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="AI3" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="AJ3" s="54"/>
-      <c r="AK3" s="54"/>
-      <c r="AL3" s="54"/>
-      <c r="AM3" s="54"/>
-      <c r="AN3" s="54"/>
-      <c r="AO3" s="55"/>
-      <c r="AU3" s="42" t="s">
+      <c r="AJ3" s="43"/>
+      <c r="AK3" s="43"/>
+      <c r="AL3" s="43"/>
+      <c r="AM3" s="43"/>
+      <c r="AN3" s="43"/>
+      <c r="AO3" s="44"/>
+      <c r="AU3" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="AV3" s="42"/>
-      <c r="AW3" s="42"/>
-      <c r="AX3" s="42"/>
-      <c r="AY3" s="42"/>
-      <c r="AZ3" s="42"/>
-      <c r="BA3" s="42"/>
+      <c r="AV3" s="49"/>
+      <c r="AW3" s="49"/>
+      <c r="AX3" s="49"/>
+      <c r="AY3" s="49"/>
+      <c r="AZ3" s="49"/>
+      <c r="BA3" s="49"/>
     </row>
     <row r="4" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
@@ -1625,15 +1633,15 @@
       <c r="G4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="53" t="s">
+      <c r="M4" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="N4" s="54"/>
-      <c r="O4" s="54"/>
-      <c r="P4" s="54"/>
-      <c r="Q4" s="54"/>
-      <c r="R4" s="54"/>
-      <c r="S4" s="55"/>
+      <c r="N4" s="43"/>
+      <c r="O4" s="43"/>
+      <c r="P4" s="43"/>
+      <c r="Q4" s="43"/>
+      <c r="R4" s="43"/>
+      <c r="S4" s="44"/>
       <c r="AI4" s="3" t="s">
         <v>2</v>
       </c>
@@ -1960,11 +1968,11 @@
       <c r="G8" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="I8" s="43" t="s">
+      <c r="I8" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="J8" s="43"/>
-      <c r="K8" s="43"/>
+      <c r="J8" s="50"/>
+      <c r="K8" s="50"/>
       <c r="M8" s="8">
         <v>3</v>
       </c>
@@ -2007,11 +2015,11 @@
       <c r="AO8" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="AQ8" s="43" t="s">
+      <c r="AQ8" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="AR8" s="43"/>
-      <c r="AS8" s="43"/>
+      <c r="AR8" s="50"/>
+      <c r="AS8" s="50"/>
       <c r="AU8" s="38">
         <v>4</v>
       </c>
@@ -2271,15 +2279,15 @@
       <c r="BA11" s="6"/>
     </row>
     <row r="12" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="42" t="s">
+      <c r="A12" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="42"/>
-      <c r="C12" s="42"/>
-      <c r="D12" s="42"/>
-      <c r="E12" s="42"/>
-      <c r="F12" s="42"/>
-      <c r="G12" s="42"/>
+      <c r="B12" s="49"/>
+      <c r="C12" s="49"/>
+      <c r="D12" s="49"/>
+      <c r="E12" s="49"/>
+      <c r="F12" s="49"/>
+      <c r="G12" s="49"/>
       <c r="L12" s="12"/>
       <c r="M12" s="8" t="s">
         <v>12</v>
@@ -2305,69 +2313,69 @@
       <c r="T12" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AI12" s="42" t="s">
+      <c r="AI12" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AJ12" s="42"/>
-      <c r="AK12" s="42"/>
-      <c r="AL12" s="42"/>
-      <c r="AM12" s="42"/>
-      <c r="AN12" s="42"/>
-      <c r="AO12" s="42"/>
+      <c r="AJ12" s="49"/>
+      <c r="AK12" s="49"/>
+      <c r="AL12" s="49"/>
+      <c r="AM12" s="49"/>
+      <c r="AN12" s="49"/>
+      <c r="AO12" s="49"/>
       <c r="AQ12" s="12"/>
-      <c r="AU12" s="42" t="s">
+      <c r="AU12" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AV12" s="42"/>
-      <c r="AW12" s="42"/>
-      <c r="AX12" s="42"/>
-      <c r="AY12" s="42"/>
-      <c r="AZ12" s="42"/>
-      <c r="BA12" s="42"/>
+      <c r="AV12" s="49"/>
+      <c r="AW12" s="49"/>
+      <c r="AX12" s="49"/>
+      <c r="AY12" s="49"/>
+      <c r="AZ12" s="49"/>
+      <c r="BA12" s="49"/>
     </row>
     <row r="13" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="L13" s="12"/>
-      <c r="M13" s="53" t="s">
+      <c r="M13" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="N13" s="54"/>
-      <c r="O13" s="54"/>
-      <c r="P13" s="54"/>
-      <c r="Q13" s="54"/>
-      <c r="R13" s="54"/>
-      <c r="S13" s="55"/>
+      <c r="N13" s="43"/>
+      <c r="O13" s="43"/>
+      <c r="P13" s="43"/>
+      <c r="Q13" s="43"/>
+      <c r="R13" s="43"/>
+      <c r="S13" s="44"/>
       <c r="AQ13" s="12"/>
     </row>
     <row r="14" spans="1:54" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="45" t="s">
+      <c r="A14" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="45"/>
-      <c r="C14" s="45"/>
-      <c r="D14" s="45"/>
-      <c r="E14" s="45"/>
-      <c r="F14" s="45"/>
-      <c r="G14" s="45"/>
-      <c r="L14" s="44" t="s">
+      <c r="B14" s="48"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="48"/>
+      <c r="E14" s="48"/>
+      <c r="F14" s="48"/>
+      <c r="G14" s="48"/>
+      <c r="L14" s="54" t="s">
         <v>32</v>
       </c>
-      <c r="M14" s="43"/>
-      <c r="N14" s="43"/>
-      <c r="AN14" s="43" t="s">
+      <c r="M14" s="50"/>
+      <c r="N14" s="50"/>
+      <c r="AN14" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="AO14" s="43"/>
-      <c r="AP14" s="43"/>
+      <c r="AO14" s="50"/>
+      <c r="AP14" s="50"/>
       <c r="AQ14" s="12"/>
-      <c r="AU14" s="45" t="s">
+      <c r="AU14" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="AV14" s="45"/>
-      <c r="AW14" s="45"/>
-      <c r="AX14" s="45"/>
-      <c r="AY14" s="45"/>
-      <c r="AZ14" s="45"/>
-      <c r="BA14" s="45"/>
+      <c r="AV14" s="48"/>
+      <c r="AW14" s="48"/>
+      <c r="AX14" s="48"/>
+      <c r="AY14" s="48"/>
+      <c r="AZ14" s="48"/>
+      <c r="BA14" s="48"/>
     </row>
     <row r="15" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
@@ -2595,19 +2603,19 @@
       <c r="G19" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="I19" s="43" t="s">
+      <c r="I19" s="50" t="s">
         <v>32</v>
       </c>
-      <c r="J19" s="43"/>
-      <c r="K19" s="43"/>
+      <c r="J19" s="50"/>
+      <c r="K19" s="50"/>
       <c r="L19" s="12"/>
       <c r="O19" s="12"/>
       <c r="AN19" s="12"/>
-      <c r="AQ19" s="44" t="s">
+      <c r="AQ19" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="AR19" s="43"/>
-      <c r="AS19" s="43"/>
+      <c r="AR19" s="50"/>
+      <c r="AS19" s="50"/>
       <c r="AU19" s="38">
         <v>4</v>
       </c>
@@ -2769,52 +2777,52 @@
       <c r="BA22" s="6"/>
     </row>
     <row r="23" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="42" t="s">
+      <c r="A23" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="B23" s="42"/>
-      <c r="C23" s="42"/>
-      <c r="D23" s="42"/>
-      <c r="E23" s="42"/>
-      <c r="F23" s="42"/>
-      <c r="G23" s="42"/>
+      <c r="B23" s="49"/>
+      <c r="C23" s="49"/>
+      <c r="D23" s="49"/>
+      <c r="E23" s="49"/>
+      <c r="F23" s="49"/>
+      <c r="G23" s="49"/>
       <c r="O23" s="12"/>
       <c r="AN23" s="12"/>
-      <c r="AU23" s="42" t="s">
+      <c r="AU23" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AV23" s="42"/>
-      <c r="AW23" s="42"/>
-      <c r="AX23" s="42"/>
-      <c r="AY23" s="42"/>
-      <c r="AZ23" s="42"/>
-      <c r="BA23" s="42"/>
+      <c r="AV23" s="49"/>
+      <c r="AW23" s="49"/>
+      <c r="AX23" s="49"/>
+      <c r="AY23" s="49"/>
+      <c r="AZ23" s="49"/>
+      <c r="BA23" s="49"/>
     </row>
     <row r="24" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="O24" s="12"/>
       <c r="AN24" s="12"/>
     </row>
     <row r="25" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="42" t="s">
+      <c r="A25" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="42"/>
-      <c r="C25" s="42"/>
-      <c r="D25" s="42"/>
-      <c r="E25" s="42"/>
-      <c r="F25" s="42"/>
-      <c r="G25" s="42"/>
+      <c r="B25" s="49"/>
+      <c r="C25" s="49"/>
+      <c r="D25" s="49"/>
+      <c r="E25" s="49"/>
+      <c r="F25" s="49"/>
+      <c r="G25" s="49"/>
       <c r="O25" s="12"/>
       <c r="AN25" s="12"/>
-      <c r="AU25" s="42" t="s">
+      <c r="AU25" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="AV25" s="42"/>
-      <c r="AW25" s="42"/>
-      <c r="AX25" s="42"/>
-      <c r="AY25" s="42"/>
-      <c r="AZ25" s="42"/>
-      <c r="BA25" s="42"/>
+      <c r="AV25" s="49"/>
+      <c r="AW25" s="49"/>
+      <c r="AX25" s="49"/>
+      <c r="AY25" s="49"/>
+      <c r="AZ25" s="49"/>
+      <c r="BA25" s="49"/>
     </row>
     <row r="26" spans="1:54" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A26" s="20" t="s">
@@ -2838,26 +2846,28 @@
       <c r="G26" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="O26" s="44"/>
-      <c r="P26" s="43"/>
-      <c r="Q26" s="43"/>
-      <c r="R26" s="43"/>
-      <c r="S26" s="43"/>
-      <c r="T26" s="43"/>
-      <c r="U26" s="43"/>
-      <c r="V26" s="43"/>
-      <c r="W26" s="43"/>
-      <c r="AE26" s="43" t="s">
+      <c r="O26" s="54" t="s">
+        <v>26</v>
+      </c>
+      <c r="P26" s="50"/>
+      <c r="Q26" s="50"/>
+      <c r="R26" s="50"/>
+      <c r="S26" s="50"/>
+      <c r="T26" s="50"/>
+      <c r="U26" s="50"/>
+      <c r="V26" s="50"/>
+      <c r="W26" s="50"/>
+      <c r="AE26" s="50" t="s">
         <v>38</v>
       </c>
-      <c r="AF26" s="43"/>
-      <c r="AG26" s="43"/>
-      <c r="AH26" s="43"/>
-      <c r="AI26" s="43"/>
-      <c r="AJ26" s="43"/>
-      <c r="AK26" s="43"/>
-      <c r="AL26" s="43"/>
-      <c r="AM26" s="49"/>
+      <c r="AF26" s="50"/>
+      <c r="AG26" s="50"/>
+      <c r="AH26" s="50"/>
+      <c r="AI26" s="50"/>
+      <c r="AJ26" s="50"/>
+      <c r="AK26" s="50"/>
+      <c r="AL26" s="50"/>
+      <c r="AM26" s="58"/>
       <c r="AU26" s="20" t="s">
         <v>2</v>
       </c>
@@ -2954,26 +2964,26 @@
         <v>54</v>
       </c>
       <c r="O28" s="12"/>
-      <c r="P28" s="53" t="s">
+      <c r="P28" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="Q28" s="54"/>
-      <c r="R28" s="54"/>
-      <c r="S28" s="54"/>
-      <c r="T28" s="54"/>
-      <c r="U28" s="54"/>
-      <c r="V28" s="55"/>
+      <c r="Q28" s="43"/>
+      <c r="R28" s="43"/>
+      <c r="S28" s="43"/>
+      <c r="T28" s="43"/>
+      <c r="U28" s="43"/>
+      <c r="V28" s="44"/>
       <c r="X28" s="12"/>
       <c r="AD28" s="13"/>
-      <c r="AF28" s="42" t="s">
+      <c r="AF28" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="AG28" s="42"/>
-      <c r="AH28" s="42"/>
-      <c r="AI28" s="42"/>
-      <c r="AJ28" s="42"/>
-      <c r="AK28" s="42"/>
-      <c r="AL28" s="42"/>
+      <c r="AG28" s="49"/>
+      <c r="AH28" s="49"/>
+      <c r="AI28" s="49"/>
+      <c r="AJ28" s="49"/>
+      <c r="AK28" s="49"/>
+      <c r="AL28" s="49"/>
       <c r="AN28" s="12"/>
       <c r="AU28" s="8">
         <v>2</v>
@@ -3109,11 +3119,11 @@
       <c r="G30" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="I30" s="43" t="s">
+      <c r="I30" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="J30" s="43"/>
-      <c r="K30" s="43"/>
+      <c r="J30" s="50"/>
+      <c r="K30" s="50"/>
       <c r="O30" s="12"/>
       <c r="P30" s="7">
         <v>1</v>
@@ -3160,11 +3170,11 @@
         <v>52</v>
       </c>
       <c r="AN30" s="12"/>
-      <c r="AQ30" s="43" t="s">
+      <c r="AQ30" s="50" t="s">
         <v>38</v>
       </c>
-      <c r="AR30" s="43"/>
-      <c r="AS30" s="43"/>
+      <c r="AR30" s="50"/>
+      <c r="AS30" s="50"/>
       <c r="AU30" s="38">
         <v>4</v>
       </c>
@@ -3397,12 +3407,18 @@
       <c r="R33" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="S33" s="13"/>
+      <c r="S33" s="13">
+        <v>4</v>
+      </c>
       <c r="T33" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="U33" s="13"/>
-      <c r="V33" s="16"/>
+      <c r="U33" s="13">
+        <v>0</v>
+      </c>
+      <c r="V33" s="16" t="s">
+        <v>98</v>
+      </c>
       <c r="X33" s="12"/>
       <c r="AD33" s="13"/>
       <c r="AF33" s="8">
@@ -3445,15 +3461,15 @@
       <c r="BA33" s="6"/>
     </row>
     <row r="34" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="42" t="s">
+      <c r="A34" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="B34" s="42"/>
-      <c r="C34" s="42"/>
-      <c r="D34" s="42"/>
-      <c r="E34" s="42"/>
-      <c r="F34" s="42"/>
-      <c r="G34" s="42"/>
+      <c r="B34" s="49"/>
+      <c r="C34" s="49"/>
+      <c r="D34" s="49"/>
+      <c r="E34" s="49"/>
+      <c r="F34" s="49"/>
+      <c r="G34" s="49"/>
       <c r="L34" s="12"/>
       <c r="O34" s="12"/>
       <c r="P34" s="8" t="s">
@@ -3465,12 +3481,18 @@
       <c r="R34" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="S34" s="13"/>
+      <c r="S34" s="13">
+        <v>1</v>
+      </c>
       <c r="T34" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="U34" s="13"/>
-      <c r="V34" s="16"/>
+      <c r="U34" s="13">
+        <v>6</v>
+      </c>
+      <c r="V34" s="16" t="s">
+        <v>99</v>
+      </c>
       <c r="X34" s="12"/>
       <c r="AD34" s="13"/>
       <c r="AF34" s="8" t="s">
@@ -3490,15 +3512,15 @@
       <c r="AL34" s="16"/>
       <c r="AN34" s="12"/>
       <c r="AQ34" s="12"/>
-      <c r="AU34" s="42" t="s">
+      <c r="AU34" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AV34" s="42"/>
-      <c r="AW34" s="42"/>
-      <c r="AX34" s="42"/>
-      <c r="AY34" s="42"/>
-      <c r="AZ34" s="42"/>
-      <c r="BA34" s="42"/>
+      <c r="AV34" s="49"/>
+      <c r="AW34" s="49"/>
+      <c r="AX34" s="49"/>
+      <c r="AY34" s="49"/>
+      <c r="AZ34" s="49"/>
+      <c r="BA34" s="49"/>
     </row>
     <row r="35" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="L35" s="12"/>
@@ -3539,20 +3561,20 @@
       <c r="AQ35" s="12"/>
     </row>
     <row r="36" spans="1:54" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="45" t="s">
+      <c r="A36" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="B36" s="45"/>
-      <c r="C36" s="45"/>
-      <c r="D36" s="45"/>
-      <c r="E36" s="45"/>
-      <c r="F36" s="45"/>
-      <c r="G36" s="45"/>
-      <c r="L36" s="44" t="s">
+      <c r="B36" s="48"/>
+      <c r="C36" s="48"/>
+      <c r="D36" s="48"/>
+      <c r="E36" s="48"/>
+      <c r="F36" s="48"/>
+      <c r="G36" s="48"/>
+      <c r="L36" s="54" t="s">
         <v>26</v>
       </c>
-      <c r="M36" s="43"/>
-      <c r="N36" s="43"/>
+      <c r="M36" s="50"/>
+      <c r="N36" s="50"/>
       <c r="O36" s="12"/>
       <c r="P36" s="8" t="s">
         <v>12</v>
@@ -3586,21 +3608,21 @@
       </c>
       <c r="AK36" s="36"/>
       <c r="AL36" s="37"/>
-      <c r="AN36" s="44" t="s">
+      <c r="AN36" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="AO36" s="43"/>
-      <c r="AP36" s="43"/>
+      <c r="AO36" s="50"/>
+      <c r="AP36" s="50"/>
       <c r="AQ36" s="12"/>
-      <c r="AU36" s="45" t="s">
+      <c r="AU36" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="AV36" s="45"/>
-      <c r="AW36" s="45"/>
-      <c r="AX36" s="45"/>
-      <c r="AY36" s="45"/>
-      <c r="AZ36" s="45"/>
-      <c r="BA36" s="45"/>
+      <c r="AV36" s="48"/>
+      <c r="AW36" s="48"/>
+      <c r="AX36" s="48"/>
+      <c r="AY36" s="48"/>
+      <c r="AZ36" s="48"/>
+      <c r="BA36" s="48"/>
     </row>
     <row r="37" spans="1:54" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A37" s="20" t="s">
@@ -3625,31 +3647,31 @@
         <v>9</v>
       </c>
       <c r="L37" s="12"/>
-      <c r="P37" s="56" t="s">
+      <c r="P37" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="Q37" s="57"/>
-      <c r="R37" s="57"/>
-      <c r="S37" s="57"/>
-      <c r="T37" s="57"/>
-      <c r="U37" s="57"/>
-      <c r="V37" s="58"/>
-      <c r="X37" s="44"/>
-      <c r="Y37" s="43"/>
-      <c r="Z37" s="43"/>
-      <c r="AA37" s="43"/>
-      <c r="AB37" s="43"/>
-      <c r="AC37" s="43"/>
-      <c r="AD37" s="49"/>
-      <c r="AF37" s="42" t="s">
+      <c r="Q37" s="46"/>
+      <c r="R37" s="46"/>
+      <c r="S37" s="46"/>
+      <c r="T37" s="46"/>
+      <c r="U37" s="46"/>
+      <c r="V37" s="47"/>
+      <c r="X37" s="54"/>
+      <c r="Y37" s="50"/>
+      <c r="Z37" s="50"/>
+      <c r="AA37" s="50"/>
+      <c r="AB37" s="50"/>
+      <c r="AC37" s="50"/>
+      <c r="AD37" s="58"/>
+      <c r="AF37" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AG37" s="42"/>
-      <c r="AH37" s="42"/>
-      <c r="AI37" s="42"/>
-      <c r="AJ37" s="42"/>
-      <c r="AK37" s="42"/>
-      <c r="AL37" s="42"/>
+      <c r="AG37" s="49"/>
+      <c r="AH37" s="49"/>
+      <c r="AI37" s="49"/>
+      <c r="AJ37" s="49"/>
+      <c r="AK37" s="49"/>
+      <c r="AL37" s="49"/>
       <c r="AQ37" s="12"/>
       <c r="AU37" s="3" t="s">
         <v>2</v>
@@ -3742,33 +3764,33 @@
         <v>53</v>
       </c>
       <c r="L39" s="12"/>
-      <c r="M39" s="53" t="s">
+      <c r="M39" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="N39" s="54"/>
-      <c r="O39" s="54"/>
-      <c r="P39" s="54"/>
-      <c r="Q39" s="54"/>
-      <c r="R39" s="54"/>
-      <c r="S39" s="55"/>
-      <c r="X39" s="42" t="s">
+      <c r="N39" s="43"/>
+      <c r="O39" s="43"/>
+      <c r="P39" s="43"/>
+      <c r="Q39" s="43"/>
+      <c r="R39" s="43"/>
+      <c r="S39" s="44"/>
+      <c r="X39" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="Y39" s="42"/>
-      <c r="Z39" s="42"/>
-      <c r="AA39" s="42"/>
-      <c r="AB39" s="42"/>
-      <c r="AC39" s="42"/>
-      <c r="AD39" s="42"/>
-      <c r="AI39" s="53" t="s">
+      <c r="Y39" s="49"/>
+      <c r="Z39" s="49"/>
+      <c r="AA39" s="49"/>
+      <c r="AB39" s="49"/>
+      <c r="AC39" s="49"/>
+      <c r="AD39" s="49"/>
+      <c r="AI39" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="AJ39" s="54"/>
-      <c r="AK39" s="54"/>
-      <c r="AL39" s="54"/>
-      <c r="AM39" s="54"/>
-      <c r="AN39" s="54"/>
-      <c r="AO39" s="55"/>
+      <c r="AJ39" s="43"/>
+      <c r="AK39" s="43"/>
+      <c r="AL39" s="43"/>
+      <c r="AM39" s="43"/>
+      <c r="AN39" s="43"/>
+      <c r="AO39" s="44"/>
       <c r="AQ39" s="12"/>
       <c r="AU39" s="8">
         <v>2</v>
@@ -3923,11 +3945,11 @@
       <c r="G41" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="I41" s="43" t="s">
+      <c r="I41" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="J41" s="43"/>
-      <c r="K41" s="43"/>
+      <c r="J41" s="50"/>
+      <c r="K41" s="50"/>
       <c r="L41" s="12"/>
       <c r="M41" s="7">
         <v>1</v>
@@ -3953,10 +3975,16 @@
       <c r="X41" s="7">
         <v>1</v>
       </c>
-      <c r="Y41" s="29"/>
-      <c r="Z41" s="23"/>
+      <c r="Y41" s="29">
+        <v>46175</v>
+      </c>
+      <c r="Z41" s="23" t="s">
+        <v>38</v>
+      </c>
       <c r="AA41" s="24"/>
-      <c r="AB41" s="23"/>
+      <c r="AB41" s="23" t="s">
+        <v>26</v>
+      </c>
       <c r="AC41" s="24"/>
       <c r="AD41" s="25"/>
       <c r="AI41" s="7">
@@ -3980,11 +4008,11 @@
       <c r="AO41" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="AQ41" s="44" t="s">
+      <c r="AQ41" s="54" t="s">
         <v>23</v>
       </c>
-      <c r="AR41" s="43"/>
-      <c r="AS41" s="43"/>
+      <c r="AR41" s="50"/>
+      <c r="AS41" s="50"/>
       <c r="AU41" s="38">
         <v>4</v>
       </c>
@@ -4056,10 +4084,16 @@
       <c r="X42" s="8">
         <v>2</v>
       </c>
-      <c r="Y42" s="27"/>
-      <c r="Z42" s="12"/>
+      <c r="Y42" s="27">
+        <v>46177</v>
+      </c>
+      <c r="Z42" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="AA42" s="13"/>
-      <c r="AB42" s="12"/>
+      <c r="AB42" s="12" t="s">
+        <v>26</v>
+      </c>
       <c r="AC42" s="13"/>
       <c r="AD42" s="16"/>
       <c r="AI42" s="8">
@@ -4154,10 +4188,16 @@
       <c r="X43" s="8">
         <v>3</v>
       </c>
-      <c r="Y43" s="27"/>
-      <c r="Z43" s="12"/>
+      <c r="Y43" s="27">
+        <v>46179</v>
+      </c>
+      <c r="Z43" s="12" t="s">
+        <v>26</v>
+      </c>
       <c r="AA43" s="13"/>
-      <c r="AB43" s="12"/>
+      <c r="AB43" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="AC43" s="13"/>
       <c r="AD43" s="16"/>
       <c r="AI43" s="8">
@@ -4246,10 +4286,16 @@
       <c r="X44" s="8">
         <v>4</v>
       </c>
-      <c r="Y44" s="27"/>
-      <c r="Z44" s="12"/>
+      <c r="Y44" s="27">
+        <v>46182</v>
+      </c>
+      <c r="Z44" s="12" t="s">
+        <v>26</v>
+      </c>
       <c r="AA44" s="13"/>
-      <c r="AB44" s="12"/>
+      <c r="AB44" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="AC44" s="13"/>
       <c r="AD44" s="16"/>
       <c r="AI44" s="8">
@@ -4290,15 +4336,15 @@
       <c r="BA44" s="6"/>
     </row>
     <row r="45" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="42" t="s">
+      <c r="A45" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="B45" s="42"/>
-      <c r="C45" s="42"/>
-      <c r="D45" s="42"/>
-      <c r="E45" s="42"/>
-      <c r="F45" s="42"/>
-      <c r="G45" s="42"/>
+      <c r="B45" s="49"/>
+      <c r="C45" s="49"/>
+      <c r="D45" s="49"/>
+      <c r="E45" s="49"/>
+      <c r="F45" s="49"/>
+      <c r="G45" s="49"/>
       <c r="M45" s="8" t="s">
         <v>11</v>
       </c>
@@ -4317,10 +4363,16 @@
       <c r="X45" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="Y45" s="27"/>
-      <c r="Z45" s="12"/>
+      <c r="Y45" s="27">
+        <v>46184</v>
+      </c>
+      <c r="Z45" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="AA45" s="13"/>
-      <c r="AB45" s="12"/>
+      <c r="AB45" s="12" t="s">
+        <v>26</v>
+      </c>
       <c r="AC45" s="13"/>
       <c r="AD45" s="16"/>
       <c r="AI45" s="8" t="s">
@@ -4347,15 +4399,15 @@
       <c r="AP45" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AU45" s="42" t="s">
+      <c r="AU45" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AV45" s="42"/>
-      <c r="AW45" s="42"/>
-      <c r="AX45" s="42"/>
-      <c r="AY45" s="42"/>
-      <c r="AZ45" s="42"/>
-      <c r="BA45" s="42"/>
+      <c r="AV45" s="49"/>
+      <c r="AW45" s="49"/>
+      <c r="AX45" s="49"/>
+      <c r="AY45" s="49"/>
+      <c r="AZ45" s="49"/>
+      <c r="BA45" s="49"/>
     </row>
     <row r="46" spans="1:54" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="M46" s="8" t="s">
@@ -4376,10 +4428,16 @@
       <c r="X46" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="Y46" s="27"/>
-      <c r="Z46" s="12"/>
+      <c r="Y46" s="27">
+        <v>46187</v>
+      </c>
+      <c r="Z46" s="12" t="s">
+        <v>26</v>
+      </c>
       <c r="AA46" s="13"/>
-      <c r="AB46" s="12"/>
+      <c r="AB46" s="12" t="s">
+        <v>38</v>
+      </c>
       <c r="AC46" s="13"/>
       <c r="AD46" s="16"/>
       <c r="AI46" s="8" t="s">
@@ -4423,10 +4481,16 @@
       <c r="X47" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="Y47" s="28"/>
-      <c r="Z47" s="14"/>
+      <c r="Y47" s="28">
+        <v>46190</v>
+      </c>
+      <c r="Z47" s="14" t="s">
+        <v>38</v>
+      </c>
       <c r="AA47" s="15"/>
-      <c r="AB47" s="14"/>
+      <c r="AB47" s="14" t="s">
+        <v>26</v>
+      </c>
       <c r="AC47" s="15"/>
       <c r="AD47" s="6"/>
       <c r="AI47" s="9" t="s">
@@ -4446,45 +4510,65 @@
       <c r="AO47" s="6"/>
     </row>
     <row r="48" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="M48" s="53" t="s">
+      <c r="M48" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="N48" s="54"/>
-      <c r="O48" s="54"/>
-      <c r="P48" s="54"/>
-      <c r="Q48" s="54"/>
-      <c r="R48" s="54"/>
-      <c r="S48" s="55"/>
-      <c r="X48" s="42" t="s">
+      <c r="N48" s="43"/>
+      <c r="O48" s="43"/>
+      <c r="P48" s="43"/>
+      <c r="Q48" s="43"/>
+      <c r="R48" s="43"/>
+      <c r="S48" s="44"/>
+      <c r="X48" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="Y48" s="42"/>
-      <c r="Z48" s="42"/>
-      <c r="AA48" s="42"/>
-      <c r="AB48" s="42"/>
-      <c r="AC48" s="42"/>
-      <c r="AD48" s="42"/>
-      <c r="AI48" s="42" t="s">
+      <c r="Y48" s="49"/>
+      <c r="Z48" s="49"/>
+      <c r="AA48" s="49"/>
+      <c r="AB48" s="49"/>
+      <c r="AC48" s="49"/>
+      <c r="AD48" s="49"/>
+      <c r="AI48" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AJ48" s="42"/>
-      <c r="AK48" s="42"/>
-      <c r="AL48" s="42"/>
-      <c r="AM48" s="42"/>
-      <c r="AN48" s="42"/>
-      <c r="AO48" s="42"/>
+      <c r="AJ48" s="49"/>
+      <c r="AK48" s="49"/>
+      <c r="AL48" s="49"/>
+      <c r="AM48" s="49"/>
+      <c r="AN48" s="49"/>
+      <c r="AO48" s="49"/>
     </row>
     <row r="49" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="M48:S48"/>
-    <mergeCell ref="M39:S39"/>
-    <mergeCell ref="P37:V37"/>
-    <mergeCell ref="P28:V28"/>
-    <mergeCell ref="A36:G36"/>
-    <mergeCell ref="A45:G45"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="AU45:BA45"/>
+    <mergeCell ref="AF28:AL28"/>
+    <mergeCell ref="AF37:AL37"/>
+    <mergeCell ref="AQ30:AS30"/>
+    <mergeCell ref="AQ41:AS41"/>
+    <mergeCell ref="AU34:BA34"/>
+    <mergeCell ref="AU36:BA36"/>
+    <mergeCell ref="AU2:BA2"/>
+    <mergeCell ref="AU3:BA3"/>
+    <mergeCell ref="AU12:BA12"/>
+    <mergeCell ref="AU14:BA14"/>
+    <mergeCell ref="AU23:BA23"/>
+    <mergeCell ref="X37:AD37"/>
+    <mergeCell ref="AE26:AM26"/>
+    <mergeCell ref="Z1:AB1"/>
+    <mergeCell ref="X39:AD39"/>
+    <mergeCell ref="X48:AD48"/>
+    <mergeCell ref="AF1:BA1"/>
+    <mergeCell ref="AI2:AO2"/>
+    <mergeCell ref="AI3:AO3"/>
+    <mergeCell ref="AI12:AO12"/>
+    <mergeCell ref="AI39:AO39"/>
+    <mergeCell ref="AU25:BA25"/>
+    <mergeCell ref="AI48:AO48"/>
+    <mergeCell ref="AN14:AP14"/>
+    <mergeCell ref="AN36:AP36"/>
+    <mergeCell ref="AQ8:AS8"/>
+    <mergeCell ref="AQ19:AS19"/>
     <mergeCell ref="A1:U1"/>
     <mergeCell ref="O26:W26"/>
     <mergeCell ref="I41:K41"/>
@@ -4501,34 +4585,14 @@
     <mergeCell ref="I8:K8"/>
     <mergeCell ref="I19:K19"/>
     <mergeCell ref="A25:G25"/>
-    <mergeCell ref="X37:AD37"/>
-    <mergeCell ref="AE26:AM26"/>
-    <mergeCell ref="Z1:AB1"/>
-    <mergeCell ref="X39:AD39"/>
-    <mergeCell ref="X48:AD48"/>
-    <mergeCell ref="AF1:BA1"/>
-    <mergeCell ref="AI2:AO2"/>
-    <mergeCell ref="AI3:AO3"/>
-    <mergeCell ref="AI12:AO12"/>
-    <mergeCell ref="AI39:AO39"/>
-    <mergeCell ref="AU25:BA25"/>
-    <mergeCell ref="AI48:AO48"/>
-    <mergeCell ref="AN14:AP14"/>
-    <mergeCell ref="AN36:AP36"/>
-    <mergeCell ref="AQ8:AS8"/>
-    <mergeCell ref="AQ19:AS19"/>
-    <mergeCell ref="AU2:BA2"/>
-    <mergeCell ref="AU3:BA3"/>
-    <mergeCell ref="AU12:BA12"/>
-    <mergeCell ref="AU14:BA14"/>
-    <mergeCell ref="AU23:BA23"/>
-    <mergeCell ref="AU45:BA45"/>
-    <mergeCell ref="AF28:AL28"/>
-    <mergeCell ref="AF37:AL37"/>
-    <mergeCell ref="AQ30:AS30"/>
-    <mergeCell ref="AQ41:AS41"/>
-    <mergeCell ref="AU34:BA34"/>
-    <mergeCell ref="AU36:BA36"/>
+    <mergeCell ref="M48:S48"/>
+    <mergeCell ref="M39:S39"/>
+    <mergeCell ref="P37:V37"/>
+    <mergeCell ref="P28:V28"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="A34:G34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/2025_2026/Playoffs/Brackets.xlsx
+++ b/2025_2026/Playoffs/Brackets.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\NHLStats\2025_2026\Playoffs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16A5E15C-97CE-48D0-86BD-B509DAA46DBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{873CEA2B-592E-4AC1-A99E-52BB2274762D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="1590" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="100">
   <si>
     <t>Eastern Conference Playoff Teams</t>
   </si>
@@ -704,6 +704,39 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -722,46 +755,13 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1131,18 +1131,18 @@
     </row>
     <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="11" spans="1:7" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="61" t="s">
+      <c r="A11" s="59" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="61"/>
-      <c r="C11" s="61" t="s">
+      <c r="B11" s="59"/>
+      <c r="C11" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="61"/>
-      <c r="E11" s="61" t="s">
+      <c r="D11" s="59"/>
+      <c r="E11" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="61"/>
+      <c r="F11" s="59"/>
       <c r="G11" s="4" t="s">
         <v>18</v>
       </c>
@@ -1171,18 +1171,18 @@
       </c>
     </row>
     <row r="13" spans="1:7" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="59" t="s">
+      <c r="A13" s="60" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="60"/>
-      <c r="C13" s="59" t="s">
+      <c r="B13" s="61"/>
+      <c r="C13" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="D13" s="60"/>
-      <c r="E13" s="59" t="s">
+      <c r="D13" s="61"/>
+      <c r="E13" s="60" t="s">
         <v>17</v>
       </c>
-      <c r="F13" s="60"/>
+      <c r="F13" s="61"/>
       <c r="G13" s="5" t="s">
         <v>26</v>
       </c>
@@ -1231,14 +1231,14 @@
       </c>
     </row>
     <row r="16" spans="1:7" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="59" t="s">
+      <c r="A16" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="60"/>
-      <c r="C16" s="59" t="s">
+      <c r="B16" s="61"/>
+      <c r="C16" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="60"/>
+      <c r="D16" s="61"/>
     </row>
     <row r="17" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
@@ -1269,10 +1269,10 @@
       </c>
     </row>
     <row r="19" spans="1:4" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="59" t="s">
+      <c r="A19" s="60" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="60"/>
+      <c r="B19" s="61"/>
     </row>
     <row r="20" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
@@ -1291,10 +1291,10 @@
       </c>
     </row>
     <row r="22" spans="1:4" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="59" t="s">
+      <c r="A22" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="60"/>
+      <c r="B22" s="61"/>
     </row>
     <row r="23" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
@@ -1379,16 +1379,16 @@
     <sortCondition ref="B2:B9"/>
   </sortState>
   <mergeCells count="10">
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C16:D16"/>
     <mergeCell ref="E11:F11"/>
     <mergeCell ref="E13:F13"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C16:D16"/>
   </mergeCells>
   <dataValidations count="16">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C14" xr:uid="{2C3D9587-ABAE-4E3F-8B22-396DF812BF02}">
@@ -1492,124 +1492,124 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:54" ht="27" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
-      <c r="M1" s="52"/>
-      <c r="N1" s="52"/>
-      <c r="O1" s="52"/>
-      <c r="P1" s="52"/>
-      <c r="Q1" s="52"/>
-      <c r="R1" s="52"/>
-      <c r="S1" s="52"/>
-      <c r="T1" s="52"/>
-      <c r="U1" s="53"/>
-      <c r="Z1" s="51" t="s">
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
+      <c r="K1" s="51"/>
+      <c r="L1" s="51"/>
+      <c r="M1" s="51"/>
+      <c r="N1" s="51"/>
+      <c r="O1" s="51"/>
+      <c r="P1" s="51"/>
+      <c r="Q1" s="51"/>
+      <c r="R1" s="51"/>
+      <c r="S1" s="51"/>
+      <c r="T1" s="51"/>
+      <c r="U1" s="52"/>
+      <c r="Z1" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="AA1" s="52"/>
-      <c r="AB1" s="53"/>
-      <c r="AF1" s="51" t="s">
+      <c r="AA1" s="51"/>
+      <c r="AB1" s="52"/>
+      <c r="AF1" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="AG1" s="52"/>
-      <c r="AH1" s="52"/>
-      <c r="AI1" s="52"/>
-      <c r="AJ1" s="52"/>
-      <c r="AK1" s="52"/>
-      <c r="AL1" s="52"/>
-      <c r="AM1" s="52"/>
-      <c r="AN1" s="52"/>
-      <c r="AO1" s="52"/>
-      <c r="AP1" s="52"/>
-      <c r="AQ1" s="52"/>
-      <c r="AR1" s="52"/>
-      <c r="AS1" s="52"/>
-      <c r="AT1" s="52"/>
-      <c r="AU1" s="52"/>
-      <c r="AV1" s="52"/>
-      <c r="AW1" s="52"/>
-      <c r="AX1" s="52"/>
-      <c r="AY1" s="52"/>
-      <c r="AZ1" s="52"/>
-      <c r="BA1" s="53"/>
+      <c r="AG1" s="51"/>
+      <c r="AH1" s="51"/>
+      <c r="AI1" s="51"/>
+      <c r="AJ1" s="51"/>
+      <c r="AK1" s="51"/>
+      <c r="AL1" s="51"/>
+      <c r="AM1" s="51"/>
+      <c r="AN1" s="51"/>
+      <c r="AO1" s="51"/>
+      <c r="AP1" s="51"/>
+      <c r="AQ1" s="51"/>
+      <c r="AR1" s="51"/>
+      <c r="AS1" s="51"/>
+      <c r="AT1" s="51"/>
+      <c r="AU1" s="51"/>
+      <c r="AV1" s="51"/>
+      <c r="AW1" s="51"/>
+      <c r="AX1" s="51"/>
+      <c r="AY1" s="51"/>
+      <c r="AZ1" s="51"/>
+      <c r="BA1" s="52"/>
     </row>
     <row r="2" spans="1:54" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="55" t="s">
+      <c r="A2" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="57"/>
-      <c r="M2" s="55" t="s">
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="48"/>
+      <c r="M2" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="56"/>
-      <c r="O2" s="56"/>
-      <c r="P2" s="56"/>
-      <c r="Q2" s="56"/>
-      <c r="R2" s="57"/>
-      <c r="AI2" s="55" t="s">
+      <c r="N2" s="47"/>
+      <c r="O2" s="47"/>
+      <c r="P2" s="47"/>
+      <c r="Q2" s="47"/>
+      <c r="R2" s="48"/>
+      <c r="AI2" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="AJ2" s="56"/>
-      <c r="AK2" s="56"/>
-      <c r="AL2" s="56"/>
-      <c r="AM2" s="56"/>
-      <c r="AN2" s="56"/>
-      <c r="AO2" s="57"/>
-      <c r="AU2" s="55" t="s">
+      <c r="AJ2" s="47"/>
+      <c r="AK2" s="47"/>
+      <c r="AL2" s="47"/>
+      <c r="AM2" s="47"/>
+      <c r="AN2" s="47"/>
+      <c r="AO2" s="48"/>
+      <c r="AU2" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="AV2" s="56"/>
-      <c r="AW2" s="56"/>
-      <c r="AX2" s="56"/>
-      <c r="AY2" s="56"/>
-      <c r="AZ2" s="56"/>
-      <c r="BA2" s="57"/>
+      <c r="AV2" s="47"/>
+      <c r="AW2" s="47"/>
+      <c r="AX2" s="47"/>
+      <c r="AY2" s="47"/>
+      <c r="AZ2" s="47"/>
+      <c r="BA2" s="48"/>
     </row>
     <row r="3" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="49" t="s">
+      <c r="A3" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="49"/>
-      <c r="C3" s="49"/>
-      <c r="D3" s="49"/>
-      <c r="E3" s="49"/>
-      <c r="F3" s="49"/>
-      <c r="G3" s="49"/>
-      <c r="AI3" s="42" t="s">
+      <c r="B3" s="42"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="42"/>
+      <c r="AI3" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="AJ3" s="43"/>
-      <c r="AK3" s="43"/>
-      <c r="AL3" s="43"/>
-      <c r="AM3" s="43"/>
-      <c r="AN3" s="43"/>
-      <c r="AO3" s="44"/>
-      <c r="AU3" s="49" t="s">
+      <c r="AJ3" s="54"/>
+      <c r="AK3" s="54"/>
+      <c r="AL3" s="54"/>
+      <c r="AM3" s="54"/>
+      <c r="AN3" s="54"/>
+      <c r="AO3" s="55"/>
+      <c r="AU3" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="AV3" s="49"/>
-      <c r="AW3" s="49"/>
-      <c r="AX3" s="49"/>
-      <c r="AY3" s="49"/>
-      <c r="AZ3" s="49"/>
-      <c r="BA3" s="49"/>
+      <c r="AV3" s="42"/>
+      <c r="AW3" s="42"/>
+      <c r="AX3" s="42"/>
+      <c r="AY3" s="42"/>
+      <c r="AZ3" s="42"/>
+      <c r="BA3" s="42"/>
     </row>
     <row r="4" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
@@ -1633,15 +1633,15 @@
       <c r="G4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="42" t="s">
+      <c r="M4" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="N4" s="43"/>
-      <c r="O4" s="43"/>
-      <c r="P4" s="43"/>
-      <c r="Q4" s="43"/>
-      <c r="R4" s="43"/>
-      <c r="S4" s="44"/>
+      <c r="N4" s="54"/>
+      <c r="O4" s="54"/>
+      <c r="P4" s="54"/>
+      <c r="Q4" s="54"/>
+      <c r="R4" s="54"/>
+      <c r="S4" s="55"/>
       <c r="AI4" s="3" t="s">
         <v>2</v>
       </c>
@@ -1968,11 +1968,11 @@
       <c r="G8" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="I8" s="50" t="s">
+      <c r="I8" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="J8" s="50"/>
-      <c r="K8" s="50"/>
+      <c r="J8" s="43"/>
+      <c r="K8" s="43"/>
       <c r="M8" s="8">
         <v>3</v>
       </c>
@@ -2015,11 +2015,11 @@
       <c r="AO8" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="AQ8" s="50" t="s">
+      <c r="AQ8" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="AR8" s="50"/>
-      <c r="AS8" s="50"/>
+      <c r="AR8" s="43"/>
+      <c r="AS8" s="43"/>
       <c r="AU8" s="38">
         <v>4</v>
       </c>
@@ -2279,15 +2279,15 @@
       <c r="BA11" s="6"/>
     </row>
     <row r="12" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="49" t="s">
+      <c r="A12" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="49"/>
-      <c r="C12" s="49"/>
-      <c r="D12" s="49"/>
-      <c r="E12" s="49"/>
-      <c r="F12" s="49"/>
-      <c r="G12" s="49"/>
+      <c r="B12" s="42"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="42"/>
       <c r="L12" s="12"/>
       <c r="M12" s="8" t="s">
         <v>12</v>
@@ -2313,69 +2313,69 @@
       <c r="T12" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AI12" s="49" t="s">
+      <c r="AI12" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AJ12" s="49"/>
-      <c r="AK12" s="49"/>
-      <c r="AL12" s="49"/>
-      <c r="AM12" s="49"/>
-      <c r="AN12" s="49"/>
-      <c r="AO12" s="49"/>
+      <c r="AJ12" s="42"/>
+      <c r="AK12" s="42"/>
+      <c r="AL12" s="42"/>
+      <c r="AM12" s="42"/>
+      <c r="AN12" s="42"/>
+      <c r="AO12" s="42"/>
       <c r="AQ12" s="12"/>
-      <c r="AU12" s="49" t="s">
+      <c r="AU12" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AV12" s="49"/>
-      <c r="AW12" s="49"/>
-      <c r="AX12" s="49"/>
-      <c r="AY12" s="49"/>
-      <c r="AZ12" s="49"/>
-      <c r="BA12" s="49"/>
+      <c r="AV12" s="42"/>
+      <c r="AW12" s="42"/>
+      <c r="AX12" s="42"/>
+      <c r="AY12" s="42"/>
+      <c r="AZ12" s="42"/>
+      <c r="BA12" s="42"/>
     </row>
     <row r="13" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="L13" s="12"/>
-      <c r="M13" s="42" t="s">
+      <c r="M13" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="N13" s="43"/>
-      <c r="O13" s="43"/>
-      <c r="P13" s="43"/>
-      <c r="Q13" s="43"/>
-      <c r="R13" s="43"/>
-      <c r="S13" s="44"/>
+      <c r="N13" s="54"/>
+      <c r="O13" s="54"/>
+      <c r="P13" s="54"/>
+      <c r="Q13" s="54"/>
+      <c r="R13" s="54"/>
+      <c r="S13" s="55"/>
       <c r="AQ13" s="12"/>
     </row>
     <row r="14" spans="1:54" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="48" t="s">
+      <c r="A14" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="48"/>
-      <c r="C14" s="48"/>
-      <c r="D14" s="48"/>
-      <c r="E14" s="48"/>
-      <c r="F14" s="48"/>
-      <c r="G14" s="48"/>
-      <c r="L14" s="54" t="s">
+      <c r="B14" s="45"/>
+      <c r="C14" s="45"/>
+      <c r="D14" s="45"/>
+      <c r="E14" s="45"/>
+      <c r="F14" s="45"/>
+      <c r="G14" s="45"/>
+      <c r="L14" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="M14" s="50"/>
-      <c r="N14" s="50"/>
-      <c r="AN14" s="50" t="s">
+      <c r="M14" s="43"/>
+      <c r="N14" s="43"/>
+      <c r="AN14" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="AO14" s="50"/>
-      <c r="AP14" s="50"/>
+      <c r="AO14" s="43"/>
+      <c r="AP14" s="43"/>
       <c r="AQ14" s="12"/>
-      <c r="AU14" s="48" t="s">
+      <c r="AU14" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="AV14" s="48"/>
-      <c r="AW14" s="48"/>
-      <c r="AX14" s="48"/>
-      <c r="AY14" s="48"/>
-      <c r="AZ14" s="48"/>
-      <c r="BA14" s="48"/>
+      <c r="AV14" s="45"/>
+      <c r="AW14" s="45"/>
+      <c r="AX14" s="45"/>
+      <c r="AY14" s="45"/>
+      <c r="AZ14" s="45"/>
+      <c r="BA14" s="45"/>
     </row>
     <row r="15" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
@@ -2603,19 +2603,19 @@
       <c r="G19" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="I19" s="50" t="s">
+      <c r="I19" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="J19" s="50"/>
-      <c r="K19" s="50"/>
+      <c r="J19" s="43"/>
+      <c r="K19" s="43"/>
       <c r="L19" s="12"/>
       <c r="O19" s="12"/>
       <c r="AN19" s="12"/>
-      <c r="AQ19" s="54" t="s">
+      <c r="AQ19" s="44" t="s">
         <v>31</v>
       </c>
-      <c r="AR19" s="50"/>
-      <c r="AS19" s="50"/>
+      <c r="AR19" s="43"/>
+      <c r="AS19" s="43"/>
       <c r="AU19" s="38">
         <v>4</v>
       </c>
@@ -2777,52 +2777,52 @@
       <c r="BA22" s="6"/>
     </row>
     <row r="23" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="49" t="s">
+      <c r="A23" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B23" s="49"/>
-      <c r="C23" s="49"/>
-      <c r="D23" s="49"/>
-      <c r="E23" s="49"/>
-      <c r="F23" s="49"/>
-      <c r="G23" s="49"/>
+      <c r="B23" s="42"/>
+      <c r="C23" s="42"/>
+      <c r="D23" s="42"/>
+      <c r="E23" s="42"/>
+      <c r="F23" s="42"/>
+      <c r="G23" s="42"/>
       <c r="O23" s="12"/>
       <c r="AN23" s="12"/>
-      <c r="AU23" s="49" t="s">
+      <c r="AU23" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AV23" s="49"/>
-      <c r="AW23" s="49"/>
-      <c r="AX23" s="49"/>
-      <c r="AY23" s="49"/>
-      <c r="AZ23" s="49"/>
-      <c r="BA23" s="49"/>
+      <c r="AV23" s="42"/>
+      <c r="AW23" s="42"/>
+      <c r="AX23" s="42"/>
+      <c r="AY23" s="42"/>
+      <c r="AZ23" s="42"/>
+      <c r="BA23" s="42"/>
     </row>
     <row r="24" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="O24" s="12"/>
       <c r="AN24" s="12"/>
     </row>
     <row r="25" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="49" t="s">
+      <c r="A25" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="49"/>
-      <c r="C25" s="49"/>
-      <c r="D25" s="49"/>
-      <c r="E25" s="49"/>
-      <c r="F25" s="49"/>
-      <c r="G25" s="49"/>
+      <c r="B25" s="42"/>
+      <c r="C25" s="42"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="42"/>
+      <c r="F25" s="42"/>
+      <c r="G25" s="42"/>
       <c r="O25" s="12"/>
       <c r="AN25" s="12"/>
-      <c r="AU25" s="49" t="s">
+      <c r="AU25" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="AV25" s="49"/>
-      <c r="AW25" s="49"/>
-      <c r="AX25" s="49"/>
-      <c r="AY25" s="49"/>
-      <c r="AZ25" s="49"/>
-      <c r="BA25" s="49"/>
+      <c r="AV25" s="42"/>
+      <c r="AW25" s="42"/>
+      <c r="AX25" s="42"/>
+      <c r="AY25" s="42"/>
+      <c r="AZ25" s="42"/>
+      <c r="BA25" s="42"/>
     </row>
     <row r="26" spans="1:54" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A26" s="20" t="s">
@@ -2846,28 +2846,28 @@
       <c r="G26" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="O26" s="54" t="s">
+      <c r="O26" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="P26" s="50"/>
-      <c r="Q26" s="50"/>
-      <c r="R26" s="50"/>
-      <c r="S26" s="50"/>
-      <c r="T26" s="50"/>
-      <c r="U26" s="50"/>
-      <c r="V26" s="50"/>
-      <c r="W26" s="50"/>
-      <c r="AE26" s="50" t="s">
+      <c r="P26" s="43"/>
+      <c r="Q26" s="43"/>
+      <c r="R26" s="43"/>
+      <c r="S26" s="43"/>
+      <c r="T26" s="43"/>
+      <c r="U26" s="43"/>
+      <c r="V26" s="43"/>
+      <c r="W26" s="43"/>
+      <c r="AE26" s="43" t="s">
         <v>38</v>
       </c>
-      <c r="AF26" s="50"/>
-      <c r="AG26" s="50"/>
-      <c r="AH26" s="50"/>
-      <c r="AI26" s="50"/>
-      <c r="AJ26" s="50"/>
-      <c r="AK26" s="50"/>
-      <c r="AL26" s="50"/>
-      <c r="AM26" s="58"/>
+      <c r="AF26" s="43"/>
+      <c r="AG26" s="43"/>
+      <c r="AH26" s="43"/>
+      <c r="AI26" s="43"/>
+      <c r="AJ26" s="43"/>
+      <c r="AK26" s="43"/>
+      <c r="AL26" s="43"/>
+      <c r="AM26" s="49"/>
       <c r="AU26" s="20" t="s">
         <v>2</v>
       </c>
@@ -2964,26 +2964,26 @@
         <v>54</v>
       </c>
       <c r="O28" s="12"/>
-      <c r="P28" s="42" t="s">
+      <c r="P28" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="Q28" s="43"/>
-      <c r="R28" s="43"/>
-      <c r="S28" s="43"/>
-      <c r="T28" s="43"/>
-      <c r="U28" s="43"/>
-      <c r="V28" s="44"/>
+      <c r="Q28" s="54"/>
+      <c r="R28" s="54"/>
+      <c r="S28" s="54"/>
+      <c r="T28" s="54"/>
+      <c r="U28" s="54"/>
+      <c r="V28" s="55"/>
       <c r="X28" s="12"/>
       <c r="AD28" s="13"/>
-      <c r="AF28" s="49" t="s">
+      <c r="AF28" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="AG28" s="49"/>
-      <c r="AH28" s="49"/>
-      <c r="AI28" s="49"/>
-      <c r="AJ28" s="49"/>
-      <c r="AK28" s="49"/>
-      <c r="AL28" s="49"/>
+      <c r="AG28" s="42"/>
+      <c r="AH28" s="42"/>
+      <c r="AI28" s="42"/>
+      <c r="AJ28" s="42"/>
+      <c r="AK28" s="42"/>
+      <c r="AL28" s="42"/>
       <c r="AN28" s="12"/>
       <c r="AU28" s="8">
         <v>2</v>
@@ -3119,11 +3119,11 @@
       <c r="G30" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="I30" s="50" t="s">
+      <c r="I30" s="43" t="s">
         <v>26</v>
       </c>
-      <c r="J30" s="50"/>
-      <c r="K30" s="50"/>
+      <c r="J30" s="43"/>
+      <c r="K30" s="43"/>
       <c r="O30" s="12"/>
       <c r="P30" s="7">
         <v>1</v>
@@ -3170,11 +3170,11 @@
         <v>52</v>
       </c>
       <c r="AN30" s="12"/>
-      <c r="AQ30" s="50" t="s">
+      <c r="AQ30" s="43" t="s">
         <v>38</v>
       </c>
-      <c r="AR30" s="50"/>
-      <c r="AS30" s="50"/>
+      <c r="AR30" s="43"/>
+      <c r="AS30" s="43"/>
       <c r="AU30" s="38">
         <v>4</v>
       </c>
@@ -3461,15 +3461,15 @@
       <c r="BA33" s="6"/>
     </row>
     <row r="34" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="49" t="s">
+      <c r="A34" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B34" s="49"/>
-      <c r="C34" s="49"/>
-      <c r="D34" s="49"/>
-      <c r="E34" s="49"/>
-      <c r="F34" s="49"/>
-      <c r="G34" s="49"/>
+      <c r="B34" s="42"/>
+      <c r="C34" s="42"/>
+      <c r="D34" s="42"/>
+      <c r="E34" s="42"/>
+      <c r="F34" s="42"/>
+      <c r="G34" s="42"/>
       <c r="L34" s="12"/>
       <c r="O34" s="12"/>
       <c r="P34" s="8" t="s">
@@ -3512,15 +3512,15 @@
       <c r="AL34" s="16"/>
       <c r="AN34" s="12"/>
       <c r="AQ34" s="12"/>
-      <c r="AU34" s="49" t="s">
+      <c r="AU34" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AV34" s="49"/>
-      <c r="AW34" s="49"/>
-      <c r="AX34" s="49"/>
-      <c r="AY34" s="49"/>
-      <c r="AZ34" s="49"/>
-      <c r="BA34" s="49"/>
+      <c r="AV34" s="42"/>
+      <c r="AW34" s="42"/>
+      <c r="AX34" s="42"/>
+      <c r="AY34" s="42"/>
+      <c r="AZ34" s="42"/>
+      <c r="BA34" s="42"/>
     </row>
     <row r="35" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="L35" s="12"/>
@@ -3561,20 +3561,20 @@
       <c r="AQ35" s="12"/>
     </row>
     <row r="36" spans="1:54" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="48" t="s">
+      <c r="A36" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="B36" s="48"/>
-      <c r="C36" s="48"/>
-      <c r="D36" s="48"/>
-      <c r="E36" s="48"/>
-      <c r="F36" s="48"/>
-      <c r="G36" s="48"/>
-      <c r="L36" s="54" t="s">
+      <c r="B36" s="45"/>
+      <c r="C36" s="45"/>
+      <c r="D36" s="45"/>
+      <c r="E36" s="45"/>
+      <c r="F36" s="45"/>
+      <c r="G36" s="45"/>
+      <c r="L36" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="M36" s="50"/>
-      <c r="N36" s="50"/>
+      <c r="M36" s="43"/>
+      <c r="N36" s="43"/>
       <c r="O36" s="12"/>
       <c r="P36" s="8" t="s">
         <v>12</v>
@@ -3608,21 +3608,21 @@
       </c>
       <c r="AK36" s="36"/>
       <c r="AL36" s="37"/>
-      <c r="AN36" s="54" t="s">
+      <c r="AN36" s="44" t="s">
         <v>38</v>
       </c>
-      <c r="AO36" s="50"/>
-      <c r="AP36" s="50"/>
+      <c r="AO36" s="43"/>
+      <c r="AP36" s="43"/>
       <c r="AQ36" s="12"/>
-      <c r="AU36" s="48" t="s">
+      <c r="AU36" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="AV36" s="48"/>
-      <c r="AW36" s="48"/>
-      <c r="AX36" s="48"/>
-      <c r="AY36" s="48"/>
-      <c r="AZ36" s="48"/>
-      <c r="BA36" s="48"/>
+      <c r="AV36" s="45"/>
+      <c r="AW36" s="45"/>
+      <c r="AX36" s="45"/>
+      <c r="AY36" s="45"/>
+      <c r="AZ36" s="45"/>
+      <c r="BA36" s="45"/>
     </row>
     <row r="37" spans="1:54" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A37" s="20" t="s">
@@ -3647,31 +3647,31 @@
         <v>9</v>
       </c>
       <c r="L37" s="12"/>
-      <c r="P37" s="45" t="s">
+      <c r="P37" s="56" t="s">
         <v>13</v>
       </c>
-      <c r="Q37" s="46"/>
-      <c r="R37" s="46"/>
-      <c r="S37" s="46"/>
-      <c r="T37" s="46"/>
-      <c r="U37" s="46"/>
-      <c r="V37" s="47"/>
-      <c r="X37" s="54"/>
-      <c r="Y37" s="50"/>
-      <c r="Z37" s="50"/>
-      <c r="AA37" s="50"/>
-      <c r="AB37" s="50"/>
-      <c r="AC37" s="50"/>
-      <c r="AD37" s="58"/>
-      <c r="AF37" s="49" t="s">
+      <c r="Q37" s="57"/>
+      <c r="R37" s="57"/>
+      <c r="S37" s="57"/>
+      <c r="T37" s="57"/>
+      <c r="U37" s="57"/>
+      <c r="V37" s="58"/>
+      <c r="X37" s="44"/>
+      <c r="Y37" s="43"/>
+      <c r="Z37" s="43"/>
+      <c r="AA37" s="43"/>
+      <c r="AB37" s="43"/>
+      <c r="AC37" s="43"/>
+      <c r="AD37" s="49"/>
+      <c r="AF37" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AG37" s="49"/>
-      <c r="AH37" s="49"/>
-      <c r="AI37" s="49"/>
-      <c r="AJ37" s="49"/>
-      <c r="AK37" s="49"/>
-      <c r="AL37" s="49"/>
+      <c r="AG37" s="42"/>
+      <c r="AH37" s="42"/>
+      <c r="AI37" s="42"/>
+      <c r="AJ37" s="42"/>
+      <c r="AK37" s="42"/>
+      <c r="AL37" s="42"/>
       <c r="AQ37" s="12"/>
       <c r="AU37" s="3" t="s">
         <v>2</v>
@@ -3764,33 +3764,33 @@
         <v>53</v>
       </c>
       <c r="L39" s="12"/>
-      <c r="M39" s="42" t="s">
+      <c r="M39" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="N39" s="43"/>
-      <c r="O39" s="43"/>
-      <c r="P39" s="43"/>
-      <c r="Q39" s="43"/>
-      <c r="R39" s="43"/>
-      <c r="S39" s="44"/>
-      <c r="X39" s="49" t="s">
+      <c r="N39" s="54"/>
+      <c r="O39" s="54"/>
+      <c r="P39" s="54"/>
+      <c r="Q39" s="54"/>
+      <c r="R39" s="54"/>
+      <c r="S39" s="55"/>
+      <c r="X39" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="Y39" s="49"/>
-      <c r="Z39" s="49"/>
-      <c r="AA39" s="49"/>
-      <c r="AB39" s="49"/>
-      <c r="AC39" s="49"/>
-      <c r="AD39" s="49"/>
-      <c r="AI39" s="42" t="s">
+      <c r="Y39" s="42"/>
+      <c r="Z39" s="42"/>
+      <c r="AA39" s="42"/>
+      <c r="AB39" s="42"/>
+      <c r="AC39" s="42"/>
+      <c r="AD39" s="42"/>
+      <c r="AI39" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="AJ39" s="43"/>
-      <c r="AK39" s="43"/>
-      <c r="AL39" s="43"/>
-      <c r="AM39" s="43"/>
-      <c r="AN39" s="43"/>
-      <c r="AO39" s="44"/>
+      <c r="AJ39" s="54"/>
+      <c r="AK39" s="54"/>
+      <c r="AL39" s="54"/>
+      <c r="AM39" s="54"/>
+      <c r="AN39" s="54"/>
+      <c r="AO39" s="55"/>
       <c r="AQ39" s="12"/>
       <c r="AU39" s="8">
         <v>2</v>
@@ -3945,11 +3945,11 @@
       <c r="G41" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="I41" s="50" t="s">
+      <c r="I41" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="J41" s="50"/>
-      <c r="K41" s="50"/>
+      <c r="J41" s="43"/>
+      <c r="K41" s="43"/>
       <c r="L41" s="12"/>
       <c r="M41" s="7">
         <v>1</v>
@@ -3981,12 +3981,18 @@
       <c r="Z41" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="AA41" s="24"/>
+      <c r="AA41" s="24">
+        <v>5</v>
+      </c>
       <c r="AB41" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="AC41" s="24"/>
-      <c r="AD41" s="25"/>
+      <c r="AC41" s="24">
+        <v>4</v>
+      </c>
+      <c r="AD41" s="25" t="s">
+        <v>52</v>
+      </c>
       <c r="AI41" s="7">
         <v>1</v>
       </c>
@@ -4008,11 +4014,11 @@
       <c r="AO41" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="AQ41" s="54" t="s">
+      <c r="AQ41" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="AR41" s="50"/>
-      <c r="AS41" s="50"/>
+      <c r="AR41" s="43"/>
+      <c r="AS41" s="43"/>
       <c r="AU41" s="38">
         <v>4</v>
       </c>
@@ -4336,15 +4342,15 @@
       <c r="BA44" s="6"/>
     </row>
     <row r="45" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="49" t="s">
+      <c r="A45" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B45" s="49"/>
-      <c r="C45" s="49"/>
-      <c r="D45" s="49"/>
-      <c r="E45" s="49"/>
-      <c r="F45" s="49"/>
-      <c r="G45" s="49"/>
+      <c r="B45" s="42"/>
+      <c r="C45" s="42"/>
+      <c r="D45" s="42"/>
+      <c r="E45" s="42"/>
+      <c r="F45" s="42"/>
+      <c r="G45" s="42"/>
       <c r="M45" s="8" t="s">
         <v>11</v>
       </c>
@@ -4399,15 +4405,15 @@
       <c r="AP45" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AU45" s="49" t="s">
+      <c r="AU45" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AV45" s="49"/>
-      <c r="AW45" s="49"/>
-      <c r="AX45" s="49"/>
-      <c r="AY45" s="49"/>
-      <c r="AZ45" s="49"/>
-      <c r="BA45" s="49"/>
+      <c r="AV45" s="42"/>
+      <c r="AW45" s="42"/>
+      <c r="AX45" s="42"/>
+      <c r="AY45" s="42"/>
+      <c r="AZ45" s="42"/>
+      <c r="BA45" s="42"/>
     </row>
     <row r="46" spans="1:54" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="M46" s="8" t="s">
@@ -4510,49 +4516,61 @@
       <c r="AO47" s="6"/>
     </row>
     <row r="48" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="M48" s="42" t="s">
+      <c r="M48" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="N48" s="43"/>
-      <c r="O48" s="43"/>
-      <c r="P48" s="43"/>
-      <c r="Q48" s="43"/>
-      <c r="R48" s="43"/>
-      <c r="S48" s="44"/>
-      <c r="X48" s="49" t="s">
+      <c r="N48" s="54"/>
+      <c r="O48" s="54"/>
+      <c r="P48" s="54"/>
+      <c r="Q48" s="54"/>
+      <c r="R48" s="54"/>
+      <c r="S48" s="55"/>
+      <c r="X48" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="Y48" s="49"/>
-      <c r="Z48" s="49"/>
-      <c r="AA48" s="49"/>
-      <c r="AB48" s="49"/>
-      <c r="AC48" s="49"/>
-      <c r="AD48" s="49"/>
-      <c r="AI48" s="49" t="s">
+      <c r="Y48" s="42"/>
+      <c r="Z48" s="42"/>
+      <c r="AA48" s="42"/>
+      <c r="AB48" s="42"/>
+      <c r="AC48" s="42"/>
+      <c r="AD48" s="42"/>
+      <c r="AI48" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AJ48" s="49"/>
-      <c r="AK48" s="49"/>
-      <c r="AL48" s="49"/>
-      <c r="AM48" s="49"/>
-      <c r="AN48" s="49"/>
-      <c r="AO48" s="49"/>
+      <c r="AJ48" s="42"/>
+      <c r="AK48" s="42"/>
+      <c r="AL48" s="42"/>
+      <c r="AM48" s="42"/>
+      <c r="AN48" s="42"/>
+      <c r="AO48" s="42"/>
     </row>
     <row r="49" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="AU45:BA45"/>
-    <mergeCell ref="AF28:AL28"/>
-    <mergeCell ref="AF37:AL37"/>
-    <mergeCell ref="AQ30:AS30"/>
-    <mergeCell ref="AQ41:AS41"/>
-    <mergeCell ref="AU34:BA34"/>
-    <mergeCell ref="AU36:BA36"/>
-    <mergeCell ref="AU2:BA2"/>
-    <mergeCell ref="AU3:BA3"/>
-    <mergeCell ref="AU12:BA12"/>
-    <mergeCell ref="AU14:BA14"/>
-    <mergeCell ref="AU23:BA23"/>
+    <mergeCell ref="M48:S48"/>
+    <mergeCell ref="M39:S39"/>
+    <mergeCell ref="P37:V37"/>
+    <mergeCell ref="P28:V28"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A1:U1"/>
+    <mergeCell ref="O26:W26"/>
+    <mergeCell ref="I41:K41"/>
+    <mergeCell ref="L14:N14"/>
+    <mergeCell ref="L36:N36"/>
+    <mergeCell ref="M2:R2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="M4:S4"/>
+    <mergeCell ref="M13:S13"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="A25:G25"/>
     <mergeCell ref="X37:AD37"/>
     <mergeCell ref="AE26:AM26"/>
     <mergeCell ref="Z1:AB1"/>
@@ -4569,30 +4587,18 @@
     <mergeCell ref="AN36:AP36"/>
     <mergeCell ref="AQ8:AS8"/>
     <mergeCell ref="AQ19:AS19"/>
-    <mergeCell ref="A1:U1"/>
-    <mergeCell ref="O26:W26"/>
-    <mergeCell ref="I41:K41"/>
-    <mergeCell ref="L14:N14"/>
-    <mergeCell ref="L36:N36"/>
-    <mergeCell ref="M2:R2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="M4:S4"/>
-    <mergeCell ref="M13:S13"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A23:G23"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="M48:S48"/>
-    <mergeCell ref="M39:S39"/>
-    <mergeCell ref="P37:V37"/>
-    <mergeCell ref="P28:V28"/>
-    <mergeCell ref="A36:G36"/>
-    <mergeCell ref="A45:G45"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="AU2:BA2"/>
+    <mergeCell ref="AU3:BA3"/>
+    <mergeCell ref="AU12:BA12"/>
+    <mergeCell ref="AU14:BA14"/>
+    <mergeCell ref="AU23:BA23"/>
+    <mergeCell ref="AU45:BA45"/>
+    <mergeCell ref="AF28:AL28"/>
+    <mergeCell ref="AF37:AL37"/>
+    <mergeCell ref="AQ30:AS30"/>
+    <mergeCell ref="AQ41:AS41"/>
+    <mergeCell ref="AU34:BA34"/>
+    <mergeCell ref="AU36:BA36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/2025_2026/Playoffs/Brackets.xlsx
+++ b/2025_2026/Playoffs/Brackets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\NHLStats\2025_2026\Playoffs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{873CEA2B-592E-4AC1-A99E-52BB2274762D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3C0C9CB-3E71-4242-A086-6DE688D120A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="1590" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="100">
   <si>
     <t>Eastern Conference Playoff Teams</t>
   </si>
@@ -704,18 +704,45 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -728,40 +755,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1131,18 +1131,18 @@
     </row>
     <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="11" spans="1:7" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="59" t="s">
+      <c r="A11" s="61" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="59"/>
-      <c r="C11" s="59" t="s">
+      <c r="B11" s="61"/>
+      <c r="C11" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="59"/>
-      <c r="E11" s="59" t="s">
+      <c r="D11" s="61"/>
+      <c r="E11" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="59"/>
+      <c r="F11" s="61"/>
       <c r="G11" s="4" t="s">
         <v>18</v>
       </c>
@@ -1171,18 +1171,18 @@
       </c>
     </row>
     <row r="13" spans="1:7" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="60" t="s">
+      <c r="A13" s="59" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="61"/>
-      <c r="C13" s="60" t="s">
+      <c r="B13" s="60"/>
+      <c r="C13" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="D13" s="61"/>
-      <c r="E13" s="60" t="s">
+      <c r="D13" s="60"/>
+      <c r="E13" s="59" t="s">
         <v>17</v>
       </c>
-      <c r="F13" s="61"/>
+      <c r="F13" s="60"/>
       <c r="G13" s="5" t="s">
         <v>26</v>
       </c>
@@ -1231,14 +1231,14 @@
       </c>
     </row>
     <row r="16" spans="1:7" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="60" t="s">
+      <c r="A16" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="61"/>
-      <c r="C16" s="60" t="s">
+      <c r="B16" s="60"/>
+      <c r="C16" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="61"/>
+      <c r="D16" s="60"/>
     </row>
     <row r="17" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
@@ -1269,10 +1269,10 @@
       </c>
     </row>
     <row r="19" spans="1:4" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="60" t="s">
+      <c r="A19" s="59" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="61"/>
+      <c r="B19" s="60"/>
     </row>
     <row r="20" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
@@ -1291,10 +1291,10 @@
       </c>
     </row>
     <row r="22" spans="1:4" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="60" t="s">
+      <c r="A22" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="61"/>
+      <c r="B22" s="60"/>
     </row>
     <row r="23" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
@@ -1379,16 +1379,16 @@
     <sortCondition ref="B2:B9"/>
   </sortState>
   <mergeCells count="10">
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A16:B16"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A16:B16"/>
   </mergeCells>
   <dataValidations count="16">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C14" xr:uid="{2C3D9587-ABAE-4E3F-8B22-396DF812BF02}">
@@ -1492,124 +1492,124 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:54" ht="27" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
-      <c r="I1" s="51"/>
-      <c r="J1" s="51"/>
-      <c r="K1" s="51"/>
-      <c r="L1" s="51"/>
-      <c r="M1" s="51"/>
-      <c r="N1" s="51"/>
-      <c r="O1" s="51"/>
-      <c r="P1" s="51"/>
-      <c r="Q1" s="51"/>
-      <c r="R1" s="51"/>
-      <c r="S1" s="51"/>
-      <c r="T1" s="51"/>
-      <c r="U1" s="52"/>
-      <c r="Z1" s="50" t="s">
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="52"/>
+      <c r="M1" s="52"/>
+      <c r="N1" s="52"/>
+      <c r="O1" s="52"/>
+      <c r="P1" s="52"/>
+      <c r="Q1" s="52"/>
+      <c r="R1" s="52"/>
+      <c r="S1" s="52"/>
+      <c r="T1" s="52"/>
+      <c r="U1" s="53"/>
+      <c r="Z1" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="AA1" s="51"/>
-      <c r="AB1" s="52"/>
-      <c r="AF1" s="50" t="s">
+      <c r="AA1" s="52"/>
+      <c r="AB1" s="53"/>
+      <c r="AF1" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="AG1" s="51"/>
-      <c r="AH1" s="51"/>
-      <c r="AI1" s="51"/>
-      <c r="AJ1" s="51"/>
-      <c r="AK1" s="51"/>
-      <c r="AL1" s="51"/>
-      <c r="AM1" s="51"/>
-      <c r="AN1" s="51"/>
-      <c r="AO1" s="51"/>
-      <c r="AP1" s="51"/>
-      <c r="AQ1" s="51"/>
-      <c r="AR1" s="51"/>
-      <c r="AS1" s="51"/>
-      <c r="AT1" s="51"/>
-      <c r="AU1" s="51"/>
-      <c r="AV1" s="51"/>
-      <c r="AW1" s="51"/>
-      <c r="AX1" s="51"/>
-      <c r="AY1" s="51"/>
-      <c r="AZ1" s="51"/>
-      <c r="BA1" s="52"/>
+      <c r="AG1" s="52"/>
+      <c r="AH1" s="52"/>
+      <c r="AI1" s="52"/>
+      <c r="AJ1" s="52"/>
+      <c r="AK1" s="52"/>
+      <c r="AL1" s="52"/>
+      <c r="AM1" s="52"/>
+      <c r="AN1" s="52"/>
+      <c r="AO1" s="52"/>
+      <c r="AP1" s="52"/>
+      <c r="AQ1" s="52"/>
+      <c r="AR1" s="52"/>
+      <c r="AS1" s="52"/>
+      <c r="AT1" s="52"/>
+      <c r="AU1" s="52"/>
+      <c r="AV1" s="52"/>
+      <c r="AW1" s="52"/>
+      <c r="AX1" s="52"/>
+      <c r="AY1" s="52"/>
+      <c r="AZ1" s="52"/>
+      <c r="BA1" s="53"/>
     </row>
     <row r="2" spans="1:54" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="48"/>
-      <c r="M2" s="46" t="s">
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="57"/>
+      <c r="M2" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="47"/>
-      <c r="O2" s="47"/>
-      <c r="P2" s="47"/>
-      <c r="Q2" s="47"/>
-      <c r="R2" s="48"/>
-      <c r="AI2" s="46" t="s">
+      <c r="N2" s="56"/>
+      <c r="O2" s="56"/>
+      <c r="P2" s="56"/>
+      <c r="Q2" s="56"/>
+      <c r="R2" s="57"/>
+      <c r="AI2" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="AJ2" s="47"/>
-      <c r="AK2" s="47"/>
-      <c r="AL2" s="47"/>
-      <c r="AM2" s="47"/>
-      <c r="AN2" s="47"/>
-      <c r="AO2" s="48"/>
-      <c r="AU2" s="46" t="s">
+      <c r="AJ2" s="56"/>
+      <c r="AK2" s="56"/>
+      <c r="AL2" s="56"/>
+      <c r="AM2" s="56"/>
+      <c r="AN2" s="56"/>
+      <c r="AO2" s="57"/>
+      <c r="AU2" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="AV2" s="47"/>
-      <c r="AW2" s="47"/>
-      <c r="AX2" s="47"/>
-      <c r="AY2" s="47"/>
-      <c r="AZ2" s="47"/>
-      <c r="BA2" s="48"/>
+      <c r="AV2" s="56"/>
+      <c r="AW2" s="56"/>
+      <c r="AX2" s="56"/>
+      <c r="AY2" s="56"/>
+      <c r="AZ2" s="56"/>
+      <c r="BA2" s="57"/>
     </row>
     <row r="3" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="42" t="s">
+      <c r="A3" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="42"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="42"/>
-      <c r="AI3" s="53" t="s">
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="AI3" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="AJ3" s="54"/>
-      <c r="AK3" s="54"/>
-      <c r="AL3" s="54"/>
-      <c r="AM3" s="54"/>
-      <c r="AN3" s="54"/>
-      <c r="AO3" s="55"/>
-      <c r="AU3" s="42" t="s">
+      <c r="AJ3" s="43"/>
+      <c r="AK3" s="43"/>
+      <c r="AL3" s="43"/>
+      <c r="AM3" s="43"/>
+      <c r="AN3" s="43"/>
+      <c r="AO3" s="44"/>
+      <c r="AU3" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="AV3" s="42"/>
-      <c r="AW3" s="42"/>
-      <c r="AX3" s="42"/>
-      <c r="AY3" s="42"/>
-      <c r="AZ3" s="42"/>
-      <c r="BA3" s="42"/>
+      <c r="AV3" s="49"/>
+      <c r="AW3" s="49"/>
+      <c r="AX3" s="49"/>
+      <c r="AY3" s="49"/>
+      <c r="AZ3" s="49"/>
+      <c r="BA3" s="49"/>
     </row>
     <row r="4" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
@@ -1633,15 +1633,15 @@
       <c r="G4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="53" t="s">
+      <c r="M4" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="N4" s="54"/>
-      <c r="O4" s="54"/>
-      <c r="P4" s="54"/>
-      <c r="Q4" s="54"/>
-      <c r="R4" s="54"/>
-      <c r="S4" s="55"/>
+      <c r="N4" s="43"/>
+      <c r="O4" s="43"/>
+      <c r="P4" s="43"/>
+      <c r="Q4" s="43"/>
+      <c r="R4" s="43"/>
+      <c r="S4" s="44"/>
       <c r="AI4" s="3" t="s">
         <v>2</v>
       </c>
@@ -1968,11 +1968,11 @@
       <c r="G8" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="I8" s="43" t="s">
+      <c r="I8" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="J8" s="43"/>
-      <c r="K8" s="43"/>
+      <c r="J8" s="50"/>
+      <c r="K8" s="50"/>
       <c r="M8" s="8">
         <v>3</v>
       </c>
@@ -2015,11 +2015,11 @@
       <c r="AO8" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="AQ8" s="43" t="s">
+      <c r="AQ8" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="AR8" s="43"/>
-      <c r="AS8" s="43"/>
+      <c r="AR8" s="50"/>
+      <c r="AS8" s="50"/>
       <c r="AU8" s="38">
         <v>4</v>
       </c>
@@ -2279,15 +2279,15 @@
       <c r="BA11" s="6"/>
     </row>
     <row r="12" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="42" t="s">
+      <c r="A12" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="42"/>
-      <c r="C12" s="42"/>
-      <c r="D12" s="42"/>
-      <c r="E12" s="42"/>
-      <c r="F12" s="42"/>
-      <c r="G12" s="42"/>
+      <c r="B12" s="49"/>
+      <c r="C12" s="49"/>
+      <c r="D12" s="49"/>
+      <c r="E12" s="49"/>
+      <c r="F12" s="49"/>
+      <c r="G12" s="49"/>
       <c r="L12" s="12"/>
       <c r="M12" s="8" t="s">
         <v>12</v>
@@ -2313,69 +2313,69 @@
       <c r="T12" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AI12" s="42" t="s">
+      <c r="AI12" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AJ12" s="42"/>
-      <c r="AK12" s="42"/>
-      <c r="AL12" s="42"/>
-      <c r="AM12" s="42"/>
-      <c r="AN12" s="42"/>
-      <c r="AO12" s="42"/>
+      <c r="AJ12" s="49"/>
+      <c r="AK12" s="49"/>
+      <c r="AL12" s="49"/>
+      <c r="AM12" s="49"/>
+      <c r="AN12" s="49"/>
+      <c r="AO12" s="49"/>
       <c r="AQ12" s="12"/>
-      <c r="AU12" s="42" t="s">
+      <c r="AU12" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AV12" s="42"/>
-      <c r="AW12" s="42"/>
-      <c r="AX12" s="42"/>
-      <c r="AY12" s="42"/>
-      <c r="AZ12" s="42"/>
-      <c r="BA12" s="42"/>
+      <c r="AV12" s="49"/>
+      <c r="AW12" s="49"/>
+      <c r="AX12" s="49"/>
+      <c r="AY12" s="49"/>
+      <c r="AZ12" s="49"/>
+      <c r="BA12" s="49"/>
     </row>
     <row r="13" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="L13" s="12"/>
-      <c r="M13" s="53" t="s">
+      <c r="M13" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="N13" s="54"/>
-      <c r="O13" s="54"/>
-      <c r="P13" s="54"/>
-      <c r="Q13" s="54"/>
-      <c r="R13" s="54"/>
-      <c r="S13" s="55"/>
+      <c r="N13" s="43"/>
+      <c r="O13" s="43"/>
+      <c r="P13" s="43"/>
+      <c r="Q13" s="43"/>
+      <c r="R13" s="43"/>
+      <c r="S13" s="44"/>
       <c r="AQ13" s="12"/>
     </row>
     <row r="14" spans="1:54" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="45" t="s">
+      <c r="A14" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="45"/>
-      <c r="C14" s="45"/>
-      <c r="D14" s="45"/>
-      <c r="E14" s="45"/>
-      <c r="F14" s="45"/>
-      <c r="G14" s="45"/>
-      <c r="L14" s="44" t="s">
+      <c r="B14" s="48"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="48"/>
+      <c r="E14" s="48"/>
+      <c r="F14" s="48"/>
+      <c r="G14" s="48"/>
+      <c r="L14" s="54" t="s">
         <v>32</v>
       </c>
-      <c r="M14" s="43"/>
-      <c r="N14" s="43"/>
-      <c r="AN14" s="43" t="s">
+      <c r="M14" s="50"/>
+      <c r="N14" s="50"/>
+      <c r="AN14" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="AO14" s="43"/>
-      <c r="AP14" s="43"/>
+      <c r="AO14" s="50"/>
+      <c r="AP14" s="50"/>
       <c r="AQ14" s="12"/>
-      <c r="AU14" s="45" t="s">
+      <c r="AU14" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="AV14" s="45"/>
-      <c r="AW14" s="45"/>
-      <c r="AX14" s="45"/>
-      <c r="AY14" s="45"/>
-      <c r="AZ14" s="45"/>
-      <c r="BA14" s="45"/>
+      <c r="AV14" s="48"/>
+      <c r="AW14" s="48"/>
+      <c r="AX14" s="48"/>
+      <c r="AY14" s="48"/>
+      <c r="AZ14" s="48"/>
+      <c r="BA14" s="48"/>
     </row>
     <row r="15" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
@@ -2603,19 +2603,19 @@
       <c r="G19" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="I19" s="43" t="s">
+      <c r="I19" s="50" t="s">
         <v>32</v>
       </c>
-      <c r="J19" s="43"/>
-      <c r="K19" s="43"/>
+      <c r="J19" s="50"/>
+      <c r="K19" s="50"/>
       <c r="L19" s="12"/>
       <c r="O19" s="12"/>
       <c r="AN19" s="12"/>
-      <c r="AQ19" s="44" t="s">
+      <c r="AQ19" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="AR19" s="43"/>
-      <c r="AS19" s="43"/>
+      <c r="AR19" s="50"/>
+      <c r="AS19" s="50"/>
       <c r="AU19" s="38">
         <v>4</v>
       </c>
@@ -2777,52 +2777,52 @@
       <c r="BA22" s="6"/>
     </row>
     <row r="23" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="42" t="s">
+      <c r="A23" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="B23" s="42"/>
-      <c r="C23" s="42"/>
-      <c r="D23" s="42"/>
-      <c r="E23" s="42"/>
-      <c r="F23" s="42"/>
-      <c r="G23" s="42"/>
+      <c r="B23" s="49"/>
+      <c r="C23" s="49"/>
+      <c r="D23" s="49"/>
+      <c r="E23" s="49"/>
+      <c r="F23" s="49"/>
+      <c r="G23" s="49"/>
       <c r="O23" s="12"/>
       <c r="AN23" s="12"/>
-      <c r="AU23" s="42" t="s">
+      <c r="AU23" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AV23" s="42"/>
-      <c r="AW23" s="42"/>
-      <c r="AX23" s="42"/>
-      <c r="AY23" s="42"/>
-      <c r="AZ23" s="42"/>
-      <c r="BA23" s="42"/>
+      <c r="AV23" s="49"/>
+      <c r="AW23" s="49"/>
+      <c r="AX23" s="49"/>
+      <c r="AY23" s="49"/>
+      <c r="AZ23" s="49"/>
+      <c r="BA23" s="49"/>
     </row>
     <row r="24" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="O24" s="12"/>
       <c r="AN24" s="12"/>
     </row>
     <row r="25" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="42" t="s">
+      <c r="A25" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="42"/>
-      <c r="C25" s="42"/>
-      <c r="D25" s="42"/>
-      <c r="E25" s="42"/>
-      <c r="F25" s="42"/>
-      <c r="G25" s="42"/>
+      <c r="B25" s="49"/>
+      <c r="C25" s="49"/>
+      <c r="D25" s="49"/>
+      <c r="E25" s="49"/>
+      <c r="F25" s="49"/>
+      <c r="G25" s="49"/>
       <c r="O25" s="12"/>
       <c r="AN25" s="12"/>
-      <c r="AU25" s="42" t="s">
+      <c r="AU25" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="AV25" s="42"/>
-      <c r="AW25" s="42"/>
-      <c r="AX25" s="42"/>
-      <c r="AY25" s="42"/>
-      <c r="AZ25" s="42"/>
-      <c r="BA25" s="42"/>
+      <c r="AV25" s="49"/>
+      <c r="AW25" s="49"/>
+      <c r="AX25" s="49"/>
+      <c r="AY25" s="49"/>
+      <c r="AZ25" s="49"/>
+      <c r="BA25" s="49"/>
     </row>
     <row r="26" spans="1:54" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A26" s="20" t="s">
@@ -2846,28 +2846,28 @@
       <c r="G26" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="O26" s="44" t="s">
+      <c r="O26" s="54" t="s">
         <v>26</v>
       </c>
-      <c r="P26" s="43"/>
-      <c r="Q26" s="43"/>
-      <c r="R26" s="43"/>
-      <c r="S26" s="43"/>
-      <c r="T26" s="43"/>
-      <c r="U26" s="43"/>
-      <c r="V26" s="43"/>
-      <c r="W26" s="43"/>
-      <c r="AE26" s="43" t="s">
+      <c r="P26" s="50"/>
+      <c r="Q26" s="50"/>
+      <c r="R26" s="50"/>
+      <c r="S26" s="50"/>
+      <c r="T26" s="50"/>
+      <c r="U26" s="50"/>
+      <c r="V26" s="50"/>
+      <c r="W26" s="50"/>
+      <c r="AE26" s="50" t="s">
         <v>38</v>
       </c>
-      <c r="AF26" s="43"/>
-      <c r="AG26" s="43"/>
-      <c r="AH26" s="43"/>
-      <c r="AI26" s="43"/>
-      <c r="AJ26" s="43"/>
-      <c r="AK26" s="43"/>
-      <c r="AL26" s="43"/>
-      <c r="AM26" s="49"/>
+      <c r="AF26" s="50"/>
+      <c r="AG26" s="50"/>
+      <c r="AH26" s="50"/>
+      <c r="AI26" s="50"/>
+      <c r="AJ26" s="50"/>
+      <c r="AK26" s="50"/>
+      <c r="AL26" s="50"/>
+      <c r="AM26" s="58"/>
       <c r="AU26" s="20" t="s">
         <v>2</v>
       </c>
@@ -2964,26 +2964,26 @@
         <v>54</v>
       </c>
       <c r="O28" s="12"/>
-      <c r="P28" s="53" t="s">
+      <c r="P28" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="Q28" s="54"/>
-      <c r="R28" s="54"/>
-      <c r="S28" s="54"/>
-      <c r="T28" s="54"/>
-      <c r="U28" s="54"/>
-      <c r="V28" s="55"/>
+      <c r="Q28" s="43"/>
+      <c r="R28" s="43"/>
+      <c r="S28" s="43"/>
+      <c r="T28" s="43"/>
+      <c r="U28" s="43"/>
+      <c r="V28" s="44"/>
       <c r="X28" s="12"/>
       <c r="AD28" s="13"/>
-      <c r="AF28" s="42" t="s">
+      <c r="AF28" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="AG28" s="42"/>
-      <c r="AH28" s="42"/>
-      <c r="AI28" s="42"/>
-      <c r="AJ28" s="42"/>
-      <c r="AK28" s="42"/>
-      <c r="AL28" s="42"/>
+      <c r="AG28" s="49"/>
+      <c r="AH28" s="49"/>
+      <c r="AI28" s="49"/>
+      <c r="AJ28" s="49"/>
+      <c r="AK28" s="49"/>
+      <c r="AL28" s="49"/>
       <c r="AN28" s="12"/>
       <c r="AU28" s="8">
         <v>2</v>
@@ -3119,11 +3119,11 @@
       <c r="G30" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="I30" s="43" t="s">
+      <c r="I30" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="J30" s="43"/>
-      <c r="K30" s="43"/>
+      <c r="J30" s="50"/>
+      <c r="K30" s="50"/>
       <c r="O30" s="12"/>
       <c r="P30" s="7">
         <v>1</v>
@@ -3170,11 +3170,11 @@
         <v>52</v>
       </c>
       <c r="AN30" s="12"/>
-      <c r="AQ30" s="43" t="s">
+      <c r="AQ30" s="50" t="s">
         <v>38</v>
       </c>
-      <c r="AR30" s="43"/>
-      <c r="AS30" s="43"/>
+      <c r="AR30" s="50"/>
+      <c r="AS30" s="50"/>
       <c r="AU30" s="38">
         <v>4</v>
       </c>
@@ -3461,15 +3461,15 @@
       <c r="BA33" s="6"/>
     </row>
     <row r="34" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="42" t="s">
+      <c r="A34" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="B34" s="42"/>
-      <c r="C34" s="42"/>
-      <c r="D34" s="42"/>
-      <c r="E34" s="42"/>
-      <c r="F34" s="42"/>
-      <c r="G34" s="42"/>
+      <c r="B34" s="49"/>
+      <c r="C34" s="49"/>
+      <c r="D34" s="49"/>
+      <c r="E34" s="49"/>
+      <c r="F34" s="49"/>
+      <c r="G34" s="49"/>
       <c r="L34" s="12"/>
       <c r="O34" s="12"/>
       <c r="P34" s="8" t="s">
@@ -3512,15 +3512,15 @@
       <c r="AL34" s="16"/>
       <c r="AN34" s="12"/>
       <c r="AQ34" s="12"/>
-      <c r="AU34" s="42" t="s">
+      <c r="AU34" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AV34" s="42"/>
-      <c r="AW34" s="42"/>
-      <c r="AX34" s="42"/>
-      <c r="AY34" s="42"/>
-      <c r="AZ34" s="42"/>
-      <c r="BA34" s="42"/>
+      <c r="AV34" s="49"/>
+      <c r="AW34" s="49"/>
+      <c r="AX34" s="49"/>
+      <c r="AY34" s="49"/>
+      <c r="AZ34" s="49"/>
+      <c r="BA34" s="49"/>
     </row>
     <row r="35" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="L35" s="12"/>
@@ -3561,20 +3561,20 @@
       <c r="AQ35" s="12"/>
     </row>
     <row r="36" spans="1:54" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="45" t="s">
+      <c r="A36" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="B36" s="45"/>
-      <c r="C36" s="45"/>
-      <c r="D36" s="45"/>
-      <c r="E36" s="45"/>
-      <c r="F36" s="45"/>
-      <c r="G36" s="45"/>
-      <c r="L36" s="44" t="s">
+      <c r="B36" s="48"/>
+      <c r="C36" s="48"/>
+      <c r="D36" s="48"/>
+      <c r="E36" s="48"/>
+      <c r="F36" s="48"/>
+      <c r="G36" s="48"/>
+      <c r="L36" s="54" t="s">
         <v>26</v>
       </c>
-      <c r="M36" s="43"/>
-      <c r="N36" s="43"/>
+      <c r="M36" s="50"/>
+      <c r="N36" s="50"/>
       <c r="O36" s="12"/>
       <c r="P36" s="8" t="s">
         <v>12</v>
@@ -3608,21 +3608,21 @@
       </c>
       <c r="AK36" s="36"/>
       <c r="AL36" s="37"/>
-      <c r="AN36" s="44" t="s">
+      <c r="AN36" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="AO36" s="43"/>
-      <c r="AP36" s="43"/>
+      <c r="AO36" s="50"/>
+      <c r="AP36" s="50"/>
       <c r="AQ36" s="12"/>
-      <c r="AU36" s="45" t="s">
+      <c r="AU36" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="AV36" s="45"/>
-      <c r="AW36" s="45"/>
-      <c r="AX36" s="45"/>
-      <c r="AY36" s="45"/>
-      <c r="AZ36" s="45"/>
-      <c r="BA36" s="45"/>
+      <c r="AV36" s="48"/>
+      <c r="AW36" s="48"/>
+      <c r="AX36" s="48"/>
+      <c r="AY36" s="48"/>
+      <c r="AZ36" s="48"/>
+      <c r="BA36" s="48"/>
     </row>
     <row r="37" spans="1:54" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A37" s="20" t="s">
@@ -3647,31 +3647,31 @@
         <v>9</v>
       </c>
       <c r="L37" s="12"/>
-      <c r="P37" s="56" t="s">
+      <c r="P37" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="Q37" s="57"/>
-      <c r="R37" s="57"/>
-      <c r="S37" s="57"/>
-      <c r="T37" s="57"/>
-      <c r="U37" s="57"/>
-      <c r="V37" s="58"/>
-      <c r="X37" s="44"/>
-      <c r="Y37" s="43"/>
-      <c r="Z37" s="43"/>
-      <c r="AA37" s="43"/>
-      <c r="AB37" s="43"/>
-      <c r="AC37" s="43"/>
-      <c r="AD37" s="49"/>
-      <c r="AF37" s="42" t="s">
+      <c r="Q37" s="46"/>
+      <c r="R37" s="46"/>
+      <c r="S37" s="46"/>
+      <c r="T37" s="46"/>
+      <c r="U37" s="46"/>
+      <c r="V37" s="47"/>
+      <c r="X37" s="54"/>
+      <c r="Y37" s="50"/>
+      <c r="Z37" s="50"/>
+      <c r="AA37" s="50"/>
+      <c r="AB37" s="50"/>
+      <c r="AC37" s="50"/>
+      <c r="AD37" s="58"/>
+      <c r="AF37" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AG37" s="42"/>
-      <c r="AH37" s="42"/>
-      <c r="AI37" s="42"/>
-      <c r="AJ37" s="42"/>
-      <c r="AK37" s="42"/>
-      <c r="AL37" s="42"/>
+      <c r="AG37" s="49"/>
+      <c r="AH37" s="49"/>
+      <c r="AI37" s="49"/>
+      <c r="AJ37" s="49"/>
+      <c r="AK37" s="49"/>
+      <c r="AL37" s="49"/>
       <c r="AQ37" s="12"/>
       <c r="AU37" s="3" t="s">
         <v>2</v>
@@ -3764,33 +3764,33 @@
         <v>53</v>
       </c>
       <c r="L39" s="12"/>
-      <c r="M39" s="53" t="s">
+      <c r="M39" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="N39" s="54"/>
-      <c r="O39" s="54"/>
-      <c r="P39" s="54"/>
-      <c r="Q39" s="54"/>
-      <c r="R39" s="54"/>
-      <c r="S39" s="55"/>
-      <c r="X39" s="42" t="s">
+      <c r="N39" s="43"/>
+      <c r="O39" s="43"/>
+      <c r="P39" s="43"/>
+      <c r="Q39" s="43"/>
+      <c r="R39" s="43"/>
+      <c r="S39" s="44"/>
+      <c r="X39" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="Y39" s="42"/>
-      <c r="Z39" s="42"/>
-      <c r="AA39" s="42"/>
-      <c r="AB39" s="42"/>
-      <c r="AC39" s="42"/>
-      <c r="AD39" s="42"/>
-      <c r="AI39" s="53" t="s">
+      <c r="Y39" s="49"/>
+      <c r="Z39" s="49"/>
+      <c r="AA39" s="49"/>
+      <c r="AB39" s="49"/>
+      <c r="AC39" s="49"/>
+      <c r="AD39" s="49"/>
+      <c r="AI39" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="AJ39" s="54"/>
-      <c r="AK39" s="54"/>
-      <c r="AL39" s="54"/>
-      <c r="AM39" s="54"/>
-      <c r="AN39" s="54"/>
-      <c r="AO39" s="55"/>
+      <c r="AJ39" s="43"/>
+      <c r="AK39" s="43"/>
+      <c r="AL39" s="43"/>
+      <c r="AM39" s="43"/>
+      <c r="AN39" s="43"/>
+      <c r="AO39" s="44"/>
       <c r="AQ39" s="12"/>
       <c r="AU39" s="8">
         <v>2</v>
@@ -3945,11 +3945,11 @@
       <c r="G41" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="I41" s="43" t="s">
+      <c r="I41" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="J41" s="43"/>
-      <c r="K41" s="43"/>
+      <c r="J41" s="50"/>
+      <c r="K41" s="50"/>
       <c r="L41" s="12"/>
       <c r="M41" s="7">
         <v>1</v>
@@ -4014,11 +4014,11 @@
       <c r="AO41" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="AQ41" s="44" t="s">
+      <c r="AQ41" s="54" t="s">
         <v>23</v>
       </c>
-      <c r="AR41" s="43"/>
-      <c r="AS41" s="43"/>
+      <c r="AR41" s="50"/>
+      <c r="AS41" s="50"/>
       <c r="AU41" s="38">
         <v>4</v>
       </c>
@@ -4096,12 +4096,21 @@
       <c r="Z42" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="AA42" s="13"/>
+      <c r="AA42" s="13">
+        <v>3</v>
+      </c>
       <c r="AB42" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="AC42" s="13"/>
-      <c r="AD42" s="16"/>
+      <c r="AC42" s="13">
+        <v>4</v>
+      </c>
+      <c r="AD42" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE42" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="AI42" s="8">
         <v>2</v>
       </c>
@@ -4342,15 +4351,15 @@
       <c r="BA44" s="6"/>
     </row>
     <row r="45" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="42" t="s">
+      <c r="A45" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="B45" s="42"/>
-      <c r="C45" s="42"/>
-      <c r="D45" s="42"/>
-      <c r="E45" s="42"/>
-      <c r="F45" s="42"/>
-      <c r="G45" s="42"/>
+      <c r="B45" s="49"/>
+      <c r="C45" s="49"/>
+      <c r="D45" s="49"/>
+      <c r="E45" s="49"/>
+      <c r="F45" s="49"/>
+      <c r="G45" s="49"/>
       <c r="M45" s="8" t="s">
         <v>11</v>
       </c>
@@ -4405,15 +4414,15 @@
       <c r="AP45" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AU45" s="42" t="s">
+      <c r="AU45" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AV45" s="42"/>
-      <c r="AW45" s="42"/>
-      <c r="AX45" s="42"/>
-      <c r="AY45" s="42"/>
-      <c r="AZ45" s="42"/>
-      <c r="BA45" s="42"/>
+      <c r="AV45" s="49"/>
+      <c r="AW45" s="49"/>
+      <c r="AX45" s="49"/>
+      <c r="AY45" s="49"/>
+      <c r="AZ45" s="49"/>
+      <c r="BA45" s="49"/>
     </row>
     <row r="46" spans="1:54" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="M46" s="8" t="s">
@@ -4516,45 +4525,65 @@
       <c r="AO47" s="6"/>
     </row>
     <row r="48" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="M48" s="53" t="s">
+      <c r="M48" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="N48" s="54"/>
-      <c r="O48" s="54"/>
-      <c r="P48" s="54"/>
-      <c r="Q48" s="54"/>
-      <c r="R48" s="54"/>
-      <c r="S48" s="55"/>
-      <c r="X48" s="42" t="s">
+      <c r="N48" s="43"/>
+      <c r="O48" s="43"/>
+      <c r="P48" s="43"/>
+      <c r="Q48" s="43"/>
+      <c r="R48" s="43"/>
+      <c r="S48" s="44"/>
+      <c r="X48" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="Y48" s="42"/>
-      <c r="Z48" s="42"/>
-      <c r="AA48" s="42"/>
-      <c r="AB48" s="42"/>
-      <c r="AC48" s="42"/>
-      <c r="AD48" s="42"/>
-      <c r="AI48" s="42" t="s">
+      <c r="Y48" s="49"/>
+      <c r="Z48" s="49"/>
+      <c r="AA48" s="49"/>
+      <c r="AB48" s="49"/>
+      <c r="AC48" s="49"/>
+      <c r="AD48" s="49"/>
+      <c r="AI48" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AJ48" s="42"/>
-      <c r="AK48" s="42"/>
-      <c r="AL48" s="42"/>
-      <c r="AM48" s="42"/>
-      <c r="AN48" s="42"/>
-      <c r="AO48" s="42"/>
+      <c r="AJ48" s="49"/>
+      <c r="AK48" s="49"/>
+      <c r="AL48" s="49"/>
+      <c r="AM48" s="49"/>
+      <c r="AN48" s="49"/>
+      <c r="AO48" s="49"/>
     </row>
     <row r="49" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="M48:S48"/>
-    <mergeCell ref="M39:S39"/>
-    <mergeCell ref="P37:V37"/>
-    <mergeCell ref="P28:V28"/>
-    <mergeCell ref="A36:G36"/>
-    <mergeCell ref="A45:G45"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="AU45:BA45"/>
+    <mergeCell ref="AF28:AL28"/>
+    <mergeCell ref="AF37:AL37"/>
+    <mergeCell ref="AQ30:AS30"/>
+    <mergeCell ref="AQ41:AS41"/>
+    <mergeCell ref="AU34:BA34"/>
+    <mergeCell ref="AU36:BA36"/>
+    <mergeCell ref="AU2:BA2"/>
+    <mergeCell ref="AU3:BA3"/>
+    <mergeCell ref="AU12:BA12"/>
+    <mergeCell ref="AU14:BA14"/>
+    <mergeCell ref="AU23:BA23"/>
+    <mergeCell ref="X37:AD37"/>
+    <mergeCell ref="AE26:AM26"/>
+    <mergeCell ref="Z1:AB1"/>
+    <mergeCell ref="X39:AD39"/>
+    <mergeCell ref="X48:AD48"/>
+    <mergeCell ref="AF1:BA1"/>
+    <mergeCell ref="AI2:AO2"/>
+    <mergeCell ref="AI3:AO3"/>
+    <mergeCell ref="AI12:AO12"/>
+    <mergeCell ref="AI39:AO39"/>
+    <mergeCell ref="AU25:BA25"/>
+    <mergeCell ref="AI48:AO48"/>
+    <mergeCell ref="AN14:AP14"/>
+    <mergeCell ref="AN36:AP36"/>
+    <mergeCell ref="AQ8:AS8"/>
+    <mergeCell ref="AQ19:AS19"/>
     <mergeCell ref="A1:U1"/>
     <mergeCell ref="O26:W26"/>
     <mergeCell ref="I41:K41"/>
@@ -4571,34 +4600,14 @@
     <mergeCell ref="I8:K8"/>
     <mergeCell ref="I19:K19"/>
     <mergeCell ref="A25:G25"/>
-    <mergeCell ref="X37:AD37"/>
-    <mergeCell ref="AE26:AM26"/>
-    <mergeCell ref="Z1:AB1"/>
-    <mergeCell ref="X39:AD39"/>
-    <mergeCell ref="X48:AD48"/>
-    <mergeCell ref="AF1:BA1"/>
-    <mergeCell ref="AI2:AO2"/>
-    <mergeCell ref="AI3:AO3"/>
-    <mergeCell ref="AI12:AO12"/>
-    <mergeCell ref="AI39:AO39"/>
-    <mergeCell ref="AU25:BA25"/>
-    <mergeCell ref="AI48:AO48"/>
-    <mergeCell ref="AN14:AP14"/>
-    <mergeCell ref="AN36:AP36"/>
-    <mergeCell ref="AQ8:AS8"/>
-    <mergeCell ref="AQ19:AS19"/>
-    <mergeCell ref="AU2:BA2"/>
-    <mergeCell ref="AU3:BA3"/>
-    <mergeCell ref="AU12:BA12"/>
-    <mergeCell ref="AU14:BA14"/>
-    <mergeCell ref="AU23:BA23"/>
-    <mergeCell ref="AU45:BA45"/>
-    <mergeCell ref="AF28:AL28"/>
-    <mergeCell ref="AF37:AL37"/>
-    <mergeCell ref="AQ30:AS30"/>
-    <mergeCell ref="AQ41:AS41"/>
-    <mergeCell ref="AU34:BA34"/>
-    <mergeCell ref="AU36:BA36"/>
+    <mergeCell ref="M48:S48"/>
+    <mergeCell ref="M39:S39"/>
+    <mergeCell ref="P37:V37"/>
+    <mergeCell ref="P28:V28"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="A34:G34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/2025_2026/Playoffs/Brackets.xlsx
+++ b/2025_2026/Playoffs/Brackets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\NHLStats\2025_2026\Playoffs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3C0C9CB-3E71-4242-A086-6DE688D120A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F9B35B9-1239-4CB5-988C-4C57CD37C7C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="1590" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="101">
   <si>
     <t>Eastern Conference Playoff Teams</t>
   </si>
@@ -326,6 +326,9 @@
   </si>
   <si>
     <t>Hurricanes Win Series 4-1</t>
+  </si>
+  <si>
+    <t>Golden Knights Lead 2-1</t>
   </si>
 </sst>
 </file>
@@ -704,6 +707,39 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -722,46 +758,13 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1131,18 +1134,18 @@
     </row>
     <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="11" spans="1:7" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="61" t="s">
+      <c r="A11" s="59" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="61"/>
-      <c r="C11" s="61" t="s">
+      <c r="B11" s="59"/>
+      <c r="C11" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="61"/>
-      <c r="E11" s="61" t="s">
+      <c r="D11" s="59"/>
+      <c r="E11" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="61"/>
+      <c r="F11" s="59"/>
       <c r="G11" s="4" t="s">
         <v>18</v>
       </c>
@@ -1171,18 +1174,18 @@
       </c>
     </row>
     <row r="13" spans="1:7" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="59" t="s">
+      <c r="A13" s="60" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="60"/>
-      <c r="C13" s="59" t="s">
+      <c r="B13" s="61"/>
+      <c r="C13" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="D13" s="60"/>
-      <c r="E13" s="59" t="s">
+      <c r="D13" s="61"/>
+      <c r="E13" s="60" t="s">
         <v>17</v>
       </c>
-      <c r="F13" s="60"/>
+      <c r="F13" s="61"/>
       <c r="G13" s="5" t="s">
         <v>26</v>
       </c>
@@ -1231,14 +1234,14 @@
       </c>
     </row>
     <row r="16" spans="1:7" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="59" t="s">
+      <c r="A16" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="60"/>
-      <c r="C16" s="59" t="s">
+      <c r="B16" s="61"/>
+      <c r="C16" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="60"/>
+      <c r="D16" s="61"/>
     </row>
     <row r="17" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
@@ -1269,10 +1272,10 @@
       </c>
     </row>
     <row r="19" spans="1:4" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="59" t="s">
+      <c r="A19" s="60" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="60"/>
+      <c r="B19" s="61"/>
     </row>
     <row r="20" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
@@ -1291,10 +1294,10 @@
       </c>
     </row>
     <row r="22" spans="1:4" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="59" t="s">
+      <c r="A22" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="60"/>
+      <c r="B22" s="61"/>
     </row>
     <row r="23" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
@@ -1379,16 +1382,16 @@
     <sortCondition ref="B2:B9"/>
   </sortState>
   <mergeCells count="10">
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C16:D16"/>
     <mergeCell ref="E11:F11"/>
     <mergeCell ref="E13:F13"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C16:D16"/>
   </mergeCells>
   <dataValidations count="16">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C14" xr:uid="{2C3D9587-ABAE-4E3F-8B22-396DF812BF02}">
@@ -1492,124 +1495,124 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:54" ht="27" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
-      <c r="M1" s="52"/>
-      <c r="N1" s="52"/>
-      <c r="O1" s="52"/>
-      <c r="P1" s="52"/>
-      <c r="Q1" s="52"/>
-      <c r="R1" s="52"/>
-      <c r="S1" s="52"/>
-      <c r="T1" s="52"/>
-      <c r="U1" s="53"/>
-      <c r="Z1" s="51" t="s">
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
+      <c r="K1" s="51"/>
+      <c r="L1" s="51"/>
+      <c r="M1" s="51"/>
+      <c r="N1" s="51"/>
+      <c r="O1" s="51"/>
+      <c r="P1" s="51"/>
+      <c r="Q1" s="51"/>
+      <c r="R1" s="51"/>
+      <c r="S1" s="51"/>
+      <c r="T1" s="51"/>
+      <c r="U1" s="52"/>
+      <c r="Z1" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="AA1" s="52"/>
-      <c r="AB1" s="53"/>
-      <c r="AF1" s="51" t="s">
+      <c r="AA1" s="51"/>
+      <c r="AB1" s="52"/>
+      <c r="AF1" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="AG1" s="52"/>
-      <c r="AH1" s="52"/>
-      <c r="AI1" s="52"/>
-      <c r="AJ1" s="52"/>
-      <c r="AK1" s="52"/>
-      <c r="AL1" s="52"/>
-      <c r="AM1" s="52"/>
-      <c r="AN1" s="52"/>
-      <c r="AO1" s="52"/>
-      <c r="AP1" s="52"/>
-      <c r="AQ1" s="52"/>
-      <c r="AR1" s="52"/>
-      <c r="AS1" s="52"/>
-      <c r="AT1" s="52"/>
-      <c r="AU1" s="52"/>
-      <c r="AV1" s="52"/>
-      <c r="AW1" s="52"/>
-      <c r="AX1" s="52"/>
-      <c r="AY1" s="52"/>
-      <c r="AZ1" s="52"/>
-      <c r="BA1" s="53"/>
+      <c r="AG1" s="51"/>
+      <c r="AH1" s="51"/>
+      <c r="AI1" s="51"/>
+      <c r="AJ1" s="51"/>
+      <c r="AK1" s="51"/>
+      <c r="AL1" s="51"/>
+      <c r="AM1" s="51"/>
+      <c r="AN1" s="51"/>
+      <c r="AO1" s="51"/>
+      <c r="AP1" s="51"/>
+      <c r="AQ1" s="51"/>
+      <c r="AR1" s="51"/>
+      <c r="AS1" s="51"/>
+      <c r="AT1" s="51"/>
+      <c r="AU1" s="51"/>
+      <c r="AV1" s="51"/>
+      <c r="AW1" s="51"/>
+      <c r="AX1" s="51"/>
+      <c r="AY1" s="51"/>
+      <c r="AZ1" s="51"/>
+      <c r="BA1" s="52"/>
     </row>
     <row r="2" spans="1:54" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="55" t="s">
+      <c r="A2" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="57"/>
-      <c r="M2" s="55" t="s">
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="48"/>
+      <c r="M2" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="56"/>
-      <c r="O2" s="56"/>
-      <c r="P2" s="56"/>
-      <c r="Q2" s="56"/>
-      <c r="R2" s="57"/>
-      <c r="AI2" s="55" t="s">
+      <c r="N2" s="47"/>
+      <c r="O2" s="47"/>
+      <c r="P2" s="47"/>
+      <c r="Q2" s="47"/>
+      <c r="R2" s="48"/>
+      <c r="AI2" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="AJ2" s="56"/>
-      <c r="AK2" s="56"/>
-      <c r="AL2" s="56"/>
-      <c r="AM2" s="56"/>
-      <c r="AN2" s="56"/>
-      <c r="AO2" s="57"/>
-      <c r="AU2" s="55" t="s">
+      <c r="AJ2" s="47"/>
+      <c r="AK2" s="47"/>
+      <c r="AL2" s="47"/>
+      <c r="AM2" s="47"/>
+      <c r="AN2" s="47"/>
+      <c r="AO2" s="48"/>
+      <c r="AU2" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="AV2" s="56"/>
-      <c r="AW2" s="56"/>
-      <c r="AX2" s="56"/>
-      <c r="AY2" s="56"/>
-      <c r="AZ2" s="56"/>
-      <c r="BA2" s="57"/>
+      <c r="AV2" s="47"/>
+      <c r="AW2" s="47"/>
+      <c r="AX2" s="47"/>
+      <c r="AY2" s="47"/>
+      <c r="AZ2" s="47"/>
+      <c r="BA2" s="48"/>
     </row>
     <row r="3" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="49" t="s">
+      <c r="A3" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="49"/>
-      <c r="C3" s="49"/>
-      <c r="D3" s="49"/>
-      <c r="E3" s="49"/>
-      <c r="F3" s="49"/>
-      <c r="G3" s="49"/>
-      <c r="AI3" s="42" t="s">
+      <c r="B3" s="42"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="42"/>
+      <c r="AI3" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="AJ3" s="43"/>
-      <c r="AK3" s="43"/>
-      <c r="AL3" s="43"/>
-      <c r="AM3" s="43"/>
-      <c r="AN3" s="43"/>
-      <c r="AO3" s="44"/>
-      <c r="AU3" s="49" t="s">
+      <c r="AJ3" s="54"/>
+      <c r="AK3" s="54"/>
+      <c r="AL3" s="54"/>
+      <c r="AM3" s="54"/>
+      <c r="AN3" s="54"/>
+      <c r="AO3" s="55"/>
+      <c r="AU3" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="AV3" s="49"/>
-      <c r="AW3" s="49"/>
-      <c r="AX3" s="49"/>
-      <c r="AY3" s="49"/>
-      <c r="AZ3" s="49"/>
-      <c r="BA3" s="49"/>
+      <c r="AV3" s="42"/>
+      <c r="AW3" s="42"/>
+      <c r="AX3" s="42"/>
+      <c r="AY3" s="42"/>
+      <c r="AZ3" s="42"/>
+      <c r="BA3" s="42"/>
     </row>
     <row r="4" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
@@ -1633,15 +1636,15 @@
       <c r="G4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="42" t="s">
+      <c r="M4" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="N4" s="43"/>
-      <c r="O4" s="43"/>
-      <c r="P4" s="43"/>
-      <c r="Q4" s="43"/>
-      <c r="R4" s="43"/>
-      <c r="S4" s="44"/>
+      <c r="N4" s="54"/>
+      <c r="O4" s="54"/>
+      <c r="P4" s="54"/>
+      <c r="Q4" s="54"/>
+      <c r="R4" s="54"/>
+      <c r="S4" s="55"/>
       <c r="AI4" s="3" t="s">
         <v>2</v>
       </c>
@@ -1968,11 +1971,11 @@
       <c r="G8" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="I8" s="50" t="s">
+      <c r="I8" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="J8" s="50"/>
-      <c r="K8" s="50"/>
+      <c r="J8" s="43"/>
+      <c r="K8" s="43"/>
       <c r="M8" s="8">
         <v>3</v>
       </c>
@@ -2015,11 +2018,11 @@
       <c r="AO8" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="AQ8" s="50" t="s">
+      <c r="AQ8" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="AR8" s="50"/>
-      <c r="AS8" s="50"/>
+      <c r="AR8" s="43"/>
+      <c r="AS8" s="43"/>
       <c r="AU8" s="38">
         <v>4</v>
       </c>
@@ -2279,15 +2282,15 @@
       <c r="BA11" s="6"/>
     </row>
     <row r="12" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="49" t="s">
+      <c r="A12" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="49"/>
-      <c r="C12" s="49"/>
-      <c r="D12" s="49"/>
-      <c r="E12" s="49"/>
-      <c r="F12" s="49"/>
-      <c r="G12" s="49"/>
+      <c r="B12" s="42"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="42"/>
       <c r="L12" s="12"/>
       <c r="M12" s="8" t="s">
         <v>12</v>
@@ -2313,69 +2316,69 @@
       <c r="T12" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AI12" s="49" t="s">
+      <c r="AI12" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AJ12" s="49"/>
-      <c r="AK12" s="49"/>
-      <c r="AL12" s="49"/>
-      <c r="AM12" s="49"/>
-      <c r="AN12" s="49"/>
-      <c r="AO12" s="49"/>
+      <c r="AJ12" s="42"/>
+      <c r="AK12" s="42"/>
+      <c r="AL12" s="42"/>
+      <c r="AM12" s="42"/>
+      <c r="AN12" s="42"/>
+      <c r="AO12" s="42"/>
       <c r="AQ12" s="12"/>
-      <c r="AU12" s="49" t="s">
+      <c r="AU12" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AV12" s="49"/>
-      <c r="AW12" s="49"/>
-      <c r="AX12" s="49"/>
-      <c r="AY12" s="49"/>
-      <c r="AZ12" s="49"/>
-      <c r="BA12" s="49"/>
+      <c r="AV12" s="42"/>
+      <c r="AW12" s="42"/>
+      <c r="AX12" s="42"/>
+      <c r="AY12" s="42"/>
+      <c r="AZ12" s="42"/>
+      <c r="BA12" s="42"/>
     </row>
     <row r="13" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="L13" s="12"/>
-      <c r="M13" s="42" t="s">
+      <c r="M13" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="N13" s="43"/>
-      <c r="O13" s="43"/>
-      <c r="P13" s="43"/>
-      <c r="Q13" s="43"/>
-      <c r="R13" s="43"/>
-      <c r="S13" s="44"/>
+      <c r="N13" s="54"/>
+      <c r="O13" s="54"/>
+      <c r="P13" s="54"/>
+      <c r="Q13" s="54"/>
+      <c r="R13" s="54"/>
+      <c r="S13" s="55"/>
       <c r="AQ13" s="12"/>
     </row>
     <row r="14" spans="1:54" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="48" t="s">
+      <c r="A14" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="48"/>
-      <c r="C14" s="48"/>
-      <c r="D14" s="48"/>
-      <c r="E14" s="48"/>
-      <c r="F14" s="48"/>
-      <c r="G14" s="48"/>
-      <c r="L14" s="54" t="s">
+      <c r="B14" s="45"/>
+      <c r="C14" s="45"/>
+      <c r="D14" s="45"/>
+      <c r="E14" s="45"/>
+      <c r="F14" s="45"/>
+      <c r="G14" s="45"/>
+      <c r="L14" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="M14" s="50"/>
-      <c r="N14" s="50"/>
-      <c r="AN14" s="50" t="s">
+      <c r="M14" s="43"/>
+      <c r="N14" s="43"/>
+      <c r="AN14" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="AO14" s="50"/>
-      <c r="AP14" s="50"/>
+      <c r="AO14" s="43"/>
+      <c r="AP14" s="43"/>
       <c r="AQ14" s="12"/>
-      <c r="AU14" s="48" t="s">
+      <c r="AU14" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="AV14" s="48"/>
-      <c r="AW14" s="48"/>
-      <c r="AX14" s="48"/>
-      <c r="AY14" s="48"/>
-      <c r="AZ14" s="48"/>
-      <c r="BA14" s="48"/>
+      <c r="AV14" s="45"/>
+      <c r="AW14" s="45"/>
+      <c r="AX14" s="45"/>
+      <c r="AY14" s="45"/>
+      <c r="AZ14" s="45"/>
+      <c r="BA14" s="45"/>
     </row>
     <row r="15" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
@@ -2603,19 +2606,19 @@
       <c r="G19" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="I19" s="50" t="s">
+      <c r="I19" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="J19" s="50"/>
-      <c r="K19" s="50"/>
+      <c r="J19" s="43"/>
+      <c r="K19" s="43"/>
       <c r="L19" s="12"/>
       <c r="O19" s="12"/>
       <c r="AN19" s="12"/>
-      <c r="AQ19" s="54" t="s">
+      <c r="AQ19" s="44" t="s">
         <v>31</v>
       </c>
-      <c r="AR19" s="50"/>
-      <c r="AS19" s="50"/>
+      <c r="AR19" s="43"/>
+      <c r="AS19" s="43"/>
       <c r="AU19" s="38">
         <v>4</v>
       </c>
@@ -2777,52 +2780,52 @@
       <c r="BA22" s="6"/>
     </row>
     <row r="23" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="49" t="s">
+      <c r="A23" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B23" s="49"/>
-      <c r="C23" s="49"/>
-      <c r="D23" s="49"/>
-      <c r="E23" s="49"/>
-      <c r="F23" s="49"/>
-      <c r="G23" s="49"/>
+      <c r="B23" s="42"/>
+      <c r="C23" s="42"/>
+      <c r="D23" s="42"/>
+      <c r="E23" s="42"/>
+      <c r="F23" s="42"/>
+      <c r="G23" s="42"/>
       <c r="O23" s="12"/>
       <c r="AN23" s="12"/>
-      <c r="AU23" s="49" t="s">
+      <c r="AU23" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AV23" s="49"/>
-      <c r="AW23" s="49"/>
-      <c r="AX23" s="49"/>
-      <c r="AY23" s="49"/>
-      <c r="AZ23" s="49"/>
-      <c r="BA23" s="49"/>
+      <c r="AV23" s="42"/>
+      <c r="AW23" s="42"/>
+      <c r="AX23" s="42"/>
+      <c r="AY23" s="42"/>
+      <c r="AZ23" s="42"/>
+      <c r="BA23" s="42"/>
     </row>
     <row r="24" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="O24" s="12"/>
       <c r="AN24" s="12"/>
     </row>
     <row r="25" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="49" t="s">
+      <c r="A25" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="49"/>
-      <c r="C25" s="49"/>
-      <c r="D25" s="49"/>
-      <c r="E25" s="49"/>
-      <c r="F25" s="49"/>
-      <c r="G25" s="49"/>
+      <c r="B25" s="42"/>
+      <c r="C25" s="42"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="42"/>
+      <c r="F25" s="42"/>
+      <c r="G25" s="42"/>
       <c r="O25" s="12"/>
       <c r="AN25" s="12"/>
-      <c r="AU25" s="49" t="s">
+      <c r="AU25" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="AV25" s="49"/>
-      <c r="AW25" s="49"/>
-      <c r="AX25" s="49"/>
-      <c r="AY25" s="49"/>
-      <c r="AZ25" s="49"/>
-      <c r="BA25" s="49"/>
+      <c r="AV25" s="42"/>
+      <c r="AW25" s="42"/>
+      <c r="AX25" s="42"/>
+      <c r="AY25" s="42"/>
+      <c r="AZ25" s="42"/>
+      <c r="BA25" s="42"/>
     </row>
     <row r="26" spans="1:54" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A26" s="20" t="s">
@@ -2846,28 +2849,28 @@
       <c r="G26" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="O26" s="54" t="s">
+      <c r="O26" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="P26" s="50"/>
-      <c r="Q26" s="50"/>
-      <c r="R26" s="50"/>
-      <c r="S26" s="50"/>
-      <c r="T26" s="50"/>
-      <c r="U26" s="50"/>
-      <c r="V26" s="50"/>
-      <c r="W26" s="50"/>
-      <c r="AE26" s="50" t="s">
+      <c r="P26" s="43"/>
+      <c r="Q26" s="43"/>
+      <c r="R26" s="43"/>
+      <c r="S26" s="43"/>
+      <c r="T26" s="43"/>
+      <c r="U26" s="43"/>
+      <c r="V26" s="43"/>
+      <c r="W26" s="43"/>
+      <c r="AE26" s="43" t="s">
         <v>38</v>
       </c>
-      <c r="AF26" s="50"/>
-      <c r="AG26" s="50"/>
-      <c r="AH26" s="50"/>
-      <c r="AI26" s="50"/>
-      <c r="AJ26" s="50"/>
-      <c r="AK26" s="50"/>
-      <c r="AL26" s="50"/>
-      <c r="AM26" s="58"/>
+      <c r="AF26" s="43"/>
+      <c r="AG26" s="43"/>
+      <c r="AH26" s="43"/>
+      <c r="AI26" s="43"/>
+      <c r="AJ26" s="43"/>
+      <c r="AK26" s="43"/>
+      <c r="AL26" s="43"/>
+      <c r="AM26" s="49"/>
       <c r="AU26" s="20" t="s">
         <v>2</v>
       </c>
@@ -2964,26 +2967,26 @@
         <v>54</v>
       </c>
       <c r="O28" s="12"/>
-      <c r="P28" s="42" t="s">
+      <c r="P28" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="Q28" s="43"/>
-      <c r="R28" s="43"/>
-      <c r="S28" s="43"/>
-      <c r="T28" s="43"/>
-      <c r="U28" s="43"/>
-      <c r="V28" s="44"/>
+      <c r="Q28" s="54"/>
+      <c r="R28" s="54"/>
+      <c r="S28" s="54"/>
+      <c r="T28" s="54"/>
+      <c r="U28" s="54"/>
+      <c r="V28" s="55"/>
       <c r="X28" s="12"/>
       <c r="AD28" s="13"/>
-      <c r="AF28" s="49" t="s">
+      <c r="AF28" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="AG28" s="49"/>
-      <c r="AH28" s="49"/>
-      <c r="AI28" s="49"/>
-      <c r="AJ28" s="49"/>
-      <c r="AK28" s="49"/>
-      <c r="AL28" s="49"/>
+      <c r="AG28" s="42"/>
+      <c r="AH28" s="42"/>
+      <c r="AI28" s="42"/>
+      <c r="AJ28" s="42"/>
+      <c r="AK28" s="42"/>
+      <c r="AL28" s="42"/>
       <c r="AN28" s="12"/>
       <c r="AU28" s="8">
         <v>2</v>
@@ -3119,11 +3122,11 @@
       <c r="G30" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="I30" s="50" t="s">
+      <c r="I30" s="43" t="s">
         <v>26</v>
       </c>
-      <c r="J30" s="50"/>
-      <c r="K30" s="50"/>
+      <c r="J30" s="43"/>
+      <c r="K30" s="43"/>
       <c r="O30" s="12"/>
       <c r="P30" s="7">
         <v>1</v>
@@ -3170,11 +3173,11 @@
         <v>52</v>
       </c>
       <c r="AN30" s="12"/>
-      <c r="AQ30" s="50" t="s">
+      <c r="AQ30" s="43" t="s">
         <v>38</v>
       </c>
-      <c r="AR30" s="50"/>
-      <c r="AS30" s="50"/>
+      <c r="AR30" s="43"/>
+      <c r="AS30" s="43"/>
       <c r="AU30" s="38">
         <v>4</v>
       </c>
@@ -3461,15 +3464,15 @@
       <c r="BA33" s="6"/>
     </row>
     <row r="34" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="49" t="s">
+      <c r="A34" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B34" s="49"/>
-      <c r="C34" s="49"/>
-      <c r="D34" s="49"/>
-      <c r="E34" s="49"/>
-      <c r="F34" s="49"/>
-      <c r="G34" s="49"/>
+      <c r="B34" s="42"/>
+      <c r="C34" s="42"/>
+      <c r="D34" s="42"/>
+      <c r="E34" s="42"/>
+      <c r="F34" s="42"/>
+      <c r="G34" s="42"/>
       <c r="L34" s="12"/>
       <c r="O34" s="12"/>
       <c r="P34" s="8" t="s">
@@ -3512,15 +3515,15 @@
       <c r="AL34" s="16"/>
       <c r="AN34" s="12"/>
       <c r="AQ34" s="12"/>
-      <c r="AU34" s="49" t="s">
+      <c r="AU34" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AV34" s="49"/>
-      <c r="AW34" s="49"/>
-      <c r="AX34" s="49"/>
-      <c r="AY34" s="49"/>
-      <c r="AZ34" s="49"/>
-      <c r="BA34" s="49"/>
+      <c r="AV34" s="42"/>
+      <c r="AW34" s="42"/>
+      <c r="AX34" s="42"/>
+      <c r="AY34" s="42"/>
+      <c r="AZ34" s="42"/>
+      <c r="BA34" s="42"/>
     </row>
     <row r="35" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="L35" s="12"/>
@@ -3561,20 +3564,20 @@
       <c r="AQ35" s="12"/>
     </row>
     <row r="36" spans="1:54" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="48" t="s">
+      <c r="A36" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="B36" s="48"/>
-      <c r="C36" s="48"/>
-      <c r="D36" s="48"/>
-      <c r="E36" s="48"/>
-      <c r="F36" s="48"/>
-      <c r="G36" s="48"/>
-      <c r="L36" s="54" t="s">
+      <c r="B36" s="45"/>
+      <c r="C36" s="45"/>
+      <c r="D36" s="45"/>
+      <c r="E36" s="45"/>
+      <c r="F36" s="45"/>
+      <c r="G36" s="45"/>
+      <c r="L36" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="M36" s="50"/>
-      <c r="N36" s="50"/>
+      <c r="M36" s="43"/>
+      <c r="N36" s="43"/>
       <c r="O36" s="12"/>
       <c r="P36" s="8" t="s">
         <v>12</v>
@@ -3608,21 +3611,21 @@
       </c>
       <c r="AK36" s="36"/>
       <c r="AL36" s="37"/>
-      <c r="AN36" s="54" t="s">
+      <c r="AN36" s="44" t="s">
         <v>38</v>
       </c>
-      <c r="AO36" s="50"/>
-      <c r="AP36" s="50"/>
+      <c r="AO36" s="43"/>
+      <c r="AP36" s="43"/>
       <c r="AQ36" s="12"/>
-      <c r="AU36" s="48" t="s">
+      <c r="AU36" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="AV36" s="48"/>
-      <c r="AW36" s="48"/>
-      <c r="AX36" s="48"/>
-      <c r="AY36" s="48"/>
-      <c r="AZ36" s="48"/>
-      <c r="BA36" s="48"/>
+      <c r="AV36" s="45"/>
+      <c r="AW36" s="45"/>
+      <c r="AX36" s="45"/>
+      <c r="AY36" s="45"/>
+      <c r="AZ36" s="45"/>
+      <c r="BA36" s="45"/>
     </row>
     <row r="37" spans="1:54" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A37" s="20" t="s">
@@ -3647,31 +3650,31 @@
         <v>9</v>
       </c>
       <c r="L37" s="12"/>
-      <c r="P37" s="45" t="s">
+      <c r="P37" s="56" t="s">
         <v>13</v>
       </c>
-      <c r="Q37" s="46"/>
-      <c r="R37" s="46"/>
-      <c r="S37" s="46"/>
-      <c r="T37" s="46"/>
-      <c r="U37" s="46"/>
-      <c r="V37" s="47"/>
-      <c r="X37" s="54"/>
-      <c r="Y37" s="50"/>
-      <c r="Z37" s="50"/>
-      <c r="AA37" s="50"/>
-      <c r="AB37" s="50"/>
-      <c r="AC37" s="50"/>
-      <c r="AD37" s="58"/>
-      <c r="AF37" s="49" t="s">
+      <c r="Q37" s="57"/>
+      <c r="R37" s="57"/>
+      <c r="S37" s="57"/>
+      <c r="T37" s="57"/>
+      <c r="U37" s="57"/>
+      <c r="V37" s="58"/>
+      <c r="X37" s="44"/>
+      <c r="Y37" s="43"/>
+      <c r="Z37" s="43"/>
+      <c r="AA37" s="43"/>
+      <c r="AB37" s="43"/>
+      <c r="AC37" s="43"/>
+      <c r="AD37" s="49"/>
+      <c r="AF37" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AG37" s="49"/>
-      <c r="AH37" s="49"/>
-      <c r="AI37" s="49"/>
-      <c r="AJ37" s="49"/>
-      <c r="AK37" s="49"/>
-      <c r="AL37" s="49"/>
+      <c r="AG37" s="42"/>
+      <c r="AH37" s="42"/>
+      <c r="AI37" s="42"/>
+      <c r="AJ37" s="42"/>
+      <c r="AK37" s="42"/>
+      <c r="AL37" s="42"/>
       <c r="AQ37" s="12"/>
       <c r="AU37" s="3" t="s">
         <v>2</v>
@@ -3764,33 +3767,33 @@
         <v>53</v>
       </c>
       <c r="L39" s="12"/>
-      <c r="M39" s="42" t="s">
+      <c r="M39" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="N39" s="43"/>
-      <c r="O39" s="43"/>
-      <c r="P39" s="43"/>
-      <c r="Q39" s="43"/>
-      <c r="R39" s="43"/>
-      <c r="S39" s="44"/>
-      <c r="X39" s="49" t="s">
+      <c r="N39" s="54"/>
+      <c r="O39" s="54"/>
+      <c r="P39" s="54"/>
+      <c r="Q39" s="54"/>
+      <c r="R39" s="54"/>
+      <c r="S39" s="55"/>
+      <c r="X39" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="Y39" s="49"/>
-      <c r="Z39" s="49"/>
-      <c r="AA39" s="49"/>
-      <c r="AB39" s="49"/>
-      <c r="AC39" s="49"/>
-      <c r="AD39" s="49"/>
-      <c r="AI39" s="42" t="s">
+      <c r="Y39" s="42"/>
+      <c r="Z39" s="42"/>
+      <c r="AA39" s="42"/>
+      <c r="AB39" s="42"/>
+      <c r="AC39" s="42"/>
+      <c r="AD39" s="42"/>
+      <c r="AI39" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="AJ39" s="43"/>
-      <c r="AK39" s="43"/>
-      <c r="AL39" s="43"/>
-      <c r="AM39" s="43"/>
-      <c r="AN39" s="43"/>
-      <c r="AO39" s="44"/>
+      <c r="AJ39" s="54"/>
+      <c r="AK39" s="54"/>
+      <c r="AL39" s="54"/>
+      <c r="AM39" s="54"/>
+      <c r="AN39" s="54"/>
+      <c r="AO39" s="55"/>
       <c r="AQ39" s="12"/>
       <c r="AU39" s="8">
         <v>2</v>
@@ -3945,11 +3948,11 @@
       <c r="G41" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="I41" s="50" t="s">
+      <c r="I41" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="J41" s="50"/>
-      <c r="K41" s="50"/>
+      <c r="J41" s="43"/>
+      <c r="K41" s="43"/>
       <c r="L41" s="12"/>
       <c r="M41" s="7">
         <v>1</v>
@@ -4014,11 +4017,11 @@
       <c r="AO41" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="AQ41" s="54" t="s">
+      <c r="AQ41" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="AR41" s="50"/>
-      <c r="AS41" s="50"/>
+      <c r="AR41" s="43"/>
+      <c r="AS41" s="43"/>
       <c r="AU41" s="38">
         <v>4</v>
       </c>
@@ -4209,12 +4212,21 @@
       <c r="Z43" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="AA43" s="13"/>
+      <c r="AA43" s="13">
+        <v>4</v>
+      </c>
       <c r="AB43" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="AC43" s="13"/>
-      <c r="AD43" s="16"/>
+      <c r="AC43" s="13">
+        <v>5</v>
+      </c>
+      <c r="AD43" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="AE43" s="1" t="s">
+        <v>54</v>
+      </c>
       <c r="AI43" s="8">
         <v>3</v>
       </c>
@@ -4351,15 +4363,15 @@
       <c r="BA44" s="6"/>
     </row>
     <row r="45" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="49" t="s">
+      <c r="A45" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B45" s="49"/>
-      <c r="C45" s="49"/>
-      <c r="D45" s="49"/>
-      <c r="E45" s="49"/>
-      <c r="F45" s="49"/>
-      <c r="G45" s="49"/>
+      <c r="B45" s="42"/>
+      <c r="C45" s="42"/>
+      <c r="D45" s="42"/>
+      <c r="E45" s="42"/>
+      <c r="F45" s="42"/>
+      <c r="G45" s="42"/>
       <c r="M45" s="8" t="s">
         <v>11</v>
       </c>
@@ -4414,15 +4426,15 @@
       <c r="AP45" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AU45" s="49" t="s">
+      <c r="AU45" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AV45" s="49"/>
-      <c r="AW45" s="49"/>
-      <c r="AX45" s="49"/>
-      <c r="AY45" s="49"/>
-      <c r="AZ45" s="49"/>
-      <c r="BA45" s="49"/>
+      <c r="AV45" s="42"/>
+      <c r="AW45" s="42"/>
+      <c r="AX45" s="42"/>
+      <c r="AY45" s="42"/>
+      <c r="AZ45" s="42"/>
+      <c r="BA45" s="42"/>
     </row>
     <row r="46" spans="1:54" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="M46" s="8" t="s">
@@ -4525,49 +4537,61 @@
       <c r="AO47" s="6"/>
     </row>
     <row r="48" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="M48" s="42" t="s">
+      <c r="M48" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="N48" s="43"/>
-      <c r="O48" s="43"/>
-      <c r="P48" s="43"/>
-      <c r="Q48" s="43"/>
-      <c r="R48" s="43"/>
-      <c r="S48" s="44"/>
-      <c r="X48" s="49" t="s">
+      <c r="N48" s="54"/>
+      <c r="O48" s="54"/>
+      <c r="P48" s="54"/>
+      <c r="Q48" s="54"/>
+      <c r="R48" s="54"/>
+      <c r="S48" s="55"/>
+      <c r="X48" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="Y48" s="49"/>
-      <c r="Z48" s="49"/>
-      <c r="AA48" s="49"/>
-      <c r="AB48" s="49"/>
-      <c r="AC48" s="49"/>
-      <c r="AD48" s="49"/>
-      <c r="AI48" s="49" t="s">
+      <c r="Y48" s="42"/>
+      <c r="Z48" s="42"/>
+      <c r="AA48" s="42"/>
+      <c r="AB48" s="42"/>
+      <c r="AC48" s="42"/>
+      <c r="AD48" s="42"/>
+      <c r="AI48" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AJ48" s="49"/>
-      <c r="AK48" s="49"/>
-      <c r="AL48" s="49"/>
-      <c r="AM48" s="49"/>
-      <c r="AN48" s="49"/>
-      <c r="AO48" s="49"/>
+      <c r="AJ48" s="42"/>
+      <c r="AK48" s="42"/>
+      <c r="AL48" s="42"/>
+      <c r="AM48" s="42"/>
+      <c r="AN48" s="42"/>
+      <c r="AO48" s="42"/>
     </row>
     <row r="49" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="AU45:BA45"/>
-    <mergeCell ref="AF28:AL28"/>
-    <mergeCell ref="AF37:AL37"/>
-    <mergeCell ref="AQ30:AS30"/>
-    <mergeCell ref="AQ41:AS41"/>
-    <mergeCell ref="AU34:BA34"/>
-    <mergeCell ref="AU36:BA36"/>
-    <mergeCell ref="AU2:BA2"/>
-    <mergeCell ref="AU3:BA3"/>
-    <mergeCell ref="AU12:BA12"/>
-    <mergeCell ref="AU14:BA14"/>
-    <mergeCell ref="AU23:BA23"/>
+    <mergeCell ref="M48:S48"/>
+    <mergeCell ref="M39:S39"/>
+    <mergeCell ref="P37:V37"/>
+    <mergeCell ref="P28:V28"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A1:U1"/>
+    <mergeCell ref="O26:W26"/>
+    <mergeCell ref="I41:K41"/>
+    <mergeCell ref="L14:N14"/>
+    <mergeCell ref="L36:N36"/>
+    <mergeCell ref="M2:R2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="M4:S4"/>
+    <mergeCell ref="M13:S13"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="A25:G25"/>
     <mergeCell ref="X37:AD37"/>
     <mergeCell ref="AE26:AM26"/>
     <mergeCell ref="Z1:AB1"/>
@@ -4584,30 +4608,18 @@
     <mergeCell ref="AN36:AP36"/>
     <mergeCell ref="AQ8:AS8"/>
     <mergeCell ref="AQ19:AS19"/>
-    <mergeCell ref="A1:U1"/>
-    <mergeCell ref="O26:W26"/>
-    <mergeCell ref="I41:K41"/>
-    <mergeCell ref="L14:N14"/>
-    <mergeCell ref="L36:N36"/>
-    <mergeCell ref="M2:R2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="M4:S4"/>
-    <mergeCell ref="M13:S13"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A23:G23"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="M48:S48"/>
-    <mergeCell ref="M39:S39"/>
-    <mergeCell ref="P37:V37"/>
-    <mergeCell ref="P28:V28"/>
-    <mergeCell ref="A36:G36"/>
-    <mergeCell ref="A45:G45"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="AU2:BA2"/>
+    <mergeCell ref="AU3:BA3"/>
+    <mergeCell ref="AU12:BA12"/>
+    <mergeCell ref="AU14:BA14"/>
+    <mergeCell ref="AU23:BA23"/>
+    <mergeCell ref="AU45:BA45"/>
+    <mergeCell ref="AF28:AL28"/>
+    <mergeCell ref="AF37:AL37"/>
+    <mergeCell ref="AQ30:AS30"/>
+    <mergeCell ref="AQ41:AS41"/>
+    <mergeCell ref="AU34:BA34"/>
+    <mergeCell ref="AU36:BA36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/2025_2026/Playoffs/Brackets.xlsx
+++ b/2025_2026/Playoffs/Brackets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\NHLStats\2025_2026\Playoffs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F9B35B9-1239-4CB5-988C-4C57CD37C7C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C7256A2-9190-4CC4-B53D-453FEE3E6A94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="1590" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="101">
   <si>
     <t>Eastern Conference Playoff Teams</t>
   </si>
@@ -707,18 +707,45 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -731,40 +758,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1134,18 +1134,18 @@
     </row>
     <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="11" spans="1:7" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="59" t="s">
+      <c r="A11" s="61" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="59"/>
-      <c r="C11" s="59" t="s">
+      <c r="B11" s="61"/>
+      <c r="C11" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="59"/>
-      <c r="E11" s="59" t="s">
+      <c r="D11" s="61"/>
+      <c r="E11" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="59"/>
+      <c r="F11" s="61"/>
       <c r="G11" s="4" t="s">
         <v>18</v>
       </c>
@@ -1174,18 +1174,18 @@
       </c>
     </row>
     <row r="13" spans="1:7" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="60" t="s">
+      <c r="A13" s="59" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="61"/>
-      <c r="C13" s="60" t="s">
+      <c r="B13" s="60"/>
+      <c r="C13" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="D13" s="61"/>
-      <c r="E13" s="60" t="s">
+      <c r="D13" s="60"/>
+      <c r="E13" s="59" t="s">
         <v>17</v>
       </c>
-      <c r="F13" s="61"/>
+      <c r="F13" s="60"/>
       <c r="G13" s="5" t="s">
         <v>26</v>
       </c>
@@ -1234,14 +1234,14 @@
       </c>
     </row>
     <row r="16" spans="1:7" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="60" t="s">
+      <c r="A16" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="61"/>
-      <c r="C16" s="60" t="s">
+      <c r="B16" s="60"/>
+      <c r="C16" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="61"/>
+      <c r="D16" s="60"/>
     </row>
     <row r="17" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
@@ -1272,10 +1272,10 @@
       </c>
     </row>
     <row r="19" spans="1:4" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="60" t="s">
+      <c r="A19" s="59" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="61"/>
+      <c r="B19" s="60"/>
     </row>
     <row r="20" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
@@ -1294,10 +1294,10 @@
       </c>
     </row>
     <row r="22" spans="1:4" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="60" t="s">
+      <c r="A22" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="61"/>
+      <c r="B22" s="60"/>
     </row>
     <row r="23" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
@@ -1382,16 +1382,16 @@
     <sortCondition ref="B2:B9"/>
   </sortState>
   <mergeCells count="10">
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A16:B16"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A16:B16"/>
   </mergeCells>
   <dataValidations count="16">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C14" xr:uid="{2C3D9587-ABAE-4E3F-8B22-396DF812BF02}">
@@ -1495,124 +1495,124 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:54" ht="27" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
-      <c r="I1" s="51"/>
-      <c r="J1" s="51"/>
-      <c r="K1" s="51"/>
-      <c r="L1" s="51"/>
-      <c r="M1" s="51"/>
-      <c r="N1" s="51"/>
-      <c r="O1" s="51"/>
-      <c r="P1" s="51"/>
-      <c r="Q1" s="51"/>
-      <c r="R1" s="51"/>
-      <c r="S1" s="51"/>
-      <c r="T1" s="51"/>
-      <c r="U1" s="52"/>
-      <c r="Z1" s="50" t="s">
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="52"/>
+      <c r="M1" s="52"/>
+      <c r="N1" s="52"/>
+      <c r="O1" s="52"/>
+      <c r="P1" s="52"/>
+      <c r="Q1" s="52"/>
+      <c r="R1" s="52"/>
+      <c r="S1" s="52"/>
+      <c r="T1" s="52"/>
+      <c r="U1" s="53"/>
+      <c r="Z1" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="AA1" s="51"/>
-      <c r="AB1" s="52"/>
-      <c r="AF1" s="50" t="s">
+      <c r="AA1" s="52"/>
+      <c r="AB1" s="53"/>
+      <c r="AF1" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="AG1" s="51"/>
-      <c r="AH1" s="51"/>
-      <c r="AI1" s="51"/>
-      <c r="AJ1" s="51"/>
-      <c r="AK1" s="51"/>
-      <c r="AL1" s="51"/>
-      <c r="AM1" s="51"/>
-      <c r="AN1" s="51"/>
-      <c r="AO1" s="51"/>
-      <c r="AP1" s="51"/>
-      <c r="AQ1" s="51"/>
-      <c r="AR1" s="51"/>
-      <c r="AS1" s="51"/>
-      <c r="AT1" s="51"/>
-      <c r="AU1" s="51"/>
-      <c r="AV1" s="51"/>
-      <c r="AW1" s="51"/>
-      <c r="AX1" s="51"/>
-      <c r="AY1" s="51"/>
-      <c r="AZ1" s="51"/>
-      <c r="BA1" s="52"/>
+      <c r="AG1" s="52"/>
+      <c r="AH1" s="52"/>
+      <c r="AI1" s="52"/>
+      <c r="AJ1" s="52"/>
+      <c r="AK1" s="52"/>
+      <c r="AL1" s="52"/>
+      <c r="AM1" s="52"/>
+      <c r="AN1" s="52"/>
+      <c r="AO1" s="52"/>
+      <c r="AP1" s="52"/>
+      <c r="AQ1" s="52"/>
+      <c r="AR1" s="52"/>
+      <c r="AS1" s="52"/>
+      <c r="AT1" s="52"/>
+      <c r="AU1" s="52"/>
+      <c r="AV1" s="52"/>
+      <c r="AW1" s="52"/>
+      <c r="AX1" s="52"/>
+      <c r="AY1" s="52"/>
+      <c r="AZ1" s="52"/>
+      <c r="BA1" s="53"/>
     </row>
     <row r="2" spans="1:54" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="48"/>
-      <c r="M2" s="46" t="s">
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="57"/>
+      <c r="M2" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="47"/>
-      <c r="O2" s="47"/>
-      <c r="P2" s="47"/>
-      <c r="Q2" s="47"/>
-      <c r="R2" s="48"/>
-      <c r="AI2" s="46" t="s">
+      <c r="N2" s="56"/>
+      <c r="O2" s="56"/>
+      <c r="P2" s="56"/>
+      <c r="Q2" s="56"/>
+      <c r="R2" s="57"/>
+      <c r="AI2" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="AJ2" s="47"/>
-      <c r="AK2" s="47"/>
-      <c r="AL2" s="47"/>
-      <c r="AM2" s="47"/>
-      <c r="AN2" s="47"/>
-      <c r="AO2" s="48"/>
-      <c r="AU2" s="46" t="s">
+      <c r="AJ2" s="56"/>
+      <c r="AK2" s="56"/>
+      <c r="AL2" s="56"/>
+      <c r="AM2" s="56"/>
+      <c r="AN2" s="56"/>
+      <c r="AO2" s="57"/>
+      <c r="AU2" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="AV2" s="47"/>
-      <c r="AW2" s="47"/>
-      <c r="AX2" s="47"/>
-      <c r="AY2" s="47"/>
-      <c r="AZ2" s="47"/>
-      <c r="BA2" s="48"/>
+      <c r="AV2" s="56"/>
+      <c r="AW2" s="56"/>
+      <c r="AX2" s="56"/>
+      <c r="AY2" s="56"/>
+      <c r="AZ2" s="56"/>
+      <c r="BA2" s="57"/>
     </row>
     <row r="3" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="42" t="s">
+      <c r="A3" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="42"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="42"/>
-      <c r="AI3" s="53" t="s">
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="AI3" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="AJ3" s="54"/>
-      <c r="AK3" s="54"/>
-      <c r="AL3" s="54"/>
-      <c r="AM3" s="54"/>
-      <c r="AN3" s="54"/>
-      <c r="AO3" s="55"/>
-      <c r="AU3" s="42" t="s">
+      <c r="AJ3" s="43"/>
+      <c r="AK3" s="43"/>
+      <c r="AL3" s="43"/>
+      <c r="AM3" s="43"/>
+      <c r="AN3" s="43"/>
+      <c r="AO3" s="44"/>
+      <c r="AU3" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="AV3" s="42"/>
-      <c r="AW3" s="42"/>
-      <c r="AX3" s="42"/>
-      <c r="AY3" s="42"/>
-      <c r="AZ3" s="42"/>
-      <c r="BA3" s="42"/>
+      <c r="AV3" s="49"/>
+      <c r="AW3" s="49"/>
+      <c r="AX3" s="49"/>
+      <c r="AY3" s="49"/>
+      <c r="AZ3" s="49"/>
+      <c r="BA3" s="49"/>
     </row>
     <row r="4" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
@@ -1636,15 +1636,15 @@
       <c r="G4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="53" t="s">
+      <c r="M4" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="N4" s="54"/>
-      <c r="O4" s="54"/>
-      <c r="P4" s="54"/>
-      <c r="Q4" s="54"/>
-      <c r="R4" s="54"/>
-      <c r="S4" s="55"/>
+      <c r="N4" s="43"/>
+      <c r="O4" s="43"/>
+      <c r="P4" s="43"/>
+      <c r="Q4" s="43"/>
+      <c r="R4" s="43"/>
+      <c r="S4" s="44"/>
       <c r="AI4" s="3" t="s">
         <v>2</v>
       </c>
@@ -1971,11 +1971,11 @@
       <c r="G8" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="I8" s="43" t="s">
+      <c r="I8" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="J8" s="43"/>
-      <c r="K8" s="43"/>
+      <c r="J8" s="50"/>
+      <c r="K8" s="50"/>
       <c r="M8" s="8">
         <v>3</v>
       </c>
@@ -2018,11 +2018,11 @@
       <c r="AO8" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="AQ8" s="43" t="s">
+      <c r="AQ8" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="AR8" s="43"/>
-      <c r="AS8" s="43"/>
+      <c r="AR8" s="50"/>
+      <c r="AS8" s="50"/>
       <c r="AU8" s="38">
         <v>4</v>
       </c>
@@ -2282,15 +2282,15 @@
       <c r="BA11" s="6"/>
     </row>
     <row r="12" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="42" t="s">
+      <c r="A12" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="42"/>
-      <c r="C12" s="42"/>
-      <c r="D12" s="42"/>
-      <c r="E12" s="42"/>
-      <c r="F12" s="42"/>
-      <c r="G12" s="42"/>
+      <c r="B12" s="49"/>
+      <c r="C12" s="49"/>
+      <c r="D12" s="49"/>
+      <c r="E12" s="49"/>
+      <c r="F12" s="49"/>
+      <c r="G12" s="49"/>
       <c r="L12" s="12"/>
       <c r="M12" s="8" t="s">
         <v>12</v>
@@ -2316,69 +2316,69 @@
       <c r="T12" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AI12" s="42" t="s">
+      <c r="AI12" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AJ12" s="42"/>
-      <c r="AK12" s="42"/>
-      <c r="AL12" s="42"/>
-      <c r="AM12" s="42"/>
-      <c r="AN12" s="42"/>
-      <c r="AO12" s="42"/>
+      <c r="AJ12" s="49"/>
+      <c r="AK12" s="49"/>
+      <c r="AL12" s="49"/>
+      <c r="AM12" s="49"/>
+      <c r="AN12" s="49"/>
+      <c r="AO12" s="49"/>
       <c r="AQ12" s="12"/>
-      <c r="AU12" s="42" t="s">
+      <c r="AU12" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AV12" s="42"/>
-      <c r="AW12" s="42"/>
-      <c r="AX12" s="42"/>
-      <c r="AY12" s="42"/>
-      <c r="AZ12" s="42"/>
-      <c r="BA12" s="42"/>
+      <c r="AV12" s="49"/>
+      <c r="AW12" s="49"/>
+      <c r="AX12" s="49"/>
+      <c r="AY12" s="49"/>
+      <c r="AZ12" s="49"/>
+      <c r="BA12" s="49"/>
     </row>
     <row r="13" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="L13" s="12"/>
-      <c r="M13" s="53" t="s">
+      <c r="M13" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="N13" s="54"/>
-      <c r="O13" s="54"/>
-      <c r="P13" s="54"/>
-      <c r="Q13" s="54"/>
-      <c r="R13" s="54"/>
-      <c r="S13" s="55"/>
+      <c r="N13" s="43"/>
+      <c r="O13" s="43"/>
+      <c r="P13" s="43"/>
+      <c r="Q13" s="43"/>
+      <c r="R13" s="43"/>
+      <c r="S13" s="44"/>
       <c r="AQ13" s="12"/>
     </row>
     <row r="14" spans="1:54" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="45" t="s">
+      <c r="A14" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="45"/>
-      <c r="C14" s="45"/>
-      <c r="D14" s="45"/>
-      <c r="E14" s="45"/>
-      <c r="F14" s="45"/>
-      <c r="G14" s="45"/>
-      <c r="L14" s="44" t="s">
+      <c r="B14" s="48"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="48"/>
+      <c r="E14" s="48"/>
+      <c r="F14" s="48"/>
+      <c r="G14" s="48"/>
+      <c r="L14" s="54" t="s">
         <v>32</v>
       </c>
-      <c r="M14" s="43"/>
-      <c r="N14" s="43"/>
-      <c r="AN14" s="43" t="s">
+      <c r="M14" s="50"/>
+      <c r="N14" s="50"/>
+      <c r="AN14" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="AO14" s="43"/>
-      <c r="AP14" s="43"/>
+      <c r="AO14" s="50"/>
+      <c r="AP14" s="50"/>
       <c r="AQ14" s="12"/>
-      <c r="AU14" s="45" t="s">
+      <c r="AU14" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="AV14" s="45"/>
-      <c r="AW14" s="45"/>
-      <c r="AX14" s="45"/>
-      <c r="AY14" s="45"/>
-      <c r="AZ14" s="45"/>
-      <c r="BA14" s="45"/>
+      <c r="AV14" s="48"/>
+      <c r="AW14" s="48"/>
+      <c r="AX14" s="48"/>
+      <c r="AY14" s="48"/>
+      <c r="AZ14" s="48"/>
+      <c r="BA14" s="48"/>
     </row>
     <row r="15" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
@@ -2606,19 +2606,19 @@
       <c r="G19" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="I19" s="43" t="s">
+      <c r="I19" s="50" t="s">
         <v>32</v>
       </c>
-      <c r="J19" s="43"/>
-      <c r="K19" s="43"/>
+      <c r="J19" s="50"/>
+      <c r="K19" s="50"/>
       <c r="L19" s="12"/>
       <c r="O19" s="12"/>
       <c r="AN19" s="12"/>
-      <c r="AQ19" s="44" t="s">
+      <c r="AQ19" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="AR19" s="43"/>
-      <c r="AS19" s="43"/>
+      <c r="AR19" s="50"/>
+      <c r="AS19" s="50"/>
       <c r="AU19" s="38">
         <v>4</v>
       </c>
@@ -2780,52 +2780,52 @@
       <c r="BA22" s="6"/>
     </row>
     <row r="23" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="42" t="s">
+      <c r="A23" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="B23" s="42"/>
-      <c r="C23" s="42"/>
-      <c r="D23" s="42"/>
-      <c r="E23" s="42"/>
-      <c r="F23" s="42"/>
-      <c r="G23" s="42"/>
+      <c r="B23" s="49"/>
+      <c r="C23" s="49"/>
+      <c r="D23" s="49"/>
+      <c r="E23" s="49"/>
+      <c r="F23" s="49"/>
+      <c r="G23" s="49"/>
       <c r="O23" s="12"/>
       <c r="AN23" s="12"/>
-      <c r="AU23" s="42" t="s">
+      <c r="AU23" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AV23" s="42"/>
-      <c r="AW23" s="42"/>
-      <c r="AX23" s="42"/>
-      <c r="AY23" s="42"/>
-      <c r="AZ23" s="42"/>
-      <c r="BA23" s="42"/>
+      <c r="AV23" s="49"/>
+      <c r="AW23" s="49"/>
+      <c r="AX23" s="49"/>
+      <c r="AY23" s="49"/>
+      <c r="AZ23" s="49"/>
+      <c r="BA23" s="49"/>
     </row>
     <row r="24" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="O24" s="12"/>
       <c r="AN24" s="12"/>
     </row>
     <row r="25" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="42" t="s">
+      <c r="A25" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="42"/>
-      <c r="C25" s="42"/>
-      <c r="D25" s="42"/>
-      <c r="E25" s="42"/>
-      <c r="F25" s="42"/>
-      <c r="G25" s="42"/>
+      <c r="B25" s="49"/>
+      <c r="C25" s="49"/>
+      <c r="D25" s="49"/>
+      <c r="E25" s="49"/>
+      <c r="F25" s="49"/>
+      <c r="G25" s="49"/>
       <c r="O25" s="12"/>
       <c r="AN25" s="12"/>
-      <c r="AU25" s="42" t="s">
+      <c r="AU25" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="AV25" s="42"/>
-      <c r="AW25" s="42"/>
-      <c r="AX25" s="42"/>
-      <c r="AY25" s="42"/>
-      <c r="AZ25" s="42"/>
-      <c r="BA25" s="42"/>
+      <c r="AV25" s="49"/>
+      <c r="AW25" s="49"/>
+      <c r="AX25" s="49"/>
+      <c r="AY25" s="49"/>
+      <c r="AZ25" s="49"/>
+      <c r="BA25" s="49"/>
     </row>
     <row r="26" spans="1:54" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A26" s="20" t="s">
@@ -2849,28 +2849,28 @@
       <c r="G26" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="O26" s="44" t="s">
+      <c r="O26" s="54" t="s">
         <v>26</v>
       </c>
-      <c r="P26" s="43"/>
-      <c r="Q26" s="43"/>
-      <c r="R26" s="43"/>
-      <c r="S26" s="43"/>
-      <c r="T26" s="43"/>
-      <c r="U26" s="43"/>
-      <c r="V26" s="43"/>
-      <c r="W26" s="43"/>
-      <c r="AE26" s="43" t="s">
+      <c r="P26" s="50"/>
+      <c r="Q26" s="50"/>
+      <c r="R26" s="50"/>
+      <c r="S26" s="50"/>
+      <c r="T26" s="50"/>
+      <c r="U26" s="50"/>
+      <c r="V26" s="50"/>
+      <c r="W26" s="50"/>
+      <c r="AE26" s="50" t="s">
         <v>38</v>
       </c>
-      <c r="AF26" s="43"/>
-      <c r="AG26" s="43"/>
-      <c r="AH26" s="43"/>
-      <c r="AI26" s="43"/>
-      <c r="AJ26" s="43"/>
-      <c r="AK26" s="43"/>
-      <c r="AL26" s="43"/>
-      <c r="AM26" s="49"/>
+      <c r="AF26" s="50"/>
+      <c r="AG26" s="50"/>
+      <c r="AH26" s="50"/>
+      <c r="AI26" s="50"/>
+      <c r="AJ26" s="50"/>
+      <c r="AK26" s="50"/>
+      <c r="AL26" s="50"/>
+      <c r="AM26" s="58"/>
       <c r="AU26" s="20" t="s">
         <v>2</v>
       </c>
@@ -2967,26 +2967,26 @@
         <v>54</v>
       </c>
       <c r="O28" s="12"/>
-      <c r="P28" s="53" t="s">
+      <c r="P28" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="Q28" s="54"/>
-      <c r="R28" s="54"/>
-      <c r="S28" s="54"/>
-      <c r="T28" s="54"/>
-      <c r="U28" s="54"/>
-      <c r="V28" s="55"/>
+      <c r="Q28" s="43"/>
+      <c r="R28" s="43"/>
+      <c r="S28" s="43"/>
+      <c r="T28" s="43"/>
+      <c r="U28" s="43"/>
+      <c r="V28" s="44"/>
       <c r="X28" s="12"/>
       <c r="AD28" s="13"/>
-      <c r="AF28" s="42" t="s">
+      <c r="AF28" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="AG28" s="42"/>
-      <c r="AH28" s="42"/>
-      <c r="AI28" s="42"/>
-      <c r="AJ28" s="42"/>
-      <c r="AK28" s="42"/>
-      <c r="AL28" s="42"/>
+      <c r="AG28" s="49"/>
+      <c r="AH28" s="49"/>
+      <c r="AI28" s="49"/>
+      <c r="AJ28" s="49"/>
+      <c r="AK28" s="49"/>
+      <c r="AL28" s="49"/>
       <c r="AN28" s="12"/>
       <c r="AU28" s="8">
         <v>2</v>
@@ -3122,11 +3122,11 @@
       <c r="G30" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="I30" s="43" t="s">
+      <c r="I30" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="J30" s="43"/>
-      <c r="K30" s="43"/>
+      <c r="J30" s="50"/>
+      <c r="K30" s="50"/>
       <c r="O30" s="12"/>
       <c r="P30" s="7">
         <v>1</v>
@@ -3173,11 +3173,11 @@
         <v>52</v>
       </c>
       <c r="AN30" s="12"/>
-      <c r="AQ30" s="43" t="s">
+      <c r="AQ30" s="50" t="s">
         <v>38</v>
       </c>
-      <c r="AR30" s="43"/>
-      <c r="AS30" s="43"/>
+      <c r="AR30" s="50"/>
+      <c r="AS30" s="50"/>
       <c r="AU30" s="38">
         <v>4</v>
       </c>
@@ -3464,15 +3464,15 @@
       <c r="BA33" s="6"/>
     </row>
     <row r="34" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="42" t="s">
+      <c r="A34" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="B34" s="42"/>
-      <c r="C34" s="42"/>
-      <c r="D34" s="42"/>
-      <c r="E34" s="42"/>
-      <c r="F34" s="42"/>
-      <c r="G34" s="42"/>
+      <c r="B34" s="49"/>
+      <c r="C34" s="49"/>
+      <c r="D34" s="49"/>
+      <c r="E34" s="49"/>
+      <c r="F34" s="49"/>
+      <c r="G34" s="49"/>
       <c r="L34" s="12"/>
       <c r="O34" s="12"/>
       <c r="P34" s="8" t="s">
@@ -3515,15 +3515,15 @@
       <c r="AL34" s="16"/>
       <c r="AN34" s="12"/>
       <c r="AQ34" s="12"/>
-      <c r="AU34" s="42" t="s">
+      <c r="AU34" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AV34" s="42"/>
-      <c r="AW34" s="42"/>
-      <c r="AX34" s="42"/>
-      <c r="AY34" s="42"/>
-      <c r="AZ34" s="42"/>
-      <c r="BA34" s="42"/>
+      <c r="AV34" s="49"/>
+      <c r="AW34" s="49"/>
+      <c r="AX34" s="49"/>
+      <c r="AY34" s="49"/>
+      <c r="AZ34" s="49"/>
+      <c r="BA34" s="49"/>
     </row>
     <row r="35" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="L35" s="12"/>
@@ -3564,20 +3564,20 @@
       <c r="AQ35" s="12"/>
     </row>
     <row r="36" spans="1:54" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="45" t="s">
+      <c r="A36" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="B36" s="45"/>
-      <c r="C36" s="45"/>
-      <c r="D36" s="45"/>
-      <c r="E36" s="45"/>
-      <c r="F36" s="45"/>
-      <c r="G36" s="45"/>
-      <c r="L36" s="44" t="s">
+      <c r="B36" s="48"/>
+      <c r="C36" s="48"/>
+      <c r="D36" s="48"/>
+      <c r="E36" s="48"/>
+      <c r="F36" s="48"/>
+      <c r="G36" s="48"/>
+      <c r="L36" s="54" t="s">
         <v>26</v>
       </c>
-      <c r="M36" s="43"/>
-      <c r="N36" s="43"/>
+      <c r="M36" s="50"/>
+      <c r="N36" s="50"/>
       <c r="O36" s="12"/>
       <c r="P36" s="8" t="s">
         <v>12</v>
@@ -3611,21 +3611,21 @@
       </c>
       <c r="AK36" s="36"/>
       <c r="AL36" s="37"/>
-      <c r="AN36" s="44" t="s">
+      <c r="AN36" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="AO36" s="43"/>
-      <c r="AP36" s="43"/>
+      <c r="AO36" s="50"/>
+      <c r="AP36" s="50"/>
       <c r="AQ36" s="12"/>
-      <c r="AU36" s="45" t="s">
+      <c r="AU36" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="AV36" s="45"/>
-      <c r="AW36" s="45"/>
-      <c r="AX36" s="45"/>
-      <c r="AY36" s="45"/>
-      <c r="AZ36" s="45"/>
-      <c r="BA36" s="45"/>
+      <c r="AV36" s="48"/>
+      <c r="AW36" s="48"/>
+      <c r="AX36" s="48"/>
+      <c r="AY36" s="48"/>
+      <c r="AZ36" s="48"/>
+      <c r="BA36" s="48"/>
     </row>
     <row r="37" spans="1:54" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A37" s="20" t="s">
@@ -3650,31 +3650,31 @@
         <v>9</v>
       </c>
       <c r="L37" s="12"/>
-      <c r="P37" s="56" t="s">
+      <c r="P37" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="Q37" s="57"/>
-      <c r="R37" s="57"/>
-      <c r="S37" s="57"/>
-      <c r="T37" s="57"/>
-      <c r="U37" s="57"/>
-      <c r="V37" s="58"/>
-      <c r="X37" s="44"/>
-      <c r="Y37" s="43"/>
-      <c r="Z37" s="43"/>
-      <c r="AA37" s="43"/>
-      <c r="AB37" s="43"/>
-      <c r="AC37" s="43"/>
-      <c r="AD37" s="49"/>
-      <c r="AF37" s="42" t="s">
+      <c r="Q37" s="46"/>
+      <c r="R37" s="46"/>
+      <c r="S37" s="46"/>
+      <c r="T37" s="46"/>
+      <c r="U37" s="46"/>
+      <c r="V37" s="47"/>
+      <c r="X37" s="54"/>
+      <c r="Y37" s="50"/>
+      <c r="Z37" s="50"/>
+      <c r="AA37" s="50"/>
+      <c r="AB37" s="50"/>
+      <c r="AC37" s="50"/>
+      <c r="AD37" s="58"/>
+      <c r="AF37" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AG37" s="42"/>
-      <c r="AH37" s="42"/>
-      <c r="AI37" s="42"/>
-      <c r="AJ37" s="42"/>
-      <c r="AK37" s="42"/>
-      <c r="AL37" s="42"/>
+      <c r="AG37" s="49"/>
+      <c r="AH37" s="49"/>
+      <c r="AI37" s="49"/>
+      <c r="AJ37" s="49"/>
+      <c r="AK37" s="49"/>
+      <c r="AL37" s="49"/>
       <c r="AQ37" s="12"/>
       <c r="AU37" s="3" t="s">
         <v>2</v>
@@ -3767,33 +3767,33 @@
         <v>53</v>
       </c>
       <c r="L39" s="12"/>
-      <c r="M39" s="53" t="s">
+      <c r="M39" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="N39" s="54"/>
-      <c r="O39" s="54"/>
-      <c r="P39" s="54"/>
-      <c r="Q39" s="54"/>
-      <c r="R39" s="54"/>
-      <c r="S39" s="55"/>
-      <c r="X39" s="42" t="s">
+      <c r="N39" s="43"/>
+      <c r="O39" s="43"/>
+      <c r="P39" s="43"/>
+      <c r="Q39" s="43"/>
+      <c r="R39" s="43"/>
+      <c r="S39" s="44"/>
+      <c r="X39" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="Y39" s="42"/>
-      <c r="Z39" s="42"/>
-      <c r="AA39" s="42"/>
-      <c r="AB39" s="42"/>
-      <c r="AC39" s="42"/>
-      <c r="AD39" s="42"/>
-      <c r="AI39" s="53" t="s">
+      <c r="Y39" s="49"/>
+      <c r="Z39" s="49"/>
+      <c r="AA39" s="49"/>
+      <c r="AB39" s="49"/>
+      <c r="AC39" s="49"/>
+      <c r="AD39" s="49"/>
+      <c r="AI39" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="AJ39" s="54"/>
-      <c r="AK39" s="54"/>
-      <c r="AL39" s="54"/>
-      <c r="AM39" s="54"/>
-      <c r="AN39" s="54"/>
-      <c r="AO39" s="55"/>
+      <c r="AJ39" s="43"/>
+      <c r="AK39" s="43"/>
+      <c r="AL39" s="43"/>
+      <c r="AM39" s="43"/>
+      <c r="AN39" s="43"/>
+      <c r="AO39" s="44"/>
       <c r="AQ39" s="12"/>
       <c r="AU39" s="8">
         <v>2</v>
@@ -3948,11 +3948,11 @@
       <c r="G41" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="I41" s="43" t="s">
+      <c r="I41" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="J41" s="43"/>
-      <c r="K41" s="43"/>
+      <c r="J41" s="50"/>
+      <c r="K41" s="50"/>
       <c r="L41" s="12"/>
       <c r="M41" s="7">
         <v>1</v>
@@ -4017,11 +4017,11 @@
       <c r="AO41" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="AQ41" s="44" t="s">
+      <c r="AQ41" s="54" t="s">
         <v>23</v>
       </c>
-      <c r="AR41" s="43"/>
-      <c r="AS41" s="43"/>
+      <c r="AR41" s="50"/>
+      <c r="AS41" s="50"/>
       <c r="AU41" s="38">
         <v>4</v>
       </c>
@@ -4319,12 +4319,18 @@
       <c r="Z44" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="AA44" s="13"/>
+      <c r="AA44" s="13">
+        <v>5</v>
+      </c>
       <c r="AB44" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="AC44" s="13"/>
-      <c r="AD44" s="16"/>
+      <c r="AC44" s="13">
+        <v>3</v>
+      </c>
+      <c r="AD44" s="16" t="s">
+        <v>68</v>
+      </c>
       <c r="AI44" s="8">
         <v>4</v>
       </c>
@@ -4363,15 +4369,15 @@
       <c r="BA44" s="6"/>
     </row>
     <row r="45" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="42" t="s">
+      <c r="A45" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="B45" s="42"/>
-      <c r="C45" s="42"/>
-      <c r="D45" s="42"/>
-      <c r="E45" s="42"/>
-      <c r="F45" s="42"/>
-      <c r="G45" s="42"/>
+      <c r="B45" s="49"/>
+      <c r="C45" s="49"/>
+      <c r="D45" s="49"/>
+      <c r="E45" s="49"/>
+      <c r="F45" s="49"/>
+      <c r="G45" s="49"/>
       <c r="M45" s="8" t="s">
         <v>11</v>
       </c>
@@ -4426,15 +4432,15 @@
       <c r="AP45" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AU45" s="42" t="s">
+      <c r="AU45" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AV45" s="42"/>
-      <c r="AW45" s="42"/>
-      <c r="AX45" s="42"/>
-      <c r="AY45" s="42"/>
-      <c r="AZ45" s="42"/>
-      <c r="BA45" s="42"/>
+      <c r="AV45" s="49"/>
+      <c r="AW45" s="49"/>
+      <c r="AX45" s="49"/>
+      <c r="AY45" s="49"/>
+      <c r="AZ45" s="49"/>
+      <c r="BA45" s="49"/>
     </row>
     <row r="46" spans="1:54" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="M46" s="8" t="s">
@@ -4537,45 +4543,65 @@
       <c r="AO47" s="6"/>
     </row>
     <row r="48" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="M48" s="53" t="s">
+      <c r="M48" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="N48" s="54"/>
-      <c r="O48" s="54"/>
-      <c r="P48" s="54"/>
-      <c r="Q48" s="54"/>
-      <c r="R48" s="54"/>
-      <c r="S48" s="55"/>
-      <c r="X48" s="42" t="s">
+      <c r="N48" s="43"/>
+      <c r="O48" s="43"/>
+      <c r="P48" s="43"/>
+      <c r="Q48" s="43"/>
+      <c r="R48" s="43"/>
+      <c r="S48" s="44"/>
+      <c r="X48" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="Y48" s="42"/>
-      <c r="Z48" s="42"/>
-      <c r="AA48" s="42"/>
-      <c r="AB48" s="42"/>
-      <c r="AC48" s="42"/>
-      <c r="AD48" s="42"/>
-      <c r="AI48" s="42" t="s">
+      <c r="Y48" s="49"/>
+      <c r="Z48" s="49"/>
+      <c r="AA48" s="49"/>
+      <c r="AB48" s="49"/>
+      <c r="AC48" s="49"/>
+      <c r="AD48" s="49"/>
+      <c r="AI48" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AJ48" s="42"/>
-      <c r="AK48" s="42"/>
-      <c r="AL48" s="42"/>
-      <c r="AM48" s="42"/>
-      <c r="AN48" s="42"/>
-      <c r="AO48" s="42"/>
+      <c r="AJ48" s="49"/>
+      <c r="AK48" s="49"/>
+      <c r="AL48" s="49"/>
+      <c r="AM48" s="49"/>
+      <c r="AN48" s="49"/>
+      <c r="AO48" s="49"/>
     </row>
     <row r="49" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="M48:S48"/>
-    <mergeCell ref="M39:S39"/>
-    <mergeCell ref="P37:V37"/>
-    <mergeCell ref="P28:V28"/>
-    <mergeCell ref="A36:G36"/>
-    <mergeCell ref="A45:G45"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="AU45:BA45"/>
+    <mergeCell ref="AF28:AL28"/>
+    <mergeCell ref="AF37:AL37"/>
+    <mergeCell ref="AQ30:AS30"/>
+    <mergeCell ref="AQ41:AS41"/>
+    <mergeCell ref="AU34:BA34"/>
+    <mergeCell ref="AU36:BA36"/>
+    <mergeCell ref="AU2:BA2"/>
+    <mergeCell ref="AU3:BA3"/>
+    <mergeCell ref="AU12:BA12"/>
+    <mergeCell ref="AU14:BA14"/>
+    <mergeCell ref="AU23:BA23"/>
+    <mergeCell ref="X37:AD37"/>
+    <mergeCell ref="AE26:AM26"/>
+    <mergeCell ref="Z1:AB1"/>
+    <mergeCell ref="X39:AD39"/>
+    <mergeCell ref="X48:AD48"/>
+    <mergeCell ref="AF1:BA1"/>
+    <mergeCell ref="AI2:AO2"/>
+    <mergeCell ref="AI3:AO3"/>
+    <mergeCell ref="AI12:AO12"/>
+    <mergeCell ref="AI39:AO39"/>
+    <mergeCell ref="AU25:BA25"/>
+    <mergeCell ref="AI48:AO48"/>
+    <mergeCell ref="AN14:AP14"/>
+    <mergeCell ref="AN36:AP36"/>
+    <mergeCell ref="AQ8:AS8"/>
+    <mergeCell ref="AQ19:AS19"/>
     <mergeCell ref="A1:U1"/>
     <mergeCell ref="O26:W26"/>
     <mergeCell ref="I41:K41"/>
@@ -4592,34 +4618,14 @@
     <mergeCell ref="I8:K8"/>
     <mergeCell ref="I19:K19"/>
     <mergeCell ref="A25:G25"/>
-    <mergeCell ref="X37:AD37"/>
-    <mergeCell ref="AE26:AM26"/>
-    <mergeCell ref="Z1:AB1"/>
-    <mergeCell ref="X39:AD39"/>
-    <mergeCell ref="X48:AD48"/>
-    <mergeCell ref="AF1:BA1"/>
-    <mergeCell ref="AI2:AO2"/>
-    <mergeCell ref="AI3:AO3"/>
-    <mergeCell ref="AI12:AO12"/>
-    <mergeCell ref="AI39:AO39"/>
-    <mergeCell ref="AU25:BA25"/>
-    <mergeCell ref="AI48:AO48"/>
-    <mergeCell ref="AN14:AP14"/>
-    <mergeCell ref="AN36:AP36"/>
-    <mergeCell ref="AQ8:AS8"/>
-    <mergeCell ref="AQ19:AS19"/>
-    <mergeCell ref="AU2:BA2"/>
-    <mergeCell ref="AU3:BA3"/>
-    <mergeCell ref="AU12:BA12"/>
-    <mergeCell ref="AU14:BA14"/>
-    <mergeCell ref="AU23:BA23"/>
-    <mergeCell ref="AU45:BA45"/>
-    <mergeCell ref="AF28:AL28"/>
-    <mergeCell ref="AF37:AL37"/>
-    <mergeCell ref="AQ30:AS30"/>
-    <mergeCell ref="AQ41:AS41"/>
-    <mergeCell ref="AU34:BA34"/>
-    <mergeCell ref="AU36:BA36"/>
+    <mergeCell ref="M48:S48"/>
+    <mergeCell ref="M39:S39"/>
+    <mergeCell ref="P37:V37"/>
+    <mergeCell ref="P28:V28"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="A34:G34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/2025_2026/Playoffs/Brackets.xlsx
+++ b/2025_2026/Playoffs/Brackets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\NHLStats\2025_2026\Playoffs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C7256A2-9190-4CC4-B53D-453FEE3E6A94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77B5898A-4CE2-41C3-890C-E62D88AE4777}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="1590" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="102">
   <si>
     <t>Eastern Conference Playoff Teams</t>
   </si>
@@ -329,6 +329,9 @@
   </si>
   <si>
     <t>Golden Knights Lead 2-1</t>
+  </si>
+  <si>
+    <t>Hurricanes Lead 3-2</t>
   </si>
 </sst>
 </file>
@@ -707,6 +710,39 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -725,46 +761,13 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1134,18 +1137,18 @@
     </row>
     <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="11" spans="1:7" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="61" t="s">
+      <c r="A11" s="59" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="61"/>
-      <c r="C11" s="61" t="s">
+      <c r="B11" s="59"/>
+      <c r="C11" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="61"/>
-      <c r="E11" s="61" t="s">
+      <c r="D11" s="59"/>
+      <c r="E11" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="61"/>
+      <c r="F11" s="59"/>
       <c r="G11" s="4" t="s">
         <v>18</v>
       </c>
@@ -1174,18 +1177,18 @@
       </c>
     </row>
     <row r="13" spans="1:7" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="59" t="s">
+      <c r="A13" s="60" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="60"/>
-      <c r="C13" s="59" t="s">
+      <c r="B13" s="61"/>
+      <c r="C13" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="D13" s="60"/>
-      <c r="E13" s="59" t="s">
+      <c r="D13" s="61"/>
+      <c r="E13" s="60" t="s">
         <v>17</v>
       </c>
-      <c r="F13" s="60"/>
+      <c r="F13" s="61"/>
       <c r="G13" s="5" t="s">
         <v>26</v>
       </c>
@@ -1234,14 +1237,14 @@
       </c>
     </row>
     <row r="16" spans="1:7" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="59" t="s">
+      <c r="A16" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="60"/>
-      <c r="C16" s="59" t="s">
+      <c r="B16" s="61"/>
+      <c r="C16" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="60"/>
+      <c r="D16" s="61"/>
     </row>
     <row r="17" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
@@ -1272,10 +1275,10 @@
       </c>
     </row>
     <row r="19" spans="1:4" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="59" t="s">
+      <c r="A19" s="60" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="60"/>
+      <c r="B19" s="61"/>
     </row>
     <row r="20" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
@@ -1294,10 +1297,10 @@
       </c>
     </row>
     <row r="22" spans="1:4" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="59" t="s">
+      <c r="A22" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="60"/>
+      <c r="B22" s="61"/>
     </row>
     <row r="23" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
@@ -1382,16 +1385,16 @@
     <sortCondition ref="B2:B9"/>
   </sortState>
   <mergeCells count="10">
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C16:D16"/>
     <mergeCell ref="E11:F11"/>
     <mergeCell ref="E13:F13"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C16:D16"/>
   </mergeCells>
   <dataValidations count="16">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C14" xr:uid="{2C3D9587-ABAE-4E3F-8B22-396DF812BF02}">
@@ -1495,124 +1498,124 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:54" ht="27" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
-      <c r="M1" s="52"/>
-      <c r="N1" s="52"/>
-      <c r="O1" s="52"/>
-      <c r="P1" s="52"/>
-      <c r="Q1" s="52"/>
-      <c r="R1" s="52"/>
-      <c r="S1" s="52"/>
-      <c r="T1" s="52"/>
-      <c r="U1" s="53"/>
-      <c r="Z1" s="51" t="s">
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
+      <c r="K1" s="51"/>
+      <c r="L1" s="51"/>
+      <c r="M1" s="51"/>
+      <c r="N1" s="51"/>
+      <c r="O1" s="51"/>
+      <c r="P1" s="51"/>
+      <c r="Q1" s="51"/>
+      <c r="R1" s="51"/>
+      <c r="S1" s="51"/>
+      <c r="T1" s="51"/>
+      <c r="U1" s="52"/>
+      <c r="Z1" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="AA1" s="52"/>
-      <c r="AB1" s="53"/>
-      <c r="AF1" s="51" t="s">
+      <c r="AA1" s="51"/>
+      <c r="AB1" s="52"/>
+      <c r="AF1" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="AG1" s="52"/>
-      <c r="AH1" s="52"/>
-      <c r="AI1" s="52"/>
-      <c r="AJ1" s="52"/>
-      <c r="AK1" s="52"/>
-      <c r="AL1" s="52"/>
-      <c r="AM1" s="52"/>
-      <c r="AN1" s="52"/>
-      <c r="AO1" s="52"/>
-      <c r="AP1" s="52"/>
-      <c r="AQ1" s="52"/>
-      <c r="AR1" s="52"/>
-      <c r="AS1" s="52"/>
-      <c r="AT1" s="52"/>
-      <c r="AU1" s="52"/>
-      <c r="AV1" s="52"/>
-      <c r="AW1" s="52"/>
-      <c r="AX1" s="52"/>
-      <c r="AY1" s="52"/>
-      <c r="AZ1" s="52"/>
-      <c r="BA1" s="53"/>
+      <c r="AG1" s="51"/>
+      <c r="AH1" s="51"/>
+      <c r="AI1" s="51"/>
+      <c r="AJ1" s="51"/>
+      <c r="AK1" s="51"/>
+      <c r="AL1" s="51"/>
+      <c r="AM1" s="51"/>
+      <c r="AN1" s="51"/>
+      <c r="AO1" s="51"/>
+      <c r="AP1" s="51"/>
+      <c r="AQ1" s="51"/>
+      <c r="AR1" s="51"/>
+      <c r="AS1" s="51"/>
+      <c r="AT1" s="51"/>
+      <c r="AU1" s="51"/>
+      <c r="AV1" s="51"/>
+      <c r="AW1" s="51"/>
+      <c r="AX1" s="51"/>
+      <c r="AY1" s="51"/>
+      <c r="AZ1" s="51"/>
+      <c r="BA1" s="52"/>
     </row>
     <row r="2" spans="1:54" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="55" t="s">
+      <c r="A2" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="57"/>
-      <c r="M2" s="55" t="s">
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="48"/>
+      <c r="M2" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="56"/>
-      <c r="O2" s="56"/>
-      <c r="P2" s="56"/>
-      <c r="Q2" s="56"/>
-      <c r="R2" s="57"/>
-      <c r="AI2" s="55" t="s">
+      <c r="N2" s="47"/>
+      <c r="O2" s="47"/>
+      <c r="P2" s="47"/>
+      <c r="Q2" s="47"/>
+      <c r="R2" s="48"/>
+      <c r="AI2" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="AJ2" s="56"/>
-      <c r="AK2" s="56"/>
-      <c r="AL2" s="56"/>
-      <c r="AM2" s="56"/>
-      <c r="AN2" s="56"/>
-      <c r="AO2" s="57"/>
-      <c r="AU2" s="55" t="s">
+      <c r="AJ2" s="47"/>
+      <c r="AK2" s="47"/>
+      <c r="AL2" s="47"/>
+      <c r="AM2" s="47"/>
+      <c r="AN2" s="47"/>
+      <c r="AO2" s="48"/>
+      <c r="AU2" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="AV2" s="56"/>
-      <c r="AW2" s="56"/>
-      <c r="AX2" s="56"/>
-      <c r="AY2" s="56"/>
-      <c r="AZ2" s="56"/>
-      <c r="BA2" s="57"/>
+      <c r="AV2" s="47"/>
+      <c r="AW2" s="47"/>
+      <c r="AX2" s="47"/>
+      <c r="AY2" s="47"/>
+      <c r="AZ2" s="47"/>
+      <c r="BA2" s="48"/>
     </row>
     <row r="3" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="49" t="s">
+      <c r="A3" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="49"/>
-      <c r="C3" s="49"/>
-      <c r="D3" s="49"/>
-      <c r="E3" s="49"/>
-      <c r="F3" s="49"/>
-      <c r="G3" s="49"/>
-      <c r="AI3" s="42" t="s">
+      <c r="B3" s="42"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="42"/>
+      <c r="AI3" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="AJ3" s="43"/>
-      <c r="AK3" s="43"/>
-      <c r="AL3" s="43"/>
-      <c r="AM3" s="43"/>
-      <c r="AN3" s="43"/>
-      <c r="AO3" s="44"/>
-      <c r="AU3" s="49" t="s">
+      <c r="AJ3" s="54"/>
+      <c r="AK3" s="54"/>
+      <c r="AL3" s="54"/>
+      <c r="AM3" s="54"/>
+      <c r="AN3" s="54"/>
+      <c r="AO3" s="55"/>
+      <c r="AU3" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="AV3" s="49"/>
-      <c r="AW3" s="49"/>
-      <c r="AX3" s="49"/>
-      <c r="AY3" s="49"/>
-      <c r="AZ3" s="49"/>
-      <c r="BA3" s="49"/>
+      <c r="AV3" s="42"/>
+      <c r="AW3" s="42"/>
+      <c r="AX3" s="42"/>
+      <c r="AY3" s="42"/>
+      <c r="AZ3" s="42"/>
+      <c r="BA3" s="42"/>
     </row>
     <row r="4" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
@@ -1636,15 +1639,15 @@
       <c r="G4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="42" t="s">
+      <c r="M4" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="N4" s="43"/>
-      <c r="O4" s="43"/>
-      <c r="P4" s="43"/>
-      <c r="Q4" s="43"/>
-      <c r="R4" s="43"/>
-      <c r="S4" s="44"/>
+      <c r="N4" s="54"/>
+      <c r="O4" s="54"/>
+      <c r="P4" s="54"/>
+      <c r="Q4" s="54"/>
+      <c r="R4" s="54"/>
+      <c r="S4" s="55"/>
       <c r="AI4" s="3" t="s">
         <v>2</v>
       </c>
@@ -1971,11 +1974,11 @@
       <c r="G8" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="I8" s="50" t="s">
+      <c r="I8" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="J8" s="50"/>
-      <c r="K8" s="50"/>
+      <c r="J8" s="43"/>
+      <c r="K8" s="43"/>
       <c r="M8" s="8">
         <v>3</v>
       </c>
@@ -2018,11 +2021,11 @@
       <c r="AO8" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="AQ8" s="50" t="s">
+      <c r="AQ8" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="AR8" s="50"/>
-      <c r="AS8" s="50"/>
+      <c r="AR8" s="43"/>
+      <c r="AS8" s="43"/>
       <c r="AU8" s="38">
         <v>4</v>
       </c>
@@ -2282,15 +2285,15 @@
       <c r="BA11" s="6"/>
     </row>
     <row r="12" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="49" t="s">
+      <c r="A12" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="49"/>
-      <c r="C12" s="49"/>
-      <c r="D12" s="49"/>
-      <c r="E12" s="49"/>
-      <c r="F12" s="49"/>
-      <c r="G12" s="49"/>
+      <c r="B12" s="42"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="42"/>
       <c r="L12" s="12"/>
       <c r="M12" s="8" t="s">
         <v>12</v>
@@ -2316,69 +2319,69 @@
       <c r="T12" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AI12" s="49" t="s">
+      <c r="AI12" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AJ12" s="49"/>
-      <c r="AK12" s="49"/>
-      <c r="AL12" s="49"/>
-      <c r="AM12" s="49"/>
-      <c r="AN12" s="49"/>
-      <c r="AO12" s="49"/>
+      <c r="AJ12" s="42"/>
+      <c r="AK12" s="42"/>
+      <c r="AL12" s="42"/>
+      <c r="AM12" s="42"/>
+      <c r="AN12" s="42"/>
+      <c r="AO12" s="42"/>
       <c r="AQ12" s="12"/>
-      <c r="AU12" s="49" t="s">
+      <c r="AU12" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AV12" s="49"/>
-      <c r="AW12" s="49"/>
-      <c r="AX12" s="49"/>
-      <c r="AY12" s="49"/>
-      <c r="AZ12" s="49"/>
-      <c r="BA12" s="49"/>
+      <c r="AV12" s="42"/>
+      <c r="AW12" s="42"/>
+      <c r="AX12" s="42"/>
+      <c r="AY12" s="42"/>
+      <c r="AZ12" s="42"/>
+      <c r="BA12" s="42"/>
     </row>
     <row r="13" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="L13" s="12"/>
-      <c r="M13" s="42" t="s">
+      <c r="M13" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="N13" s="43"/>
-      <c r="O13" s="43"/>
-      <c r="P13" s="43"/>
-      <c r="Q13" s="43"/>
-      <c r="R13" s="43"/>
-      <c r="S13" s="44"/>
+      <c r="N13" s="54"/>
+      <c r="O13" s="54"/>
+      <c r="P13" s="54"/>
+      <c r="Q13" s="54"/>
+      <c r="R13" s="54"/>
+      <c r="S13" s="55"/>
       <c r="AQ13" s="12"/>
     </row>
     <row r="14" spans="1:54" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="48" t="s">
+      <c r="A14" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="48"/>
-      <c r="C14" s="48"/>
-      <c r="D14" s="48"/>
-      <c r="E14" s="48"/>
-      <c r="F14" s="48"/>
-      <c r="G14" s="48"/>
-      <c r="L14" s="54" t="s">
+      <c r="B14" s="45"/>
+      <c r="C14" s="45"/>
+      <c r="D14" s="45"/>
+      <c r="E14" s="45"/>
+      <c r="F14" s="45"/>
+      <c r="G14" s="45"/>
+      <c r="L14" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="M14" s="50"/>
-      <c r="N14" s="50"/>
-      <c r="AN14" s="50" t="s">
+      <c r="M14" s="43"/>
+      <c r="N14" s="43"/>
+      <c r="AN14" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="AO14" s="50"/>
-      <c r="AP14" s="50"/>
+      <c r="AO14" s="43"/>
+      <c r="AP14" s="43"/>
       <c r="AQ14" s="12"/>
-      <c r="AU14" s="48" t="s">
+      <c r="AU14" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="AV14" s="48"/>
-      <c r="AW14" s="48"/>
-      <c r="AX14" s="48"/>
-      <c r="AY14" s="48"/>
-      <c r="AZ14" s="48"/>
-      <c r="BA14" s="48"/>
+      <c r="AV14" s="45"/>
+      <c r="AW14" s="45"/>
+      <c r="AX14" s="45"/>
+      <c r="AY14" s="45"/>
+      <c r="AZ14" s="45"/>
+      <c r="BA14" s="45"/>
     </row>
     <row r="15" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
@@ -2606,19 +2609,19 @@
       <c r="G19" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="I19" s="50" t="s">
+      <c r="I19" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="J19" s="50"/>
-      <c r="K19" s="50"/>
+      <c r="J19" s="43"/>
+      <c r="K19" s="43"/>
       <c r="L19" s="12"/>
       <c r="O19" s="12"/>
       <c r="AN19" s="12"/>
-      <c r="AQ19" s="54" t="s">
+      <c r="AQ19" s="44" t="s">
         <v>31</v>
       </c>
-      <c r="AR19" s="50"/>
-      <c r="AS19" s="50"/>
+      <c r="AR19" s="43"/>
+      <c r="AS19" s="43"/>
       <c r="AU19" s="38">
         <v>4</v>
       </c>
@@ -2780,52 +2783,52 @@
       <c r="BA22" s="6"/>
     </row>
     <row r="23" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="49" t="s">
+      <c r="A23" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B23" s="49"/>
-      <c r="C23" s="49"/>
-      <c r="D23" s="49"/>
-      <c r="E23" s="49"/>
-      <c r="F23" s="49"/>
-      <c r="G23" s="49"/>
+      <c r="B23" s="42"/>
+      <c r="C23" s="42"/>
+      <c r="D23" s="42"/>
+      <c r="E23" s="42"/>
+      <c r="F23" s="42"/>
+      <c r="G23" s="42"/>
       <c r="O23" s="12"/>
       <c r="AN23" s="12"/>
-      <c r="AU23" s="49" t="s">
+      <c r="AU23" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AV23" s="49"/>
-      <c r="AW23" s="49"/>
-      <c r="AX23" s="49"/>
-      <c r="AY23" s="49"/>
-      <c r="AZ23" s="49"/>
-      <c r="BA23" s="49"/>
+      <c r="AV23" s="42"/>
+      <c r="AW23" s="42"/>
+      <c r="AX23" s="42"/>
+      <c r="AY23" s="42"/>
+      <c r="AZ23" s="42"/>
+      <c r="BA23" s="42"/>
     </row>
     <row r="24" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="O24" s="12"/>
       <c r="AN24" s="12"/>
     </row>
     <row r="25" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="49" t="s">
+      <c r="A25" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="49"/>
-      <c r="C25" s="49"/>
-      <c r="D25" s="49"/>
-      <c r="E25" s="49"/>
-      <c r="F25" s="49"/>
-      <c r="G25" s="49"/>
+      <c r="B25" s="42"/>
+      <c r="C25" s="42"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="42"/>
+      <c r="F25" s="42"/>
+      <c r="G25" s="42"/>
       <c r="O25" s="12"/>
       <c r="AN25" s="12"/>
-      <c r="AU25" s="49" t="s">
+      <c r="AU25" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="AV25" s="49"/>
-      <c r="AW25" s="49"/>
-      <c r="AX25" s="49"/>
-      <c r="AY25" s="49"/>
-      <c r="AZ25" s="49"/>
-      <c r="BA25" s="49"/>
+      <c r="AV25" s="42"/>
+      <c r="AW25" s="42"/>
+      <c r="AX25" s="42"/>
+      <c r="AY25" s="42"/>
+      <c r="AZ25" s="42"/>
+      <c r="BA25" s="42"/>
     </row>
     <row r="26" spans="1:54" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A26" s="20" t="s">
@@ -2849,28 +2852,28 @@
       <c r="G26" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="O26" s="54" t="s">
+      <c r="O26" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="P26" s="50"/>
-      <c r="Q26" s="50"/>
-      <c r="R26" s="50"/>
-      <c r="S26" s="50"/>
-      <c r="T26" s="50"/>
-      <c r="U26" s="50"/>
-      <c r="V26" s="50"/>
-      <c r="W26" s="50"/>
-      <c r="AE26" s="50" t="s">
+      <c r="P26" s="43"/>
+      <c r="Q26" s="43"/>
+      <c r="R26" s="43"/>
+      <c r="S26" s="43"/>
+      <c r="T26" s="43"/>
+      <c r="U26" s="43"/>
+      <c r="V26" s="43"/>
+      <c r="W26" s="43"/>
+      <c r="AE26" s="43" t="s">
         <v>38</v>
       </c>
-      <c r="AF26" s="50"/>
-      <c r="AG26" s="50"/>
-      <c r="AH26" s="50"/>
-      <c r="AI26" s="50"/>
-      <c r="AJ26" s="50"/>
-      <c r="AK26" s="50"/>
-      <c r="AL26" s="50"/>
-      <c r="AM26" s="58"/>
+      <c r="AF26" s="43"/>
+      <c r="AG26" s="43"/>
+      <c r="AH26" s="43"/>
+      <c r="AI26" s="43"/>
+      <c r="AJ26" s="43"/>
+      <c r="AK26" s="43"/>
+      <c r="AL26" s="43"/>
+      <c r="AM26" s="49"/>
       <c r="AU26" s="20" t="s">
         <v>2</v>
       </c>
@@ -2967,26 +2970,26 @@
         <v>54</v>
       </c>
       <c r="O28" s="12"/>
-      <c r="P28" s="42" t="s">
+      <c r="P28" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="Q28" s="43"/>
-      <c r="R28" s="43"/>
-      <c r="S28" s="43"/>
-      <c r="T28" s="43"/>
-      <c r="U28" s="43"/>
-      <c r="V28" s="44"/>
+      <c r="Q28" s="54"/>
+      <c r="R28" s="54"/>
+      <c r="S28" s="54"/>
+      <c r="T28" s="54"/>
+      <c r="U28" s="54"/>
+      <c r="V28" s="55"/>
       <c r="X28" s="12"/>
       <c r="AD28" s="13"/>
-      <c r="AF28" s="49" t="s">
+      <c r="AF28" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="AG28" s="49"/>
-      <c r="AH28" s="49"/>
-      <c r="AI28" s="49"/>
-      <c r="AJ28" s="49"/>
-      <c r="AK28" s="49"/>
-      <c r="AL28" s="49"/>
+      <c r="AG28" s="42"/>
+      <c r="AH28" s="42"/>
+      <c r="AI28" s="42"/>
+      <c r="AJ28" s="42"/>
+      <c r="AK28" s="42"/>
+      <c r="AL28" s="42"/>
       <c r="AN28" s="12"/>
       <c r="AU28" s="8">
         <v>2</v>
@@ -3122,11 +3125,11 @@
       <c r="G30" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="I30" s="50" t="s">
+      <c r="I30" s="43" t="s">
         <v>26</v>
       </c>
-      <c r="J30" s="50"/>
-      <c r="K30" s="50"/>
+      <c r="J30" s="43"/>
+      <c r="K30" s="43"/>
       <c r="O30" s="12"/>
       <c r="P30" s="7">
         <v>1</v>
@@ -3173,11 +3176,11 @@
         <v>52</v>
       </c>
       <c r="AN30" s="12"/>
-      <c r="AQ30" s="50" t="s">
+      <c r="AQ30" s="43" t="s">
         <v>38</v>
       </c>
-      <c r="AR30" s="50"/>
-      <c r="AS30" s="50"/>
+      <c r="AR30" s="43"/>
+      <c r="AS30" s="43"/>
       <c r="AU30" s="38">
         <v>4</v>
       </c>
@@ -3464,15 +3467,15 @@
       <c r="BA33" s="6"/>
     </row>
     <row r="34" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="49" t="s">
+      <c r="A34" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B34" s="49"/>
-      <c r="C34" s="49"/>
-      <c r="D34" s="49"/>
-      <c r="E34" s="49"/>
-      <c r="F34" s="49"/>
-      <c r="G34" s="49"/>
+      <c r="B34" s="42"/>
+      <c r="C34" s="42"/>
+      <c r="D34" s="42"/>
+      <c r="E34" s="42"/>
+      <c r="F34" s="42"/>
+      <c r="G34" s="42"/>
       <c r="L34" s="12"/>
       <c r="O34" s="12"/>
       <c r="P34" s="8" t="s">
@@ -3515,15 +3518,15 @@
       <c r="AL34" s="16"/>
       <c r="AN34" s="12"/>
       <c r="AQ34" s="12"/>
-      <c r="AU34" s="49" t="s">
+      <c r="AU34" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AV34" s="49"/>
-      <c r="AW34" s="49"/>
-      <c r="AX34" s="49"/>
-      <c r="AY34" s="49"/>
-      <c r="AZ34" s="49"/>
-      <c r="BA34" s="49"/>
+      <c r="AV34" s="42"/>
+      <c r="AW34" s="42"/>
+      <c r="AX34" s="42"/>
+      <c r="AY34" s="42"/>
+      <c r="AZ34" s="42"/>
+      <c r="BA34" s="42"/>
     </row>
     <row r="35" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="L35" s="12"/>
@@ -3564,20 +3567,20 @@
       <c r="AQ35" s="12"/>
     </row>
     <row r="36" spans="1:54" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="48" t="s">
+      <c r="A36" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="B36" s="48"/>
-      <c r="C36" s="48"/>
-      <c r="D36" s="48"/>
-      <c r="E36" s="48"/>
-      <c r="F36" s="48"/>
-      <c r="G36" s="48"/>
-      <c r="L36" s="54" t="s">
+      <c r="B36" s="45"/>
+      <c r="C36" s="45"/>
+      <c r="D36" s="45"/>
+      <c r="E36" s="45"/>
+      <c r="F36" s="45"/>
+      <c r="G36" s="45"/>
+      <c r="L36" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="M36" s="50"/>
-      <c r="N36" s="50"/>
+      <c r="M36" s="43"/>
+      <c r="N36" s="43"/>
       <c r="O36" s="12"/>
       <c r="P36" s="8" t="s">
         <v>12</v>
@@ -3611,21 +3614,21 @@
       </c>
       <c r="AK36" s="36"/>
       <c r="AL36" s="37"/>
-      <c r="AN36" s="54" t="s">
+      <c r="AN36" s="44" t="s">
         <v>38</v>
       </c>
-      <c r="AO36" s="50"/>
-      <c r="AP36" s="50"/>
+      <c r="AO36" s="43"/>
+      <c r="AP36" s="43"/>
       <c r="AQ36" s="12"/>
-      <c r="AU36" s="48" t="s">
+      <c r="AU36" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="AV36" s="48"/>
-      <c r="AW36" s="48"/>
-      <c r="AX36" s="48"/>
-      <c r="AY36" s="48"/>
-      <c r="AZ36" s="48"/>
-      <c r="BA36" s="48"/>
+      <c r="AV36" s="45"/>
+      <c r="AW36" s="45"/>
+      <c r="AX36" s="45"/>
+      <c r="AY36" s="45"/>
+      <c r="AZ36" s="45"/>
+      <c r="BA36" s="45"/>
     </row>
     <row r="37" spans="1:54" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A37" s="20" t="s">
@@ -3650,31 +3653,31 @@
         <v>9</v>
       </c>
       <c r="L37" s="12"/>
-      <c r="P37" s="45" t="s">
+      <c r="P37" s="56" t="s">
         <v>13</v>
       </c>
-      <c r="Q37" s="46"/>
-      <c r="R37" s="46"/>
-      <c r="S37" s="46"/>
-      <c r="T37" s="46"/>
-      <c r="U37" s="46"/>
-      <c r="V37" s="47"/>
-      <c r="X37" s="54"/>
-      <c r="Y37" s="50"/>
-      <c r="Z37" s="50"/>
-      <c r="AA37" s="50"/>
-      <c r="AB37" s="50"/>
-      <c r="AC37" s="50"/>
-      <c r="AD37" s="58"/>
-      <c r="AF37" s="49" t="s">
+      <c r="Q37" s="57"/>
+      <c r="R37" s="57"/>
+      <c r="S37" s="57"/>
+      <c r="T37" s="57"/>
+      <c r="U37" s="57"/>
+      <c r="V37" s="58"/>
+      <c r="X37" s="44"/>
+      <c r="Y37" s="43"/>
+      <c r="Z37" s="43"/>
+      <c r="AA37" s="43"/>
+      <c r="AB37" s="43"/>
+      <c r="AC37" s="43"/>
+      <c r="AD37" s="49"/>
+      <c r="AF37" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AG37" s="49"/>
-      <c r="AH37" s="49"/>
-      <c r="AI37" s="49"/>
-      <c r="AJ37" s="49"/>
-      <c r="AK37" s="49"/>
-      <c r="AL37" s="49"/>
+      <c r="AG37" s="42"/>
+      <c r="AH37" s="42"/>
+      <c r="AI37" s="42"/>
+      <c r="AJ37" s="42"/>
+      <c r="AK37" s="42"/>
+      <c r="AL37" s="42"/>
       <c r="AQ37" s="12"/>
       <c r="AU37" s="3" t="s">
         <v>2</v>
@@ -3767,33 +3770,33 @@
         <v>53</v>
       </c>
       <c r="L39" s="12"/>
-      <c r="M39" s="42" t="s">
+      <c r="M39" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="N39" s="43"/>
-      <c r="O39" s="43"/>
-      <c r="P39" s="43"/>
-      <c r="Q39" s="43"/>
-      <c r="R39" s="43"/>
-      <c r="S39" s="44"/>
-      <c r="X39" s="49" t="s">
+      <c r="N39" s="54"/>
+      <c r="O39" s="54"/>
+      <c r="P39" s="54"/>
+      <c r="Q39" s="54"/>
+      <c r="R39" s="54"/>
+      <c r="S39" s="55"/>
+      <c r="X39" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="Y39" s="49"/>
-      <c r="Z39" s="49"/>
-      <c r="AA39" s="49"/>
-      <c r="AB39" s="49"/>
-      <c r="AC39" s="49"/>
-      <c r="AD39" s="49"/>
-      <c r="AI39" s="42" t="s">
+      <c r="Y39" s="42"/>
+      <c r="Z39" s="42"/>
+      <c r="AA39" s="42"/>
+      <c r="AB39" s="42"/>
+      <c r="AC39" s="42"/>
+      <c r="AD39" s="42"/>
+      <c r="AI39" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="AJ39" s="43"/>
-      <c r="AK39" s="43"/>
-      <c r="AL39" s="43"/>
-      <c r="AM39" s="43"/>
-      <c r="AN39" s="43"/>
-      <c r="AO39" s="44"/>
+      <c r="AJ39" s="54"/>
+      <c r="AK39" s="54"/>
+      <c r="AL39" s="54"/>
+      <c r="AM39" s="54"/>
+      <c r="AN39" s="54"/>
+      <c r="AO39" s="55"/>
       <c r="AQ39" s="12"/>
       <c r="AU39" s="8">
         <v>2</v>
@@ -3948,11 +3951,11 @@
       <c r="G41" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="I41" s="50" t="s">
+      <c r="I41" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="J41" s="50"/>
-      <c r="K41" s="50"/>
+      <c r="J41" s="43"/>
+      <c r="K41" s="43"/>
       <c r="L41" s="12"/>
       <c r="M41" s="7">
         <v>1</v>
@@ -4017,11 +4020,11 @@
       <c r="AO41" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="AQ41" s="54" t="s">
+      <c r="AQ41" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="AR41" s="50"/>
-      <c r="AS41" s="50"/>
+      <c r="AR41" s="43"/>
+      <c r="AS41" s="43"/>
       <c r="AU41" s="38">
         <v>4</v>
       </c>
@@ -4369,15 +4372,15 @@
       <c r="BA44" s="6"/>
     </row>
     <row r="45" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="49" t="s">
+      <c r="A45" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B45" s="49"/>
-      <c r="C45" s="49"/>
-      <c r="D45" s="49"/>
-      <c r="E45" s="49"/>
-      <c r="F45" s="49"/>
-      <c r="G45" s="49"/>
+      <c r="B45" s="42"/>
+      <c r="C45" s="42"/>
+      <c r="D45" s="42"/>
+      <c r="E45" s="42"/>
+      <c r="F45" s="42"/>
+      <c r="G45" s="42"/>
       <c r="M45" s="8" t="s">
         <v>11</v>
       </c>
@@ -4402,12 +4405,18 @@
       <c r="Z45" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="AA45" s="13"/>
+      <c r="AA45" s="13">
+        <v>2</v>
+      </c>
       <c r="AB45" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="AC45" s="13"/>
-      <c r="AD45" s="16"/>
+      <c r="AC45" s="13">
+        <v>4</v>
+      </c>
+      <c r="AD45" s="16" t="s">
+        <v>101</v>
+      </c>
       <c r="AI45" s="8" t="s">
         <v>11</v>
       </c>
@@ -4432,15 +4441,15 @@
       <c r="AP45" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AU45" s="49" t="s">
+      <c r="AU45" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AV45" s="49"/>
-      <c r="AW45" s="49"/>
-      <c r="AX45" s="49"/>
-      <c r="AY45" s="49"/>
-      <c r="AZ45" s="49"/>
-      <c r="BA45" s="49"/>
+      <c r="AV45" s="42"/>
+      <c r="AW45" s="42"/>
+      <c r="AX45" s="42"/>
+      <c r="AY45" s="42"/>
+      <c r="AZ45" s="42"/>
+      <c r="BA45" s="42"/>
     </row>
     <row r="46" spans="1:54" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="M46" s="8" t="s">
@@ -4543,49 +4552,61 @@
       <c r="AO47" s="6"/>
     </row>
     <row r="48" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="M48" s="42" t="s">
+      <c r="M48" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="N48" s="43"/>
-      <c r="O48" s="43"/>
-      <c r="P48" s="43"/>
-      <c r="Q48" s="43"/>
-      <c r="R48" s="43"/>
-      <c r="S48" s="44"/>
-      <c r="X48" s="49" t="s">
+      <c r="N48" s="54"/>
+      <c r="O48" s="54"/>
+      <c r="P48" s="54"/>
+      <c r="Q48" s="54"/>
+      <c r="R48" s="54"/>
+      <c r="S48" s="55"/>
+      <c r="X48" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="Y48" s="49"/>
-      <c r="Z48" s="49"/>
-      <c r="AA48" s="49"/>
-      <c r="AB48" s="49"/>
-      <c r="AC48" s="49"/>
-      <c r="AD48" s="49"/>
-      <c r="AI48" s="49" t="s">
+      <c r="Y48" s="42"/>
+      <c r="Z48" s="42"/>
+      <c r="AA48" s="42"/>
+      <c r="AB48" s="42"/>
+      <c r="AC48" s="42"/>
+      <c r="AD48" s="42"/>
+      <c r="AI48" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AJ48" s="49"/>
-      <c r="AK48" s="49"/>
-      <c r="AL48" s="49"/>
-      <c r="AM48" s="49"/>
-      <c r="AN48" s="49"/>
-      <c r="AO48" s="49"/>
+      <c r="AJ48" s="42"/>
+      <c r="AK48" s="42"/>
+      <c r="AL48" s="42"/>
+      <c r="AM48" s="42"/>
+      <c r="AN48" s="42"/>
+      <c r="AO48" s="42"/>
     </row>
     <row r="49" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="AU45:BA45"/>
-    <mergeCell ref="AF28:AL28"/>
-    <mergeCell ref="AF37:AL37"/>
-    <mergeCell ref="AQ30:AS30"/>
-    <mergeCell ref="AQ41:AS41"/>
-    <mergeCell ref="AU34:BA34"/>
-    <mergeCell ref="AU36:BA36"/>
-    <mergeCell ref="AU2:BA2"/>
-    <mergeCell ref="AU3:BA3"/>
-    <mergeCell ref="AU12:BA12"/>
-    <mergeCell ref="AU14:BA14"/>
-    <mergeCell ref="AU23:BA23"/>
+    <mergeCell ref="M48:S48"/>
+    <mergeCell ref="M39:S39"/>
+    <mergeCell ref="P37:V37"/>
+    <mergeCell ref="P28:V28"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A1:U1"/>
+    <mergeCell ref="O26:W26"/>
+    <mergeCell ref="I41:K41"/>
+    <mergeCell ref="L14:N14"/>
+    <mergeCell ref="L36:N36"/>
+    <mergeCell ref="M2:R2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="M4:S4"/>
+    <mergeCell ref="M13:S13"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="A25:G25"/>
     <mergeCell ref="X37:AD37"/>
     <mergeCell ref="AE26:AM26"/>
     <mergeCell ref="Z1:AB1"/>
@@ -4602,30 +4623,18 @@
     <mergeCell ref="AN36:AP36"/>
     <mergeCell ref="AQ8:AS8"/>
     <mergeCell ref="AQ19:AS19"/>
-    <mergeCell ref="A1:U1"/>
-    <mergeCell ref="O26:W26"/>
-    <mergeCell ref="I41:K41"/>
-    <mergeCell ref="L14:N14"/>
-    <mergeCell ref="L36:N36"/>
-    <mergeCell ref="M2:R2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="M4:S4"/>
-    <mergeCell ref="M13:S13"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A23:G23"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="M48:S48"/>
-    <mergeCell ref="M39:S39"/>
-    <mergeCell ref="P37:V37"/>
-    <mergeCell ref="P28:V28"/>
-    <mergeCell ref="A36:G36"/>
-    <mergeCell ref="A45:G45"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="AU2:BA2"/>
+    <mergeCell ref="AU3:BA3"/>
+    <mergeCell ref="AU12:BA12"/>
+    <mergeCell ref="AU14:BA14"/>
+    <mergeCell ref="AU23:BA23"/>
+    <mergeCell ref="AU45:BA45"/>
+    <mergeCell ref="AF28:AL28"/>
+    <mergeCell ref="AF37:AL37"/>
+    <mergeCell ref="AQ30:AS30"/>
+    <mergeCell ref="AQ41:AS41"/>
+    <mergeCell ref="AU34:BA34"/>
+    <mergeCell ref="AU36:BA36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/2025_2026/Playoffs/Brackets.xlsx
+++ b/2025_2026/Playoffs/Brackets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\NHLStats\2025_2026\Playoffs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77B5898A-4CE2-41C3-890C-E62D88AE4777}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0551219-B553-415A-9AEF-B3B326C132D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="1590" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="103">
   <si>
     <t>Eastern Conference Playoff Teams</t>
   </si>
@@ -332,6 +332,9 @@
   </si>
   <si>
     <t>Hurricanes Lead 3-2</t>
+  </si>
+  <si>
+    <t>Hurricanes Win Series 4-2</t>
   </si>
 </sst>
 </file>
@@ -710,18 +713,45 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -734,40 +764,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1137,18 +1140,18 @@
     </row>
     <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="11" spans="1:7" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="59" t="s">
+      <c r="A11" s="61" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="59"/>
-      <c r="C11" s="59" t="s">
+      <c r="B11" s="61"/>
+      <c r="C11" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="59"/>
-      <c r="E11" s="59" t="s">
+      <c r="D11" s="61"/>
+      <c r="E11" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="59"/>
+      <c r="F11" s="61"/>
       <c r="G11" s="4" t="s">
         <v>18</v>
       </c>
@@ -1177,18 +1180,18 @@
       </c>
     </row>
     <row r="13" spans="1:7" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="60" t="s">
+      <c r="A13" s="59" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="61"/>
-      <c r="C13" s="60" t="s">
+      <c r="B13" s="60"/>
+      <c r="C13" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="D13" s="61"/>
-      <c r="E13" s="60" t="s">
+      <c r="D13" s="60"/>
+      <c r="E13" s="59" t="s">
         <v>17</v>
       </c>
-      <c r="F13" s="61"/>
+      <c r="F13" s="60"/>
       <c r="G13" s="5" t="s">
         <v>26</v>
       </c>
@@ -1237,14 +1240,14 @@
       </c>
     </row>
     <row r="16" spans="1:7" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="60" t="s">
+      <c r="A16" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="61"/>
-      <c r="C16" s="60" t="s">
+      <c r="B16" s="60"/>
+      <c r="C16" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="61"/>
+      <c r="D16" s="60"/>
     </row>
     <row r="17" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
@@ -1275,10 +1278,10 @@
       </c>
     </row>
     <row r="19" spans="1:4" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="60" t="s">
+      <c r="A19" s="59" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="61"/>
+      <c r="B19" s="60"/>
     </row>
     <row r="20" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
@@ -1297,10 +1300,10 @@
       </c>
     </row>
     <row r="22" spans="1:4" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="60" t="s">
+      <c r="A22" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="61"/>
+      <c r="B22" s="60"/>
     </row>
     <row r="23" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
@@ -1385,16 +1388,16 @@
     <sortCondition ref="B2:B9"/>
   </sortState>
   <mergeCells count="10">
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A16:B16"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A16:B16"/>
   </mergeCells>
   <dataValidations count="16">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C14" xr:uid="{2C3D9587-ABAE-4E3F-8B22-396DF812BF02}">
@@ -1477,7 +1480,7 @@
     <col min="24" max="24" width="21.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="25" max="28" width="21.44140625" style="1" customWidth="1"/>
     <col min="29" max="29" width="9.109375" style="1"/>
-    <col min="30" max="30" width="22.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="25.6640625" style="1" customWidth="1"/>
     <col min="31" max="32" width="9.109375" style="1"/>
     <col min="33" max="33" width="23.6640625" style="1" customWidth="1"/>
     <col min="34" max="34" width="22.88671875" style="1" customWidth="1"/>
@@ -1498,124 +1501,124 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:54" ht="27" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
-      <c r="I1" s="51"/>
-      <c r="J1" s="51"/>
-      <c r="K1" s="51"/>
-      <c r="L1" s="51"/>
-      <c r="M1" s="51"/>
-      <c r="N1" s="51"/>
-      <c r="O1" s="51"/>
-      <c r="P1" s="51"/>
-      <c r="Q1" s="51"/>
-      <c r="R1" s="51"/>
-      <c r="S1" s="51"/>
-      <c r="T1" s="51"/>
-      <c r="U1" s="52"/>
-      <c r="Z1" s="50" t="s">
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="52"/>
+      <c r="M1" s="52"/>
+      <c r="N1" s="52"/>
+      <c r="O1" s="52"/>
+      <c r="P1" s="52"/>
+      <c r="Q1" s="52"/>
+      <c r="R1" s="52"/>
+      <c r="S1" s="52"/>
+      <c r="T1" s="52"/>
+      <c r="U1" s="53"/>
+      <c r="Z1" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="AA1" s="51"/>
-      <c r="AB1" s="52"/>
-      <c r="AF1" s="50" t="s">
+      <c r="AA1" s="52"/>
+      <c r="AB1" s="53"/>
+      <c r="AF1" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="AG1" s="51"/>
-      <c r="AH1" s="51"/>
-      <c r="AI1" s="51"/>
-      <c r="AJ1" s="51"/>
-      <c r="AK1" s="51"/>
-      <c r="AL1" s="51"/>
-      <c r="AM1" s="51"/>
-      <c r="AN1" s="51"/>
-      <c r="AO1" s="51"/>
-      <c r="AP1" s="51"/>
-      <c r="AQ1" s="51"/>
-      <c r="AR1" s="51"/>
-      <c r="AS1" s="51"/>
-      <c r="AT1" s="51"/>
-      <c r="AU1" s="51"/>
-      <c r="AV1" s="51"/>
-      <c r="AW1" s="51"/>
-      <c r="AX1" s="51"/>
-      <c r="AY1" s="51"/>
-      <c r="AZ1" s="51"/>
-      <c r="BA1" s="52"/>
+      <c r="AG1" s="52"/>
+      <c r="AH1" s="52"/>
+      <c r="AI1" s="52"/>
+      <c r="AJ1" s="52"/>
+      <c r="AK1" s="52"/>
+      <c r="AL1" s="52"/>
+      <c r="AM1" s="52"/>
+      <c r="AN1" s="52"/>
+      <c r="AO1" s="52"/>
+      <c r="AP1" s="52"/>
+      <c r="AQ1" s="52"/>
+      <c r="AR1" s="52"/>
+      <c r="AS1" s="52"/>
+      <c r="AT1" s="52"/>
+      <c r="AU1" s="52"/>
+      <c r="AV1" s="52"/>
+      <c r="AW1" s="52"/>
+      <c r="AX1" s="52"/>
+      <c r="AY1" s="52"/>
+      <c r="AZ1" s="52"/>
+      <c r="BA1" s="53"/>
     </row>
     <row r="2" spans="1:54" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="48"/>
-      <c r="M2" s="46" t="s">
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="57"/>
+      <c r="M2" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="47"/>
-      <c r="O2" s="47"/>
-      <c r="P2" s="47"/>
-      <c r="Q2" s="47"/>
-      <c r="R2" s="48"/>
-      <c r="AI2" s="46" t="s">
+      <c r="N2" s="56"/>
+      <c r="O2" s="56"/>
+      <c r="P2" s="56"/>
+      <c r="Q2" s="56"/>
+      <c r="R2" s="57"/>
+      <c r="AI2" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="AJ2" s="47"/>
-      <c r="AK2" s="47"/>
-      <c r="AL2" s="47"/>
-      <c r="AM2" s="47"/>
-      <c r="AN2" s="47"/>
-      <c r="AO2" s="48"/>
-      <c r="AU2" s="46" t="s">
+      <c r="AJ2" s="56"/>
+      <c r="AK2" s="56"/>
+      <c r="AL2" s="56"/>
+      <c r="AM2" s="56"/>
+      <c r="AN2" s="56"/>
+      <c r="AO2" s="57"/>
+      <c r="AU2" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="AV2" s="47"/>
-      <c r="AW2" s="47"/>
-      <c r="AX2" s="47"/>
-      <c r="AY2" s="47"/>
-      <c r="AZ2" s="47"/>
-      <c r="BA2" s="48"/>
+      <c r="AV2" s="56"/>
+      <c r="AW2" s="56"/>
+      <c r="AX2" s="56"/>
+      <c r="AY2" s="56"/>
+      <c r="AZ2" s="56"/>
+      <c r="BA2" s="57"/>
     </row>
     <row r="3" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="42" t="s">
+      <c r="A3" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="42"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="42"/>
-      <c r="AI3" s="53" t="s">
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="AI3" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="AJ3" s="54"/>
-      <c r="AK3" s="54"/>
-      <c r="AL3" s="54"/>
-      <c r="AM3" s="54"/>
-      <c r="AN3" s="54"/>
-      <c r="AO3" s="55"/>
-      <c r="AU3" s="42" t="s">
+      <c r="AJ3" s="43"/>
+      <c r="AK3" s="43"/>
+      <c r="AL3" s="43"/>
+      <c r="AM3" s="43"/>
+      <c r="AN3" s="43"/>
+      <c r="AO3" s="44"/>
+      <c r="AU3" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="AV3" s="42"/>
-      <c r="AW3" s="42"/>
-      <c r="AX3" s="42"/>
-      <c r="AY3" s="42"/>
-      <c r="AZ3" s="42"/>
-      <c r="BA3" s="42"/>
+      <c r="AV3" s="49"/>
+      <c r="AW3" s="49"/>
+      <c r="AX3" s="49"/>
+      <c r="AY3" s="49"/>
+      <c r="AZ3" s="49"/>
+      <c r="BA3" s="49"/>
     </row>
     <row r="4" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
@@ -1639,15 +1642,15 @@
       <c r="G4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="53" t="s">
+      <c r="M4" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="N4" s="54"/>
-      <c r="O4" s="54"/>
-      <c r="P4" s="54"/>
-      <c r="Q4" s="54"/>
-      <c r="R4" s="54"/>
-      <c r="S4" s="55"/>
+      <c r="N4" s="43"/>
+      <c r="O4" s="43"/>
+      <c r="P4" s="43"/>
+      <c r="Q4" s="43"/>
+      <c r="R4" s="43"/>
+      <c r="S4" s="44"/>
       <c r="AI4" s="3" t="s">
         <v>2</v>
       </c>
@@ -1974,11 +1977,11 @@
       <c r="G8" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="I8" s="43" t="s">
+      <c r="I8" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="J8" s="43"/>
-      <c r="K8" s="43"/>
+      <c r="J8" s="50"/>
+      <c r="K8" s="50"/>
       <c r="M8" s="8">
         <v>3</v>
       </c>
@@ -2021,11 +2024,11 @@
       <c r="AO8" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="AQ8" s="43" t="s">
+      <c r="AQ8" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="AR8" s="43"/>
-      <c r="AS8" s="43"/>
+      <c r="AR8" s="50"/>
+      <c r="AS8" s="50"/>
       <c r="AU8" s="38">
         <v>4</v>
       </c>
@@ -2285,15 +2288,15 @@
       <c r="BA11" s="6"/>
     </row>
     <row r="12" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="42" t="s">
+      <c r="A12" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="42"/>
-      <c r="C12" s="42"/>
-      <c r="D12" s="42"/>
-      <c r="E12" s="42"/>
-      <c r="F12" s="42"/>
-      <c r="G12" s="42"/>
+      <c r="B12" s="49"/>
+      <c r="C12" s="49"/>
+      <c r="D12" s="49"/>
+      <c r="E12" s="49"/>
+      <c r="F12" s="49"/>
+      <c r="G12" s="49"/>
       <c r="L12" s="12"/>
       <c r="M12" s="8" t="s">
         <v>12</v>
@@ -2319,69 +2322,69 @@
       <c r="T12" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AI12" s="42" t="s">
+      <c r="AI12" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AJ12" s="42"/>
-      <c r="AK12" s="42"/>
-      <c r="AL12" s="42"/>
-      <c r="AM12" s="42"/>
-      <c r="AN12" s="42"/>
-      <c r="AO12" s="42"/>
+      <c r="AJ12" s="49"/>
+      <c r="AK12" s="49"/>
+      <c r="AL12" s="49"/>
+      <c r="AM12" s="49"/>
+      <c r="AN12" s="49"/>
+      <c r="AO12" s="49"/>
       <c r="AQ12" s="12"/>
-      <c r="AU12" s="42" t="s">
+      <c r="AU12" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AV12" s="42"/>
-      <c r="AW12" s="42"/>
-      <c r="AX12" s="42"/>
-      <c r="AY12" s="42"/>
-      <c r="AZ12" s="42"/>
-      <c r="BA12" s="42"/>
+      <c r="AV12" s="49"/>
+      <c r="AW12" s="49"/>
+      <c r="AX12" s="49"/>
+      <c r="AY12" s="49"/>
+      <c r="AZ12" s="49"/>
+      <c r="BA12" s="49"/>
     </row>
     <row r="13" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="L13" s="12"/>
-      <c r="M13" s="53" t="s">
+      <c r="M13" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="N13" s="54"/>
-      <c r="O13" s="54"/>
-      <c r="P13" s="54"/>
-      <c r="Q13" s="54"/>
-      <c r="R13" s="54"/>
-      <c r="S13" s="55"/>
+      <c r="N13" s="43"/>
+      <c r="O13" s="43"/>
+      <c r="P13" s="43"/>
+      <c r="Q13" s="43"/>
+      <c r="R13" s="43"/>
+      <c r="S13" s="44"/>
       <c r="AQ13" s="12"/>
     </row>
     <row r="14" spans="1:54" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="45" t="s">
+      <c r="A14" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="45"/>
-      <c r="C14" s="45"/>
-      <c r="D14" s="45"/>
-      <c r="E14" s="45"/>
-      <c r="F14" s="45"/>
-      <c r="G14" s="45"/>
-      <c r="L14" s="44" t="s">
+      <c r="B14" s="48"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="48"/>
+      <c r="E14" s="48"/>
+      <c r="F14" s="48"/>
+      <c r="G14" s="48"/>
+      <c r="L14" s="54" t="s">
         <v>32</v>
       </c>
-      <c r="M14" s="43"/>
-      <c r="N14" s="43"/>
-      <c r="AN14" s="43" t="s">
+      <c r="M14" s="50"/>
+      <c r="N14" s="50"/>
+      <c r="AN14" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="AO14" s="43"/>
-      <c r="AP14" s="43"/>
+      <c r="AO14" s="50"/>
+      <c r="AP14" s="50"/>
       <c r="AQ14" s="12"/>
-      <c r="AU14" s="45" t="s">
+      <c r="AU14" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="AV14" s="45"/>
-      <c r="AW14" s="45"/>
-      <c r="AX14" s="45"/>
-      <c r="AY14" s="45"/>
-      <c r="AZ14" s="45"/>
-      <c r="BA14" s="45"/>
+      <c r="AV14" s="48"/>
+      <c r="AW14" s="48"/>
+      <c r="AX14" s="48"/>
+      <c r="AY14" s="48"/>
+      <c r="AZ14" s="48"/>
+      <c r="BA14" s="48"/>
     </row>
     <row r="15" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
@@ -2609,19 +2612,19 @@
       <c r="G19" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="I19" s="43" t="s">
+      <c r="I19" s="50" t="s">
         <v>32</v>
       </c>
-      <c r="J19" s="43"/>
-      <c r="K19" s="43"/>
+      <c r="J19" s="50"/>
+      <c r="K19" s="50"/>
       <c r="L19" s="12"/>
       <c r="O19" s="12"/>
       <c r="AN19" s="12"/>
-      <c r="AQ19" s="44" t="s">
+      <c r="AQ19" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="AR19" s="43"/>
-      <c r="AS19" s="43"/>
+      <c r="AR19" s="50"/>
+      <c r="AS19" s="50"/>
       <c r="AU19" s="38">
         <v>4</v>
       </c>
@@ -2783,52 +2786,52 @@
       <c r="BA22" s="6"/>
     </row>
     <row r="23" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="42" t="s">
+      <c r="A23" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="B23" s="42"/>
-      <c r="C23" s="42"/>
-      <c r="D23" s="42"/>
-      <c r="E23" s="42"/>
-      <c r="F23" s="42"/>
-      <c r="G23" s="42"/>
+      <c r="B23" s="49"/>
+      <c r="C23" s="49"/>
+      <c r="D23" s="49"/>
+      <c r="E23" s="49"/>
+      <c r="F23" s="49"/>
+      <c r="G23" s="49"/>
       <c r="O23" s="12"/>
       <c r="AN23" s="12"/>
-      <c r="AU23" s="42" t="s">
+      <c r="AU23" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AV23" s="42"/>
-      <c r="AW23" s="42"/>
-      <c r="AX23" s="42"/>
-      <c r="AY23" s="42"/>
-      <c r="AZ23" s="42"/>
-      <c r="BA23" s="42"/>
+      <c r="AV23" s="49"/>
+      <c r="AW23" s="49"/>
+      <c r="AX23" s="49"/>
+      <c r="AY23" s="49"/>
+      <c r="AZ23" s="49"/>
+      <c r="BA23" s="49"/>
     </row>
     <row r="24" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="O24" s="12"/>
       <c r="AN24" s="12"/>
     </row>
     <row r="25" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="42" t="s">
+      <c r="A25" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="42"/>
-      <c r="C25" s="42"/>
-      <c r="D25" s="42"/>
-      <c r="E25" s="42"/>
-      <c r="F25" s="42"/>
-      <c r="G25" s="42"/>
+      <c r="B25" s="49"/>
+      <c r="C25" s="49"/>
+      <c r="D25" s="49"/>
+      <c r="E25" s="49"/>
+      <c r="F25" s="49"/>
+      <c r="G25" s="49"/>
       <c r="O25" s="12"/>
       <c r="AN25" s="12"/>
-      <c r="AU25" s="42" t="s">
+      <c r="AU25" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="AV25" s="42"/>
-      <c r="AW25" s="42"/>
-      <c r="AX25" s="42"/>
-      <c r="AY25" s="42"/>
-      <c r="AZ25" s="42"/>
-      <c r="BA25" s="42"/>
+      <c r="AV25" s="49"/>
+      <c r="AW25" s="49"/>
+      <c r="AX25" s="49"/>
+      <c r="AY25" s="49"/>
+      <c r="AZ25" s="49"/>
+      <c r="BA25" s="49"/>
     </row>
     <row r="26" spans="1:54" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A26" s="20" t="s">
@@ -2852,28 +2855,28 @@
       <c r="G26" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="O26" s="44" t="s">
+      <c r="O26" s="54" t="s">
         <v>26</v>
       </c>
-      <c r="P26" s="43"/>
-      <c r="Q26" s="43"/>
-      <c r="R26" s="43"/>
-      <c r="S26" s="43"/>
-      <c r="T26" s="43"/>
-      <c r="U26" s="43"/>
-      <c r="V26" s="43"/>
-      <c r="W26" s="43"/>
-      <c r="AE26" s="43" t="s">
+      <c r="P26" s="50"/>
+      <c r="Q26" s="50"/>
+      <c r="R26" s="50"/>
+      <c r="S26" s="50"/>
+      <c r="T26" s="50"/>
+      <c r="U26" s="50"/>
+      <c r="V26" s="50"/>
+      <c r="W26" s="50"/>
+      <c r="AE26" s="50" t="s">
         <v>38</v>
       </c>
-      <c r="AF26" s="43"/>
-      <c r="AG26" s="43"/>
-      <c r="AH26" s="43"/>
-      <c r="AI26" s="43"/>
-      <c r="AJ26" s="43"/>
-      <c r="AK26" s="43"/>
-      <c r="AL26" s="43"/>
-      <c r="AM26" s="49"/>
+      <c r="AF26" s="50"/>
+      <c r="AG26" s="50"/>
+      <c r="AH26" s="50"/>
+      <c r="AI26" s="50"/>
+      <c r="AJ26" s="50"/>
+      <c r="AK26" s="50"/>
+      <c r="AL26" s="50"/>
+      <c r="AM26" s="58"/>
       <c r="AU26" s="20" t="s">
         <v>2</v>
       </c>
@@ -2970,26 +2973,26 @@
         <v>54</v>
       </c>
       <c r="O28" s="12"/>
-      <c r="P28" s="53" t="s">
+      <c r="P28" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="Q28" s="54"/>
-      <c r="R28" s="54"/>
-      <c r="S28" s="54"/>
-      <c r="T28" s="54"/>
-      <c r="U28" s="54"/>
-      <c r="V28" s="55"/>
+      <c r="Q28" s="43"/>
+      <c r="R28" s="43"/>
+      <c r="S28" s="43"/>
+      <c r="T28" s="43"/>
+      <c r="U28" s="43"/>
+      <c r="V28" s="44"/>
       <c r="X28" s="12"/>
       <c r="AD28" s="13"/>
-      <c r="AF28" s="42" t="s">
+      <c r="AF28" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="AG28" s="42"/>
-      <c r="AH28" s="42"/>
-      <c r="AI28" s="42"/>
-      <c r="AJ28" s="42"/>
-      <c r="AK28" s="42"/>
-      <c r="AL28" s="42"/>
+      <c r="AG28" s="49"/>
+      <c r="AH28" s="49"/>
+      <c r="AI28" s="49"/>
+      <c r="AJ28" s="49"/>
+      <c r="AK28" s="49"/>
+      <c r="AL28" s="49"/>
       <c r="AN28" s="12"/>
       <c r="AU28" s="8">
         <v>2</v>
@@ -3125,11 +3128,11 @@
       <c r="G30" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="I30" s="43" t="s">
+      <c r="I30" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="J30" s="43"/>
-      <c r="K30" s="43"/>
+      <c r="J30" s="50"/>
+      <c r="K30" s="50"/>
       <c r="O30" s="12"/>
       <c r="P30" s="7">
         <v>1</v>
@@ -3176,11 +3179,11 @@
         <v>52</v>
       </c>
       <c r="AN30" s="12"/>
-      <c r="AQ30" s="43" t="s">
+      <c r="AQ30" s="50" t="s">
         <v>38</v>
       </c>
-      <c r="AR30" s="43"/>
-      <c r="AS30" s="43"/>
+      <c r="AR30" s="50"/>
+      <c r="AS30" s="50"/>
       <c r="AU30" s="38">
         <v>4</v>
       </c>
@@ -3467,15 +3470,15 @@
       <c r="BA33" s="6"/>
     </row>
     <row r="34" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="42" t="s">
+      <c r="A34" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="B34" s="42"/>
-      <c r="C34" s="42"/>
-      <c r="D34" s="42"/>
-      <c r="E34" s="42"/>
-      <c r="F34" s="42"/>
-      <c r="G34" s="42"/>
+      <c r="B34" s="49"/>
+      <c r="C34" s="49"/>
+      <c r="D34" s="49"/>
+      <c r="E34" s="49"/>
+      <c r="F34" s="49"/>
+      <c r="G34" s="49"/>
       <c r="L34" s="12"/>
       <c r="O34" s="12"/>
       <c r="P34" s="8" t="s">
@@ -3518,15 +3521,15 @@
       <c r="AL34" s="16"/>
       <c r="AN34" s="12"/>
       <c r="AQ34" s="12"/>
-      <c r="AU34" s="42" t="s">
+      <c r="AU34" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AV34" s="42"/>
-      <c r="AW34" s="42"/>
-      <c r="AX34" s="42"/>
-      <c r="AY34" s="42"/>
-      <c r="AZ34" s="42"/>
-      <c r="BA34" s="42"/>
+      <c r="AV34" s="49"/>
+      <c r="AW34" s="49"/>
+      <c r="AX34" s="49"/>
+      <c r="AY34" s="49"/>
+      <c r="AZ34" s="49"/>
+      <c r="BA34" s="49"/>
     </row>
     <row r="35" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="L35" s="12"/>
@@ -3567,20 +3570,20 @@
       <c r="AQ35" s="12"/>
     </row>
     <row r="36" spans="1:54" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="45" t="s">
+      <c r="A36" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="B36" s="45"/>
-      <c r="C36" s="45"/>
-      <c r="D36" s="45"/>
-      <c r="E36" s="45"/>
-      <c r="F36" s="45"/>
-      <c r="G36" s="45"/>
-      <c r="L36" s="44" t="s">
+      <c r="B36" s="48"/>
+      <c r="C36" s="48"/>
+      <c r="D36" s="48"/>
+      <c r="E36" s="48"/>
+      <c r="F36" s="48"/>
+      <c r="G36" s="48"/>
+      <c r="L36" s="54" t="s">
         <v>26</v>
       </c>
-      <c r="M36" s="43"/>
-      <c r="N36" s="43"/>
+      <c r="M36" s="50"/>
+      <c r="N36" s="50"/>
       <c r="O36" s="12"/>
       <c r="P36" s="8" t="s">
         <v>12</v>
@@ -3614,21 +3617,21 @@
       </c>
       <c r="AK36" s="36"/>
       <c r="AL36" s="37"/>
-      <c r="AN36" s="44" t="s">
+      <c r="AN36" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="AO36" s="43"/>
-      <c r="AP36" s="43"/>
+      <c r="AO36" s="50"/>
+      <c r="AP36" s="50"/>
       <c r="AQ36" s="12"/>
-      <c r="AU36" s="45" t="s">
+      <c r="AU36" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="AV36" s="45"/>
-      <c r="AW36" s="45"/>
-      <c r="AX36" s="45"/>
-      <c r="AY36" s="45"/>
-      <c r="AZ36" s="45"/>
-      <c r="BA36" s="45"/>
+      <c r="AV36" s="48"/>
+      <c r="AW36" s="48"/>
+      <c r="AX36" s="48"/>
+      <c r="AY36" s="48"/>
+      <c r="AZ36" s="48"/>
+      <c r="BA36" s="48"/>
     </row>
     <row r="37" spans="1:54" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A37" s="20" t="s">
@@ -3653,31 +3656,31 @@
         <v>9</v>
       </c>
       <c r="L37" s="12"/>
-      <c r="P37" s="56" t="s">
+      <c r="P37" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="Q37" s="57"/>
-      <c r="R37" s="57"/>
-      <c r="S37" s="57"/>
-      <c r="T37" s="57"/>
-      <c r="U37" s="57"/>
-      <c r="V37" s="58"/>
-      <c r="X37" s="44"/>
-      <c r="Y37" s="43"/>
-      <c r="Z37" s="43"/>
-      <c r="AA37" s="43"/>
-      <c r="AB37" s="43"/>
-      <c r="AC37" s="43"/>
-      <c r="AD37" s="49"/>
-      <c r="AF37" s="42" t="s">
+      <c r="Q37" s="46"/>
+      <c r="R37" s="46"/>
+      <c r="S37" s="46"/>
+      <c r="T37" s="46"/>
+      <c r="U37" s="46"/>
+      <c r="V37" s="47"/>
+      <c r="X37" s="54"/>
+      <c r="Y37" s="50"/>
+      <c r="Z37" s="50"/>
+      <c r="AA37" s="50"/>
+      <c r="AB37" s="50"/>
+      <c r="AC37" s="50"/>
+      <c r="AD37" s="58"/>
+      <c r="AF37" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AG37" s="42"/>
-      <c r="AH37" s="42"/>
-      <c r="AI37" s="42"/>
-      <c r="AJ37" s="42"/>
-      <c r="AK37" s="42"/>
-      <c r="AL37" s="42"/>
+      <c r="AG37" s="49"/>
+      <c r="AH37" s="49"/>
+      <c r="AI37" s="49"/>
+      <c r="AJ37" s="49"/>
+      <c r="AK37" s="49"/>
+      <c r="AL37" s="49"/>
       <c r="AQ37" s="12"/>
       <c r="AU37" s="3" t="s">
         <v>2</v>
@@ -3770,33 +3773,33 @@
         <v>53</v>
       </c>
       <c r="L39" s="12"/>
-      <c r="M39" s="53" t="s">
+      <c r="M39" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="N39" s="54"/>
-      <c r="O39" s="54"/>
-      <c r="P39" s="54"/>
-      <c r="Q39" s="54"/>
-      <c r="R39" s="54"/>
-      <c r="S39" s="55"/>
-      <c r="X39" s="42" t="s">
+      <c r="N39" s="43"/>
+      <c r="O39" s="43"/>
+      <c r="P39" s="43"/>
+      <c r="Q39" s="43"/>
+      <c r="R39" s="43"/>
+      <c r="S39" s="44"/>
+      <c r="X39" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="Y39" s="42"/>
-      <c r="Z39" s="42"/>
-      <c r="AA39" s="42"/>
-      <c r="AB39" s="42"/>
-      <c r="AC39" s="42"/>
-      <c r="AD39" s="42"/>
-      <c r="AI39" s="53" t="s">
+      <c r="Y39" s="49"/>
+      <c r="Z39" s="49"/>
+      <c r="AA39" s="49"/>
+      <c r="AB39" s="49"/>
+      <c r="AC39" s="49"/>
+      <c r="AD39" s="49"/>
+      <c r="AI39" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="AJ39" s="54"/>
-      <c r="AK39" s="54"/>
-      <c r="AL39" s="54"/>
-      <c r="AM39" s="54"/>
-      <c r="AN39" s="54"/>
-      <c r="AO39" s="55"/>
+      <c r="AJ39" s="43"/>
+      <c r="AK39" s="43"/>
+      <c r="AL39" s="43"/>
+      <c r="AM39" s="43"/>
+      <c r="AN39" s="43"/>
+      <c r="AO39" s="44"/>
       <c r="AQ39" s="12"/>
       <c r="AU39" s="8">
         <v>2</v>
@@ -3951,11 +3954,11 @@
       <c r="G41" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="I41" s="43" t="s">
+      <c r="I41" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="J41" s="43"/>
-      <c r="K41" s="43"/>
+      <c r="J41" s="50"/>
+      <c r="K41" s="50"/>
       <c r="L41" s="12"/>
       <c r="M41" s="7">
         <v>1</v>
@@ -4020,11 +4023,11 @@
       <c r="AO41" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="AQ41" s="44" t="s">
+      <c r="AQ41" s="54" t="s">
         <v>23</v>
       </c>
-      <c r="AR41" s="43"/>
-      <c r="AS41" s="43"/>
+      <c r="AR41" s="50"/>
+      <c r="AS41" s="50"/>
       <c r="AU41" s="38">
         <v>4</v>
       </c>
@@ -4372,15 +4375,15 @@
       <c r="BA44" s="6"/>
     </row>
     <row r="45" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="42" t="s">
+      <c r="A45" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="B45" s="42"/>
-      <c r="C45" s="42"/>
-      <c r="D45" s="42"/>
-      <c r="E45" s="42"/>
-      <c r="F45" s="42"/>
-      <c r="G45" s="42"/>
+      <c r="B45" s="49"/>
+      <c r="C45" s="49"/>
+      <c r="D45" s="49"/>
+      <c r="E45" s="49"/>
+      <c r="F45" s="49"/>
+      <c r="G45" s="49"/>
       <c r="M45" s="8" t="s">
         <v>11</v>
       </c>
@@ -4441,15 +4444,15 @@
       <c r="AP45" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AU45" s="42" t="s">
+      <c r="AU45" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AV45" s="42"/>
-      <c r="AW45" s="42"/>
-      <c r="AX45" s="42"/>
-      <c r="AY45" s="42"/>
-      <c r="AZ45" s="42"/>
-      <c r="BA45" s="42"/>
+      <c r="AV45" s="49"/>
+      <c r="AW45" s="49"/>
+      <c r="AX45" s="49"/>
+      <c r="AY45" s="49"/>
+      <c r="AZ45" s="49"/>
+      <c r="BA45" s="49"/>
     </row>
     <row r="46" spans="1:54" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="M46" s="8" t="s">
@@ -4476,12 +4479,18 @@
       <c r="Z46" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="AA46" s="13"/>
+      <c r="AA46" s="13">
+        <v>3</v>
+      </c>
       <c r="AB46" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="AC46" s="13"/>
-      <c r="AD46" s="16"/>
+      <c r="AC46" s="13">
+        <v>1</v>
+      </c>
+      <c r="AD46" s="16" t="s">
+        <v>102</v>
+      </c>
       <c r="AI46" s="8" t="s">
         <v>10</v>
       </c>
@@ -4552,45 +4561,65 @@
       <c r="AO47" s="6"/>
     </row>
     <row r="48" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="M48" s="53" t="s">
+      <c r="M48" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="N48" s="54"/>
-      <c r="O48" s="54"/>
-      <c r="P48" s="54"/>
-      <c r="Q48" s="54"/>
-      <c r="R48" s="54"/>
-      <c r="S48" s="55"/>
-      <c r="X48" s="42" t="s">
+      <c r="N48" s="43"/>
+      <c r="O48" s="43"/>
+      <c r="P48" s="43"/>
+      <c r="Q48" s="43"/>
+      <c r="R48" s="43"/>
+      <c r="S48" s="44"/>
+      <c r="X48" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="Y48" s="42"/>
-      <c r="Z48" s="42"/>
-      <c r="AA48" s="42"/>
-      <c r="AB48" s="42"/>
-      <c r="AC48" s="42"/>
-      <c r="AD48" s="42"/>
-      <c r="AI48" s="42" t="s">
+      <c r="Y48" s="49"/>
+      <c r="Z48" s="49"/>
+      <c r="AA48" s="49"/>
+      <c r="AB48" s="49"/>
+      <c r="AC48" s="49"/>
+      <c r="AD48" s="49"/>
+      <c r="AI48" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AJ48" s="42"/>
-      <c r="AK48" s="42"/>
-      <c r="AL48" s="42"/>
-      <c r="AM48" s="42"/>
-      <c r="AN48" s="42"/>
-      <c r="AO48" s="42"/>
+      <c r="AJ48" s="49"/>
+      <c r="AK48" s="49"/>
+      <c r="AL48" s="49"/>
+      <c r="AM48" s="49"/>
+      <c r="AN48" s="49"/>
+      <c r="AO48" s="49"/>
     </row>
     <row r="49" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="M48:S48"/>
-    <mergeCell ref="M39:S39"/>
-    <mergeCell ref="P37:V37"/>
-    <mergeCell ref="P28:V28"/>
-    <mergeCell ref="A36:G36"/>
-    <mergeCell ref="A45:G45"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="AU45:BA45"/>
+    <mergeCell ref="AF28:AL28"/>
+    <mergeCell ref="AF37:AL37"/>
+    <mergeCell ref="AQ30:AS30"/>
+    <mergeCell ref="AQ41:AS41"/>
+    <mergeCell ref="AU34:BA34"/>
+    <mergeCell ref="AU36:BA36"/>
+    <mergeCell ref="AU2:BA2"/>
+    <mergeCell ref="AU3:BA3"/>
+    <mergeCell ref="AU12:BA12"/>
+    <mergeCell ref="AU14:BA14"/>
+    <mergeCell ref="AU23:BA23"/>
+    <mergeCell ref="X37:AD37"/>
+    <mergeCell ref="AE26:AM26"/>
+    <mergeCell ref="Z1:AB1"/>
+    <mergeCell ref="X39:AD39"/>
+    <mergeCell ref="X48:AD48"/>
+    <mergeCell ref="AF1:BA1"/>
+    <mergeCell ref="AI2:AO2"/>
+    <mergeCell ref="AI3:AO3"/>
+    <mergeCell ref="AI12:AO12"/>
+    <mergeCell ref="AI39:AO39"/>
+    <mergeCell ref="AU25:BA25"/>
+    <mergeCell ref="AI48:AO48"/>
+    <mergeCell ref="AN14:AP14"/>
+    <mergeCell ref="AN36:AP36"/>
+    <mergeCell ref="AQ8:AS8"/>
+    <mergeCell ref="AQ19:AS19"/>
     <mergeCell ref="A1:U1"/>
     <mergeCell ref="O26:W26"/>
     <mergeCell ref="I41:K41"/>
@@ -4607,34 +4636,14 @@
     <mergeCell ref="I8:K8"/>
     <mergeCell ref="I19:K19"/>
     <mergeCell ref="A25:G25"/>
-    <mergeCell ref="X37:AD37"/>
-    <mergeCell ref="AE26:AM26"/>
-    <mergeCell ref="Z1:AB1"/>
-    <mergeCell ref="X39:AD39"/>
-    <mergeCell ref="X48:AD48"/>
-    <mergeCell ref="AF1:BA1"/>
-    <mergeCell ref="AI2:AO2"/>
-    <mergeCell ref="AI3:AO3"/>
-    <mergeCell ref="AI12:AO12"/>
-    <mergeCell ref="AI39:AO39"/>
-    <mergeCell ref="AU25:BA25"/>
-    <mergeCell ref="AI48:AO48"/>
-    <mergeCell ref="AN14:AP14"/>
-    <mergeCell ref="AN36:AP36"/>
-    <mergeCell ref="AQ8:AS8"/>
-    <mergeCell ref="AQ19:AS19"/>
-    <mergeCell ref="AU2:BA2"/>
-    <mergeCell ref="AU3:BA3"/>
-    <mergeCell ref="AU12:BA12"/>
-    <mergeCell ref="AU14:BA14"/>
-    <mergeCell ref="AU23:BA23"/>
-    <mergeCell ref="AU45:BA45"/>
-    <mergeCell ref="AF28:AL28"/>
-    <mergeCell ref="AF37:AL37"/>
-    <mergeCell ref="AQ30:AS30"/>
-    <mergeCell ref="AQ41:AS41"/>
-    <mergeCell ref="AU34:BA34"/>
-    <mergeCell ref="AU36:BA36"/>
+    <mergeCell ref="M48:S48"/>
+    <mergeCell ref="M39:S39"/>
+    <mergeCell ref="P37:V37"/>
+    <mergeCell ref="P28:V28"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="A34:G34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/2025_2026/Playoffs/Brackets.xlsx
+++ b/2025_2026/Playoffs/Brackets.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\NHLStats\2025_2026\Playoffs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0551219-B553-415A-9AEF-B3B326C132D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D23EFBD6-56D2-47DB-9C02-691EA508C649}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="1590" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="103">
   <si>
     <t>Eastern Conference Playoff Teams</t>
   </si>
@@ -713,6 +713,39 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -731,46 +764,13 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1140,18 +1140,18 @@
     </row>
     <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="11" spans="1:7" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="61" t="s">
+      <c r="A11" s="59" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="61"/>
-      <c r="C11" s="61" t="s">
+      <c r="B11" s="59"/>
+      <c r="C11" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="61"/>
-      <c r="E11" s="61" t="s">
+      <c r="D11" s="59"/>
+      <c r="E11" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="61"/>
+      <c r="F11" s="59"/>
       <c r="G11" s="4" t="s">
         <v>18</v>
       </c>
@@ -1180,18 +1180,18 @@
       </c>
     </row>
     <row r="13" spans="1:7" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="59" t="s">
+      <c r="A13" s="60" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="60"/>
-      <c r="C13" s="59" t="s">
+      <c r="B13" s="61"/>
+      <c r="C13" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="D13" s="60"/>
-      <c r="E13" s="59" t="s">
+      <c r="D13" s="61"/>
+      <c r="E13" s="60" t="s">
         <v>17</v>
       </c>
-      <c r="F13" s="60"/>
+      <c r="F13" s="61"/>
       <c r="G13" s="5" t="s">
         <v>26</v>
       </c>
@@ -1240,14 +1240,14 @@
       </c>
     </row>
     <row r="16" spans="1:7" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="59" t="s">
+      <c r="A16" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="60"/>
-      <c r="C16" s="59" t="s">
+      <c r="B16" s="61"/>
+      <c r="C16" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="60"/>
+      <c r="D16" s="61"/>
     </row>
     <row r="17" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
@@ -1278,10 +1278,10 @@
       </c>
     </row>
     <row r="19" spans="1:4" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="59" t="s">
+      <c r="A19" s="60" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="60"/>
+      <c r="B19" s="61"/>
     </row>
     <row r="20" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
@@ -1300,10 +1300,10 @@
       </c>
     </row>
     <row r="22" spans="1:4" ht="16.8" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="59" t="s">
+      <c r="A22" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="60"/>
+      <c r="B22" s="61"/>
     </row>
     <row r="23" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
@@ -1388,16 +1388,16 @@
     <sortCondition ref="B2:B9"/>
   </sortState>
   <mergeCells count="10">
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C16:D16"/>
     <mergeCell ref="E11:F11"/>
     <mergeCell ref="E13:F13"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C16:D16"/>
   </mergeCells>
   <dataValidations count="16">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C14" xr:uid="{2C3D9587-ABAE-4E3F-8B22-396DF812BF02}">
@@ -1501,124 +1501,124 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:54" ht="27" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
-      <c r="M1" s="52"/>
-      <c r="N1" s="52"/>
-      <c r="O1" s="52"/>
-      <c r="P1" s="52"/>
-      <c r="Q1" s="52"/>
-      <c r="R1" s="52"/>
-      <c r="S1" s="52"/>
-      <c r="T1" s="52"/>
-      <c r="U1" s="53"/>
-      <c r="Z1" s="51" t="s">
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
+      <c r="K1" s="51"/>
+      <c r="L1" s="51"/>
+      <c r="M1" s="51"/>
+      <c r="N1" s="51"/>
+      <c r="O1" s="51"/>
+      <c r="P1" s="51"/>
+      <c r="Q1" s="51"/>
+      <c r="R1" s="51"/>
+      <c r="S1" s="51"/>
+      <c r="T1" s="51"/>
+      <c r="U1" s="52"/>
+      <c r="Z1" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="AA1" s="52"/>
-      <c r="AB1" s="53"/>
-      <c r="AF1" s="51" t="s">
+      <c r="AA1" s="51"/>
+      <c r="AB1" s="52"/>
+      <c r="AF1" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="AG1" s="52"/>
-      <c r="AH1" s="52"/>
-      <c r="AI1" s="52"/>
-      <c r="AJ1" s="52"/>
-      <c r="AK1" s="52"/>
-      <c r="AL1" s="52"/>
-      <c r="AM1" s="52"/>
-      <c r="AN1" s="52"/>
-      <c r="AO1" s="52"/>
-      <c r="AP1" s="52"/>
-      <c r="AQ1" s="52"/>
-      <c r="AR1" s="52"/>
-      <c r="AS1" s="52"/>
-      <c r="AT1" s="52"/>
-      <c r="AU1" s="52"/>
-      <c r="AV1" s="52"/>
-      <c r="AW1" s="52"/>
-      <c r="AX1" s="52"/>
-      <c r="AY1" s="52"/>
-      <c r="AZ1" s="52"/>
-      <c r="BA1" s="53"/>
+      <c r="AG1" s="51"/>
+      <c r="AH1" s="51"/>
+      <c r="AI1" s="51"/>
+      <c r="AJ1" s="51"/>
+      <c r="AK1" s="51"/>
+      <c r="AL1" s="51"/>
+      <c r="AM1" s="51"/>
+      <c r="AN1" s="51"/>
+      <c r="AO1" s="51"/>
+      <c r="AP1" s="51"/>
+      <c r="AQ1" s="51"/>
+      <c r="AR1" s="51"/>
+      <c r="AS1" s="51"/>
+      <c r="AT1" s="51"/>
+      <c r="AU1" s="51"/>
+      <c r="AV1" s="51"/>
+      <c r="AW1" s="51"/>
+      <c r="AX1" s="51"/>
+      <c r="AY1" s="51"/>
+      <c r="AZ1" s="51"/>
+      <c r="BA1" s="52"/>
     </row>
     <row r="2" spans="1:54" ht="19.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="55" t="s">
+      <c r="A2" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="57"/>
-      <c r="M2" s="55" t="s">
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="48"/>
+      <c r="M2" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="56"/>
-      <c r="O2" s="56"/>
-      <c r="P2" s="56"/>
-      <c r="Q2" s="56"/>
-      <c r="R2" s="57"/>
-      <c r="AI2" s="55" t="s">
+      <c r="N2" s="47"/>
+      <c r="O2" s="47"/>
+      <c r="P2" s="47"/>
+      <c r="Q2" s="47"/>
+      <c r="R2" s="48"/>
+      <c r="AI2" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="AJ2" s="56"/>
-      <c r="AK2" s="56"/>
-      <c r="AL2" s="56"/>
-      <c r="AM2" s="56"/>
-      <c r="AN2" s="56"/>
-      <c r="AO2" s="57"/>
-      <c r="AU2" s="55" t="s">
+      <c r="AJ2" s="47"/>
+      <c r="AK2" s="47"/>
+      <c r="AL2" s="47"/>
+      <c r="AM2" s="47"/>
+      <c r="AN2" s="47"/>
+      <c r="AO2" s="48"/>
+      <c r="AU2" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="AV2" s="56"/>
-      <c r="AW2" s="56"/>
-      <c r="AX2" s="56"/>
-      <c r="AY2" s="56"/>
-      <c r="AZ2" s="56"/>
-      <c r="BA2" s="57"/>
+      <c r="AV2" s="47"/>
+      <c r="AW2" s="47"/>
+      <c r="AX2" s="47"/>
+      <c r="AY2" s="47"/>
+      <c r="AZ2" s="47"/>
+      <c r="BA2" s="48"/>
     </row>
     <row r="3" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="49" t="s">
+      <c r="A3" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="49"/>
-      <c r="C3" s="49"/>
-      <c r="D3" s="49"/>
-      <c r="E3" s="49"/>
-      <c r="F3" s="49"/>
-      <c r="G3" s="49"/>
-      <c r="AI3" s="42" t="s">
+      <c r="B3" s="42"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="42"/>
+      <c r="AI3" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="AJ3" s="43"/>
-      <c r="AK3" s="43"/>
-      <c r="AL3" s="43"/>
-      <c r="AM3" s="43"/>
-      <c r="AN3" s="43"/>
-      <c r="AO3" s="44"/>
-      <c r="AU3" s="49" t="s">
+      <c r="AJ3" s="54"/>
+      <c r="AK3" s="54"/>
+      <c r="AL3" s="54"/>
+      <c r="AM3" s="54"/>
+      <c r="AN3" s="54"/>
+      <c r="AO3" s="55"/>
+      <c r="AU3" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="AV3" s="49"/>
-      <c r="AW3" s="49"/>
-      <c r="AX3" s="49"/>
-      <c r="AY3" s="49"/>
-      <c r="AZ3" s="49"/>
-      <c r="BA3" s="49"/>
+      <c r="AV3" s="42"/>
+      <c r="AW3" s="42"/>
+      <c r="AX3" s="42"/>
+      <c r="AY3" s="42"/>
+      <c r="AZ3" s="42"/>
+      <c r="BA3" s="42"/>
     </row>
     <row r="4" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
@@ -1642,15 +1642,15 @@
       <c r="G4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="42" t="s">
+      <c r="M4" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="N4" s="43"/>
-      <c r="O4" s="43"/>
-      <c r="P4" s="43"/>
-      <c r="Q4" s="43"/>
-      <c r="R4" s="43"/>
-      <c r="S4" s="44"/>
+      <c r="N4" s="54"/>
+      <c r="O4" s="54"/>
+      <c r="P4" s="54"/>
+      <c r="Q4" s="54"/>
+      <c r="R4" s="54"/>
+      <c r="S4" s="55"/>
       <c r="AI4" s="3" t="s">
         <v>2</v>
       </c>
@@ -1977,11 +1977,11 @@
       <c r="G8" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="I8" s="50" t="s">
+      <c r="I8" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="J8" s="50"/>
-      <c r="K8" s="50"/>
+      <c r="J8" s="43"/>
+      <c r="K8" s="43"/>
       <c r="M8" s="8">
         <v>3</v>
       </c>
@@ -2024,11 +2024,11 @@
       <c r="AO8" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="AQ8" s="50" t="s">
+      <c r="AQ8" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="AR8" s="50"/>
-      <c r="AS8" s="50"/>
+      <c r="AR8" s="43"/>
+      <c r="AS8" s="43"/>
       <c r="AU8" s="38">
         <v>4</v>
       </c>
@@ -2288,15 +2288,15 @@
       <c r="BA11" s="6"/>
     </row>
     <row r="12" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="49" t="s">
+      <c r="A12" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="49"/>
-      <c r="C12" s="49"/>
-      <c r="D12" s="49"/>
-      <c r="E12" s="49"/>
-      <c r="F12" s="49"/>
-      <c r="G12" s="49"/>
+      <c r="B12" s="42"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="42"/>
       <c r="L12" s="12"/>
       <c r="M12" s="8" t="s">
         <v>12</v>
@@ -2322,69 +2322,69 @@
       <c r="T12" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AI12" s="49" t="s">
+      <c r="AI12" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AJ12" s="49"/>
-      <c r="AK12" s="49"/>
-      <c r="AL12" s="49"/>
-      <c r="AM12" s="49"/>
-      <c r="AN12" s="49"/>
-      <c r="AO12" s="49"/>
+      <c r="AJ12" s="42"/>
+      <c r="AK12" s="42"/>
+      <c r="AL12" s="42"/>
+      <c r="AM12" s="42"/>
+      <c r="AN12" s="42"/>
+      <c r="AO12" s="42"/>
       <c r="AQ12" s="12"/>
-      <c r="AU12" s="49" t="s">
+      <c r="AU12" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AV12" s="49"/>
-      <c r="AW12" s="49"/>
-      <c r="AX12" s="49"/>
-      <c r="AY12" s="49"/>
-      <c r="AZ12" s="49"/>
-      <c r="BA12" s="49"/>
+      <c r="AV12" s="42"/>
+      <c r="AW12" s="42"/>
+      <c r="AX12" s="42"/>
+      <c r="AY12" s="42"/>
+      <c r="AZ12" s="42"/>
+      <c r="BA12" s="42"/>
     </row>
     <row r="13" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="L13" s="12"/>
-      <c r="M13" s="42" t="s">
+      <c r="M13" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="N13" s="43"/>
-      <c r="O13" s="43"/>
-      <c r="P13" s="43"/>
-      <c r="Q13" s="43"/>
-      <c r="R13" s="43"/>
-      <c r="S13" s="44"/>
+      <c r="N13" s="54"/>
+      <c r="O13" s="54"/>
+      <c r="P13" s="54"/>
+      <c r="Q13" s="54"/>
+      <c r="R13" s="54"/>
+      <c r="S13" s="55"/>
       <c r="AQ13" s="12"/>
     </row>
     <row r="14" spans="1:54" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="48" t="s">
+      <c r="A14" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="48"/>
-      <c r="C14" s="48"/>
-      <c r="D14" s="48"/>
-      <c r="E14" s="48"/>
-      <c r="F14" s="48"/>
-      <c r="G14" s="48"/>
-      <c r="L14" s="54" t="s">
+      <c r="B14" s="45"/>
+      <c r="C14" s="45"/>
+      <c r="D14" s="45"/>
+      <c r="E14" s="45"/>
+      <c r="F14" s="45"/>
+      <c r="G14" s="45"/>
+      <c r="L14" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="M14" s="50"/>
-      <c r="N14" s="50"/>
-      <c r="AN14" s="50" t="s">
+      <c r="M14" s="43"/>
+      <c r="N14" s="43"/>
+      <c r="AN14" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="AO14" s="50"/>
-      <c r="AP14" s="50"/>
+      <c r="AO14" s="43"/>
+      <c r="AP14" s="43"/>
       <c r="AQ14" s="12"/>
-      <c r="AU14" s="48" t="s">
+      <c r="AU14" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="AV14" s="48"/>
-      <c r="AW14" s="48"/>
-      <c r="AX14" s="48"/>
-      <c r="AY14" s="48"/>
-      <c r="AZ14" s="48"/>
-      <c r="BA14" s="48"/>
+      <c r="AV14" s="45"/>
+      <c r="AW14" s="45"/>
+      <c r="AX14" s="45"/>
+      <c r="AY14" s="45"/>
+      <c r="AZ14" s="45"/>
+      <c r="BA14" s="45"/>
     </row>
     <row r="15" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
@@ -2612,19 +2612,19 @@
       <c r="G19" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="I19" s="50" t="s">
+      <c r="I19" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="J19" s="50"/>
-      <c r="K19" s="50"/>
+      <c r="J19" s="43"/>
+      <c r="K19" s="43"/>
       <c r="L19" s="12"/>
       <c r="O19" s="12"/>
       <c r="AN19" s="12"/>
-      <c r="AQ19" s="54" t="s">
+      <c r="AQ19" s="44" t="s">
         <v>31</v>
       </c>
-      <c r="AR19" s="50"/>
-      <c r="AS19" s="50"/>
+      <c r="AR19" s="43"/>
+      <c r="AS19" s="43"/>
       <c r="AU19" s="38">
         <v>4</v>
       </c>
@@ -2786,52 +2786,52 @@
       <c r="BA22" s="6"/>
     </row>
     <row r="23" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="49" t="s">
+      <c r="A23" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B23" s="49"/>
-      <c r="C23" s="49"/>
-      <c r="D23" s="49"/>
-      <c r="E23" s="49"/>
-      <c r="F23" s="49"/>
-      <c r="G23" s="49"/>
+      <c r="B23" s="42"/>
+      <c r="C23" s="42"/>
+      <c r="D23" s="42"/>
+      <c r="E23" s="42"/>
+      <c r="F23" s="42"/>
+      <c r="G23" s="42"/>
       <c r="O23" s="12"/>
       <c r="AN23" s="12"/>
-      <c r="AU23" s="49" t="s">
+      <c r="AU23" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AV23" s="49"/>
-      <c r="AW23" s="49"/>
-      <c r="AX23" s="49"/>
-      <c r="AY23" s="49"/>
-      <c r="AZ23" s="49"/>
-      <c r="BA23" s="49"/>
+      <c r="AV23" s="42"/>
+      <c r="AW23" s="42"/>
+      <c r="AX23" s="42"/>
+      <c r="AY23" s="42"/>
+      <c r="AZ23" s="42"/>
+      <c r="BA23" s="42"/>
     </row>
     <row r="24" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="O24" s="12"/>
       <c r="AN24" s="12"/>
     </row>
     <row r="25" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="49" t="s">
+      <c r="A25" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="49"/>
-      <c r="C25" s="49"/>
-      <c r="D25" s="49"/>
-      <c r="E25" s="49"/>
-      <c r="F25" s="49"/>
-      <c r="G25" s="49"/>
+      <c r="B25" s="42"/>
+      <c r="C25" s="42"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="42"/>
+      <c r="F25" s="42"/>
+      <c r="G25" s="42"/>
       <c r="O25" s="12"/>
       <c r="AN25" s="12"/>
-      <c r="AU25" s="49" t="s">
+      <c r="AU25" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="AV25" s="49"/>
-      <c r="AW25" s="49"/>
-      <c r="AX25" s="49"/>
-      <c r="AY25" s="49"/>
-      <c r="AZ25" s="49"/>
-      <c r="BA25" s="49"/>
+      <c r="AV25" s="42"/>
+      <c r="AW25" s="42"/>
+      <c r="AX25" s="42"/>
+      <c r="AY25" s="42"/>
+      <c r="AZ25" s="42"/>
+      <c r="BA25" s="42"/>
     </row>
     <row r="26" spans="1:54" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A26" s="20" t="s">
@@ -2855,28 +2855,28 @@
       <c r="G26" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="O26" s="54" t="s">
+      <c r="O26" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="P26" s="50"/>
-      <c r="Q26" s="50"/>
-      <c r="R26" s="50"/>
-      <c r="S26" s="50"/>
-      <c r="T26" s="50"/>
-      <c r="U26" s="50"/>
-      <c r="V26" s="50"/>
-      <c r="W26" s="50"/>
-      <c r="AE26" s="50" t="s">
+      <c r="P26" s="43"/>
+      <c r="Q26" s="43"/>
+      <c r="R26" s="43"/>
+      <c r="S26" s="43"/>
+      <c r="T26" s="43"/>
+      <c r="U26" s="43"/>
+      <c r="V26" s="43"/>
+      <c r="W26" s="43"/>
+      <c r="AE26" s="43" t="s">
         <v>38</v>
       </c>
-      <c r="AF26" s="50"/>
-      <c r="AG26" s="50"/>
-      <c r="AH26" s="50"/>
-      <c r="AI26" s="50"/>
-      <c r="AJ26" s="50"/>
-      <c r="AK26" s="50"/>
-      <c r="AL26" s="50"/>
-      <c r="AM26" s="58"/>
+      <c r="AF26" s="43"/>
+      <c r="AG26" s="43"/>
+      <c r="AH26" s="43"/>
+      <c r="AI26" s="43"/>
+      <c r="AJ26" s="43"/>
+      <c r="AK26" s="43"/>
+      <c r="AL26" s="43"/>
+      <c r="AM26" s="49"/>
       <c r="AU26" s="20" t="s">
         <v>2</v>
       </c>
@@ -2973,26 +2973,26 @@
         <v>54</v>
       </c>
       <c r="O28" s="12"/>
-      <c r="P28" s="42" t="s">
+      <c r="P28" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="Q28" s="43"/>
-      <c r="R28" s="43"/>
-      <c r="S28" s="43"/>
-      <c r="T28" s="43"/>
-      <c r="U28" s="43"/>
-      <c r="V28" s="44"/>
+      <c r="Q28" s="54"/>
+      <c r="R28" s="54"/>
+      <c r="S28" s="54"/>
+      <c r="T28" s="54"/>
+      <c r="U28" s="54"/>
+      <c r="V28" s="55"/>
       <c r="X28" s="12"/>
       <c r="AD28" s="13"/>
-      <c r="AF28" s="49" t="s">
+      <c r="AF28" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="AG28" s="49"/>
-      <c r="AH28" s="49"/>
-      <c r="AI28" s="49"/>
-      <c r="AJ28" s="49"/>
-      <c r="AK28" s="49"/>
-      <c r="AL28" s="49"/>
+      <c r="AG28" s="42"/>
+      <c r="AH28" s="42"/>
+      <c r="AI28" s="42"/>
+      <c r="AJ28" s="42"/>
+      <c r="AK28" s="42"/>
+      <c r="AL28" s="42"/>
       <c r="AN28" s="12"/>
       <c r="AU28" s="8">
         <v>2</v>
@@ -3128,11 +3128,11 @@
       <c r="G30" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="I30" s="50" t="s">
+      <c r="I30" s="43" t="s">
         <v>26</v>
       </c>
-      <c r="J30" s="50"/>
-      <c r="K30" s="50"/>
+      <c r="J30" s="43"/>
+      <c r="K30" s="43"/>
       <c r="O30" s="12"/>
       <c r="P30" s="7">
         <v>1</v>
@@ -3179,11 +3179,11 @@
         <v>52</v>
       </c>
       <c r="AN30" s="12"/>
-      <c r="AQ30" s="50" t="s">
+      <c r="AQ30" s="43" t="s">
         <v>38</v>
       </c>
-      <c r="AR30" s="50"/>
-      <c r="AS30" s="50"/>
+      <c r="AR30" s="43"/>
+      <c r="AS30" s="43"/>
       <c r="AU30" s="38">
         <v>4</v>
       </c>
@@ -3470,15 +3470,15 @@
       <c r="BA33" s="6"/>
     </row>
     <row r="34" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="49" t="s">
+      <c r="A34" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B34" s="49"/>
-      <c r="C34" s="49"/>
-      <c r="D34" s="49"/>
-      <c r="E34" s="49"/>
-      <c r="F34" s="49"/>
-      <c r="G34" s="49"/>
+      <c r="B34" s="42"/>
+      <c r="C34" s="42"/>
+      <c r="D34" s="42"/>
+      <c r="E34" s="42"/>
+      <c r="F34" s="42"/>
+      <c r="G34" s="42"/>
       <c r="L34" s="12"/>
       <c r="O34" s="12"/>
       <c r="P34" s="8" t="s">
@@ -3521,15 +3521,15 @@
       <c r="AL34" s="16"/>
       <c r="AN34" s="12"/>
       <c r="AQ34" s="12"/>
-      <c r="AU34" s="49" t="s">
+      <c r="AU34" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AV34" s="49"/>
-      <c r="AW34" s="49"/>
-      <c r="AX34" s="49"/>
-      <c r="AY34" s="49"/>
-      <c r="AZ34" s="49"/>
-      <c r="BA34" s="49"/>
+      <c r="AV34" s="42"/>
+      <c r="AW34" s="42"/>
+      <c r="AX34" s="42"/>
+      <c r="AY34" s="42"/>
+      <c r="AZ34" s="42"/>
+      <c r="BA34" s="42"/>
     </row>
     <row r="35" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="L35" s="12"/>
@@ -3570,20 +3570,20 @@
       <c r="AQ35" s="12"/>
     </row>
     <row r="36" spans="1:54" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="48" t="s">
+      <c r="A36" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="B36" s="48"/>
-      <c r="C36" s="48"/>
-      <c r="D36" s="48"/>
-      <c r="E36" s="48"/>
-      <c r="F36" s="48"/>
-      <c r="G36" s="48"/>
-      <c r="L36" s="54" t="s">
+      <c r="B36" s="45"/>
+      <c r="C36" s="45"/>
+      <c r="D36" s="45"/>
+      <c r="E36" s="45"/>
+      <c r="F36" s="45"/>
+      <c r="G36" s="45"/>
+      <c r="L36" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="M36" s="50"/>
-      <c r="N36" s="50"/>
+      <c r="M36" s="43"/>
+      <c r="N36" s="43"/>
       <c r="O36" s="12"/>
       <c r="P36" s="8" t="s">
         <v>12</v>
@@ -3617,21 +3617,21 @@
       </c>
       <c r="AK36" s="36"/>
       <c r="AL36" s="37"/>
-      <c r="AN36" s="54" t="s">
+      <c r="AN36" s="44" t="s">
         <v>38</v>
       </c>
-      <c r="AO36" s="50"/>
-      <c r="AP36" s="50"/>
+      <c r="AO36" s="43"/>
+      <c r="AP36" s="43"/>
       <c r="AQ36" s="12"/>
-      <c r="AU36" s="48" t="s">
+      <c r="AU36" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="AV36" s="48"/>
-      <c r="AW36" s="48"/>
-      <c r="AX36" s="48"/>
-      <c r="AY36" s="48"/>
-      <c r="AZ36" s="48"/>
-      <c r="BA36" s="48"/>
+      <c r="AV36" s="45"/>
+      <c r="AW36" s="45"/>
+      <c r="AX36" s="45"/>
+      <c r="AY36" s="45"/>
+      <c r="AZ36" s="45"/>
+      <c r="BA36" s="45"/>
     </row>
     <row r="37" spans="1:54" ht="22.2" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A37" s="20" t="s">
@@ -3656,31 +3656,33 @@
         <v>9</v>
       </c>
       <c r="L37" s="12"/>
-      <c r="P37" s="45" t="s">
+      <c r="P37" s="56" t="s">
         <v>13</v>
       </c>
-      <c r="Q37" s="46"/>
-      <c r="R37" s="46"/>
-      <c r="S37" s="46"/>
-      <c r="T37" s="46"/>
-      <c r="U37" s="46"/>
-      <c r="V37" s="47"/>
-      <c r="X37" s="54"/>
-      <c r="Y37" s="50"/>
-      <c r="Z37" s="50"/>
-      <c r="AA37" s="50"/>
-      <c r="AB37" s="50"/>
-      <c r="AC37" s="50"/>
-      <c r="AD37" s="58"/>
-      <c r="AF37" s="49" t="s">
+      <c r="Q37" s="57"/>
+      <c r="R37" s="57"/>
+      <c r="S37" s="57"/>
+      <c r="T37" s="57"/>
+      <c r="U37" s="57"/>
+      <c r="V37" s="58"/>
+      <c r="X37" s="44" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y37" s="43"/>
+      <c r="Z37" s="43"/>
+      <c r="AA37" s="43"/>
+      <c r="AB37" s="43"/>
+      <c r="AC37" s="43"/>
+      <c r="AD37" s="49"/>
+      <c r="AF37" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AG37" s="49"/>
-      <c r="AH37" s="49"/>
-      <c r="AI37" s="49"/>
-      <c r="AJ37" s="49"/>
-      <c r="AK37" s="49"/>
-      <c r="AL37" s="49"/>
+      <c r="AG37" s="42"/>
+      <c r="AH37" s="42"/>
+      <c r="AI37" s="42"/>
+      <c r="AJ37" s="42"/>
+      <c r="AK37" s="42"/>
+      <c r="AL37" s="42"/>
       <c r="AQ37" s="12"/>
       <c r="AU37" s="3" t="s">
         <v>2</v>
@@ -3773,33 +3775,33 @@
         <v>53</v>
       </c>
       <c r="L39" s="12"/>
-      <c r="M39" s="42" t="s">
+      <c r="M39" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="N39" s="43"/>
-      <c r="O39" s="43"/>
-      <c r="P39" s="43"/>
-      <c r="Q39" s="43"/>
-      <c r="R39" s="43"/>
-      <c r="S39" s="44"/>
-      <c r="X39" s="49" t="s">
+      <c r="N39" s="54"/>
+      <c r="O39" s="54"/>
+      <c r="P39" s="54"/>
+      <c r="Q39" s="54"/>
+      <c r="R39" s="54"/>
+      <c r="S39" s="55"/>
+      <c r="X39" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="Y39" s="49"/>
-      <c r="Z39" s="49"/>
-      <c r="AA39" s="49"/>
-      <c r="AB39" s="49"/>
-      <c r="AC39" s="49"/>
-      <c r="AD39" s="49"/>
-      <c r="AI39" s="42" t="s">
+      <c r="Y39" s="42"/>
+      <c r="Z39" s="42"/>
+      <c r="AA39" s="42"/>
+      <c r="AB39" s="42"/>
+      <c r="AC39" s="42"/>
+      <c r="AD39" s="42"/>
+      <c r="AI39" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="AJ39" s="43"/>
-      <c r="AK39" s="43"/>
-      <c r="AL39" s="43"/>
-      <c r="AM39" s="43"/>
-      <c r="AN39" s="43"/>
-      <c r="AO39" s="44"/>
+      <c r="AJ39" s="54"/>
+      <c r="AK39" s="54"/>
+      <c r="AL39" s="54"/>
+      <c r="AM39" s="54"/>
+      <c r="AN39" s="54"/>
+      <c r="AO39" s="55"/>
       <c r="AQ39" s="12"/>
       <c r="AU39" s="8">
         <v>2</v>
@@ -3954,11 +3956,11 @@
       <c r="G41" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="I41" s="50" t="s">
+      <c r="I41" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="J41" s="50"/>
-      <c r="K41" s="50"/>
+      <c r="J41" s="43"/>
+      <c r="K41" s="43"/>
       <c r="L41" s="12"/>
       <c r="M41" s="7">
         <v>1</v>
@@ -4023,11 +4025,11 @@
       <c r="AO41" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="AQ41" s="54" t="s">
+      <c r="AQ41" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="AR41" s="50"/>
-      <c r="AS41" s="50"/>
+      <c r="AR41" s="43"/>
+      <c r="AS41" s="43"/>
       <c r="AU41" s="38">
         <v>4</v>
       </c>
@@ -4375,15 +4377,15 @@
       <c r="BA44" s="6"/>
     </row>
     <row r="45" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="49" t="s">
+      <c r="A45" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B45" s="49"/>
-      <c r="C45" s="49"/>
-      <c r="D45" s="49"/>
-      <c r="E45" s="49"/>
-      <c r="F45" s="49"/>
-      <c r="G45" s="49"/>
+      <c r="B45" s="42"/>
+      <c r="C45" s="42"/>
+      <c r="D45" s="42"/>
+      <c r="E45" s="42"/>
+      <c r="F45" s="42"/>
+      <c r="G45" s="42"/>
       <c r="M45" s="8" t="s">
         <v>11</v>
       </c>
@@ -4444,15 +4446,15 @@
       <c r="AP45" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AU45" s="49" t="s">
+      <c r="AU45" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AV45" s="49"/>
-      <c r="AW45" s="49"/>
-      <c r="AX45" s="49"/>
-      <c r="AY45" s="49"/>
-      <c r="AZ45" s="49"/>
-      <c r="BA45" s="49"/>
+      <c r="AV45" s="42"/>
+      <c r="AW45" s="42"/>
+      <c r="AX45" s="42"/>
+      <c r="AY45" s="42"/>
+      <c r="AZ45" s="42"/>
+      <c r="BA45" s="42"/>
     </row>
     <row r="46" spans="1:54" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="M46" s="8" t="s">
@@ -4561,49 +4563,61 @@
       <c r="AO47" s="6"/>
     </row>
     <row r="48" spans="1:54" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="M48" s="42" t="s">
+      <c r="M48" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="N48" s="43"/>
-      <c r="O48" s="43"/>
-      <c r="P48" s="43"/>
-      <c r="Q48" s="43"/>
-      <c r="R48" s="43"/>
-      <c r="S48" s="44"/>
-      <c r="X48" s="49" t="s">
+      <c r="N48" s="54"/>
+      <c r="O48" s="54"/>
+      <c r="P48" s="54"/>
+      <c r="Q48" s="54"/>
+      <c r="R48" s="54"/>
+      <c r="S48" s="55"/>
+      <c r="X48" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="Y48" s="49"/>
-      <c r="Z48" s="49"/>
-      <c r="AA48" s="49"/>
-      <c r="AB48" s="49"/>
-      <c r="AC48" s="49"/>
-      <c r="AD48" s="49"/>
-      <c r="AI48" s="49" t="s">
+      <c r="Y48" s="42"/>
+      <c r="Z48" s="42"/>
+      <c r="AA48" s="42"/>
+      <c r="AB48" s="42"/>
+      <c r="AC48" s="42"/>
+      <c r="AD48" s="42"/>
+      <c r="AI48" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="AJ48" s="49"/>
-      <c r="AK48" s="49"/>
-      <c r="AL48" s="49"/>
-      <c r="AM48" s="49"/>
-      <c r="AN48" s="49"/>
-      <c r="AO48" s="49"/>
+      <c r="AJ48" s="42"/>
+      <c r="AK48" s="42"/>
+      <c r="AL48" s="42"/>
+      <c r="AM48" s="42"/>
+      <c r="AN48" s="42"/>
+      <c r="AO48" s="42"/>
     </row>
     <row r="49" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="AU45:BA45"/>
-    <mergeCell ref="AF28:AL28"/>
-    <mergeCell ref="AF37:AL37"/>
-    <mergeCell ref="AQ30:AS30"/>
-    <mergeCell ref="AQ41:AS41"/>
-    <mergeCell ref="AU34:BA34"/>
-    <mergeCell ref="AU36:BA36"/>
-    <mergeCell ref="AU2:BA2"/>
-    <mergeCell ref="AU3:BA3"/>
-    <mergeCell ref="AU12:BA12"/>
-    <mergeCell ref="AU14:BA14"/>
-    <mergeCell ref="AU23:BA23"/>
+    <mergeCell ref="M48:S48"/>
+    <mergeCell ref="M39:S39"/>
+    <mergeCell ref="P37:V37"/>
+    <mergeCell ref="P28:V28"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A1:U1"/>
+    <mergeCell ref="O26:W26"/>
+    <mergeCell ref="I41:K41"/>
+    <mergeCell ref="L14:N14"/>
+    <mergeCell ref="L36:N36"/>
+    <mergeCell ref="M2:R2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="M4:S4"/>
+    <mergeCell ref="M13:S13"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="A25:G25"/>
     <mergeCell ref="X37:AD37"/>
     <mergeCell ref="AE26:AM26"/>
     <mergeCell ref="Z1:AB1"/>
@@ -4620,30 +4634,18 @@
     <mergeCell ref="AN36:AP36"/>
     <mergeCell ref="AQ8:AS8"/>
     <mergeCell ref="AQ19:AS19"/>
-    <mergeCell ref="A1:U1"/>
-    <mergeCell ref="O26:W26"/>
-    <mergeCell ref="I41:K41"/>
-    <mergeCell ref="L14:N14"/>
-    <mergeCell ref="L36:N36"/>
-    <mergeCell ref="M2:R2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="M4:S4"/>
-    <mergeCell ref="M13:S13"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A23:G23"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="M48:S48"/>
-    <mergeCell ref="M39:S39"/>
-    <mergeCell ref="P37:V37"/>
-    <mergeCell ref="P28:V28"/>
-    <mergeCell ref="A36:G36"/>
-    <mergeCell ref="A45:G45"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="AU2:BA2"/>
+    <mergeCell ref="AU3:BA3"/>
+    <mergeCell ref="AU12:BA12"/>
+    <mergeCell ref="AU14:BA14"/>
+    <mergeCell ref="AU23:BA23"/>
+    <mergeCell ref="AU45:BA45"/>
+    <mergeCell ref="AF28:AL28"/>
+    <mergeCell ref="AF37:AL37"/>
+    <mergeCell ref="AQ30:AS30"/>
+    <mergeCell ref="AQ41:AS41"/>
+    <mergeCell ref="AU34:BA34"/>
+    <mergeCell ref="AU36:BA36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
